--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -5,22 +5,23 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Music\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AED67B9A-8BE4-430E-9428-34B11194C8E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{290E4C99-13C6-44A3-A46F-AA074B3FCE9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="albums analysis" sheetId="1" r:id="rId1"/>
+    <sheet name="albums" sheetId="2" r:id="rId1"/>
+    <sheet name="tracks" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="67">
   <si>
     <t>Καλλιτέχνης</t>
   </si>
@@ -61,9 +62,6 @@
     <t>29 May 2026</t>
   </si>
   <si>
-    <t>#</t>
-  </si>
-  <si>
     <t>Red Rocking Chair</t>
   </si>
   <si>
@@ -94,9 +92,6 @@
     <t>Saturn Song</t>
   </si>
   <si>
-    <t>BMG – 964236001 (Apple Black Wave)</t>
-  </si>
-  <si>
     <t>Blues Rock, Psychedelic Rock</t>
   </si>
   <si>
@@ -127,9 +122,6 @@
     <t>Blues Rock, Stoner Rock, Psychedelic Rock</t>
   </si>
   <si>
-    <t>—</t>
-  </si>
-  <si>
     <t>Σκοτεινό, low-tempo ξεκίνημα με παραδοσιακό blues-rock χαρακτήρα και λασπωμένα fuzz περάσματα.</t>
   </si>
   <si>
@@ -160,14 +152,83 @@
     <t>Το απόλυτο space/doom blues έπος του άλμπουμ. Ένα μακροσκελές, ελεύθερο jam με τεράστιο dynamic range, όπου η μπάντα αφήνεται σε ένα ψυχεδελικό κρεσέντο γεμάτο αναλογικό feedback.</t>
   </si>
   <si>
-    <t>Α) Ιστορικό Πλαίσιο &amp; Παραγωγή: Το «House Of Mirrors» (2026, BMG) επισφραγίζει την ωριμότητα των All Them Witches ως power trio. Η ηχογράφηση πραγματοποιήθηκε με live-in-the-studio φιλοσοφία, αποφεύγοντας τα πολλαπλά ψηφιακά overdubs και το brickwall compression. Η παραγωγή εστιάζει στην αναλογική ζεστασιά και τη διατήρηση του headroom. Η μουσική κατεύθυνση ισορροπεί με χειρουργική ακρίβεια ανάμεσα στο raw stoner rock, το βαρύ ψυχεδελικό blues και το space rock, καθιστώντας την έκδοση βινυλίου «Apple Black Wave» ιδανική για όσους αναζητούν ρεαλιστικές δυναμικές και φυσικό soundstage. | Hard Facts: Plating: GZ Media (315212E). Pressing: PRP Canada (10-117456). Lead-in τάφος (ήσυχο), οκ.</t>
+    <t>Album_ID</t>
+  </si>
+  <si>
+    <t>Death</t>
+  </si>
+  <si>
+    <t>Proto-Punk, Garage Rock</t>
+  </si>
+  <si>
+    <t>...For The Whole World To See</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Ηχογραφήθηκε το 1975 στα United Sound Systems του Detroit και παρέμεινε θαμμένο για δεκαετίες. Μια απίστευτη έκρηξη καταιγιστικού proto-punk από τρία αφροαμερικάνικα αδέρφια. Ωμή, αναλογική παραγωγή με επιθετικές κιθάρες. **\| Hard Facts Έκδοσης Βινυλίου:** Drag City (DC386). Pressing: RTI, εξαιρετική, καθαρή κοπή. Lead-in τάφος (ήσυχο), δυναμικές στο κόκκινο χωρίς ψηφιακή συμπίεση.</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το «House Of Mirrors» (2026, BMG) επισφραγίζει την ωριμότητα των All Them Witches ως power trio. Η ηχογράφηση πραγματοποιήθηκε με live-in-the-studio φιλοσοφία, αποφεύγοντας τα πολλαπλά ψηφιακά overdubs και το brickwall compression. Η παραγωγή εστιάζει στην αναλογική ζεστασιά και τη διατήρηση του headroom. Η μουσική κατεύθυνση ισορροπεί με χειρουργική ακρίβεια ανάμεσα στο raw stoner rock, το βαρύ ψυχεδελικό blues και το space rock, καθιστώντας την έκδοση βινυλίου «Apple Black Wave» ιδανική για όσους αναζητούν ρεαλιστικές δυναμικές και φυσικό soundstage. | Hard Facts: Plating: GZ Media (315212E). Pressing: PRP Canada (10-117456). Lead-in τάφος (ήσυχο), οκ.</t>
+  </si>
+  <si>
+    <t>Keep On Knocking</t>
+  </si>
+  <si>
+    <t>Proto-Punk</t>
+  </si>
+  <si>
+    <t>Rock-N-Roll Victim</t>
+  </si>
+  <si>
+    <t>You're A Prisoner</t>
+  </si>
+  <si>
+    <t>Where Do We Go From Here?</t>
+  </si>
+  <si>
+    <t>Proto-Punk, Power Pop</t>
+  </si>
+  <si>
+    <t>Freakin Out</t>
+  </si>
+  <si>
+    <t>Let The World Turn</t>
+  </si>
+  <si>
+    <t>Proto-Punk, Psychedelic Rock</t>
+  </si>
+  <si>
+    <t>Proto-Punk, Hard Rock</t>
+  </si>
+  <si>
+    <t>Politicians In My Eyes</t>
+  </si>
+  <si>
+    <t>Εκρηκτική εισαγωγή με καταιγιστικά τύμπανα που ορίζουν την ταχύτητα του επερχόμενου punk κινήματος, χρόνια πριν από την εμφάνισή του στην Αγγλία.</t>
+  </si>
+  <si>
+    <t>Ένα από τα πιο επιθετικά κομμάτια του δίσκου. Τα γρήγορα riffs της κιθάρας του David Hackney συνδυάζονται άψογα με τα ωμά φωνητικά, δημιουργώντας έναν καθαρό proto-punk δυναμίτη.</t>
+  </si>
+  <si>
+    <t>Μια πιο experimental και ψυχεδελική προσέγγιση. Είναι το μεγαλύτερο σε διάρκεια κομμάτι της πρώτης πλευράς, δίνοντας χώρο στα όργανα να αναπνεύσουν και αναδεικνύοντας το layering της αρχικής ηχογράφησης.</t>
+  </si>
+  <si>
+    <t>Χαρακτηρίζεται από έντονα hard rock riff και στίχους κοινωνικής απομόνωσης. Η κιθάρα κυριαρχεί στο στερεοφωνικό πεδίο κλείνοντας ιδανικά την A πλευρά.</t>
+  </si>
+  <si>
+    <t>Σύντομο, γρήγορο και straight-to-the-point κομμάτι που βασίζεται σε ένα απλό αλλά εθιστικό riff, προάγγελος της garage αναβίωσης.</t>
+  </si>
+  <si>
+    <t>Δείχνει την ικανότητα της μπάντας να γράφει mid-tempo ρυθμούς με pop ευαισθησίες, χωρίς να χάνει την αιχμηρότητά της.</t>
+  </si>
+  <si>
+    <t>Το αδιαμφισβήτητο highlight του άλμπουμ που κλείνει τον δίσκο. Ένα πολιτικοποιημένο έπος με συγκλονιστική αλλαγή ρυθμού στο pre-chorus, επιθετικά φωνητικά και ένα extended κιθαριστικό σόλο γεμάτο feedback.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -190,16 +251,8 @@
       <family val="2"/>
       <charset val="161"/>
     </font>
-    <font>
-      <i/>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-      <charset val="161"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -221,12 +274,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6F2FF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -258,25 +305,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -284,23 +319,11 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -308,8 +331,20 @@
     <xf numFmtId="2" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -614,404 +649,576 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="38.85546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="96.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="63" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>964236001</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="3">
+        <v>3.37</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="42" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>1739129</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="4">
+        <v>2009</v>
+      </c>
+      <c r="E3" s="4">
+        <v>3.82</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="13.140625" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.140625" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.28515625" style="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29.28515625" style="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.28515625" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.5703125" style="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.7109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="50.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.7109375" style="11" customWidth="1"/>
+    <col min="2" max="2" width="3.7109375" style="12" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" style="13" customWidth="1"/>
+    <col min="4" max="4" width="29.7109375" style="13" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" style="12" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" style="12" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="65.7109375" style="11" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>964236001</v>
+      </c>
+      <c r="B2" s="3">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="7">
+        <v>3.94</v>
+      </c>
+      <c r="F2" s="7">
+        <v>4</v>
+      </c>
+      <c r="G2" s="7">
+        <v>4.2</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>964236001</v>
+      </c>
+      <c r="B3" s="4">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="C3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="8">
+        <v>3.81</v>
+      </c>
+      <c r="F3" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="G3" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>964236001</v>
+      </c>
+      <c r="B4" s="3">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="C4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="7">
+        <v>3.57</v>
+      </c>
+      <c r="F4" s="7">
+        <v>3.9</v>
+      </c>
+      <c r="G4" s="7">
+        <v>4.3</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <v>964236001</v>
+      </c>
+      <c r="B5" s="4">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="C5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="8">
+        <v>3.71</v>
+      </c>
+      <c r="F5" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="G5" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>964236001</v>
+      </c>
+      <c r="B6" s="3">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="C6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="7">
+        <v>3.48</v>
+      </c>
+      <c r="F6" s="7">
+        <v>3.7</v>
+      </c>
+      <c r="G6" s="7">
+        <v>4</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>964236001</v>
+      </c>
+      <c r="B7" s="4">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="C7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="8">
+        <v>3.78</v>
+      </c>
+      <c r="F7" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G7" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>964236001</v>
+      </c>
+      <c r="B8" s="3">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="C8" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="7">
+        <v>3.39</v>
+      </c>
+      <c r="F8" s="7">
+        <v>4.2</v>
+      </c>
+      <c r="G8" s="7">
+        <v>4.2</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <v>964236001</v>
+      </c>
+      <c r="B9" s="4">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="C9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="8">
+        <v>3.54</v>
+      </c>
+      <c r="F9" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G9" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>964236001</v>
+      </c>
+      <c r="B10" s="3">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="21" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+      <c r="C10" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="7">
+        <v>3.66</v>
+      </c>
+      <c r="F10" s="7">
+        <v>3.8</v>
+      </c>
+      <c r="G10" s="7">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <v>964236001</v>
+      </c>
+      <c r="B11" s="4">
         <v>10</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D2" s="7">
+      <c r="C11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="8">
+        <v>3.68</v>
+      </c>
+      <c r="F11" s="8">
+        <v>4.7</v>
+      </c>
+      <c r="G11" s="8">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>1739129</v>
+      </c>
+      <c r="B12" s="3">
         <v>1</v>
       </c>
-      <c r="E2" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" s="15">
-        <v>3.94</v>
-      </c>
-      <c r="H2" s="15">
+      <c r="C12" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="7">
+        <v>4.22</v>
+      </c>
+      <c r="F12" s="7">
+        <v>4.2</v>
+      </c>
+      <c r="G12" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
+        <v>1739129</v>
+      </c>
+      <c r="B13" s="4">
+        <v>2</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" s="8">
+        <v>3.96</v>
+      </c>
+      <c r="F13" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G13" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <v>1739129</v>
+      </c>
+      <c r="B14" s="3">
+        <v>3</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" s="7">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="F14" s="7">
         <v>4</v>
       </c>
-      <c r="I2" s="15">
-        <v>4.2</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="21" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="8">
-        <v>2026</v>
-      </c>
-      <c r="D3" s="8">
-        <v>2</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="16">
-        <v>3.81</v>
-      </c>
-      <c r="H3" s="16">
-        <v>4.2</v>
-      </c>
-      <c r="I3" s="16">
-        <v>4.5</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="21" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D4" s="7">
-        <v>3</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" s="15">
-        <v>3.57</v>
-      </c>
-      <c r="H4" s="15">
+      <c r="G14" s="7">
+        <v>4</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
+        <v>1739129</v>
+      </c>
+      <c r="B15" s="4">
+        <v>4</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" s="8">
+        <v>3.83</v>
+      </c>
+      <c r="F15" s="8">
+        <v>4</v>
+      </c>
+      <c r="G15" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
+        <v>1739129</v>
+      </c>
+      <c r="B16" s="3">
+        <v>5</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="7">
         <v>3.9</v>
       </c>
-      <c r="I4" s="15">
+      <c r="F16" s="7">
         <v>4.3</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="21" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="8">
-        <v>2026</v>
-      </c>
-      <c r="D5" s="8">
-        <v>4</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" s="16">
-        <v>3.71</v>
-      </c>
-      <c r="H5" s="16">
-        <v>4.5</v>
-      </c>
-      <c r="I5" s="16">
+      <c r="G16" s="7">
+        <v>3.7</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
+        <v>1739129</v>
+      </c>
+      <c r="B17" s="4">
+        <v>6</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E17" s="8">
+        <v>3.93</v>
+      </c>
+      <c r="F17" s="8">
         <v>4.0999999999999996</v>
       </c>
-      <c r="J5" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="21" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D6" s="7">
-        <v>5</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="15">
-        <v>3.48</v>
-      </c>
-      <c r="H6" s="15">
-        <v>3.7</v>
-      </c>
-      <c r="I6" s="15">
-        <v>4</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="21" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="8">
-        <v>2026</v>
-      </c>
-      <c r="D7" s="8">
-        <v>6</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="16">
-        <v>3.78</v>
-      </c>
-      <c r="H7" s="16">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="I7" s="16">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="21" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D8" s="7">
+      <c r="G17" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
+        <v>1739129</v>
+      </c>
+      <c r="B18" s="3">
         <v>7</v>
       </c>
-      <c r="E8" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="15">
-        <v>3.39</v>
-      </c>
-      <c r="H8" s="15">
-        <v>4.2</v>
-      </c>
-      <c r="I8" s="15">
-        <v>4.2</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="21" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="8">
-        <v>2026</v>
-      </c>
-      <c r="D9" s="8">
-        <v>8</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="G9" s="16">
-        <v>3.54</v>
-      </c>
-      <c r="H9" s="16">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="I9" s="16">
-        <v>4.5</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="21" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D10" s="7">
-        <v>9</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" s="15">
-        <v>3.66</v>
-      </c>
-      <c r="H10" s="15">
-        <v>3.8</v>
-      </c>
-      <c r="I10" s="15">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="8">
-        <v>2026</v>
-      </c>
-      <c r="D11" s="8">
-        <v>10</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="G11" s="16">
-        <v>3.68</v>
-      </c>
-      <c r="H11" s="16">
-        <v>4.7</v>
-      </c>
-      <c r="I11" s="16">
+      <c r="C18" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18" s="7">
+        <v>4.43</v>
+      </c>
+      <c r="F18" s="7">
         <v>4.9000000000000004</v>
       </c>
-      <c r="J11" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="126" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="G12" s="17">
-        <v>3.37</v>
-      </c>
-      <c r="H12" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="I12" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>46</v>
+      <c r="G18" s="7">
+        <v>3.9</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{290E4C99-13C6-44A3-A46F-AA074B3FCE9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B211DA75-B38A-4B6E-BD5B-859EF1B4994B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -203,25 +203,25 @@
     <t>Politicians In My Eyes</t>
   </si>
   <si>
-    <t>Εκρηκτική εισαγωγή με καταιγιστικά τύμπανα που ορίζουν την ταχύτητα του επερχόμενου punk κινήματος, χρόνια πριν από την εμφάνισή του στην Αγγλία.</t>
-  </si>
-  <si>
-    <t>Ένα από τα πιο επιθετικά κομμάτια του δίσκου. Τα γρήγορα riffs της κιθάρας του David Hackney συνδυάζονται άψογα με τα ωμά φωνητικά, δημιουργώντας έναν καθαρό proto-punk δυναμίτη.</t>
-  </si>
-  <si>
-    <t>Μια πιο experimental και ψυχεδελική προσέγγιση. Είναι το μεγαλύτερο σε διάρκεια κομμάτι της πρώτης πλευράς, δίνοντας χώρο στα όργανα να αναπνεύσουν και αναδεικνύοντας το layering της αρχικής ηχογράφησης.</t>
-  </si>
-  <si>
-    <t>Χαρακτηρίζεται από έντονα hard rock riff και στίχους κοινωνικής απομόνωσης. Η κιθάρα κυριαρχεί στο στερεοφωνικό πεδίο κλείνοντας ιδανικά την A πλευρά.</t>
-  </si>
-  <si>
-    <t>Σύντομο, γρήγορο και straight-to-the-point κομμάτι που βασίζεται σε ένα απλό αλλά εθιστικό riff, προάγγελος της garage αναβίωσης.</t>
-  </si>
-  <si>
-    <t>Δείχνει την ικανότητα της μπάντας να γράφει mid-tempo ρυθμούς με pop ευαισθησίες, χωρίς να χάνει την αιχμηρότητά της.</t>
-  </si>
-  <si>
-    <t>Το αδιαμφισβήτητο highlight του άλμπουμ που κλείνει τον δίσκο. Ένα πολιτικοποιημένο έπος με συγκλονιστική αλλαγή ρυθμού στο pre-chorus, επιθετικά φωνητικά και ένα extended κιθαριστικό σόλο γεμάτο feedback.</t>
+    <t>Δίνει τον ρυθμό του δίσκου με ευθύτητα, χωρίς όμως συνθετικές εξάρσεις.</t>
+  </si>
+  <si>
+    <t>Παραμένει σε ρηχά, τυπικά garage rock νερά, χωρίς να παρουσιάζει δομική εξέλιξη.</t>
+  </si>
+  <si>
+    <t>Η μεγάλη έκπληξη του δίσκου. Η πολυπλοκότητα των τυμπάνων και το layering των κιθάρων το καθιστούν το πιο ολοκληρωμένο και ηχητικά ενδιαφέρον κομμάτι της πρώτης πλευράς.</t>
+  </si>
+  <si>
+    <t>Ένα κομμάτι που γεμίζει τη ροή του δίσκου χωρίς να διεκδικεί δάφνες πρωτοτυπίας.</t>
+  </si>
+  <si>
+    <t>Αντισταθμίζει τη συνθετική απλότητα με ωμή, punk ενέργεια.</t>
+  </si>
+  <si>
+    <t>Ξεχωρίζει για την καθαρή του ατμόσφαιρα, αν και συνθετικά δεν αγγίζει την κορυφή.</t>
+  </si>
+  <si>
+    <t>Ένα αντικειμενικό αριστούργημα (5.0/5) που δικαιώνει τη φήμη του. Η δομή, το riff και η ρυθμική εναλλαγή στο pre-chorus το τοποθετούν στην κορυφή του είδους, ανεξάρτητα από κάθε ιστορικό μύθο.</t>
   </si>
 </sst>
 </file>
@@ -749,7 +749,7 @@
     <col min="5" max="5" width="10.7109375" style="12" customWidth="1"/>
     <col min="6" max="6" width="17.7109375" style="12" customWidth="1"/>
     <col min="7" max="7" width="16.7109375" style="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="65.7109375" style="11" customWidth="1"/>
+    <col min="8" max="8" width="50.7109375" style="11" customWidth="1"/>
     <col min="9" max="16384" width="9.140625" style="11"/>
   </cols>
   <sheetData>
@@ -1059,13 +1059,13 @@
         <v>4.2</v>
       </c>
       <c r="G12" s="7">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="21" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>1739129</v>
       </c>
@@ -1082,7 +1082,7 @@
         <v>3.96</v>
       </c>
       <c r="F13" s="8">
-        <v>4.4000000000000004</v>
+        <v>3.6</v>
       </c>
       <c r="G13" s="8">
         <v>3.6</v>
@@ -1108,10 +1108,10 @@
         <v>4.0199999999999996</v>
       </c>
       <c r="F14" s="7">
-        <v>4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="G14" s="7">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>62</v>
@@ -1134,7 +1134,7 @@
         <v>3.83</v>
       </c>
       <c r="F15" s="8">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="G15" s="8">
         <v>3.6</v>
@@ -1143,7 +1143,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>1739129</v>
       </c>
@@ -1160,10 +1160,10 @@
         <v>3.9</v>
       </c>
       <c r="F16" s="7">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="G16" s="7">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>64</v>
@@ -1186,10 +1186,10 @@
         <v>3.93</v>
       </c>
       <c r="F17" s="8">
-        <v>4.0999999999999996</v>
+        <v>3.7</v>
       </c>
       <c r="G17" s="8">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>65</v>
@@ -1212,10 +1212,10 @@
         <v>4.43</v>
       </c>
       <c r="F18" s="7">
-        <v>4.9000000000000004</v>
+        <v>5</v>
       </c>
       <c r="G18" s="7">
-        <v>3.9</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>66</v>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B211DA75-B38A-4B6E-BD5B-859EF1B4994B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54D0B397-FA44-4ED6-96DB-0E1DBB46484B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54D0B397-FA44-4ED6-96DB-0E1DBB46484B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29345BB6-A85A-42BE-857A-F4D30033B3AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -723,7 +723,7 @@
         <v>2009</v>
       </c>
       <c r="E3" s="4">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>45</v>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29345BB6-A85A-42BE-857A-F4D30033B3AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{681FDFE8-2325-4428-9399-303B620DEB06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -21,38 +21,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="67">
-  <si>
-    <t>Καλλιτέχνης</t>
-  </si>
-  <si>
-    <t>Άλμπουμ</t>
-  </si>
-  <si>
-    <t>Έτος Κυκλοφορίας</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="69">
   <si>
     <t>No</t>
   </si>
   <si>
-    <t>Track / Έκδοση</t>
-  </si>
-  <si>
-    <t>Genres / Subgenres</t>
-  </si>
-  <si>
-    <t>RYM Rating</t>
-  </si>
-  <si>
-    <t>Compositional Value</t>
-  </si>
-  <si>
-    <t>Audiophile Interest</t>
-  </si>
-  <si>
-    <t>Σημειώσεις / Hard Facts</t>
-  </si>
-  <si>
     <t>All Them Witches</t>
   </si>
   <si>
@@ -222,6 +195,39 @@
   </si>
   <si>
     <t>Ένα αντικειμενικό αριστούργημα (5.0/5) που δικαιώνει τη φήμη του. Η δομή, το riff και η ρυθμική εναλλαγή στο pre-chorus το τοποθετούν στην κορυφή του είδους, ανεξάρτητα από κάθε ιστορικό μύθο.</t>
+  </si>
+  <si>
+    <t>Artist</t>
+  </si>
+  <si>
+    <t>Album</t>
+  </si>
+  <si>
+    <t>Release_Year</t>
+  </si>
+  <si>
+    <t>RYM_Rating</t>
+  </si>
+  <si>
+    <t>Genres_Subgenres</t>
+  </si>
+  <si>
+    <t>Notes_Hard_Facts</t>
+  </si>
+  <si>
+    <t>Label_Pressing</t>
+  </si>
+  <si>
+    <t>Discogs_URL</t>
+  </si>
+  <si>
+    <t>Track_Title</t>
+  </si>
+  <si>
+    <t>Compositional_Value</t>
+  </si>
+  <si>
+    <t>Audiophile_Interest</t>
   </si>
 </sst>
 </file>
@@ -650,7 +656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="9" bestFit="1" customWidth="1"/>
@@ -660,64 +666,72 @@
     <col min="5" max="5" width="10.85546875" style="9" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38.85546875" style="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="96.28515625" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="9"/>
+    <col min="8" max="8" width="13.7109375" style="9" customWidth="1"/>
+    <col min="9" max="9" width="11.7109375" style="9" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="63" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="63" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>964236001</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E2" s="3">
         <v>3.37</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="42" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>1739129</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D3" s="4">
         <v>2009</v>
@@ -726,10 +740,10 @@
         <v>3.78</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -746,37 +760,37 @@
     <col min="2" max="2" width="3.7109375" style="12" customWidth="1"/>
     <col min="3" max="3" width="28.7109375" style="13" customWidth="1"/>
     <col min="4" max="4" width="29.7109375" style="13" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" style="12" customWidth="1"/>
-    <col min="6" max="6" width="17.7109375" style="12" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" style="12" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" style="12" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" style="12" customWidth="1"/>
     <col min="8" max="8" width="50.7109375" style="11" customWidth="1"/>
     <col min="9" max="16384" width="9.140625" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>7</v>
+        <v>67</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>9</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -787,10 +801,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E2" s="7">
         <v>3.94</v>
@@ -802,7 +816,7 @@
         <v>4.2</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -813,10 +827,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E3" s="8">
         <v>3.81</v>
@@ -828,7 +842,7 @@
         <v>4.5</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -839,10 +853,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E4" s="7">
         <v>3.57</v>
@@ -854,7 +868,7 @@
         <v>4.3</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -865,10 +879,10 @@
         <v>4</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E5" s="8">
         <v>3.71</v>
@@ -880,7 +894,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -891,10 +905,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E6" s="7">
         <v>3.48</v>
@@ -906,7 +920,7 @@
         <v>4</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -917,10 +931,10 @@
         <v>6</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E7" s="8">
         <v>3.78</v>
@@ -932,7 +946,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -943,10 +957,10 @@
         <v>7</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E8" s="7">
         <v>3.39</v>
@@ -958,7 +972,7 @@
         <v>4.2</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -969,10 +983,10 @@
         <v>8</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E9" s="8">
         <v>3.54</v>
@@ -984,7 +998,7 @@
         <v>4.5</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -995,10 +1009,10 @@
         <v>9</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E10" s="7">
         <v>3.66</v>
@@ -1010,7 +1024,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
@@ -1021,10 +1035,10 @@
         <v>10</v>
       </c>
       <c r="C11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>31</v>
       </c>
       <c r="E11" s="8">
         <v>3.68</v>
@@ -1036,7 +1050,7 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -1047,10 +1061,10 @@
         <v>1</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E12" s="7">
         <v>4.22</v>
@@ -1062,7 +1076,7 @@
         <v>3.8</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -1073,10 +1087,10 @@
         <v>2</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E13" s="8">
         <v>3.96</v>
@@ -1088,7 +1102,7 @@
         <v>3.6</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
@@ -1099,10 +1113,10 @@
         <v>3</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="E14" s="7">
         <v>4.0199999999999996</v>
@@ -1114,7 +1128,7 @@
         <v>4.3</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -1125,10 +1139,10 @@
         <v>4</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E15" s="8">
         <v>3.83</v>
@@ -1140,7 +1154,7 @@
         <v>3.6</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1151,10 +1165,10 @@
         <v>5</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E16" s="7">
         <v>3.9</v>
@@ -1166,7 +1180,7 @@
         <v>3.8</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -1177,10 +1191,10 @@
         <v>6</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E17" s="8">
         <v>3.93</v>
@@ -1192,7 +1206,7 @@
         <v>4</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
@@ -1203,10 +1217,10 @@
         <v>7</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="E18" s="7">
         <v>4.43</v>
@@ -1218,7 +1232,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{681FDFE8-2325-4428-9399-303B620DEB06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01AC4421-50B2-40A9-BDAA-1603C7736D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="73">
   <si>
     <t>No</t>
   </si>
@@ -228,6 +228,18 @@
   </si>
   <si>
     <t>Audiophile_Interest</t>
+  </si>
+  <si>
+    <t>BMG (Apple Black Wave Edition)</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/1739129-Death-For-The-Whole-World-To-See</t>
+  </si>
+  <si>
+    <t>Drag City (DC386 / RTI Pressing)</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/37467900-All-Them-Witches-House-Of-Mirrors</t>
   </si>
 </sst>
 </file>
@@ -666,12 +678,12 @@
     <col min="5" max="5" width="10.85546875" style="9" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38.85546875" style="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="96.28515625" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.7109375" style="9" customWidth="1"/>
-    <col min="9" max="9" width="11.7109375" style="9" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="9" customWidth="1"/>
+    <col min="9" max="9" width="35.7109375" style="9" customWidth="1"/>
     <col min="10" max="16384" width="9.140625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>34</v>
       </c>
@@ -722,6 +734,12 @@
       <c r="G2" s="5" t="s">
         <v>39</v>
       </c>
+      <c r="H2" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="3" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
@@ -745,8 +763,17 @@
       <c r="G3" s="6" t="s">
         <v>38</v>
       </c>
+      <c r="H3" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>70</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I3" r:id="rId1" xr:uid="{9C0994CE-C554-4210-BCA2-17F8D17FB784}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01AC4421-50B2-40A9-BDAA-1603C7736D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D21E96A1-464A-46D9-85F9-4CDEBBDBCD9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="76">
   <si>
     <t>No</t>
   </si>
@@ -240,6 +240,15 @@
   </si>
   <si>
     <t>https://www.discogs.com/release/37467900-All-Them-Witches-House-Of-Mirrors</t>
+  </si>
+  <si>
+    <t>Image_URL</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/BbR8IssROc2VvmbpG4dyp5vmRby-YwTpbCZdbxVxhc4/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTM3NDY3/OTAwLTE3Nzk5ODEw/MzUtMTMwMC5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/LWBxYXcvqgEKOA_k5wMSIQW2IMzjgmISwNiS-cvq8Kg/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTE3Mzkx/MjktMTI0MDYyMTg3/MC5qcGVn.jpeg</t>
   </si>
 </sst>
 </file>
@@ -668,7 +677,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="9" bestFit="1" customWidth="1"/>
@@ -680,10 +689,11 @@
     <col min="7" max="7" width="96.28515625" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.7109375" style="9" customWidth="1"/>
     <col min="9" max="9" width="35.7109375" style="9" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="9"/>
+    <col min="10" max="10" width="50.42578125" style="9" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>34</v>
       </c>
@@ -711,8 +721,11 @@
       <c r="I1" s="10" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="J1" s="10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="63" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>964236001</v>
       </c>
@@ -740,8 +753,11 @@
       <c r="I2" s="1" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="J2" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="42" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>1739129</v>
       </c>
@@ -768,11 +784,16 @@
       </c>
       <c r="I3" s="2" t="s">
         <v>70</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="I3" r:id="rId1" xr:uid="{9C0994CE-C554-4210-BCA2-17F8D17FB784}"/>
+    <hyperlink ref="J2" r:id="rId2" xr:uid="{AD58B770-BB72-48BD-AE29-27E61830C8AC}"/>
+    <hyperlink ref="J3" r:id="rId3" xr:uid="{A295F22A-5B8A-48C2-8ADD-A473C972D75C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D21E96A1-464A-46D9-85F9-4CDEBBDBCD9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBB13364-97DD-42C7-AFFA-7C169503BC81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,12 +16,12 @@
     <sheet name="albums" sheetId="2" r:id="rId1"/>
     <sheet name="tracks" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="115">
   <si>
     <t>No</t>
   </si>
@@ -249,13 +249,130 @@
   </si>
   <si>
     <t>https://i.discogs.com/LWBxYXcvqgEKOA_k5wMSIQW2IMzjgmISwNiS-cvq8Kg/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTE3Mzkx/MjktMTI0MDYyMTg3/MC5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/37452171-Joey-Qui%C3%B1ones-Inna-Soul-Steady-Situation</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/PiZxtCiprVTcEdhAFdqb4wuu_rnBMzCXBwuN-XguZe8/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTM3NDUy/MTcxLTE3ODA3NTk4/OTMtMTUzMS5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το «Inna Soul Steady Situation» (2026, Colemine) αποτελεί μια υποδειγματική γέφυρα ανάμεσα στο 60s/70s Rocksteady και το Chicano/Sweet Soul. Αναλογική φιλοσοφία παραγωγής με πλούσιο headroom και ευρύ, ζεστό soundstage. | Hard Facts: Mastering/Cutting: Well Made Music. Pressing: RTI. Ήσυχο lead-in groove, κορυφαία αναλογική ζεστασιά και φυσικό low-end.</t>
+  </si>
+  <si>
+    <t>Colemine Records (US Orange Vinyl First Pressing)</t>
+  </si>
+  <si>
+    <t>Reggae, Funk / Soul, Chicano Soul, Rocksteady</t>
+  </si>
+  <si>
+    <t>Inna Soul Steady Situation</t>
+  </si>
+  <si>
+    <t>Guess That's Just Loving You</t>
+  </si>
+  <si>
+    <t>There Must Be Something</t>
+  </si>
+  <si>
+    <t>Don't Let Go</t>
+  </si>
+  <si>
+    <t>In My Arms</t>
+  </si>
+  <si>
+    <t>For You</t>
+  </si>
+  <si>
+    <t>Driftin'</t>
+  </si>
+  <si>
+    <t>Don't Be Late</t>
+  </si>
+  <si>
+    <t>Bolsita</t>
+  </si>
+  <si>
+    <t>One More Night</t>
+  </si>
+  <si>
+    <t>Situation 2</t>
+  </si>
+  <si>
+    <t>Rocksteady, Chicano Soul</t>
+  </si>
+  <si>
+    <t>Brown-Eyed Soul, Souldies</t>
+  </si>
+  <si>
+    <t>Lowrider Soul, Sweet Soul</t>
+  </si>
+  <si>
+    <t>Dreamy Soul</t>
+  </si>
+  <si>
+    <t>Sweet Soul</t>
+  </si>
+  <si>
+    <t>Roots Reggae, Rocksteady</t>
+  </si>
+  <si>
+    <t>Melancholic R&amp;B, Soul</t>
+  </si>
+  <si>
+    <t>Ska Revival, Rocksteady</t>
+  </si>
+  <si>
+    <t>Latin Soul, Chicano Soul</t>
+  </si>
+  <si>
+    <t>Teen-Soul, Souldies</t>
+  </si>
+  <si>
+    <t>Instrumental Outro, Rocksteady</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>Ιδανικό άνοιγμα με σφιχτό rocksteady ρυθμό και κρυστάλλινο διαχωρισμό στα όργανα. Στιβαρό, καθαρό analog session, αλλά αφήνει περιθώριο για τη συνέχεια.</t>
+  </si>
+  <si>
+    <t>Αμιγώς lowrider soul αισθητική με ζεστές μεσαίες συχνότητες. Πιο lo-fi / souldies προσέγγιση, εστιασμένη στη ζεστασιά των μεσαίων.</t>
+  </si>
+  <si>
+    <t>Ρυθμικό κομμάτι με εξαιρετική μεταβατική απόκριση στα τύμπανα. Πολύ δυνατό low-end μπάσο, εξαιρετικό test για rocksteady transients</t>
+  </si>
+  <si>
+    <t>Μια βαθιά soul μπαλάντα που αναδεικνύει το βάθος του soundstage. Βαθύ soundstage με 70s reverbs</t>
+  </si>
+  <si>
+    <t>Vintage harmonies και πλούσιο layering στα δεύτερα φωνητικά. Από τα ηχητικά highlight, υποδειγματικό layering στα falsetto φωνητικά</t>
+  </si>
+  <si>
+    <t>Πιο έντονο τζαμαϊκανό feel με το rhythm section να δοκιμάζει τον έλεγχο των χαμηλών συχνοτήτων. Καθαρό, straightforward reggae/rocksteady rhythm section</t>
+  </si>
+  <si>
+    <t>Αέρινη ενορχήστρωση με εξαιρετική στερεοφωνική εικόνα. Κορυφαίος διαχωρισμός οργάνων και στερεοφωνική εικόνα που απλώνει στο δωμάτιο</t>
+  </si>
+  <si>
+    <t>Στιβαρό groove με τα πνευστά να έχουν σωστό «αέρα» χωρίς τραχύτητα. Ωραίος «αέρας» στα πνευστά, χωρίς ίχνος τραχύτητας</t>
+  </si>
+  <si>
+    <t>Όμορφες latin πινελιές που προσθέτουν ποικιλία στα ηχοχρώματα του δίσκου. Πιο μαζεμένη, cozy latin soul παραγωγή</t>
+  </si>
+  <si>
+    <t>Συνθετική κορυφή του άλμπουμ με εξαιρετικά εκφραστική ερμηνεία. Εστιασμένο στην καθαρότητα της lead φωνής.</t>
+  </si>
+  <si>
+    <t>Instrumental κλείσιμο με τεράστιο dynamic range, ιδανικό για audiophile τεστ. Instrumental με εξαιρετικό dynamic range και headroom</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -274,6 +391,22 @@
     <font>
       <sz val="8"/>
       <color theme="1"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="161"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="8"/>
+      <color theme="10"/>
       <name val="Tahoma"/>
       <family val="2"/>
       <charset val="161"/>
@@ -329,10 +462,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -373,9 +507,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Κανονικό" xfId="0" builtinId="0"/>
+    <cellStyle name="Υπερ-σύνδεση" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -677,7 +815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="9" bestFit="1" customWidth="1"/>
@@ -789,11 +927,33 @@
         <v>75</v>
       </c>
     </row>
+    <row r="4" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+      <c r="E4" s="3">
+        <v>3.73</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="J4" s="14" t="s">
+        <v>77</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="I3" r:id="rId1" xr:uid="{9C0994CE-C554-4210-BCA2-17F8D17FB784}"/>
     <hyperlink ref="J2" r:id="rId2" xr:uid="{AD58B770-BB72-48BD-AE29-27E61830C8AC}"/>
     <hyperlink ref="J3" r:id="rId3" xr:uid="{A295F22A-5B8A-48C2-8ADD-A473C972D75C}"/>
+    <hyperlink ref="I4" r:id="rId4" xr:uid="{B8F43599-8636-4878-AA63-74EF8E8FA4A0}"/>
+    <hyperlink ref="J4" r:id="rId5" xr:uid="{0383213A-C9D8-4706-B4BC-090F4D744EE5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -801,7 +961,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="11" customWidth="1"/>
@@ -1283,6 +1443,292 @@
         <v>57</v>
       </c>
     </row>
+    <row r="19" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="4">
+        <v>37452171</v>
+      </c>
+      <c r="B19" s="4">
+        <v>1</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="F19" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="G19" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>37452171</v>
+      </c>
+      <c r="B20" s="3">
+        <v>2</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="F20" s="7">
+        <v>3</v>
+      </c>
+      <c r="G20" s="7">
+        <v>3.4</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A21" s="4">
+        <v>37452171</v>
+      </c>
+      <c r="B21" s="4">
+        <v>3</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="F21" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="G21" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
+        <v>37452171</v>
+      </c>
+      <c r="B22" s="3">
+        <v>4</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="F22" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="G22" s="7">
+        <v>3.6</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A23" s="4">
+        <v>37452171</v>
+      </c>
+      <c r="B23" s="4">
+        <v>5</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="F23" s="8">
+        <v>4</v>
+      </c>
+      <c r="G23" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
+        <v>37452171</v>
+      </c>
+      <c r="B24" s="3">
+        <v>6</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="F24" s="7">
+        <v>3</v>
+      </c>
+      <c r="G24" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A25" s="4">
+        <v>37452171</v>
+      </c>
+      <c r="B25" s="4">
+        <v>7</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="F25" s="8">
+        <v>4</v>
+      </c>
+      <c r="G25" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A26" s="3">
+        <v>37452171</v>
+      </c>
+      <c r="B26" s="3">
+        <v>8</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="F26" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="G26" s="7">
+        <v>3.7</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A27" s="4">
+        <v>37452171</v>
+      </c>
+      <c r="B27" s="4">
+        <v>9</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="F27" s="8">
+        <v>3</v>
+      </c>
+      <c r="G27" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A28" s="3">
+        <v>37452171</v>
+      </c>
+      <c r="B28" s="3">
+        <v>10</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="F28" s="7">
+        <v>3</v>
+      </c>
+      <c r="G28" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A29" s="4">
+        <v>37452171</v>
+      </c>
+      <c r="B29" s="4">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="F29" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="G29" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBB13364-97DD-42C7-AFFA-7C169503BC81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{158725CD-BB00-438C-8120-EAD5F6CEB58E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="116">
   <si>
     <t>No</t>
   </si>
@@ -366,6 +366,9 @@
   </si>
   <si>
     <t>Instrumental κλείσιμο με τεράστιο dynamic range, ιδανικό για audiophile τεστ. Instrumental με εξαιρετικό dynamic range και headroom</t>
+  </si>
+  <si>
+    <t>Joey Quiñones</t>
   </si>
 </sst>
 </file>
@@ -928,6 +931,18 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>37452171</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E4" s="3">
         <v>3.73</v>
       </c>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{158725CD-BB00-438C-8120-EAD5F6CEB58E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F9A80F3-1840-4FC6-B379-F055B76D00D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="154">
   <si>
     <t>No</t>
   </si>
@@ -369,6 +369,120 @@
   </si>
   <si>
     <t>Joey Quiñones</t>
+  </si>
+  <si>
+    <t>Peacefield</t>
+  </si>
+  <si>
+    <t>Lachryma</t>
+  </si>
+  <si>
+    <t>Satanized</t>
+  </si>
+  <si>
+    <t>Guiding Lights</t>
+  </si>
+  <si>
+    <t>De Profundis Borealis</t>
+  </si>
+  <si>
+    <t>Cenotaph</t>
+  </si>
+  <si>
+    <t>Missilia Amori</t>
+  </si>
+  <si>
+    <t>Marks Of The Evil One</t>
+  </si>
+  <si>
+    <t>Umbra</t>
+  </si>
+  <si>
+    <t>Excelsis</t>
+  </si>
+  <si>
+    <t>Ghost</t>
+  </si>
+  <si>
+    <t>Skeletá</t>
+  </si>
+  <si>
+    <t>25 Apr 2025</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το «Skeletá» (2025) συνεχίζει τη στροφή των Ghost προς ένα AOR και arena rock ύφος. Η παραγωγή διακρίνεται για το εξαιρετικό imaging και τον διαχωρισμό οργάνων, αν και η σύγχρονη αισθητική loudness περιορίζει το baseline dynamic range. | Hard Facts Έκδοσης: Lacquer Cutting: Joe Nino-Hernes (JNH) στη Sterling Sound (RE1 Cut). Pressing: Memphis Record Pressing (MRP). Ήσυχο lead-in groove και καθαρή Violet μάζα βινυλίου με ελάχιστο θόρυβο επιφανείας (4.2/5).</t>
+  </si>
+  <si>
+    <t>Loma Vista (US Violet Indie Exclusive - Sterling/MRP Pressing)</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/33790944-Ghost-Skelet%C3%A1</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/ysvbXcnobHFT7F3L6bzQxi4y1MSOhA5JpYUUaJJTJoY/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTMzNzkw/OTQ0LTE3NDU3NzUx/NTYtNDI3Ni5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>AOR, Hard Rock, Glam Metal, Pop Rock, Heavy Metal, Alternative Metal</t>
+  </si>
+  <si>
+    <t>Δυνατό χορωδιακό άνοιγμα και palm-muted riff, αλλά η μελωδική δομή του ρεφρέν πλησιάζει Journey φόρμουλες. Καθαρά transients στις κιθάρες.</t>
+  </si>
+  <si>
+    <t>Hard Rock, Arena Rock</t>
+  </si>
+  <si>
+    <t>Hard Rock, Gothic Rock</t>
+  </si>
+  <si>
+    <t>Hard Rock, Gothic Metal</t>
+  </si>
+  <si>
+    <t>Power Ballad, AOR</t>
+  </si>
+  <si>
+    <t>Hard Rock, Doom Rock</t>
+  </si>
+  <si>
+    <t>Heartland Rock, Hard Rock</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Power Ballad</t>
+  </si>
+  <si>
+    <t>Hard Rock, Glam Rock</t>
+  </si>
+  <si>
+    <t>Hard Rock, Progressive Rock</t>
+  </si>
+  <si>
+    <t>Βρώμικο riff με σαφή μεταλλικότητα και αξιομνημόνευτο ρεφρέν με αναφορές σε Alice Cooper. Εξαιρετική ευκρίνεια στη lead φωνή.</t>
+  </si>
+  <si>
+    <t>Συνδυάζει doom αισθητική με μελωδικό ρεφρέν. Η συμμετοχή του F. Åkesson (Opeth) προσθέτει τεχνική αξία. Πιο μαζεμένο headroom.</t>
+  </si>
+  <si>
+    <t>Λειτουργεί ως inverted μπαλάντα, αλλά ακολουθεί προβλέψιμες AOR δομές. Φυσική μείξη στα πλήκτρα.</t>
+  </si>
+  <si>
+    <t>Σκοτεινή απεικόνιση και πιο βαριά δομή, λειτουργεί ως προετοιμασία. Καλή στερεοφωνική εικόνα.</t>
+  </si>
+  <si>
+    <t>Ζωηρό, radio-ready, αλλά σχετικά απλοϊκή δομή σε σχέση με άλλα tracks. Σφιχτά transients στα τύμπανα.</t>
+  </si>
+  <si>
+    <t>Καλή ενέργεια/swagger αλλά αδύναμο λυρικό περιεχόμενο με κλισέ στίχους. Στιβαρό rhythm section.</t>
+  </si>
+  <si>
+    <t>Δυνατό riff-driven κομμάτι με ισχυρή εικονογραφία (Four Horsemen). Καθαρός διαχωρισμός στις διπλές κιθάρες.</t>
+  </si>
+  <si>
+    <t>Το πιο ολοκληρωμένο κομμάτι, συνδυάζει occult rock, proto-metal και prog. Το απόλυτο ηχητικό highlight με το μεγαλύτερο dynamic range.</t>
+  </si>
+  <si>
+    <t>Επικό κλείσιμο με σαφή αναφορά στο "Life Eternal" σε μεγαλύτερη κλίμακα. Φυσικό σβήσιμο/decay.</t>
   </si>
 </sst>
 </file>
@@ -469,7 +583,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -511,6 +625,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -818,7 +935,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="9" bestFit="1" customWidth="1"/>
@@ -828,7 +945,7 @@
     <col min="5" max="5" width="10.85546875" style="9" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38.85546875" style="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="96.28515625" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="9" customWidth="1"/>
+    <col min="8" max="8" width="18.7109375" style="9" customWidth="1"/>
     <col min="9" max="9" width="35.7109375" style="9" customWidth="1"/>
     <col min="10" max="10" width="50.42578125" style="9" customWidth="1"/>
     <col min="11" max="16384" width="9.140625" style="9"/>
@@ -962,6 +1079,38 @@
         <v>77</v>
       </c>
     </row>
+    <row r="5" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <v>33790944</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E5" s="4">
+        <v>3.11</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>132</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="I3" r:id="rId1" xr:uid="{9C0994CE-C554-4210-BCA2-17F8D17FB784}"/>
@@ -969,6 +1118,8 @@
     <hyperlink ref="J3" r:id="rId3" xr:uid="{A295F22A-5B8A-48C2-8ADD-A473C972D75C}"/>
     <hyperlink ref="I4" r:id="rId4" xr:uid="{B8F43599-8636-4878-AA63-74EF8E8FA4A0}"/>
     <hyperlink ref="J4" r:id="rId5" xr:uid="{0383213A-C9D8-4706-B4BC-090F4D744EE5}"/>
+    <hyperlink ref="I5" r:id="rId6" xr:uid="{AB95816D-AFF8-4769-B964-AFEE7801899B}"/>
+    <hyperlink ref="J5" r:id="rId7" xr:uid="{25A0AA85-7925-4EA8-8C8E-F60C69923F4F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -976,7 +1127,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="11" customWidth="1"/>
@@ -1744,6 +1895,266 @@
         <v>114</v>
       </c>
     </row>
+    <row r="30" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A30" s="3">
+        <v>33790944</v>
+      </c>
+      <c r="B30" s="3">
+        <v>1</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="E30" s="7">
+        <v>3.63</v>
+      </c>
+      <c r="F30" s="7">
+        <v>3.7</v>
+      </c>
+      <c r="G30" s="7">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A31" s="4">
+        <v>33790944</v>
+      </c>
+      <c r="B31" s="4">
+        <v>2</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="E31" s="8">
+        <v>3.72</v>
+      </c>
+      <c r="F31" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G31" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A32" s="3">
+        <v>33790944</v>
+      </c>
+      <c r="B32" s="3">
+        <v>3</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="E32" s="7">
+        <v>3.65</v>
+      </c>
+      <c r="F32" s="7">
+        <v>3.8</v>
+      </c>
+      <c r="G32" s="7">
+        <v>4</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A33" s="4">
+        <v>33790944</v>
+      </c>
+      <c r="B33" s="4">
+        <v>4</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E33" s="8">
+        <v>3.15</v>
+      </c>
+      <c r="F33" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="G33" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A34" s="3">
+        <v>33790944</v>
+      </c>
+      <c r="B34" s="3">
+        <v>5</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="E34" s="7">
+        <v>3.35</v>
+      </c>
+      <c r="F34" s="7">
+        <v>3.6</v>
+      </c>
+      <c r="G34" s="7">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A35" s="4">
+        <v>33790944</v>
+      </c>
+      <c r="B35" s="4">
+        <v>6</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="E35" s="8">
+        <v>3.21</v>
+      </c>
+      <c r="F35" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="G35" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A36" s="3">
+        <v>33790944</v>
+      </c>
+      <c r="B36" s="3">
+        <v>7</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="E36" s="7">
+        <v>3.12</v>
+      </c>
+      <c r="F36" s="7">
+        <v>3.2</v>
+      </c>
+      <c r="G36" s="7">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A37" s="4">
+        <v>33790944</v>
+      </c>
+      <c r="B37" s="4">
+        <v>8</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="E37" s="8">
+        <v>3.43</v>
+      </c>
+      <c r="F37" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="G37" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A38" s="3">
+        <v>33790944</v>
+      </c>
+      <c r="B38" s="3">
+        <v>9</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="E38" s="7">
+        <v>3.62</v>
+      </c>
+      <c r="F38" s="7">
+        <v>4.2</v>
+      </c>
+      <c r="G38" s="7">
+        <v>4.7</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A39" s="4">
+        <v>33790944</v>
+      </c>
+      <c r="B39" s="4">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="E39" s="8">
+        <v>3.15</v>
+      </c>
+      <c r="F39" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="G39" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F9A80F3-1840-4FC6-B379-F055B76D00D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2107474-A717-49A5-9F7A-F24500511F57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -413,9 +413,6 @@
     <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το «Skeletá» (2025) συνεχίζει τη στροφή των Ghost προς ένα AOR και arena rock ύφος. Η παραγωγή διακρίνεται για το εξαιρετικό imaging και τον διαχωρισμό οργάνων, αν και η σύγχρονη αισθητική loudness περιορίζει το baseline dynamic range. | Hard Facts Έκδοσης: Lacquer Cutting: Joe Nino-Hernes (JNH) στη Sterling Sound (RE1 Cut). Pressing: Memphis Record Pressing (MRP). Ήσυχο lead-in groove και καθαρή Violet μάζα βινυλίου με ελάχιστο θόρυβο επιφανείας (4.2/5).</t>
   </si>
   <si>
-    <t>Loma Vista (US Violet Indie Exclusive - Sterling/MRP Pressing)</t>
-  </si>
-  <si>
     <t>https://www.discogs.com/release/33790944-Ghost-Skelet%C3%A1</t>
   </si>
   <si>
@@ -483,6 +480,9 @@
   </si>
   <si>
     <t>Επικό κλείσιμο με σαφή αναφορά στο "Life Eternal" σε μεγαλύτερη κλίμακα. Φυσικό σβήσιμο/decay.</t>
+  </si>
+  <si>
+    <t>Loma Vista (US/EU Violet Indie Exclusive - Sterling/GZ Media Pressing)</t>
   </si>
 </sst>
 </file>
@@ -1096,19 +1096,19 @@
         <v>3.11</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>129</v>
       </c>
       <c r="H5" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="I5" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="J5" s="15" t="s">
         <v>131</v>
-      </c>
-      <c r="J5" s="15" t="s">
-        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -1906,7 +1906,7 @@
         <v>116</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E30" s="7">
         <v>3.63</v>
@@ -1918,7 +1918,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -1932,7 +1932,7 @@
         <v>117</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E31" s="8">
         <v>3.72</v>
@@ -1944,7 +1944,7 @@
         <v>4.5</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -1958,7 +1958,7 @@
         <v>118</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E32" s="7">
         <v>3.65</v>
@@ -1970,7 +1970,7 @@
         <v>4</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -1984,7 +1984,7 @@
         <v>119</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E33" s="8">
         <v>3.15</v>
@@ -1996,7 +1996,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -2010,7 +2010,7 @@
         <v>120</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E34" s="7">
         <v>3.35</v>
@@ -2022,7 +2022,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -2036,7 +2036,7 @@
         <v>121</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E35" s="8">
         <v>3.21</v>
@@ -2048,7 +2048,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -2062,7 +2062,7 @@
         <v>122</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E36" s="7">
         <v>3.12</v>
@@ -2074,7 +2074,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -2088,7 +2088,7 @@
         <v>123</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E37" s="8">
         <v>3.43</v>
@@ -2100,7 +2100,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -2114,7 +2114,7 @@
         <v>124</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E38" s="7">
         <v>3.62</v>
@@ -2126,7 +2126,7 @@
         <v>4.7</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -2140,7 +2140,7 @@
         <v>125</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E39" s="8">
         <v>3.15</v>
@@ -2152,7 +2152,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2107474-A717-49A5-9F7A-F24500511F57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A7294E-E441-432C-B7D5-4468E706418F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="181">
   <si>
     <t>No</t>
   </si>
@@ -483,6 +483,87 @@
   </si>
   <si>
     <t>Loma Vista (US/EU Violet Indie Exclusive - Sterling/GZ Media Pressing)</t>
+  </si>
+  <si>
+    <t>Anne Neggen</t>
+  </si>
+  <si>
+    <t>If I Were Britannia I'd Waive The Rules</t>
+  </si>
+  <si>
+    <t>You're Opening Doors</t>
+  </si>
+  <si>
+    <t>Quacktor And Bureaucats</t>
+  </si>
+  <si>
+    <t>Sky High Percentage</t>
+  </si>
+  <si>
+    <t>Heaven Knows Our Name</t>
+  </si>
+  <si>
+    <t>Black Velvet Stallion</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal</t>
+  </si>
+  <si>
+    <t>Hard Rock, Funk Rock</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock</t>
+  </si>
+  <si>
+    <t>Hard Rock</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Hard Rock</t>
+  </si>
+  <si>
+    <t>Δυνατό, riff-driven opener που κρατάει τη βαριά κληρονομιά της μπάντας. Straightforward δομή με καλή ενέργεια.</t>
+  </si>
+  <si>
+    <t>Το ομώνυμο track εισάγει το slap μπάσο του Burke Shelley. Ενδιαφέρουσα αλλαγή κατεύθυνσης, αλλά στερείται το heavy impact των προηγούμενων δίσκων</t>
+  </si>
+  <si>
+    <t>Πιο παραδοσιακό hard rock track που προετοιμάζει το έδαφος για το φινάλε, με καλά δομημένες κιθάρες και σταθερό ρυθμό.</t>
+  </si>
+  <si>
+    <t>Επικό κλείσιμο και ένα από τα κορυφαία κομμάτια της καριέρας τους. Υποδειγματική prog ανάπτυξη 8 λεπτών με σκοτεινή, ατμοσφαιρική αισθητική, όπως επιβεβαιώνεται και από το ProgArchives.</t>
+  </si>
+  <si>
+    <t>Driving mid-tempo κομμάτι με έντονο το groove στοιχείο, το οποίο όμως επαναλαμβάνεται στη δομή του χωρίς να προσφέρει εκπλήξεις.</t>
+  </si>
+  <si>
+    <t>Καλογραμμένο bluesy banger με εξαιρετικό σόλο κιθάρας από τον Tony Bourge. Παρά τις επιφυλάξεις του ProgArchives που το θεωρεί αδύναμο, η συνθετική του ροή το δικαιώνει.</t>
+  </si>
+  <si>
+    <t>Ξεχωρίζει για τη δομή και τις κιθαριστικές αρμονίες του. Καλή φωνητική απόδοση και ενδιαφέροντα funk στοιχεία στο κλείσιμο, αν και λιγότερο βαρύ.</t>
+  </si>
+  <si>
+    <t>Hard Rock, Prog Rock</t>
+  </si>
+  <si>
+    <t>Budgie</t>
+  </si>
+  <si>
+    <t>If I Were Brittania I'd Waive the Rules</t>
+  </si>
+  <si>
+    <t>23 April 1976</t>
+  </si>
+  <si>
+    <t>A&amp;M Records (UK First Pressing - Arun Chakraverty Cut)</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το 6ο άλμπουμ των Budgie (1976) σηματοδοτεί μια στροφή προς πιο funky και mainstream hard rock φόρμουλες, προκαλώντας συγκρατημένες αντιδράσεις στην κοινότητα. Μοναδικό prog αριστούργημα το «Black Velvet Stallion». | Hard Facts Έκδοσης: Lacquer Cutting: Arun Chakraverty (χάραξη "ARUN" στη Side A) στα The Master Room. Pressing: UK First Press (A2/B2 κοπή, CBS Pressing Plant, Aston Clinton). Ηχητική Αξιολόγηση (4.3/5): Πολύ στιβαρό αναλογικό χαμηλό (low-end) χάρη στο slap-bass focus της παραγωγής, με εξαιρετικά transients στις κιθάρες του Tony Bourge και καθαρό, δυναμικό soundstage.</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/926332-Budgie-If-I-Were-Brittania-Id-Waive-The-Rules</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/s48TJXMMj1dZm-dxTfoqzQsrfZx95dI4YpnOA0h-rzg/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTkyNjMz/Mi0xNzM2MjY1MzM4/LTkyNTMuanBlZw.jpeg</t>
   </si>
 </sst>
 </file>
@@ -935,7 +1016,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="9" bestFit="1" customWidth="1"/>
@@ -1111,6 +1192,38 @@
         <v>131</v>
       </c>
     </row>
+    <row r="6" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>926332</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E6" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>180</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="I3" r:id="rId1" xr:uid="{9C0994CE-C554-4210-BCA2-17F8D17FB784}"/>
@@ -1120,6 +1233,8 @@
     <hyperlink ref="J4" r:id="rId5" xr:uid="{0383213A-C9D8-4706-B4BC-090F4D744EE5}"/>
     <hyperlink ref="I5" r:id="rId6" xr:uid="{AB95816D-AFF8-4769-B964-AFEE7801899B}"/>
     <hyperlink ref="J5" r:id="rId7" xr:uid="{25A0AA85-7925-4EA8-8C8E-F60C69923F4F}"/>
+    <hyperlink ref="I6" r:id="rId8" xr:uid="{5AE9F467-1B53-498C-B81D-02660B01BCA7}"/>
+    <hyperlink ref="J6" r:id="rId9" xr:uid="{AC0A6553-0986-4BB7-9D5A-C231F8C231FF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1127,7 +1242,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="11" customWidth="1"/>
@@ -2155,6 +2270,188 @@
         <v>152</v>
       </c>
     </row>
+    <row r="40" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A40" s="3">
+        <v>926332</v>
+      </c>
+      <c r="B40" s="3">
+        <v>1</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="E40" s="7">
+        <v>3.41</v>
+      </c>
+      <c r="F40" s="7">
+        <v>3.8</v>
+      </c>
+      <c r="G40" s="7">
+        <v>4.2</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A41" s="4">
+        <v>926332</v>
+      </c>
+      <c r="B41" s="4">
+        <v>2</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="E41" s="8">
+        <v>3.29</v>
+      </c>
+      <c r="F41" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="G41" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A42" s="3">
+        <v>926332</v>
+      </c>
+      <c r="B42" s="3">
+        <v>3</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="E42" s="7">
+        <v>3.03</v>
+      </c>
+      <c r="F42" s="7">
+        <v>3.7</v>
+      </c>
+      <c r="G42" s="7">
+        <v>4.2</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A43" s="4">
+        <v>926332</v>
+      </c>
+      <c r="B43" s="4">
+        <v>4</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E43" s="8">
+        <v>3.08</v>
+      </c>
+      <c r="F43" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="G43" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A44" s="3">
+        <v>926332</v>
+      </c>
+      <c r="B44" s="3">
+        <v>5</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="E44" s="7">
+        <v>3.28</v>
+      </c>
+      <c r="F44" s="7">
+        <v>3.4</v>
+      </c>
+      <c r="G44" s="7">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A45" s="4">
+        <v>926332</v>
+      </c>
+      <c r="B45" s="4">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="E45" s="8">
+        <v>3.04</v>
+      </c>
+      <c r="F45" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="G45" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A46" s="3">
+        <v>926332</v>
+      </c>
+      <c r="B46" s="3">
+        <v>7</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E46" s="7">
+        <v>3.45</v>
+      </c>
+      <c r="F46" s="7">
+        <v>5</v>
+      </c>
+      <c r="G46" s="7">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A7294E-E441-432C-B7D5-4468E706418F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46DAE9FC-A932-4AED-9FFD-0DA1D503DD47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="214">
   <si>
     <t>No</t>
   </si>
@@ -407,9 +407,6 @@
     <t>Skeletá</t>
   </si>
   <si>
-    <t>25 Apr 2025</t>
-  </si>
-  <si>
     <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το «Skeletá» (2025) συνεχίζει τη στροφή των Ghost προς ένα AOR και arena rock ύφος. Η παραγωγή διακρίνεται για το εξαιρετικό imaging και τον διαχωρισμό οργάνων, αν και η σύγχρονη αισθητική loudness περιορίζει το baseline dynamic range. | Hard Facts Έκδοσης: Lacquer Cutting: Joe Nino-Hernes (JNH) στη Sterling Sound (RE1 Cut). Pressing: Memphis Record Pressing (MRP). Ήσυχο lead-in groove και καθαρή Violet μάζα βινυλίου με ελάχιστο θόρυβο επιφανείας (4.2/5).</t>
   </si>
   <si>
@@ -564,6 +561,108 @@
   </si>
   <si>
     <t>https://i.discogs.com/s48TJXMMj1dZm-dxTfoqzQsrfZx95dI4YpnOA0h-rzg/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTkyNjMz/Mi0xNzM2MjY1MzM4/LTkyNTMuanBlZw.jpeg</t>
+  </si>
+  <si>
+    <t>Al Stewart</t>
+  </si>
+  <si>
+    <t>Time Passages</t>
+  </si>
+  <si>
+    <t>8 September 1978</t>
+  </si>
+  <si>
+    <t>25 April 2025</t>
+  </si>
+  <si>
+    <t>Soft Rock, Folk Rock, Pop Rock, Art Rock</t>
+  </si>
+  <si>
+    <t>RCA Victor (German First Pressing - Gatefold)</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Η άμεση συνέχεια του «Year of the Cat» σε παραγωγή και μηχανική ήχου από τον Alan Parsons. Υπόδειγμα 70s Soft/Prog Rock παραγωγής με πλούσιες ενορχηστρώσεις, σαξόφωνα (Phil Kenzie) και αέρινες ακουστικές κιθάρες. | Hard Facts Έκδοσης: Lacquer Cut στα Tonstudio Pfanz (χάραξη "PF" στα runouts) και πρεσάρισμα από την Teldec-Press GmbH στη Γερμανία. Matrix/Runout: RCA • PL • 25173 • A PF / B PF. Ηχητική Αξιολόγηση (4.7/5): Κορυφαία γερμανική κοπή με μηδενικό θόρυβο επιφάνειας, τεράστιο dynamic range, βαθύ soundstage και την κλασική audiophile διαύγεια του Alan Parsons στα φωνητικά και τα πιάτα.</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/10079558-Al-Stewart-Time-Passages</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/oZK7v6TCtISF2MTt_-1-RndqacgtmRG7eBAGaJ5immY/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTEwMDc5/NTU4LTE0OTEyNDc1/NTItMjMxNy5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Valentina Way</t>
+  </si>
+  <si>
+    <t>Life In Dark Water</t>
+  </si>
+  <si>
+    <t>A Man For All Seasons</t>
+  </si>
+  <si>
+    <t>Almost Lucy</t>
+  </si>
+  <si>
+    <t>Palace Of Versailles</t>
+  </si>
+  <si>
+    <t>Timeless Skies</t>
+  </si>
+  <si>
+    <t>Song On The Radio</t>
+  </si>
+  <si>
+    <t>End Of The Day</t>
+  </si>
+  <si>
+    <t>Pop Rock, Soft Rock, AOR</t>
+  </si>
+  <si>
+    <t>Το ομώνυμο διαμάντι. Εκπληκτική ενορχήστρωση με το χαρακτηριστικό σόλο σαξόφωνου του Phil Kenzie και αέρινες ακουστικές κιθάρες. Reference ηχογράφηση. Απίστευτη στερεοφωνική εικόνα, αέρας στα πιάτα και εξαιρετικό dynamic range.</t>
+  </si>
+  <si>
+    <t>Pop Rock, Soft Rock</t>
+  </si>
+  <si>
+    <t>Up-tempo, ρυθμικό κομμάτι με οδήγηση από το πιάνο που εξισορροπεί την ηρεμία του εναρκτήριου track. Εξαιρετικός διαχωρισμός στα φωνητικά</t>
+  </si>
+  <si>
+    <t>Progressive Pop, Soft Rock</t>
+  </si>
+  <si>
+    <t>Σκοτεινό, θεματικό track για εγκλωβισμένο υποβρύχιο. Ξεχωρίζει για τις prog αποχρώσεις και τα synth περάσματα. Βαθύ soundstage με layered synthesizer εφέ</t>
+  </si>
+  <si>
+    <t>Folk Rock, Soft Rock</t>
+  </si>
+  <si>
+    <t>Soft Rock, Pop Rock</t>
+  </si>
+  <si>
+    <t>Progressive Pop, Folk Rock</t>
+  </si>
+  <si>
+    <t>Soft Rock, Pop Rock, AOR</t>
+  </si>
+  <si>
+    <t>Soft Rock, Folk Rock</t>
+  </si>
+  <si>
+    <t>Νοσταλγικό, μελαγχολικό κλείσιμο με όμορφο decay στα κύμβαλα. Φυσική ηχογράφηση φωνητικών.</t>
+  </si>
+  <si>
+    <t>Το δεύτερο μεγάλο single. Εκπληκτικό groove με πλούσια σόλο σαξόφωνου και κιθάρας. Υποδειγματικός διαχωρισμός οργάνων, το σαξόφωνο αναπνέει στο χώρο.</t>
+  </si>
+  <si>
+    <t>Κλασική λυρική γραφή με ιστορικές αναφορές και ρευστό rhythm section. Φυσικότητα στα έγχορδα και καθαρά transients.</t>
+  </si>
+  <si>
+    <t>Πολύ όμορφο mid-tempo άνοιγμα της B πλευράς με μελωδικό ρεφρέν και καθαρή κιθαριστική συνοδεία. Πολύ ζεστή αναλογική υφή στα φωνητικά</t>
+  </si>
+  <si>
+    <t>Ιστορικό έπος βασισμένο στη Γαλλική Επανάσταση. Εξαιρετικές αλλαγές δυναμικής και πλούσιο layering. Πλούσια ενορχήστρωση με κλασικά όργανα και συνθεσάιζερ.</t>
+  </si>
+  <si>
+    <t>Ήρεμο, ταξιδιάρικο ακουστικό κομμάτι με ανάλαφρη αίσθηση. Εξαιρετική αποτύπωση των δαχτύλων στις χορδές της ακουστικής κιθάρας.</t>
   </si>
 </sst>
 </file>
@@ -664,7 +763,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -683,12 +782,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -709,6 +802,24 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1016,51 +1127,51 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.28515625" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="38.85546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="96.28515625" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.7109375" style="9" customWidth="1"/>
-    <col min="9" max="9" width="35.7109375" style="9" customWidth="1"/>
-    <col min="10" max="10" width="50.42578125" style="9" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="9"/>
+    <col min="1" max="1" width="10" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="38.85546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="96.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.7109375" style="7" customWidth="1"/>
+    <col min="9" max="9" width="35.7109375" style="7" customWidth="1"/>
+    <col min="10" max="10" width="50.42578125" style="7" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="8" t="s">
         <v>73</v>
       </c>
     </row>
@@ -1077,7 +1188,7 @@
       <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="14">
         <v>3.37</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -1109,7 +1220,7 @@
       <c r="D3" s="4">
         <v>2009</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="15">
         <v>3.78</v>
       </c>
       <c r="F3" s="2" t="s">
@@ -1141,7 +1252,7 @@
       <c r="D4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="14">
         <v>3.73</v>
       </c>
       <c r="F4" s="1" t="s">
@@ -1153,10 +1264,10 @@
       <c r="H4" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="I4" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="J4" s="12" t="s">
         <v>77</v>
       </c>
     </row>
@@ -1171,25 +1282,25 @@
         <v>127</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="E5" s="15">
+        <v>3.11</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="E5" s="4">
-        <v>3.11</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G5" s="6" t="s">
+      <c r="H5" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="I5" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="I5" s="15" t="s">
+      <c r="J5" s="13" t="s">
         <v>130</v>
-      </c>
-      <c r="J5" s="15" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
@@ -1197,31 +1308,63 @@
         <v>926332</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="14">
+        <v>3.29</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="E6" s="3">
-        <v>3.29</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="G6" s="5" t="s">
+      <c r="I6" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="I6" s="14" t="s">
+      <c r="J6" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="J6" s="14" t="s">
+    </row>
+    <row r="7" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>10079558</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>180</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="E7" s="15">
+        <v>3.6</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>188</v>
       </c>
     </row>
   </sheetData>
@@ -1235,6 +1378,8 @@
     <hyperlink ref="J5" r:id="rId7" xr:uid="{25A0AA85-7925-4EA8-8C8E-F60C69923F4F}"/>
     <hyperlink ref="I6" r:id="rId8" xr:uid="{5AE9F467-1B53-498C-B81D-02660B01BCA7}"/>
     <hyperlink ref="J6" r:id="rId9" xr:uid="{AC0A6553-0986-4BB7-9D5A-C231F8C231FF}"/>
+    <hyperlink ref="I7" r:id="rId10" xr:uid="{24D188DA-4F4D-40DC-9308-931FFF6A0E7F}"/>
+    <hyperlink ref="J7" r:id="rId11" xr:uid="{B14913EA-FB65-4D7E-A85A-5BFD89D186DD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1242,1214 +1387,1448 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" style="11" customWidth="1"/>
-    <col min="2" max="2" width="3.7109375" style="12" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" style="13" customWidth="1"/>
-    <col min="4" max="4" width="29.7109375" style="13" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" style="12" customWidth="1"/>
-    <col min="6" max="6" width="18.7109375" style="12" customWidth="1"/>
-    <col min="7" max="7" width="17.7109375" style="12" customWidth="1"/>
-    <col min="8" max="8" width="50.7109375" style="11" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="11"/>
+    <col min="1" max="1" width="9.7109375" style="9" customWidth="1"/>
+    <col min="2" max="2" width="3.7109375" style="10" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" style="11" customWidth="1"/>
+    <col min="4" max="4" width="29.7109375" style="11" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" style="10" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" style="10" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" style="10" customWidth="1"/>
+    <col min="8" max="8" width="50.7109375" style="9" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="8" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
+      <c r="A2" s="16">
         <v>964236001</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="16">
         <v>1</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="18">
         <v>3.94</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="18">
         <v>4</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="18">
         <v>4.2</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="19" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
+      <c r="A3" s="16">
         <v>964236001</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="16">
         <v>2</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="18">
         <v>3.81</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="18">
         <v>4.2</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="18">
         <v>4.5</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="19" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
+      <c r="A4" s="16">
         <v>964236001</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="16">
         <v>3</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="18">
         <v>3.57</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="18">
         <v>3.9</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="18">
         <v>4.3</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="19" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
+      <c r="A5" s="16">
         <v>964236001</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="16">
         <v>4</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="18">
         <v>3.71</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="18">
         <v>4.5</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="18">
         <v>4.0999999999999996</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="19" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
+      <c r="A6" s="16">
         <v>964236001</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="16">
         <v>5</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="18">
         <v>3.48</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="18">
         <v>3.7</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="18">
         <v>4</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="19" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
+      <c r="A7" s="16">
         <v>964236001</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="16">
         <v>6</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="18">
         <v>3.78</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="18">
         <v>4.0999999999999996</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="18">
         <v>4.4000000000000004</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="19" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
+      <c r="A8" s="16">
         <v>964236001</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="16">
         <v>7</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="18">
         <v>3.39</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="18">
         <v>4.2</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="18">
         <v>4.2</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" s="19" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
+      <c r="A9" s="16">
         <v>964236001</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="16">
         <v>8</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="18">
         <v>3.54</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="18">
         <v>4.5999999999999996</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="18">
         <v>4.5</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="19" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
+      <c r="A10" s="16">
         <v>964236001</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="16">
         <v>9</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="18">
         <v>3.66</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="18">
         <v>3.8</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="18">
         <v>4.0999999999999996</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="H10" s="19" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
+      <c r="A11" s="16">
         <v>964236001</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="16">
         <v>10</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="18">
         <v>3.68</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="18">
         <v>4.7</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="18">
         <v>4.9000000000000004</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H11" s="19" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
+      <c r="A12" s="16">
         <v>1739129</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="16">
         <v>1</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="18">
         <v>4.22</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="18">
         <v>4.2</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="18">
         <v>3.8</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="H12" s="19" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
+      <c r="A13" s="16">
         <v>1739129</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="16">
         <v>2</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="18">
         <v>3.96</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13" s="18">
         <v>3.6</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="18">
         <v>3.6</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H13" s="19" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
+      <c r="A14" s="16">
         <v>1739129</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="16">
         <v>3</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="18">
         <v>4.0199999999999996</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="18">
         <v>4.4000000000000004</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="18">
         <v>4.3</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="H14" s="19" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
+      <c r="A15" s="16">
         <v>1739129</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="16">
         <v>4</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="18">
         <v>3.83</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="18">
         <v>3.5</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G15" s="18">
         <v>3.6</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="H15" s="19" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
+      <c r="A16" s="16">
         <v>1739129</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="16">
         <v>5</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="18">
         <v>3.9</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="18">
         <v>3.8</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="18">
         <v>3.8</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H16" s="19" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
+      <c r="A17" s="16">
         <v>1739129</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="16">
         <v>6</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="18">
         <v>3.93</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17" s="18">
         <v>3.7</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G17" s="18">
         <v>4</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="H17" s="19" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
+      <c r="A18" s="16">
         <v>1739129</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="16">
         <v>7</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E18" s="18">
         <v>4.43</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="18">
         <v>5</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G18" s="18">
         <v>4.5999999999999996</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="H18" s="19" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="4">
+      <c r="A19" s="16">
         <v>37452171</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19" s="16">
         <v>1</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="18">
         <v>3.5</v>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="18">
         <v>3.7</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="H19" s="19" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
+      <c r="A20" s="16">
         <v>37452171</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20" s="16">
         <v>2</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F20" s="18">
         <v>3</v>
       </c>
-      <c r="G20" s="7">
+      <c r="G20" s="18">
         <v>3.4</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="H20" s="19" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A21" s="4">
+      <c r="A21" s="16">
         <v>37452171</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B21" s="16">
         <v>3</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="E21" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="F21" s="8">
+      <c r="F21" s="18">
         <v>3.5</v>
       </c>
-      <c r="G21" s="8">
+      <c r="G21" s="18">
         <v>3.8</v>
       </c>
-      <c r="H21" s="2" t="s">
+      <c r="H21" s="19" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A22" s="3">
+      <c r="A22" s="16">
         <v>37452171</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22" s="16">
         <v>4</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="F22" s="7">
+      <c r="F22" s="18">
         <v>3.5</v>
       </c>
-      <c r="G22" s="7">
+      <c r="G22" s="18">
         <v>3.6</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="H22" s="19" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A23" s="4">
+      <c r="A23" s="16">
         <v>37452171</v>
       </c>
-      <c r="B23" s="4">
+      <c r="B23" s="16">
         <v>5</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="E23" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="F23" s="8">
+      <c r="F23" s="18">
         <v>4</v>
       </c>
-      <c r="G23" s="8">
+      <c r="G23" s="18">
         <v>4.0999999999999996</v>
       </c>
-      <c r="H23" s="2" t="s">
+      <c r="H23" s="19" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
+      <c r="A24" s="16">
         <v>37452171</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24" s="16">
         <v>6</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F24" s="18">
         <v>3</v>
       </c>
-      <c r="G24" s="7">
+      <c r="G24" s="18">
         <v>3.5</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="H24" s="19" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="4">
+      <c r="A25" s="16">
         <v>37452171</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25" s="16">
         <v>7</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="E25" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="F25" s="8">
+      <c r="F25" s="18">
         <v>4</v>
       </c>
-      <c r="G25" s="8">
+      <c r="G25" s="18">
         <v>4.2</v>
       </c>
-      <c r="H25" s="2" t="s">
+      <c r="H25" s="19" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A26" s="3">
+      <c r="A26" s="16">
         <v>37452171</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26" s="16">
         <v>8</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F26" s="18">
         <v>3.5</v>
       </c>
-      <c r="G26" s="7">
+      <c r="G26" s="18">
         <v>3.7</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="H26" s="19" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A27" s="4">
+      <c r="A27" s="16">
         <v>37452171</v>
       </c>
-      <c r="B27" s="4">
+      <c r="B27" s="16">
         <v>9</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="E27" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="F27" s="8">
+      <c r="F27" s="18">
         <v>3</v>
       </c>
-      <c r="G27" s="8">
+      <c r="G27" s="18">
         <v>3.4</v>
       </c>
-      <c r="H27" s="2" t="s">
+      <c r="H27" s="19" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A28" s="3">
+      <c r="A28" s="16">
         <v>37452171</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B28" s="16">
         <v>10</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="F28" s="7">
+      <c r="F28" s="18">
         <v>3</v>
       </c>
-      <c r="G28" s="7">
+      <c r="G28" s="18">
         <v>3.5</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="H28" s="19" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A29" s="4">
+      <c r="A29" s="16">
         <v>37452171</v>
       </c>
-      <c r="B29" s="4">
+      <c r="B29" s="16">
         <v>11</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="E29" s="8" t="s">
+      <c r="E29" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="F29" s="8">
+      <c r="F29" s="18">
         <v>3.5</v>
       </c>
-      <c r="G29" s="8">
+      <c r="G29" s="18">
         <v>3.9</v>
       </c>
-      <c r="H29" s="2" t="s">
+      <c r="H29" s="19" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A30" s="3">
+      <c r="A30" s="16">
         <v>33790944</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B30" s="16">
         <v>1</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D30" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="E30" s="18">
+        <v>3.63</v>
+      </c>
+      <c r="F30" s="18">
+        <v>3.7</v>
+      </c>
+      <c r="G30" s="18">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H30" s="19" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A31" s="16">
+        <v>33790944</v>
+      </c>
+      <c r="B31" s="16">
+        <v>2</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="D31" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="E30" s="7">
+      <c r="E31" s="18">
+        <v>3.72</v>
+      </c>
+      <c r="F31" s="18">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G31" s="18">
+        <v>4.5</v>
+      </c>
+      <c r="H31" s="19" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A32" s="16">
+        <v>33790944</v>
+      </c>
+      <c r="B32" s="16">
+        <v>3</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="E32" s="18">
+        <v>3.65</v>
+      </c>
+      <c r="F32" s="18">
+        <v>3.8</v>
+      </c>
+      <c r="G32" s="18">
+        <v>4</v>
+      </c>
+      <c r="H32" s="19" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A33" s="16">
+        <v>33790944</v>
+      </c>
+      <c r="B33" s="16">
+        <v>4</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="D33" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="E33" s="18">
+        <v>3.15</v>
+      </c>
+      <c r="F33" s="18">
+        <v>3.5</v>
+      </c>
+      <c r="G33" s="18">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H33" s="19" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A34" s="16">
+        <v>33790944</v>
+      </c>
+      <c r="B34" s="16">
+        <v>5</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="D34" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="E34" s="18">
+        <v>3.35</v>
+      </c>
+      <c r="F34" s="18">
+        <v>3.6</v>
+      </c>
+      <c r="G34" s="18">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H34" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A35" s="16">
+        <v>33790944</v>
+      </c>
+      <c r="B35" s="16">
+        <v>6</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="D35" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="E35" s="18">
+        <v>3.21</v>
+      </c>
+      <c r="F35" s="18">
+        <v>3.4</v>
+      </c>
+      <c r="G35" s="18">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H35" s="19" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A36" s="16">
+        <v>33790944</v>
+      </c>
+      <c r="B36" s="16">
+        <v>7</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="D36" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="E36" s="18">
+        <v>3.12</v>
+      </c>
+      <c r="F36" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="G36" s="18">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H36" s="19" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A37" s="16">
+        <v>33790944</v>
+      </c>
+      <c r="B37" s="16">
+        <v>8</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="D37" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="E37" s="18">
+        <v>3.43</v>
+      </c>
+      <c r="F37" s="18">
+        <v>3.7</v>
+      </c>
+      <c r="G37" s="18">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H37" s="19" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A38" s="16">
+        <v>33790944</v>
+      </c>
+      <c r="B38" s="16">
+        <v>9</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="D38" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="E38" s="18">
+        <v>3.62</v>
+      </c>
+      <c r="F38" s="18">
+        <v>4.2</v>
+      </c>
+      <c r="G38" s="18">
+        <v>4.7</v>
+      </c>
+      <c r="H38" s="19" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A39" s="16">
+        <v>33790944</v>
+      </c>
+      <c r="B39" s="16">
+        <v>10</v>
+      </c>
+      <c r="C39" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="D39" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="E39" s="18">
+        <v>3.15</v>
+      </c>
+      <c r="F39" s="18">
+        <v>3.6</v>
+      </c>
+      <c r="G39" s="18">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H39" s="19" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A40" s="16">
+        <v>926332</v>
+      </c>
+      <c r="B40" s="16">
+        <v>1</v>
+      </c>
+      <c r="C40" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="D40" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="E40" s="18">
+        <v>3.41</v>
+      </c>
+      <c r="F40" s="18">
+        <v>3.8</v>
+      </c>
+      <c r="G40" s="18">
+        <v>4.2</v>
+      </c>
+      <c r="H40" s="19" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A41" s="16">
+        <v>926332</v>
+      </c>
+      <c r="B41" s="16">
+        <v>2</v>
+      </c>
+      <c r="C41" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="D41" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="E41" s="18">
+        <v>3.29</v>
+      </c>
+      <c r="F41" s="18">
+        <v>3.6</v>
+      </c>
+      <c r="G41" s="18">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H41" s="19" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A42" s="16">
+        <v>926332</v>
+      </c>
+      <c r="B42" s="16">
+        <v>3</v>
+      </c>
+      <c r="C42" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="D42" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="E42" s="18">
+        <v>3.03</v>
+      </c>
+      <c r="F42" s="18">
+        <v>3.7</v>
+      </c>
+      <c r="G42" s="18">
+        <v>4.2</v>
+      </c>
+      <c r="H42" s="19" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A43" s="16">
+        <v>926332</v>
+      </c>
+      <c r="B43" s="16">
+        <v>4</v>
+      </c>
+      <c r="C43" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="D43" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="E43" s="18">
+        <v>3.08</v>
+      </c>
+      <c r="F43" s="18">
+        <v>3.5</v>
+      </c>
+      <c r="G43" s="18">
+        <v>3.8</v>
+      </c>
+      <c r="H43" s="19" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A44" s="16">
+        <v>926332</v>
+      </c>
+      <c r="B44" s="16">
+        <v>5</v>
+      </c>
+      <c r="C44" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="D44" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="E44" s="18">
+        <v>3.28</v>
+      </c>
+      <c r="F44" s="18">
+        <v>3.4</v>
+      </c>
+      <c r="G44" s="18">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H44" s="19" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A45" s="16">
+        <v>926332</v>
+      </c>
+      <c r="B45" s="16">
+        <v>6</v>
+      </c>
+      <c r="C45" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="D45" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="E45" s="18">
+        <v>3.04</v>
+      </c>
+      <c r="F45" s="18">
+        <v>3.6</v>
+      </c>
+      <c r="G45" s="18">
+        <v>4.3</v>
+      </c>
+      <c r="H45" s="19" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A46" s="16">
+        <v>926332</v>
+      </c>
+      <c r="B46" s="16">
+        <v>7</v>
+      </c>
+      <c r="C46" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D46" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="E46" s="18">
+        <v>3.45</v>
+      </c>
+      <c r="F46" s="18">
+        <v>5</v>
+      </c>
+      <c r="G46" s="18">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H46" s="19" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="42" x14ac:dyDescent="0.25">
+      <c r="A47" s="16">
+        <v>10079558</v>
+      </c>
+      <c r="B47" s="16">
+        <v>1</v>
+      </c>
+      <c r="C47" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="D47" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="E47" s="18">
+        <v>3.91</v>
+      </c>
+      <c r="F47" s="18">
+        <v>4.3</v>
+      </c>
+      <c r="G47" s="18">
+        <v>4.8</v>
+      </c>
+      <c r="H47" s="19" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A48" s="16">
+        <v>10079558</v>
+      </c>
+      <c r="B48" s="16">
+        <v>2</v>
+      </c>
+      <c r="C48" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="D48" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="E48" s="18">
         <v>3.63</v>
       </c>
-      <c r="F30" s="7">
+      <c r="F48" s="18">
+        <v>3.6</v>
+      </c>
+      <c r="G48" s="18">
+        <v>4.3</v>
+      </c>
+      <c r="H48" s="19" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A49" s="16">
+        <v>10079558</v>
+      </c>
+      <c r="B49" s="16">
+        <v>3</v>
+      </c>
+      <c r="C49" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="D49" s="17" t="s">
+        <v>201</v>
+      </c>
+      <c r="E49" s="18">
+        <v>4.04</v>
+      </c>
+      <c r="F49" s="18">
+        <v>4</v>
+      </c>
+      <c r="G49" s="18">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H49" s="19" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A50" s="16">
+        <v>10079558</v>
+      </c>
+      <c r="B50" s="16">
+        <v>4</v>
+      </c>
+      <c r="C50" s="17" t="s">
+        <v>191</v>
+      </c>
+      <c r="D50" s="17" t="s">
+        <v>203</v>
+      </c>
+      <c r="E50" s="18">
+        <v>3.63</v>
+      </c>
+      <c r="F50" s="18">
+        <v>3.8</v>
+      </c>
+      <c r="G50" s="18">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H50" s="19" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A51" s="16">
+        <v>10079558</v>
+      </c>
+      <c r="B51" s="16">
+        <v>5</v>
+      </c>
+      <c r="C51" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="D51" s="17" t="s">
+        <v>204</v>
+      </c>
+      <c r="E51" s="18">
+        <v>3.67</v>
+      </c>
+      <c r="F51" s="18">
         <v>3.7</v>
       </c>
-      <c r="G30" s="7">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A31" s="4">
-        <v>33790944</v>
-      </c>
-      <c r="B31" s="4">
-        <v>2</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="E31" s="8">
-        <v>3.72</v>
-      </c>
-      <c r="F31" s="8">
+      <c r="G51" s="18">
+        <v>4.3</v>
+      </c>
+      <c r="H51" s="19" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A52" s="16">
+        <v>10079558</v>
+      </c>
+      <c r="B52" s="16">
+        <v>6</v>
+      </c>
+      <c r="C52" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="D52" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="E52" s="18">
+        <v>4.03</v>
+      </c>
+      <c r="F52" s="18">
+        <v>4.2</v>
+      </c>
+      <c r="G52" s="18">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H52" s="19" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A53" s="16">
+        <v>10079558</v>
+      </c>
+      <c r="B53" s="16">
+        <v>7</v>
+      </c>
+      <c r="C53" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="D53" s="17" t="s">
+        <v>203</v>
+      </c>
+      <c r="E53" s="18">
+        <v>3.58</v>
+      </c>
+      <c r="F53" s="18">
+        <v>3.5</v>
+      </c>
+      <c r="G53" s="18">
+        <v>4.3</v>
+      </c>
+      <c r="H53" s="19" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A54" s="16">
+        <v>10079558</v>
+      </c>
+      <c r="B54" s="16">
+        <v>8</v>
+      </c>
+      <c r="C54" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="D54" s="17" t="s">
+        <v>206</v>
+      </c>
+      <c r="E54" s="18">
+        <v>3.66</v>
+      </c>
+      <c r="F54" s="18">
         <v>4.0999999999999996</v>
       </c>
-      <c r="G31" s="8">
+      <c r="G54" s="18">
+        <v>4.7</v>
+      </c>
+      <c r="H54" s="19" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A55" s="16">
+        <v>10079558</v>
+      </c>
+      <c r="B55" s="16">
+        <v>9</v>
+      </c>
+      <c r="C55" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="D55" s="17" t="s">
+        <v>207</v>
+      </c>
+      <c r="E55" s="18">
+        <v>3.73</v>
+      </c>
+      <c r="F55" s="18">
+        <v>3.7</v>
+      </c>
+      <c r="G55" s="18">
         <v>4.5</v>
       </c>
-      <c r="H31" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A32" s="3">
-        <v>33790944</v>
-      </c>
-      <c r="B32" s="3">
-        <v>3</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="E32" s="7">
-        <v>3.65</v>
-      </c>
-      <c r="F32" s="7">
-        <v>3.8</v>
-      </c>
-      <c r="G32" s="7">
-        <v>4</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A33" s="4">
-        <v>33790944</v>
-      </c>
-      <c r="B33" s="4">
-        <v>4</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="E33" s="8">
-        <v>3.15</v>
-      </c>
-      <c r="F33" s="8">
-        <v>3.5</v>
-      </c>
-      <c r="G33" s="8">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A34" s="3">
-        <v>33790944</v>
-      </c>
-      <c r="B34" s="3">
-        <v>5</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="E34" s="7">
-        <v>3.35</v>
-      </c>
-      <c r="F34" s="7">
-        <v>3.6</v>
-      </c>
-      <c r="G34" s="7">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A35" s="4">
-        <v>33790944</v>
-      </c>
-      <c r="B35" s="4">
-        <v>6</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="E35" s="8">
-        <v>3.21</v>
-      </c>
-      <c r="F35" s="8">
-        <v>3.4</v>
-      </c>
-      <c r="G35" s="8">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A36" s="3">
-        <v>33790944</v>
-      </c>
-      <c r="B36" s="3">
-        <v>7</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="E36" s="7">
-        <v>3.12</v>
-      </c>
-      <c r="F36" s="7">
-        <v>3.2</v>
-      </c>
-      <c r="G36" s="7">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A37" s="4">
-        <v>33790944</v>
-      </c>
-      <c r="B37" s="4">
-        <v>8</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="E37" s="8">
-        <v>3.43</v>
-      </c>
-      <c r="F37" s="8">
-        <v>3.7</v>
-      </c>
-      <c r="G37" s="8">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A38" s="3">
-        <v>33790944</v>
-      </c>
-      <c r="B38" s="3">
-        <v>9</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="E38" s="7">
-        <v>3.62</v>
-      </c>
-      <c r="F38" s="7">
-        <v>4.2</v>
-      </c>
-      <c r="G38" s="7">
-        <v>4.7</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A39" s="4">
-        <v>33790944</v>
-      </c>
-      <c r="B39" s="4">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="E39" s="8">
-        <v>3.15</v>
-      </c>
-      <c r="F39" s="8">
-        <v>3.6</v>
-      </c>
-      <c r="G39" s="8">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A40" s="3">
-        <v>926332</v>
-      </c>
-      <c r="B40" s="3">
-        <v>1</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="E40" s="7">
-        <v>3.41</v>
-      </c>
-      <c r="F40" s="7">
-        <v>3.8</v>
-      </c>
-      <c r="G40" s="7">
-        <v>4.2</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A41" s="4">
-        <v>926332</v>
-      </c>
-      <c r="B41" s="4">
-        <v>2</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="E41" s="8">
-        <v>3.29</v>
-      </c>
-      <c r="F41" s="8">
-        <v>3.6</v>
-      </c>
-      <c r="G41" s="8">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A42" s="3">
-        <v>926332</v>
-      </c>
-      <c r="B42" s="3">
-        <v>3</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="E42" s="7">
-        <v>3.03</v>
-      </c>
-      <c r="F42" s="7">
-        <v>3.7</v>
-      </c>
-      <c r="G42" s="7">
-        <v>4.2</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A43" s="4">
-        <v>926332</v>
-      </c>
-      <c r="B43" s="4">
-        <v>4</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="E43" s="8">
-        <v>3.08</v>
-      </c>
-      <c r="F43" s="8">
-        <v>3.5</v>
-      </c>
-      <c r="G43" s="8">
-        <v>3.8</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A44" s="3">
-        <v>926332</v>
-      </c>
-      <c r="B44" s="3">
-        <v>5</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="E44" s="7">
-        <v>3.28</v>
-      </c>
-      <c r="F44" s="7">
-        <v>3.4</v>
-      </c>
-      <c r="G44" s="7">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A45" s="4">
-        <v>926332</v>
-      </c>
-      <c r="B45" s="4">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="E45" s="8">
-        <v>3.04</v>
-      </c>
-      <c r="F45" s="8">
-        <v>3.6</v>
-      </c>
-      <c r="G45" s="8">
-        <v>4.3</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A46" s="3">
-        <v>926332</v>
-      </c>
-      <c r="B46" s="3">
-        <v>7</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="E46" s="7">
-        <v>3.45</v>
-      </c>
-      <c r="F46" s="7">
-        <v>5</v>
-      </c>
-      <c r="G46" s="7">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>169</v>
+      <c r="H55" s="19" t="s">
+        <v>208</v>
       </c>
     </row>
   </sheetData>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46DAE9FC-A932-4AED-9FFD-0DA1D503DD47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01D67460-A34D-4F79-BBEE-6BAD35A4DE49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="239">
   <si>
     <t>No</t>
   </si>
@@ -663,6 +663,81 @@
   </si>
   <si>
     <t>Ήρεμο, ταξιδιάρικο ακουστικό κομμάτι με ανάλαφρη αίσθηση. Εξαιρετική αποτύπωση των δαχτύλων στις χορδές της ακουστικής κιθάρας.</t>
+  </si>
+  <si>
+    <t>Racing Cars</t>
+  </si>
+  <si>
+    <t>Downtown Tonight</t>
+  </si>
+  <si>
+    <t>September 1976</t>
+  </si>
+  <si>
+    <t>Soft Rock, Blues Rock, AOR, Pub Rock</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το εντυπωσιακό ντεμπούτο των Racing Cars (1976) που συνδυάζει 70s Pub Rock, Blues Rock και AOR με τα εξαιρετικά συναισθηματικά φωνητικά του Gareth Mortimer (Morty). Περιλαμβάνει το διαχρονικό αριστούργημα «They Shoot Horses Don't They?». | Hard Facts Έκδοσης: Lacquer Cutting από τον θρυλικό Harry Moss στα Abbey Road Studios (σφραγίδα "HTM" &amp; "EG" στα runouts). UK First Pressing (Variant 2 με πλάγιο "1" χάραγμα). Matrix/Runout: CHR 1099 A EG ↮ HTM I-4 / CHR 1099 B EG ↮ HTM I-5. Ηχητική Αξιολόγηση (4.6/5): Εκπληκτικό αναλογικό mastering από τον Harry Moss. Φυσικότατα φωνητικά, εξαιρετική αέρινη παρουσία στις κιθάρες, βαθύ soundstage και πολύ καλό dynamic range στα ξεσπάσματα των 6λεπτων tracks.</t>
+  </si>
+  <si>
+    <t>Chrysalis (UK First Pressing - HTM Cut / Variant 2)</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/2027786-Racing-Cars-Downtown-Tonight</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/OuoF6VxZroSkfhJZwCc29rQ0dq2_cBa0MIZuLybMVm0/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTIwMjc3/ODYtMTM5NjI2ODI3/MS02MzUwLmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>Calling The Tune</t>
+  </si>
+  <si>
+    <t>Hard Working Woman</t>
+  </si>
+  <si>
+    <t>Ladee-Lo</t>
+  </si>
+  <si>
+    <t>Pass The Bottle</t>
+  </si>
+  <si>
+    <t>Moonshine Fandango</t>
+  </si>
+  <si>
+    <t>Four Wheel Drive</t>
+  </si>
+  <si>
+    <t>Get Out And Get It</t>
+  </si>
+  <si>
+    <t>They Shoot Horses Don't They?</t>
+  </si>
+  <si>
+    <t>Δυνατό, mid-tempo opener με ωραίο ρυθμό, χαρακτηριστικά 70s κιθαριστικά γεμίσματα και τα πολύ ιδιαίτερα soul φωνητικά του Morty. Καθαρός αναλογικός διαχωρισμός στις κιθάρες και φυσική αίσθηση στα τύμπανα.</t>
+  </si>
+  <si>
+    <t>Ρυθμικό, bluesy track με στιβαρό groove. Straightforward δομή που αναδεικνύει την ενέργεια της μπάντας. Σφιχτό rhythm section με καλά transients.</t>
+  </si>
+  <si>
+    <t>Πιο ανάλαφρο, μελωδικό κομμάτι με πιασάρικο ρεφρέν που εξισορροπεί την ένταση της Α πλευράς. Ζεστός, αναλογικός ήχος στα φωνητικά.</t>
+  </si>
+  <si>
+    <t>Το 6λεπτο ομώνυμο έπος που κλείνει την Α πλευρά. Εξαιρετική κλιμάκωση, ατμοσφαιρικά περάσματα και κορυφαία ερμηνεία με πλούσιες κιθαριστικές αρμονίες. Πολύ ευρύ soundstage με μεγάλο dynamic range στις αλλαγές έντασης.</t>
+  </si>
+  <si>
+    <t>Up-tempo, ξεσηκωτικό track για το άνοιγμα της B πλευράς με έντονο το pub rock/boogie στοιχείο. Ζωντανή, "in-your-face" ηχογράφηση.</t>
+  </si>
+  <si>
+    <t>Ενδιαφέρουσα country/folk-rock πινελιά με ρυθμική ποικιλία. Καθαρή αποτύπωση των ακουστικών οργάνων.</t>
+  </si>
+  <si>
+    <t>Σύντομο, γρήγορο rock 'n' roll ξέσπασμα 2:50 λεπτών με δυνατές κιθάρες.</t>
+  </si>
+  <si>
+    <t>Δυναμικό, ρυθμικό κομμάτι που προετοιμάζει το έδαφος για το φινάλε.</t>
+  </si>
+  <si>
+    <t>Το αδιαμφισβήτητο magnum opus της μπάντας και η μεγαλύτερη επιτυχία τους [UK Top 14]. Εκπληκτική, συναισθηματικά φορτισμένη μπαλάντα 6+ λεπτών με συγκλονιστική ερμηνεία, έγχορδα και κορυφαία κιθαριστική κορύφωση. Reference ηχογράφηση με απίστευτο βάθος, αέρα στα πιάτα και πλούσιο layering στα όργανα</t>
   </si>
 </sst>
 </file>
@@ -709,7 +784,7 @@
       <charset val="161"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -719,18 +794,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2F4F4F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5F5F5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -763,26 +826,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -798,17 +843,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -816,10 +861,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1127,244 +1175,276 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="38.85546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="96.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.7109375" style="7" customWidth="1"/>
-    <col min="9" max="9" width="35.7109375" style="7" customWidth="1"/>
-    <col min="10" max="10" width="50.42578125" style="7" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="7"/>
+    <col min="1" max="1" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="38.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="96.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.7109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="35.7109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="50.42578125" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="63" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
+      <c r="A2" s="10">
         <v>964236001</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="14">
+      <c r="E2" s="12">
         <v>3.37</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="13" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="42" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
+      <c r="A3" s="10">
         <v>1739129</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="10">
         <v>2009</v>
       </c>
-      <c r="E3" s="15">
+      <c r="E3" s="12">
         <v>3.78</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="13" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="42" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
+      <c r="A4" s="10">
         <v>37452171</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="12">
         <v>3.73</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="J4" s="14" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="42" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
+      <c r="A5" s="10">
         <v>33790944</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="12">
         <v>3.11</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="I5" s="13" t="s">
+      <c r="I5" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="J5" s="13" t="s">
+      <c r="J5" s="14" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
+      <c r="A6" s="10">
         <v>926332</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="12">
         <v>3.29</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="J6" s="12" t="s">
+      <c r="J6" s="14" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="63" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
+      <c r="A7" s="10">
         <v>10079558</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="12">
         <v>3.6</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="I7" s="13" t="s">
+      <c r="I7" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="J7" s="13" t="s">
+      <c r="J7" s="14" t="s">
         <v>188</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+      <c r="A8" s="10">
+        <v>2027786</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="E8" s="12">
+        <v>3.45</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -1380,6 +1460,8 @@
     <hyperlink ref="J6" r:id="rId9" xr:uid="{AC0A6553-0986-4BB7-9D5A-C231F8C231FF}"/>
     <hyperlink ref="I7" r:id="rId10" xr:uid="{24D188DA-4F4D-40DC-9308-931FFF6A0E7F}"/>
     <hyperlink ref="J7" r:id="rId11" xr:uid="{B14913EA-FB65-4D7E-A85A-5BFD89D186DD}"/>
+    <hyperlink ref="I8" r:id="rId12" xr:uid="{84F45C40-1251-4DE1-88F3-8BC3CD9CE503}"/>
+    <hyperlink ref="J8" r:id="rId13" xr:uid="{2916FB00-92B8-41FF-873A-2CB7478D6FC5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1387,1448 +1469,1664 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" style="9" customWidth="1"/>
-    <col min="2" max="2" width="3.7109375" style="10" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" style="11" customWidth="1"/>
-    <col min="4" max="4" width="29.7109375" style="11" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" style="10" customWidth="1"/>
-    <col min="6" max="6" width="18.7109375" style="10" customWidth="1"/>
-    <col min="7" max="7" width="17.7109375" style="10" customWidth="1"/>
-    <col min="8" max="8" width="50.7109375" style="9" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="9"/>
+    <col min="1" max="1" width="9.7109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="3.7109375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" style="5" customWidth="1"/>
+    <col min="4" max="4" width="29.7109375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" style="4" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" style="4" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" style="4" customWidth="1"/>
+    <col min="8" max="8" width="50.7109375" style="3" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="2" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A2" s="16">
+      <c r="A2" s="6">
         <v>964236001</v>
       </c>
-      <c r="B2" s="16">
+      <c r="B2" s="6">
         <v>1</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="18">
+      <c r="E2" s="8">
         <v>3.94</v>
       </c>
-      <c r="F2" s="18">
+      <c r="F2" s="8">
         <v>4</v>
       </c>
-      <c r="G2" s="18">
+      <c r="G2" s="8">
         <v>4.2</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="9" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A3" s="16">
+      <c r="A3" s="6">
         <v>964236001</v>
       </c>
-      <c r="B3" s="16">
+      <c r="B3" s="6">
         <v>2</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="18">
+      <c r="E3" s="8">
         <v>3.81</v>
       </c>
-      <c r="F3" s="18">
+      <c r="F3" s="8">
         <v>4.2</v>
       </c>
-      <c r="G3" s="18">
+      <c r="G3" s="8">
         <v>4.5</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="H3" s="9" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A4" s="16">
+      <c r="A4" s="6">
         <v>964236001</v>
       </c>
-      <c r="B4" s="16">
+      <c r="B4" s="6">
         <v>3</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="18">
+      <c r="E4" s="8">
         <v>3.57</v>
       </c>
-      <c r="F4" s="18">
+      <c r="F4" s="8">
         <v>3.9</v>
       </c>
-      <c r="G4" s="18">
+      <c r="G4" s="8">
         <v>4.3</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="H4" s="9" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A5" s="16">
+      <c r="A5" s="6">
         <v>964236001</v>
       </c>
-      <c r="B5" s="16">
+      <c r="B5" s="6">
         <v>4</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="8">
         <v>3.71</v>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="8">
         <v>4.5</v>
       </c>
-      <c r="G5" s="18">
+      <c r="G5" s="8">
         <v>4.0999999999999996</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="H5" s="9" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A6" s="16">
+      <c r="A6" s="6">
         <v>964236001</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="6">
         <v>5</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="8">
         <v>3.48</v>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="8">
         <v>3.7</v>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="8">
         <v>4</v>
       </c>
-      <c r="H6" s="19" t="s">
+      <c r="H6" s="9" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A7" s="16">
+      <c r="A7" s="6">
         <v>964236001</v>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="6">
         <v>6</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="8">
         <v>3.78</v>
       </c>
-      <c r="F7" s="18">
+      <c r="F7" s="8">
         <v>4.0999999999999996</v>
       </c>
-      <c r="G7" s="18">
+      <c r="G7" s="8">
         <v>4.4000000000000004</v>
       </c>
-      <c r="H7" s="19" t="s">
+      <c r="H7" s="9" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A8" s="16">
+      <c r="A8" s="6">
         <v>964236001</v>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="6">
         <v>7</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="8">
         <v>3.39</v>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="8">
         <v>4.2</v>
       </c>
-      <c r="G8" s="18">
+      <c r="G8" s="8">
         <v>4.2</v>
       </c>
-      <c r="H8" s="19" t="s">
+      <c r="H8" s="9" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A9" s="16">
+      <c r="A9" s="6">
         <v>964236001</v>
       </c>
-      <c r="B9" s="16">
+      <c r="B9" s="6">
         <v>8</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="8">
         <v>3.54</v>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="8">
         <v>4.5999999999999996</v>
       </c>
-      <c r="G9" s="18">
+      <c r="G9" s="8">
         <v>4.5</v>
       </c>
-      <c r="H9" s="19" t="s">
+      <c r="H9" s="9" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A10" s="16">
+      <c r="A10" s="6">
         <v>964236001</v>
       </c>
-      <c r="B10" s="16">
+      <c r="B10" s="6">
         <v>9</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="8">
         <v>3.66</v>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="8">
         <v>3.8</v>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="8">
         <v>4.0999999999999996</v>
       </c>
-      <c r="H10" s="19" t="s">
+      <c r="H10" s="9" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="16">
+      <c r="A11" s="6">
         <v>964236001</v>
       </c>
-      <c r="B11" s="16">
+      <c r="B11" s="6">
         <v>10</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="8">
         <v>3.68</v>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="8">
         <v>4.7</v>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="8">
         <v>4.9000000000000004</v>
       </c>
-      <c r="H11" s="19" t="s">
+      <c r="H11" s="9" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A12" s="16">
+      <c r="A12" s="6">
         <v>1739129</v>
       </c>
-      <c r="B12" s="16">
+      <c r="B12" s="6">
         <v>1</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="8">
         <v>4.22</v>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="8">
         <v>4.2</v>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="8">
         <v>3.8</v>
       </c>
-      <c r="H12" s="19" t="s">
+      <c r="H12" s="9" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A13" s="16">
+      <c r="A13" s="6">
         <v>1739129</v>
       </c>
-      <c r="B13" s="16">
+      <c r="B13" s="6">
         <v>2</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="8">
         <v>3.96</v>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="8">
         <v>3.6</v>
       </c>
-      <c r="G13" s="18">
+      <c r="G13" s="8">
         <v>3.6</v>
       </c>
-      <c r="H13" s="19" t="s">
+      <c r="H13" s="9" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="16">
+      <c r="A14" s="6">
         <v>1739129</v>
       </c>
-      <c r="B14" s="16">
+      <c r="B14" s="6">
         <v>3</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="8">
         <v>4.0199999999999996</v>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="8">
         <v>4.4000000000000004</v>
       </c>
-      <c r="G14" s="18">
+      <c r="G14" s="8">
         <v>4.3</v>
       </c>
-      <c r="H14" s="19" t="s">
+      <c r="H14" s="9" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A15" s="16">
+      <c r="A15" s="6">
         <v>1739129</v>
       </c>
-      <c r="B15" s="16">
+      <c r="B15" s="6">
         <v>4</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="17" t="s">
+      <c r="D15" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="8">
         <v>3.83</v>
       </c>
-      <c r="F15" s="18">
+      <c r="F15" s="8">
         <v>3.5</v>
       </c>
-      <c r="G15" s="18">
+      <c r="G15" s="8">
         <v>3.6</v>
       </c>
-      <c r="H15" s="19" t="s">
+      <c r="H15" s="9" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="16">
+      <c r="A16" s="6">
         <v>1739129</v>
       </c>
-      <c r="B16" s="16">
+      <c r="B16" s="6">
         <v>5</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D16" s="17" t="s">
+      <c r="D16" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E16" s="18">
+      <c r="E16" s="8">
         <v>3.9</v>
       </c>
-      <c r="F16" s="18">
+      <c r="F16" s="8">
         <v>3.8</v>
       </c>
-      <c r="G16" s="18">
+      <c r="G16" s="8">
         <v>3.8</v>
       </c>
-      <c r="H16" s="19" t="s">
+      <c r="H16" s="9" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A17" s="16">
+      <c r="A17" s="6">
         <v>1739129</v>
       </c>
-      <c r="B17" s="16">
+      <c r="B17" s="6">
         <v>6</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D17" s="17" t="s">
+      <c r="D17" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="18">
+      <c r="E17" s="8">
         <v>3.93</v>
       </c>
-      <c r="F17" s="18">
+      <c r="F17" s="8">
         <v>3.7</v>
       </c>
-      <c r="G17" s="18">
+      <c r="G17" s="8">
         <v>4</v>
       </c>
-      <c r="H17" s="19" t="s">
+      <c r="H17" s="9" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="16">
+      <c r="A18" s="6">
         <v>1739129</v>
       </c>
-      <c r="B18" s="16">
+      <c r="B18" s="6">
         <v>7</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C18" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="17" t="s">
+      <c r="D18" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="E18" s="18">
+      <c r="E18" s="8">
         <v>4.43</v>
       </c>
-      <c r="F18" s="18">
+      <c r="F18" s="8">
         <v>5</v>
       </c>
-      <c r="G18" s="18">
+      <c r="G18" s="8">
         <v>4.5999999999999996</v>
       </c>
-      <c r="H18" s="19" t="s">
+      <c r="H18" s="9" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="16">
+      <c r="A19" s="6">
         <v>37452171</v>
       </c>
-      <c r="B19" s="16">
+      <c r="B19" s="6">
         <v>1</v>
       </c>
-      <c r="C19" s="17" t="s">
+      <c r="C19" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D19" s="17" t="s">
+      <c r="D19" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="E19" s="18" t="s">
+      <c r="E19" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="F19" s="18">
+      <c r="F19" s="8">
         <v>3.5</v>
       </c>
-      <c r="G19" s="18">
+      <c r="G19" s="8">
         <v>3.7</v>
       </c>
-      <c r="H19" s="19" t="s">
+      <c r="H19" s="9" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A20" s="16">
+      <c r="A20" s="6">
         <v>37452171</v>
       </c>
-      <c r="B20" s="16">
+      <c r="B20" s="6">
         <v>2</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="E20" s="18" t="s">
+      <c r="E20" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="F20" s="18">
+      <c r="F20" s="8">
         <v>3</v>
       </c>
-      <c r="G20" s="18">
+      <c r="G20" s="8">
         <v>3.4</v>
       </c>
-      <c r="H20" s="19" t="s">
+      <c r="H20" s="9" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A21" s="16">
+      <c r="A21" s="6">
         <v>37452171</v>
       </c>
-      <c r="B21" s="16">
+      <c r="B21" s="6">
         <v>3</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="C21" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="D21" s="17" t="s">
+      <c r="D21" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E21" s="18" t="s">
+      <c r="E21" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="F21" s="18">
+      <c r="F21" s="8">
         <v>3.5</v>
       </c>
-      <c r="G21" s="18">
+      <c r="G21" s="8">
         <v>3.8</v>
       </c>
-      <c r="H21" s="19" t="s">
+      <c r="H21" s="9" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A22" s="16">
+      <c r="A22" s="6">
         <v>37452171</v>
       </c>
-      <c r="B22" s="16">
+      <c r="B22" s="6">
         <v>4</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C22" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="D22" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="E22" s="18" t="s">
+      <c r="E22" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="F22" s="18">
+      <c r="F22" s="8">
         <v>3.5</v>
       </c>
-      <c r="G22" s="18">
+      <c r="G22" s="8">
         <v>3.6</v>
       </c>
-      <c r="H22" s="19" t="s">
+      <c r="H22" s="9" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A23" s="16">
+      <c r="A23" s="6">
         <v>37452171</v>
       </c>
-      <c r="B23" s="16">
+      <c r="B23" s="6">
         <v>5</v>
       </c>
-      <c r="C23" s="17" t="s">
+      <c r="C23" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="D23" s="17" t="s">
+      <c r="D23" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="E23" s="18" t="s">
+      <c r="E23" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="F23" s="18">
+      <c r="F23" s="8">
         <v>4</v>
       </c>
-      <c r="G23" s="18">
+      <c r="G23" s="8">
         <v>4.0999999999999996</v>
       </c>
-      <c r="H23" s="19" t="s">
+      <c r="H23" s="9" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="16">
+      <c r="A24" s="6">
         <v>37452171</v>
       </c>
-      <c r="B24" s="16">
+      <c r="B24" s="6">
         <v>6</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D24" s="17" t="s">
+      <c r="D24" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="E24" s="18" t="s">
+      <c r="E24" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="F24" s="18">
+      <c r="F24" s="8">
         <v>3</v>
       </c>
-      <c r="G24" s="18">
+      <c r="G24" s="8">
         <v>3.5</v>
       </c>
-      <c r="H24" s="19" t="s">
+      <c r="H24" s="9" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="16">
+      <c r="A25" s="6">
         <v>37452171</v>
       </c>
-      <c r="B25" s="16">
+      <c r="B25" s="6">
         <v>7</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="D25" s="17" t="s">
+      <c r="D25" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="E25" s="18" t="s">
+      <c r="E25" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="F25" s="18">
+      <c r="F25" s="8">
         <v>4</v>
       </c>
-      <c r="G25" s="18">
+      <c r="G25" s="8">
         <v>4.2</v>
       </c>
-      <c r="H25" s="19" t="s">
+      <c r="H25" s="9" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A26" s="16">
+      <c r="A26" s="6">
         <v>37452171</v>
       </c>
-      <c r="B26" s="16">
+      <c r="B26" s="6">
         <v>8</v>
       </c>
-      <c r="C26" s="17" t="s">
+      <c r="C26" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="D26" s="17" t="s">
+      <c r="D26" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="E26" s="18" t="s">
+      <c r="E26" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="F26" s="18">
+      <c r="F26" s="8">
         <v>3.5</v>
       </c>
-      <c r="G26" s="18">
+      <c r="G26" s="8">
         <v>3.7</v>
       </c>
-      <c r="H26" s="19" t="s">
+      <c r="H26" s="9" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A27" s="16">
+      <c r="A27" s="6">
         <v>37452171</v>
       </c>
-      <c r="B27" s="16">
+      <c r="B27" s="6">
         <v>9</v>
       </c>
-      <c r="C27" s="17" t="s">
+      <c r="C27" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="D27" s="17" t="s">
+      <c r="D27" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="E27" s="18" t="s">
+      <c r="E27" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="F27" s="18">
+      <c r="F27" s="8">
         <v>3</v>
       </c>
-      <c r="G27" s="18">
+      <c r="G27" s="8">
         <v>3.4</v>
       </c>
-      <c r="H27" s="19" t="s">
+      <c r="H27" s="9" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A28" s="16">
+      <c r="A28" s="6">
         <v>37452171</v>
       </c>
-      <c r="B28" s="16">
+      <c r="B28" s="6">
         <v>10</v>
       </c>
-      <c r="C28" s="17" t="s">
+      <c r="C28" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="D28" s="17" t="s">
+      <c r="D28" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="E28" s="18" t="s">
+      <c r="E28" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="F28" s="18">
+      <c r="F28" s="8">
         <v>3</v>
       </c>
-      <c r="G28" s="18">
+      <c r="G28" s="8">
         <v>3.5</v>
       </c>
-      <c r="H28" s="19" t="s">
+      <c r="H28" s="9" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A29" s="16">
+      <c r="A29" s="6">
         <v>37452171</v>
       </c>
-      <c r="B29" s="16">
+      <c r="B29" s="6">
         <v>11</v>
       </c>
-      <c r="C29" s="17" t="s">
+      <c r="C29" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="D29" s="17" t="s">
+      <c r="D29" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="E29" s="18" t="s">
+      <c r="E29" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="F29" s="18">
+      <c r="F29" s="8">
         <v>3.5</v>
       </c>
-      <c r="G29" s="18">
+      <c r="G29" s="8">
         <v>3.9</v>
       </c>
-      <c r="H29" s="19" t="s">
+      <c r="H29" s="9" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A30" s="16">
+      <c r="A30" s="6">
         <v>33790944</v>
       </c>
-      <c r="B30" s="16">
+      <c r="B30" s="6">
         <v>1</v>
       </c>
-      <c r="C30" s="17" t="s">
+      <c r="C30" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="D30" s="17" t="s">
+      <c r="D30" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="E30" s="18">
+      <c r="E30" s="8">
         <v>3.63</v>
       </c>
-      <c r="F30" s="18">
+      <c r="F30" s="8">
         <v>3.7</v>
       </c>
-      <c r="G30" s="18">
+      <c r="G30" s="8">
         <v>4.4000000000000004</v>
       </c>
-      <c r="H30" s="19" t="s">
+      <c r="H30" s="9" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A31" s="16">
+      <c r="A31" s="6">
         <v>33790944</v>
       </c>
-      <c r="B31" s="16">
+      <c r="B31" s="6">
         <v>2</v>
       </c>
-      <c r="C31" s="17" t="s">
+      <c r="C31" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="D31" s="17" t="s">
+      <c r="D31" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="E31" s="18">
+      <c r="E31" s="8">
         <v>3.72</v>
       </c>
-      <c r="F31" s="18">
+      <c r="F31" s="8">
         <v>4.0999999999999996</v>
       </c>
-      <c r="G31" s="18">
+      <c r="G31" s="8">
         <v>4.5</v>
       </c>
-      <c r="H31" s="19" t="s">
+      <c r="H31" s="9" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A32" s="16">
+      <c r="A32" s="6">
         <v>33790944</v>
       </c>
-      <c r="B32" s="16">
+      <c r="B32" s="6">
         <v>3</v>
       </c>
-      <c r="C32" s="17" t="s">
+      <c r="C32" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="D32" s="17" t="s">
+      <c r="D32" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="E32" s="18">
+      <c r="E32" s="8">
         <v>3.65</v>
       </c>
-      <c r="F32" s="18">
+      <c r="F32" s="8">
         <v>3.8</v>
       </c>
-      <c r="G32" s="18">
+      <c r="G32" s="8">
         <v>4</v>
       </c>
-      <c r="H32" s="19" t="s">
+      <c r="H32" s="9" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A33" s="16">
+      <c r="A33" s="6">
         <v>33790944</v>
       </c>
-      <c r="B33" s="16">
+      <c r="B33" s="6">
         <v>4</v>
       </c>
-      <c r="C33" s="17" t="s">
+      <c r="C33" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="D33" s="17" t="s">
+      <c r="D33" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="E33" s="18">
+      <c r="E33" s="8">
         <v>3.15</v>
       </c>
-      <c r="F33" s="18">
+      <c r="F33" s="8">
         <v>3.5</v>
       </c>
-      <c r="G33" s="18">
+      <c r="G33" s="8">
         <v>4.4000000000000004</v>
       </c>
-      <c r="H33" s="19" t="s">
+      <c r="H33" s="9" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A34" s="16">
+      <c r="A34" s="6">
         <v>33790944</v>
       </c>
-      <c r="B34" s="16">
+      <c r="B34" s="6">
         <v>5</v>
       </c>
-      <c r="C34" s="17" t="s">
+      <c r="C34" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="D34" s="17" t="s">
+      <c r="D34" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="E34" s="18">
+      <c r="E34" s="8">
         <v>3.35</v>
       </c>
-      <c r="F34" s="18">
+      <c r="F34" s="8">
         <v>3.6</v>
       </c>
-      <c r="G34" s="18">
+      <c r="G34" s="8">
         <v>4.5999999999999996</v>
       </c>
-      <c r="H34" s="19" t="s">
+      <c r="H34" s="9" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A35" s="16">
+      <c r="A35" s="6">
         <v>33790944</v>
       </c>
-      <c r="B35" s="16">
+      <c r="B35" s="6">
         <v>6</v>
       </c>
-      <c r="C35" s="17" t="s">
+      <c r="C35" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="D35" s="17" t="s">
+      <c r="D35" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="E35" s="18">
+      <c r="E35" s="8">
         <v>3.21</v>
       </c>
-      <c r="F35" s="18">
+      <c r="F35" s="8">
         <v>3.4</v>
       </c>
-      <c r="G35" s="18">
+      <c r="G35" s="8">
         <v>4.0999999999999996</v>
       </c>
-      <c r="H35" s="19" t="s">
+      <c r="H35" s="9" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A36" s="16">
+      <c r="A36" s="6">
         <v>33790944</v>
       </c>
-      <c r="B36" s="16">
+      <c r="B36" s="6">
         <v>7</v>
       </c>
-      <c r="C36" s="17" t="s">
+      <c r="C36" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="D36" s="17" t="s">
+      <c r="D36" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="E36" s="18">
+      <c r="E36" s="8">
         <v>3.12</v>
       </c>
-      <c r="F36" s="18">
+      <c r="F36" s="8">
         <v>3.2</v>
       </c>
-      <c r="G36" s="18">
+      <c r="G36" s="8">
         <v>4.0999999999999996</v>
       </c>
-      <c r="H36" s="19" t="s">
+      <c r="H36" s="9" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A37" s="16">
+      <c r="A37" s="6">
         <v>33790944</v>
       </c>
-      <c r="B37" s="16">
+      <c r="B37" s="6">
         <v>8</v>
       </c>
-      <c r="C37" s="17" t="s">
+      <c r="C37" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D37" s="17" t="s">
+      <c r="D37" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="E37" s="18">
+      <c r="E37" s="8">
         <v>3.43</v>
       </c>
-      <c r="F37" s="18">
+      <c r="F37" s="8">
         <v>3.7</v>
       </c>
-      <c r="G37" s="18">
+      <c r="G37" s="8">
         <v>4.4000000000000004</v>
       </c>
-      <c r="H37" s="19" t="s">
+      <c r="H37" s="9" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A38" s="16">
+      <c r="A38" s="6">
         <v>33790944</v>
       </c>
-      <c r="B38" s="16">
+      <c r="B38" s="6">
         <v>9</v>
       </c>
-      <c r="C38" s="17" t="s">
+      <c r="C38" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="D38" s="17" t="s">
+      <c r="D38" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="E38" s="18">
+      <c r="E38" s="8">
         <v>3.62</v>
       </c>
-      <c r="F38" s="18">
+      <c r="F38" s="8">
         <v>4.2</v>
       </c>
-      <c r="G38" s="18">
+      <c r="G38" s="8">
         <v>4.7</v>
       </c>
-      <c r="H38" s="19" t="s">
+      <c r="H38" s="9" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A39" s="16">
+      <c r="A39" s="6">
         <v>33790944</v>
       </c>
-      <c r="B39" s="16">
+      <c r="B39" s="6">
         <v>10</v>
       </c>
-      <c r="C39" s="17" t="s">
+      <c r="C39" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="D39" s="17" t="s">
+      <c r="D39" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="E39" s="18">
+      <c r="E39" s="8">
         <v>3.15</v>
       </c>
-      <c r="F39" s="18">
+      <c r="F39" s="8">
         <v>3.6</v>
       </c>
-      <c r="G39" s="18">
+      <c r="G39" s="8">
         <v>4.4000000000000004</v>
       </c>
-      <c r="H39" s="19" t="s">
+      <c r="H39" s="9" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A40" s="16">
+      <c r="A40" s="6">
         <v>926332</v>
       </c>
-      <c r="B40" s="16">
+      <c r="B40" s="6">
         <v>1</v>
       </c>
-      <c r="C40" s="17" t="s">
+      <c r="C40" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="D40" s="17" t="s">
+      <c r="D40" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="E40" s="18">
+      <c r="E40" s="8">
         <v>3.41</v>
       </c>
-      <c r="F40" s="18">
+      <c r="F40" s="8">
         <v>3.8</v>
       </c>
-      <c r="G40" s="18">
+      <c r="G40" s="8">
         <v>4.2</v>
       </c>
-      <c r="H40" s="19" t="s">
+      <c r="H40" s="9" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A41" s="16">
+      <c r="A41" s="6">
         <v>926332</v>
       </c>
-      <c r="B41" s="16">
+      <c r="B41" s="6">
         <v>2</v>
       </c>
-      <c r="C41" s="17" t="s">
+      <c r="C41" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="D41" s="17" t="s">
+      <c r="D41" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E41" s="18">
+      <c r="E41" s="8">
         <v>3.29</v>
       </c>
-      <c r="F41" s="18">
+      <c r="F41" s="8">
         <v>3.6</v>
       </c>
-      <c r="G41" s="18">
+      <c r="G41" s="8">
         <v>4.4000000000000004</v>
       </c>
-      <c r="H41" s="19" t="s">
+      <c r="H41" s="9" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A42" s="16">
+      <c r="A42" s="6">
         <v>926332</v>
       </c>
-      <c r="B42" s="16">
+      <c r="B42" s="6">
         <v>3</v>
       </c>
-      <c r="C42" s="17" t="s">
+      <c r="C42" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="D42" s="17" t="s">
+      <c r="D42" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="E42" s="18">
+      <c r="E42" s="8">
         <v>3.03</v>
       </c>
-      <c r="F42" s="18">
+      <c r="F42" s="8">
         <v>3.7</v>
       </c>
-      <c r="G42" s="18">
+      <c r="G42" s="8">
         <v>4.2</v>
       </c>
-      <c r="H42" s="19" t="s">
+      <c r="H42" s="9" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A43" s="16">
+      <c r="A43" s="6">
         <v>926332</v>
       </c>
-      <c r="B43" s="16">
+      <c r="B43" s="6">
         <v>4</v>
       </c>
-      <c r="C43" s="17" t="s">
+      <c r="C43" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="D43" s="17" t="s">
+      <c r="D43" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="E43" s="18">
+      <c r="E43" s="8">
         <v>3.08</v>
       </c>
-      <c r="F43" s="18">
+      <c r="F43" s="8">
         <v>3.5</v>
       </c>
-      <c r="G43" s="18">
+      <c r="G43" s="8">
         <v>3.8</v>
       </c>
-      <c r="H43" s="19" t="s">
+      <c r="H43" s="9" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A44" s="16">
+      <c r="A44" s="6">
         <v>926332</v>
       </c>
-      <c r="B44" s="16">
+      <c r="B44" s="6">
         <v>5</v>
       </c>
-      <c r="C44" s="17" t="s">
+      <c r="C44" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D44" s="17" t="s">
+      <c r="D44" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E44" s="18">
+      <c r="E44" s="8">
         <v>3.28</v>
       </c>
-      <c r="F44" s="18">
+      <c r="F44" s="8">
         <v>3.4</v>
       </c>
-      <c r="G44" s="18">
+      <c r="G44" s="8">
         <v>4.0999999999999996</v>
       </c>
-      <c r="H44" s="19" t="s">
+      <c r="H44" s="9" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A45" s="16">
+      <c r="A45" s="6">
         <v>926332</v>
       </c>
-      <c r="B45" s="16">
+      <c r="B45" s="6">
         <v>6</v>
       </c>
-      <c r="C45" s="17" t="s">
+      <c r="C45" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="D45" s="17" t="s">
+      <c r="D45" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="E45" s="18">
+      <c r="E45" s="8">
         <v>3.04</v>
       </c>
-      <c r="F45" s="18">
+      <c r="F45" s="8">
         <v>3.6</v>
       </c>
-      <c r="G45" s="18">
+      <c r="G45" s="8">
         <v>4.3</v>
       </c>
-      <c r="H45" s="19" t="s">
+      <c r="H45" s="9" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A46" s="16">
+      <c r="A46" s="6">
         <v>926332</v>
       </c>
-      <c r="B46" s="16">
+      <c r="B46" s="6">
         <v>7</v>
       </c>
-      <c r="C46" s="17" t="s">
+      <c r="C46" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="D46" s="17" t="s">
+      <c r="D46" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="E46" s="18">
+      <c r="E46" s="8">
         <v>3.45</v>
       </c>
-      <c r="F46" s="18">
+      <c r="F46" s="8">
         <v>5</v>
       </c>
-      <c r="G46" s="18">
+      <c r="G46" s="8">
         <v>4.5999999999999996</v>
       </c>
-      <c r="H46" s="19" t="s">
+      <c r="H46" s="9" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="42" x14ac:dyDescent="0.25">
-      <c r="A47" s="16">
+      <c r="A47" s="6">
         <v>10079558</v>
       </c>
-      <c r="B47" s="16">
+      <c r="B47" s="6">
         <v>1</v>
       </c>
-      <c r="C47" s="17" t="s">
+      <c r="C47" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="D47" s="17" t="s">
+      <c r="D47" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="E47" s="18">
+      <c r="E47" s="8">
         <v>3.91</v>
       </c>
-      <c r="F47" s="18">
+      <c r="F47" s="8">
         <v>4.3</v>
       </c>
-      <c r="G47" s="18">
+      <c r="G47" s="8">
         <v>4.8</v>
       </c>
-      <c r="H47" s="19" t="s">
+      <c r="H47" s="9" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A48" s="16">
+      <c r="A48" s="6">
         <v>10079558</v>
       </c>
-      <c r="B48" s="16">
+      <c r="B48" s="6">
         <v>2</v>
       </c>
-      <c r="C48" s="17" t="s">
+      <c r="C48" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="D48" s="17" t="s">
+      <c r="D48" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="E48" s="18">
+      <c r="E48" s="8">
         <v>3.63</v>
       </c>
-      <c r="F48" s="18">
+      <c r="F48" s="8">
         <v>3.6</v>
       </c>
-      <c r="G48" s="18">
+      <c r="G48" s="8">
         <v>4.3</v>
       </c>
-      <c r="H48" s="19" t="s">
+      <c r="H48" s="9" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A49" s="16">
+      <c r="A49" s="6">
         <v>10079558</v>
       </c>
-      <c r="B49" s="16">
+      <c r="B49" s="6">
         <v>3</v>
       </c>
-      <c r="C49" s="17" t="s">
+      <c r="C49" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="D49" s="17" t="s">
+      <c r="D49" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="E49" s="18">
+      <c r="E49" s="8">
         <v>4.04</v>
       </c>
-      <c r="F49" s="18">
+      <c r="F49" s="8">
         <v>4</v>
       </c>
-      <c r="G49" s="18">
+      <c r="G49" s="8">
         <v>4.5999999999999996</v>
       </c>
-      <c r="H49" s="19" t="s">
+      <c r="H49" s="9" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A50" s="16">
+      <c r="A50" s="6">
         <v>10079558</v>
       </c>
-      <c r="B50" s="16">
+      <c r="B50" s="6">
         <v>4</v>
       </c>
-      <c r="C50" s="17" t="s">
+      <c r="C50" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="D50" s="17" t="s">
+      <c r="D50" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="E50" s="18">
+      <c r="E50" s="8">
         <v>3.63</v>
       </c>
-      <c r="F50" s="18">
+      <c r="F50" s="8">
         <v>3.8</v>
       </c>
-      <c r="G50" s="18">
+      <c r="G50" s="8">
         <v>4.4000000000000004</v>
       </c>
-      <c r="H50" s="19" t="s">
+      <c r="H50" s="9" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A51" s="16">
+      <c r="A51" s="6">
         <v>10079558</v>
       </c>
-      <c r="B51" s="16">
+      <c r="B51" s="6">
         <v>5</v>
       </c>
-      <c r="C51" s="17" t="s">
+      <c r="C51" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="D51" s="17" t="s">
+      <c r="D51" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="E51" s="18">
+      <c r="E51" s="8">
         <v>3.67</v>
       </c>
-      <c r="F51" s="18">
+      <c r="F51" s="8">
         <v>3.7</v>
       </c>
-      <c r="G51" s="18">
+      <c r="G51" s="8">
         <v>4.3</v>
       </c>
-      <c r="H51" s="19" t="s">
+      <c r="H51" s="9" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A52" s="16">
+      <c r="A52" s="6">
         <v>10079558</v>
       </c>
-      <c r="B52" s="16">
+      <c r="B52" s="6">
         <v>6</v>
       </c>
-      <c r="C52" s="17" t="s">
+      <c r="C52" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="D52" s="17" t="s">
+      <c r="D52" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="E52" s="18">
+      <c r="E52" s="8">
         <v>4.03</v>
       </c>
-      <c r="F52" s="18">
+      <c r="F52" s="8">
         <v>4.2</v>
       </c>
-      <c r="G52" s="18">
+      <c r="G52" s="8">
         <v>4.5999999999999996</v>
       </c>
-      <c r="H52" s="19" t="s">
+      <c r="H52" s="9" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A53" s="16">
+      <c r="A53" s="6">
         <v>10079558</v>
       </c>
-      <c r="B53" s="16">
+      <c r="B53" s="6">
         <v>7</v>
       </c>
-      <c r="C53" s="17" t="s">
+      <c r="C53" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="D53" s="17" t="s">
+      <c r="D53" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="E53" s="18">
+      <c r="E53" s="8">
         <v>3.58</v>
       </c>
-      <c r="F53" s="18">
+      <c r="F53" s="8">
         <v>3.5</v>
       </c>
-      <c r="G53" s="18">
+      <c r="G53" s="8">
         <v>4.3</v>
       </c>
-      <c r="H53" s="19" t="s">
+      <c r="H53" s="9" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A54" s="16">
+      <c r="A54" s="6">
         <v>10079558</v>
       </c>
-      <c r="B54" s="16">
+      <c r="B54" s="6">
         <v>8</v>
       </c>
-      <c r="C54" s="17" t="s">
+      <c r="C54" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="D54" s="17" t="s">
+      <c r="D54" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="E54" s="18">
+      <c r="E54" s="8">
         <v>3.66</v>
       </c>
-      <c r="F54" s="18">
+      <c r="F54" s="8">
         <v>4.0999999999999996</v>
       </c>
-      <c r="G54" s="18">
+      <c r="G54" s="8">
         <v>4.7</v>
       </c>
-      <c r="H54" s="19" t="s">
+      <c r="H54" s="9" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A55" s="16">
+      <c r="A55" s="6">
         <v>10079558</v>
       </c>
-      <c r="B55" s="16">
+      <c r="B55" s="6">
         <v>9</v>
       </c>
-      <c r="C55" s="17" t="s">
+      <c r="C55" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="D55" s="17" t="s">
+      <c r="D55" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="E55" s="18">
+      <c r="E55" s="8">
         <v>3.73</v>
       </c>
-      <c r="F55" s="18">
+      <c r="F55" s="8">
         <v>3.7</v>
       </c>
-      <c r="G55" s="18">
+      <c r="G55" s="8">
         <v>4.5</v>
       </c>
-      <c r="H55" s="19" t="s">
+      <c r="H55" s="9" t="s">
         <v>208</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="42" x14ac:dyDescent="0.25">
+      <c r="A56" s="6">
+        <v>2027786</v>
+      </c>
+      <c r="B56" s="6">
+        <v>1</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="D56" s="7"/>
+      <c r="E56" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="F56" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="G56" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="H56" s="9" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A57" s="6">
+        <v>2027786</v>
+      </c>
+      <c r="B57" s="6">
+        <v>2</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="D57" s="7"/>
+      <c r="E57" s="8">
+        <v>3.42</v>
+      </c>
+      <c r="F57" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="G57" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="H57" s="9" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A58" s="6">
+        <v>2027786</v>
+      </c>
+      <c r="B58" s="6">
+        <v>3</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="D58" s="7"/>
+      <c r="E58" s="8">
+        <v>3.05</v>
+      </c>
+      <c r="F58" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="G58" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H58" s="9" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="42" x14ac:dyDescent="0.25">
+      <c r="A59" s="6">
+        <v>2027786</v>
+      </c>
+      <c r="B59" s="6">
+        <v>4</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="D59" s="7"/>
+      <c r="E59" s="8">
+        <v>3.44</v>
+      </c>
+      <c r="F59" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="G59" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="H59" s="9" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A60" s="6">
+        <v>2027786</v>
+      </c>
+      <c r="B60" s="6">
+        <v>5</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="D60" s="7"/>
+      <c r="E60" s="8">
+        <v>3.34</v>
+      </c>
+      <c r="F60" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="G60" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="H60" s="9" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A61" s="6">
+        <v>2027786</v>
+      </c>
+      <c r="B61" s="6">
+        <v>6</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="D61" s="7"/>
+      <c r="E61" s="8">
+        <v>3.31</v>
+      </c>
+      <c r="F61" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="G61" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H61" s="9" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A62" s="6">
+        <v>2027786</v>
+      </c>
+      <c r="B62" s="6">
+        <v>7</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="D62" s="7"/>
+      <c r="E62" s="8">
+        <v>2.97</v>
+      </c>
+      <c r="F62" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="G62" s="8">
+        <v>4</v>
+      </c>
+      <c r="H62" s="9" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="6">
+        <v>2027786</v>
+      </c>
+      <c r="B63" s="6">
+        <v>8</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="D63" s="7"/>
+      <c r="E63" s="8">
+        <v>2.96</v>
+      </c>
+      <c r="F63" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="G63" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H63" s="9" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A64" s="6">
+        <v>2027786</v>
+      </c>
+      <c r="B64" s="6">
+        <v>9</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D64" s="7"/>
+      <c r="E64" s="8">
+        <v>2.99</v>
+      </c>
+      <c r="F64" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G64" s="8">
+        <v>4.7</v>
+      </c>
+      <c r="H64" s="9" t="s">
+        <v>238</v>
       </c>
     </row>
   </sheetData>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01D67460-A34D-4F79-BBEE-6BAD35A4DE49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7950E99-8CAD-4E2B-8CC6-2736244884FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="270">
   <si>
     <t>No</t>
   </si>
@@ -738,6 +738,99 @@
   </si>
   <si>
     <t>Το αδιαμφισβήτητο magnum opus της μπάντας και η μεγαλύτερη επιτυχία τους [UK Top 14]. Εκπληκτική, συναισθηματικά φορτισμένη μπαλάντα 6+ λεπτών με συγκλονιστική ερμηνεία, έγχορδα και κορυφαία κιθαριστική κορύφωση. Reference ηχογράφηση με απίστευτο βάθος, αέρα στα πιάτα και πλούσιο layering στα όργανα</t>
+  </si>
+  <si>
+    <t>One Blue Morning</t>
+  </si>
+  <si>
+    <t>Goodbye My Love</t>
+  </si>
+  <si>
+    <t>Ain't Today Tomorrow's Yesterday</t>
+  </si>
+  <si>
+    <t>Hallelujah</t>
+  </si>
+  <si>
+    <t>Feeling Uneasy</t>
+  </si>
+  <si>
+    <t>Live In Jericho</t>
+  </si>
+  <si>
+    <t>Amon Düül II</t>
+  </si>
+  <si>
+    <t>Almost Alive…</t>
+  </si>
+  <si>
+    <t>Krautrock, Art Rock, Space Rock, Prog Rock</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το 10ο studio album των Krautrock/Prog πρωτοπόρων Amon Düül II (1977). Συνδυάζει πιο προσβάσιμες late-70s Art Rock φόρμουλες με το εντυπωσιακό 13λεπτο space-prog έπος «Live In Jericho». | Hard Facts Έκδοσης: Lacquer Cut στα θρυλικά Utopia Studios στο Λονδίνο (σύμβολο λύρας στα runouts) και πρεσάρισμα στη Γερμανία (Nova/Teldec). Matrix/Runout: 6.23 305-01-1 [Utopia lyre symbol] Manufactured in Germany / 6.23 305-01-2 [Utopia lyre symbol] Manufactured in Germany. Ηχητική Αξιολόγηση (4.5/5): Εξαιρετικό βρετανικό mastering από την Utopia με αέρινο soundstage, πολύ ήσυχο γερμανικό υπόβαθρο, πλούσια dynamic range και εξαιρετική ευκρίνεια στις πολυεπίπεδες ενορχηστρώσεις.</t>
+  </si>
+  <si>
+    <t>Nova (German First Pressing - Utopia Cut)</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/35339929-Amon-D%C3%BC%C3%BCl-II-Almost-Alive</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/sEqBfaQ9D1v9lwG_E9bm6wadhL7rDGKfvIgMin0lW2A/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTE0NDgz/OTgtMTIyMTAyMDk5/MS5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Pub Rock, Soft Rock</t>
+  </si>
+  <si>
+    <t>Blues Rock, Pub Rock</t>
+  </si>
+  <si>
+    <t>Soft Rock, AOR</t>
+  </si>
+  <si>
+    <t>Country Rock, Soft Rock</t>
+  </si>
+  <si>
+    <t>Hard Rock, Pub Rock</t>
+  </si>
+  <si>
+    <t>Pub Rock, Blues Rock</t>
+  </si>
+  <si>
+    <t>Prog Rock, Art Rock</t>
+  </si>
+  <si>
+    <t>Art Rock, Prog Rock, Soft Rock</t>
+  </si>
+  <si>
+    <t>Hard Rock, Art Rock</t>
+  </si>
+  <si>
+    <t>Art Rock, Pop Rock</t>
+  </si>
+  <si>
+    <t>Prog Rock, Hard Rock</t>
+  </si>
+  <si>
+    <t>Prog Rock, Space Rock, Krautrock</t>
+  </si>
+  <si>
+    <t>Πολύ δυνατή 7λεπτη έναρξη με εναλλαγές ακουστικών/ηλεκτρικών μερών, ρευστά synthesizer περάσματα και τα χαρακτηριστικά φωνητικά της Renate Knaup. Αέρινο Utopia mastering με εξαιρετικό διαχωρισμό στα keyboards.</t>
+  </si>
+  <si>
+    <t>Επιστρατεύει φωνητικά από τη Claudja Barry. Εκτεταμένη, μελωδική σύνθεση με ατμοσφαιρικά περάσματα. Πολύ ζεστή αναλογική υφή στα φωνητικά.</t>
+  </si>
+  <si>
+    <t>Ρυθμικό, πολυεπίπεδο track με έγχορδα σε ενορχήστρωση Jörg Evers και στιβαρό rhythm section. Σφιχτά transients στα τύμπανα και πλούσιο layering.</t>
+  </si>
+  <si>
+    <t>Σύντομο, ρυθμικό track με ιδιαίτερες φωνητικές γραμμές που ανοίγει τη B πλευρά. Καθαρή ηχογράφηση.</t>
+  </si>
+  <si>
+    <t>Δυναμικό track με ενδιαφέρουσες αλλαγές ρυθμού, σκοτεινή ατμόσφαιρα και καλά κιθαριστικά σόλο. Πολύ καλή στερεοφωνική εικόνα.</t>
+  </si>
+  <si>
+    <t>Το αδιαμφισβήτητο έπος του δίσκου. Ένας 13λεπτος progressive/space αυτοσχεδιαστικός χείμαρρος που θυμίζει τις χρυσές μέρες της μπάντας. Τεράστιο soundstage, βαθύ χαμηλό και αέρινα synth pads που δοκιμάζουν την ευκρίνεια του συστήματος.</t>
   </si>
 </sst>
 </file>
@@ -826,7 +919,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -855,17 +948,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1175,7 +1259,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="1" bestFit="1" customWidth="1"/>
@@ -1224,244 +1308,279 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="63" x14ac:dyDescent="0.25">
-      <c r="A2" s="10">
+      <c r="A2" s="6">
         <v>964236001</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="12">
+      <c r="E2" s="10">
         <v>3.37</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="J2" s="11" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="42" x14ac:dyDescent="0.25">
-      <c r="A3" s="10">
+      <c r="A3" s="6">
         <v>1739129</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="6">
         <v>2009</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="10">
         <v>3.78</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="J3" s="13" t="s">
+      <c r="J3" s="11" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="42" x14ac:dyDescent="0.25">
-      <c r="A4" s="10">
+      <c r="A4" s="6">
         <v>37452171</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="10">
         <v>3.73</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="I4" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="J4" s="11" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="42" x14ac:dyDescent="0.25">
-      <c r="A5" s="10">
+      <c r="A5" s="6">
         <v>33790944</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="10">
         <v>3.11</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="I5" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="J5" s="14" t="s">
+      <c r="J5" s="11" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="10">
+      <c r="A6" s="6">
         <v>926332</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="10">
         <v>3.29</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="I6" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="J6" s="14" t="s">
+      <c r="J6" s="11" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="63" x14ac:dyDescent="0.25">
-      <c r="A7" s="10">
+      <c r="A7" s="6">
         <v>10079558</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="10">
         <v>3.6</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="I7" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="J7" s="14" t="s">
+      <c r="J7" s="11" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="63" x14ac:dyDescent="0.25">
-      <c r="A8" s="10">
+      <c r="A8" s="6">
         <v>2027786</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="10">
         <v>3.45</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="H8" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="I8" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="J8" s="14" t="s">
+      <c r="J8" s="11" t="s">
         <v>221</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
+        <v>35339929</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D9" s="6">
+        <v>1977</v>
+      </c>
+      <c r="E9" s="10">
+        <v>2.84</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>251</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I3" r:id="rId1" xr:uid="{9C0994CE-C554-4210-BCA2-17F8D17FB784}"/>
-    <hyperlink ref="J2" r:id="rId2" xr:uid="{AD58B770-BB72-48BD-AE29-27E61830C8AC}"/>
-    <hyperlink ref="J3" r:id="rId3" xr:uid="{A295F22A-5B8A-48C2-8ADD-A473C972D75C}"/>
-    <hyperlink ref="I4" r:id="rId4" xr:uid="{B8F43599-8636-4878-AA63-74EF8E8FA4A0}"/>
-    <hyperlink ref="J4" r:id="rId5" xr:uid="{0383213A-C9D8-4706-B4BC-090F4D744EE5}"/>
-    <hyperlink ref="I5" r:id="rId6" xr:uid="{AB95816D-AFF8-4769-B964-AFEE7801899B}"/>
-    <hyperlink ref="J5" r:id="rId7" xr:uid="{25A0AA85-7925-4EA8-8C8E-F60C69923F4F}"/>
-    <hyperlink ref="I6" r:id="rId8" xr:uid="{5AE9F467-1B53-498C-B81D-02660B01BCA7}"/>
-    <hyperlink ref="J6" r:id="rId9" xr:uid="{AC0A6553-0986-4BB7-9D5A-C231F8C231FF}"/>
-    <hyperlink ref="I7" r:id="rId10" xr:uid="{24D188DA-4F4D-40DC-9308-931FFF6A0E7F}"/>
-    <hyperlink ref="J7" r:id="rId11" xr:uid="{B14913EA-FB65-4D7E-A85A-5BFD89D186DD}"/>
-    <hyperlink ref="I8" r:id="rId12" xr:uid="{84F45C40-1251-4DE1-88F3-8BC3CD9CE503}"/>
-    <hyperlink ref="J8" r:id="rId13" xr:uid="{2916FB00-92B8-41FF-873A-2CB7478D6FC5}"/>
+    <hyperlink ref="I4" r:id="rId1" xr:uid="{B8F43599-8636-4878-AA63-74EF8E8FA4A0}"/>
+    <hyperlink ref="J4" r:id="rId2" xr:uid="{0383213A-C9D8-4706-B4BC-090F4D744EE5}"/>
+    <hyperlink ref="I5" r:id="rId3" xr:uid="{AB95816D-AFF8-4769-B964-AFEE7801899B}"/>
+    <hyperlink ref="J5" r:id="rId4" xr:uid="{25A0AA85-7925-4EA8-8C8E-F60C69923F4F}"/>
+    <hyperlink ref="I6" r:id="rId5" xr:uid="{5AE9F467-1B53-498C-B81D-02660B01BCA7}"/>
+    <hyperlink ref="J6" r:id="rId6" xr:uid="{AC0A6553-0986-4BB7-9D5A-C231F8C231FF}"/>
+    <hyperlink ref="I7" r:id="rId7" xr:uid="{24D188DA-4F4D-40DC-9308-931FFF6A0E7F}"/>
+    <hyperlink ref="J7" r:id="rId8" xr:uid="{B14913EA-FB65-4D7E-A85A-5BFD89D186DD}"/>
+    <hyperlink ref="I8" r:id="rId9" xr:uid="{84F45C40-1251-4DE1-88F3-8BC3CD9CE503}"/>
+    <hyperlink ref="J8" r:id="rId10" xr:uid="{2916FB00-92B8-41FF-873A-2CB7478D6FC5}"/>
+    <hyperlink ref="I9" r:id="rId11" xr:uid="{669AAD1D-6FB3-4BE1-9EC0-D6FE3CB4304D}"/>
+    <hyperlink ref="I2" r:id="rId12" xr:uid="{7D09EF64-81E8-4700-B5A5-D38E3A5C492A}"/>
+    <hyperlink ref="I3" r:id="rId13" xr:uid="{BB1EEAD6-C614-40E2-A50B-1EEB4DCC9896}"/>
+    <hyperlink ref="J2" r:id="rId14" xr:uid="{49D10AEE-6D1A-4296-92C2-D587EAECD209}"/>
+    <hyperlink ref="J3" r:id="rId15" xr:uid="{2470A1B8-40B8-42E7-9CB8-1E35669D6179}"/>
+    <hyperlink ref="J9" r:id="rId16" xr:uid="{02D0C9ED-45B1-40B7-B545-8796C14C1EDD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1469,7 +1588,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="3" customWidth="1"/>
@@ -2923,7 +3042,9 @@
       <c r="C56" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="D56" s="7"/>
+      <c r="D56" s="7" t="s">
+        <v>252</v>
+      </c>
       <c r="E56" s="8">
         <v>3.6</v>
       </c>
@@ -2947,7 +3068,9 @@
       <c r="C57" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="D57" s="7"/>
+      <c r="D57" s="7" t="s">
+        <v>253</v>
+      </c>
       <c r="E57" s="8">
         <v>3.42</v>
       </c>
@@ -2971,7 +3094,9 @@
       <c r="C58" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="D58" s="7"/>
+      <c r="D58" s="7" t="s">
+        <v>204</v>
+      </c>
       <c r="E58" s="8">
         <v>3.05</v>
       </c>
@@ -2995,7 +3120,9 @@
       <c r="C59" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="D59" s="7"/>
+      <c r="D59" s="7" t="s">
+        <v>254</v>
+      </c>
       <c r="E59" s="8">
         <v>3.44</v>
       </c>
@@ -3019,7 +3146,9 @@
       <c r="C60" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="D60" s="7"/>
+      <c r="D60" s="7" t="s">
+        <v>253</v>
+      </c>
       <c r="E60" s="8">
         <v>3.34</v>
       </c>
@@ -3043,7 +3172,9 @@
       <c r="C61" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="D61" s="7"/>
+      <c r="D61" s="7" t="s">
+        <v>255</v>
+      </c>
       <c r="E61" s="8">
         <v>3.31</v>
       </c>
@@ -3067,7 +3198,9 @@
       <c r="C62" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="D62" s="7"/>
+      <c r="D62" s="7" t="s">
+        <v>256</v>
+      </c>
       <c r="E62" s="8">
         <v>2.97</v>
       </c>
@@ -3091,7 +3224,9 @@
       <c r="C63" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="D63" s="7"/>
+      <c r="D63" s="7" t="s">
+        <v>257</v>
+      </c>
       <c r="E63" s="8">
         <v>2.96</v>
       </c>
@@ -3115,7 +3250,9 @@
       <c r="C64" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="D64" s="7"/>
+      <c r="D64" s="7" t="s">
+        <v>206</v>
+      </c>
       <c r="E64" s="8">
         <v>2.99</v>
       </c>
@@ -3127,6 +3264,162 @@
       </c>
       <c r="H64" s="9" t="s">
         <v>238</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="42" x14ac:dyDescent="0.25">
+      <c r="A65" s="6">
+        <v>35339929</v>
+      </c>
+      <c r="B65" s="6">
+        <v>1</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="E65" s="8">
+        <v>3.07</v>
+      </c>
+      <c r="F65" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="G65" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H65" s="9" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A66" s="6">
+        <v>35339929</v>
+      </c>
+      <c r="B66" s="6">
+        <v>2</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="E66" s="8">
+        <v>2.81</v>
+      </c>
+      <c r="F66" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="G66" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="H66" s="9" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A67" s="6">
+        <v>35339929</v>
+      </c>
+      <c r="B67" s="6">
+        <v>3</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="E67" s="8">
+        <v>3.31</v>
+      </c>
+      <c r="F67" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="G67" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H67" s="9" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A68" s="6">
+        <v>35339929</v>
+      </c>
+      <c r="B68" s="6">
+        <v>4</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="E68" s="8">
+        <v>3.24</v>
+      </c>
+      <c r="F68" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="G68" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H68" s="9" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A69" s="6">
+        <v>35339929</v>
+      </c>
+      <c r="B69" s="6">
+        <v>5</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="E69" s="8">
+        <v>3.27</v>
+      </c>
+      <c r="F69" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="G69" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="H69" s="9" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="42" x14ac:dyDescent="0.25">
+      <c r="A70" s="6">
+        <v>35339929</v>
+      </c>
+      <c r="B70" s="6">
+        <v>6</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="E70" s="8">
+        <v>3.51</v>
+      </c>
+      <c r="F70" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="G70" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H70" s="9" t="s">
+        <v>269</v>
       </c>
     </row>
   </sheetData>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7950E99-8CAD-4E2B-8CC6-2736244884FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D09389D3-3BEB-4EBA-85E1-7033C8BB2A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="291">
   <si>
     <t>No</t>
   </si>
@@ -831,6 +831,69 @@
   </si>
   <si>
     <t>Το αδιαμφισβήτητο έπος του δίσκου. Ένας 13λεπτος progressive/space αυτοσχεδιαστικός χείμαρρος που θυμίζει τις χρυσές μέρες της μπάντας. Τεράστιο soundstage, βαθύ χαμηλό και αέρινα synth pads που δοκιμάζουν την ευκρίνεια του συστήματος.</t>
+  </si>
+  <si>
+    <t>Eleanor Rigby</t>
+  </si>
+  <si>
+    <t>Still Life</t>
+  </si>
+  <si>
+    <t>Painted Lady</t>
+  </si>
+  <si>
+    <t>Obsession</t>
+  </si>
+  <si>
+    <t>The Rape</t>
+  </si>
+  <si>
+    <t>Last Tango</t>
+  </si>
+  <si>
+    <t>Esperanto</t>
+  </si>
+  <si>
+    <t>May 1975</t>
+  </si>
+  <si>
+    <t>Symphonic Rock, Prog Rock, Art Rock</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το κύκνειο άσμα των Esperanto (1975) και το απόλυτο αριστούργημά τους. Ένα υπερ-φιλόδοξο Symphonic Prog Rock διαμάντι με πλούσια έγχορδα (βιολιά/τσέλα) και τη μνημειώδη διασκευή στο «Eleanor Rigby». | Hard Facts Έκδοσης: US Promo Pressing (White Label/DJ) πρεσαρισμένο στο εργοστάσιο της Columbia στο Pitman, New Jersey από τα πρώτα stampers (P1). Matrix/Runout: A&amp;M SP4785-P1 / A&amp;M SP4786-P1. Ηχητική Αξιολόγηση (4.7/5): Κορυφαία promo ακρόαση με τεράστιο dynamic range. Εκπληκτικός διαχωρισμός στα βιολιά και τα τσέλα, αέρινα ψηλά και μηδενικός θόρυβος επιφάνειας λόγω των φρέσκων P1 matrices.</t>
+  </si>
+  <si>
+    <t>A&amp;M Records (US Promo Pressing - Pitman P1 Cut)</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/31106519-Esperanto-Last-Tango</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/10MEdFRtYIJU7qTHbPxrMPW1fP5nMPKfRsRj7geZKKs/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTMxMTA2/NTE5LTE3MTk4MzM5/NTItNzYxMy5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Symphonic Rock, Prog Rock</t>
+  </si>
+  <si>
+    <t>Symphonic Rock, Art Rock</t>
+  </si>
+  <si>
+    <t>Μία από τις πιο εμπνευσμένες και επικές διασκευές στο κλασικό κομμάτι των Beatles. Εκρηκτικό ξεκίνημα με καταιγιστικά έγχορδα, hard rock κιθάρες και πολυεπίπεδα φωνητικά. Τεράστιο dynamic range, εκπληκτική αίσθηση του χώρου στα έγχορδα και φοβερά transients στα κύμβαλα.</t>
+  </si>
+  <si>
+    <t>Λυρική, μελωδική σύνθεση με όμορφη ανάπτυξη στα ακουστικά όργανα και τα φωνητικά του Keith Christmas. Πολύ καθαρός διαχωρισμός στα έγχορδα και ζεστή αναλογική υφή.</t>
+  </si>
+  <si>
+    <t>Δυναμικό track με κοφτά riffs, επιθετικά βιολιά και εξαιρετική ρυθμική ενέργεια που κλείνει ιδανικά την A πλευρά. Σφιχτό rhythm section με γρήγορα transients.</t>
+  </si>
+  <si>
+    <t>Ατμοσφαιρικό άνοιγμα της B πλευράς με σκοτεινά θέματα στα βιολιά και περίτεχνες αλλαγές μέτρου. Ευρύ soundstage με πλούσιο layering στα όργανα.</t>
+  </si>
+  <si>
+    <t>Δυνατό, δραματικό έπος με έντονη θεατρικότητα, πολύπλοκες συμφωνικές δομές και κιθαριστικά ξεσπάσματα. Εκπληκτική δυναμική περιοχή στα περάσματα από τα χαμηλόφωνα έγχορδα στις πλήρεις tutti κλιμακώσεις.</t>
+  </si>
+  <si>
+    <t>Το ομώνυμο track που κλείνει το άλμπουμ. Ιδιόμορφος συνδυασμός ρυθμού tango με symphonic prog, πλούσιες αρμονίες και εντυπωσιακό φινάλε. Πολύ καλή στερεοφωνική εικόνα και φυσικότητα στις ψηλές συχνότητες των βιολιών.</t>
   </si>
 </sst>
 </file>
@@ -1259,7 +1322,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="1" bestFit="1" customWidth="1"/>
@@ -1563,6 +1626,38 @@
         <v>251</v>
       </c>
     </row>
+    <row r="10" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
+        <v>31106519</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="E10" s="10">
+        <v>3.69</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>282</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="I4" r:id="rId1" xr:uid="{B8F43599-8636-4878-AA63-74EF8E8FA4A0}"/>
@@ -1581,6 +1676,8 @@
     <hyperlink ref="J2" r:id="rId14" xr:uid="{49D10AEE-6D1A-4296-92C2-D587EAECD209}"/>
     <hyperlink ref="J3" r:id="rId15" xr:uid="{2470A1B8-40B8-42E7-9CB8-1E35669D6179}"/>
     <hyperlink ref="J9" r:id="rId16" xr:uid="{02D0C9ED-45B1-40B7-B545-8796C14C1EDD}"/>
+    <hyperlink ref="I10" r:id="rId17" xr:uid="{538D88B9-C4FF-4DC8-B052-5482F535D3F2}"/>
+    <hyperlink ref="J10" r:id="rId18" xr:uid="{BA6CBFDC-FFDE-41CF-AA5C-8D87A3AF9F62}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1588,7 +1685,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="3" customWidth="1"/>
@@ -3422,6 +3519,162 @@
         <v>269</v>
       </c>
     </row>
+    <row r="71" spans="1:8" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A71" s="6">
+        <v>31106519</v>
+      </c>
+      <c r="B71" s="6">
+        <v>1</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="E71" s="8">
+        <v>4.17</v>
+      </c>
+      <c r="F71" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="G71" s="8">
+        <v>4.7</v>
+      </c>
+      <c r="H71" s="9" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A72" s="6">
+        <v>31106519</v>
+      </c>
+      <c r="B72" s="6">
+        <v>2</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="E72" s="8">
+        <v>3.52</v>
+      </c>
+      <c r="F72" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="G72" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="H72" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A73" s="6">
+        <v>31106519</v>
+      </c>
+      <c r="B73" s="6">
+        <v>3</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="E73" s="8">
+        <v>2.91</v>
+      </c>
+      <c r="F73" s="8">
+        <v>4</v>
+      </c>
+      <c r="G73" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H73" s="9" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A74" s="6">
+        <v>31106519</v>
+      </c>
+      <c r="B74" s="6">
+        <v>4</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="E74" s="8">
+        <v>3.38</v>
+      </c>
+      <c r="F74" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="G74" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H74" s="9" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="42" x14ac:dyDescent="0.25">
+      <c r="A75" s="6">
+        <v>31106519</v>
+      </c>
+      <c r="B75" s="6">
+        <v>5</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="E75" s="8">
+        <v>3.67</v>
+      </c>
+      <c r="F75" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="G75" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H75" s="9" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="42" x14ac:dyDescent="0.25">
+      <c r="A76" s="6">
+        <v>31106519</v>
+      </c>
+      <c r="B76" s="6">
+        <v>6</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="E76" s="8">
+        <v>3.04</v>
+      </c>
+      <c r="F76" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="G76" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="H76" s="9" t="s">
+        <v>290</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D09389D3-3BEB-4EBA-85E1-7033C8BB2A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D1709B4-D69C-4EFE-B629-E265DA06BA20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="312">
   <si>
     <t>No</t>
   </si>
@@ -32,9 +32,6 @@
     <t>House Of Mirrors</t>
   </si>
   <si>
-    <t>29 May 2026</t>
-  </si>
-  <si>
     <t>Red Rocking Chair</t>
   </si>
   <si>
@@ -548,9 +545,6 @@
     <t>If I Were Brittania I'd Waive the Rules</t>
   </si>
   <si>
-    <t>23 April 1976</t>
-  </si>
-  <si>
     <t>A&amp;M Records (UK First Pressing - Arun Chakraverty Cut)</t>
   </si>
   <si>
@@ -569,12 +563,6 @@
     <t>Time Passages</t>
   </si>
   <si>
-    <t>8 September 1978</t>
-  </si>
-  <si>
-    <t>25 April 2025</t>
-  </si>
-  <si>
     <t>Soft Rock, Folk Rock, Pop Rock, Art Rock</t>
   </si>
   <si>
@@ -671,9 +659,6 @@
     <t>Downtown Tonight</t>
   </si>
   <si>
-    <t>September 1976</t>
-  </si>
-  <si>
     <t>Soft Rock, Blues Rock, AOR, Pub Rock</t>
   </si>
   <si>
@@ -854,9 +839,6 @@
     <t>Esperanto</t>
   </si>
   <si>
-    <t>May 1975</t>
-  </si>
-  <si>
     <t>Symphonic Rock, Prog Rock, Art Rock</t>
   </si>
   <si>
@@ -894,6 +876,87 @@
   </si>
   <si>
     <t>Το ομώνυμο track που κλείνει το άλμπουμ. Ιδιόμορφος συνδυασμός ρυθμού tango με symphonic prog, πλούσιες αρμονίες και εντυπωσιακό φινάλε. Πολύ καλή στερεοφωνική εικόνα και φυσικότητα στις ψηλές συχνότητες των βιολιών.</t>
+  </si>
+  <si>
+    <t>The Allman Brothers Band</t>
+  </si>
+  <si>
+    <t>Blues Rock, Southern Rock, Hard Rock</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το μνημειώδες ντεμπούτο των The Allman Brothers Band (1969) που σηματοδότησε τη γέννηση του Southern Rock. Περιλαμβάνει τις διπλές κιθάρες των Duane Allman &amp; Dickey Betts και τα διαχρονικά έπη «Dreams» και «Whipping Post». | Hard Facts Έκδοσης: Σειρά «Blues In Vinile» (Repress ID 28392787). Lacquer Cut στα SST Studios από τον Martin Krenkel (σφραγίδα Kr SST) και πρεσάρισμα 180g στο γαλλικό εργοστάσιο MPO. Matrix/Runout: LPBI ALMANDBB A Kr SST MPO MPO21229517 / LPBI ALMANDBB B Kr SST MPO MPO21229427. Ηχητική Αξιολόγηση (4.7/5): Εξαιρετική αναλογική μεταφορά με σφιχτό μπάσο, φοβερή αίσθηση του Hammond B3 και των διπλών τυμπάνων, πολύ χαμηλό noise floor λόγω του MPO πρεσαρίσματος.</t>
+  </si>
+  <si>
+    <t>Polydor / DeAgostini (Italian Repress - 180g / SST Kr Cut / MPO)</t>
+  </si>
+  <si>
+    <t>1969 (Reissue Release)</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/28392787-The-Allman-Brothers-Band-The-Allman-Brothers-Band</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/iSEANs6nvVWtyqWE9xle0On1YdI4LoLDOjkJN1LQDWA/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI4Mzky/Nzg3LTE2OTc5NjQ2/NDUtMTUwNS5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Whipping Post</t>
+  </si>
+  <si>
+    <t>Dreams</t>
+  </si>
+  <si>
+    <t>Black Hearted Woman</t>
+  </si>
+  <si>
+    <t>Don't Want You No More</t>
+  </si>
+  <si>
+    <t>Trouble No More</t>
+  </si>
+  <si>
+    <t>Every Hungry Woman</t>
+  </si>
+  <si>
+    <t>It's Not My Cross To Bear</t>
+  </si>
+  <si>
+    <t>Blues Rock, Jazz Rock</t>
+  </si>
+  <si>
+    <t>Blues Rock, Southern Rock</t>
+  </si>
+  <si>
+    <t>Blues Rock, Hard Rock</t>
+  </si>
+  <si>
+    <t>Blues Rock, Electric Blues</t>
+  </si>
+  <si>
+    <t>Southern Rock, Psychedelic Rock, Blues Rock</t>
+  </si>
+  <si>
+    <t>Southern Rock, Blues Rock, Hard Rock</t>
+  </si>
+  <si>
+    <t>Το αδιαμφισβήτητο magnum opus του δίσκου. Έπος σε 11/8 μέτρο, γεμάτο οργή, πάθος και οργανική τελειότητα. Εκρηκτική δυναμική περιοχή, φοβερά transients στο μπάσο του Berry Oakley και τις κάσες των τυμπάνων.</t>
+  </si>
+  <si>
+    <t>Το απόλυτο ψυχεδελικό/blues διαμάντι 7+ λεπτών σε 3/4 μέτρο. Καθηλωτική ερμηνεία και ένα από τα σπουδαιότερα σόλο κιθάρας στην ιστορία της ροκ. Reference ηχογράφηση. Τεράστιο βάθος πεδίου, αέρινα Hammond pads και εκπληκτική φυσικότητα.</t>
+  </si>
+  <si>
+    <t>Δυναμικό άνοιγμα για τη Β πλευρά με ρυθμικές αλλαγές μέτρου και έντονη αλληλεπίδραση στις κιθάρες. Πλούσιες μεσαίες συχνότητες και καθαρά φωνητικά.</t>
+  </si>
+  <si>
+    <t>Η κλασική διασκευή στο κομμάτι του Muddy Waters. Αυθεντικό, ηλεκτρικό blues με το slide του Duane Allman σε πρώτο πλάνο. Φυσικός ήχος στους ενισχυτές και εξαιρετική στερεοφωνική εικόνα.</t>
+  </si>
+  <si>
+    <t>Up-tempo, επιθετικό track με δυνατά κιθαριστικά riffs και εξαιρετικό jamming στο μεσαίο μέρος. Δυναμικά τύμπανα με σφιχτή αίσθηση στις χαμηλές συχνότητες.</t>
+  </si>
+  <si>
+    <t>Απευθείας μετάβαση από το A1. Αργό, σκοτεινό blues με τη βραχνή, ψυχωμένη ερμηνεία του Gregg Allman και το θρυλικό slide του Duane. Βαθύ soundstage, ζεστή αναλογική υφή στα φωνητικά.</t>
+  </si>
+  <si>
+    <t>Καταιγιστικό, οργανικό instrumental άνοιγμα. Έντονο jazz-rock groove με το Hammond B3 και τις δίδυμες κιθάρες. Πολύ καθαρός διαχωρισμός στα κανάλια, αέρας στα πιάτα και γρήγορα transients στα τύμπανα.</t>
   </si>
 </sst>
 </file>
@@ -1322,52 +1385,52 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="38.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="34.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="96.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.7109375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="35.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="50.42578125" style="1" customWidth="1"/>
     <col min="11" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="J1" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="63" x14ac:dyDescent="0.25">
@@ -1380,26 +1443,26 @@
       <c r="C2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>3</v>
+      <c r="D2" s="6">
+        <v>2026</v>
       </c>
       <c r="E2" s="10">
         <v>3.37</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="42" x14ac:dyDescent="0.25">
@@ -1407,10 +1470,10 @@
         <v>1739129</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D3" s="6">
         <v>2009</v>
@@ -1419,19 +1482,19 @@
         <v>3.78</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="42" x14ac:dyDescent="0.25">
@@ -1439,31 +1502,31 @@
         <v>37452171</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>3</v>
+        <v>80</v>
+      </c>
+      <c r="D4" s="6">
+        <v>2026</v>
       </c>
       <c r="E4" s="10">
         <v>3.73</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G4" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="H4" s="6" t="s">
-        <v>79</v>
-      </c>
       <c r="I4" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="J4" s="11" t="s">
         <v>76</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="42" x14ac:dyDescent="0.25">
@@ -1471,31 +1534,31 @@
         <v>33790944</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>183</v>
+      <c r="D5" s="6">
+        <v>2025</v>
       </c>
       <c r="E5" s="10">
         <v>3.11</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G5" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="I5" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="H5" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="I5" s="11" t="s">
+      <c r="J5" s="11" t="s">
         <v>129</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
@@ -1503,31 +1566,31 @@
         <v>926332</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>175</v>
+      <c r="D6" s="6">
+        <v>1976</v>
       </c>
       <c r="E6" s="10">
         <v>3.29</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G6" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="J6" s="11" t="s">
         <v>177</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="63" x14ac:dyDescent="0.25">
@@ -1535,31 +1598,31 @@
         <v>10079558</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
+      </c>
+      <c r="D7" s="6">
+        <v>1978</v>
       </c>
       <c r="E7" s="10">
         <v>3.6</v>
       </c>
       <c r="F7" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="J7" s="11" t="s">
         <v>184</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="J7" s="11" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="63" x14ac:dyDescent="0.25">
@@ -1567,31 +1630,31 @@
         <v>2027786</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>216</v>
+        <v>211</v>
+      </c>
+      <c r="D8" s="6">
+        <v>1976</v>
       </c>
       <c r="E8" s="10">
         <v>3.45</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="63" x14ac:dyDescent="0.25">
@@ -1599,10 +1662,10 @@
         <v>35339929</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="D9" s="6">
         <v>1977</v>
@@ -1611,19 +1674,19 @@
         <v>2.84</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="63" x14ac:dyDescent="0.25">
@@ -1631,31 +1694,63 @@
         <v>31106519</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>277</v>
+        <v>270</v>
+      </c>
+      <c r="D10" s="6">
+        <v>1975</v>
       </c>
       <c r="E10" s="10">
         <v>3.69</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>282</v>
+        <v>276</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
+        <v>21229427</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="E11" s="10">
+        <v>3.8</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>291</v>
       </c>
     </row>
   </sheetData>
@@ -1678,6 +1773,8 @@
     <hyperlink ref="J9" r:id="rId16" xr:uid="{02D0C9ED-45B1-40B7-B545-8796C14C1EDD}"/>
     <hyperlink ref="I10" r:id="rId17" xr:uid="{538D88B9-C4FF-4DC8-B052-5482F535D3F2}"/>
     <hyperlink ref="J10" r:id="rId18" xr:uid="{BA6CBFDC-FFDE-41CF-AA5C-8D87A3AF9F62}"/>
+    <hyperlink ref="I11" r:id="rId19" xr:uid="{41088898-623F-47B4-BF91-B4B1CD818D4E}"/>
+    <hyperlink ref="J11" r:id="rId20" xr:uid="{E113C2CF-CD08-4D0D-B347-3943034BA748}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1685,44 +1782,44 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="3.7109375" style="4" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" style="5" customWidth="1"/>
-    <col min="4" max="4" width="29.7109375" style="5" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" style="4" customWidth="1"/>
-    <col min="6" max="6" width="18.7109375" style="4" customWidth="1"/>
-    <col min="7" max="7" width="17.7109375" style="4" customWidth="1"/>
+    <col min="1" max="1" width="9" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.42578125" style="4" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="50.7109375" style="3" customWidth="1"/>
     <col min="9" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="G1" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -1733,10 +1830,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E2" s="8">
         <v>3.94</v>
@@ -1748,7 +1845,7 @@
         <v>4.2</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -1759,10 +1856,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E3" s="8">
         <v>3.81</v>
@@ -1774,7 +1871,7 @@
         <v>4.5</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -1785,10 +1882,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E4" s="8">
         <v>3.57</v>
@@ -1800,7 +1897,7 @@
         <v>4.3</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -1811,10 +1908,10 @@
         <v>4</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E5" s="8">
         <v>3.71</v>
@@ -1826,7 +1923,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -1837,10 +1934,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E6" s="8">
         <v>3.48</v>
@@ -1852,7 +1949,7 @@
         <v>4</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -1863,10 +1960,10 @@
         <v>6</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E7" s="8">
         <v>3.78</v>
@@ -1878,7 +1975,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -1889,10 +1986,10 @@
         <v>7</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E8" s="8">
         <v>3.39</v>
@@ -1904,7 +2001,7 @@
         <v>4.2</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -1915,10 +2012,10 @@
         <v>8</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E9" s="8">
         <v>3.54</v>
@@ -1930,7 +2027,7 @@
         <v>4.5</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -1941,10 +2038,10 @@
         <v>9</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E10" s="8">
         <v>3.66</v>
@@ -1956,7 +2053,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
@@ -1967,10 +2064,10 @@
         <v>10</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E11" s="8">
         <v>3.68</v>
@@ -1982,7 +2079,7 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -1993,10 +2090,10 @@
         <v>1</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E12" s="8">
         <v>4.22</v>
@@ -2008,7 +2105,7 @@
         <v>3.8</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -2019,10 +2116,10 @@
         <v>2</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E13" s="8">
         <v>3.96</v>
@@ -2034,7 +2131,7 @@
         <v>3.6</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
@@ -2045,10 +2142,10 @@
         <v>3</v>
       </c>
       <c r="C14" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>47</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>48</v>
       </c>
       <c r="E14" s="8">
         <v>4.0199999999999996</v>
@@ -2060,7 +2157,7 @@
         <v>4.3</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -2071,10 +2168,10 @@
         <v>4</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E15" s="8">
         <v>3.83</v>
@@ -2086,7 +2183,7 @@
         <v>3.6</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -2097,10 +2194,10 @@
         <v>5</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E16" s="8">
         <v>3.9</v>
@@ -2112,7 +2209,7 @@
         <v>3.8</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -2123,10 +2220,10 @@
         <v>6</v>
       </c>
       <c r="C17" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="7" t="s">
         <v>44</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>45</v>
       </c>
       <c r="E17" s="8">
         <v>3.93</v>
@@ -2138,7 +2235,7 @@
         <v>4</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
@@ -2149,10 +2246,10 @@
         <v>7</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E18" s="8">
         <v>4.43</v>
@@ -2164,7 +2261,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
@@ -2175,13 +2272,13 @@
         <v>1</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F19" s="8">
         <v>3.5</v>
@@ -2190,7 +2287,7 @@
         <v>3.7</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -2201,13 +2298,13 @@
         <v>2</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F20" s="8">
         <v>3</v>
@@ -2216,7 +2313,7 @@
         <v>3.4</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -2227,13 +2324,13 @@
         <v>3</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F21" s="8">
         <v>3.5</v>
@@ -2242,7 +2339,7 @@
         <v>3.8</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -2253,13 +2350,13 @@
         <v>4</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F22" s="8">
         <v>3.5</v>
@@ -2268,7 +2365,7 @@
         <v>3.6</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -2279,13 +2376,13 @@
         <v>5</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F23" s="8">
         <v>4</v>
@@ -2294,7 +2391,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
@@ -2305,13 +2402,13 @@
         <v>6</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F24" s="8">
         <v>3</v>
@@ -2320,7 +2417,7 @@
         <v>3.5</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
@@ -2331,13 +2428,13 @@
         <v>7</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F25" s="8">
         <v>4</v>
@@ -2346,7 +2443,7 @@
         <v>4.2</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -2357,13 +2454,13 @@
         <v>8</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F26" s="8">
         <v>3.5</v>
@@ -2372,7 +2469,7 @@
         <v>3.7</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -2383,13 +2480,13 @@
         <v>9</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F27" s="8">
         <v>3</v>
@@ -2398,7 +2495,7 @@
         <v>3.4</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -2409,13 +2506,13 @@
         <v>10</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F28" s="8">
         <v>3</v>
@@ -2424,7 +2521,7 @@
         <v>3.5</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
@@ -2435,13 +2532,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D29" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="E29" s="8" t="s">
         <v>102</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>103</v>
       </c>
       <c r="F29" s="8">
         <v>3.5</v>
@@ -2450,7 +2547,7 @@
         <v>3.9</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
@@ -2461,10 +2558,10 @@
         <v>1</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E30" s="8">
         <v>3.63</v>
@@ -2476,7 +2573,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -2487,10 +2584,10 @@
         <v>2</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E31" s="8">
         <v>3.72</v>
@@ -2502,7 +2599,7 @@
         <v>4.5</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -2513,10 +2610,10 @@
         <v>3</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E32" s="8">
         <v>3.65</v>
@@ -2528,7 +2625,7 @@
         <v>4</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -2539,10 +2636,10 @@
         <v>4</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E33" s="8">
         <v>3.15</v>
@@ -2554,7 +2651,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -2565,10 +2662,10 @@
         <v>5</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E34" s="8">
         <v>3.35</v>
@@ -2580,7 +2677,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -2591,10 +2688,10 @@
         <v>6</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E35" s="8">
         <v>3.21</v>
@@ -2606,7 +2703,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -2617,10 +2714,10 @@
         <v>7</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E36" s="8">
         <v>3.12</v>
@@ -2632,7 +2729,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -2643,10 +2740,10 @@
         <v>8</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E37" s="8">
         <v>3.43</v>
@@ -2658,7 +2755,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -2669,10 +2766,10 @@
         <v>9</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E38" s="8">
         <v>3.62</v>
@@ -2684,7 +2781,7 @@
         <v>4.7</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -2695,10 +2792,10 @@
         <v>10</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E39" s="8">
         <v>3.15</v>
@@ -2710,7 +2807,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -2721,10 +2818,10 @@
         <v>1</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E40" s="8">
         <v>3.41</v>
@@ -2736,7 +2833,7 @@
         <v>4.2</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
@@ -2747,10 +2844,10 @@
         <v>2</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E41" s="8">
         <v>3.29</v>
@@ -2762,7 +2859,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
@@ -2773,10 +2870,10 @@
         <v>3</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E42" s="8">
         <v>3.03</v>
@@ -2788,7 +2885,7 @@
         <v>4.2</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
@@ -2799,10 +2896,10 @@
         <v>4</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E43" s="8">
         <v>3.08</v>
@@ -2814,7 +2911,7 @@
         <v>3.8</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -2825,10 +2922,10 @@
         <v>5</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E44" s="8">
         <v>3.28</v>
@@ -2840,7 +2937,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -2851,10 +2948,10 @@
         <v>6</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E45" s="8">
         <v>3.04</v>
@@ -2866,7 +2963,7 @@
         <v>4.3</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
@@ -2877,10 +2974,10 @@
         <v>7</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E46" s="8">
         <v>3.45</v>
@@ -2892,7 +2989,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="42" x14ac:dyDescent="0.25">
@@ -2903,10 +3000,10 @@
         <v>1</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E47" s="8">
         <v>3.91</v>
@@ -2918,7 +3015,7 @@
         <v>4.8</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
@@ -2929,10 +3026,10 @@
         <v>2</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E48" s="8">
         <v>3.63</v>
@@ -2944,7 +3041,7 @@
         <v>4.3</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
@@ -2955,10 +3052,10 @@
         <v>3</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E49" s="8">
         <v>4.04</v>
@@ -2970,7 +3067,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -2981,10 +3078,10 @@
         <v>4</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="E50" s="8">
         <v>3.63</v>
@@ -2996,7 +3093,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
@@ -3007,10 +3104,10 @@
         <v>5</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E51" s="8">
         <v>3.67</v>
@@ -3022,7 +3119,7 @@
         <v>4.3</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
@@ -3033,10 +3130,10 @@
         <v>6</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E52" s="8">
         <v>4.03</v>
@@ -3048,7 +3145,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
@@ -3059,10 +3156,10 @@
         <v>7</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="E53" s="8">
         <v>3.58</v>
@@ -3074,7 +3171,7 @@
         <v>4.3</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
@@ -3085,10 +3182,10 @@
         <v>8</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E54" s="8">
         <v>3.66</v>
@@ -3100,7 +3197,7 @@
         <v>4.7</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -3111,10 +3208,10 @@
         <v>9</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="E55" s="8">
         <v>3.73</v>
@@ -3126,7 +3223,7 @@
         <v>4.5</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="42" x14ac:dyDescent="0.25">
@@ -3137,10 +3234,10 @@
         <v>1</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E56" s="8">
         <v>3.6</v>
@@ -3152,7 +3249,7 @@
         <v>4.2</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
@@ -3163,10 +3260,10 @@
         <v>2</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="E57" s="8">
         <v>3.42</v>
@@ -3178,7 +3275,7 @@
         <v>4.5</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
@@ -3189,10 +3286,10 @@
         <v>3</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E58" s="8">
         <v>3.05</v>
@@ -3204,7 +3301,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="42" x14ac:dyDescent="0.25">
@@ -3215,10 +3312,10 @@
         <v>4</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="E59" s="8">
         <v>3.44</v>
@@ -3230,7 +3327,7 @@
         <v>4.5</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -3241,10 +3338,10 @@
         <v>5</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="E60" s="8">
         <v>3.34</v>
@@ -3256,7 +3353,7 @@
         <v>4.2</v>
       </c>
       <c r="H60" s="9" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -3267,10 +3364,10 @@
         <v>6</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E61" s="8">
         <v>3.31</v>
@@ -3282,7 +3379,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -3293,10 +3390,10 @@
         <v>7</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E62" s="8">
         <v>2.97</v>
@@ -3308,7 +3405,7 @@
         <v>4</v>
       </c>
       <c r="H62" s="9" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -3319,10 +3416,10 @@
         <v>8</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="E63" s="8">
         <v>2.96</v>
@@ -3334,7 +3431,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="52.5" x14ac:dyDescent="0.25">
@@ -3345,10 +3442,10 @@
         <v>9</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E64" s="8">
         <v>2.99</v>
@@ -3360,7 +3457,7 @@
         <v>4.7</v>
       </c>
       <c r="H64" s="9" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="42" x14ac:dyDescent="0.25">
@@ -3371,10 +3468,10 @@
         <v>1</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="E65" s="8">
         <v>3.07</v>
@@ -3386,7 +3483,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
@@ -3397,10 +3494,10 @@
         <v>2</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="E66" s="8">
         <v>2.81</v>
@@ -3412,7 +3509,7 @@
         <v>4.3</v>
       </c>
       <c r="H66" s="9" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
@@ -3423,10 +3520,10 @@
         <v>3</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E67" s="8">
         <v>3.31</v>
@@ -3438,7 +3535,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -3449,10 +3546,10 @@
         <v>4</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="E68" s="8">
         <v>3.24</v>
@@ -3464,7 +3561,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H68" s="9" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
@@ -3475,10 +3572,10 @@
         <v>5</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="E69" s="8">
         <v>3.27</v>
@@ -3490,7 +3587,7 @@
         <v>4.3</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="42" x14ac:dyDescent="0.25">
@@ -3501,10 +3598,10 @@
         <v>6</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="E70" s="8">
         <v>3.51</v>
@@ -3516,7 +3613,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H70" s="9" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="52.5" x14ac:dyDescent="0.25">
@@ -3527,10 +3624,10 @@
         <v>1</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="E71" s="8">
         <v>4.17</v>
@@ -3542,7 +3639,7 @@
         <v>4.7</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
@@ -3553,10 +3650,10 @@
         <v>2</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="E72" s="8">
         <v>3.52</v>
@@ -3568,7 +3665,7 @@
         <v>4.3</v>
       </c>
       <c r="H72" s="9" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
@@ -3579,10 +3676,10 @@
         <v>3</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="E73" s="8">
         <v>2.91</v>
@@ -3594,7 +3691,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
@@ -3605,10 +3702,10 @@
         <v>4</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="E74" s="8">
         <v>3.38</v>
@@ -3620,7 +3717,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H74" s="9" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="42" x14ac:dyDescent="0.25">
@@ -3631,10 +3728,10 @@
         <v>5</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="E75" s="8">
         <v>3.67</v>
@@ -3646,7 +3743,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="42" x14ac:dyDescent="0.25">
@@ -3657,10 +3754,10 @@
         <v>6</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="E76" s="8">
         <v>3.04</v>
@@ -3672,7 +3769,189 @@
         <v>4.5</v>
       </c>
       <c r="H76" s="9" t="s">
-        <v>290</v>
+        <v>284</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="42" x14ac:dyDescent="0.25">
+      <c r="A77" s="6">
+        <v>21229427</v>
+      </c>
+      <c r="B77" s="6">
+        <v>1</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="E77" s="8">
+        <v>3.86</v>
+      </c>
+      <c r="F77" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="G77" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="H77" s="9" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A78" s="6">
+        <v>21229427</v>
+      </c>
+      <c r="B78" s="6">
+        <v>2</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="E78" s="8">
+        <v>3.96</v>
+      </c>
+      <c r="F78" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G78" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H78" s="9" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A79" s="6">
+        <v>21229427</v>
+      </c>
+      <c r="B79" s="6">
+        <v>3</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="E79" s="8">
+        <v>3.84</v>
+      </c>
+      <c r="F79" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G79" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H79" s="9" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A80" s="6">
+        <v>21229427</v>
+      </c>
+      <c r="B80" s="6">
+        <v>4</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="E80" s="8">
+        <v>3.78</v>
+      </c>
+      <c r="F80" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="G80" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="H80" s="9" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A81" s="6">
+        <v>21229427</v>
+      </c>
+      <c r="B81" s="6">
+        <v>5</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="E81" s="8">
+        <v>3.67</v>
+      </c>
+      <c r="F81" s="8">
+        <v>4</v>
+      </c>
+      <c r="G81" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="H81" s="9" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="42" x14ac:dyDescent="0.25">
+      <c r="A82" s="6">
+        <v>21229427</v>
+      </c>
+      <c r="B82" s="6">
+        <v>6</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="E82" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="F82" s="8">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G82" s="8">
+        <v>4.8</v>
+      </c>
+      <c r="H82" s="9" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="42" x14ac:dyDescent="0.25">
+      <c r="A83" s="6">
+        <v>21229427</v>
+      </c>
+      <c r="B83" s="6">
+        <v>7</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="E83" s="8">
+        <v>4.34</v>
+      </c>
+      <c r="F83" s="8">
+        <v>5</v>
+      </c>
+      <c r="G83" s="8">
+        <v>4.8</v>
+      </c>
+      <c r="H83" s="9" t="s">
+        <v>305</v>
       </c>
     </row>
   </sheetData>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D1709B4-D69C-4EFE-B629-E265DA06BA20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B45466B-2F43-4294-97E8-85A412FCDB83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="314">
   <si>
     <t>No</t>
   </si>
@@ -957,6 +957,12 @@
   </si>
   <si>
     <t>Καταιγιστικό, οργανικό instrumental άνοιγμα. Έντονο jazz-rock groove με το Hammond B3 και τις δίδυμες κιθάρες. Πολύ καθαρός διαχωρισμός στα κανάλια, αέρας στα πιάτα και γρήγορα transients στα τύμπανα.</t>
+  </si>
+  <si>
+    <t>Victoria_Track</t>
+  </si>
+  <si>
+    <t>V</t>
   </si>
 </sst>
 </file>
@@ -1782,7 +1788,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H83"/>
+  <dimension ref="A1:I83"/>
   <sheetFormatPr defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="3" bestFit="1" customWidth="1"/>
@@ -1793,10 +1799,11 @@
     <col min="6" max="6" width="18.140625" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.42578125" style="4" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="50.7109375" style="3" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="3"/>
+    <col min="9" max="9" width="12.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>33</v>
       </c>
@@ -1821,8 +1828,11 @@
       <c r="H1" s="2" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="I1" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
         <v>964236001</v>
       </c>
@@ -1847,8 +1857,9 @@
       <c r="H2" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="I2" s="6"/>
+    </row>
+    <row r="3" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>964236001</v>
       </c>
@@ -1873,8 +1884,9 @@
       <c r="H3" s="9" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="I3" s="6"/>
+    </row>
+    <row r="4" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>964236001</v>
       </c>
@@ -1899,8 +1911,9 @@
       <c r="H4" s="9" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="I4" s="6"/>
+    </row>
+    <row r="5" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>964236001</v>
       </c>
@@ -1925,8 +1938,9 @@
       <c r="H5" s="9" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="I5" s="6"/>
+    </row>
+    <row r="6" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>964236001</v>
       </c>
@@ -1951,8 +1965,9 @@
       <c r="H6" s="9" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="I6" s="6"/>
+    </row>
+    <row r="7" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>964236001</v>
       </c>
@@ -1977,8 +1992,9 @@
       <c r="H7" s="9" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="I7" s="6"/>
+    </row>
+    <row r="8" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>964236001</v>
       </c>
@@ -2003,8 +2019,9 @@
       <c r="H8" s="9" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="I8" s="6"/>
+    </row>
+    <row r="9" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>964236001</v>
       </c>
@@ -2029,8 +2046,9 @@
       <c r="H9" s="9" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="I9" s="6"/>
+    </row>
+    <row r="10" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>964236001</v>
       </c>
@@ -2055,8 +2073,9 @@
       <c r="H10" s="9" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="I10" s="6"/>
+    </row>
+    <row r="11" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>964236001</v>
       </c>
@@ -2081,8 +2100,9 @@
       <c r="H11" s="9" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="I11" s="6"/>
+    </row>
+    <row r="12" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>1739129</v>
       </c>
@@ -2107,8 +2127,9 @@
       <c r="H12" s="9" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="I12" s="6"/>
+    </row>
+    <row r="13" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>1739129</v>
       </c>
@@ -2133,8 +2154,9 @@
       <c r="H13" s="9" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="I13" s="6"/>
+    </row>
+    <row r="14" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>1739129</v>
       </c>
@@ -2159,8 +2181,9 @@
       <c r="H14" s="9" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="I14" s="6"/>
+    </row>
+    <row r="15" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>1739129</v>
       </c>
@@ -2185,8 +2208,9 @@
       <c r="H15" s="9" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I15" s="6"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>1739129</v>
       </c>
@@ -2211,8 +2235,9 @@
       <c r="H16" s="9" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="I16" s="6"/>
+    </row>
+    <row r="17" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>1739129</v>
       </c>
@@ -2237,8 +2262,9 @@
       <c r="H17" s="9" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="I17" s="6"/>
+    </row>
+    <row r="18" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>1739129</v>
       </c>
@@ -2263,8 +2289,9 @@
       <c r="H18" s="9" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="I18" s="6"/>
+    </row>
+    <row r="19" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>37452171</v>
       </c>
@@ -2289,8 +2316,9 @@
       <c r="H19" s="9" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="I19" s="6"/>
+    </row>
+    <row r="20" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>37452171</v>
       </c>
@@ -2315,8 +2343,9 @@
       <c r="H20" s="9" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="I20" s="6"/>
+    </row>
+    <row r="21" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>37452171</v>
       </c>
@@ -2341,8 +2370,9 @@
       <c r="H21" s="9" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="I21" s="6"/>
+    </row>
+    <row r="22" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>37452171</v>
       </c>
@@ -2367,8 +2397,9 @@
       <c r="H22" s="9" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="I22" s="6"/>
+    </row>
+    <row r="23" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>37452171</v>
       </c>
@@ -2393,8 +2424,9 @@
       <c r="H23" s="9" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="I23" s="6"/>
+    </row>
+    <row r="24" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>37452171</v>
       </c>
@@ -2419,8 +2451,9 @@
       <c r="H24" s="9" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="I24" s="6"/>
+    </row>
+    <row r="25" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>37452171</v>
       </c>
@@ -2445,8 +2478,9 @@
       <c r="H25" s="9" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="I25" s="6"/>
+    </row>
+    <row r="26" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>37452171</v>
       </c>
@@ -2471,8 +2505,9 @@
       <c r="H26" s="9" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="I26" s="6"/>
+    </row>
+    <row r="27" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>37452171</v>
       </c>
@@ -2497,8 +2532,9 @@
       <c r="H27" s="9" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="I27" s="6"/>
+    </row>
+    <row r="28" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>37452171</v>
       </c>
@@ -2523,8 +2559,9 @@
       <c r="H28" s="9" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="I28" s="6"/>
+    </row>
+    <row r="29" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>37452171</v>
       </c>
@@ -2549,8 +2586,9 @@
       <c r="H29" s="9" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="I29" s="6"/>
+    </row>
+    <row r="30" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>33790944</v>
       </c>
@@ -2575,8 +2613,9 @@
       <c r="H30" s="9" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="I30" s="6"/>
+    </row>
+    <row r="31" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>33790944</v>
       </c>
@@ -2601,8 +2640,9 @@
       <c r="H31" s="9" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="I31" s="6"/>
+    </row>
+    <row r="32" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>33790944</v>
       </c>
@@ -2627,8 +2667,9 @@
       <c r="H32" s="9" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="I32" s="6"/>
+    </row>
+    <row r="33" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>33790944</v>
       </c>
@@ -2653,8 +2694,9 @@
       <c r="H33" s="9" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="I33" s="6"/>
+    </row>
+    <row r="34" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>33790944</v>
       </c>
@@ -2679,8 +2721,9 @@
       <c r="H34" s="9" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="I34" s="6"/>
+    </row>
+    <row r="35" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>33790944</v>
       </c>
@@ -2705,8 +2748,9 @@
       <c r="H35" s="9" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="I35" s="6"/>
+    </row>
+    <row r="36" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>33790944</v>
       </c>
@@ -2731,8 +2775,9 @@
       <c r="H36" s="9" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="I36" s="6"/>
+    </row>
+    <row r="37" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>33790944</v>
       </c>
@@ -2757,8 +2802,9 @@
       <c r="H37" s="9" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="I37" s="6"/>
+    </row>
+    <row r="38" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>33790944</v>
       </c>
@@ -2783,8 +2829,9 @@
       <c r="H38" s="9" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="I38" s="6"/>
+    </row>
+    <row r="39" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>33790944</v>
       </c>
@@ -2809,8 +2856,9 @@
       <c r="H39" s="9" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="I39" s="6"/>
+    </row>
+    <row r="40" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>926332</v>
       </c>
@@ -2835,8 +2883,9 @@
       <c r="H40" s="9" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="I40" s="6"/>
+    </row>
+    <row r="41" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>926332</v>
       </c>
@@ -2861,8 +2910,9 @@
       <c r="H41" s="9" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="I41" s="6"/>
+    </row>
+    <row r="42" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>926332</v>
       </c>
@@ -2887,8 +2937,9 @@
       <c r="H42" s="9" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="I42" s="6"/>
+    </row>
+    <row r="43" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>926332</v>
       </c>
@@ -2913,8 +2964,9 @@
       <c r="H43" s="9" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="I43" s="6"/>
+    </row>
+    <row r="44" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>926332</v>
       </c>
@@ -2939,8 +2991,9 @@
       <c r="H44" s="9" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="I44" s="6"/>
+    </row>
+    <row r="45" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>926332</v>
       </c>
@@ -2965,8 +3018,9 @@
       <c r="H45" s="9" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="I45" s="6"/>
+    </row>
+    <row r="46" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>926332</v>
       </c>
@@ -2991,8 +3045,9 @@
       <c r="H46" s="9" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" ht="42" x14ac:dyDescent="0.25">
+      <c r="I46" s="6"/>
+    </row>
+    <row r="47" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>10079558</v>
       </c>
@@ -3017,8 +3072,9 @@
       <c r="H47" s="9" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="I47" s="6"/>
+    </row>
+    <row r="48" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>10079558</v>
       </c>
@@ -3043,8 +3099,9 @@
       <c r="H48" s="9" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="I48" s="6"/>
+    </row>
+    <row r="49" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>10079558</v>
       </c>
@@ -3069,8 +3126,9 @@
       <c r="H49" s="9" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="I49" s="6"/>
+    </row>
+    <row r="50" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>10079558</v>
       </c>
@@ -3095,8 +3153,9 @@
       <c r="H50" s="9" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="I50" s="6"/>
+    </row>
+    <row r="51" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>10079558</v>
       </c>
@@ -3121,8 +3180,9 @@
       <c r="H51" s="9" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="52" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="I51" s="6"/>
+    </row>
+    <row r="52" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>10079558</v>
       </c>
@@ -3147,8 +3207,9 @@
       <c r="H52" s="9" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="I52" s="6"/>
+    </row>
+    <row r="53" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>10079558</v>
       </c>
@@ -3173,8 +3234,9 @@
       <c r="H53" s="9" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="I53" s="6"/>
+    </row>
+    <row r="54" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
         <v>10079558</v>
       </c>
@@ -3199,8 +3261,9 @@
       <c r="H54" s="9" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="55" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="I54" s="6"/>
+    </row>
+    <row r="55" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
         <v>10079558</v>
       </c>
@@ -3225,8 +3288,9 @@
       <c r="H55" s="9" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="56" spans="1:8" ht="42" x14ac:dyDescent="0.25">
+      <c r="I55" s="6"/>
+    </row>
+    <row r="56" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
         <v>2027786</v>
       </c>
@@ -3251,8 +3315,9 @@
       <c r="H56" s="9" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="I56" s="6"/>
+    </row>
+    <row r="57" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
         <v>2027786</v>
       </c>
@@ -3277,8 +3342,9 @@
       <c r="H57" s="9" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="I57" s="6"/>
+    </row>
+    <row r="58" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
         <v>2027786</v>
       </c>
@@ -3303,8 +3369,9 @@
       <c r="H58" s="9" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" ht="42" x14ac:dyDescent="0.25">
+      <c r="I58" s="6"/>
+    </row>
+    <row r="59" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
         <v>2027786</v>
       </c>
@@ -3329,8 +3396,9 @@
       <c r="H59" s="9" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="I59" s="6"/>
+    </row>
+    <row r="60" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
         <v>2027786</v>
       </c>
@@ -3355,8 +3423,9 @@
       <c r="H60" s="9" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="I60" s="6"/>
+    </row>
+    <row r="61" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
         <v>2027786</v>
       </c>
@@ -3381,8 +3450,9 @@
       <c r="H61" s="9" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="I61" s="6"/>
+    </row>
+    <row r="62" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
         <v>2027786</v>
       </c>
@@ -3407,8 +3477,9 @@
       <c r="H62" s="9" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I62" s="6"/>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
         <v>2027786</v>
       </c>
@@ -3433,8 +3504,9 @@
       <c r="H63" s="9" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="I63" s="6"/>
+    </row>
+    <row r="64" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
         <v>2027786</v>
       </c>
@@ -3459,8 +3531,9 @@
       <c r="H64" s="9" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="65" spans="1:8" ht="42" x14ac:dyDescent="0.25">
+      <c r="I64" s="6"/>
+    </row>
+    <row r="65" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
         <v>35339929</v>
       </c>
@@ -3485,8 +3558,9 @@
       <c r="H65" s="9" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="66" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="I65" s="6"/>
+    </row>
+    <row r="66" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
         <v>35339929</v>
       </c>
@@ -3511,8 +3585,9 @@
       <c r="H66" s="9" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="67" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="I66" s="6"/>
+    </row>
+    <row r="67" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>35339929</v>
       </c>
@@ -3537,8 +3612,9 @@
       <c r="H67" s="9" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="68" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="I67" s="6"/>
+    </row>
+    <row r="68" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
         <v>35339929</v>
       </c>
@@ -3563,8 +3639,9 @@
       <c r="H68" s="9" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="69" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="I68" s="6"/>
+    </row>
+    <row r="69" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
         <v>35339929</v>
       </c>
@@ -3589,8 +3666,9 @@
       <c r="H69" s="9" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="70" spans="1:8" ht="42" x14ac:dyDescent="0.25">
+      <c r="I69" s="6"/>
+    </row>
+    <row r="70" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
         <v>35339929</v>
       </c>
@@ -3615,8 +3693,9 @@
       <c r="H70" s="9" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="71" spans="1:8" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="I70" s="6"/>
+    </row>
+    <row r="71" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
         <v>31106519</v>
       </c>
@@ -3641,8 +3720,9 @@
       <c r="H71" s="9" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="72" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="I71" s="6"/>
+    </row>
+    <row r="72" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
         <v>31106519</v>
       </c>
@@ -3667,8 +3747,9 @@
       <c r="H72" s="9" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="73" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="I72" s="6"/>
+    </row>
+    <row r="73" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
         <v>31106519</v>
       </c>
@@ -3693,8 +3774,9 @@
       <c r="H73" s="9" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="74" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="I73" s="6"/>
+    </row>
+    <row r="74" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
         <v>31106519</v>
       </c>
@@ -3719,8 +3801,9 @@
       <c r="H74" s="9" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="75" spans="1:8" ht="42" x14ac:dyDescent="0.25">
+      <c r="I74" s="6"/>
+    </row>
+    <row r="75" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
         <v>31106519</v>
       </c>
@@ -3745,8 +3828,9 @@
       <c r="H75" s="9" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="76" spans="1:8" ht="42" x14ac:dyDescent="0.25">
+      <c r="I75" s="6"/>
+    </row>
+    <row r="76" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
         <v>31106519</v>
       </c>
@@ -3771,8 +3855,9 @@
       <c r="H76" s="9" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="77" spans="1:8" ht="42" x14ac:dyDescent="0.25">
+      <c r="I76" s="6"/>
+    </row>
+    <row r="77" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
         <v>21229427</v>
       </c>
@@ -3797,8 +3882,9 @@
       <c r="H77" s="9" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="78" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="I77" s="6"/>
+    </row>
+    <row r="78" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
         <v>21229427</v>
       </c>
@@ -3823,8 +3909,9 @@
       <c r="H78" s="9" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="79" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="I78" s="6"/>
+    </row>
+    <row r="79" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
         <v>21229427</v>
       </c>
@@ -3849,8 +3936,9 @@
       <c r="H79" s="9" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="80" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="I79" s="6"/>
+    </row>
+    <row r="80" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
         <v>21229427</v>
       </c>
@@ -3875,8 +3963,9 @@
       <c r="H80" s="9" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="81" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="I80" s="6"/>
+    </row>
+    <row r="81" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
         <v>21229427</v>
       </c>
@@ -3901,8 +3990,9 @@
       <c r="H81" s="9" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="82" spans="1:8" ht="42" x14ac:dyDescent="0.25">
+      <c r="I81" s="6"/>
+    </row>
+    <row r="82" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
         <v>21229427</v>
       </c>
@@ -3927,8 +4017,9 @@
       <c r="H82" s="9" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="83" spans="1:8" ht="42" x14ac:dyDescent="0.25">
+      <c r="I82" s="6"/>
+    </row>
+    <row r="83" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
         <v>21229427</v>
       </c>
@@ -3952,6 +4043,9 @@
       </c>
       <c r="H83" s="9" t="s">
         <v>305</v>
+      </c>
+      <c r="I83" s="6" t="s">
+        <v>313</v>
       </c>
     </row>
   </sheetData>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B45466B-2F43-4294-97E8-85A412FCDB83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F089554-C4FC-4FE0-B69C-701AA50D177D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="358">
   <si>
     <t>No</t>
   </si>
@@ -963,6 +963,138 @@
   </si>
   <si>
     <t>V</t>
+  </si>
+  <si>
+    <t>Arctic Monkeys</t>
+  </si>
+  <si>
+    <t>AM</t>
+  </si>
+  <si>
+    <t>2013 (Original) / 2022 (Repress)</t>
+  </si>
+  <si>
+    <t>Indie Rock, Hard Rock, Stomp Rock, R&amp;B</t>
+  </si>
+  <si>
+    <t>Domino – WIGLP317 (Europe Reissue Gatefold / GZ Media WIZZARD Cut - ID 24362534)</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το 5ο άλμπουμ-σταθμός των Arctic Monkeys (2013) που πάντρεψε το βαρύ stoner rock με R&amp;B grooves. Περιλαμβάνει τα διαχρονικά «Do I Wanna Know?», «R U Mine?» και «Why'd You Only Call Me When You're High?». | Hard Facts Έκδοσης: Ευρωπαϊκή επανέκδοση της Domino σε Gatefold εξώφυλλο (WIGLP317 / ID 24362534). Lacquer Cutting από τον Dominic Sorrell (σφραγίδα «THE WIZZARD») και πρεσάρισμα στο εργοστάσιο της GZ Media (Τσεχία). Matrix/Runout: WIGLP317-A1 THE WIZZARD 1518332 237517E1 / WIGLP317-B-3 1546689 237517E2 (GZ Batch Run). Ηχητική Αξιολόγηση (4.6/5): Πολύ γεμάτο χαμηλό στις κάσες των τυμπάνων και το μπάσο, σφιχτός αναλογικός χαρακτήρας στις fuzz κιθάρες και εξαιρετική ευκρίνεια στα πολυεπίπεδα φωνητικά του Alex Turner.</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/24362534-Arctic-Monkeys-AM?redirected=true</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/iL1WQwjZQ-chGeZ9Ii39Hz9lDZxlSIzMDzXPamxcppA/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI0MzYy/NTM0LTE2NjE4ODk4/NjctMjE2MS5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Do I Wanna Know?</t>
+  </si>
+  <si>
+    <t>R U Mine?</t>
+  </si>
+  <si>
+    <t>Why'd You Only Call Me When You're High?</t>
+  </si>
+  <si>
+    <t>Arabella</t>
+  </si>
+  <si>
+    <t>Knee Socks</t>
+  </si>
+  <si>
+    <t>I Wanna Be Yours</t>
+  </si>
+  <si>
+    <t>Fireside</t>
+  </si>
+  <si>
+    <t>Mad Sounds</t>
+  </si>
+  <si>
+    <t>I Want It All</t>
+  </si>
+  <si>
+    <t>Indie Rock, Stomp Rock, Desert Rock</t>
+  </si>
+  <si>
+    <t>Το απόλυτο riff της δεκαετίας του 2010. Βαρύ, υπνωτιστικό stomp groove με εξαιρετική κλιμάκωση. Δυνατό χαμηλό στις κάσες και σφιχτό μπάσο.</t>
+  </si>
+  <si>
+    <t>Hard Rock, Garage Rock, Stoner Rock</t>
+  </si>
+  <si>
+    <t>Καταιγιστικό, επιθετικό track με βαριά fuzz κιθάρα, ασταμάτητο rhythm section και χαρακτηριστικά falsetto φωνητικά στα backups.</t>
+  </si>
+  <si>
+    <t>One For The Road</t>
+  </si>
+  <si>
+    <t>No.1 Party Anthem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snap Out Of It </t>
+  </si>
+  <si>
+    <t>Indie Rock, R&amp;B Rock</t>
+  </si>
+  <si>
+    <t>Mid-tempo νυχτερινό groove με R&amp;B αισθητική στα drums, φαλτσέτα φωνητικά και κοφτό σόλο κιθάρας στο φινάλε. Εξαιρετικός αέρας στα ψηλά.</t>
+  </si>
+  <si>
+    <t>Heavy Rock, Psychedelic Rock</t>
+  </si>
+  <si>
+    <t>Εκπληκτική γέφυρα ανάμεσα στο hip-hop beat των κουπλέ και το Sabbath-esque hard rock ξέσπασμα στο ρεφρέν. Μεγάλη δυναμική περιοχή.</t>
+  </si>
+  <si>
+    <t>Glam Rock, Indie Rock</t>
+  </si>
+  <si>
+    <t>Up-tempo track με glam 80s επιρροές, σφυρίγματα και έντονα backing vocals. Καθαρός διαχωρισμός καναλιών.</t>
+  </si>
+  <si>
+    <t>Glam Heritage Ballad, Indie Pop</t>
+  </si>
+  <si>
+    <t>Εξαιρετική 70s glam μπαλάντα με μελαγχολικό πιάνο και φωνητική ερμηνεία θυμίζοντας Bowie/Lennon. Πολύ φυσική αναλογική ζεστή ηχώ.</t>
+  </si>
+  <si>
+    <t>Lou Reed-esque Rock, Soul Rock</t>
+  </si>
+  <si>
+    <t>Βασισμένο στο ποίημα του John Cooper Clarke. Σκοτεινό, ατμοσφαιρικό, υπνωτιστικό κλείσιμο. Βαθιά reverb effects και αέρινη αίσθηση χώρου.</t>
+  </si>
+  <si>
+    <t>Πολύπλοκη δομή, φανταστική αλληλεπίδραση κιθάρας/μπάσου και outro με τη συμμετοχή του Josh Homme. Πολυεπίπεδο soundstage.</t>
+  </si>
+  <si>
+    <t>Downtempo, Ambient Rock, Psychedelic Soul</t>
+  </si>
+  <si>
+    <t>R&amp;B Rock, Indie Rock</t>
+  </si>
+  <si>
+    <t>Pop Rock, Glam Rock</t>
+  </si>
+  <si>
+    <t>Ρυθμικό, πιανιστικό groove με κολλητικό ρεφρέν και παλαμάκια. Πολύ καθαρή άρθρωση στα φωνητικά.</t>
+  </si>
+  <si>
+    <t>Εθιστικό bassline, hip-hop ρυθμικό στήσιμο και κυνικοί, ρεαλιστικοί στίχοι. Reference κομμάτι για τον έλεγχο των χαμηλών συχνοτήτων στο σύστημα.</t>
+  </si>
+  <si>
+    <t>Funk Rock, R&amp;B, Alternative Rock</t>
+  </si>
+  <si>
+    <t>Indie Pop, Acoustic Rock</t>
+  </si>
+  <si>
+    <t>Ακουστικές κιθάρες, γρήγορο percussion και μελαγχολική ατμόσφαιρα. Ξεχωρίζει για την εσωτερικότητα και τη μελωδική του εξέλιξη.</t>
+  </si>
+  <si>
+    <t>Ήρεμο, οργανικό track με επιρροές από Velvet Underground. Εκπληκτικά οργανικά transients στα κρουστά και το ηλεκτρικό πιάνο Wurlitzer.</t>
   </si>
 </sst>
 </file>
@@ -1391,7 +1523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
@@ -1757,6 +1889,38 @@
       </c>
       <c r="J11" s="11" t="s">
         <v>291</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
+        <v>24362534</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="E12" s="10">
+        <v>3.08</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -1781,6 +1945,8 @@
     <hyperlink ref="J10" r:id="rId18" xr:uid="{BA6CBFDC-FFDE-41CF-AA5C-8D87A3AF9F62}"/>
     <hyperlink ref="I11" r:id="rId19" xr:uid="{41088898-623F-47B4-BF91-B4B1CD818D4E}"/>
     <hyperlink ref="J11" r:id="rId20" xr:uid="{E113C2CF-CD08-4D0D-B347-3943034BA748}"/>
+    <hyperlink ref="I12" r:id="rId21" xr:uid="{16FF05EB-D3D0-4933-A9A7-1991D2A4347A}"/>
+    <hyperlink ref="J12" r:id="rId22" xr:uid="{7F3FDF6A-4AF3-43DA-A4B5-C708BEBBC5AC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1788,7 +1954,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I95"/>
   <sheetFormatPr defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="3" bestFit="1" customWidth="1"/>
@@ -3045,7 +3211,9 @@
       <c r="H46" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="I46" s="6"/>
+      <c r="I46" s="6" t="s">
+        <v>313</v>
+      </c>
     </row>
     <row r="47" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
@@ -3072,7 +3240,9 @@
       <c r="H47" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="I47" s="6"/>
+      <c r="I47" s="6" t="s">
+        <v>313</v>
+      </c>
     </row>
     <row r="48" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
@@ -3180,7 +3350,9 @@
       <c r="H51" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="I51" s="6"/>
+      <c r="I51" s="6" t="s">
+        <v>313</v>
+      </c>
     </row>
     <row r="52" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
@@ -3315,7 +3487,9 @@
       <c r="H56" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="I56" s="6"/>
+      <c r="I56" s="6" t="s">
+        <v>313</v>
+      </c>
     </row>
     <row r="57" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
@@ -3558,7 +3732,9 @@
       <c r="H65" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="I65" s="6"/>
+      <c r="I65" s="6" t="s">
+        <v>313</v>
+      </c>
     </row>
     <row r="66" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
@@ -3720,7 +3896,9 @@
       <c r="H71" s="9" t="s">
         <v>279</v>
       </c>
-      <c r="I71" s="6"/>
+      <c r="I71" s="6" t="s">
+        <v>313</v>
+      </c>
     </row>
     <row r="72" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
@@ -3747,7 +3925,9 @@
       <c r="H72" s="9" t="s">
         <v>280</v>
       </c>
-      <c r="I72" s="6"/>
+      <c r="I72" s="6" t="s">
+        <v>313</v>
+      </c>
     </row>
     <row r="73" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
@@ -3801,7 +3981,9 @@
       <c r="H74" s="9" t="s">
         <v>282</v>
       </c>
-      <c r="I74" s="6"/>
+      <c r="I74" s="6" t="s">
+        <v>313</v>
+      </c>
     </row>
     <row r="75" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
@@ -3855,7 +4037,9 @@
       <c r="H76" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="I76" s="6"/>
+      <c r="I76" s="6" t="s">
+        <v>313</v>
+      </c>
     </row>
     <row r="77" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
@@ -4047,6 +4231,330 @@
       <c r="I83" s="6" t="s">
         <v>313</v>
       </c>
+    </row>
+    <row r="84" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A84" s="6">
+        <v>24362534</v>
+      </c>
+      <c r="B84" s="6">
+        <v>1</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="E84" s="8">
+        <v>3.98</v>
+      </c>
+      <c r="F84" s="8">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G84" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H84" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="I84" s="6"/>
+    </row>
+    <row r="85" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A85" s="6">
+        <v>24362534</v>
+      </c>
+      <c r="B85" s="6">
+        <v>2</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="E85" s="8">
+        <v>3.96</v>
+      </c>
+      <c r="F85" s="8">
+        <v>4.8</v>
+      </c>
+      <c r="G85" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="H85" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="I85" s="6"/>
+    </row>
+    <row r="86" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A86" s="6">
+        <v>24362534</v>
+      </c>
+      <c r="B86" s="6">
+        <v>3</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="E86" s="8">
+        <v>3.22</v>
+      </c>
+      <c r="F86" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="G86" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H86" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="I86" s="6"/>
+    </row>
+    <row r="87" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A87" s="6">
+        <v>24362534</v>
+      </c>
+      <c r="B87" s="6">
+        <v>4</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="E87" s="8">
+        <v>3.56</v>
+      </c>
+      <c r="F87" s="8">
+        <v>4.7</v>
+      </c>
+      <c r="G87" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H87" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="I87" s="6"/>
+    </row>
+    <row r="88" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A88" s="6">
+        <v>24362534</v>
+      </c>
+      <c r="B88" s="6">
+        <v>5</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="E88" s="8">
+        <v>2.93</v>
+      </c>
+      <c r="F88" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="G88" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="H88" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="I88" s="6"/>
+    </row>
+    <row r="89" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A89" s="6">
+        <v>24362534</v>
+      </c>
+      <c r="B89" s="6">
+        <v>6</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="E89" s="8">
+        <v>3.46</v>
+      </c>
+      <c r="F89" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G89" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="H89" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="I89" s="6"/>
+    </row>
+    <row r="90" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A90" s="6">
+        <v>24362534</v>
+      </c>
+      <c r="B90" s="6">
+        <v>7</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="E90" s="8">
+        <v>2.97</v>
+      </c>
+      <c r="F90" s="8">
+        <v>4</v>
+      </c>
+      <c r="G90" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H90" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="I90" s="6"/>
+    </row>
+    <row r="91" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A91" s="6">
+        <v>24362534</v>
+      </c>
+      <c r="B91" s="6">
+        <v>8</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="E91" s="8">
+        <v>3.26</v>
+      </c>
+      <c r="F91" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="G91" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="H91" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="I91" s="6"/>
+    </row>
+    <row r="92" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A92" s="6">
+        <v>24362534</v>
+      </c>
+      <c r="B92" s="6">
+        <v>9</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="D92" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="E92" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="F92" s="8">
+        <v>4.75</v>
+      </c>
+      <c r="G92" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="H92" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="I92" s="6"/>
+    </row>
+    <row r="93" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A93" s="6">
+        <v>24362534</v>
+      </c>
+      <c r="B93" s="6">
+        <v>10</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="E93" s="8">
+        <v>3.47</v>
+      </c>
+      <c r="F93" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G93" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="H93" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="I93" s="6"/>
+    </row>
+    <row r="94" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A94" s="6">
+        <v>24362534</v>
+      </c>
+      <c r="B94" s="6">
+        <v>11</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="E94" s="8">
+        <v>3.47</v>
+      </c>
+      <c r="F94" s="8">
+        <v>4.7</v>
+      </c>
+      <c r="G94" s="8">
+        <v>4.7</v>
+      </c>
+      <c r="H94" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="I94" s="6"/>
+    </row>
+    <row r="95" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A95" s="6">
+        <v>24362534</v>
+      </c>
+      <c r="B95" s="6">
+        <v>12</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="E95" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="F95" s="8">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="G95" s="8">
+        <v>4.75</v>
+      </c>
+      <c r="H95" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="I95" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -1,27 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pak\Music\Victoria\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F089554-C4FC-4FE0-B69C-701AA50D177D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{932C3D31-649B-4F3F-9B64-702739301B75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
     <sheet name="tracks" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="407">
   <si>
     <t>No</t>
   </si>
@@ -1095,6 +1108,153 @@
   </si>
   <si>
     <t>Ήρεμο, οργανικό track με επιρροές από Velvet Underground. Εκπληκτικά οργανικά transients στα κρουστά και το ηλεκτρικό πιάνο Wurlitzer.</t>
+  </si>
+  <si>
+    <t>Black Sabbath</t>
+  </si>
+  <si>
+    <t>Master Of Reality</t>
+  </si>
+  <si>
+    <t>1971 (Original) / 2015 (BMG/Sanctuary Reissue)</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Proto-Doom Metal, Proto-Stoner, Heavy Blues Rock</t>
+  </si>
+  <si>
+    <t>Sanctuary / BMG – BMGRM055LP (EU 180g / Embossed Cover / Optimal Media JP Cut - ID 24831386)</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/24831386-Black-Sabbath-Master-Of-Reality</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/o6dVhUUYZVPntZNOnZDmMkZxzAyur3f9CNHbiR96wvM/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI0ODMx/Mzg2LTE2NjU4Mzk4/OTQtMjA4NC5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Sweet Leaf</t>
+  </si>
+  <si>
+    <t>After Forever</t>
+  </si>
+  <si>
+    <t>Embryo</t>
+  </si>
+  <si>
+    <t>Children Of The Grave</t>
+  </si>
+  <si>
+    <t>Orchid</t>
+  </si>
+  <si>
+    <t>Lord Of This World</t>
+  </si>
+  <si>
+    <t>Solitude</t>
+  </si>
+  <si>
+    <t>Into The Void</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Progressive Rock</t>
+  </si>
+  <si>
+    <t>Acoustic Interlude, Renaissance Folk</t>
+  </si>
+  <si>
+    <t>Μνημειώδες, καλπάζον heavy metal riffing που επηρέασε ολόκληρες γενιές. Εκπληκτικά κρουστά/percussion layers στο βάθος και εφιαλτικό, ατμοσφαιρικό fade-out.</t>
+  </si>
+  <si>
+    <t>Acoustic Folk, Classical Acoustic</t>
+  </si>
+  <si>
+    <t>Πανέμορφη ακουστική οργανική σύνθεση με διπλές ακουστικές κιθάρες και ελαφρύ αέρα/reverb. Αναδεικνύει την κλασική/μελωδική πλευρά του Iommi.</t>
+  </si>
+  <si>
+    <t>Αργό, εφιαλτικά βαρύ groove με το μπάσο του Geezer Butler να τρίζει τα ηχεία. Εκπληκτικό σόλο από τον Iommi και από τις πιο σκοτεινές ερμηνείες του Ozzy.</t>
+  </si>
+  <si>
+    <t>Psychedelic Folk, Progressive Rock, Ambient Rock</t>
+  </si>
+  <si>
+    <t>Ήσυχη, μελαγχολική μπαλάντα με φλάουτο και ακουστική κιθάρα, ενώ ο Ozzy προσφέρει μια σπάνια, αιθέρια ερμηνεία. Τεράστια αίσθηση χώρου.</t>
+  </si>
+  <si>
+    <t>Το απόλυτο riff-fest. Ξεκινά με ένα από τα βαρύτερα intro στην ιστορία της μουσικής και εξελίσσεται σε ένα συγκλονιστικό έπος. Το απόλυτο benchmark για το χαμηλό του συστήματος.</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock, Proto-Stoner</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Proto-Thrash, Proto-Doom</t>
+  </si>
+  <si>
+    <t>Proto-Doom Metal, Heavy Blues Rock</t>
+  </si>
+  <si>
+    <t>Proto-Doom Metal, Heavy Metal, Proto-Sludge</t>
+  </si>
+  <si>
+    <t>Το ιστορικό βήξιμο του Tony Iommi στην εισαγωγή ανοίγει το απόλυτο heavy anthem. Down-tuned (C# [C-sharp tuning]) κιθάρες με φοβερή αίσθηση όγκου και καταιγιστικό uptempo ξέσπασμα.</t>
+  </si>
+  <si>
+    <t>Ξεκινά με το σύντομο instrumental "Elegy". Up-tempo riffing με εξαιρετικά πολύπλοκη δομή, στίχους του Geezer Butler γύρω από τη θρησκεία και πίστη.</t>
+  </si>
+  <si>
+    <t>Σύντομο ακουστικό πέρασμα (28 δευτερολέπτων) με μεσαιωνική αισθητική, που λειτουργεί ως ηχητικός "αναπνευστήρας" πριν την έκρηξη του Children of the Grave.</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το 3ο άλμπουμ-σταθμός των Black Sabbath (1971) που θεμελίωσε το Doom Metal και το Stoner Rock χάρη στο down-tuning (C#) του Tony Iommi και του Geezer Butler. Περιλαμβάνει τα μνημειώδη "Sweet Leaf", "Children of the Grave" και "Into the Void". | Hard Facts Έκδοσης: Επίσημη ευρωπαϊκή επανέκδοση 180g της BMG/Sanctuary σε ανάγλυφο (Embossed) εξώφυλλο (BMGRM055LP / ID 24831386). Lacquer Cutting από τον Jörg Pieper (σφραγίδα «JP») και πρεσάρισμα στο Optimal Media (Γερμανία). Matrix/Runout: BMGRM055LP BF85260-01 A1 JP / BMGRM055LP BF85260-01 B1 JP. Ηχητική Αξιολόγηση (4.75/5): Τεράστιος, σκοτεινός αναλογικός όγκος στα μπάσα, αθόρυβο υπόβαθρο (low noise floor) και εξαιρετική δυναμική περιοχή που αναδεικνύει την αυθεντική παραγωγή του Rodger Bain.</t>
+  </si>
+  <si>
+    <t>Land Of No Body</t>
+  </si>
+  <si>
+    <t>Krautrock, Heavy Progressive Rock, Space Rock</t>
+  </si>
+  <si>
+    <t>17λεπτο progressive έπος που καταλαμβάνει ολόκληρη την πλευρά A. Κυριαρχείται από πολυεπίπεδα Hammond solos, υπνωτικά μπάσα, συνεχείς αλλαγές ρυθμών και ψυχεδελικά κιθαριστικά ξεσπάσματα.</t>
+  </si>
+  <si>
+    <t>Inside</t>
+  </si>
+  <si>
+    <t>Krautrock, Space Rock, Heavy Prog</t>
+  </si>
+  <si>
+    <t>Το ομώνυμο κομμάτι με αργή, ατμοσφαιρική εισαγωγή. Σταδιακά κλιμακώνεται με βαριά κιθαριστικά riffs, έντονο Leslie εφέ στο Hammond organ και διαστημικά φωνητικά.</t>
+  </si>
+  <si>
+    <t>Future City</t>
+  </si>
+  <si>
+    <t>Heavy Progressive Rock, Hard Rock</t>
+  </si>
+  <si>
+    <t>Το πιο άμεσο και ρυθμικό track του δίσκου. Καταιγιστικό bassline, κοφτά κιθαριστικά chords και επιθετικό παίξιμο στα τύμπανα με εξαιρετικό στερεοφωνικό διαχωρισμό.</t>
+  </si>
+  <si>
+    <t>Up And Down</t>
+  </si>
+  <si>
+    <t>Krautrock, Progressive Organ Rock</t>
+  </si>
+  <si>
+    <t>Οργανικό, ψυχεδελικό κλείσιμο με βαριά groovy μπασογραμμή, εκτεταμένο Hammond jamming και ατμοσφαιρικά περάσματα που θυμίζουν τις πρώιμες δουλειές των Pink Floyd &amp; Uriah Heep.</t>
+  </si>
+  <si>
+    <t>Eloy</t>
+  </si>
+  <si>
+    <t>EMI Electrola / Harvest – 29 479-2 (Germany Original 1st Pressing - Matrix: 29 479 A-1 / B-1 - ID 6503426)</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το 2ο άλμπουμ των Γερμανών Eloy (1973) και το πρώτο που τους καθιέρωσε στην ηγεσία του γερμανικού Space/Progressive Rock. Κυριαρχείται από τα ασταμάτητα Hammond B3 όργανα, βαριές progressive κιθάρες και 17λεπτες συνθέσεις. | Hard Facts Έκδοσης: Αυθεντική 1η γερμανική έκδοση της Harvest/EMI Electrola (29 479-2). Πρώτες μήτρες A1 / B1 (29 479 A - 1 / 29 479 B - 1). Ηχητική Αξιολόγηση (4.80/5): Κορυφαίος αναλογικός ήχος δεκαετίας '70 απευθείας από τα master tapes. Τεράστια δυναμική περιοχή (headroom), φυσική αντήχηση στο Hammond organ και σφιχτό, οργανικό χαμηλό στα τύμπανα και το μπάσο.</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/6503426-Eloy-Inside</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/Cs-MD9yqq0a1InQwB2TLzIvOfzdVsDgOPgE2IjVVHTg/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTY1MDM0/MjYtMTU0MjI3NTY4/Ny05NzA4LmpwZWc.jpeg</t>
   </si>
 </sst>
 </file>
@@ -1220,8 +1380,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Κανονικό" xfId="0" builtinId="0"/>
-    <cellStyle name="Υπερ-σύνδεση" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1523,23 +1683,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J14"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="34.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="96.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="35.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="50.42578125" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="7.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="96.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="50.44140625" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>33</v>
       </c>
@@ -1571,7 +1731,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="61.2" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>964236001</v>
       </c>
@@ -1603,7 +1763,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="40.799999999999997" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>1739129</v>
       </c>
@@ -1635,7 +1795,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>37452171</v>
       </c>
@@ -1667,7 +1827,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="40.799999999999997" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>33790944</v>
       </c>
@@ -1699,7 +1859,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="51" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>926332</v>
       </c>
@@ -1731,7 +1891,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="51" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>10079558</v>
       </c>
@@ -1763,7 +1923,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="61.2" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>2027786</v>
       </c>
@@ -1795,7 +1955,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="61.2" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>35339929</v>
       </c>
@@ -1827,7 +1987,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="51" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>31106519</v>
       </c>
@@ -1859,7 +2019,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="61.2" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>21229427</v>
       </c>
@@ -1891,7 +2051,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="73.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="61.2" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>24362534</v>
       </c>
@@ -1921,6 +2081,70 @@
       </c>
       <c r="J12" s="11" t="s">
         <v>321</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="61.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="6">
+        <v>24831386</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="E13" s="10">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="51" x14ac:dyDescent="0.3">
+      <c r="A14" s="6">
+        <v>6503426</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="D14" s="6">
+        <v>1973</v>
+      </c>
+      <c r="E14" s="10">
+        <v>3.66</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>405</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>406</v>
       </c>
     </row>
   </sheetData>
@@ -1947,6 +2171,10 @@
     <hyperlink ref="J11" r:id="rId20" xr:uid="{E113C2CF-CD08-4D0D-B347-3943034BA748}"/>
     <hyperlink ref="I12" r:id="rId21" xr:uid="{16FF05EB-D3D0-4933-A9A7-1991D2A4347A}"/>
     <hyperlink ref="J12" r:id="rId22" xr:uid="{7F3FDF6A-4AF3-43DA-A4B5-C708BEBBC5AC}"/>
+    <hyperlink ref="I13" r:id="rId23" xr:uid="{9D7EA281-7164-4EC6-8613-E6D1AAA72828}"/>
+    <hyperlink ref="J13" r:id="rId24" xr:uid="{8EE506D2-8E16-47D1-A8EC-6F5329B2DA47}"/>
+    <hyperlink ref="I14" r:id="rId25" xr:uid="{D99AD04E-22D7-4523-A906-354DCA3D59B8}"/>
+    <hyperlink ref="J14" r:id="rId26" xr:uid="{3F9ECA46-C0F1-4A2C-A780-DD9645DE1436}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1954,22 +2182,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I95"/>
-  <sheetFormatPr defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I107"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="10.199999999999999" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="3" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="50.7109375" style="3" customWidth="1"/>
-    <col min="9" max="9" width="12.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="3"/>
+    <col min="3" max="3" width="28.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.44140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="50.6640625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>33</v>
       </c>
@@ -1998,7 +2226,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>964236001</v>
       </c>
@@ -2025,7 +2253,7 @@
       </c>
       <c r="I2" s="6"/>
     </row>
-    <row r="3" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>964236001</v>
       </c>
@@ -2052,7 +2280,7 @@
       </c>
       <c r="I3" s="6"/>
     </row>
-    <row r="4" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>964236001</v>
       </c>
@@ -2079,7 +2307,7 @@
       </c>
       <c r="I4" s="6"/>
     </row>
-    <row r="5" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>964236001</v>
       </c>
@@ -2106,7 +2334,7 @@
       </c>
       <c r="I5" s="6"/>
     </row>
-    <row r="6" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>964236001</v>
       </c>
@@ -2133,7 +2361,7 @@
       </c>
       <c r="I6" s="6"/>
     </row>
-    <row r="7" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>964236001</v>
       </c>
@@ -2160,7 +2388,7 @@
       </c>
       <c r="I7" s="6"/>
     </row>
-    <row r="8" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>964236001</v>
       </c>
@@ -2187,7 +2415,7 @@
       </c>
       <c r="I8" s="6"/>
     </row>
-    <row r="9" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>964236001</v>
       </c>
@@ -2214,7 +2442,7 @@
       </c>
       <c r="I9" s="6"/>
     </row>
-    <row r="10" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>964236001</v>
       </c>
@@ -2241,7 +2469,7 @@
       </c>
       <c r="I10" s="6"/>
     </row>
-    <row r="11" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>964236001</v>
       </c>
@@ -2268,7 +2496,7 @@
       </c>
       <c r="I11" s="6"/>
     </row>
-    <row r="12" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>1739129</v>
       </c>
@@ -2295,7 +2523,7 @@
       </c>
       <c r="I12" s="6"/>
     </row>
-    <row r="13" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>1739129</v>
       </c>
@@ -2322,7 +2550,7 @@
       </c>
       <c r="I13" s="6"/>
     </row>
-    <row r="14" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>1739129</v>
       </c>
@@ -2349,7 +2577,7 @@
       </c>
       <c r="I14" s="6"/>
     </row>
-    <row r="15" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>1739129</v>
       </c>
@@ -2376,7 +2604,7 @@
       </c>
       <c r="I15" s="6"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>1739129</v>
       </c>
@@ -2403,7 +2631,7 @@
       </c>
       <c r="I16" s="6"/>
     </row>
-    <row r="17" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>1739129</v>
       </c>
@@ -2430,7 +2658,7 @@
       </c>
       <c r="I17" s="6"/>
     </row>
-    <row r="18" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>1739129</v>
       </c>
@@ -2457,7 +2685,7 @@
       </c>
       <c r="I18" s="6"/>
     </row>
-    <row r="19" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>37452171</v>
       </c>
@@ -2484,7 +2712,7 @@
       </c>
       <c r="I19" s="6"/>
     </row>
-    <row r="20" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>37452171</v>
       </c>
@@ -2511,7 +2739,7 @@
       </c>
       <c r="I20" s="6"/>
     </row>
-    <row r="21" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>37452171</v>
       </c>
@@ -2538,7 +2766,7 @@
       </c>
       <c r="I21" s="6"/>
     </row>
-    <row r="22" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>37452171</v>
       </c>
@@ -2565,7 +2793,7 @@
       </c>
       <c r="I22" s="6"/>
     </row>
-    <row r="23" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>37452171</v>
       </c>
@@ -2592,7 +2820,7 @@
       </c>
       <c r="I23" s="6"/>
     </row>
-    <row r="24" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>37452171</v>
       </c>
@@ -2619,7 +2847,7 @@
       </c>
       <c r="I24" s="6"/>
     </row>
-    <row r="25" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>37452171</v>
       </c>
@@ -2646,7 +2874,7 @@
       </c>
       <c r="I25" s="6"/>
     </row>
-    <row r="26" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A26" s="6">
         <v>37452171</v>
       </c>
@@ -2673,7 +2901,7 @@
       </c>
       <c r="I26" s="6"/>
     </row>
-    <row r="27" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A27" s="6">
         <v>37452171</v>
       </c>
@@ -2700,7 +2928,7 @@
       </c>
       <c r="I27" s="6"/>
     </row>
-    <row r="28" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>37452171</v>
       </c>
@@ -2727,7 +2955,7 @@
       </c>
       <c r="I28" s="6"/>
     </row>
-    <row r="29" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A29" s="6">
         <v>37452171</v>
       </c>
@@ -2754,7 +2982,7 @@
       </c>
       <c r="I29" s="6"/>
     </row>
-    <row r="30" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A30" s="6">
         <v>33790944</v>
       </c>
@@ -2781,7 +3009,7 @@
       </c>
       <c r="I30" s="6"/>
     </row>
-    <row r="31" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A31" s="6">
         <v>33790944</v>
       </c>
@@ -2808,7 +3036,7 @@
       </c>
       <c r="I31" s="6"/>
     </row>
-    <row r="32" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A32" s="6">
         <v>33790944</v>
       </c>
@@ -2835,7 +3063,7 @@
       </c>
       <c r="I32" s="6"/>
     </row>
-    <row r="33" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A33" s="6">
         <v>33790944</v>
       </c>
@@ -2862,7 +3090,7 @@
       </c>
       <c r="I33" s="6"/>
     </row>
-    <row r="34" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A34" s="6">
         <v>33790944</v>
       </c>
@@ -2889,7 +3117,7 @@
       </c>
       <c r="I34" s="6"/>
     </row>
-    <row r="35" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A35" s="6">
         <v>33790944</v>
       </c>
@@ -2916,7 +3144,7 @@
       </c>
       <c r="I35" s="6"/>
     </row>
-    <row r="36" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A36" s="6">
         <v>33790944</v>
       </c>
@@ -2943,7 +3171,7 @@
       </c>
       <c r="I36" s="6"/>
     </row>
-    <row r="37" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A37" s="6">
         <v>33790944</v>
       </c>
@@ -2970,7 +3198,7 @@
       </c>
       <c r="I37" s="6"/>
     </row>
-    <row r="38" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A38" s="6">
         <v>33790944</v>
       </c>
@@ -2997,7 +3225,7 @@
       </c>
       <c r="I38" s="6"/>
     </row>
-    <row r="39" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A39" s="6">
         <v>33790944</v>
       </c>
@@ -3024,7 +3252,7 @@
       </c>
       <c r="I39" s="6"/>
     </row>
-    <row r="40" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A40" s="6">
         <v>926332</v>
       </c>
@@ -3051,7 +3279,7 @@
       </c>
       <c r="I40" s="6"/>
     </row>
-    <row r="41" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A41" s="6">
         <v>926332</v>
       </c>
@@ -3078,7 +3306,7 @@
       </c>
       <c r="I41" s="6"/>
     </row>
-    <row r="42" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A42" s="6">
         <v>926332</v>
       </c>
@@ -3105,7 +3333,7 @@
       </c>
       <c r="I42" s="6"/>
     </row>
-    <row r="43" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A43" s="6">
         <v>926332</v>
       </c>
@@ -3132,7 +3360,7 @@
       </c>
       <c r="I43" s="6"/>
     </row>
-    <row r="44" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A44" s="6">
         <v>926332</v>
       </c>
@@ -3159,7 +3387,7 @@
       </c>
       <c r="I44" s="6"/>
     </row>
-    <row r="45" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A45" s="6">
         <v>926332</v>
       </c>
@@ -3186,7 +3414,7 @@
       </c>
       <c r="I45" s="6"/>
     </row>
-    <row r="46" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A46" s="6">
         <v>926332</v>
       </c>
@@ -3215,7 +3443,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" ht="40.799999999999997" x14ac:dyDescent="0.3">
       <c r="A47" s="6">
         <v>10079558</v>
       </c>
@@ -3244,7 +3472,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A48" s="6">
         <v>10079558</v>
       </c>
@@ -3271,7 +3499,7 @@
       </c>
       <c r="I48" s="6"/>
     </row>
-    <row r="49" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A49" s="6">
         <v>10079558</v>
       </c>
@@ -3298,7 +3526,7 @@
       </c>
       <c r="I49" s="6"/>
     </row>
-    <row r="50" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A50" s="6">
         <v>10079558</v>
       </c>
@@ -3325,7 +3553,7 @@
       </c>
       <c r="I50" s="6"/>
     </row>
-    <row r="51" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A51" s="6">
         <v>10079558</v>
       </c>
@@ -3354,7 +3582,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A52" s="6">
         <v>10079558</v>
       </c>
@@ -3381,7 +3609,7 @@
       </c>
       <c r="I52" s="6"/>
     </row>
-    <row r="53" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A53" s="6">
         <v>10079558</v>
       </c>
@@ -3408,7 +3636,7 @@
       </c>
       <c r="I53" s="6"/>
     </row>
-    <row r="54" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A54" s="6">
         <v>10079558</v>
       </c>
@@ -3435,7 +3663,7 @@
       </c>
       <c r="I54" s="6"/>
     </row>
-    <row r="55" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A55" s="6">
         <v>10079558</v>
       </c>
@@ -3462,7 +3690,7 @@
       </c>
       <c r="I55" s="6"/>
     </row>
-    <row r="56" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A56" s="6">
         <v>2027786</v>
       </c>
@@ -3491,7 +3719,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A57" s="6">
         <v>2027786</v>
       </c>
@@ -3518,7 +3746,7 @@
       </c>
       <c r="I57" s="6"/>
     </row>
-    <row r="58" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A58" s="6">
         <v>2027786</v>
       </c>
@@ -3545,7 +3773,7 @@
       </c>
       <c r="I58" s="6"/>
     </row>
-    <row r="59" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" ht="40.799999999999997" x14ac:dyDescent="0.3">
       <c r="A59" s="6">
         <v>2027786</v>
       </c>
@@ -3572,7 +3800,7 @@
       </c>
       <c r="I59" s="6"/>
     </row>
-    <row r="60" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A60" s="6">
         <v>2027786</v>
       </c>
@@ -3599,7 +3827,7 @@
       </c>
       <c r="I60" s="6"/>
     </row>
-    <row r="61" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A61" s="6">
         <v>2027786</v>
       </c>
@@ -3626,7 +3854,7 @@
       </c>
       <c r="I61" s="6"/>
     </row>
-    <row r="62" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="6">
         <v>2027786</v>
       </c>
@@ -3653,7 +3881,7 @@
       </c>
       <c r="I62" s="6"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="6">
         <v>2027786</v>
       </c>
@@ -3680,7 +3908,7 @@
       </c>
       <c r="I63" s="6"/>
     </row>
-    <row r="64" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" ht="51" x14ac:dyDescent="0.3">
       <c r="A64" s="6">
         <v>2027786</v>
       </c>
@@ -3707,7 +3935,7 @@
       </c>
       <c r="I64" s="6"/>
     </row>
-    <row r="65" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A65" s="6">
         <v>35339929</v>
       </c>
@@ -3736,7 +3964,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A66" s="6">
         <v>35339929</v>
       </c>
@@ -3763,7 +3991,7 @@
       </c>
       <c r="I66" s="6"/>
     </row>
-    <row r="67" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A67" s="6">
         <v>35339929</v>
       </c>
@@ -3790,7 +4018,7 @@
       </c>
       <c r="I67" s="6"/>
     </row>
-    <row r="68" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A68" s="6">
         <v>35339929</v>
       </c>
@@ -3817,7 +4045,7 @@
       </c>
       <c r="I68" s="6"/>
     </row>
-    <row r="69" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A69" s="6">
         <v>35339929</v>
       </c>
@@ -3844,7 +4072,7 @@
       </c>
       <c r="I69" s="6"/>
     </row>
-    <row r="70" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" ht="40.799999999999997" x14ac:dyDescent="0.3">
       <c r="A70" s="6">
         <v>35339929</v>
       </c>
@@ -3871,7 +4099,7 @@
       </c>
       <c r="I70" s="6"/>
     </row>
-    <row r="71" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" ht="40.799999999999997" x14ac:dyDescent="0.3">
       <c r="A71" s="6">
         <v>31106519</v>
       </c>
@@ -3900,7 +4128,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A72" s="6">
         <v>31106519</v>
       </c>
@@ -3929,7 +4157,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A73" s="6">
         <v>31106519</v>
       </c>
@@ -3956,7 +4184,7 @@
       </c>
       <c r="I73" s="6"/>
     </row>
-    <row r="74" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A74" s="6">
         <v>31106519</v>
       </c>
@@ -3985,7 +4213,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A75" s="6">
         <v>31106519</v>
       </c>
@@ -4012,7 +4240,7 @@
       </c>
       <c r="I75" s="6"/>
     </row>
-    <row r="76" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" ht="40.799999999999997" x14ac:dyDescent="0.3">
       <c r="A76" s="6">
         <v>31106519</v>
       </c>
@@ -4041,7 +4269,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A77" s="6">
         <v>21229427</v>
       </c>
@@ -4068,7 +4296,7 @@
       </c>
       <c r="I77" s="6"/>
     </row>
-    <row r="78" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A78" s="6">
         <v>21229427</v>
       </c>
@@ -4095,7 +4323,7 @@
       </c>
       <c r="I78" s="6"/>
     </row>
-    <row r="79" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A79" s="6">
         <v>21229427</v>
       </c>
@@ -4122,7 +4350,7 @@
       </c>
       <c r="I79" s="6"/>
     </row>
-    <row r="80" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A80" s="6">
         <v>21229427</v>
       </c>
@@ -4149,7 +4377,7 @@
       </c>
       <c r="I80" s="6"/>
     </row>
-    <row r="81" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A81" s="6">
         <v>21229427</v>
       </c>
@@ -4176,7 +4404,7 @@
       </c>
       <c r="I81" s="6"/>
     </row>
-    <row r="82" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" ht="40.799999999999997" x14ac:dyDescent="0.3">
       <c r="A82" s="6">
         <v>21229427</v>
       </c>
@@ -4203,7 +4431,7 @@
       </c>
       <c r="I82" s="6"/>
     </row>
-    <row r="83" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A83" s="6">
         <v>21229427</v>
       </c>
@@ -4232,7 +4460,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A84" s="6">
         <v>24362534</v>
       </c>
@@ -4259,7 +4487,7 @@
       </c>
       <c r="I84" s="6"/>
     </row>
-    <row r="85" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A85" s="6">
         <v>24362534</v>
       </c>
@@ -4286,7 +4514,7 @@
       </c>
       <c r="I85" s="6"/>
     </row>
-    <row r="86" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A86" s="6">
         <v>24362534</v>
       </c>
@@ -4313,7 +4541,7 @@
       </c>
       <c r="I86" s="6"/>
     </row>
-    <row r="87" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A87" s="6">
         <v>24362534</v>
       </c>
@@ -4340,7 +4568,7 @@
       </c>
       <c r="I87" s="6"/>
     </row>
-    <row r="88" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A88" s="6">
         <v>24362534</v>
       </c>
@@ -4367,7 +4595,7 @@
       </c>
       <c r="I88" s="6"/>
     </row>
-    <row r="89" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A89" s="6">
         <v>24362534</v>
       </c>
@@ -4394,7 +4622,7 @@
       </c>
       <c r="I89" s="6"/>
     </row>
-    <row r="90" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A90" s="6">
         <v>24362534</v>
       </c>
@@ -4421,7 +4649,7 @@
       </c>
       <c r="I90" s="6"/>
     </row>
-    <row r="91" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A91" s="6">
         <v>24362534</v>
       </c>
@@ -4448,7 +4676,7 @@
       </c>
       <c r="I91" s="6"/>
     </row>
-    <row r="92" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A92" s="6">
         <v>24362534</v>
       </c>
@@ -4475,7 +4703,7 @@
       </c>
       <c r="I92" s="6"/>
     </row>
-    <row r="93" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A93" s="6">
         <v>24362534</v>
       </c>
@@ -4502,7 +4730,7 @@
       </c>
       <c r="I93" s="6"/>
     </row>
-    <row r="94" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A94" s="6">
         <v>24362534</v>
       </c>
@@ -4529,7 +4757,7 @@
       </c>
       <c r="I94" s="6"/>
     </row>
-    <row r="95" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A95" s="6">
         <v>24362534</v>
       </c>
@@ -4555,6 +4783,338 @@
         <v>347</v>
       </c>
       <c r="I95" s="6"/>
+    </row>
+    <row r="96" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A96" s="6">
+        <v>24831386</v>
+      </c>
+      <c r="B96" s="6">
+        <v>1</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="D96" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="E96" s="8">
+        <v>4.47</v>
+      </c>
+      <c r="F96" s="8">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G96" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H96" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="I96" s="6" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A97" s="6">
+        <v>24831386</v>
+      </c>
+      <c r="B97" s="6">
+        <v>2</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="E97" s="8">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="F97" s="8">
+        <v>4.75</v>
+      </c>
+      <c r="G97" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="H97" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="I97" s="6"/>
+    </row>
+    <row r="98" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A98" s="6">
+        <v>24831386</v>
+      </c>
+      <c r="B98" s="6">
+        <v>3</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="E98" s="8">
+        <v>3.63</v>
+      </c>
+      <c r="F98" s="8">
+        <v>4</v>
+      </c>
+      <c r="G98" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="H98" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="I98" s="6"/>
+    </row>
+    <row r="99" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A99" s="6">
+        <v>24831386</v>
+      </c>
+      <c r="B99" s="6">
+        <v>4</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="E99" s="8">
+        <v>4.58</v>
+      </c>
+      <c r="F99" s="8">
+        <v>5</v>
+      </c>
+      <c r="G99" s="8">
+        <v>4.8</v>
+      </c>
+      <c r="H99" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="I99" s="6" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A100" s="6">
+        <v>24831386</v>
+      </c>
+      <c r="B100" s="6">
+        <v>5</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="D100" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="E100" s="8">
+        <v>3.86</v>
+      </c>
+      <c r="F100" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="G100" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="H100" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="I100" s="6"/>
+    </row>
+    <row r="101" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A101" s="6">
+        <v>24831386</v>
+      </c>
+      <c r="B101" s="6">
+        <v>6</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="E101" s="8">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="F101" s="8">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="G101" s="8">
+        <v>4.7</v>
+      </c>
+      <c r="H101" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="I101" s="6"/>
+    </row>
+    <row r="102" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A102" s="6">
+        <v>24831386</v>
+      </c>
+      <c r="B102" s="6">
+        <v>7</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="D102" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="E102" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="F102" s="8">
+        <v>4.8</v>
+      </c>
+      <c r="G102" s="8">
+        <v>4.75</v>
+      </c>
+      <c r="H102" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="I102" s="6"/>
+    </row>
+    <row r="103" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A103" s="6">
+        <v>24831386</v>
+      </c>
+      <c r="B103" s="6">
+        <v>8</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="E103" s="8">
+        <v>4.49</v>
+      </c>
+      <c r="F103" s="8">
+        <v>5</v>
+      </c>
+      <c r="G103" s="8">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="H103" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="I103" s="6" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A104" s="6">
+        <v>6503426</v>
+      </c>
+      <c r="B104" s="6">
+        <v>1</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="D104" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="E104" s="8">
+        <v>3.87</v>
+      </c>
+      <c r="F104" s="8">
+        <v>4.8</v>
+      </c>
+      <c r="G104" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H104" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="I104" s="6"/>
+    </row>
+    <row r="105" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A105" s="6">
+        <v>6503426</v>
+      </c>
+      <c r="B105" s="6">
+        <v>2</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="D105" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="E105" s="8">
+        <v>3.82</v>
+      </c>
+      <c r="F105" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G105" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="H105" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="I105" s="6"/>
+    </row>
+    <row r="106" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A106" s="6">
+        <v>6503426</v>
+      </c>
+      <c r="B106" s="6">
+        <v>3</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="D106" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="E106" s="8">
+        <v>3.65</v>
+      </c>
+      <c r="F106" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="G106" s="8">
+        <v>4.45</v>
+      </c>
+      <c r="H106" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="I106" s="6" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A107" s="6">
+        <v>6503426</v>
+      </c>
+      <c r="B107" s="6">
+        <v>4</v>
+      </c>
+      <c r="C107" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="D107" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="E107" s="8">
+        <v>3.57</v>
+      </c>
+      <c r="F107" s="8">
+        <v>4.25</v>
+      </c>
+      <c r="G107" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H107" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="I107" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pak\Music\Victoria\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{932C3D31-649B-4F3F-9B64-702739301B75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA438290-4395-46D5-9EF7-0CEFC31AAC7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="439">
   <si>
     <t>No</t>
   </si>
@@ -1255,6 +1255,102 @@
   </si>
   <si>
     <t>https://i.discogs.com/Cs-MD9yqq0a1InQwB2TLzIvOfzdVsDgOPgE2IjVVHTg/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTY1MDM0/MjYtMTU0MjI3NTY4/Ny05NzA4LmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>Fargo</t>
+  </si>
+  <si>
+    <t>Frontpage Lover</t>
+  </si>
+  <si>
+    <t>Harvest / EMI Electrola – 1C 064-46 280 (Germany Original 1st Pressing - LC 1305 - Matrix: 46280-A2 / 46280-B2 - ID 920311)</t>
+  </si>
+  <si>
+    <t>Hard Rock, AOR</t>
+  </si>
+  <si>
+    <t>A Girl Like A Trigger</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Rock</t>
+  </si>
+  <si>
+    <t>Sumaker</t>
+  </si>
+  <si>
+    <t>27 Hours A Day</t>
+  </si>
+  <si>
+    <t>Hard Rock, Melodic Rock</t>
+  </si>
+  <si>
+    <t>Arrows In The Wind</t>
+  </si>
+  <si>
+    <t>Hard Rock, Rock Ballad</t>
+  </si>
+  <si>
+    <t>Tokyo</t>
+  </si>
+  <si>
+    <t>Angel</t>
+  </si>
+  <si>
+    <t>Little Miss Mystery</t>
+  </si>
+  <si>
+    <t>Heavy Rock, Hard Rock</t>
+  </si>
+  <si>
+    <t>Take Saeix</t>
+  </si>
+  <si>
+    <t>Hard Rock Interlude</t>
+  </si>
+  <si>
+    <t>Wheel Of Fortune</t>
+  </si>
+  <si>
+    <t>Hard Rock, Melodic Rock, AOR</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το 3ο στούντιο άλμπουμ των Γερμανών πρωτοπόρων του hard rock Fargo (1981) στην Harvest. Παραγωγή στα Horus Sound Studios και EMI Studios Cologne. Σύμφωνα με κριτικές αρχείων (John Tucker / Arrow Lords of Metal), ο δίσκος χαρακτηρίζεται από έντονα 80s στοιχεία, με το ομώνυμο κομμάτι και το επικό «Little Miss Mystery» να ξεχωρίζουν. | Hard Facts Έκδοσης: Αυθεντική 1η γερμανική κοπή (1C 064-46 280 / LC 1305 / ID 920311). Χαραγμένες μήτρες 46280-A2 / 46280-B2. Ηχητική Αξιολόγηση (4.20/5): Κλασική, διαυγής παραγωγή αρχών δεκαετίας '80 από την EMI Electrola, με καθαρά φωνητικά, καλό στερεοφωνικό διαχωρισμό και τυπικό analog mastering της εποχής.</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/920311-Fargo-Frontpage-Lover</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/QVvxbNBePe7chMHTZIrtFqGDMIiMcqkg1qJViofeAaY/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTkyMDMx/MS0xNjg5NzUxMjM1/LTc4MTguanBlZw.jpeg</t>
+  </si>
+  <si>
+    <t>Το ομώνυμο εναρκτήριο κομμάτι που ξεχωρίζει στον δίσκο. Κλασικό 80s hard rock riff, κολλητικό ρεφρέν και καθαρή γερμανική παραγωγή.</t>
+  </si>
+  <si>
+    <t>Ευθύγραμμο γερμανικό hard rock με γρήγορο tempo και στιβαρό rhythm section.</t>
+  </si>
+  <si>
+    <t>Τυπικό track της A-side, λειτουργεί υποστηρικτικά στη ροή του άλμπουμ.</t>
+  </si>
+  <si>
+    <t>Mid-tempo μελωδική σύνθεση με καθαρή άρθρωση στα φωνητικά και ισορροπημένη μίξη.</t>
+  </si>
+  <si>
+    <t>Διαθέτει ακουστικά περάσματα που διευρύνουν το dynamic range της πρώτης πλευράς.</t>
+  </si>
+  <si>
+    <t>Ένα από τα δυνατά σημεία του δίσκου. Γρήγορο tempo, κοφτά riffs και επιθετικό παίξιμο στα τύμπανα.</t>
+  </si>
+  <si>
+    <t>Τυπική 80s AOR/μελωδική φόρμα με προβλέψιμη δομή.</t>
+  </si>
+  <si>
+    <t>Το συνθετικό αποκορύφωμα και μεγαλύτερο σε διάρκεια κομμάτι του LP (5:38). Πιο σύνθετη δομή και πολυεπίπεδα κιθαριστικά μέρη.</t>
+  </si>
+  <si>
+    <t>Σύντομο οργανικό/ρυθμικό πέρασμα 33 δευτερολέπτων.</t>
+  </si>
+  <si>
+    <t>Δυναμικό κλείσιμο του δίσκου με σταθερό ρυθμικό δέσιμο.</t>
   </si>
 </sst>
 </file>
@@ -1683,7 +1779,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" style="1" bestFit="1" customWidth="1"/>
@@ -2145,6 +2241,38 @@
       </c>
       <c r="J14" s="11" t="s">
         <v>406</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="51" x14ac:dyDescent="0.3">
+      <c r="A15" s="6">
+        <v>920311</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="D15" s="6">
+        <v>1981</v>
+      </c>
+      <c r="E15" s="10">
+        <v>3.45</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>427</v>
+      </c>
+      <c r="J15" s="11" t="s">
+        <v>428</v>
       </c>
     </row>
   </sheetData>
@@ -2175,6 +2303,8 @@
     <hyperlink ref="J13" r:id="rId24" xr:uid="{8EE506D2-8E16-47D1-A8EC-6F5329B2DA47}"/>
     <hyperlink ref="I14" r:id="rId25" xr:uid="{D99AD04E-22D7-4523-A906-354DCA3D59B8}"/>
     <hyperlink ref="J14" r:id="rId26" xr:uid="{3F9ECA46-C0F1-4A2C-A780-DD9645DE1436}"/>
+    <hyperlink ref="I15" r:id="rId27" xr:uid="{866AD757-F7B0-4150-A72D-D36A6753C9D2}"/>
+    <hyperlink ref="J15" r:id="rId28" xr:uid="{653E9D3F-45EA-4E17-836F-D51F97914679}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2182,7 +2312,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I107"/>
+  <dimension ref="A1:I117"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="10.199999999999999" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3" bestFit="1" customWidth="1"/>
@@ -5116,7 +5246,280 @@
       </c>
       <c r="I107" s="6"/>
     </row>
+    <row r="108" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A108" s="6">
+        <v>920311</v>
+      </c>
+      <c r="B108" s="6">
+        <v>1</v>
+      </c>
+      <c r="C108" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="D108" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="E108" s="8">
+        <v>4.25</v>
+      </c>
+      <c r="F108" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="G108" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="H108" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="I108" s="6"/>
+    </row>
+    <row r="109" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A109" s="6">
+        <v>920311</v>
+      </c>
+      <c r="B109" s="6">
+        <v>2</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="D109" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="E109" s="8">
+        <v>4.25</v>
+      </c>
+      <c r="F109" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="G109" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="H109" s="9" t="s">
+        <v>430</v>
+      </c>
+      <c r="I109" s="6" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A110" s="6">
+        <v>920311</v>
+      </c>
+      <c r="B110" s="6">
+        <v>3</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="D110" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="E110" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="F110" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="G110" s="8">
+        <v>3.45</v>
+      </c>
+      <c r="H110" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="I110" s="6"/>
+    </row>
+    <row r="111" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A111" s="6">
+        <v>920311</v>
+      </c>
+      <c r="B111" s="6">
+        <v>4</v>
+      </c>
+      <c r="C111" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="D111" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="E111" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="F111" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="G111" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="H111" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="I111" s="6"/>
+    </row>
+    <row r="112" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A112" s="6">
+        <v>920311</v>
+      </c>
+      <c r="B112" s="6">
+        <v>5</v>
+      </c>
+      <c r="C112" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="D112" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="E112" s="8">
+        <v>4.33</v>
+      </c>
+      <c r="F112" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="G112" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="H112" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="I112" s="6"/>
+    </row>
+    <row r="113" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A113" s="6">
+        <v>920311</v>
+      </c>
+      <c r="B113" s="6">
+        <v>6</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="E113" s="8">
+        <v>4</v>
+      </c>
+      <c r="F113" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="G113" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="H113" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="I113" s="6"/>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A114" s="6">
+        <v>920311</v>
+      </c>
+      <c r="B114" s="6">
+        <v>7</v>
+      </c>
+      <c r="C114" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="D114" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="E114" s="8">
+        <v>4.25</v>
+      </c>
+      <c r="F114" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="G114" s="8">
+        <v>3.55</v>
+      </c>
+      <c r="H114" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="I114" s="6"/>
+    </row>
+    <row r="115" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A115" s="6">
+        <v>920311</v>
+      </c>
+      <c r="B115" s="6">
+        <v>8</v>
+      </c>
+      <c r="C115" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="D115" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="E115" s="8">
+        <v>4</v>
+      </c>
+      <c r="F115" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="G115" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="H115" s="9" t="s">
+        <v>436</v>
+      </c>
+      <c r="I115" s="6"/>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A116" s="6">
+        <v>920311</v>
+      </c>
+      <c r="B116" s="6">
+        <v>9</v>
+      </c>
+      <c r="C116" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="D116" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="E116" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="F116" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="G116" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="H116" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="I116" s="6"/>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A117" s="6">
+        <v>920311</v>
+      </c>
+      <c r="B117" s="6">
+        <v>10</v>
+      </c>
+      <c r="C117" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="D117" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="E117" s="8">
+        <v>3.75</v>
+      </c>
+      <c r="F117" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="G117" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="H117" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I117" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -1,40 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pak\Music\Victoria\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA438290-4395-46D5-9EF7-0CEFC31AAC7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E54F6306-946B-4FBD-97E6-B5DE2126AA28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
     <sheet name="tracks" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="466">
   <si>
     <t>No</t>
   </si>
@@ -1351,6 +1338,87 @@
   </si>
   <si>
     <t>Δυναμικό κλείσιμο του δίσκου με σταθερό ρυθμικό δέσιμο.</t>
+  </si>
+  <si>
+    <t>Fastway</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal, Blues Rock</t>
+  </si>
+  <si>
+    <t>CBS – CBS 25359 (Europe / UK Aston Clinton Pressing - Sterling Sound Master - Matrix: CBS 25359-A4 STERLING / CBS 25359-B4 STERLING - ID 2138840)</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/2138840-Fastway-Fastway</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/QRjX6a_r0NQZiD21bc3AaGCbJevs1vLUR7MnPt6YV4U/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTIxMzg4/NDAtMTQ5NDQ5MDcy/NS05MDk1LmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το εκρηκτικό ντεμπούτο (1983) του σχήματος των Fast Eddie Clarke (Motörhead) και Dave King στα φωνητικά. Παραγωγή από τον Eddie Kramer. | Hard Facts Έκδοσης: Ευρωπαϊκή/UK κοπή της CBS (CBS 25359 / ID 2138840). Lacquer cut στα Sterling Sound (USA) από master tapes (σφραγίδα «STERLING» στα runouts A4/B4). Ηχητική Αξιολόγηση (4.45/5): Εξαιρετικά «ζεστός» αναλογικός ήχος με Sterling Sound mastering, τεράστιο dynamic range, κοφτές κιθάρες και αέρινη στερεοφωνική εικόνα.</t>
+  </si>
+  <si>
+    <t>Easy Livin'</t>
+  </si>
+  <si>
+    <t>Το απόλυτο εναρκτήριο anthem. Καταιγιστικό riffing από τον Eddie Clarke, φοβερά φωνητικά από τον Dave King και συμπαγές rhythm section.</t>
+  </si>
+  <si>
+    <t>Feel Me, Touch Me (Do Anything You Want)</t>
+  </si>
+  <si>
+    <t>Groovy mid-tempo track με βαριά blues-rock υπόσταση. Καθαρός διαχωρισμός στα πιατίνια και σφιχτή μπότα.</t>
+  </si>
+  <si>
+    <t>All I Need Is Your Love</t>
+  </si>
+  <si>
+    <t>Δυναμικό track με κοφτά κιθαριστικά θέματα και έντονη αίσθηση χώρου στη μίξη του Kramer.</t>
+  </si>
+  <si>
+    <t>Another Day</t>
+  </si>
+  <si>
+    <t>Η πιο ατμοσφαιρική στιγμή της A-side. Ακουστικά και ηλεκτρικά layers με εξαιρετικό dynamic range.</t>
+  </si>
+  <si>
+    <t>Heft!</t>
+  </si>
+  <si>
+    <t>Heavy Metal, NWOBHM</t>
+  </si>
+  <si>
+    <t>Βαρύ, καλπάζον riff που κλείνει την πρώτη πλευρά με αστείρευτη ενέργεια.</t>
+  </si>
+  <si>
+    <t>We Become One</t>
+  </si>
+  <si>
+    <t>Εκρηκτική έναρξη της B-side. Κοφτερά riffs, εξαιρετική άρθρωση στα φωνητικά και αέρινα υψίσυχνα.</t>
+  </si>
+  <si>
+    <t>Give It All You Got</t>
+  </si>
+  <si>
+    <t>Ευθύγραμμο 80s hard rock με έντονο drive και κλασική δομή.</t>
+  </si>
+  <si>
+    <t>Say What You Will</t>
+  </si>
+  <si>
+    <t>Το συνθετικό highlight και το πιο αναγνωρίσιμο single του LP. Μνημειώδες riff και καταιγιστικός ρυθμός.</t>
+  </si>
+  <si>
+    <t>You Got Me Runnin'</t>
+  </si>
+  <si>
+    <t>B4 track. Γρήγορο, επιθετικό rocker που διατηρεί τη δυναμική της B-side.</t>
+  </si>
+  <si>
+    <t>Give It Some Action</t>
+  </si>
+  <si>
+    <t>B5 track. Μεγαλεπήβολο, bluesy κλείσιμο του δίσκου. Πολυεπίπεδη δομή, φοβερή αίσθηση βάθους (depth) και Sterling Sound dynamic range.</t>
   </si>
 </sst>
 </file>
@@ -1476,8 +1544,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Κανονικό" xfId="0" builtinId="0"/>
+    <cellStyle name="Υπερ-σύνδεση" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1779,23 +1847,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J15"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J16"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="31.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="96.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="96.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="35" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="50.44140625" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.109375" style="1"/>
+    <col min="10" max="10" width="50.42578125" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>33</v>
       </c>
@@ -1827,7 +1895,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="61.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="63" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
         <v>964236001</v>
       </c>
@@ -1859,7 +1927,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="42" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>1739129</v>
       </c>
@@ -1891,7 +1959,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="42" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>37452171</v>
       </c>
@@ -1923,7 +1991,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="42" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>33790944</v>
       </c>
@@ -1955,7 +2023,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="51" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>926332</v>
       </c>
@@ -1987,7 +2055,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="51" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="63" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>10079558</v>
       </c>
@@ -2019,7 +2087,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="61.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="63" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>2027786</v>
       </c>
@@ -2051,7 +2119,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="61.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="63" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>35339929</v>
       </c>
@@ -2083,7 +2151,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="51" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="63" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>31106519</v>
       </c>
@@ -2115,7 +2183,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="61.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="63" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>21229427</v>
       </c>
@@ -2147,7 +2215,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="61.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="73.5" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>24362534</v>
       </c>
@@ -2179,7 +2247,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="61.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="73.5" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>24831386</v>
       </c>
@@ -2211,7 +2279,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="51" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" ht="63" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>6503426</v>
       </c>
@@ -2243,7 +2311,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="51" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" ht="63" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>920311</v>
       </c>
@@ -2273,6 +2341,38 @@
       </c>
       <c r="J15" s="11" t="s">
         <v>428</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="84" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
+        <v>2138840</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="D16" s="6">
+        <v>1983</v>
+      </c>
+      <c r="E16" s="10">
+        <v>3.48</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>444</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>442</v>
+      </c>
+      <c r="J16" s="11" t="s">
+        <v>443</v>
       </c>
     </row>
   </sheetData>
@@ -2305,6 +2405,8 @@
     <hyperlink ref="J14" r:id="rId26" xr:uid="{3F9ECA46-C0F1-4A2C-A780-DD9645DE1436}"/>
     <hyperlink ref="I15" r:id="rId27" xr:uid="{866AD757-F7B0-4150-A72D-D36A6753C9D2}"/>
     <hyperlink ref="J15" r:id="rId28" xr:uid="{653E9D3F-45EA-4E17-836F-D51F97914679}"/>
+    <hyperlink ref="I16" r:id="rId29" xr:uid="{78E3F96C-2AC2-4B9F-A821-519BF5B5CA6A}"/>
+    <hyperlink ref="J16" r:id="rId30" xr:uid="{0D92D6CB-079F-4183-8D1A-1BFEDEE2C7D0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2312,22 +2414,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I117"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="10.199999999999999" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I127"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="3" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.33203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.44140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="50.6640625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="12.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.109375" style="3"/>
+    <col min="3" max="3" width="28.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="50.7109375" style="3" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>33</v>
       </c>
@@ -2356,7 +2458,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
         <v>964236001</v>
       </c>
@@ -2383,7 +2485,7 @@
       </c>
       <c r="I2" s="6"/>
     </row>
-    <row r="3" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>964236001</v>
       </c>
@@ -2410,7 +2512,7 @@
       </c>
       <c r="I3" s="6"/>
     </row>
-    <row r="4" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>964236001</v>
       </c>
@@ -2437,7 +2539,7 @@
       </c>
       <c r="I4" s="6"/>
     </row>
-    <row r="5" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>964236001</v>
       </c>
@@ -2464,7 +2566,7 @@
       </c>
       <c r="I5" s="6"/>
     </row>
-    <row r="6" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>964236001</v>
       </c>
@@ -2491,7 +2593,7 @@
       </c>
       <c r="I6" s="6"/>
     </row>
-    <row r="7" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>964236001</v>
       </c>
@@ -2518,7 +2620,7 @@
       </c>
       <c r="I7" s="6"/>
     </row>
-    <row r="8" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>964236001</v>
       </c>
@@ -2545,7 +2647,7 @@
       </c>
       <c r="I8" s="6"/>
     </row>
-    <row r="9" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>964236001</v>
       </c>
@@ -2572,7 +2674,7 @@
       </c>
       <c r="I9" s="6"/>
     </row>
-    <row r="10" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>964236001</v>
       </c>
@@ -2599,7 +2701,7 @@
       </c>
       <c r="I10" s="6"/>
     </row>
-    <row r="11" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>964236001</v>
       </c>
@@ -2626,7 +2728,7 @@
       </c>
       <c r="I11" s="6"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>1739129</v>
       </c>
@@ -2653,7 +2755,7 @@
       </c>
       <c r="I12" s="6"/>
     </row>
-    <row r="13" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>1739129</v>
       </c>
@@ -2680,7 +2782,7 @@
       </c>
       <c r="I13" s="6"/>
     </row>
-    <row r="14" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>1739129</v>
       </c>
@@ -2707,7 +2809,7 @@
       </c>
       <c r="I14" s="6"/>
     </row>
-    <row r="15" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>1739129</v>
       </c>
@@ -2734,7 +2836,7 @@
       </c>
       <c r="I15" s="6"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>1739129</v>
       </c>
@@ -2761,7 +2863,7 @@
       </c>
       <c r="I16" s="6"/>
     </row>
-    <row r="17" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>1739129</v>
       </c>
@@ -2788,7 +2890,7 @@
       </c>
       <c r="I17" s="6"/>
     </row>
-    <row r="18" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>1739129</v>
       </c>
@@ -2815,7 +2917,7 @@
       </c>
       <c r="I18" s="6"/>
     </row>
-    <row r="19" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>37452171</v>
       </c>
@@ -2842,7 +2944,7 @@
       </c>
       <c r="I19" s="6"/>
     </row>
-    <row r="20" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>37452171</v>
       </c>
@@ -2869,7 +2971,7 @@
       </c>
       <c r="I20" s="6"/>
     </row>
-    <row r="21" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>37452171</v>
       </c>
@@ -2896,7 +2998,7 @@
       </c>
       <c r="I21" s="6"/>
     </row>
-    <row r="22" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>37452171</v>
       </c>
@@ -2923,7 +3025,7 @@
       </c>
       <c r="I22" s="6"/>
     </row>
-    <row r="23" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>37452171</v>
       </c>
@@ -2950,7 +3052,7 @@
       </c>
       <c r="I23" s="6"/>
     </row>
-    <row r="24" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>37452171</v>
       </c>
@@ -2977,7 +3079,7 @@
       </c>
       <c r="I24" s="6"/>
     </row>
-    <row r="25" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>37452171</v>
       </c>
@@ -3004,7 +3106,7 @@
       </c>
       <c r="I25" s="6"/>
     </row>
-    <row r="26" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>37452171</v>
       </c>
@@ -3031,7 +3133,7 @@
       </c>
       <c r="I26" s="6"/>
     </row>
-    <row r="27" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>37452171</v>
       </c>
@@ -3058,7 +3160,7 @@
       </c>
       <c r="I27" s="6"/>
     </row>
-    <row r="28" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>37452171</v>
       </c>
@@ -3085,7 +3187,7 @@
       </c>
       <c r="I28" s="6"/>
     </row>
-    <row r="29" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>37452171</v>
       </c>
@@ -3112,7 +3214,7 @@
       </c>
       <c r="I29" s="6"/>
     </row>
-    <row r="30" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>33790944</v>
       </c>
@@ -3139,7 +3241,7 @@
       </c>
       <c r="I30" s="6"/>
     </row>
-    <row r="31" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>33790944</v>
       </c>
@@ -3166,7 +3268,7 @@
       </c>
       <c r="I31" s="6"/>
     </row>
-    <row r="32" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>33790944</v>
       </c>
@@ -3193,7 +3295,7 @@
       </c>
       <c r="I32" s="6"/>
     </row>
-    <row r="33" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>33790944</v>
       </c>
@@ -3220,7 +3322,7 @@
       </c>
       <c r="I33" s="6"/>
     </row>
-    <row r="34" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>33790944</v>
       </c>
@@ -3247,7 +3349,7 @@
       </c>
       <c r="I34" s="6"/>
     </row>
-    <row r="35" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>33790944</v>
       </c>
@@ -3274,7 +3376,7 @@
       </c>
       <c r="I35" s="6"/>
     </row>
-    <row r="36" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>33790944</v>
       </c>
@@ -3301,7 +3403,7 @@
       </c>
       <c r="I36" s="6"/>
     </row>
-    <row r="37" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>33790944</v>
       </c>
@@ -3328,7 +3430,7 @@
       </c>
       <c r="I37" s="6"/>
     </row>
-    <row r="38" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>33790944</v>
       </c>
@@ -3355,7 +3457,7 @@
       </c>
       <c r="I38" s="6"/>
     </row>
-    <row r="39" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>33790944</v>
       </c>
@@ -3382,7 +3484,7 @@
       </c>
       <c r="I39" s="6"/>
     </row>
-    <row r="40" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>926332</v>
       </c>
@@ -3409,7 +3511,7 @@
       </c>
       <c r="I40" s="6"/>
     </row>
-    <row r="41" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>926332</v>
       </c>
@@ -3436,7 +3538,7 @@
       </c>
       <c r="I41" s="6"/>
     </row>
-    <row r="42" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>926332</v>
       </c>
@@ -3463,7 +3565,7 @@
       </c>
       <c r="I42" s="6"/>
     </row>
-    <row r="43" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>926332</v>
       </c>
@@ -3490,7 +3592,7 @@
       </c>
       <c r="I43" s="6"/>
     </row>
-    <row r="44" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>926332</v>
       </c>
@@ -3517,7 +3619,7 @@
       </c>
       <c r="I44" s="6"/>
     </row>
-    <row r="45" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>926332</v>
       </c>
@@ -3544,7 +3646,7 @@
       </c>
       <c r="I45" s="6"/>
     </row>
-    <row r="46" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>926332</v>
       </c>
@@ -3573,7 +3675,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>10079558</v>
       </c>
@@ -3602,7 +3704,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>10079558</v>
       </c>
@@ -3629,7 +3731,7 @@
       </c>
       <c r="I48" s="6"/>
     </row>
-    <row r="49" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>10079558</v>
       </c>
@@ -3656,7 +3758,7 @@
       </c>
       <c r="I49" s="6"/>
     </row>
-    <row r="50" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>10079558</v>
       </c>
@@ -3683,7 +3785,7 @@
       </c>
       <c r="I50" s="6"/>
     </row>
-    <row r="51" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>10079558</v>
       </c>
@@ -3712,7 +3814,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>10079558</v>
       </c>
@@ -3739,7 +3841,7 @@
       </c>
       <c r="I52" s="6"/>
     </row>
-    <row r="53" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>10079558</v>
       </c>
@@ -3766,7 +3868,7 @@
       </c>
       <c r="I53" s="6"/>
     </row>
-    <row r="54" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
         <v>10079558</v>
       </c>
@@ -3793,7 +3895,7 @@
       </c>
       <c r="I54" s="6"/>
     </row>
-    <row r="55" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
         <v>10079558</v>
       </c>
@@ -3820,7 +3922,7 @@
       </c>
       <c r="I55" s="6"/>
     </row>
-    <row r="56" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
         <v>2027786</v>
       </c>
@@ -3849,7 +3951,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
         <v>2027786</v>
       </c>
@@ -3876,7 +3978,7 @@
       </c>
       <c r="I57" s="6"/>
     </row>
-    <row r="58" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
         <v>2027786</v>
       </c>
@@ -3903,7 +4005,7 @@
       </c>
       <c r="I58" s="6"/>
     </row>
-    <row r="59" spans="1:9" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
         <v>2027786</v>
       </c>
@@ -3930,7 +4032,7 @@
       </c>
       <c r="I59" s="6"/>
     </row>
-    <row r="60" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
         <v>2027786</v>
       </c>
@@ -3957,7 +4059,7 @@
       </c>
       <c r="I60" s="6"/>
     </row>
-    <row r="61" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
         <v>2027786</v>
       </c>
@@ -3984,7 +4086,7 @@
       </c>
       <c r="I61" s="6"/>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
         <v>2027786</v>
       </c>
@@ -4011,7 +4113,7 @@
       </c>
       <c r="I62" s="6"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
         <v>2027786</v>
       </c>
@@ -4038,7 +4140,7 @@
       </c>
       <c r="I63" s="6"/>
     </row>
-    <row r="64" spans="1:9" ht="51" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
         <v>2027786</v>
       </c>
@@ -4065,7 +4167,7 @@
       </c>
       <c r="I64" s="6"/>
     </row>
-    <row r="65" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
         <v>35339929</v>
       </c>
@@ -4094,7 +4196,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
         <v>35339929</v>
       </c>
@@ -4121,7 +4223,7 @@
       </c>
       <c r="I66" s="6"/>
     </row>
-    <row r="67" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>35339929</v>
       </c>
@@ -4148,7 +4250,7 @@
       </c>
       <c r="I67" s="6"/>
     </row>
-    <row r="68" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
         <v>35339929</v>
       </c>
@@ -4175,7 +4277,7 @@
       </c>
       <c r="I68" s="6"/>
     </row>
-    <row r="69" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
         <v>35339929</v>
       </c>
@@ -4202,7 +4304,7 @@
       </c>
       <c r="I69" s="6"/>
     </row>
-    <row r="70" spans="1:9" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
         <v>35339929</v>
       </c>
@@ -4229,7 +4331,7 @@
       </c>
       <c r="I70" s="6"/>
     </row>
-    <row r="71" spans="1:9" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
         <v>31106519</v>
       </c>
@@ -4258,7 +4360,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
         <v>31106519</v>
       </c>
@@ -4287,7 +4389,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
         <v>31106519</v>
       </c>
@@ -4314,7 +4416,7 @@
       </c>
       <c r="I73" s="6"/>
     </row>
-    <row r="74" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
         <v>31106519</v>
       </c>
@@ -4343,7 +4445,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
         <v>31106519</v>
       </c>
@@ -4370,7 +4472,7 @@
       </c>
       <c r="I75" s="6"/>
     </row>
-    <row r="76" spans="1:9" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
         <v>31106519</v>
       </c>
@@ -4399,7 +4501,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
         <v>21229427</v>
       </c>
@@ -4426,7 +4528,7 @@
       </c>
       <c r="I77" s="6"/>
     </row>
-    <row r="78" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
         <v>21229427</v>
       </c>
@@ -4453,7 +4555,7 @@
       </c>
       <c r="I78" s="6"/>
     </row>
-    <row r="79" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
         <v>21229427</v>
       </c>
@@ -4480,7 +4582,7 @@
       </c>
       <c r="I79" s="6"/>
     </row>
-    <row r="80" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
         <v>21229427</v>
       </c>
@@ -4507,7 +4609,7 @@
       </c>
       <c r="I80" s="6"/>
     </row>
-    <row r="81" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
         <v>21229427</v>
       </c>
@@ -4534,7 +4636,7 @@
       </c>
       <c r="I81" s="6"/>
     </row>
-    <row r="82" spans="1:9" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
         <v>21229427</v>
       </c>
@@ -4561,7 +4663,7 @@
       </c>
       <c r="I82" s="6"/>
     </row>
-    <row r="83" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
         <v>21229427</v>
       </c>
@@ -4590,7 +4692,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
         <v>24362534</v>
       </c>
@@ -4617,7 +4719,7 @@
       </c>
       <c r="I84" s="6"/>
     </row>
-    <row r="85" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
         <v>24362534</v>
       </c>
@@ -4644,7 +4746,7 @@
       </c>
       <c r="I85" s="6"/>
     </row>
-    <row r="86" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
         <v>24362534</v>
       </c>
@@ -4671,7 +4773,7 @@
       </c>
       <c r="I86" s="6"/>
     </row>
-    <row r="87" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
         <v>24362534</v>
       </c>
@@ -4698,7 +4800,7 @@
       </c>
       <c r="I87" s="6"/>
     </row>
-    <row r="88" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A88" s="6">
         <v>24362534</v>
       </c>
@@ -4725,7 +4827,7 @@
       </c>
       <c r="I88" s="6"/>
     </row>
-    <row r="89" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
         <v>24362534</v>
       </c>
@@ -4752,7 +4854,7 @@
       </c>
       <c r="I89" s="6"/>
     </row>
-    <row r="90" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A90" s="6">
         <v>24362534</v>
       </c>
@@ -4779,7 +4881,7 @@
       </c>
       <c r="I90" s="6"/>
     </row>
-    <row r="91" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
         <v>24362534</v>
       </c>
@@ -4806,7 +4908,7 @@
       </c>
       <c r="I91" s="6"/>
     </row>
-    <row r="92" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
         <v>24362534</v>
       </c>
@@ -4833,7 +4935,7 @@
       </c>
       <c r="I92" s="6"/>
     </row>
-    <row r="93" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A93" s="6">
         <v>24362534</v>
       </c>
@@ -4860,7 +4962,7 @@
       </c>
       <c r="I93" s="6"/>
     </row>
-    <row r="94" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
         <v>24362534</v>
       </c>
@@ -4887,7 +4989,7 @@
       </c>
       <c r="I94" s="6"/>
     </row>
-    <row r="95" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A95" s="6">
         <v>24362534</v>
       </c>
@@ -4914,7 +5016,7 @@
       </c>
       <c r="I95" s="6"/>
     </row>
-    <row r="96" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
         <v>24831386</v>
       </c>
@@ -4943,7 +5045,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
         <v>24831386</v>
       </c>
@@ -4970,7 +5072,7 @@
       </c>
       <c r="I97" s="6"/>
     </row>
-    <row r="98" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
         <v>24831386</v>
       </c>
@@ -4997,7 +5099,7 @@
       </c>
       <c r="I98" s="6"/>
     </row>
-    <row r="99" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A99" s="6">
         <v>24831386</v>
       </c>
@@ -5026,7 +5128,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A100" s="6">
         <v>24831386</v>
       </c>
@@ -5053,7 +5155,7 @@
       </c>
       <c r="I100" s="6"/>
     </row>
-    <row r="101" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A101" s="6">
         <v>24831386</v>
       </c>
@@ -5080,7 +5182,7 @@
       </c>
       <c r="I101" s="6"/>
     </row>
-    <row r="102" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A102" s="6">
         <v>24831386</v>
       </c>
@@ -5107,7 +5209,7 @@
       </c>
       <c r="I102" s="6"/>
     </row>
-    <row r="103" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A103" s="6">
         <v>24831386</v>
       </c>
@@ -5136,7 +5238,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A104" s="6">
         <v>6503426</v>
       </c>
@@ -5163,7 +5265,7 @@
       </c>
       <c r="I104" s="6"/>
     </row>
-    <row r="105" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A105" s="6">
         <v>6503426</v>
       </c>
@@ -5190,7 +5292,7 @@
       </c>
       <c r="I105" s="6"/>
     </row>
-    <row r="106" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A106" s="6">
         <v>6503426</v>
       </c>
@@ -5219,7 +5321,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A107" s="6">
         <v>6503426</v>
       </c>
@@ -5246,7 +5348,7 @@
       </c>
       <c r="I107" s="6"/>
     </row>
-    <row r="108" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A108" s="6">
         <v>920311</v>
       </c>
@@ -5273,7 +5375,7 @@
       </c>
       <c r="I108" s="6"/>
     </row>
-    <row r="109" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A109" s="6">
         <v>920311</v>
       </c>
@@ -5302,7 +5404,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A110" s="6">
         <v>920311</v>
       </c>
@@ -5329,7 +5431,7 @@
       </c>
       <c r="I110" s="6"/>
     </row>
-    <row r="111" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A111" s="6">
         <v>920311</v>
       </c>
@@ -5356,7 +5458,7 @@
       </c>
       <c r="I111" s="6"/>
     </row>
-    <row r="112" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A112" s="6">
         <v>920311</v>
       </c>
@@ -5383,7 +5485,7 @@
       </c>
       <c r="I112" s="6"/>
     </row>
-    <row r="113" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A113" s="6">
         <v>920311</v>
       </c>
@@ -5410,7 +5512,7 @@
       </c>
       <c r="I113" s="6"/>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="6">
         <v>920311</v>
       </c>
@@ -5437,7 +5539,7 @@
       </c>
       <c r="I114" s="6"/>
     </row>
-    <row r="115" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A115" s="6">
         <v>920311</v>
       </c>
@@ -5464,7 +5566,7 @@
       </c>
       <c r="I115" s="6"/>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="6">
         <v>920311</v>
       </c>
@@ -5491,7 +5593,7 @@
       </c>
       <c r="I116" s="6"/>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="6">
         <v>920311</v>
       </c>
@@ -5517,6 +5619,282 @@
         <v>438</v>
       </c>
       <c r="I117" s="6"/>
+    </row>
+    <row r="118" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A118" s="6">
+        <v>2138840</v>
+      </c>
+      <c r="B118" s="6">
+        <v>1</v>
+      </c>
+      <c r="C118" s="7" t="s">
+        <v>445</v>
+      </c>
+      <c r="D118" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E118" s="8">
+        <v>3.59</v>
+      </c>
+      <c r="F118" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G118" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H118" s="9" t="s">
+        <v>446</v>
+      </c>
+      <c r="I118" s="6" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A119" s="6">
+        <v>2138840</v>
+      </c>
+      <c r="B119" s="6">
+        <v>2</v>
+      </c>
+      <c r="C119" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="D119" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="E119" s="8">
+        <v>3.38</v>
+      </c>
+      <c r="F119" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="G119" s="8">
+        <v>4</v>
+      </c>
+      <c r="H119" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="I119" s="6"/>
+    </row>
+    <row r="120" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A120" s="6">
+        <v>2138840</v>
+      </c>
+      <c r="B120" s="6">
+        <v>3</v>
+      </c>
+      <c r="C120" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="D120" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E120" s="8">
+        <v>3.27</v>
+      </c>
+      <c r="F120" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="G120" s="8">
+        <v>4.05</v>
+      </c>
+      <c r="H120" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="I120" s="6"/>
+    </row>
+    <row r="121" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A121" s="6">
+        <v>2138840</v>
+      </c>
+      <c r="B121" s="6">
+        <v>4</v>
+      </c>
+      <c r="C121" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="D121" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="E121" s="8">
+        <v>3.58</v>
+      </c>
+      <c r="F121" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="G121" s="8">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="H121" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="I121" s="6" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A122" s="6">
+        <v>2138840</v>
+      </c>
+      <c r="B122" s="6">
+        <v>5</v>
+      </c>
+      <c r="C122" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="D122" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="E122" s="8">
+        <v>3.49</v>
+      </c>
+      <c r="F122" s="8">
+        <v>3.85</v>
+      </c>
+      <c r="G122" s="8">
+        <v>4</v>
+      </c>
+      <c r="H122" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="I122" s="6"/>
+    </row>
+    <row r="123" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A123" s="6">
+        <v>2138840</v>
+      </c>
+      <c r="B123" s="6">
+        <v>6</v>
+      </c>
+      <c r="C123" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="D123" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E123" s="8">
+        <v>3.48</v>
+      </c>
+      <c r="F123" s="8">
+        <v>4</v>
+      </c>
+      <c r="G123" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H123" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="I123" s="6"/>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A124" s="6">
+        <v>2138840</v>
+      </c>
+      <c r="B124" s="6">
+        <v>7</v>
+      </c>
+      <c r="C124" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="D124" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="E124" s="8">
+        <v>3.34</v>
+      </c>
+      <c r="F124" s="8">
+        <v>3.75</v>
+      </c>
+      <c r="G124" s="8">
+        <v>3.95</v>
+      </c>
+      <c r="H124" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="I124" s="6"/>
+    </row>
+    <row r="125" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A125" s="6">
+        <v>2138840</v>
+      </c>
+      <c r="B125" s="6">
+        <v>8</v>
+      </c>
+      <c r="C125" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="D125" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E125" s="8">
+        <v>3.65</v>
+      </c>
+      <c r="F125" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="G125" s="8">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="H125" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="I125" s="6" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A126" s="6">
+        <v>2138840</v>
+      </c>
+      <c r="B126" s="6">
+        <v>9</v>
+      </c>
+      <c r="C126" s="7" t="s">
+        <v>462</v>
+      </c>
+      <c r="D126" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="E126" s="8">
+        <v>3.21</v>
+      </c>
+      <c r="F126" s="8">
+        <v>3.65</v>
+      </c>
+      <c r="G126" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="H126" s="9" t="s">
+        <v>463</v>
+      </c>
+      <c r="I126" s="6"/>
+    </row>
+    <row r="127" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A127" s="6">
+        <v>2138840</v>
+      </c>
+      <c r="B127" s="6">
+        <v>10</v>
+      </c>
+      <c r="C127" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="D127" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="E127" s="8">
+        <v>3.35</v>
+      </c>
+      <c r="F127" s="8">
+        <v>4</v>
+      </c>
+      <c r="G127" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="H127" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="I127" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E54F6306-946B-4FBD-97E6-B5DE2126AA28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B3EE302-FF05-455B-8D64-7F6171BC9C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="507">
   <si>
     <t>No</t>
   </si>
@@ -1419,6 +1419,129 @@
   </si>
   <si>
     <t>B5 track. Μεγαλεπήβολο, bluesy κλείσιμο του δίσκου. Πολυεπίπεδη δομή, φοβερή αίσθηση βάθους (depth) και Sterling Sound dynamic range.</t>
+  </si>
+  <si>
+    <t>Warrior Soul</t>
+  </si>
+  <si>
+    <t>Salutations From The Ghetto Nation</t>
+  </si>
+  <si>
+    <t>Alternative Metal, Hard Rock, Heavy Metal, Punk Metal</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Αυθεντική πρώτη γερμανική κοπή σε βινύλιο (DGC / Geffen Records / Cat No: GEF 24488 / Barcode: 7 20642 44881 2 / Label Code: LC 7266 / Price Codes: D: SE / F:BM270 / ID: 10867099). **Condition:** Near Mint (NM) κατάσταση βινυλίου και εξωφύλλου. **Sleeve/Disc Details:** Εξώφυλλο τυπωμένο στην Ολλανδία ("Printed in Holland"), βινύλιο πρεσαρισμένο στη Γερμανία από τη BMG Ariola ("Made in Germany. Fabriqué en Allemagne" στην ετικέτα). **Matrix / Runout Details:** Χαραγμένα runouts Side 1: 08-31275-20-1A-1 GEF 24488 B / Side 2: 08-31275-20-1B-1 GEF 24488 A. Περιλαμβάνει printed inner sleeve με στίχους.</t>
+  </si>
+  <si>
+    <t>DGC / Geffen Records – GEF 24488 / 08-031275-20 (Germany Original 1st Pressing - Matrix: 08-31275-20-1A-1 GEF 24488 B / 08-31275-20-1B-1 GEF 24488 A - ID 10867099)</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/10867099-Warrior-Soul-Salutations-From-The-Ghetto-Nation?redirected=true</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/OTco4pVsmHpPCJTKKEXRFM8eJmE6Vl9HXD1L5Leb10M/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTEwODY3/MDk5LTE1MDU2NTUz/MTItODQwMS5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Love Destruction</t>
+  </si>
+  <si>
+    <t>Blown</t>
+  </si>
+  <si>
+    <t>Shine Like It</t>
+  </si>
+  <si>
+    <t>Dimension</t>
+  </si>
+  <si>
+    <t>Punk And Belligerent</t>
+  </si>
+  <si>
+    <t>Ass-Kickin</t>
+  </si>
+  <si>
+    <t>The Party</t>
+  </si>
+  <si>
+    <t>The Golden Shore</t>
+  </si>
+  <si>
+    <t>Trip Rider</t>
+  </si>
+  <si>
+    <t>I Love You</t>
+  </si>
+  <si>
+    <t>The Fallen</t>
+  </si>
+  <si>
+    <t>Ghetto Nation</t>
+  </si>
+  <si>
+    <t>Alternative Metal, Hard Rock</t>
+  </si>
+  <si>
+    <t>Το lead single του άλμπουμ. Εκρηκτική έναρξη με επιθετικά κιθαριστικά riffs, πολιτικοποιημένους στίχους και στιβαρό drumming.</t>
+  </si>
+  <si>
+    <t>Γρήγορο, ρυθμικό track με punk αιχμή, κοφτές κιθάρες και εξαιρετική στερεοφωνική εικόνα.</t>
+  </si>
+  <si>
+    <t>Hard Rock, Punk Metal</t>
+  </si>
+  <si>
+    <t>Alternative Metal, Heavy Metal</t>
+  </si>
+  <si>
+    <t>Punk Metal, Hard Rock</t>
+  </si>
+  <si>
+    <t>Mid-tempo heavy groove με ζεστό μπάσο από τον Pete McClanahan και αεροστεγή μίξη.</t>
+  </si>
+  <si>
+    <t>Από τα συνθετικά highlights της A-side. Σκοτεινή ατμόσφαιρα, υπνωτική μπασογραμμή και πλούσιο headroom.</t>
+  </si>
+  <si>
+    <t>Επιθετικό punk/metal ξέσπασμα με φρενήρη ρυθμό και ωμή φωνητική ερμηνεία.</t>
+  </si>
+  <si>
+    <t>Inner groove track της Side A. Ευθύγραμμο, δυναμικό hard rock με καθαρό πάτημα στη μπότα.</t>
+  </si>
+  <si>
+    <t>Alternative Metal, Glam Metal / Punk</t>
+  </si>
+  <si>
+    <t>Δυνατή έναρξη της Side B. Ειρωνικοί στίχοι για την παρακμή, με groovy ρυθμό και δυναμικά κιθαριστικά solo.</t>
+  </si>
+  <si>
+    <t>Alternative Metal, Epic Rock</t>
+  </si>
+  <si>
+    <t>Το μεγαλύτερο σε διάρκεια track και το απόλυτο συνθετικό/audiophile highlight του άλμπουμ. Πολύπλοκη κλιμάκωση, ατμοσφαιρικά κιθαριστικά layers και κορυφαία διαστρωμάτωση συχνοτήτων.</t>
+  </si>
+  <si>
+    <t>Ατμοσφαιρικό, ψυχεδελικό hard rock κομμάτι με εξαιρετικό βάθος πεδίου (depth) και αέρινη ηχητική εικόνα.</t>
+  </si>
+  <si>
+    <t>Σκοτεινή, ιδιόμορφη μπαλάντα με ειρωνικό τόνο και ζεστή αναλογική χροιά στις ακουστικές/ηλεκτρικές κιθάρες.</t>
+  </si>
+  <si>
+    <t>Βαρύ, αργό και ατμοσφαιρικό track με δραματική ερμηνεία, στιβαρό μπάσο και πλούσιες χαμηλές συχνότητες.</t>
+  </si>
+  <si>
+    <t>Inner groove track της Side B. Το ομώνυμο φινάλε του άλμπουμ. Πολιτική οργή, καταιγιστικός ρυθμός και αθόρυβο fade-out.</t>
+  </si>
+  <si>
+    <t>Alternative Metal, Psychedelic Rock</t>
+  </si>
+  <si>
+    <t>Hard Rock, Ballad / Punk</t>
+  </si>
+  <si>
+    <t>Alternative Metal, Doom / Heavy Metal</t>
+  </si>
+  <si>
+    <t>Alternative Metal, Punk Metal</t>
   </si>
 </sst>
 </file>
@@ -1847,17 +1970,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" style="1" customWidth="1"/>
     <col min="6" max="6" width="31.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="96.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.7109375" style="1" customWidth="1"/>
     <col min="9" max="9" width="35" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="50.42578125" style="1" customWidth="1"/>
     <col min="11" max="16384" width="9.140625" style="1"/>
@@ -2373,6 +2496,38 @@
       </c>
       <c r="J16" s="11" t="s">
         <v>443</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="84" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
+        <v>10867099</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="D17" s="6">
+        <v>1992</v>
+      </c>
+      <c r="E17" s="10">
+        <v>3.67</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>469</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>470</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>471</v>
+      </c>
+      <c r="J17" s="11" t="s">
+        <v>472</v>
       </c>
     </row>
   </sheetData>
@@ -2414,7 +2569,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I127"/>
+  <dimension ref="A1:I139"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="3" bestFit="1" customWidth="1"/>
@@ -5896,6 +6051,330 @@
       </c>
       <c r="I127" s="6"/>
     </row>
+    <row r="128" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A128" s="6">
+        <v>10867099</v>
+      </c>
+      <c r="B128" s="6">
+        <v>1</v>
+      </c>
+      <c r="C128" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D128" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="E128" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="F128" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="G128" s="8">
+        <v>4.25</v>
+      </c>
+      <c r="H128" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="I128" s="6"/>
+    </row>
+    <row r="129" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A129" s="6">
+        <v>10867099</v>
+      </c>
+      <c r="B129" s="6">
+        <v>2</v>
+      </c>
+      <c r="C129" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="D129" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="E129" s="8">
+        <v>3.72</v>
+      </c>
+      <c r="F129" s="8">
+        <v>3.95</v>
+      </c>
+      <c r="G129" s="8">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="H129" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="I129" s="6"/>
+    </row>
+    <row r="130" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A130" s="6">
+        <v>10867099</v>
+      </c>
+      <c r="B130" s="6">
+        <v>3</v>
+      </c>
+      <c r="C130" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="D130" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="E130" s="8">
+        <v>3.81</v>
+      </c>
+      <c r="F130" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="G130" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H130" s="9" t="s">
+        <v>491</v>
+      </c>
+      <c r="I130" s="6"/>
+    </row>
+    <row r="131" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A131" s="6">
+        <v>10867099</v>
+      </c>
+      <c r="B131" s="6">
+        <v>4</v>
+      </c>
+      <c r="C131" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="D131" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="E131" s="8">
+        <v>3.57</v>
+      </c>
+      <c r="F131" s="8">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="G131" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="H131" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="I131" s="6"/>
+    </row>
+    <row r="132" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A132" s="6">
+        <v>10867099</v>
+      </c>
+      <c r="B132" s="6">
+        <v>5</v>
+      </c>
+      <c r="C132" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="D132" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="E132" s="8">
+        <v>3.98</v>
+      </c>
+      <c r="F132" s="8">
+        <v>3.85</v>
+      </c>
+      <c r="G132" s="8">
+        <v>4.05</v>
+      </c>
+      <c r="H132" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="I132" s="6"/>
+    </row>
+    <row r="133" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A133" s="6">
+        <v>10867099</v>
+      </c>
+      <c r="B133" s="6">
+        <v>6</v>
+      </c>
+      <c r="C133" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="D133" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E133" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="F133" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="G133" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H133" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="I133" s="6"/>
+    </row>
+    <row r="134" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A134" s="6">
+        <v>10867099</v>
+      </c>
+      <c r="B134" s="6">
+        <v>7</v>
+      </c>
+      <c r="C134" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="D134" s="7" t="s">
+        <v>495</v>
+      </c>
+      <c r="E134" s="8">
+        <v>3.55</v>
+      </c>
+      <c r="F134" s="8">
+        <v>4.05</v>
+      </c>
+      <c r="G134" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="H134" s="9" t="s">
+        <v>496</v>
+      </c>
+      <c r="I134" s="6"/>
+    </row>
+    <row r="135" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A135" s="6">
+        <v>10867099</v>
+      </c>
+      <c r="B135" s="6">
+        <v>8</v>
+      </c>
+      <c r="C135" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="D135" s="7" t="s">
+        <v>497</v>
+      </c>
+      <c r="E135" s="8">
+        <v>3.55</v>
+      </c>
+      <c r="F135" s="8">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="G135" s="8">
+        <v>4.45</v>
+      </c>
+      <c r="H135" s="9" t="s">
+        <v>498</v>
+      </c>
+      <c r="I135" s="6"/>
+    </row>
+    <row r="136" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A136" s="6">
+        <v>10867099</v>
+      </c>
+      <c r="B136" s="6">
+        <v>9</v>
+      </c>
+      <c r="C136" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="D136" s="7" t="s">
+        <v>503</v>
+      </c>
+      <c r="E136" s="8">
+        <v>3.55</v>
+      </c>
+      <c r="F136" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G136" s="8">
+        <v>4.25</v>
+      </c>
+      <c r="H136" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="I136" s="6"/>
+    </row>
+    <row r="137" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A137" s="6">
+        <v>10867099</v>
+      </c>
+      <c r="B137" s="6">
+        <v>10</v>
+      </c>
+      <c r="C137" s="7" t="s">
+        <v>482</v>
+      </c>
+      <c r="D137" s="7" t="s">
+        <v>504</v>
+      </c>
+      <c r="E137" s="8">
+        <v>3.68</v>
+      </c>
+      <c r="F137" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="G137" s="8">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="H137" s="9" t="s">
+        <v>500</v>
+      </c>
+      <c r="I137" s="6"/>
+    </row>
+    <row r="138" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A138" s="6">
+        <v>10867099</v>
+      </c>
+      <c r="B138" s="6">
+        <v>11</v>
+      </c>
+      <c r="C138" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="D138" s="7" t="s">
+        <v>505</v>
+      </c>
+      <c r="E138" s="8">
+        <v>3.89</v>
+      </c>
+      <c r="F138" s="8">
+        <v>4.25</v>
+      </c>
+      <c r="G138" s="8">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="H138" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="I138" s="6"/>
+    </row>
+    <row r="139" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A139" s="6">
+        <v>10867099</v>
+      </c>
+      <c r="B139" s="6">
+        <v>12</v>
+      </c>
+      <c r="C139" s="7" t="s">
+        <v>484</v>
+      </c>
+      <c r="D139" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="E139" s="8">
+        <v>3.87</v>
+      </c>
+      <c r="F139" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="G139" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="H139" s="9" t="s">
+        <v>502</v>
+      </c>
+      <c r="I139" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B3EE302-FF05-455B-8D64-7F6171BC9C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{054EAA0C-3BAD-4EF2-8BFA-6DBA954AF67E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="541">
   <si>
     <t>No</t>
   </si>
@@ -1542,6 +1542,108 @@
   </si>
   <si>
     <t>Alternative Metal, Punk Metal</t>
+  </si>
+  <si>
+    <t>I See The Ruins</t>
+  </si>
+  <si>
+    <t>We Cry Out</t>
+  </si>
+  <si>
+    <t>The Losers</t>
+  </si>
+  <si>
+    <t>Downtown</t>
+  </si>
+  <si>
+    <t>Trippin' On Ecstasy</t>
+  </si>
+  <si>
+    <t>One Minute Year</t>
+  </si>
+  <si>
+    <t>Superpower Dreamland</t>
+  </si>
+  <si>
+    <t>Charlie's Out Of Prison</t>
+  </si>
+  <si>
+    <t>Blown Away</t>
+  </si>
+  <si>
+    <t>Lullaby</t>
+  </si>
+  <si>
+    <t>In Conclusion</t>
+  </si>
+  <si>
+    <t>Hard Rock, Alternative Metal, Sleaze Rock, Psychedelic Rock</t>
+  </si>
+  <si>
+    <t>DGC – 24285 (US Original Promo Pressing - Specialty Records - ID 2797526)</t>
+  </si>
+  <si>
+    <t>Last Decade Dead Century</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/master/290842-Warrior-Soul-Last-Decade-Dead-Century?format=Vinyl&amp;year=1990</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/iqkRbTQZ-wViH06UyMvNd6nvUiBMCx45Ma3Tm91PRWI/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI3OTc1/MjYtMTMwNTg4Njgz/MC5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Hard Rock, Alternative Metal</t>
+  </si>
+  <si>
+    <t>Alternative Metal, Sleaze Rock</t>
+  </si>
+  <si>
+    <t>Hard Rock, Sleaze Rock</t>
+  </si>
+  <si>
+    <t>Psychedelic Rock, Alternative Metal</t>
+  </si>
+  <si>
+    <t>Alternative Metal, Intro</t>
+  </si>
+  <si>
+    <t>Alternative Metal, Ballad</t>
+  </si>
+  <si>
+    <t>Mid-tempo, υπνωτικός ρυθμός που στηρίζεται σε μια στιβαρή, μπροστά στη μίξη μπασογραμμή. Εξαιρετικός διαχωρισμός οργάνων και στερεοφωνική εικόνα στις κιθάρες του John Ricco.</t>
+  </si>
+  <si>
+    <t>Το συνθετικό highlight της A πλευράς. Ένα επικό, ατμοσφαιρικό κομμάτι με σταδιακή κλιμάκωση, όπου τα φωνητικά του Clarke αποκτούν μια σχεδόν θεατρική τραχύτητα. Υψηλή audiophile αξία λόγω των καθαρών αναλογικών μεταβατικών (transients).</t>
+  </si>
+  <si>
+    <t>Επιθετικό street-rock κομμάτι με punk/metal αιχμή. Γρήγορα περάσματα στα πιάτα και κοφτά riffs που δοκιμάζουν την απόκριση συχνότητας του συστήματος.</t>
+  </si>
+  <si>
+    <t>Σύντομη, σκοτεινή και ατμοσφαιρική εισαγωγή της Side B με ambient/industrial ηχοτοπία που προετοιμάζουν το έδαφος για τη δεύτερη πλευρά.</t>
+  </si>
+  <si>
+    <t>Καταιγιστικό, γρήγορο track με punk-metal ενέργεια. Punchy μπάσο και κοφτά drums που αναδεικνύουν την ταχύτητα απόκρισης της βελόνας.</t>
+  </si>
+  <si>
+    <t>Έντονα groovy ρυθμός με θεατρική ερμηνεία και σαρκαστικό στίχο. Εξαιρετική ισορροπία στις χαμηλές συχνότητες χωρίς να μπουμιάζει το χαμηλό χαμηλό.</t>
+  </si>
+  <si>
+    <t>Συμπυκνωμένο hard rock ξέσπασμα με επιθετικά σόλο κιθάρας και υψηλή ενέργεια στη μίξη.</t>
+  </si>
+  <si>
+    <t>Σκοτεινή, συναισθηματική μπαλάντα με βαθιά ατμόσφαιρα. Η φωνή του Clarke ακούγεται γυμνή και ανάγλυφη στο κέντρο της σκηνής.</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Αρχική αμερικανική promo κοπή (DGC / Cat No: DGC 24285 / Barcode: 7599-24285-1). Φέρει τη χρυσή ανάγλυφη σφραγίδα "Lent for Promotional Use Only..." στο εμπρός εξώφυλλο. Πρεσαρισμένο από τη Specialty Records Corporation (SP). **Production &amp; Engineering:** Παραγωγή: Geoff Workman &amp; Kory Clarke. Co-production &amp; Engineering: Paul Church. Ηχογραφήθηκε &amp; μιξάστηκε στα Cherokee Studios (Los Angeles) &amp; Sound City Studios, με προ-παραγωγή στα Don Fury Studios. Management: Q Prime Inc. **Audio Mastering:** Mastered at Sterling Sound, NY από τον George Marino ("STERLING" stamped) με τεχνολογία Direct Metal Mastering ("DMM"). **Sleeve/Disc Details:** Printed inner sleeve με στίχους, credits &amp; artwork (Art Direction: Roger Gorman / Reiner Design Consultants). **Matrix / Runout Details:** Side A: GHS-24285-A-SRI-DMM-SRI SP I-I STERLING / Side B: GHS-24285-B-SRI-DMM-SRI SP I-I STERLING.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Εκρηκτική έναρξη με σκοτεινά, βαριά riffs και επιθετικό πολιτικοκοινωνικό στίχο του Kory Clarke. Ηχογραφημένο στα Cherokee Studios σε μίξη Geoff Workman &amp; George Marino mastering, δίνοντας τεράστιο όγκο στα τύμπανα του Paul Ferguson, εκμεταλλευόμενη πλήρως το δυναμικό εύρος του DMM mastering. </t>
+  </si>
+  <si>
+    <t>Inner groove track της Side B &amp; το επικό φινάλε του άλμπουμ. Πολύπλοκη δομή 6.5 λεπτών κοντά στο κέντρο του δίσκου. Δοκιμάζει την ικανότητα tracking της βελόνας, προσφέροντας ένα εντυπωσιακά καθαρό και δυναμικό κλείσιμο. Το αψεγάδιαστο tracking στα inner grooves οφείλεται στη συνεργασία του DMM με την κοπή του George Marino.</t>
+  </si>
+  <si>
+    <t>Inner groove track της Side A. Ψυχεδελικές κιθάρες με έντονα εφέ και πολυεπίπεδη μίξη. Χάρη στο Sterling DMM χαραγή, διατηρείται η διαύγεια στα πρίμα χωρίς ίχνος Inner Groove Distortion (IGD). Το αψεγάδιαστο tracking στα inner grooves οφείλεται στη συνεργασία του DMM με την κοπή του George Marino.</t>
   </si>
 </sst>
 </file>
@@ -1970,7 +2072,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -2466,7 +2568,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="84" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="73.5" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>2138840</v>
       </c>
@@ -2528,6 +2630,38 @@
       </c>
       <c r="J17" s="11" t="s">
         <v>472</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="84" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
+        <v>2797526</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>520</v>
+      </c>
+      <c r="D18" s="6">
+        <v>1990</v>
+      </c>
+      <c r="E18" s="10">
+        <v>3.55</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>518</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>537</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>519</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>521</v>
+      </c>
+      <c r="J18" s="11" t="s">
+        <v>522</v>
       </c>
     </row>
   </sheetData>
@@ -2562,6 +2696,8 @@
     <hyperlink ref="J15" r:id="rId28" xr:uid="{653E9D3F-45EA-4E17-836F-D51F97914679}"/>
     <hyperlink ref="I16" r:id="rId29" xr:uid="{78E3F96C-2AC2-4B9F-A821-519BF5B5CA6A}"/>
     <hyperlink ref="J16" r:id="rId30" xr:uid="{0D92D6CB-079F-4183-8D1A-1BFEDEE2C7D0}"/>
+    <hyperlink ref="I18" r:id="rId31" xr:uid="{74A79CD1-48E8-40EB-874F-B9B4C5CE10CB}"/>
+    <hyperlink ref="J18" r:id="rId32" xr:uid="{63686497-3E87-4FD7-8A7E-EAC076C0B3FF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2569,7 +2705,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I139"/>
+  <dimension ref="A1:I150"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="3" bestFit="1" customWidth="1"/>
@@ -6375,6 +6511,303 @@
       </c>
       <c r="I139" s="6"/>
     </row>
+    <row r="140" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A140" s="6">
+        <v>2797526</v>
+      </c>
+      <c r="B140" s="6">
+        <v>1</v>
+      </c>
+      <c r="C140" s="7" t="s">
+        <v>507</v>
+      </c>
+      <c r="D140" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E140" s="8">
+        <v>3.87</v>
+      </c>
+      <c r="F140" s="8">
+        <v>4.25</v>
+      </c>
+      <c r="G140" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="H140" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="I140" s="6"/>
+    </row>
+    <row r="141" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A141" s="6">
+        <v>2797526</v>
+      </c>
+      <c r="B141" s="6">
+        <v>2</v>
+      </c>
+      <c r="C141" s="7" t="s">
+        <v>508</v>
+      </c>
+      <c r="D141" s="7" t="s">
+        <v>524</v>
+      </c>
+      <c r="E141" s="8">
+        <v>3.91</v>
+      </c>
+      <c r="F141" s="8">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="G141" s="8">
+        <v>4.25</v>
+      </c>
+      <c r="H141" s="9" t="s">
+        <v>529</v>
+      </c>
+      <c r="I141" s="6"/>
+    </row>
+    <row r="142" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A142" s="6">
+        <v>2797526</v>
+      </c>
+      <c r="B142" s="6">
+        <v>3</v>
+      </c>
+      <c r="C142" s="7" t="s">
+        <v>509</v>
+      </c>
+      <c r="D142" s="7" t="s">
+        <v>497</v>
+      </c>
+      <c r="E142" s="8">
+        <v>3.97</v>
+      </c>
+      <c r="F142" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G142" s="8">
+        <v>4.45</v>
+      </c>
+      <c r="H142" s="9" t="s">
+        <v>530</v>
+      </c>
+      <c r="I142" s="6"/>
+    </row>
+    <row r="143" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A143" s="6">
+        <v>2797526</v>
+      </c>
+      <c r="B143" s="6">
+        <v>4</v>
+      </c>
+      <c r="C143" s="7" t="s">
+        <v>510</v>
+      </c>
+      <c r="D143" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="E143" s="8">
+        <v>3.87</v>
+      </c>
+      <c r="F143" s="8">
+        <v>3.95</v>
+      </c>
+      <c r="G143" s="8">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="H143" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="I143" s="6"/>
+    </row>
+    <row r="144" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A144" s="6">
+        <v>2797526</v>
+      </c>
+      <c r="B144" s="6">
+        <v>5</v>
+      </c>
+      <c r="C144" s="7" t="s">
+        <v>511</v>
+      </c>
+      <c r="D144" s="7" t="s">
+        <v>526</v>
+      </c>
+      <c r="E144" s="8">
+        <v>3.76</v>
+      </c>
+      <c r="F144" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G144" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="H144" s="9" t="s">
+        <v>540</v>
+      </c>
+      <c r="I144" s="6"/>
+    </row>
+    <row r="145" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A145" s="6">
+        <v>2797526</v>
+      </c>
+      <c r="B145" s="6">
+        <v>6</v>
+      </c>
+      <c r="C145" s="7" t="s">
+        <v>512</v>
+      </c>
+      <c r="D145" s="7" t="s">
+        <v>527</v>
+      </c>
+      <c r="E145" s="8">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="F145" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="G145" s="8">
+        <v>4</v>
+      </c>
+      <c r="H145" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="I145" s="6"/>
+    </row>
+    <row r="146" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A146" s="6">
+        <v>2797526</v>
+      </c>
+      <c r="B146" s="6">
+        <v>7</v>
+      </c>
+      <c r="C146" s="7" t="s">
+        <v>513</v>
+      </c>
+      <c r="D146" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="E146" s="8">
+        <v>3.54</v>
+      </c>
+      <c r="F146" s="8">
+        <v>4.05</v>
+      </c>
+      <c r="G146" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="H146" s="9" t="s">
+        <v>533</v>
+      </c>
+      <c r="I146" s="6"/>
+    </row>
+    <row r="147" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A147" s="6">
+        <v>2797526</v>
+      </c>
+      <c r="B147" s="6">
+        <v>8</v>
+      </c>
+      <c r="C147" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="D147" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="E147" s="8">
+        <v>3.69</v>
+      </c>
+      <c r="F147" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="G147" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="H147" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="I147" s="6"/>
+    </row>
+    <row r="148" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A148" s="6">
+        <v>2797526</v>
+      </c>
+      <c r="B148" s="6">
+        <v>9</v>
+      </c>
+      <c r="C148" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="D148" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E148" s="8">
+        <v>3.65</v>
+      </c>
+      <c r="F148" s="8">
+        <v>4</v>
+      </c>
+      <c r="G148" s="8">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="H148" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="I148" s="6"/>
+    </row>
+    <row r="149" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A149" s="6">
+        <v>2797526</v>
+      </c>
+      <c r="B149" s="6">
+        <v>10</v>
+      </c>
+      <c r="C149" s="7" t="s">
+        <v>516</v>
+      </c>
+      <c r="D149" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="E149" s="8">
+        <v>3.64</v>
+      </c>
+      <c r="F149" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="G149" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H149" s="9" t="s">
+        <v>536</v>
+      </c>
+      <c r="I149" s="6"/>
+    </row>
+    <row r="150" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A150" s="6">
+        <v>2797526</v>
+      </c>
+      <c r="B150" s="6">
+        <v>11</v>
+      </c>
+      <c r="C150" s="7" t="s">
+        <v>517</v>
+      </c>
+      <c r="D150" s="7" t="s">
+        <v>497</v>
+      </c>
+      <c r="E150" s="8">
+        <v>3.77</v>
+      </c>
+      <c r="F150" s="8">
+        <v>4.45</v>
+      </c>
+      <c r="G150" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="H150" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="I150" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{054EAA0C-3BAD-4EF2-8BFA-6DBA954AF67E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15F6D104-9E52-4CCF-9459-D227339DEECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="589">
   <si>
     <t>No</t>
   </si>
@@ -1644,6 +1644,150 @@
   </si>
   <si>
     <t>Inner groove track της Side A. Ψυχεδελικές κιθάρες με έντονα εφέ και πολυεπίπεδη μίξη. Χάρη στο Sterling DMM χαραγή, διατηρείται η διαύγεια στα πρίμα χωρίς ίχνος Inner Groove Distortion (IGD). Το αψεγάδιαστο tracking στα inner grooves οφείλεται στη συνεργασία του DMM με την κοπή του George Marino.</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Αρχική αμερικανική κυκλοφορία σε βινύλιο (RidingEasy Records / Cat No: EZRDR-158 / Barcode: 603111759210 / ID: 28270285). **Production &amp; Engineering:** Engineered by Phil Becker at El Studio (San Francisco), με πρόσθετες ηχογραφήσεις στο studio της μπάντας στο Oakland. **Audio Mastering &amp; Pressing Details:** Lacquer cut από τον Nick Townsend (Townsend Mastering, "NT" στο runout). Επιμετάλλωση (metalwork/plating) στα audiophile εργαστήρια της Record Technology Incorporated (RTI, κωδικός 42021). **Matrix / Runout Details:** Side A: EZRDR 158-A NT 42021.1(3)... / Side B: EZRDR 158-B NT 42021.2(3)...</t>
+  </si>
+  <si>
+    <t>Psychedelic Rock, Progressive Rock, Heavy Psych, Space Rock</t>
+  </si>
+  <si>
+    <t>RidingEasy Records – EZRDR-158 (US Original Pressing, Plated at RTI - ID 28270285)</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/28270285-Mondo-Drag-Through-The-Hourglass-</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/3AhfnEgNv02OvdL85UgFVryDitrIRCW2rb_TD8Lx5ZU/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI4Mjcw/Mjg1LTE3MTMwODE4/NzItNjQ1Ny5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Burning Daylight Pt. 1</t>
+  </si>
+  <si>
+    <t>Burning Daylight Pt. 2</t>
+  </si>
+  <si>
+    <t>Passages</t>
+  </si>
+  <si>
+    <t>Through The Hourglass</t>
+  </si>
+  <si>
+    <t>Death In Spring</t>
+  </si>
+  <si>
+    <t>Run</t>
+  </si>
+  <si>
+    <t>Heavy Psych, Progressive Rock</t>
+  </si>
+  <si>
+    <t>Δυνατή, επιθετική έναρξη με βαριά riffs, κοφτά τύμπανα και αναλογικά συνθεσάιζερ. Πολύ καλό punch στις χαμηλομεσαίες συχνότητες και εξαιρετική ταχύτητα βελόνας στις μεταβατικές (transients)</t>
+  </si>
+  <si>
+    <t>Οργανική συνέχεια με πιο πειραματικά, υπνωτικά μοτίβα και πολυεπίπεδη στερεοφωνική μίξη στα vintage πλήκτρα (Hammond / analog synths).</t>
+  </si>
+  <si>
+    <t>Psychedelic Rock, Krautrock</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Space Rock</t>
+  </si>
+  <si>
+    <t>Το 11λεπτο prog έπος της A πλευράς. Θυμίζει Pink Floyd εποχής Meddle. Εκπληκτικό soundstage, ατμοσφαιρικά περάσματα πιάνου/Hammond και κιθαριστικές κλιμακώσεις. Αψεγάδιαστο tracking κοντά στο κέντρο χωρίς ίχνος IGD χάρη στην κοπή του Nick Townsend (NT).</t>
+  </si>
+  <si>
+    <t>Ομώνυμο track με ταξιδιάρικη ατμόσφαιρα, vintage ηχοχρώματα και ζεστό, γεμάτο αναλογικό μπάσο.</t>
+  </si>
+  <si>
+    <t>Σκοτεινό, μελαγχολικό και ατμοσφαιρικό highlight της B πλευράς. Εξαιρετική ισορροπία στις χαμηλές συχνότητες χωρίς να μπουμιάζει το χαμηλό, με φυσικότατη απόδοση στα φωνητικά.</t>
+  </si>
+  <si>
+    <t>Δυναμικό, επικό φινάλε του άλμπουμ. Εξαιρετική δουλειά στα τύμπανα με υψηλή διαύγεια στα πιάτα, που δοκιμάζει την ικανότητα απόκρισης του συστήματος κοντά στο κέντρο του δίσκου.</t>
+  </si>
+  <si>
+    <t>Heavy Psych, Proto-Doom</t>
+  </si>
+  <si>
+    <t>Killing Floor</t>
+  </si>
+  <si>
+    <t>Monolith</t>
+  </si>
+  <si>
+    <t>Out Of Existence</t>
+  </si>
+  <si>
+    <t>Ancestral Recall</t>
+  </si>
+  <si>
+    <t>Magickal Cost</t>
+  </si>
+  <si>
+    <t>Into Being</t>
+  </si>
+  <si>
+    <t>The Valley</t>
+  </si>
+  <si>
+    <t>Βαθιές χαμηλές συχνότητες και αργός, υποβλητικός ρυθμός που δοκιμάζει τον έλεγχο των χαμηλών του συστήματος.</t>
+  </si>
+  <si>
+    <t>Ένα από τα κορυφαία κομμάτια του δίσκου. Δυναμική κλιμάκωση, εξαιρετική στερεοφωνική εικόνα και ισορροπημένη μίξη.</t>
+  </si>
+  <si>
+    <t>Σκοτεινή, αργόσυρτη σύνθεση με τεράστιο κιθαριστικό βάρος και αιθέρια φωνητικά περάσματα από την Rundle.</t>
+  </si>
+  <si>
+    <t>Συμπαγές track με γρήγορο τέμπο, κοφτές κιθάρες και έντονη ατμόσφαιρα. Καθαρός διαχωρισμός στις συχνότητες των κιθαρών.</t>
+  </si>
+  <si>
+    <t>Εκρηκτική έναρξη με βαριά sludge riffs και άμεση εναλλαγή φωνητικών. Εξαιρετικός όγκος στα τύμπανα και συμπαγής απόκριση χαμηλών.</t>
+  </si>
+  <si>
+    <t>Highlight της πρώτης πλευράς με έντονη 90s grunge αισθητική και επιθετικό ρυθμό. Αψεγάδιαστο tracking κοντά στο κέντρο.</t>
+  </si>
+  <si>
+    <t>Sludge Metal, Post-Metal</t>
+  </si>
+  <si>
+    <t>Post-Metal, Atmospheric Sludge</t>
+  </si>
+  <si>
+    <t>Sludge Metal, Doom Metal</t>
+  </si>
+  <si>
+    <t>Sludge Metal, Grunge</t>
+  </si>
+  <si>
+    <t>Atmospheric Sludge, Post-Metal</t>
+  </si>
+  <si>
+    <t>Το 9λεπτο επικό φινάλε του άλμπουμ. Τεράστιο soundstage, συναισθηματική κορύφωση και καθαρή απόδοση χωρίς παραμόρφωση στο κέντρο.</t>
+  </si>
+  <si>
+    <t>Mondo Drag</t>
+  </si>
+  <si>
+    <t>Emma Ruth Rundle &amp; Thou</t>
+  </si>
+  <si>
+    <t>May Our Chambers Be Full</t>
+  </si>
+  <si>
+    <t>Atmospheric Sludge Metal, Post-Metal, Doom Metal, Grunge</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Συνεργατικό άλμπουμ των Emma Ruth Rundle και Thou (αρχική κυκλοφορία 2020, Reissue 2022 / Blue And Purple Galaxy Vinyl). Ηχογραφήθηκε και μιξάστηκε στο HighTower Recording στο New Orleans από τον James Whitten (Αύγουστος 2019). **Audio Mastering &amp; Pressing Details:** Mastering από τον Adam Tucker (Signature Sound). Πρεσάρισμα στα εργαστήρια της GZ Media (Τσεχία, κωδικός πρέσας 207551E). **Ηχητική Αξιολόγηση:** Ογκόδης, σκοτεινή και καταθλιπτική παραγωγή όπου το βαρύ sludge/doom υπόβαθρο των Thou ισορροπεί με τα αιθέρια αλλά αιχμηρά φωνητικά της Rundle. Τεράστια δυναμικά ξεσπάσματα και συμπαγής χαμηλή περιοχή.</t>
+  </si>
+  <si>
+    <t>Sacred Bones Records – SBA-007 (US Reissue 2022, Blue &amp; Purple Galaxy Vinyl, GZ Media Pressing - ID 24184766)</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/24184766-Emma-Ruth-Rundle-Thou-May-Our-Chambers-Be-Full</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/SxEGjTOeaIiLu8hEqKPGjWvHrwhZhDfSVnWbWWmahxc/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI0MTg0/NzY2LTE2NjAzNTE3/OTItNTMzMi5qcGVn.jpeg</t>
   </si>
 </sst>
 </file>
@@ -2072,11 +2216,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="25.7109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="12.7109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="10.7109375" style="1" customWidth="1"/>
@@ -2662,6 +2806,70 @@
       </c>
       <c r="J18" s="11" t="s">
         <v>522</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
+        <v>28270285</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>581</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>549</v>
+      </c>
+      <c r="D19" s="6">
+        <v>2023</v>
+      </c>
+      <c r="E19" s="10">
+        <v>3.56</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>542</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>541</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="I19" s="11" t="s">
+        <v>544</v>
+      </c>
+      <c r="J19" s="11" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+      <c r="A20" s="6">
+        <v>24184766</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>582</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>583</v>
+      </c>
+      <c r="D20" s="6">
+        <v>2020</v>
+      </c>
+      <c r="E20" s="10">
+        <v>3.51</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>584</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>585</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>586</v>
+      </c>
+      <c r="I20" s="11" t="s">
+        <v>587</v>
+      </c>
+      <c r="J20" s="11" t="s">
+        <v>588</v>
       </c>
     </row>
   </sheetData>
@@ -2698,6 +2906,10 @@
     <hyperlink ref="J16" r:id="rId30" xr:uid="{0D92D6CB-079F-4183-8D1A-1BFEDEE2C7D0}"/>
     <hyperlink ref="I18" r:id="rId31" xr:uid="{74A79CD1-48E8-40EB-874F-B9B4C5CE10CB}"/>
     <hyperlink ref="J18" r:id="rId32" xr:uid="{63686497-3E87-4FD7-8A7E-EAC076C0B3FF}"/>
+    <hyperlink ref="I19" r:id="rId33" xr:uid="{21285B48-6B68-40F0-9B76-D4C8B9229EA4}"/>
+    <hyperlink ref="J19" r:id="rId34" xr:uid="{BAB202AA-F491-4E39-A1A2-D6EBCE96D971}"/>
+    <hyperlink ref="I20" r:id="rId35" xr:uid="{6F630CCD-C8C5-48E5-BF62-170422F60808}"/>
+    <hyperlink ref="J20" r:id="rId36" xr:uid="{84319BCE-7BDE-4F59-BC89-A927A5EE3AFD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2705,7 +2917,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I150"/>
+  <dimension ref="A1:I163"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="3" bestFit="1" customWidth="1"/>
@@ -6808,6 +7020,357 @@
       </c>
       <c r="I150" s="6"/>
     </row>
+    <row r="151" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A151" s="6">
+        <v>28270285</v>
+      </c>
+      <c r="B151" s="6">
+        <v>1</v>
+      </c>
+      <c r="C151" s="7" t="s">
+        <v>546</v>
+      </c>
+      <c r="D151" s="7" t="s">
+        <v>552</v>
+      </c>
+      <c r="E151" s="8">
+        <v>3.31</v>
+      </c>
+      <c r="F151" s="8">
+        <v>4</v>
+      </c>
+      <c r="G151" s="8">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="H151" s="9" t="s">
+        <v>553</v>
+      </c>
+      <c r="I151" s="6"/>
+    </row>
+    <row r="152" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A152" s="6">
+        <v>28270285</v>
+      </c>
+      <c r="B152" s="6">
+        <v>2</v>
+      </c>
+      <c r="C152" s="7" t="s">
+        <v>547</v>
+      </c>
+      <c r="D152" s="7" t="s">
+        <v>555</v>
+      </c>
+      <c r="E152" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="F152" s="8">
+        <v>3.85</v>
+      </c>
+      <c r="G152" s="8">
+        <v>4.25</v>
+      </c>
+      <c r="H152" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="I152" s="6"/>
+    </row>
+    <row r="153" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A153" s="6">
+        <v>28270285</v>
+      </c>
+      <c r="B153" s="6">
+        <v>3</v>
+      </c>
+      <c r="C153" s="7" t="s">
+        <v>548</v>
+      </c>
+      <c r="D153" s="7" t="s">
+        <v>556</v>
+      </c>
+      <c r="E153" s="8">
+        <v>4.07</v>
+      </c>
+      <c r="F153" s="8">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="G153" s="8">
+        <v>4.7</v>
+      </c>
+      <c r="H153" s="9" t="s">
+        <v>557</v>
+      </c>
+      <c r="I153" s="6"/>
+    </row>
+    <row r="154" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A154" s="6">
+        <v>28270285</v>
+      </c>
+      <c r="B154" s="6">
+        <v>4</v>
+      </c>
+      <c r="C154" s="7" t="s">
+        <v>549</v>
+      </c>
+      <c r="D154" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E154" s="8">
+        <v>3.74</v>
+      </c>
+      <c r="F154" s="8">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="G154" s="8">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="H154" s="9" t="s">
+        <v>558</v>
+      </c>
+      <c r="I154" s="6"/>
+    </row>
+    <row r="155" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A155" s="6">
+        <v>28270285</v>
+      </c>
+      <c r="B155" s="6">
+        <v>5</v>
+      </c>
+      <c r="C155" s="7" t="s">
+        <v>550</v>
+      </c>
+      <c r="D155" s="7" t="s">
+        <v>561</v>
+      </c>
+      <c r="E155" s="8">
+        <v>3.73</v>
+      </c>
+      <c r="F155" s="8">
+        <v>4.45</v>
+      </c>
+      <c r="G155" s="8">
+        <v>4.55</v>
+      </c>
+      <c r="H155" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="I155" s="6"/>
+    </row>
+    <row r="156" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A156" s="6">
+        <v>28270285</v>
+      </c>
+      <c r="B156" s="6">
+        <v>6</v>
+      </c>
+      <c r="C156" s="7" t="s">
+        <v>551</v>
+      </c>
+      <c r="D156" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E156" s="8">
+        <v>3.65</v>
+      </c>
+      <c r="F156" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="G156" s="8">
+        <v>4.45</v>
+      </c>
+      <c r="H156" s="9" t="s">
+        <v>560</v>
+      </c>
+      <c r="I156" s="6"/>
+    </row>
+    <row r="157" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A157" s="6">
+        <v>24184766</v>
+      </c>
+      <c r="B157" s="6">
+        <v>1</v>
+      </c>
+      <c r="C157" s="7" t="s">
+        <v>562</v>
+      </c>
+      <c r="D157" s="7" t="s">
+        <v>575</v>
+      </c>
+      <c r="E157" s="8">
+        <v>3.77</v>
+      </c>
+      <c r="F157" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G157" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="H157" s="9" t="s">
+        <v>573</v>
+      </c>
+      <c r="I157" s="6"/>
+    </row>
+    <row r="158" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A158" s="6">
+        <v>24184766</v>
+      </c>
+      <c r="B158" s="6">
+        <v>2</v>
+      </c>
+      <c r="C158" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="D158" s="7" t="s">
+        <v>576</v>
+      </c>
+      <c r="E158" s="8">
+        <v>3.53</v>
+      </c>
+      <c r="F158" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="G158" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="H158" s="9" t="s">
+        <v>572</v>
+      </c>
+      <c r="I158" s="6"/>
+    </row>
+    <row r="159" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A159" s="6">
+        <v>24184766</v>
+      </c>
+      <c r="B159" s="6">
+        <v>3</v>
+      </c>
+      <c r="C159" s="7" t="s">
+        <v>564</v>
+      </c>
+      <c r="D159" s="7" t="s">
+        <v>577</v>
+      </c>
+      <c r="E159" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="F159" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="G159" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="H159" s="9" t="s">
+        <v>571</v>
+      </c>
+      <c r="I159" s="6"/>
+    </row>
+    <row r="160" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A160" s="6">
+        <v>24184766</v>
+      </c>
+      <c r="B160" s="6">
+        <v>4</v>
+      </c>
+      <c r="C160" s="7" t="s">
+        <v>565</v>
+      </c>
+      <c r="D160" s="7" t="s">
+        <v>578</v>
+      </c>
+      <c r="E160" s="8">
+        <v>3.71</v>
+      </c>
+      <c r="F160" s="8">
+        <v>4</v>
+      </c>
+      <c r="G160" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="H160" s="9" t="s">
+        <v>574</v>
+      </c>
+      <c r="I160" s="6"/>
+    </row>
+    <row r="161" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A161" s="6">
+        <v>24184766</v>
+      </c>
+      <c r="B161" s="6">
+        <v>5</v>
+      </c>
+      <c r="C161" s="7" t="s">
+        <v>566</v>
+      </c>
+      <c r="D161" s="7" t="s">
+        <v>579</v>
+      </c>
+      <c r="E161" s="8">
+        <v>3.67</v>
+      </c>
+      <c r="F161" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="G161" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="H161" s="9" t="s">
+        <v>570</v>
+      </c>
+      <c r="I161" s="6"/>
+    </row>
+    <row r="162" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A162" s="6">
+        <v>24184766</v>
+      </c>
+      <c r="B162" s="6">
+        <v>6</v>
+      </c>
+      <c r="C162" s="7" t="s">
+        <v>567</v>
+      </c>
+      <c r="D162" s="7" t="s">
+        <v>577</v>
+      </c>
+      <c r="E162" s="8">
+        <v>3.57</v>
+      </c>
+      <c r="F162" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="G162" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="H162" s="9" t="s">
+        <v>569</v>
+      </c>
+      <c r="I162" s="6"/>
+    </row>
+    <row r="163" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A163" s="6">
+        <v>24184766</v>
+      </c>
+      <c r="B163" s="6">
+        <v>7</v>
+      </c>
+      <c r="C163" s="7" t="s">
+        <v>568</v>
+      </c>
+      <c r="D163" s="7" t="s">
+        <v>576</v>
+      </c>
+      <c r="E163" s="8">
+        <v>3.96</v>
+      </c>
+      <c r="F163" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G163" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="H163" s="9" t="s">
+        <v>580</v>
+      </c>
+      <c r="I163" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15F6D104-9E52-4CCF-9459-D227339DEECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C56C87FC-2D2E-40AE-A607-FF4B3D78F4F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="624">
   <si>
     <t>No</t>
   </si>
@@ -1788,6 +1788,111 @@
   </si>
   <si>
     <t>https://i.discogs.com/SxEGjTOeaIiLu8hEqKPGjWvHrwhZhDfSVnWbWWmahxc/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI0MTg0/NzY2LTE2NjAzNTE3/OTItNTMzMi5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Mean Old Sun</t>
+  </si>
+  <si>
+    <t>Brought Me</t>
+  </si>
+  <si>
+    <t>Lucille</t>
+  </si>
+  <si>
+    <t>Chipping Mill</t>
+  </si>
+  <si>
+    <t>The Rut</t>
+  </si>
+  <si>
+    <t>A Cat In The Rain</t>
+  </si>
+  <si>
+    <t>Black Sky</t>
+  </si>
+  <si>
+    <t>East Side Love Song (Bottoms Up)</t>
+  </si>
+  <si>
+    <t>Three More Days</t>
+  </si>
+  <si>
+    <t>Won't You Give Me One More Chance</t>
+  </si>
+  <si>
+    <t>Country Rock, Red Dirt</t>
+  </si>
+  <si>
+    <t>Americana, Country Rock</t>
+  </si>
+  <si>
+    <t>Country Rock</t>
+  </si>
+  <si>
+    <t>Bluegrass, Red Dirt</t>
+  </si>
+  <si>
+    <t>Americana, Country</t>
+  </si>
+  <si>
+    <t>Country Rock, Americana</t>
+  </si>
+  <si>
+    <t>Americana, Folk</t>
+  </si>
+  <si>
+    <t>Red Dirt, Country Rock</t>
+  </si>
+  <si>
+    <t>Country, Acoustic Folk</t>
+  </si>
+  <si>
+    <t>Σκοτεινή, swampy είσοδος με σταδιακό fade-in. Κυριαρχεί το χαρακτηριστικό minor-key jam με ρυθμικό banjo, βιολί και στιβαρά τύμπανα, ενώ ο Felker τραγουδά για έναν αμετανόητο τζογαδόρο.</t>
+  </si>
+  <si>
+    <t>Mid-tempo clapalong σύνθεση που λειτουργεί ως «ευχαριστήριο γράμμα» της μπάντας προς το κοινό της που στάθηκε πιστό στα χρόνια της απουσίας τους. Ζεστά φωνητικά και pedal steel.</t>
+  </si>
+  <si>
+    <t>Κλασικός country-rock ρυθμός με νοσταλγική ατμόσφαιρα. Ξεχωρίζει για την καθαρότητα των οργάνων και το μελωδικό hook στο ρεφρέν.</t>
+  </si>
+  <si>
+    <t>Σύνθεση του μπασίστα R.C. Edwards. Αυθεντικό Red Dirt κομμάτι με γρήγορο τέμπο, ακορντεόν, banjo και ποιητικούς στίχους περί θνητότητας. Εξαιρετική ακουστική ευκρίνεια.</t>
+  </si>
+  <si>
+    <t>Βαθιά εξομολογητικό highlight όπου ο Felker αναφέρεται ευθέως στην απεξάρτησή του από το αλκοόλ («I don't miss the taste of liquor»). Υποβλητική κιθάρα και Hank Early στο pedal steel.</t>
+  </si>
+  <si>
+    <t>Το ομώνυμο track, εμπνευσμένο από την ιστορία του Hemingway. Παραγωγή Shooter Jennings, με μεστό αναλογικό ήχο, πλούσια στρώματα κιθάρας και θέμα την αντοχή στις δυσκολίες.</t>
+  </si>
+  <si>
+    <t>Διασκευή στο κλασικό track των Ozark Mountain Daredevils. Βαρύς, αργός ρυθμός με δυναμική παρουσία φυσαρμόνικας και steel guitar που δίνει ποικιλία στον δίσκο.</t>
+  </si>
+  <si>
+    <t>Ατμοσφαιρική, ταξιδιάρικη μπαλάντα με αέρινο rhythm section. Εστιάζει στις αναμνήσεις και την επιστροφή στο Ανατολικό Τέξας κατά την περίοδο της παύσης του συγκροτήματος.</t>
+  </si>
+  <si>
+    <t>Γραμμένο από τον John Fulbright. Ρυθμικό track περιοδείας γεμάτο προσμονή για την επιστροφή στο σπίτι, με φωνητικές αρμονίες και κλαψιάρικη steel guitar.</t>
+  </si>
+  <si>
+    <t>Διασκευή στο κομμάτι του Jerry Jeff Walker. Ακουστικό campfire φινάλε με φυσαρμόνικα και βιολί, που αποδίδει μια αίσθηση συγχώρεσης και συναισθηματικής λύτρωσης.</t>
+  </si>
+  <si>
+    <t>Turnpike Troubadours</t>
+  </si>
+  <si>
+    <t>Red Dirt, Country Rock, Americana, Bluegrass</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/28074505-Turnpike-Troubadours-A-Cat-In-The-Rain</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/N8MbZZNhBraoEavZnmGL6x7fo71L_btKbJroc1t_Cy8/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI4MDc0/NTA1LTE2OTQwNTU5/NDEtNjgwOS5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Πρώτος δίσκος της μπάντας μετά από 6 χρόνια απουσίας και την απεξάρτηση του Evan Felker. Ηχογραφήθηκε στα Fame Recording Studios (Muscle Shoals) και Dave's Room (LA) σε παραγωγή Shooter Jennings. Audio Mastering &amp; Pressing Details: Mastering από τον Pete Lyman (Infrasonic Sound). Πρεσάρισμα σε Opaque Tan Vinyl (Indie Retail Exclusive) από τη Bossier City Records. Ηχητική Αξιολόγηση: Εξαιρετικά αναλογική, οργανική παραγωγή με ζεστό soundstage, πλούσια ακουστικά όργανα (βιολί, banjo, ακορντεόν, pedal steel) και εξαιρετικό διαχωρισμό συχνοτήτων.</t>
+  </si>
+  <si>
+    <t>Bossier City Records – BCR05 (US 2023, Opaque Tan Vinyl, Indie Retail Exclusive - ID 28074505)</t>
   </si>
 </sst>
 </file>
@@ -2216,7 +2321,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -2870,6 +2975,38 @@
       </c>
       <c r="J20" s="11" t="s">
         <v>588</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="6">
+        <v>28074505</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>618</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>594</v>
+      </c>
+      <c r="D21" s="6">
+        <v>2023</v>
+      </c>
+      <c r="E21" s="10">
+        <v>3.57</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>622</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>623</v>
+      </c>
+      <c r="I21" s="11" t="s">
+        <v>620</v>
+      </c>
+      <c r="J21" s="11" t="s">
+        <v>621</v>
       </c>
     </row>
   </sheetData>
@@ -2910,6 +3047,8 @@
     <hyperlink ref="J19" r:id="rId34" xr:uid="{BAB202AA-F491-4E39-A1A2-D6EBCE96D971}"/>
     <hyperlink ref="I20" r:id="rId35" xr:uid="{6F630CCD-C8C5-48E5-BF62-170422F60808}"/>
     <hyperlink ref="J20" r:id="rId36" xr:uid="{84319BCE-7BDE-4F59-BC89-A927A5EE3AFD}"/>
+    <hyperlink ref="I21" r:id="rId37" xr:uid="{457FA6A6-590F-4091-90C9-097732A21B44}"/>
+    <hyperlink ref="J21" r:id="rId38" xr:uid="{820070CD-F89D-439E-8345-B1B8BD267685}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2917,7 +3056,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I163"/>
+  <dimension ref="A1:I173"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="3" bestFit="1" customWidth="1"/>
@@ -7371,6 +7510,276 @@
       </c>
       <c r="I163" s="6"/>
     </row>
+    <row r="164" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A164" s="6">
+        <v>28074505</v>
+      </c>
+      <c r="B164" s="6">
+        <v>1</v>
+      </c>
+      <c r="C164" s="7" t="s">
+        <v>589</v>
+      </c>
+      <c r="D164" s="7" t="s">
+        <v>599</v>
+      </c>
+      <c r="E164" s="8">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="F164" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G164" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="H164" s="9" t="s">
+        <v>608</v>
+      </c>
+      <c r="I164" s="6"/>
+    </row>
+    <row r="165" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A165" s="6">
+        <v>28074505</v>
+      </c>
+      <c r="B165" s="6">
+        <v>2</v>
+      </c>
+      <c r="C165" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="D165" s="7" t="s">
+        <v>600</v>
+      </c>
+      <c r="E165" s="8">
+        <v>4.13</v>
+      </c>
+      <c r="F165" s="8">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="G165" s="8">
+        <v>4.25</v>
+      </c>
+      <c r="H165" s="9" t="s">
+        <v>609</v>
+      </c>
+      <c r="I165" s="6"/>
+    </row>
+    <row r="166" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A166" s="6">
+        <v>28074505</v>
+      </c>
+      <c r="B166" s="6">
+        <v>3</v>
+      </c>
+      <c r="C166" s="7" t="s">
+        <v>591</v>
+      </c>
+      <c r="D166" s="7" t="s">
+        <v>601</v>
+      </c>
+      <c r="E166" s="8">
+        <v>3.88</v>
+      </c>
+      <c r="F166" s="8">
+        <v>4</v>
+      </c>
+      <c r="G166" s="8">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="H166" s="9" t="s">
+        <v>610</v>
+      </c>
+      <c r="I166" s="6"/>
+    </row>
+    <row r="167" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A167" s="6">
+        <v>28074505</v>
+      </c>
+      <c r="B167" s="6">
+        <v>4</v>
+      </c>
+      <c r="C167" s="7" t="s">
+        <v>592</v>
+      </c>
+      <c r="D167" s="7" t="s">
+        <v>602</v>
+      </c>
+      <c r="E167" s="8">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="F167" s="8">
+        <v>4.45</v>
+      </c>
+      <c r="G167" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H167" s="9" t="s">
+        <v>611</v>
+      </c>
+      <c r="I167" s="6"/>
+    </row>
+    <row r="168" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A168" s="6">
+        <v>28074505</v>
+      </c>
+      <c r="B168" s="6">
+        <v>5</v>
+      </c>
+      <c r="C168" s="7" t="s">
+        <v>593</v>
+      </c>
+      <c r="D168" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="E168" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="F168" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="G168" s="8">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="H168" s="9" t="s">
+        <v>612</v>
+      </c>
+      <c r="I168" s="6"/>
+    </row>
+    <row r="169" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A169" s="6">
+        <v>28074505</v>
+      </c>
+      <c r="B169" s="6">
+        <v>6</v>
+      </c>
+      <c r="C169" s="7" t="s">
+        <v>594</v>
+      </c>
+      <c r="D169" s="7" t="s">
+        <v>604</v>
+      </c>
+      <c r="E169" s="8">
+        <v>4.12</v>
+      </c>
+      <c r="F169" s="8">
+        <v>4.45</v>
+      </c>
+      <c r="G169" s="8">
+        <v>4.45</v>
+      </c>
+      <c r="H169" s="9" t="s">
+        <v>613</v>
+      </c>
+      <c r="I169" s="6"/>
+    </row>
+    <row r="170" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A170" s="6">
+        <v>28074505</v>
+      </c>
+      <c r="B170" s="6">
+        <v>7</v>
+      </c>
+      <c r="C170" s="7" t="s">
+        <v>595</v>
+      </c>
+      <c r="D170" s="7" t="s">
+        <v>601</v>
+      </c>
+      <c r="E170" s="8">
+        <v>3.56</v>
+      </c>
+      <c r="F170" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="G170" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H170" s="9" t="s">
+        <v>614</v>
+      </c>
+      <c r="I170" s="6"/>
+    </row>
+    <row r="171" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A171" s="6">
+        <v>28074505</v>
+      </c>
+      <c r="B171" s="6">
+        <v>8</v>
+      </c>
+      <c r="C171" s="7" t="s">
+        <v>596</v>
+      </c>
+      <c r="D171" s="7" t="s">
+        <v>605</v>
+      </c>
+      <c r="E171" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="F171" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G171" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="H171" s="9" t="s">
+        <v>615</v>
+      </c>
+      <c r="I171" s="6"/>
+    </row>
+    <row r="172" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A172" s="6">
+        <v>28074505</v>
+      </c>
+      <c r="B172" s="6">
+        <v>9</v>
+      </c>
+      <c r="C172" s="7" t="s">
+        <v>597</v>
+      </c>
+      <c r="D172" s="7" t="s">
+        <v>606</v>
+      </c>
+      <c r="E172" s="8">
+        <v>3.71</v>
+      </c>
+      <c r="F172" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="G172" s="8">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="H172" s="9" t="s">
+        <v>616</v>
+      </c>
+      <c r="I172" s="6"/>
+    </row>
+    <row r="173" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A173" s="6">
+        <v>28074505</v>
+      </c>
+      <c r="B173" s="6">
+        <v>10</v>
+      </c>
+      <c r="C173" s="7" t="s">
+        <v>598</v>
+      </c>
+      <c r="D173" s="7" t="s">
+        <v>607</v>
+      </c>
+      <c r="E173" s="8">
+        <v>3.83</v>
+      </c>
+      <c r="F173" s="8">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="G173" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="H173" s="9" t="s">
+        <v>617</v>
+      </c>
+      <c r="I173" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C56C87FC-2D2E-40AE-A607-FF4B3D78F4F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D347814-B6C9-4A13-964D-1F91CFB3A2FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="648">
   <si>
     <t>No</t>
   </si>
@@ -1893,6 +1893,78 @@
   </si>
   <si>
     <t>Bossier City Records – BCR05 (US 2023, Opaque Tan Vinyl, Indie Retail Exclusive - ID 28074505)</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το αριστούργημα του Robin Trower (αρχική κυκλοφορία 1974). Ηχογραφήθηκε στα AIR Studios στο Λονδίνο με παραγωγό τον Matthew Fisher (πρώην σύνοδο στοιχείο των Procol Harum) και ηχολήπτη τον Geoff Emerick (θρυλικό μηχανικό των Beatles). Audio Mastering &amp; Pressing Details: Ευρωπαϊκή επανέκδοση 2014 σε 180g βινύλιο (Chrysalis / Parlophone). Πρεσάρισμα στα εργαστήρια της Optimal Media GmbH (Γερμανία / Πολωνία, κωδικός 010008688). Ηχητική Αξιολόγηση: Εκπληκτικά ογκόδης, ψυχεδελικός blues rock ήχος με βαθύ φινάλε στο μπάσο του James Dewar και τον χαρακτηριστικό Uni-Vibe/Marshall vintage ήχο κιθάρας του Trower.</t>
+  </si>
+  <si>
+    <t>Chrysalis – CHR. 1057 / 2564629703 (Europe 2014 Reissue, 180g Vinyl, Optimal Media Pressing - ID 25695898)</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/25695898-Robin-Trower-Bridge-Of-Sighs</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/v7tOubRvbz0K6KNJnafJwpw2VzhZeeL57K9csrRaZkg/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI1Njk1/ODk4LTE2NzMxNjk5/NTYtOTE5My5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Robin Trower</t>
+  </si>
+  <si>
+    <t>Bridge Of Sighs</t>
+  </si>
+  <si>
+    <t>Blues Rock, Psychedelic Rock, Hard Rock</t>
+  </si>
+  <si>
+    <t>Day Of The Eagle</t>
+  </si>
+  <si>
+    <t>Psychedelic Rock, Blues Rock</t>
+  </si>
+  <si>
+    <t>In This Place</t>
+  </si>
+  <si>
+    <t>Psychedelic Rock, Blues</t>
+  </si>
+  <si>
+    <t>The Fool And Me</t>
+  </si>
+  <si>
+    <t>Too Rolling Stoned</t>
+  </si>
+  <si>
+    <t>About To Begin</t>
+  </si>
+  <si>
+    <t>Lady Love</t>
+  </si>
+  <si>
+    <t>Little Bit Of Sympathy</t>
+  </si>
+  <si>
+    <t>Εκρηκτική έναρξη με επιθετικό, βαρύ riffing. Ξεχωρίζει η σπαρακτική ερμηνεία του James Dewar και η απότομη μετάβαση σε ένα αργό, υποβλητικό blues jam στο κλείσιμο. Εξαιρετικό punch στα τύμπανα του Reg Isidore και καθαρός διαχωρισμός κιθάρας.</t>
+  </si>
+  <si>
+    <t>Το ακρογωνιαίο κομμάτι του άλμπουμ. Ύμνος του ψυχεδελικού blues με βαριά χρήση Uni-Vibe εφέ, εφέ ανέμου και βαθύ τρισδιάστατο soundstage από τη μίξη του Geoff Emerick. Υποδειγματική ατμόσφαιρα με τεράστια ηχητική έκταση.</t>
+  </si>
+  <si>
+    <t>Ατμοσφαιρική, ταξιδιάρικη μπαλάντα με αέρινα κιθαριστικά textures. Το μπάσο του Dewar «αναπνέει» ζεστά στο προσκήνιο, προσφέροντας έναν εξαιρετικά αναλογικό, οργανικό ήχο.</t>
+  </si>
+  <si>
+    <t>Funky hard rock ρυθμός με κοφτά riffing και στιβαρή βάση στο rhythm section. Παρά την τοποθέτησή του κοντά στο κέντρο του δίσκου, διατηρεί υψηλή δυναμική περιοχή χωρίς παραμορφώσεις.</t>
+  </si>
+  <si>
+    <t>Επικό 7λεπτο track που ανοίγει με εκρηκτικό blues-funk groove και εξελίσσεται σε ένα από τα σπουδαιότερα, γεμάτα συναίσθημα σόλο του Trower. Τεράστιο εύρος συχνοτήτων με τη Stratocaster να δεσπόζει.</t>
+  </si>
+  <si>
+    <t>Ήρεμη, μελωδική σύνθεση που λειτουργεί ως ηχητική ανάσα. Δίνει έμφαση στις δυναμικές αυξομειώσεις, με την κιθάρα να καθαρίζει και το μπάσο να προσφέρει γεμάτο, στρογγυλεμένο χαμηλό.</t>
+  </si>
+  <si>
+    <t>Up-tempo, ραδιοφωνικό track με τεχνικό κιθαριστικό groove και εξαιρετικό stereo imaging στα πιάτα των τυμπάνων.</t>
+  </si>
+  <si>
+    <t>Καταιγιστικό φινάλε με γρήγορο τέμπο, επιθετικά σόλο και καταιγισμό στα τύμπανα. Η 180g πρέσα της Optimal διατηρεί την αιχμή και την ορμή του κομματιού μέχρι το τελευταίο αυλάκι.</t>
   </si>
 </sst>
 </file>
@@ -2321,7 +2393,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -3007,6 +3079,38 @@
       </c>
       <c r="J21" s="11" t="s">
         <v>621</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+      <c r="A22" s="6">
+        <v>25695898</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>628</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>629</v>
+      </c>
+      <c r="D22" s="6">
+        <v>1974</v>
+      </c>
+      <c r="E22" s="10">
+        <v>3.8</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>630</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>624</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>625</v>
+      </c>
+      <c r="I22" s="11" t="s">
+        <v>626</v>
+      </c>
+      <c r="J22" s="11" t="s">
+        <v>627</v>
       </c>
     </row>
   </sheetData>
@@ -3049,6 +3153,8 @@
     <hyperlink ref="J20" r:id="rId36" xr:uid="{84319BCE-7BDE-4F59-BC89-A927A5EE3AFD}"/>
     <hyperlink ref="I21" r:id="rId37" xr:uid="{457FA6A6-590F-4091-90C9-097732A21B44}"/>
     <hyperlink ref="J21" r:id="rId38" xr:uid="{820070CD-F89D-439E-8345-B1B8BD267685}"/>
+    <hyperlink ref="I22" r:id="rId39" xr:uid="{98CBE1F2-7113-4F22-A79D-E2DA1CA84C81}"/>
+    <hyperlink ref="J22" r:id="rId40" xr:uid="{F2F8B5E7-6D7A-4F6F-8D25-76E610D168E1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3056,7 +3162,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I173"/>
+  <dimension ref="A1:I181"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="3" bestFit="1" customWidth="1"/>
@@ -7780,6 +7886,224 @@
       </c>
       <c r="I173" s="6"/>
     </row>
+    <row r="174" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A174" s="6">
+        <v>25695898</v>
+      </c>
+      <c r="B174" s="6">
+        <v>1</v>
+      </c>
+      <c r="C174" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="D174" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="E174" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="F174" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G174" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="H174" s="9" t="s">
+        <v>640</v>
+      </c>
+      <c r="I174" s="6"/>
+    </row>
+    <row r="175" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A175" s="6">
+        <v>25695898</v>
+      </c>
+      <c r="B175" s="6">
+        <v>2</v>
+      </c>
+      <c r="C175" s="7" t="s">
+        <v>629</v>
+      </c>
+      <c r="D175" s="7" t="s">
+        <v>632</v>
+      </c>
+      <c r="E175" s="8">
+        <v>4.12</v>
+      </c>
+      <c r="F175" s="8">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="G175" s="8">
+        <v>4.75</v>
+      </c>
+      <c r="H175" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="I175" s="6" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A176" s="6">
+        <v>25695898</v>
+      </c>
+      <c r="B176" s="6">
+        <v>3</v>
+      </c>
+      <c r="C176" s="7" t="s">
+        <v>633</v>
+      </c>
+      <c r="D176" s="7" t="s">
+        <v>634</v>
+      </c>
+      <c r="E176" s="8">
+        <v>3.82</v>
+      </c>
+      <c r="F176" s="8">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="G176" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H176" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="I176" s="6"/>
+    </row>
+    <row r="177" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A177" s="6">
+        <v>25695898</v>
+      </c>
+      <c r="B177" s="6">
+        <v>4</v>
+      </c>
+      <c r="C177" s="7" t="s">
+        <v>635</v>
+      </c>
+      <c r="D177" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E177" s="8">
+        <v>3.94</v>
+      </c>
+      <c r="F177" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="G177" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="H177" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="I177" s="6"/>
+    </row>
+    <row r="178" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A178" s="6">
+        <v>25695898</v>
+      </c>
+      <c r="B178" s="6">
+        <v>5</v>
+      </c>
+      <c r="C178" s="7" t="s">
+        <v>636</v>
+      </c>
+      <c r="D178" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="E178" s="8">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="F178" s="8">
+        <v>4.7</v>
+      </c>
+      <c r="G178" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H178" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="I178" s="6"/>
+    </row>
+    <row r="179" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A179" s="6">
+        <v>25695898</v>
+      </c>
+      <c r="B179" s="6">
+        <v>6</v>
+      </c>
+      <c r="C179" s="7" t="s">
+        <v>637</v>
+      </c>
+      <c r="D179" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E179" s="8">
+        <v>3.79</v>
+      </c>
+      <c r="F179" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G179" s="8">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="H179" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="I179" s="6"/>
+    </row>
+    <row r="180" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A180" s="6">
+        <v>25695898</v>
+      </c>
+      <c r="B180" s="6">
+        <v>7</v>
+      </c>
+      <c r="C180" s="7" t="s">
+        <v>638</v>
+      </c>
+      <c r="D180" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E180" s="8">
+        <v>3.85</v>
+      </c>
+      <c r="F180" s="8">
+        <v>4.25</v>
+      </c>
+      <c r="G180" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="H180" s="9" t="s">
+        <v>646</v>
+      </c>
+      <c r="I180" s="6"/>
+    </row>
+    <row r="181" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A181" s="6">
+        <v>25695898</v>
+      </c>
+      <c r="B181" s="6">
+        <v>8</v>
+      </c>
+      <c r="C181" s="7" t="s">
+        <v>639</v>
+      </c>
+      <c r="D181" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="E181" s="8">
+        <v>3.87</v>
+      </c>
+      <c r="F181" s="8">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="G181" s="8">
+        <v>4.45</v>
+      </c>
+      <c r="H181" s="9" t="s">
+        <v>647</v>
+      </c>
+      <c r="I181" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D347814-B6C9-4A13-964D-1F91CFB3A2FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C81F7C3-F656-4DDB-A08B-D03C10034234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="648">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="727">
   <si>
     <t>No</t>
   </si>
@@ -1965,6 +1965,243 @@
   </si>
   <si>
     <t>Καταιγιστικό φινάλε με γρήγορο τέμπο, επιθετικά σόλο και καταιγισμό στα τύμπανα. Η 180g πρέσα της Optimal διατηρεί την αιχμή και την ορμή του κομματιού μέχρι το τελευταίο αυλάκι.</t>
+  </si>
+  <si>
+    <t>Stinkfist</t>
+  </si>
+  <si>
+    <t>Eulogy</t>
+  </si>
+  <si>
+    <t>H.</t>
+  </si>
+  <si>
+    <t>Useful Idiot</t>
+  </si>
+  <si>
+    <t>Forty Six &amp; 2</t>
+  </si>
+  <si>
+    <t>Message To Harry Manback</t>
+  </si>
+  <si>
+    <t>Hooker With A Penis</t>
+  </si>
+  <si>
+    <t>Intermission</t>
+  </si>
+  <si>
+    <t>Jimmy</t>
+  </si>
+  <si>
+    <t>Die Eier Von Satan</t>
+  </si>
+  <si>
+    <t>Pushit</t>
+  </si>
+  <si>
+    <t>Cesaro Summability</t>
+  </si>
+  <si>
+    <t>Ænema</t>
+  </si>
+  <si>
+    <t>(-) Ions</t>
+  </si>
+  <si>
+    <t>Third Eye</t>
+  </si>
+  <si>
+    <t>Tool</t>
+  </si>
+  <si>
+    <t>Aenima</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/11981817-Tool-%C3%86nima</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/UolnScJgeOV1KOhRaCyG7zmyMP5RAGyfCeKHTd10aU0/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTE1Nzgx/NjItMTIyOTc3OTYz/Ni5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Alternative Metal, Progressive Metal, Art Rock</t>
+  </si>
+  <si>
+    <t>Zoo Entertainment / BMG Entertainment (Unofficial / Counterfeit)</t>
+  </si>
+  <si>
+    <t>Progressive Metal</t>
+  </si>
+  <si>
+    <t>Dark Ambient, Drone</t>
+  </si>
+  <si>
+    <t>Dark Ambient, Spoken Word</t>
+  </si>
+  <si>
+    <t>Organ, Lounge</t>
+  </si>
+  <si>
+    <t>Industrial Metal, Spoken Word</t>
+  </si>
+  <si>
+    <t>Noise, Ambient</t>
+  </si>
+  <si>
+    <t>Musique Concrète, Industrial</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Heavy Metal</t>
+  </si>
+  <si>
+    <t>Progressive Metal, Alternative Metal</t>
+  </si>
+  <si>
+    <t>Το εναρκτήριο λάκτισμα του δίσκου και κορυφαίο single. Ο Adam Jones κεντάει με το κοφτερό, υπνωτικό riff και τη χρήση pitch-shifter, χτίζοντας μια ασφυκτική ατμόσφαιρα που εκτονώνεται σταδιακά στα εκρηκτικά ρεφρέν.</t>
+  </si>
+  <si>
+    <t>Μνημειώδης, πολυεπίπεδη σύνθεση που ξεκινά σχεδόν ψιθυριστά με ηλεκτρονικούς ήχους και εξελίσσεται σε progressive πανδαισία. Ο Danny Carey δίνει ρεσιτάλ πολυρυθμίας και δυναμικής στα τύμπανα.</t>
+  </si>
+  <si>
+    <t>Alternative Metal, Progressive Metal</t>
+  </si>
+  <si>
+    <t>Βαθιά εσωτερικό και μελαγχολικό κομμάτι, υποβασταζόμενο από το βαρύ, μελωδικό μπάσο του Justin Chancellor. Τα φωνητικά του Maynard περνούν από την απόλυτη εσωστρέφεση σε σπαρακτικά ξεσπάσματα.</t>
+  </si>
+  <si>
+    <t>Μινιμαλιστική ηχητική γέφυρα που αναπαράγει τον χαρακτηριστικό, επίμονο θόρυβο από το «σκάλωμα» και το φύσημα της βελόνας στο αυλάκι ενός βινυλίου.</t>
+  </si>
+  <si>
+    <t>Αξεπέραστο αριστούργημα του είδους. Χτίζεται γύρω από ένα από τα πιο αναγνωρίσιμα και εθιστικά basslines στην ιστορία της ροκ, οδηγώντας σε ένα πρωτοφανές, καταιγιστικό drum solo στο φινάλε.</t>
+  </si>
+  <si>
+    <t>Σαρκαστικό και σκοτεινό ιντερμέδιο· μια μελαγχολική, μινιμαλιστική μελωδία πιάνου συνοδεύει ένα πραγματικό, παραληρηματικό και υβριστικό μήνυμα που είχε αφήσει αγανακτισμένος ακροατής στον τηλεφωνητή τους.</t>
+  </si>
+  <si>
+    <t>Sludge Metal, Alternative Metal</t>
+  </si>
+  <si>
+    <t>Ωμό, επιθετικό και σαρκαστικό χαστούκι προς την εμπορική μουσική βιομηχανία και όσους κατηγόρησαν τη μπάντα για ξεπούλημα, με sludge/punk ενέργεια και κοφτερά riffs.</t>
+  </si>
+  <si>
+    <t>Μια παράξενη, ειρωνική διασκευή του βασικού μελωδικού θέματος του επερχόμενου "Jimmy", παιγμένη αποκλειστικά σε vintage όργανο πανηγυριού/λούνα παρκ.</t>
+  </si>
+  <si>
+    <t>Η φυσική, σκοτεινή συνέχεια του "Intermission". Κινείται σε αργόσυρτους, βαριούς ρυθμούς με χαμηλόκουρδισμένες κιθάρες και προσωπικούς, κρυπτικούς στίχους για τα παιδικά χρόνια του Maynard.</t>
+  </si>
+  <si>
+    <t>Βιομηχανικός, μηχανικός ρυθμός march κάτω από μια γερμανική, αυταρχική απαγγελία που θυμίζει ναζιστική προπαγάνδα, η οποία όμως –προς έκπληξη όλων– αποδεικνύεται πως είναι μια παραδοσιακή συνταγή για χριστουγεννιάτικα μπισκότα χωρίς αυγά!</t>
+  </si>
+  <si>
+    <t>Ένα δεκάλεπτο έπος ψυχολογικής και μουσικής εκτόνωσης. Χτίζεται με υπομονή από την απόλυτη ηρεμία σε έναν οργασμικό, λυτρωτικό παροξυσμό εντάσεων και μελωδίας.</t>
+  </si>
+  <si>
+    <t>Δυστοπικό ηχητικό κολάζ (soundscape) γεμάτο από παράσιτα, ανάποδα φιλμ, βιομηχανικό θόρυβο και το σπαρακτικό κλάμα ενός νεογέννητου μωρού που κόβει την ανάσα.</t>
+  </si>
+  <si>
+    <t>Το εμβληματικό τραγούδι-ορόσημο που χάρισε στη μπάντα Grammy. Χαρακτηρίζεται από τις αριστοτεχνικές αλλαγές μέτρου (από 3/4 σε 4/4) και τον καυστικό, μηδενιστικό στίχο που εύχεται να βουλιάξει επιτέλους το Λος Άντζελες στον ωκεανό.</t>
+  </si>
+  <si>
+    <t>Ατμοσφαιρικό πείραμα ηλεκτροαουστικής μουσικής που αναπαριστά την αίσθηση μιας επικείμενης, ηλεκτρικής καταιγίδας και συσσώρευσης στατικού ηλεκτρισμού πριν το μεγάλο φινάλε.</t>
+  </si>
+  <si>
+    <t>Το απόλυτο, 14λεπτο υπερθέαμα του δίσκου. Ενσωματώνει φιλοσοφικά αποσπάσματα από τα stand-up του Bill Hicks, υπνωτικά πολυρυθμικά μοτίβα και αποτελεί την κορυφαία ψυχεδελική/μεταλ εμπειρία του άλμπουμ.</t>
+  </si>
+  <si>
+    <t>What Is Hip?</t>
+  </si>
+  <si>
+    <t>Clever Girl</t>
+  </si>
+  <si>
+    <t>This Time It's Real</t>
+  </si>
+  <si>
+    <t>Will I Ever Find A Love?</t>
+  </si>
+  <si>
+    <t>Get Yo' Feet Back On The Ground</t>
+  </si>
+  <si>
+    <t>So Very Hard To Go</t>
+  </si>
+  <si>
+    <t>Soul Vaccination</t>
+  </si>
+  <si>
+    <t>Both Sorry Over Nothin'</t>
+  </si>
+  <si>
+    <t>Clean Slate</t>
+  </si>
+  <si>
+    <t>Just Another Day</t>
+  </si>
+  <si>
+    <t>Tower Of Power</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/uAxYNnRQiqOgDXtuqigJ_V2_GAygJIvmQY7QP4-5REs/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI5MjY0/NDIyLTE3MDg1NTEw/MTAtNjI0NC5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/29264422-Tower-Of-Power-Tower-Of-Power</t>
+  </si>
+  <si>
+    <t>Jazz-Funk, Soul, Funk</t>
+  </si>
+  <si>
+    <t>Music On Vinyl – MOVLP1243 (EU Reissue, Numbered, 180 Gram, Yellow Translucent)</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Unofficial Pressing / Bootleg (2xLP, Black Vinyl, Gatefold Sleeve). Gatefold jacket with green artwork inside, printed insert/inners; no barcode on rear cover. Matrix / Runout (Stamped): 72445 11087 A / B / C / D. Side A features locked runout groove as original. Discogs Release ID: [r11981817]</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Επίσημη επανεκδοση της Music On Vinyl, περιορισμένης/αριθμημένης κοπής σε κίτρινο ημιδιαφανές βινύλιο 180 γραμμαρίων. Matrix / Runout (Runout πλευράς Α): 10518 1A MOVLP 1243. Matrix / Runout (Runout πλευράς Β): 10518 1B MOVLP 1243. Κοπή από την Record Industry.</t>
+  </si>
+  <si>
+    <t>Απολαυστικό funk μνημείο με το ασύλληπτο, κοφτό slap bass του Francis Rocco Prestia και τα κοφτερά πνευστά να δίνουν ρυθμικό οίστρο σε ένα από τα πιο αναγνωρίσιμα grooves στην ιστορία του είδους.</t>
+  </si>
+  <si>
+    <t>Funk, Jazz-Funk</t>
+  </si>
+  <si>
+    <t>Εξαιρετικό soul/funk δείγμα γραφής με έμφαση στα γλυκά φωνητικά harmony lines και την εξαιρετική ισορροπία των πνευστών της East Bay Grease ορχήστρας.</t>
+  </si>
+  <si>
+    <t>Soul, Funk</t>
+  </si>
+  <si>
+    <t>Φοβερά μελωδική ψυχεδελική soul σύνθεση με τον Lenny Williams στα φωνητικά να δίνει ρέστα, υποβασταζόμενος από μια πλούσια, ζεστή ενορχήστρωση.</t>
+  </si>
+  <si>
+    <t>Αργόσυρτη, αισθησιακή soul μπαλάντα με έντονα τα στοιχεία του κλασικού R&amp;B της εποχής και υποδειγματική, καθαρή αναλογική ηχογράφηση στα φωνητικά.</t>
+  </si>
+  <si>
+    <t>Soul, Rhythm &amp; Blues</t>
+  </si>
+  <si>
+    <t>Funk, Soul</t>
+  </si>
+  <si>
+    <t>Χορευτικός δυναμιτισμός με κοφτερά ρυθμικά μέρη από τα τύμπανα του David Garibaldi και groovy πνευστά που σε ξεσηκώνουν από το πρώτο δευτερόλεπτο.</t>
+  </si>
+  <si>
+    <t>Το απόλυτο ερωτικό αριστούργημα και τεράστια επιτυχία της μπάντας. Αξέχαστη μελωδία, υπέροχα φωνητικά και μια από τις πιο εκφραστικές παραγωγές τους.</t>
+  </si>
+  <si>
+    <t>Soul, Quiet Storm</t>
+  </si>
+  <si>
+    <t>Ένα πραγματικό masterclass στα πνευστά και στο funk groove· ταχύρρυθμο, τεχνικότατο και γεμάτο ζωντάνια, ιδανικό για να τεστάρεις τα δυναμικά του συστήματός σου.</t>
+  </si>
+  <si>
+    <t>Ρυθμικό και συμπαγές κομμάτι που συνδυάζει την ψυχή της soul με τα κοφτερά, κοπαδιαστά περάσματα των οργάνων και των πνευστών.</t>
+  </si>
+  <si>
+    <t>Δυναμικό κομμάτι με εξαιρετικό δέσιμο ανάμεσα στα τύμπανα και το μπάσο, αναδεικνύοντας τη χαρακτηριστική "East Bay" υπογραφή τους.</t>
+  </si>
+  <si>
+    <t>Εύθυμο και πολυσύνθετο φινάλε που κλείνει ιδανικά τον δίσκο, αφήνοντας τις καλύτερες εντυπώσεις με το πλούσιο ηχητικό του εύρος.</t>
   </si>
 </sst>
 </file>
@@ -2393,7 +2630,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -3111,6 +3348,70 @@
       </c>
       <c r="J22" s="11" t="s">
         <v>627</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="6">
+        <v>11981817</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>663</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>664</v>
+      </c>
+      <c r="D23" s="6">
+        <v>1996</v>
+      </c>
+      <c r="E23" s="10">
+        <v>3.94</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>667</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>710</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>668</v>
+      </c>
+      <c r="I23" s="11" t="s">
+        <v>665</v>
+      </c>
+      <c r="J23" s="11" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+      <c r="A24" s="6">
+        <v>29264422</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>705</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>705</v>
+      </c>
+      <c r="D24" s="6">
+        <v>1973</v>
+      </c>
+      <c r="E24" s="10">
+        <v>3.58</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>708</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>711</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>709</v>
+      </c>
+      <c r="I24" s="11" t="s">
+        <v>707</v>
+      </c>
+      <c r="J24" s="11" t="s">
+        <v>706</v>
       </c>
     </row>
   </sheetData>
@@ -3155,6 +3456,10 @@
     <hyperlink ref="J21" r:id="rId38" xr:uid="{820070CD-F89D-439E-8345-B1B8BD267685}"/>
     <hyperlink ref="I22" r:id="rId39" xr:uid="{98CBE1F2-7113-4F22-A79D-E2DA1CA84C81}"/>
     <hyperlink ref="J22" r:id="rId40" xr:uid="{F2F8B5E7-6D7A-4F6F-8D25-76E610D168E1}"/>
+    <hyperlink ref="I23" r:id="rId41" xr:uid="{CA3FCADF-3756-4A65-8A98-0AB7143633F2}"/>
+    <hyperlink ref="J23" r:id="rId42" xr:uid="{3575A396-31E6-40CA-9AE5-93286E535880}"/>
+    <hyperlink ref="J24" r:id="rId43" xr:uid="{6E0506A5-8A8E-4A23-BB64-838F694F517F}"/>
+    <hyperlink ref="I24" r:id="rId44" xr:uid="{0D6B3B88-F335-416B-8E1F-865D3DD5E2F0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3162,7 +3467,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I181"/>
+  <dimension ref="A1:I206"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="3" bestFit="1" customWidth="1"/>
@@ -8104,6 +8409,681 @@
       </c>
       <c r="I181" s="6"/>
     </row>
+    <row r="182" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A182" s="6">
+        <v>11981817</v>
+      </c>
+      <c r="B182" s="6">
+        <v>1</v>
+      </c>
+      <c r="C182" s="7" t="s">
+        <v>648</v>
+      </c>
+      <c r="D182" s="7" t="s">
+        <v>677</v>
+      </c>
+      <c r="E182" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="F182" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G182" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="H182" s="9" t="s">
+        <v>678</v>
+      </c>
+      <c r="I182" s="6"/>
+    </row>
+    <row r="183" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A183" s="6">
+        <v>11981817</v>
+      </c>
+      <c r="B183" s="6">
+        <v>2</v>
+      </c>
+      <c r="C183" s="7" t="s">
+        <v>649</v>
+      </c>
+      <c r="D183" s="7" t="s">
+        <v>669</v>
+      </c>
+      <c r="E183" s="8">
+        <v>4.37</v>
+      </c>
+      <c r="F183" s="8">
+        <v>4.8</v>
+      </c>
+      <c r="G183" s="8">
+        <v>4.7</v>
+      </c>
+      <c r="H183" s="9" t="s">
+        <v>679</v>
+      </c>
+      <c r="I183" s="6"/>
+    </row>
+    <row r="184" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A184" s="6">
+        <v>11981817</v>
+      </c>
+      <c r="B184" s="6">
+        <v>3</v>
+      </c>
+      <c r="C184" s="7" t="s">
+        <v>650</v>
+      </c>
+      <c r="D184" s="7" t="s">
+        <v>680</v>
+      </c>
+      <c r="E184" s="8">
+        <v>4.25</v>
+      </c>
+      <c r="F184" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="G184" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H184" s="9" t="s">
+        <v>681</v>
+      </c>
+      <c r="I184" s="6"/>
+    </row>
+    <row r="185" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A185" s="6">
+        <v>11981817</v>
+      </c>
+      <c r="B185" s="6">
+        <v>4</v>
+      </c>
+      <c r="C185" s="7" t="s">
+        <v>651</v>
+      </c>
+      <c r="D185" s="7" t="s">
+        <v>670</v>
+      </c>
+      <c r="E185" s="8">
+        <v>3.01</v>
+      </c>
+      <c r="F185" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="G185" s="8">
+        <v>3</v>
+      </c>
+      <c r="H185" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="I185" s="6"/>
+    </row>
+    <row r="186" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A186" s="6">
+        <v>11981817</v>
+      </c>
+      <c r="B186" s="6">
+        <v>5</v>
+      </c>
+      <c r="C186" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="D186" s="7" t="s">
+        <v>669</v>
+      </c>
+      <c r="E186" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="F186" s="8">
+        <v>5</v>
+      </c>
+      <c r="G186" s="8">
+        <v>4.8</v>
+      </c>
+      <c r="H186" s="9" t="s">
+        <v>683</v>
+      </c>
+      <c r="I186" s="6"/>
+    </row>
+    <row r="187" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A187" s="6">
+        <v>11981817</v>
+      </c>
+      <c r="B187" s="6">
+        <v>6</v>
+      </c>
+      <c r="C187" s="7" t="s">
+        <v>653</v>
+      </c>
+      <c r="D187" s="7" t="s">
+        <v>671</v>
+      </c>
+      <c r="E187" s="8">
+        <v>3.18</v>
+      </c>
+      <c r="F187" s="8">
+        <v>3</v>
+      </c>
+      <c r="G187" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="H187" s="9" t="s">
+        <v>684</v>
+      </c>
+      <c r="I187" s="6"/>
+    </row>
+    <row r="188" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A188" s="6">
+        <v>11981817</v>
+      </c>
+      <c r="B188" s="6">
+        <v>7</v>
+      </c>
+      <c r="C188" s="7" t="s">
+        <v>654</v>
+      </c>
+      <c r="D188" s="7" t="s">
+        <v>685</v>
+      </c>
+      <c r="E188" s="8">
+        <v>4.04</v>
+      </c>
+      <c r="F188" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="G188" s="8">
+        <v>4</v>
+      </c>
+      <c r="H188" s="9" t="s">
+        <v>686</v>
+      </c>
+      <c r="I188" s="6"/>
+    </row>
+    <row r="189" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A189" s="6">
+        <v>11981817</v>
+      </c>
+      <c r="B189" s="6">
+        <v>8</v>
+      </c>
+      <c r="C189" s="7" t="s">
+        <v>655</v>
+      </c>
+      <c r="D189" s="7" t="s">
+        <v>672</v>
+      </c>
+      <c r="E189" s="8">
+        <v>3.41</v>
+      </c>
+      <c r="F189" s="8">
+        <v>2.8</v>
+      </c>
+      <c r="G189" s="8">
+        <v>3</v>
+      </c>
+      <c r="H189" s="9" t="s">
+        <v>687</v>
+      </c>
+      <c r="I189" s="6"/>
+    </row>
+    <row r="190" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A190" s="6">
+        <v>11981817</v>
+      </c>
+      <c r="B190" s="6">
+        <v>9</v>
+      </c>
+      <c r="C190" s="7" t="s">
+        <v>656</v>
+      </c>
+      <c r="D190" s="7" t="s">
+        <v>669</v>
+      </c>
+      <c r="E190" s="8">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="F190" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G190" s="8">
+        <v>4</v>
+      </c>
+      <c r="H190" s="9" t="s">
+        <v>688</v>
+      </c>
+      <c r="I190" s="6"/>
+    </row>
+    <row r="191" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A191" s="6">
+        <v>11981817</v>
+      </c>
+      <c r="B191" s="6">
+        <v>10</v>
+      </c>
+      <c r="C191" s="7" t="s">
+        <v>657</v>
+      </c>
+      <c r="D191" s="7" t="s">
+        <v>673</v>
+      </c>
+      <c r="E191" s="8">
+        <v>3.27</v>
+      </c>
+      <c r="F191" s="8">
+        <v>3.27</v>
+      </c>
+      <c r="G191" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="H191" s="9" t="s">
+        <v>689</v>
+      </c>
+      <c r="I191" s="6"/>
+    </row>
+    <row r="192" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A192" s="6">
+        <v>11981817</v>
+      </c>
+      <c r="B192" s="6">
+        <v>11</v>
+      </c>
+      <c r="C192" s="7" t="s">
+        <v>658</v>
+      </c>
+      <c r="D192" s="7" t="s">
+        <v>669</v>
+      </c>
+      <c r="E192" s="8">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="F192" s="8">
+        <v>4.8</v>
+      </c>
+      <c r="G192" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H192" s="9" t="s">
+        <v>690</v>
+      </c>
+      <c r="I192" s="6"/>
+    </row>
+    <row r="193" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A193" s="6">
+        <v>11981817</v>
+      </c>
+      <c r="B193" s="6">
+        <v>12</v>
+      </c>
+      <c r="C193" s="7" t="s">
+        <v>659</v>
+      </c>
+      <c r="D193" s="7" t="s">
+        <v>674</v>
+      </c>
+      <c r="E193" s="8">
+        <v>2.73</v>
+      </c>
+      <c r="F193" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G193" s="8">
+        <v>3</v>
+      </c>
+      <c r="H193" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="I193" s="6"/>
+    </row>
+    <row r="194" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A194" s="6">
+        <v>11981817</v>
+      </c>
+      <c r="B194" s="6">
+        <v>13</v>
+      </c>
+      <c r="C194" s="7" t="s">
+        <v>660</v>
+      </c>
+      <c r="D194" s="7" t="s">
+        <v>677</v>
+      </c>
+      <c r="E194" s="8">
+        <v>4.43</v>
+      </c>
+      <c r="F194" s="8">
+        <v>5</v>
+      </c>
+      <c r="G194" s="8">
+        <v>4.7</v>
+      </c>
+      <c r="H194" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="I194" s="6"/>
+    </row>
+    <row r="195" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A195" s="6">
+        <v>11981817</v>
+      </c>
+      <c r="B195" s="6">
+        <v>14</v>
+      </c>
+      <c r="C195" s="7" t="s">
+        <v>661</v>
+      </c>
+      <c r="D195" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="E195" s="8">
+        <v>2.99</v>
+      </c>
+      <c r="F195" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G195" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="H195" s="9" t="s">
+        <v>693</v>
+      </c>
+      <c r="I195" s="6"/>
+    </row>
+    <row r="196" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A196" s="6">
+        <v>11981817</v>
+      </c>
+      <c r="B196" s="6">
+        <v>15</v>
+      </c>
+      <c r="C196" s="7" t="s">
+        <v>662</v>
+      </c>
+      <c r="D196" s="7" t="s">
+        <v>676</v>
+      </c>
+      <c r="E196" s="8">
+        <v>4.24</v>
+      </c>
+      <c r="F196" s="8">
+        <v>5</v>
+      </c>
+      <c r="G196" s="8">
+        <v>4.8</v>
+      </c>
+      <c r="H196" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="I196" s="6"/>
+    </row>
+    <row r="197" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A197" s="6">
+        <v>29264422</v>
+      </c>
+      <c r="B197" s="6">
+        <v>1</v>
+      </c>
+      <c r="C197" s="7" t="s">
+        <v>695</v>
+      </c>
+      <c r="D197" s="7" t="s">
+        <v>713</v>
+      </c>
+      <c r="E197" s="8">
+        <v>4.01</v>
+      </c>
+      <c r="F197" s="8">
+        <v>4.8</v>
+      </c>
+      <c r="G197" s="8">
+        <v>4.7</v>
+      </c>
+      <c r="H197" s="9" t="s">
+        <v>712</v>
+      </c>
+      <c r="I197" s="6"/>
+    </row>
+    <row r="198" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A198" s="6">
+        <v>29264422</v>
+      </c>
+      <c r="B198" s="6">
+        <v>2</v>
+      </c>
+      <c r="C198" s="7" t="s">
+        <v>696</v>
+      </c>
+      <c r="D198" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="E198" s="8">
+        <v>3.64</v>
+      </c>
+      <c r="F198" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="G198" s="8">
+        <v>4</v>
+      </c>
+      <c r="H198" s="9" t="s">
+        <v>714</v>
+      </c>
+      <c r="I198" s="6"/>
+    </row>
+    <row r="199" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A199" s="6">
+        <v>29264422</v>
+      </c>
+      <c r="B199" s="6">
+        <v>3</v>
+      </c>
+      <c r="C199" s="7" t="s">
+        <v>697</v>
+      </c>
+      <c r="D199" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="E199" s="8">
+        <v>3.69</v>
+      </c>
+      <c r="F199" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="G199" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H199" s="9" t="s">
+        <v>716</v>
+      </c>
+      <c r="I199" s="6"/>
+    </row>
+    <row r="200" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A200" s="6">
+        <v>29264422</v>
+      </c>
+      <c r="B200" s="6">
+        <v>4</v>
+      </c>
+      <c r="C200" s="7" t="s">
+        <v>698</v>
+      </c>
+      <c r="D200" s="7" t="s">
+        <v>718</v>
+      </c>
+      <c r="E200" s="8">
+        <v>3.34</v>
+      </c>
+      <c r="F200" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="G200" s="8">
+        <v>4</v>
+      </c>
+      <c r="H200" s="9" t="s">
+        <v>717</v>
+      </c>
+      <c r="I200" s="6"/>
+    </row>
+    <row r="201" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A201" s="6">
+        <v>29264422</v>
+      </c>
+      <c r="B201" s="6">
+        <v>5</v>
+      </c>
+      <c r="C201" s="7" t="s">
+        <v>699</v>
+      </c>
+      <c r="D201" s="7" t="s">
+        <v>719</v>
+      </c>
+      <c r="E201" s="8">
+        <v>3.73</v>
+      </c>
+      <c r="F201" s="8">
+        <v>4</v>
+      </c>
+      <c r="G201" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="H201" s="9" t="s">
+        <v>720</v>
+      </c>
+      <c r="I201" s="6"/>
+    </row>
+    <row r="202" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A202" s="6">
+        <v>29264422</v>
+      </c>
+      <c r="B202" s="6">
+        <v>6</v>
+      </c>
+      <c r="C202" s="7" t="s">
+        <v>700</v>
+      </c>
+      <c r="D202" s="7" t="s">
+        <v>722</v>
+      </c>
+      <c r="E202" s="8">
+        <v>4.01</v>
+      </c>
+      <c r="F202" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G202" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="H202" s="9" t="s">
+        <v>721</v>
+      </c>
+      <c r="I202" s="6"/>
+    </row>
+    <row r="203" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A203" s="6">
+        <v>29264422</v>
+      </c>
+      <c r="B203" s="6">
+        <v>7</v>
+      </c>
+      <c r="C203" s="7" t="s">
+        <v>701</v>
+      </c>
+      <c r="D203" s="7" t="s">
+        <v>713</v>
+      </c>
+      <c r="E203" s="8">
+        <v>3.81</v>
+      </c>
+      <c r="F203" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G203" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H203" s="9" t="s">
+        <v>723</v>
+      </c>
+      <c r="I203" s="6"/>
+    </row>
+    <row r="204" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A204" s="6">
+        <v>29264422</v>
+      </c>
+      <c r="B204" s="6">
+        <v>8</v>
+      </c>
+      <c r="C204" s="7" t="s">
+        <v>702</v>
+      </c>
+      <c r="D204" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="E204" s="8">
+        <v>3.54</v>
+      </c>
+      <c r="F204" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="G204" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="H204" s="9" t="s">
+        <v>724</v>
+      </c>
+      <c r="I204" s="6"/>
+    </row>
+    <row r="205" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A205" s="6">
+        <v>29264422</v>
+      </c>
+      <c r="B205" s="6">
+        <v>9</v>
+      </c>
+      <c r="C205" s="7" t="s">
+        <v>703</v>
+      </c>
+      <c r="D205" s="7" t="s">
+        <v>713</v>
+      </c>
+      <c r="E205" s="8">
+        <v>3.46</v>
+      </c>
+      <c r="F205" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="G205" s="8">
+        <v>4</v>
+      </c>
+      <c r="H205" s="9" t="s">
+        <v>725</v>
+      </c>
+      <c r="I205" s="6"/>
+    </row>
+    <row r="206" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A206" s="6">
+        <v>29264422</v>
+      </c>
+      <c r="B206" s="6">
+        <v>10</v>
+      </c>
+      <c r="C206" s="7" t="s">
+        <v>704</v>
+      </c>
+      <c r="D206" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="E206" s="8">
+        <v>3.56</v>
+      </c>
+      <c r="F206" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="G206" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H206" s="9" t="s">
+        <v>726</v>
+      </c>
+      <c r="I206" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C81F7C3-F656-4DDB-A08B-D03C10034234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{260904B7-87FF-4D95-B3BC-F95709163C09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -2156,9 +2156,6 @@
     <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Unofficial Pressing / Bootleg (2xLP, Black Vinyl, Gatefold Sleeve). Gatefold jacket with green artwork inside, printed insert/inners; no barcode on rear cover. Matrix / Runout (Stamped): 72445 11087 A / B / C / D. Side A features locked runout groove as original. Discogs Release ID: [r11981817]</t>
   </si>
   <si>
-    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Επίσημη επανεκδοση της Music On Vinyl, περιορισμένης/αριθμημένης κοπής σε κίτρινο ημιδιαφανές βινύλιο 180 γραμμαρίων. Matrix / Runout (Runout πλευράς Α): 10518 1A MOVLP 1243. Matrix / Runout (Runout πλευράς Β): 10518 1B MOVLP 1243. Κοπή από την Record Industry.</t>
-  </si>
-  <si>
     <t>Απολαυστικό funk μνημείο με το ασύλληπτο, κοφτό slap bass του Francis Rocco Prestia και τα κοφτερά πνευστά να δίνουν ρυθμικό οίστρο σε ένα από τα πιο αναγνωρίσιμα grooves στην ιστορία του είδους.</t>
   </si>
   <si>
@@ -2202,6 +2199,9 @@
   </si>
   <si>
     <t>Εύθυμο και πολυσύνθετο φινάλε που κλείνει ιδανικά τον δίσκο, αφήνοντας τις καλύτερες εντυπώσεις με το πλούσιο ηχητικό του εύρος.</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Επίσημη επανεκδοση της Music On Vinyl, περιορισμένης/αριθμημένης κοπής 2000 αντιτύπων σε κίτρινο ημιδιαφανές βινύλιο 180 γραμμαρίων (με το χαρακτηριστικό χρυσό hype sticker). Matrix / Runout (Side A): 10518 1A MOVLP 1243. Matrix / Runout (Side B): 10518 1B MOVLP 1243. Κοπή από την Record Industry.</t>
   </si>
 </sst>
 </file>
@@ -3402,7 +3402,7 @@
         <v>708</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>711</v>
+        <v>726</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>709</v>
@@ -8825,7 +8825,7 @@
         <v>695</v>
       </c>
       <c r="D197" s="7" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E197" s="8">
         <v>4.01</v>
@@ -8837,7 +8837,7 @@
         <v>4.7</v>
       </c>
       <c r="H197" s="9" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="I197" s="6"/>
     </row>
@@ -8852,7 +8852,7 @@
         <v>696</v>
       </c>
       <c r="D198" s="7" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E198" s="8">
         <v>3.64</v>
@@ -8864,7 +8864,7 @@
         <v>4</v>
       </c>
       <c r="H198" s="9" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="I198" s="6"/>
     </row>
@@ -8879,7 +8879,7 @@
         <v>697</v>
       </c>
       <c r="D199" s="7" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E199" s="8">
         <v>3.69</v>
@@ -8891,7 +8891,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H199" s="9" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="I199" s="6"/>
     </row>
@@ -8906,7 +8906,7 @@
         <v>698</v>
       </c>
       <c r="D200" s="7" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="E200" s="8">
         <v>3.34</v>
@@ -8918,7 +8918,7 @@
         <v>4</v>
       </c>
       <c r="H200" s="9" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="I200" s="6"/>
     </row>
@@ -8933,7 +8933,7 @@
         <v>699</v>
       </c>
       <c r="D201" s="7" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="E201" s="8">
         <v>3.73</v>
@@ -8945,7 +8945,7 @@
         <v>4.2</v>
       </c>
       <c r="H201" s="9" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="I201" s="6"/>
     </row>
@@ -8960,7 +8960,7 @@
         <v>700</v>
       </c>
       <c r="D202" s="7" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="E202" s="8">
         <v>4.01</v>
@@ -8972,7 +8972,7 @@
         <v>4.5</v>
       </c>
       <c r="H202" s="9" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="I202" s="6"/>
     </row>
@@ -8987,7 +8987,7 @@
         <v>701</v>
       </c>
       <c r="D203" s="7" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E203" s="8">
         <v>3.81</v>
@@ -8999,7 +8999,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H203" s="9" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="I203" s="6"/>
     </row>
@@ -9014,7 +9014,7 @@
         <v>702</v>
       </c>
       <c r="D204" s="7" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E204" s="8">
         <v>3.54</v>
@@ -9026,7 +9026,7 @@
         <v>3.9</v>
       </c>
       <c r="H204" s="9" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="I204" s="6"/>
     </row>
@@ -9041,7 +9041,7 @@
         <v>703</v>
       </c>
       <c r="D205" s="7" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E205" s="8">
         <v>3.46</v>
@@ -9053,7 +9053,7 @@
         <v>4</v>
       </c>
       <c r="H205" s="9" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="I205" s="6"/>
     </row>
@@ -9068,7 +9068,7 @@
         <v>704</v>
       </c>
       <c r="D206" s="7" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E206" s="8">
         <v>3.56</v>
@@ -9080,7 +9080,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H206" s="9" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="I206" s="6"/>
     </row>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{260904B7-87FF-4D95-B3BC-F95709163C09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85D638E3-EDE8-4323-854F-4CC516E78E31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="727">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="777">
   <si>
     <t>No</t>
   </si>
@@ -2202,6 +2202,156 @@
   </si>
   <si>
     <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Επίσημη επανεκδοση της Music On Vinyl, περιορισμένης/αριθμημένης κοπής 2000 αντιτύπων σε κίτρινο ημιδιαφανές βινύλιο 180 γραμμαρίων (με το χαρακτηριστικό χρυσό hype sticker). Matrix / Runout (Side A): 10518 1A MOVLP 1243. Matrix / Runout (Side B): 10518 1B MOVLP 1243. Κοπή από την Record Industry.</t>
+  </si>
+  <si>
+    <t>Citadel (Galantia Part 1)</t>
+  </si>
+  <si>
+    <t>Book Of Changes</t>
+  </si>
+  <si>
+    <t>Wing Of The Owl (Galantia Part 2)</t>
+  </si>
+  <si>
+    <t>Cassini's Deadly Plunge</t>
+  </si>
+  <si>
+    <t>Under The Stars</t>
+  </si>
+  <si>
+    <t>Mountain</t>
+  </si>
+  <si>
+    <t>Eleven Years</t>
+  </si>
+  <si>
+    <t>Dionysus</t>
+  </si>
+  <si>
+    <t>Under The Stars (Reprise)</t>
+  </si>
+  <si>
+    <t>Tanith</t>
+  </si>
+  <si>
+    <t>In Another Time</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/28667458-Tanith-In-Another-Time</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/GmkiNcJZNUUNTb8yegokQUR_9CQmPwvUTBp8kvqqxLg/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI4NjY3/NDU4LTE3MDczMTgx/NTMtNjg2NS5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Επίσημη ευρωπαϊκή επανεκδοση του 2023 από τη Metal Blade Records, περιορισμένης κοπής 500 αντιτύπων σε mint green marbled βινύλιο. Φέρει hype sticker με βαθμολογία 8,5/10 από το Deaf Forever ("High-class 70s Heavy Rock"). Περιλαμβάνει αφίσα, ένθετο με στίχους και download card. Barcode (Sticker): 039841565683. Label Code: LC 6705. Rights Society: GEMA.</t>
+  </si>
+  <si>
+    <t>Metal Blade Records – 3984-15656-1 (Europe Reissue, 2023, Mint Green Marbled Vinyl)</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal, NWOBHM</t>
+  </si>
+  <si>
+    <t>Εξαιρετικό εναρκτήριο κομμάτι και η απόλυτη αιχμή του δόρατος του άλμπουμ. Τα διπλά κιθαριστικά θέματα (twin-lead guitars) θυμίζουν έντονα τη χρυσή εποχή των Thin Lizzy και των Wishbone Ash, ενώ το ρυθμικό δέσιμο και η ερμηνεία δημιουργούν μια επιβλητική 70s ατμόσφαιρα.</t>
+  </si>
+  <si>
+    <t>Πιο ρυθμικό και άμεσο, βασίζεται σε ένα κοφτερό, heavy rock riff. Ξεχωρίζει για τα υπέροχα, ισορροπημένα φωνητικά harmony lines ανάμεσα στον Russ Tippins και την Cindy Maynard, που δίνουν μια χαρακτηριστική μελωδική ζεστασιά.</t>
+  </si>
+  <si>
+    <t>Ένα mid-tempo κομμάτι με έντονο μυσταγωγικό και ταξιδιάρικο χαρακτήρα. Η ενορχήστρωση δίνει χώρο στις κιθάρες να αναπνεύσουν, αναδεικνύοντας την οργανική και φυσική χροιά της αναλογικής ηχογράφησης.</t>
+  </si>
+  <si>
+    <t>Οργανικό κομμάτι-σταθμός, χτισμένο γύρω από απαιτητικά, πολυεπίπεδα lead κιθαριστικά μέρη και στιβαρό, κοφτό drumming που αποδίδει άψογα τη retro heavy metal αισθητική της μπάντας.</t>
+  </si>
+  <si>
+    <t>Μια πιο νωχελική, ατμοσφαιρική σύνθεση που ακροβατεί ανάμεσα στο hard rock και τα blues. Το μπάσο κρατάει τον εσωτερικό πυρήνα του ρυθμού, ενώ η ερμηνεία προσδίδει μια μελαγχολική, νοσταλγική χροιά.</t>
+  </si>
+  <si>
+    <t>Βαρύτερο και πιο ευθύβολο ηχητικά, με doom/hard rock καταβολές. Εστιάζει σε έναν πιο συμπαγή, ογκώδη ήχο στα riffs, προσφέροντας μια ωμή,γειωμένη ενέργεια.</t>
+  </si>
+  <si>
+    <t>Από τις πιο ολοκληρωμένες συνθέσεις της δεύτερης πλευράς, με έξυπνες εναλλαγές δυναμικών, εκφραστικά φωνητικά και καθαρά, κοφτερά μελωδικά περάσματα στις κιθάρες.</t>
+  </si>
+  <si>
+    <t>Ζωντανό και ρυθμικό heavy metal κομμάτι με αρχαιοελληνικές αναφορές στον τίτλο του. Ξεχωρίζει για την πηγαία,νεανική ενέργεια των 70s και το ανεβαστικό του tempo.</t>
+  </si>
+  <si>
+    <t>Σύντομος ακουστικός επίλογος που λειτουργεί ως οργανική/ακουστική ανάσα, ρίχνοντας τους τόνους και αφήνοντας μια γλυκιά, μινιμαλιστική επίγευση στο τέλος του δίσκου.</t>
+  </si>
+  <si>
+    <t>Acoustic, Outro</t>
+  </si>
+  <si>
+    <t>Heavy Metal</t>
+  </si>
+  <si>
+    <t>Voyage</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/hWgshp3_gNHo6LjYX1IhPpJz8zycl9L6kXI4tiITIqs/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI2ODU3/MzMxLTE2ODIyNjcw/ODEtNDcwOS5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/26857331-Tanith-Voyage</t>
+  </si>
+  <si>
+    <t>Snow Tiger</t>
+  </si>
+  <si>
+    <t>Falling Wizard</t>
+  </si>
+  <si>
+    <t>Olympus By Dawn</t>
+  </si>
+  <si>
+    <t>Architects Of Time</t>
+  </si>
+  <si>
+    <t>Adrasteia</t>
+  </si>
+  <si>
+    <t>Mother Of Exile</t>
+  </si>
+  <si>
+    <t>Seven Moons (Galantia Pt. 2)</t>
+  </si>
+  <si>
+    <t>Flame</t>
+  </si>
+  <si>
+    <t>Never Look Back</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Επίσημη ευρωπαϊκή κυκλοφορία του 2023 από τη Metal Blade Records σε μαύρο βινύλιο 180 γραμμαρίων. Περιλαμβάνει mp3 download card. Φέρει χαρακτηριστικό hype sticker που δηλώνει: "This is a fully analogue product (The album was recorded and mastered on 24 track analogue tape and has never been digitized from recording to pressing)". Barcode: 039841604412.</t>
+  </si>
+  <si>
+    <t>Εξαιρετικό εναρκτήριο κομμάτι με τεράστια 70s ενέργεια. Τα διπλά κιθαριστικά θέματα (twin-lead guitars) των Russ Tippins και Charles Newton αποδίδονται με υποδειγματική διαύγεια χάρη στην 24-track αναλογική ταινία, δίνοντας αμέσως τον τόνο της κόπιας.</t>
+  </si>
+  <si>
+    <t>Πιο σκοτεινό και εσωτερικό track, με στιβαρό, γήινο ρυθμικό υπόβαθρο από τον Keith Robinson στα τύμπανα και μια χαρακτηριστική vintage ατμόσφαιρα που θυμίζει πρώιμο doom/hard rock.</t>
+  </si>
+  <si>
+    <t>Από τα απόλυτα highlights του δίσκου. Ξεχωρίζει για την υψηλή μελωδική του ανάπτυξη, τις εξαιρετικές φωνητικές αρμονίες ανάμεσα σε Cindy Maynard και Russ Tippins και την οργανική ζεστασιά στη μίξη.</t>
+  </si>
+  <si>
+    <t>Ρυθμικό, πολυεπίπεδο κομμάτι με προσεγμένη ενορχηστρωτική δομή, όπου το μπάσο της Cindy Maynard κρατάει τον κύριο όγκο και δένει αρμονικά με τις κιθάρες.</t>
+  </si>
+  <si>
+    <t>Ατμοσφαιρικό mid-tempo με μυσταγωγική και ταξιδιάρικη διάθεση. Δίνει χώρο στα όργανα να αναπνεύσουν, αναδεικνύοντας τα φυσικά, μη ψηφιακά transients του ήχου.</t>
+  </si>
+  <si>
+    <t>Μια πιο εσωτερική, αφηγηματική σύνθεση που κινείται σε κλασικές 70s φόρμες, δίνοντας έμφαση στην εκφραστική ερμηνεία των φωνητικών.</t>
+  </si>
+  <si>
+    <t>Συνέχεια της θεματικής σειράς Galantia, με πλούσιες αρμονίες στις κιθάρες, ωραίες εναλλαγές δυναμικών και έντονη επική, νοσταλγική αύρα.</t>
+  </si>
+  <si>
+    <t>Γρήγορο και κοφτό heavy metal κομμάτι, πιο άμεσο και ευθύβολο, με γρήγορα riffs και έντονη συναυλιακή ενέργεια.</t>
+  </si>
+  <si>
+    <t>Επιβλητικό κλείσιμο άλμπουμ. Διαθέτει πλούσιο οργανικό φινάλε, εξαιρετική στερεοφωνική εικόνα και αποδεικνύει περίφημα τα οφέλη μιας καθαρόαιμης all-analog παραγωγής.</t>
+  </si>
+  <si>
+    <t>Metal Blade Records – 3984-16044-1 (Europe, 2023, 180g Black Vinyl)</t>
   </si>
 </sst>
 </file>
@@ -2630,7 +2780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -3412,6 +3562,70 @@
       </c>
       <c r="J24" s="11" t="s">
         <v>706</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+      <c r="A25" s="6">
+        <v>28667458</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>736</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>737</v>
+      </c>
+      <c r="D25" s="6">
+        <v>2019</v>
+      </c>
+      <c r="E25" s="10">
+        <v>3.49</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>742</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>740</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>741</v>
+      </c>
+      <c r="I25" s="11" t="s">
+        <v>738</v>
+      </c>
+      <c r="J25" s="11" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+      <c r="A26" s="6">
+        <v>26857331</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>736</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>754</v>
+      </c>
+      <c r="D26" s="6">
+        <v>2023</v>
+      </c>
+      <c r="E26" s="10">
+        <v>3.48</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>742</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>766</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>776</v>
+      </c>
+      <c r="I26" s="11" t="s">
+        <v>756</v>
+      </c>
+      <c r="J26" s="11" t="s">
+        <v>755</v>
       </c>
     </row>
   </sheetData>
@@ -3460,6 +3674,10 @@
     <hyperlink ref="J23" r:id="rId42" xr:uid="{3575A396-31E6-40CA-9AE5-93286E535880}"/>
     <hyperlink ref="J24" r:id="rId43" xr:uid="{6E0506A5-8A8E-4A23-BB64-838F694F517F}"/>
     <hyperlink ref="I24" r:id="rId44" xr:uid="{0D6B3B88-F335-416B-8E1F-865D3DD5E2F0}"/>
+    <hyperlink ref="I25" r:id="rId45" xr:uid="{DF641E30-EFBA-494C-88DD-76EF1F14F9A5}"/>
+    <hyperlink ref="J25" r:id="rId46" xr:uid="{B55C32BD-FFA8-408C-863E-BCB03FB8FFD1}"/>
+    <hyperlink ref="J26" r:id="rId47" xr:uid="{2DFEA5CA-9CDD-4810-92E5-A269F3F622EB}"/>
+    <hyperlink ref="I26" r:id="rId48" xr:uid="{FF32A1D1-1E55-466C-95A9-BFC960641343}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3467,7 +3685,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I206"/>
+  <dimension ref="A1:I224"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="3" bestFit="1" customWidth="1"/>
@@ -9084,6 +9302,492 @@
       </c>
       <c r="I206" s="6"/>
     </row>
+    <row r="207" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A207" s="6">
+        <v>28667458</v>
+      </c>
+      <c r="B207" s="6">
+        <v>1</v>
+      </c>
+      <c r="C207" s="7" t="s">
+        <v>727</v>
+      </c>
+      <c r="D207" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E207" s="8">
+        <v>3.91</v>
+      </c>
+      <c r="F207" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G207" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="H207" s="9" t="s">
+        <v>743</v>
+      </c>
+      <c r="I207" s="6"/>
+    </row>
+    <row r="208" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A208" s="6">
+        <v>28667458</v>
+      </c>
+      <c r="B208" s="6">
+        <v>2</v>
+      </c>
+      <c r="C208" s="7" t="s">
+        <v>728</v>
+      </c>
+      <c r="D208" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E208" s="8">
+        <v>3.61</v>
+      </c>
+      <c r="F208" s="8">
+        <v>4</v>
+      </c>
+      <c r="G208" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="H208" s="9" t="s">
+        <v>744</v>
+      </c>
+      <c r="I208" s="6"/>
+    </row>
+    <row r="209" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A209" s="6">
+        <v>28667458</v>
+      </c>
+      <c r="B209" s="6">
+        <v>3</v>
+      </c>
+      <c r="C209" s="7" t="s">
+        <v>729</v>
+      </c>
+      <c r="D209" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="E209" s="8">
+        <v>3.55</v>
+      </c>
+      <c r="F209" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="G209" s="8">
+        <v>4</v>
+      </c>
+      <c r="H209" s="9" t="s">
+        <v>745</v>
+      </c>
+      <c r="I209" s="6"/>
+    </row>
+    <row r="210" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A210" s="6">
+        <v>28667458</v>
+      </c>
+      <c r="B210" s="6">
+        <v>4</v>
+      </c>
+      <c r="C210" s="7" t="s">
+        <v>730</v>
+      </c>
+      <c r="D210" s="7" t="s">
+        <v>753</v>
+      </c>
+      <c r="E210" s="8">
+        <v>3.54</v>
+      </c>
+      <c r="F210" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="G210" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="H210" s="9" t="s">
+        <v>746</v>
+      </c>
+      <c r="I210" s="6"/>
+    </row>
+    <row r="211" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A211" s="6">
+        <v>28667458</v>
+      </c>
+      <c r="B211" s="6">
+        <v>5</v>
+      </c>
+      <c r="C211" s="7" t="s">
+        <v>731</v>
+      </c>
+      <c r="D211" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="E211" s="8">
+        <v>3.46</v>
+      </c>
+      <c r="F211" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="G211" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="H211" s="9" t="s">
+        <v>747</v>
+      </c>
+      <c r="I211" s="6"/>
+    </row>
+    <row r="212" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A212" s="6">
+        <v>28667458</v>
+      </c>
+      <c r="B212" s="6">
+        <v>6</v>
+      </c>
+      <c r="C212" s="7" t="s">
+        <v>732</v>
+      </c>
+      <c r="D212" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E212" s="8">
+        <v>3.41</v>
+      </c>
+      <c r="F212" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="G212" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="H212" s="9" t="s">
+        <v>748</v>
+      </c>
+      <c r="I212" s="6"/>
+    </row>
+    <row r="213" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A213" s="6">
+        <v>28667458</v>
+      </c>
+      <c r="B213" s="6">
+        <v>7</v>
+      </c>
+      <c r="C213" s="7" t="s">
+        <v>733</v>
+      </c>
+      <c r="D213" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="E213" s="8">
+        <v>3.61</v>
+      </c>
+      <c r="F213" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G213" s="8">
+        <v>4</v>
+      </c>
+      <c r="H213" s="9" t="s">
+        <v>749</v>
+      </c>
+      <c r="I213" s="6"/>
+    </row>
+    <row r="214" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A214" s="6">
+        <v>28667458</v>
+      </c>
+      <c r="B214" s="6">
+        <v>8</v>
+      </c>
+      <c r="C214" s="7" t="s">
+        <v>734</v>
+      </c>
+      <c r="D214" s="7" t="s">
+        <v>753</v>
+      </c>
+      <c r="E214" s="8">
+        <v>3.65</v>
+      </c>
+      <c r="F214" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="G214" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H214" s="9" t="s">
+        <v>750</v>
+      </c>
+      <c r="I214" s="6"/>
+    </row>
+    <row r="215" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A215" s="6">
+        <v>28667458</v>
+      </c>
+      <c r="B215" s="6">
+        <v>9</v>
+      </c>
+      <c r="C215" s="7" t="s">
+        <v>735</v>
+      </c>
+      <c r="D215" s="7" t="s">
+        <v>752</v>
+      </c>
+      <c r="E215" s="8">
+        <v>3.43</v>
+      </c>
+      <c r="F215" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="G215" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="H215" s="9" t="s">
+        <v>751</v>
+      </c>
+      <c r="I215" s="6"/>
+    </row>
+    <row r="216" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A216" s="6">
+        <v>26857331</v>
+      </c>
+      <c r="B216" s="6">
+        <v>1</v>
+      </c>
+      <c r="C216" s="7" t="s">
+        <v>757</v>
+      </c>
+      <c r="D216" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E216" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="F216" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G216" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="H216" s="9" t="s">
+        <v>767</v>
+      </c>
+      <c r="I216" s="6"/>
+    </row>
+    <row r="217" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A217" s="6">
+        <v>26857331</v>
+      </c>
+      <c r="B217" s="6">
+        <v>2</v>
+      </c>
+      <c r="C217" s="7" t="s">
+        <v>758</v>
+      </c>
+      <c r="D217" s="7" t="s">
+        <v>753</v>
+      </c>
+      <c r="E217" s="8">
+        <v>3.26</v>
+      </c>
+      <c r="F217" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="G217" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="H217" s="9" t="s">
+        <v>768</v>
+      </c>
+      <c r="I217" s="6"/>
+    </row>
+    <row r="218" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A218" s="6">
+        <v>26857331</v>
+      </c>
+      <c r="B218" s="6">
+        <v>3</v>
+      </c>
+      <c r="C218" s="7" t="s">
+        <v>759</v>
+      </c>
+      <c r="D218" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="E218" s="8">
+        <v>3.81</v>
+      </c>
+      <c r="F218" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="G218" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="H218" s="9" t="s">
+        <v>769</v>
+      </c>
+      <c r="I218" s="6"/>
+    </row>
+    <row r="219" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A219" s="6">
+        <v>26857331</v>
+      </c>
+      <c r="B219" s="6">
+        <v>4</v>
+      </c>
+      <c r="C219" s="7" t="s">
+        <v>760</v>
+      </c>
+      <c r="D219" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E219" s="8">
+        <v>3.45</v>
+      </c>
+      <c r="F219" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="G219" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="H219" s="9" t="s">
+        <v>770</v>
+      </c>
+      <c r="I219" s="6"/>
+    </row>
+    <row r="220" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A220" s="6">
+        <v>26857331</v>
+      </c>
+      <c r="B220" s="6">
+        <v>5</v>
+      </c>
+      <c r="C220" s="7" t="s">
+        <v>761</v>
+      </c>
+      <c r="D220" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="E220" s="8">
+        <v>3.53</v>
+      </c>
+      <c r="F220" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="G220" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="H220" s="9" t="s">
+        <v>771</v>
+      </c>
+      <c r="I220" s="6"/>
+    </row>
+    <row r="221" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A221" s="6">
+        <v>26857331</v>
+      </c>
+      <c r="B221" s="6">
+        <v>6</v>
+      </c>
+      <c r="C221" s="7" t="s">
+        <v>762</v>
+      </c>
+      <c r="D221" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E221" s="8">
+        <v>3.19</v>
+      </c>
+      <c r="F221" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="G221" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="H221" s="9" t="s">
+        <v>772</v>
+      </c>
+      <c r="I221" s="6"/>
+    </row>
+    <row r="222" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A222" s="6">
+        <v>26857331</v>
+      </c>
+      <c r="B222" s="6">
+        <v>7</v>
+      </c>
+      <c r="C222" s="7" t="s">
+        <v>763</v>
+      </c>
+      <c r="D222" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="E222" s="8">
+        <v>3.41</v>
+      </c>
+      <c r="F222" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="G222" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="H222" s="9" t="s">
+        <v>773</v>
+      </c>
+      <c r="I222" s="6"/>
+    </row>
+    <row r="223" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A223" s="6">
+        <v>26857331</v>
+      </c>
+      <c r="B223" s="6">
+        <v>8</v>
+      </c>
+      <c r="C223" s="7" t="s">
+        <v>764</v>
+      </c>
+      <c r="D223" s="7" t="s">
+        <v>753</v>
+      </c>
+      <c r="E223" s="8">
+        <v>3.14</v>
+      </c>
+      <c r="F223" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="G223" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="H223" s="9" t="s">
+        <v>774</v>
+      </c>
+      <c r="I223" s="6"/>
+    </row>
+    <row r="224" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A224" s="6">
+        <v>26857331</v>
+      </c>
+      <c r="B224" s="6">
+        <v>9</v>
+      </c>
+      <c r="C224" s="7" t="s">
+        <v>765</v>
+      </c>
+      <c r="D224" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="E224" s="8">
+        <v>3.52</v>
+      </c>
+      <c r="F224" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="G224" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H224" s="9" t="s">
+        <v>775</v>
+      </c>
+      <c r="I224" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85D638E3-EDE8-4323-854F-4CC516E78E31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D932785-6142-452D-81FD-D0349D7B7E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="777">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="958" uniqueCount="823">
   <si>
     <t>No</t>
   </si>
@@ -2352,6 +2352,144 @@
   </si>
   <si>
     <t>Metal Blade Records – 3984-16044-1 (Europe, 2023, 180g Black Vinyl)</t>
+  </si>
+  <si>
+    <t>Sad Mary</t>
+  </si>
+  <si>
+    <t>Friend</t>
+  </si>
+  <si>
+    <t>Love 74</t>
+  </si>
+  <si>
+    <t>Mad Dogs &amp; Englishmen</t>
+  </si>
+  <si>
+    <t>Things Are Getting Better</t>
+  </si>
+  <si>
+    <t>Ode To John Law</t>
+  </si>
+  <si>
+    <t>Danger Zone</t>
+  </si>
+  <si>
+    <t>Stone The Crows</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/22420804-Stone-The-Crows-Ode-To-John-Law</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/PfAGvsLDu6qrK7a2mTje-Qi1P_FaXYVSpJdDMX52IM0/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTIyNDIw/ODA0LTE2NDY2NjQ0/NzEtMzE1OS5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Repertoire Records – V333, Repertoire Records – REP2440 (UK, 2022, Reissue, Remastered, Gatefold, 180g)</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Εξαιρετική ευρωπαϊκή επανεκδοση του 2022 από τη Repertoire Records σε βινύλιο 180 γραμμαρίων μέσα σε gatefold θήκη με ένθετο και Hype Sticker. Η ηχογράφηση είναι stereo, αποκατεστημένη και remastered από τον EROC. Περιλαμβάνει liner notes από τον Chris Welch με συνδέσμους από πρώην μέλη της μπάντας. Barcode: 4009910244012.</t>
+  </si>
+  <si>
+    <t>Blues Rock, Hard Rock, Classic Rock, British Blues</t>
+  </si>
+  <si>
+    <t>Εξαιρετικό εναρκτήριο κομμάτι με τεράστια ενέργεια. Η φωνητική ερμηνεία της Maggie Bell είναι καθηλωτική, υποστηριζόμενη από τα κοφτερά κιθαριστικά περάσματα του Les Harvey και το στιβαρό ρυθμικό δέσιμο.</t>
+  </si>
+  <si>
+    <t>Classic Rock, Blues Rock</t>
+  </si>
+  <si>
+    <t>Συναισθηματική σύνθεση με έντονα blues στοιχεία, όπου η εσωτερική μελωδία αναδεικνύεται υποδειγματικά από την καθαρή αναλογική αποκατάσταση του mastering.</t>
+  </si>
+  <si>
+    <t>Πιο σύντομο, ρυθμικό και άμεσο κομμάτι, βασισμένο σε ένα κοφτό riff που δίνει χώρο στα πλήκτρα του John McGinniss να συμπληρώσουν το ηχητικό φάσμα.</t>
+  </si>
+  <si>
+    <t>Blues Rock</t>
+  </si>
+  <si>
+    <t>Εσωτερικό blues κομμάτι με έμφαση στον αυτοσχεδιασμό και την αλληλεπίδραση των οργάνων, θυμίζοντας κλασικές live jam ατμόσφαιρες των αρχών των 70s.</t>
+  </si>
+  <si>
+    <t>Hard Rock, British Blues</t>
+  </si>
+  <si>
+    <t>Το ομότιτλο κομμάτι-σταθμός του δίσκου, χτισμένο γύror από απαιτητικές ενορχηστρώσεις και στιβαρή ερμηνεία που αποδίδει φόρο τιμής στις blues καταβολές τους.</t>
+  </si>
+  <si>
+    <t>Επιβλητικό κλείσιμο με τεράστιο δυναμικό εύρος, εξαιρετική διαύγεια στα τύμπανα και κορυφαία κιθαριστική κορύφωση που δικαιώνει απόλυτα την 180g gatefold επανεκδοση.</t>
+  </si>
+  <si>
+    <t>Το απόλυτο διαμάντι του δίσκου. Ένας μνημειώδης blues rock ύμνος που συνδυάζει την ωμή, σπαρακτική ερμηνεία της Maggie Bell με τα εκρηκτικά, κοφτερά κιθαριστικά solos του Les Harvey. Η ενορχήστρωση αναπνέει υποδειγματικά στην 180g επανεκδοση, προσφέροντας τεράστιο δυναμικό εύρος, βαθιά, φυσικά μπάσα και ασύγκριτη 70s ατμόσφαιρα.</t>
+  </si>
+  <si>
+    <t>Starvation</t>
+  </si>
+  <si>
+    <t>Queen Of The Universe</t>
+  </si>
+  <si>
+    <t>Every Dream Comes To An End</t>
+  </si>
+  <si>
+    <t>The Bride</t>
+  </si>
+  <si>
+    <t>Killer</t>
+  </si>
+  <si>
+    <t>A Day In Heaven</t>
+  </si>
+  <si>
+    <t>Time Of Pain</t>
+  </si>
+  <si>
+    <t>Mountains</t>
+  </si>
+  <si>
+    <t>Phos</t>
+  </si>
+  <si>
+    <t>Socrates</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/31880233-Socrates-Phos</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/d1JGvfZD7DGPFx-sm-RXUcwUxrrOER7S7WLXgdmDfLo/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTMxODgw/MjMzLTE3Mjc3ODQ1/NjEtMTI2Ni5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">**Ιστορικό Πλαίσιο &amp; Παραγωγή:** </t>
+  </si>
+  <si>
+    <t>Cobalt Music (2) – 520699038269 (Greece, 2024, LP, Album, Limited Edition, Numbered, Reissue, Stereo)</t>
+  </si>
+  <si>
+    <t>Εναρκτήριο λάκτισμα τεράστιας δυναμικής που θέτει αμέσως τον τόνο του άλμπουμ. Η κιθαριστική δουλειά του Γιάννη Σπάθα διαθέτει μια κοφτερή, κομψή αγριότητα, ενώ η ατμόσφαιρα που χτίζουν τα πλήκτρα του Vangelis προσθέτει μια συμφωνική, επική διάσταση. Το κομμάτι ισορροπεί υποδειγματικά ανάμεσα στο σκληρό ροκ και την προοδευτική δομή, με εξαιρετική εναλλαγή εντάσεων και αμείωτο ρυθμό.</t>
+  </si>
+  <si>
+    <t>Ένα από τα απόλυτα αριστουργήματα του ελληνικού progressive rock, παγκόσμιας κλάσης. Το κομμάτι ξεχωρίζει για τις πολυεπίπεδες ενορχηστρώσεις, όπου τα διαστημικά, εκφραστικά πλήκτρα συναντούν τα virtuoso περάσματα της κιθάρας. Η εσωτερική του δομή χτίζει σταδιακά μια δραματική κορύφωση, αποδεικνύοντας τη μοναδική χημεία της μπάντας και την παραγωγική ιδιοφυΐα του Παπαθανασίου.</t>
+  </si>
+  <si>
+    <t>Το μνημειώδες, επικό κλείσιμο του δίσκου που αφήνει τεράστιο ηχητικό αποτύπωμα. Πρόκειται για ένα true prog έπος, γεμάτο ατμοσφαιρικά τοπία, απαιτητικές αλλαγές μέτρων και έναν Σπάθα σε απόλυτη φόρμα να δίνει ρεσιτάλ στο φινάλε. Στο βινύλιο, η συγκεκριμένη σύνθεση αναδεικνύει το μέγιστο δυναμικό εύρος της κοπής, κλείνοντας το άλμπουμ με τον πιο μεγαλειώδη και συγκλονιστικό τρόπο.</t>
+  </si>
+  <si>
+    <t>Prog Rock, Symphonic Rock</t>
+  </si>
+  <si>
+    <t>Blues-rock καταβολές με σύγχρονη για την εποχή progressive ματιά και εξαιρετικό δέσιμο μπάσου-κιθάρας από Τουρκογιώργη και Σπάθα.</t>
+  </si>
+  <si>
+    <t>Ταξιδιάρικο και πολυδιάστατο, αποδεικνύει την ικανότητα των Socrates να παντρεύουν το ελληνικό συναίσθημα με το βρετανικό prog rock.</t>
+  </si>
+  <si>
+    <t>Γρήγορο, ευθύβολο και εκρηκτικό κομμάτι σύντομης διάρκειας, που λειτουργεί σαν "έκρηξη" ενέργειας μέσα στο άλμπουμ.</t>
+  </si>
+  <si>
+    <t>Σύνθεση με έντονα ατμοσφαιρικά στοιχεία και λυρισμό, όπου τα πλήκτρα του Παπαθανασίου δημιουργούν ένα μαγικό, διαστημικό χαλί κάτω από τις κιθάρες.</t>
+  </si>
+  <si>
+    <t>Πιο κοφτό και ρυθμικό, αναδεικνύει το στιβαρό παίξιμο του Γιώργου Τρανταλίδη στα τύμπανα και τη χαρακτηριστική blues-rock κληρονομιά της μπάντας.</t>
   </si>
 </sst>
 </file>
@@ -2390,7 +2528,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="8"/>
       <color theme="10"/>
       <name val="Tahoma"/>
@@ -2780,7 +2917,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -3626,6 +3763,68 @@
       </c>
       <c r="J26" s="11" t="s">
         <v>755</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+      <c r="A27" s="6">
+        <v>22420804</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>784</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>782</v>
+      </c>
+      <c r="D27" s="6">
+        <v>1970</v>
+      </c>
+      <c r="E27" s="10">
+        <v>3.66</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>789</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>788</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>787</v>
+      </c>
+      <c r="I27" s="11" t="s">
+        <v>785</v>
+      </c>
+      <c r="J27" s="11" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A28" s="6">
+        <v>31880233</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>809</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>808</v>
+      </c>
+      <c r="D28" s="6">
+        <v>1976</v>
+      </c>
+      <c r="E28" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="F28" s="9"/>
+      <c r="G28" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>813</v>
+      </c>
+      <c r="I28" s="11" t="s">
+        <v>810</v>
+      </c>
+      <c r="J28" s="11" t="s">
+        <v>811</v>
       </c>
     </row>
   </sheetData>
@@ -3678,6 +3877,10 @@
     <hyperlink ref="J25" r:id="rId46" xr:uid="{B55C32BD-FFA8-408C-863E-BCB03FB8FFD1}"/>
     <hyperlink ref="J26" r:id="rId47" xr:uid="{2DFEA5CA-9CDD-4810-92E5-A269F3F622EB}"/>
     <hyperlink ref="I26" r:id="rId48" xr:uid="{FF32A1D1-1E55-466C-95A9-BFC960641343}"/>
+    <hyperlink ref="I27" r:id="rId49" xr:uid="{87C4E708-9703-429B-AD5F-DAAD8F0949D0}"/>
+    <hyperlink ref="J27" r:id="rId50" xr:uid="{643189D3-04E5-4DA0-A6BD-DA1BBD36408B}"/>
+    <hyperlink ref="I28" r:id="rId51" xr:uid="{B401C0DB-140A-4490-819B-6D614FC8CCEE}"/>
+    <hyperlink ref="J28" r:id="rId52" xr:uid="{E3F5F8FC-7DEE-4BE0-BFCA-A5C70ADD094D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3685,7 +3888,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I224"/>
+  <dimension ref="A1:I239"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="3" bestFit="1" customWidth="1"/>
@@ -9788,6 +9991,419 @@
       </c>
       <c r="I224" s="6"/>
     </row>
+    <row r="225" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A225" s="6">
+        <v>22420804</v>
+      </c>
+      <c r="B225" s="6">
+        <v>1</v>
+      </c>
+      <c r="C225" s="7" t="s">
+        <v>777</v>
+      </c>
+      <c r="D225" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="E225" s="8">
+        <v>3.63</v>
+      </c>
+      <c r="F225" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="G225" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H225" s="9" t="s">
+        <v>790</v>
+      </c>
+      <c r="I225" s="6"/>
+    </row>
+    <row r="226" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A226" s="6">
+        <v>22420804</v>
+      </c>
+      <c r="B226" s="6">
+        <v>2</v>
+      </c>
+      <c r="C226" s="7" t="s">
+        <v>778</v>
+      </c>
+      <c r="D226" s="7" t="s">
+        <v>791</v>
+      </c>
+      <c r="E226" s="8">
+        <v>3.66</v>
+      </c>
+      <c r="F226" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G226" s="8">
+        <v>4</v>
+      </c>
+      <c r="H226" s="9" t="s">
+        <v>792</v>
+      </c>
+      <c r="I226" s="6"/>
+    </row>
+    <row r="227" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A227" s="6">
+        <v>22420804</v>
+      </c>
+      <c r="B227" s="6">
+        <v>3</v>
+      </c>
+      <c r="C227" s="7" t="s">
+        <v>779</v>
+      </c>
+      <c r="D227" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="E227" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="F227" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G227" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="H227" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="I227" s="6" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A228" s="6">
+        <v>22420804</v>
+      </c>
+      <c r="B228" s="6">
+        <v>4</v>
+      </c>
+      <c r="C228" s="7" t="s">
+        <v>780</v>
+      </c>
+      <c r="D228" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="E228" s="8">
+        <v>3.49</v>
+      </c>
+      <c r="F228" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="G228" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="H228" s="9" t="s">
+        <v>793</v>
+      </c>
+      <c r="I228" s="6"/>
+    </row>
+    <row r="229" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A229" s="6">
+        <v>22420804</v>
+      </c>
+      <c r="B229" s="6">
+        <v>5</v>
+      </c>
+      <c r="C229" s="7" t="s">
+        <v>781</v>
+      </c>
+      <c r="D229" s="7" t="s">
+        <v>794</v>
+      </c>
+      <c r="E229" s="8">
+        <v>3.29</v>
+      </c>
+      <c r="F229" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="G229" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="H229" s="9" t="s">
+        <v>795</v>
+      </c>
+      <c r="I229" s="6"/>
+    </row>
+    <row r="230" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A230" s="6">
+        <v>22420804</v>
+      </c>
+      <c r="B230" s="6">
+        <v>6</v>
+      </c>
+      <c r="C230" s="7" t="s">
+        <v>782</v>
+      </c>
+      <c r="D230" s="7" t="s">
+        <v>796</v>
+      </c>
+      <c r="E230" s="8">
+        <v>3.45</v>
+      </c>
+      <c r="F230" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="G230" s="8">
+        <v>4</v>
+      </c>
+      <c r="H230" s="9" t="s">
+        <v>797</v>
+      </c>
+      <c r="I230" s="6"/>
+    </row>
+    <row r="231" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A231" s="6">
+        <v>22420804</v>
+      </c>
+      <c r="B231" s="6">
+        <v>7</v>
+      </c>
+      <c r="C231" s="7" t="s">
+        <v>783</v>
+      </c>
+      <c r="D231" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="E231" s="8">
+        <v>3.51</v>
+      </c>
+      <c r="F231" s="8">
+        <v>4</v>
+      </c>
+      <c r="G231" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H231" s="9" t="s">
+        <v>798</v>
+      </c>
+      <c r="I231" s="6"/>
+    </row>
+    <row r="232" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A232" s="6">
+        <v>31880233</v>
+      </c>
+      <c r="B232" s="6">
+        <v>1</v>
+      </c>
+      <c r="C232" s="7" t="s">
+        <v>800</v>
+      </c>
+      <c r="D232" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="E232" s="8">
+        <v>3.76</v>
+      </c>
+      <c r="F232" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="G232" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="H232" s="9" t="s">
+        <v>814</v>
+      </c>
+      <c r="I232" s="6" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A233" s="6">
+        <v>31880233</v>
+      </c>
+      <c r="B233" s="6">
+        <v>2</v>
+      </c>
+      <c r="C233" s="7" t="s">
+        <v>801</v>
+      </c>
+      <c r="D233" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="E233" s="8">
+        <v>3.65</v>
+      </c>
+      <c r="F233" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="G233" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H233" s="9" t="s">
+        <v>815</v>
+      </c>
+      <c r="I233" s="6" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A234" s="6">
+        <v>31880233</v>
+      </c>
+      <c r="B234" s="6">
+        <v>3</v>
+      </c>
+      <c r="C234" s="7" t="s">
+        <v>802</v>
+      </c>
+      <c r="D234" s="7" t="s">
+        <v>817</v>
+      </c>
+      <c r="E234" s="8">
+        <v>3.52</v>
+      </c>
+      <c r="F234" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G234" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H234" s="9" t="s">
+        <v>821</v>
+      </c>
+      <c r="I234" s="6"/>
+    </row>
+    <row r="235" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A235" s="6">
+        <v>31880233</v>
+      </c>
+      <c r="B235" s="6">
+        <v>4</v>
+      </c>
+      <c r="C235" s="7" t="s">
+        <v>803</v>
+      </c>
+      <c r="D235" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="E235" s="8">
+        <v>3.41</v>
+      </c>
+      <c r="F235" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="G235" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="H235" s="9" t="s">
+        <v>822</v>
+      </c>
+      <c r="I235" s="6"/>
+    </row>
+    <row r="236" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A236" s="6">
+        <v>31880233</v>
+      </c>
+      <c r="B236" s="6">
+        <v>5</v>
+      </c>
+      <c r="C236" s="7" t="s">
+        <v>804</v>
+      </c>
+      <c r="D236" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="E236" s="8">
+        <v>3.68</v>
+      </c>
+      <c r="F236" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="G236" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="H236" s="9" t="s">
+        <v>820</v>
+      </c>
+      <c r="I236" s="6"/>
+    </row>
+    <row r="237" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A237" s="6">
+        <v>31880233</v>
+      </c>
+      <c r="B237" s="6">
+        <v>6</v>
+      </c>
+      <c r="C237" s="7" t="s">
+        <v>805</v>
+      </c>
+      <c r="D237" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="E237" s="8">
+        <v>3.62</v>
+      </c>
+      <c r="F237" s="8">
+        <v>4</v>
+      </c>
+      <c r="G237" s="8">
+        <v>4</v>
+      </c>
+      <c r="H237" s="9" t="s">
+        <v>819</v>
+      </c>
+      <c r="I237" s="6"/>
+    </row>
+    <row r="238" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A238" s="6">
+        <v>31880233</v>
+      </c>
+      <c r="B238" s="6">
+        <v>7</v>
+      </c>
+      <c r="C238" s="7" t="s">
+        <v>806</v>
+      </c>
+      <c r="D238" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="E238" s="8">
+        <v>3.58</v>
+      </c>
+      <c r="F238" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="G238" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="H238" s="9" t="s">
+        <v>818</v>
+      </c>
+      <c r="I238" s="6"/>
+    </row>
+    <row r="239" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A239" s="6">
+        <v>31880233</v>
+      </c>
+      <c r="B239" s="6">
+        <v>8</v>
+      </c>
+      <c r="C239" s="7" t="s">
+        <v>807</v>
+      </c>
+      <c r="D239" s="7" t="s">
+        <v>817</v>
+      </c>
+      <c r="E239" s="8">
+        <v>3.45</v>
+      </c>
+      <c r="F239" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G239" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="H239" s="9" t="s">
+        <v>816</v>
+      </c>
+      <c r="I239" s="6" t="s">
+        <v>313</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D932785-6142-452D-81FD-D0349D7B7E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{651896EA-F54A-478C-A24C-729CDCF3CA5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="958" uniqueCount="823">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="859">
   <si>
     <t>No</t>
   </si>
@@ -2459,9 +2459,6 @@
     <t>https://i.discogs.com/d1JGvfZD7DGPFx-sm-RXUcwUxrrOER7S7WLXgdmDfLo/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTMxODgw/MjMzLTE3Mjc3ODQ1/NjEtMTI2Ni5qcGVn.jpeg</t>
   </si>
   <si>
-    <t xml:space="preserve">**Ιστορικό Πλαίσιο &amp; Παραγωγή:** </t>
-  </si>
-  <si>
     <t>Cobalt Music (2) – 520699038269 (Greece, 2024, LP, Album, Limited Edition, Numbered, Reissue, Stereo)</t>
   </si>
   <si>
@@ -2490,6 +2487,117 @@
   </si>
   <si>
     <t>Πιο κοφτό και ρυθμικό, αναδεικνύει το στιβαρό παίξιμο του Γιώργου Τρανταλίδη στα τύμπανα και τη χαρακτηριστική blues-rock κληρονομιά της μπάντας.</t>
+  </si>
+  <si>
+    <t>The Situation</t>
+  </si>
+  <si>
+    <t>This Feeling</t>
+  </si>
+  <si>
+    <t>LA Skip</t>
+  </si>
+  <si>
+    <t>Can't Seem To Do Much About It</t>
+  </si>
+  <si>
+    <t>Crazy Situation Blues</t>
+  </si>
+  <si>
+    <t>Blues In My Reflection</t>
+  </si>
+  <si>
+    <t>Why Do I Still Have The Blues</t>
+  </si>
+  <si>
+    <t>You Can't Take It With You</t>
+  </si>
+  <si>
+    <t>Migration</t>
+  </si>
+  <si>
+    <t>The Lying Game</t>
+  </si>
+  <si>
+    <t>Hard Blues</t>
+  </si>
+  <si>
+    <t>I Can't Imagine</t>
+  </si>
+  <si>
+    <t>Snowy White &amp; The White Flames</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Αριθμημένη περιορισμένη έκδοση 500 αντιτύπων από την Cobalt Music (2024). Αποτελεί μια πολυαναμενόμενη εγχώρια επανεκδοση του ιστορικού άλμπουμ του 1976, με παραγωγό τον Βαγγέλη Παπαθανασίου (Vangelis), ο οποίος συμμετέχει και στα πλήκτρα. Barcode: 520699038269.</t>
+  </si>
+  <si>
+    <t>Prog Rock, Symphonic Rock, Hard Rock, Art Rock</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/31700342-Snowy-White-The-White-Flames-The-Situation</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/lVV-IlPAd7y9azX7-rCxF4t9FTHMrL3CpSCyyj-8H5c/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTMxNzAw/MzQyLTE3MjU5NzE0/MTItMzAyMy5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Blues Rock, Modern Electric Blues, Blues</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Κυκλοφόρησε το 2019 από τη Soul Food Music. Ο Snowy White, γνωστός από τη συνεργασία του με τους Thin Lizzy και τους Pink Floyd, παραδίδει ένα ώριμο, μελωδικό και βαθιά ατμοσφαιρικό blues-rock άλμπουμ, βασισμένο στην χαρακτηριστική, κρυστάλλινη κιθαριστική του τεχνική και στο χαρακτηριστικό relaxed groove των White Flames.</t>
+  </si>
+  <si>
+    <t>Not On Label (Snowy White &amp; The White Flames Self-released) – SWWF 2019LP (2xLP, Album, Deluxe Edition, 180g, Clear Vinyl, 2024)</t>
+  </si>
+  <si>
+    <t>Εισαγωγικό κομμάτι με αργό, υπνωτικό groove και την απαλή, εκφραστική κιθάρα του Snowy White να δίνει τον τόνο.</t>
+  </si>
+  <si>
+    <t>Μελωδική blues σύνθεση με ζεστή ενορχήστρωση και καθαρόαιμο βρετανικό αέρα.</t>
+  </si>
+  <si>
+    <t>Blues</t>
+  </si>
+  <si>
+    <t>Οργανικό κομμάτι που αναδεικνύει την άνεση του White στο να χτίζει διαθέσεις μόνο με τις νότες της κιθάρας του.</t>
+  </si>
+  <si>
+    <t>Εξαιρετικός ρυθμός, με τα φωνητικά του White να δένουν αρμονικά με το χαμηλόφωνο, ποιοτικό rhythm section.</t>
+  </si>
+  <si>
+    <t>Traditional Blues, Blues Rock</t>
+  </si>
+  <si>
+    <t>Πιο παραδοσιακή blues φόρμα, με ωραίο πάτημα και μεστό, αναλογικό ηχητικό αποτύπωμα.</t>
+  </si>
+  <si>
+    <t>Modern Electric Blues</t>
+  </si>
+  <si>
+    <t>Εσωτερικό και ατμοσφαιρικό, ιδανικό για χαλάρωση με ποιοτικό ηχητικό υπόβαθρο.</t>
+  </si>
+  <si>
+    <t>Blues, Soft Rock</t>
+  </si>
+  <si>
+    <t>Ήρεμο και λυρικό κλείσιμο που αφήνει μια γλυκιά, μελωδική γεύση στο τέλος του δίσκου.</t>
+  </si>
+  <si>
+    <t>Πιο "σκληρό" blues ύφος, που σπάει τη μονοτονία και δίνει μια ευχάριστη πινελιά ενέργειας.</t>
+  </si>
+  <si>
+    <t>Δυναμικότερο κομμάτι με στιβαρότερο δέσιμο και εξαιρετική μίξη που αναδεικνύει κάθε όργανο ξεχωριστά.</t>
+  </si>
+  <si>
+    <t>Από τα κορυφαία στιγμιότυπα του δίσκου. Συναισθηματικό βάθος, υποβλητική ερμηνεία και σόλο κιθάρας υποδειγματικής καθαρότητας.</t>
+  </si>
+  <si>
+    <t>Λιτή σύνθεση που κρατάει χαμηλούς τόνους και υπηρετεί πιστά το συνολικό mood του άλμπουμ.</t>
+  </si>
+  <si>
+    <t>Blues Rock, Instrumental</t>
+  </si>
+  <si>
+    <t>Ταξιδιάρικο κομμάτι με έμφαση στην κιθαριστική αφήγηση και τις δυναμικές στα τύμπανα.</t>
   </si>
 </sst>
 </file>
@@ -2917,11 +3025,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="25.7109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="12.7109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="10.7109375" style="1" customWidth="1"/>
@@ -3813,18 +3921,52 @@
       <c r="E28" s="10">
         <v>3.5</v>
       </c>
-      <c r="F28" s="9"/>
+      <c r="F28" s="9" t="s">
+        <v>836</v>
+      </c>
       <c r="G28" s="7" t="s">
+        <v>835</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>812</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>813</v>
       </c>
       <c r="I28" s="11" t="s">
         <v>810</v>
       </c>
       <c r="J28" s="11" t="s">
         <v>811</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+      <c r="A29" s="6">
+        <v>31700342</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>834</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>822</v>
+      </c>
+      <c r="D29" s="6">
+        <v>2019</v>
+      </c>
+      <c r="E29" s="10">
+        <v>3.73</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>839</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>840</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>841</v>
+      </c>
+      <c r="I29" s="11" t="s">
+        <v>837</v>
+      </c>
+      <c r="J29" s="11" t="s">
+        <v>838</v>
       </c>
     </row>
   </sheetData>
@@ -3881,6 +4023,8 @@
     <hyperlink ref="J27" r:id="rId50" xr:uid="{643189D3-04E5-4DA0-A6BD-DA1BBD36408B}"/>
     <hyperlink ref="I28" r:id="rId51" xr:uid="{B401C0DB-140A-4490-819B-6D614FC8CCEE}"/>
     <hyperlink ref="J28" r:id="rId52" xr:uid="{E3F5F8FC-7DEE-4BE0-BFCA-A5C70ADD094D}"/>
+    <hyperlink ref="I29" r:id="rId53" xr:uid="{78B04016-E4AE-47A7-8B46-35766B77AFB8}"/>
+    <hyperlink ref="J29" r:id="rId54" xr:uid="{CCEBFF18-4053-4C24-817D-27646BE05EBD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3888,7 +4032,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I239"/>
+  <dimension ref="A1:I251"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="3" bestFit="1" customWidth="1"/>
@@ -10205,7 +10349,7 @@
         <v>4.2</v>
       </c>
       <c r="H232" s="9" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="I232" s="6" t="s">
         <v>313</v>
@@ -10234,7 +10378,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H233" s="9" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="I233" s="6" t="s">
         <v>313</v>
@@ -10251,7 +10395,7 @@
         <v>802</v>
       </c>
       <c r="D234" s="7" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="E234" s="8">
         <v>3.52</v>
@@ -10263,7 +10407,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H234" s="9" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="I234" s="6"/>
     </row>
@@ -10290,7 +10434,7 @@
         <v>3.9</v>
       </c>
       <c r="H235" s="9" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="I235" s="6"/>
     </row>
@@ -10317,7 +10461,7 @@
         <v>3.8</v>
       </c>
       <c r="H236" s="9" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="I236" s="6"/>
     </row>
@@ -10344,7 +10488,7 @@
         <v>4</v>
       </c>
       <c r="H237" s="9" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="I237" s="6"/>
     </row>
@@ -10371,7 +10515,7 @@
         <v>3.9</v>
       </c>
       <c r="H238" s="9" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="I238" s="6"/>
     </row>
@@ -10386,7 +10530,7 @@
         <v>807</v>
       </c>
       <c r="D239" s="7" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="E239" s="8">
         <v>3.45</v>
@@ -10398,11 +10542,335 @@
         <v>4.5</v>
       </c>
       <c r="H239" s="9" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="I239" s="6" t="s">
         <v>313</v>
       </c>
+    </row>
+    <row r="240" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A240" s="6">
+        <v>31700342</v>
+      </c>
+      <c r="B240" s="6">
+        <v>1</v>
+      </c>
+      <c r="C240" s="7" t="s">
+        <v>822</v>
+      </c>
+      <c r="D240" s="7" t="s">
+        <v>794</v>
+      </c>
+      <c r="E240" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="F240" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="G240" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H240" s="9" t="s">
+        <v>842</v>
+      </c>
+      <c r="I240" s="6"/>
+    </row>
+    <row r="241" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A241" s="6">
+        <v>31700342</v>
+      </c>
+      <c r="B241" s="6">
+        <v>2</v>
+      </c>
+      <c r="C241" s="7" t="s">
+        <v>823</v>
+      </c>
+      <c r="D241" s="7" t="s">
+        <v>794</v>
+      </c>
+      <c r="E241" s="8">
+        <v>3.16</v>
+      </c>
+      <c r="F241" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="G241" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="H241" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="I241" s="6"/>
+    </row>
+    <row r="242" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A242" s="6">
+        <v>31700342</v>
+      </c>
+      <c r="B242" s="6">
+        <v>3</v>
+      </c>
+      <c r="C242" s="7" t="s">
+        <v>824</v>
+      </c>
+      <c r="D242" s="7" t="s">
+        <v>844</v>
+      </c>
+      <c r="E242" s="8">
+        <v>3.16</v>
+      </c>
+      <c r="F242" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="G242" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="H242" s="9" t="s">
+        <v>845</v>
+      </c>
+      <c r="I242" s="6"/>
+    </row>
+    <row r="243" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A243" s="6">
+        <v>31700342</v>
+      </c>
+      <c r="B243" s="6">
+        <v>4</v>
+      </c>
+      <c r="C243" s="7" t="s">
+        <v>825</v>
+      </c>
+      <c r="D243" s="7" t="s">
+        <v>794</v>
+      </c>
+      <c r="E243" s="8">
+        <v>3.31</v>
+      </c>
+      <c r="F243" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="G243" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="H243" s="9" t="s">
+        <v>846</v>
+      </c>
+      <c r="I243" s="6"/>
+    </row>
+    <row r="244" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A244" s="6">
+        <v>31700342</v>
+      </c>
+      <c r="B244" s="6">
+        <v>5</v>
+      </c>
+      <c r="C244" s="7" t="s">
+        <v>826</v>
+      </c>
+      <c r="D244" s="7" t="s">
+        <v>847</v>
+      </c>
+      <c r="E244" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="F244" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="G244" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="H244" s="9" t="s">
+        <v>848</v>
+      </c>
+      <c r="I244" s="6"/>
+    </row>
+    <row r="245" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A245" s="6">
+        <v>31700342</v>
+      </c>
+      <c r="B245" s="6">
+        <v>6</v>
+      </c>
+      <c r="C245" s="7" t="s">
+        <v>827</v>
+      </c>
+      <c r="D245" s="7" t="s">
+        <v>794</v>
+      </c>
+      <c r="E245" s="8">
+        <v>3.41</v>
+      </c>
+      <c r="F245" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="G245" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="H245" s="9" t="s">
+        <v>850</v>
+      </c>
+      <c r="I245" s="6"/>
+    </row>
+    <row r="246" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A246" s="6">
+        <v>31700342</v>
+      </c>
+      <c r="B246" s="6">
+        <v>7</v>
+      </c>
+      <c r="C246" s="7" t="s">
+        <v>828</v>
+      </c>
+      <c r="D246" s="7" t="s">
+        <v>849</v>
+      </c>
+      <c r="E246" s="8">
+        <v>3.75</v>
+      </c>
+      <c r="F246" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="G246" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H246" s="9" t="s">
+        <v>855</v>
+      </c>
+      <c r="I246" s="6"/>
+    </row>
+    <row r="247" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A247" s="6">
+        <v>31700342</v>
+      </c>
+      <c r="B247" s="6">
+        <v>8</v>
+      </c>
+      <c r="C247" s="7" t="s">
+        <v>829</v>
+      </c>
+      <c r="D247" s="7" t="s">
+        <v>794</v>
+      </c>
+      <c r="E247" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="F247" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="G247" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="H247" s="9" t="s">
+        <v>856</v>
+      </c>
+      <c r="I247" s="6"/>
+    </row>
+    <row r="248" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A248" s="6">
+        <v>31700342</v>
+      </c>
+      <c r="B248" s="6">
+        <v>9</v>
+      </c>
+      <c r="C248" s="7" t="s">
+        <v>830</v>
+      </c>
+      <c r="D248" s="7" t="s">
+        <v>857</v>
+      </c>
+      <c r="E248" s="8">
+        <v>3.17</v>
+      </c>
+      <c r="F248" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="G248" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="H248" s="9" t="s">
+        <v>858</v>
+      </c>
+      <c r="I248" s="6"/>
+    </row>
+    <row r="249" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A249" s="6">
+        <v>31700342</v>
+      </c>
+      <c r="B249" s="6">
+        <v>10</v>
+      </c>
+      <c r="C249" s="7" t="s">
+        <v>831</v>
+      </c>
+      <c r="D249" s="7" t="s">
+        <v>794</v>
+      </c>
+      <c r="E249" s="8">
+        <v>3.61</v>
+      </c>
+      <c r="F249" s="8">
+        <v>4</v>
+      </c>
+      <c r="G249" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H249" s="9" t="s">
+        <v>854</v>
+      </c>
+      <c r="I249" s="6"/>
+    </row>
+    <row r="250" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A250" s="6">
+        <v>31700342</v>
+      </c>
+      <c r="B250" s="6">
+        <v>11</v>
+      </c>
+      <c r="C250" s="7" t="s">
+        <v>832</v>
+      </c>
+      <c r="D250" s="7" t="s">
+        <v>794</v>
+      </c>
+      <c r="E250" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="F250" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="G250" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="H250" s="9" t="s">
+        <v>853</v>
+      </c>
+      <c r="I250" s="6"/>
+    </row>
+    <row r="251" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A251" s="6">
+        <v>31700342</v>
+      </c>
+      <c r="B251" s="6">
+        <v>12</v>
+      </c>
+      <c r="C251" s="7" t="s">
+        <v>833</v>
+      </c>
+      <c r="D251" s="7" t="s">
+        <v>851</v>
+      </c>
+      <c r="E251" s="8">
+        <v>3.39</v>
+      </c>
+      <c r="F251" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="G251" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="H251" s="9" t="s">
+        <v>852</v>
+      </c>
+      <c r="I251" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{651896EA-F54A-478C-A24C-729CDCF3CA5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C149F491-BFC2-4A52-82AA-3F99348CCFA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="859">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="888">
   <si>
     <t>No</t>
   </si>
@@ -2598,6 +2598,93 @@
   </si>
   <si>
     <t>Ταξιδιάρικο κομμάτι με έμφαση στην κιθαριστική αφήγηση και τις δυναμικές στα τύμπανα.</t>
+  </si>
+  <si>
+    <t>Squid</t>
+  </si>
+  <si>
+    <t>O Monolith</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/28251457-Squid-O-Monolith</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/iPMP3Of94J3hMgWse1OzpEl_bO1DoXG8D6wRza1BgsA/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI4MjUx/NDU3LTE2OTQ2MTg3/NzUtMTEzMy5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Swing (In A Dream)</t>
+  </si>
+  <si>
+    <t>Devil’s Den</t>
+  </si>
+  <si>
+    <t>Siphon Song</t>
+  </si>
+  <si>
+    <t>Undergrowth</t>
+  </si>
+  <si>
+    <t>The Blades</t>
+  </si>
+  <si>
+    <t>After The Flash</t>
+  </si>
+  <si>
+    <t>Green Light</t>
+  </si>
+  <si>
+    <t>If You Had Seen The Bull’s Swimming Attempts You Would Have Stayed Away</t>
+  </si>
+  <si>
+    <t>Art Punk, Post-Rock, Experimental Rock, Avant-Garde</t>
+  </si>
+  <si>
+    <t>Warp Records – WARPLP353 (LP, Album, Europe, 2023)</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Κυκλοφόρησε το 2023 από τη Warp Records με παραγωγό τον Dan Carey. Ένα πολυεπίπεδο, πειραματικό αριστούργημα που συνδυάζει την post-punk ενέργεια με τη σύγχρονη κλασική ενορχήστρωση, τα φολκ στοιχεία και τους σύνθετους, απρόβλεπτους ρυθμούς.</t>
+  </si>
+  <si>
+    <t>Art Punk, Experimental Rock</t>
+  </si>
+  <si>
+    <t>Υπνωτική και εκρηκτική εισαγωγή με εξαιρετική εναλλαγή δυναμικών και πολυεπίπεδη μίξη που αναδεικνύει κάθε ηλεκτρονική και οργανική λεπτομέρεια.</t>
+  </si>
+  <si>
+    <t>Post-Rock, Art Punk</t>
+  </si>
+  <si>
+    <t>Κλειστοφοβική ατμόσφαιρα, χτισμένη γύρω από υπόγειες μπασογραμμές και πειραματικά κρουστά που δημιουργούν υποβλητική ένταση.</t>
+  </si>
+  <si>
+    <t>Experimental Rock, Chamber Folk</t>
+  </si>
+  <si>
+    <t>Λυρική σύνθεση με κυρίαρχη τη χρήση πνευστών και οργανικών υφών, προσφέροντας έναν πιο εσωτερικό και οργανικό ήχο.</t>
+  </si>
+  <si>
+    <t>Καθηλωτικό κομμάτι σταδιακής κλιμάκωσης, με υποδειγματική διαύγεια και διαχωρισμό οργάνων στο κορύφωμα.</t>
+  </si>
+  <si>
+    <t>Ατμοσφαιρικό ηχητικό τοπίο που λειτουργεί ως απαραίτητη γέφυρα ηρεμίας και αποσυμπίεσης στη ροή του δίσκου.</t>
+  </si>
+  <si>
+    <t>Ρυθμικός λαβύρινθος με κοφτερά κιθαριστικά θέματα, αψεγάδιαστο groove και εκρηκτικό, καταιγιστικό φινάλε.</t>
+  </si>
+  <si>
+    <t>Πολυδιάστατο και ιδιόμορφο φινάλε με απαιτητική ενορχήστρωση που αφήνει έντονο πειραματικό αποτύπωμα.</t>
+  </si>
+  <si>
+    <t>Experimental Rock, Avant-Garde</t>
+  </si>
+  <si>
+    <t>Art Rock, Post-Rock</t>
+  </si>
+  <si>
+    <t>Εκτενής σύνθεση με κινηματογραφική δομή, πλούσιο ηχητικό φάσμα και άψογη ροή από τις ήρεμες στις δυναμικές φάσεις.</t>
+  </si>
+  <si>
+    <t>Ambient, Experimental</t>
   </si>
 </sst>
 </file>
@@ -3025,7 +3112,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -3967,6 +4054,38 @@
       </c>
       <c r="J29" s="11" t="s">
         <v>838</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+      <c r="A30" s="6">
+        <v>28251457</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>859</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>860</v>
+      </c>
+      <c r="D30" s="6">
+        <v>2023</v>
+      </c>
+      <c r="E30" s="10">
+        <v>3.61</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>871</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>873</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>872</v>
+      </c>
+      <c r="I30" s="11" t="s">
+        <v>861</v>
+      </c>
+      <c r="J30" s="11" t="s">
+        <v>862</v>
       </c>
     </row>
   </sheetData>
@@ -4025,6 +4144,8 @@
     <hyperlink ref="J28" r:id="rId52" xr:uid="{E3F5F8FC-7DEE-4BE0-BFCA-A5C70ADD094D}"/>
     <hyperlink ref="I29" r:id="rId53" xr:uid="{78B04016-E4AE-47A7-8B46-35766B77AFB8}"/>
     <hyperlink ref="J29" r:id="rId54" xr:uid="{CCEBFF18-4053-4C24-817D-27646BE05EBD}"/>
+    <hyperlink ref="I30" r:id="rId55" xr:uid="{94D10AC9-6F43-4F0A-B43B-92E95070FCCE}"/>
+    <hyperlink ref="J30" r:id="rId56" xr:uid="{2A30FB6F-21B9-49D1-B22B-53BACDF84062}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4032,7 +4153,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I251"/>
+  <dimension ref="A1:I259"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="3" bestFit="1" customWidth="1"/>
@@ -10872,6 +10993,222 @@
       </c>
       <c r="I251" s="6"/>
     </row>
+    <row r="252" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A252" s="6">
+        <v>28251457</v>
+      </c>
+      <c r="B252" s="6">
+        <v>1</v>
+      </c>
+      <c r="C252" s="7" t="s">
+        <v>863</v>
+      </c>
+      <c r="D252" s="7" t="s">
+        <v>874</v>
+      </c>
+      <c r="E252" s="8">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="F252" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G252" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="H252" s="9" t="s">
+        <v>875</v>
+      </c>
+      <c r="I252" s="6"/>
+    </row>
+    <row r="253" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A253" s="6">
+        <v>28251457</v>
+      </c>
+      <c r="B253" s="6">
+        <v>2</v>
+      </c>
+      <c r="C253" s="7" t="s">
+        <v>864</v>
+      </c>
+      <c r="D253" s="7" t="s">
+        <v>876</v>
+      </c>
+      <c r="E253" s="8">
+        <v>3.79</v>
+      </c>
+      <c r="F253" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="G253" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="H253" s="9" t="s">
+        <v>877</v>
+      </c>
+      <c r="I253" s="6"/>
+    </row>
+    <row r="254" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A254" s="6">
+        <v>28251457</v>
+      </c>
+      <c r="B254" s="6">
+        <v>3</v>
+      </c>
+      <c r="C254" s="7" t="s">
+        <v>865</v>
+      </c>
+      <c r="D254" s="7" t="s">
+        <v>878</v>
+      </c>
+      <c r="E254" s="8">
+        <v>3.86</v>
+      </c>
+      <c r="F254" s="8">
+        <v>4</v>
+      </c>
+      <c r="G254" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="H254" s="9" t="s">
+        <v>879</v>
+      </c>
+      <c r="I254" s="6"/>
+    </row>
+    <row r="255" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A255" s="6">
+        <v>28251457</v>
+      </c>
+      <c r="B255" s="6">
+        <v>4</v>
+      </c>
+      <c r="C255" s="7" t="s">
+        <v>866</v>
+      </c>
+      <c r="D255" s="7" t="s">
+        <v>876</v>
+      </c>
+      <c r="E255" s="8">
+        <v>4.22</v>
+      </c>
+      <c r="F255" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="G255" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="H255" s="9" t="s">
+        <v>880</v>
+      </c>
+      <c r="I255" s="6"/>
+    </row>
+    <row r="256" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A256" s="6">
+        <v>28251457</v>
+      </c>
+      <c r="B256" s="6">
+        <v>5</v>
+      </c>
+      <c r="C256" s="7" t="s">
+        <v>867</v>
+      </c>
+      <c r="D256" s="7" t="s">
+        <v>874</v>
+      </c>
+      <c r="E256" s="8">
+        <v>4.32</v>
+      </c>
+      <c r="F256" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G256" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="H256" s="9" t="s">
+        <v>882</v>
+      </c>
+      <c r="I256" s="6"/>
+    </row>
+    <row r="257" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A257" s="6">
+        <v>28251457</v>
+      </c>
+      <c r="B257" s="6">
+        <v>6</v>
+      </c>
+      <c r="C257" s="7" t="s">
+        <v>868</v>
+      </c>
+      <c r="D257" s="7" t="s">
+        <v>887</v>
+      </c>
+      <c r="E257" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="F257" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="G257" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="H257" s="9" t="s">
+        <v>881</v>
+      </c>
+      <c r="I257" s="6"/>
+    </row>
+    <row r="258" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A258" s="6">
+        <v>28251457</v>
+      </c>
+      <c r="B258" s="6">
+        <v>7</v>
+      </c>
+      <c r="C258" s="7" t="s">
+        <v>869</v>
+      </c>
+      <c r="D258" s="7" t="s">
+        <v>885</v>
+      </c>
+      <c r="E258" s="8">
+        <v>4</v>
+      </c>
+      <c r="F258" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G258" s="8">
+        <v>4</v>
+      </c>
+      <c r="H258" s="9" t="s">
+        <v>886</v>
+      </c>
+      <c r="I258" s="6"/>
+    </row>
+    <row r="259" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A259" s="6">
+        <v>28251457</v>
+      </c>
+      <c r="B259" s="6">
+        <v>8</v>
+      </c>
+      <c r="C259" s="7" t="s">
+        <v>870</v>
+      </c>
+      <c r="D259" s="7" t="s">
+        <v>884</v>
+      </c>
+      <c r="E259" s="8">
+        <v>3.86</v>
+      </c>
+      <c r="F259" s="8">
+        <v>4</v>
+      </c>
+      <c r="G259" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="H259" s="9" t="s">
+        <v>883</v>
+      </c>
+      <c r="I259" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C149F491-BFC2-4A52-82AA-3F99348CCFA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3109B51-44B2-46D8-B26F-F2C661A8EC08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="888">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="927">
   <si>
     <t>No</t>
   </si>
@@ -2685,6 +2685,123 @@
   </si>
   <si>
     <t>Ambient, Experimental</t>
+  </si>
+  <si>
+    <t>Siena Root</t>
+  </si>
+  <si>
+    <t>Revelation</t>
+  </si>
+  <si>
+    <t>Coincidence &amp; Fate</t>
+  </si>
+  <si>
+    <t>Professional Procrastinator</t>
+  </si>
+  <si>
+    <t>No Peace</t>
+  </si>
+  <si>
+    <t>Fighting Gravity</t>
+  </si>
+  <si>
+    <t>Dusty Roads</t>
+  </si>
+  <si>
+    <t>Winter Solstice</t>
+  </si>
+  <si>
+    <t>Dalecarlia Stroll</t>
+  </si>
+  <si>
+    <t>Leaving The City</t>
+  </si>
+  <si>
+    <t>Little Burden</t>
+  </si>
+  <si>
+    <t>Madukhauns</t>
+  </si>
+  <si>
+    <t>Keeper Of The Flame</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/26207852-Siena-Root-Revelation</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/q0_IeQSpoqAEwU3gC1gL7-pq6csIBpHACJg3CT7piF0/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI2MjA3/ODUyLTE2NzcyMzMx/MjUtNTE2MS5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Blues Rock, Hard Rock, Psychedelic Rock, Roots Rock</t>
+  </si>
+  <si>
+    <t>Atomic Fire – AFR0076V (LP, Album, Limited Edition, Clear Vinyl, 2023)</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Κυκλοφόρησε το 2023 σε περιορισμένη έκδοση 1000 αντιτύπων σε διάφανο βινύλιο από την Atomic Fire. Ηχογραφημένο με αναλογική φιλοσοφία και vintage εξοπλισμό, αποτυπώνει αυθεντικά την ατμόσφαιρα του 70s hard rock και blues-rock.</t>
+  </si>
+  <si>
+    <t>Classic Heavy Rock / Organ-driven Psych</t>
+  </si>
+  <si>
+    <t>Heavy Psych</t>
+  </si>
+  <si>
+    <t>Classic Rock, Boogie Rock</t>
+  </si>
+  <si>
+    <t>Roots Rock</t>
+  </si>
+  <si>
+    <t>Dark Folk, Blues, Appalachian Rock</t>
+  </si>
+  <si>
+    <t>Nordic Folk, Pagan Folk [Instrumental]</t>
+  </si>
+  <si>
+    <t>Folk Psych, Instrumental</t>
+  </si>
+  <si>
+    <t>Acoustic Ballad, Folk Rock</t>
+  </si>
+  <si>
+    <t>Eastern Psych, Indo-Rock, Instrumental Jam</t>
+  </si>
+  <si>
+    <t>Heavy Blues Rock</t>
+  </si>
+  <si>
+    <t>Δυναμικό ξεκίνημα με fuzz κιθάρες, βαρύ rhythm section και στίχους για την ευθραυστότητα της ζωής και τον φόβο του θανάτου.</t>
+  </si>
+  <si>
+    <t>Ευθύ vintage hard rock κομμάτι, επικεντρωμένο στην κοινωνική πίεση και την αναβλητικότητα της καθημερινότητας.</t>
+  </si>
+  <si>
+    <t>Ακουστικό, folk/blues διάλειμμα με slide κιθάρες και θέμα την απώλεια της εσωτερικής γαλήνης.</t>
+  </si>
+  <si>
+    <t>Κλασικό Siena Root mid-tempo track με progressive πινελιές και Hammond όργανο, που συμβολίζει την προσπάθεια υπέρβασης των φυσικών και ψυχικών περιορισμών.</t>
+  </si>
+  <si>
+    <t>Από τις κορυφαίες στιγμές του δίσκου, ένα σκοτεινό blues/folk έπος με μυσταγωγική ατμόσφαιρα ταξιδιού και απομόνωσης.</t>
+  </si>
+  <si>
+    <t>Οργανική σύνθεση εμπνευσμένη από τη σκανδιναβική φύση και τις τελετουργίες του χειμερινού ηλιοστασίου.</t>
+  </si>
+  <si>
+    <t>Οργανικό folk-psych κομμάτι που συνδυάζει σουηδικά παραδοσιακά μοτίβα με ψυχεδελικές κλιμακώσεις.</t>
+  </si>
+  <si>
+    <t>Heavy rock δυναμίτης που εστιάζει στην ανάγκη φυγής από το τσιμέντο και την επιστροφή στις ρίζες.</t>
+  </si>
+  <si>
+    <t>Μελωδική ακουστική μπαλάντα με μεσαιωνικές/αναγεννησιακές αποχρώσεις για τα προσωπικά βάρη που κουβαλά ο άνθρωπος.</t>
+  </si>
+  <si>
+    <t>Ψυχεδελική raga-rock μυσταγωγία με sitar, κρουστά και ανατολίτικες κλίμακες, συνεχίζοντας την παράδοση των μεγάλων ανατολίτικων jams της μπάντας.</t>
+  </si>
+  <si>
+    <t>Δυναμικό κλείσιμο με γεμάτο ήχο, που λειτουργεί ως μανιφέστο για τη διατήρηση της αυθεντικής vintage rock φλόγας ζωντανής.</t>
   </si>
 </sst>
 </file>
@@ -3112,7 +3229,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -4086,6 +4203,38 @@
       </c>
       <c r="J30" s="11" t="s">
         <v>862</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+      <c r="A31" s="6">
+        <v>26207852</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>888</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>889</v>
+      </c>
+      <c r="D31" s="6">
+        <v>2023</v>
+      </c>
+      <c r="E31" s="10">
+        <v>3.29</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>903</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>905</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>904</v>
+      </c>
+      <c r="I31" s="11" t="s">
+        <v>901</v>
+      </c>
+      <c r="J31" s="11" t="s">
+        <v>902</v>
       </c>
     </row>
   </sheetData>
@@ -4146,6 +4295,8 @@
     <hyperlink ref="J29" r:id="rId54" xr:uid="{CCEBFF18-4053-4C24-817D-27646BE05EBD}"/>
     <hyperlink ref="I30" r:id="rId55" xr:uid="{94D10AC9-6F43-4F0A-B43B-92E95070FCCE}"/>
     <hyperlink ref="J30" r:id="rId56" xr:uid="{2A30FB6F-21B9-49D1-B22B-53BACDF84062}"/>
+    <hyperlink ref="I31" r:id="rId57" xr:uid="{2B4FAB2A-D7A8-44D8-B205-AB8D67EAA1A2}"/>
+    <hyperlink ref="J31" r:id="rId58" xr:uid="{6E83A0B5-25C8-4527-A2C1-368E190DF4BF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4153,7 +4304,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I259"/>
+  <dimension ref="A1:I270"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="3" bestFit="1" customWidth="1"/>
@@ -11209,6 +11360,303 @@
       </c>
       <c r="I259" s="6"/>
     </row>
+    <row r="260" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A260" s="6">
+        <v>26207852</v>
+      </c>
+      <c r="B260" s="6">
+        <v>1</v>
+      </c>
+      <c r="C260" s="7" t="s">
+        <v>890</v>
+      </c>
+      <c r="D260" s="7" t="s">
+        <v>907</v>
+      </c>
+      <c r="E260" s="8">
+        <v>3.76</v>
+      </c>
+      <c r="F260" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="G260" s="8">
+        <v>4</v>
+      </c>
+      <c r="H260" s="9" t="s">
+        <v>916</v>
+      </c>
+      <c r="I260" s="6"/>
+    </row>
+    <row r="261" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A261" s="6">
+        <v>26207852</v>
+      </c>
+      <c r="B261" s="6">
+        <v>2</v>
+      </c>
+      <c r="C261" s="7" t="s">
+        <v>891</v>
+      </c>
+      <c r="D261" s="7" t="s">
+        <v>908</v>
+      </c>
+      <c r="E261" s="8">
+        <v>3.67</v>
+      </c>
+      <c r="F261" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="G261" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="H261" s="9" t="s">
+        <v>917</v>
+      </c>
+      <c r="I261" s="6"/>
+    </row>
+    <row r="262" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A262" s="6">
+        <v>26207852</v>
+      </c>
+      <c r="B262" s="6">
+        <v>3</v>
+      </c>
+      <c r="C262" s="7" t="s">
+        <v>892</v>
+      </c>
+      <c r="D262" s="7" t="s">
+        <v>794</v>
+      </c>
+      <c r="E262" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="F262" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="G262" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="H262" s="9" t="s">
+        <v>918</v>
+      </c>
+      <c r="I262" s="6"/>
+    </row>
+    <row r="263" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A263" s="6">
+        <v>26207852</v>
+      </c>
+      <c r="B263" s="6">
+        <v>4</v>
+      </c>
+      <c r="C263" s="7" t="s">
+        <v>893</v>
+      </c>
+      <c r="D263" s="7" t="s">
+        <v>909</v>
+      </c>
+      <c r="E263" s="8">
+        <v>3.33</v>
+      </c>
+      <c r="F263" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="G263" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="H263" s="9" t="s">
+        <v>919</v>
+      </c>
+      <c r="I263" s="6"/>
+    </row>
+    <row r="264" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A264" s="6">
+        <v>26207852</v>
+      </c>
+      <c r="B264" s="6">
+        <v>5</v>
+      </c>
+      <c r="C264" s="7" t="s">
+        <v>894</v>
+      </c>
+      <c r="D264" s="7" t="s">
+        <v>910</v>
+      </c>
+      <c r="E264" s="8">
+        <v>3.33</v>
+      </c>
+      <c r="F264" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G264" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="H264" s="9" t="s">
+        <v>920</v>
+      </c>
+      <c r="I264" s="6"/>
+    </row>
+    <row r="265" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A265" s="6">
+        <v>26207852</v>
+      </c>
+      <c r="B265" s="6">
+        <v>6</v>
+      </c>
+      <c r="C265" s="7" t="s">
+        <v>895</v>
+      </c>
+      <c r="D265" s="7" t="s">
+        <v>911</v>
+      </c>
+      <c r="E265" s="8">
+        <v>3.33</v>
+      </c>
+      <c r="F265" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="G265" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="H265" s="9" t="s">
+        <v>921</v>
+      </c>
+      <c r="I265" s="6"/>
+    </row>
+    <row r="266" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A266" s="6">
+        <v>26207852</v>
+      </c>
+      <c r="B266" s="6">
+        <v>7</v>
+      </c>
+      <c r="C266" s="7" t="s">
+        <v>896</v>
+      </c>
+      <c r="D266" s="7" t="s">
+        <v>912</v>
+      </c>
+      <c r="E266" s="8">
+        <v>3.33</v>
+      </c>
+      <c r="F266" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="G266" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="H266" s="9" t="s">
+        <v>922</v>
+      </c>
+      <c r="I266" s="6"/>
+    </row>
+    <row r="267" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A267" s="6">
+        <v>26207852</v>
+      </c>
+      <c r="B267" s="6">
+        <v>8</v>
+      </c>
+      <c r="C267" s="7" t="s">
+        <v>897</v>
+      </c>
+      <c r="D267" s="7" t="s">
+        <v>906</v>
+      </c>
+      <c r="E267" s="8">
+        <v>3.33</v>
+      </c>
+      <c r="F267" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="G267" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="H267" s="9" t="s">
+        <v>923</v>
+      </c>
+      <c r="I267" s="6"/>
+    </row>
+    <row r="268" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A268" s="6">
+        <v>26207852</v>
+      </c>
+      <c r="B268" s="6">
+        <v>9</v>
+      </c>
+      <c r="C268" s="7" t="s">
+        <v>898</v>
+      </c>
+      <c r="D268" s="7" t="s">
+        <v>913</v>
+      </c>
+      <c r="E268" s="8">
+        <v>3.33</v>
+      </c>
+      <c r="F268" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="G268" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="H268" s="9" t="s">
+        <v>924</v>
+      </c>
+      <c r="I268" s="6"/>
+    </row>
+    <row r="269" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A269" s="6">
+        <v>26207852</v>
+      </c>
+      <c r="B269" s="6">
+        <v>10</v>
+      </c>
+      <c r="C269" s="7" t="s">
+        <v>899</v>
+      </c>
+      <c r="D269" s="7" t="s">
+        <v>914</v>
+      </c>
+      <c r="E269" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="F269" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="G269" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="H269" s="9" t="s">
+        <v>925</v>
+      </c>
+      <c r="I269" s="6"/>
+    </row>
+    <row r="270" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A270" s="6">
+        <v>26207852</v>
+      </c>
+      <c r="B270" s="6">
+        <v>11</v>
+      </c>
+      <c r="C270" s="7" t="s">
+        <v>900</v>
+      </c>
+      <c r="D270" s="7" t="s">
+        <v>915</v>
+      </c>
+      <c r="E270" s="8">
+        <v>3.91</v>
+      </c>
+      <c r="F270" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="G270" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H270" s="9" t="s">
+        <v>926</v>
+      </c>
+      <c r="I270" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3109B51-44B2-46D8-B26F-F2C661A8EC08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78E3A205-D6C6-4271-9CA3-B0BB04CA0E2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="927">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1103" uniqueCount="955">
   <si>
     <t>No</t>
   </si>
@@ -2802,6 +2802,90 @@
   </si>
   <si>
     <t>Δυναμικό κλείσιμο με γεμάτο ήχο, που λειτουργεί ως μανιφέστο για τη διατήρηση της αυθεντικής vintage rock φλόγας ζωντανής.</t>
+  </si>
+  <si>
+    <t>Swampsnake</t>
+  </si>
+  <si>
+    <t>Gang Bang</t>
+  </si>
+  <si>
+    <t>The Faith Healer</t>
+  </si>
+  <si>
+    <t>Giddy-Up-A-Ding Dong</t>
+  </si>
+  <si>
+    <t>Next</t>
+  </si>
+  <si>
+    <t>Vambo Marble Eye</t>
+  </si>
+  <si>
+    <t>The Last Of The Teenage Idols (Parts 1 2 3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Sensational Alex Harvey Band </t>
+  </si>
+  <si>
+    <t>Next…</t>
+  </si>
+  <si>
+    <t>Art Rock, Glam Rock, Hard Rock, Blues Rock</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το τρίτο στούντιο άλμπουμ του συγκροτήματος και ένα από τα πιο πρωτοποριακά δείγματα του βρετανικού art/glam rock. Σε παραγωγή του David Batchelor, το άλμπουμ συνδυάζει θεατρικότητα, cabaret στοιχεία, βαριά blues riff και την εκκεντρική, επιβλητική προσωπικότητα του Alex Harvey.</t>
+  </si>
+  <si>
+    <t>Εισαγωγή με ένα βαρύ groove και κοφτά riff του Zal Cleminson, όπου ο Harvey τραγουδά με θεατρική πρόκληση για την ακαταμάχητη έλξη και τους πειρασμούς.</t>
+  </si>
+  <si>
+    <t>Σκληρό blues-rock με pub rock αισθητική, που σχολιάζει με σαρδόνιο χιούμορ και ωμότητα την ανδρική σεξουαλική ματαιοδοξία.</t>
+  </si>
+  <si>
+    <t>Το απόλυτο αριστούργημα της μπάντας, με υπνωτικό Krautrock συνθεσάιζερ, επιβλητικό riff και στίχους που ξεσκεπάζουν τους ψευδοπροφήτες και τους χειριστικούς ιεροκήρυκες.</t>
+  </si>
+  <si>
+    <t>Διασκευή στο 50s rock &amp; roll κομμάτι του Freddie Bell, εκτελεσμένη με ξέφρενη glam rock ενέργεια και χιουμοριστική διάθεση.</t>
+  </si>
+  <si>
+    <t>Βαρύς ύμνος αφιερωμένος στον φανταστικό χαρακτήρα κόμικ «Vambo», τον προστάτη των δρόμων της Γλασκώβης.</t>
+  </si>
+  <si>
+    <t>Ανατριχιαστική θεατρική διασκευή του «Au Suivant» του Jacques Brel, η οποία περιγράφει με συγκλονιστικό τρόπο τον εκμηδενισμό της ανθρώπινης αξιοπρέπειας μέσα σε ένα στρατιωτικό κινητό πορνείο.</t>
+  </si>
+  <si>
+    <t>Πολυεπίπεδη σουίτα τριών μερών που ξεκινά ως hard rock δυναμίτης και καταλήγει σε παρωδία 50s doo-wop, σατιρίζοντας την άνοδο και την πτώση των κατασκευασμένων ειδώλων της ποπ.</t>
+  </si>
+  <si>
+    <t>Vertigo – 6360 103 D (Germany, 1973)</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/3507697-The-Sensational-Alex-Harvey-Band-Next?redirected=true</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/IzxpGXhfn0nzI-5F5piMx3K2n2tgy8s1unE74VzwIcU/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTM1MDc2/OTctMTUyMjU4NDAz/MS0zOTYwLmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>Glam Rock, Heavy Funk Rock</t>
+  </si>
+  <si>
+    <t>Pub Rock, Boogie Rock</t>
+  </si>
+  <si>
+    <t>50s Rockabilly Revival, Hard Boogie</t>
+  </si>
+  <si>
+    <t>Dark Cabaret, Theatrical Rock, Tango</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Heavy Prog, Glam</t>
+  </si>
+  <si>
+    <t>Multi-Part Suite, Glam Rock, Doo-Wop Parody</t>
+  </si>
+  <si>
+    <t>Heavy Psych, Proto-Industrial, Art Rock</t>
   </si>
 </sst>
 </file>
@@ -3229,7 +3313,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -4235,6 +4319,38 @@
       </c>
       <c r="J31" s="11" t="s">
         <v>902</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+      <c r="A32" s="6">
+        <v>3507697</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>934</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>935</v>
+      </c>
+      <c r="D32" s="6">
+        <v>1973</v>
+      </c>
+      <c r="E32" s="10">
+        <v>3.29</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>936</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>937</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>945</v>
+      </c>
+      <c r="I32" s="11" t="s">
+        <v>946</v>
+      </c>
+      <c r="J32" s="11" t="s">
+        <v>947</v>
       </c>
     </row>
   </sheetData>
@@ -4297,6 +4413,8 @@
     <hyperlink ref="J30" r:id="rId56" xr:uid="{2A30FB6F-21B9-49D1-B22B-53BACDF84062}"/>
     <hyperlink ref="I31" r:id="rId57" xr:uid="{2B4FAB2A-D7A8-44D8-B205-AB8D67EAA1A2}"/>
     <hyperlink ref="J31" r:id="rId58" xr:uid="{6E83A0B5-25C8-4527-A2C1-368E190DF4BF}"/>
+    <hyperlink ref="I32" r:id="rId59" xr:uid="{AC32B278-CEC9-4643-B124-1F81CDC65266}"/>
+    <hyperlink ref="J32" r:id="rId60" xr:uid="{CCA851C3-A0FC-424B-8F6D-38C0FDFC9C81}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4304,12 +4422,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I270"/>
+  <dimension ref="A1:I277"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="3" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.7109375" style="5" customWidth="1"/>
     <col min="4" max="4" width="32.5703125" style="5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.85546875" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.140625" style="4" bestFit="1" customWidth="1"/>
@@ -11657,6 +11775,199 @@
       </c>
       <c r="I270" s="6"/>
     </row>
+    <row r="271" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A271" s="6">
+        <v>3507697</v>
+      </c>
+      <c r="B271" s="6">
+        <v>1</v>
+      </c>
+      <c r="C271" s="7" t="s">
+        <v>927</v>
+      </c>
+      <c r="D271" s="7" t="s">
+        <v>948</v>
+      </c>
+      <c r="E271" s="8">
+        <v>3.52</v>
+      </c>
+      <c r="F271" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="G271" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="H271" s="9" t="s">
+        <v>938</v>
+      </c>
+      <c r="I271" s="6"/>
+    </row>
+    <row r="272" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A272" s="6">
+        <v>3507697</v>
+      </c>
+      <c r="B272" s="6">
+        <v>2</v>
+      </c>
+      <c r="C272" s="7" t="s">
+        <v>928</v>
+      </c>
+      <c r="D272" s="7" t="s">
+        <v>949</v>
+      </c>
+      <c r="E272" s="8">
+        <v>3.35</v>
+      </c>
+      <c r="F272" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="G272" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="H272" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="I272" s="6"/>
+    </row>
+    <row r="273" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A273" s="6">
+        <v>3507697</v>
+      </c>
+      <c r="B273" s="6">
+        <v>3</v>
+      </c>
+      <c r="C273" s="7" t="s">
+        <v>929</v>
+      </c>
+      <c r="D273" s="7" t="s">
+        <v>954</v>
+      </c>
+      <c r="E273" s="8">
+        <v>3.66</v>
+      </c>
+      <c r="F273" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G273" s="8">
+        <v>4.7</v>
+      </c>
+      <c r="H273" s="9" t="s">
+        <v>940</v>
+      </c>
+      <c r="I273" s="6" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A274" s="6">
+        <v>3507697</v>
+      </c>
+      <c r="B274" s="6">
+        <v>4</v>
+      </c>
+      <c r="C274" s="7" t="s">
+        <v>930</v>
+      </c>
+      <c r="D274" s="7" t="s">
+        <v>950</v>
+      </c>
+      <c r="E274" s="8">
+        <v>3.18</v>
+      </c>
+      <c r="F274" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="G274" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="H274" s="9" t="s">
+        <v>941</v>
+      </c>
+      <c r="I274" s="6"/>
+    </row>
+    <row r="275" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A275" s="6">
+        <v>3507697</v>
+      </c>
+      <c r="B275" s="6">
+        <v>5</v>
+      </c>
+      <c r="C275" s="7" t="s">
+        <v>931</v>
+      </c>
+      <c r="D275" s="7" t="s">
+        <v>951</v>
+      </c>
+      <c r="E275" s="8">
+        <v>3.49</v>
+      </c>
+      <c r="F275" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="G275" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H275" s="9" t="s">
+        <v>943</v>
+      </c>
+      <c r="I275" s="6" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A276" s="6">
+        <v>3507697</v>
+      </c>
+      <c r="B276" s="6">
+        <v>6</v>
+      </c>
+      <c r="C276" s="7" t="s">
+        <v>932</v>
+      </c>
+      <c r="D276" s="7" t="s">
+        <v>952</v>
+      </c>
+      <c r="E276" s="8">
+        <v>3.45</v>
+      </c>
+      <c r="F276" s="8">
+        <v>4</v>
+      </c>
+      <c r="G276" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H276" s="9" t="s">
+        <v>942</v>
+      </c>
+      <c r="I276" s="6"/>
+    </row>
+    <row r="277" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A277" s="6">
+        <v>3507697</v>
+      </c>
+      <c r="B277" s="6">
+        <v>7</v>
+      </c>
+      <c r="C277" s="7" t="s">
+        <v>933</v>
+      </c>
+      <c r="D277" s="7" t="s">
+        <v>953</v>
+      </c>
+      <c r="E277" s="8">
+        <v>3.61</v>
+      </c>
+      <c r="F277" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G277" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="H277" s="9" t="s">
+        <v>944</v>
+      </c>
+      <c r="I277" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78E3A205-D6C6-4271-9CA3-B0BB04CA0E2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E744ACA6-0131-46FB-A453-9E525DC76747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1103" uniqueCount="955">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1175" uniqueCount="1025">
   <si>
     <t>No</t>
   </si>
@@ -2886,13 +2886,224 @@
   </si>
   <si>
     <t>Heavy Psych, Proto-Industrial, Art Rock</t>
+  </si>
+  <si>
+    <t>Moving Pictures</t>
+  </si>
+  <si>
+    <t>Rush</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/33253932-Rush-Moving-Pictures</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/IiRCeDrvU-VdD5_hLmLYOQ34HUdtUKuz8QcWt_mHVKc/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTM2OTM5/MS0xMTEwMjQ1NDIy/LmpwZw.jpeg</t>
+  </si>
+  <si>
+    <t>Tom Sawyer</t>
+  </si>
+  <si>
+    <t>Red Barchetta</t>
+  </si>
+  <si>
+    <t>YYZ</t>
+  </si>
+  <si>
+    <t>Limelight</t>
+  </si>
+  <si>
+    <t>Witch Hunt</t>
+  </si>
+  <si>
+    <t>Vital Signs</t>
+  </si>
+  <si>
+    <t>The Camera Eye (5a. Grim-Faced And Forbidding, 5b. Wide-Angle Watcher)</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Ηχογραφημένο στα Le Studio στο Morin-Heights. Η συγκεκριμένη ευρωπαϊκή κοπή διαθέτει DMM Mastering που πραγματοποιήθηκε τον Ιανουάριο του 2015 στα Abbey Road Mastering Studios από τον Sean Magee.</t>
+  </si>
+  <si>
+    <t>Mercury – B00223080-01, Universal Music Enterprises – B00223080-01, Anthem (5) – B00223080-01 (LP, Album, Reissue, Stereo, 150g, DMM, Europe, 2015)</t>
+  </si>
+  <si>
+    <t>Synth-Rock, Classic Rock</t>
+  </si>
+  <si>
+    <t>Ο απόλυτος ύμνος του συγκροτήματος, με το χαρακτηριστικό Oberheim synth sweep, το πολυρυθμικό σόλο τυμπάνων του Peart και στίχους για το αδάμαστο, ελεύθερο πνεύμα.</t>
+  </si>
+  <si>
+    <t>Sci-Fi Rock, Narrative Prog</t>
+  </si>
+  <si>
+    <t>Heavy Prog, Instrumental Virtuoso</t>
+  </si>
+  <si>
+    <t>Arena Rock, Melodic Hard Rock</t>
+  </si>
+  <si>
+    <t>Epic Progressive Rock, Synth-Prog</t>
+  </si>
+  <si>
+    <t>Heavy Prog, Dark Art Rock</t>
+  </si>
+  <si>
+    <t>Reggae-Rock, Post-Punk - Influenced Rock</t>
+  </si>
+  <si>
+    <t>Φουτουριστική αφήγηση εμπνευσμένη από το διήγημα «A Nice Morning Drive», που περιγράφει μια παράνομη διαδρομή με ένα κλασικό σπορ αυτοκίνητο σε έναν δυστοπικό κόσμο αυστηρού ελέγχου.</t>
+  </si>
+  <si>
+    <t>Εμβληματικό οργανικό κομμάτι που ξεκινά με τον ρυθμό του κώδικα Morse για το αεροδρόμιο του Τορόντο, συνδυάζοντας funk slap μπάσο, jazz-fusion κλίμακες και εκρηκτικά solos.</t>
+  </si>
+  <si>
+    <t>Βαθιά προσωπική εξομολόγηση του Peart για την αποξένωση και τη δυσκολία διαχείρισης της έκθεσης στη δημοσιότητα, υποστηριζόμενη από ένα από τα πιο μελωδικά και συναισθηματικά σόλο κιθάρας του Alex Lifeson.</t>
+  </si>
+  <si>
+    <t>Η τελευταία μεγάλη prog σουίτα (11 λεπτά) των Rush, η οποία σκιαγραφεί τις έντονες αντιθέσεις και τον πυρετώδη ρυθμό της Νέας Υόρκης και του Λονδίνου.</t>
+  </si>
+  <si>
+    <t>Το τρίτο μέρος της τετραλογίας «Fear», ένα σκοτεινό, ατμοσφαιρικό κομμάτι που στηλιτεύει τον θρησκευτικό φανατισμό, τη μαζική υστερία και τον ρατσισμό.</t>
+  </si>
+  <si>
+    <t>Πρωτοποριακό κομμάτι με ρυθμό επηρεασμένο από τους The Police και το reggae rock, γεμάτο συνθεσάιζερ sequencers και στίχους για την προσαρμοστικότητα και την ανθρώπινη επικοινωνία στην ψηφιακή εποχή.</t>
+  </si>
+  <si>
+    <t>Rolling Stones</t>
+  </si>
+  <si>
+    <t>Hackney Diamonds</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/28518808-Rolling-Stones-Hackney-Diamonds</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/kT4a1DpsiQPowYfzdCozuSkTjDOz5_Zm-w0c38Y_f8g/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI4NTE4/ODA4LTE2OTc4NzM0/MzgtOTgzMy5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Angry</t>
+  </si>
+  <si>
+    <t>Get Close</t>
+  </si>
+  <si>
+    <t>Bite My Head Off</t>
+  </si>
+  <si>
+    <t>Whole Wide World</t>
+  </si>
+  <si>
+    <t>Dreamy Skies</t>
+  </si>
+  <si>
+    <t>Mess It Up</t>
+  </si>
+  <si>
+    <t>Driving Me Too Hard</t>
+  </si>
+  <si>
+    <t>Tell Me Straight</t>
+  </si>
+  <si>
+    <t>Rolling Stone Blues</t>
+  </si>
+  <si>
+    <t>Depending on You</t>
+  </si>
+  <si>
+    <t>Live by the Sword</t>
+  </si>
+  <si>
+    <t>Sweet Sounds of Heaven [with Lady Gaga (vocals)]</t>
+  </si>
+  <si>
+    <t>Classic Rock, Hard Rock, Roots Rock</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το πρώτο στούντιο άλμπουμ των Rolling Stones με πρωτότυπο υλικό μετά από 18 χρόνια (από το A Bigger Bang του 2005). Σε παραγωγή του Andrew Watt, περιλαμβάνει τις τελευταίες ηχογραφήσεις του θρυλικού ντράμερ Charlie Watts σε δύο κομμάτια, καθώς και τεράστιες συμμετοχές (Lady Gaga, Stevie Wonder, Paul McCartney, Elton John).</t>
+  </si>
+  <si>
+    <t>Geffen Records, Polydor – 00602458393529 (LP, Album, Stereo, Gatefold)</t>
+  </si>
+  <si>
+    <t>Classic Rock, Glam-Rock - infused Pop Rock</t>
+  </si>
+  <si>
+    <t>Funk Rock, Saxophone-driven Rock</t>
+  </si>
+  <si>
+    <t>Rock Ballad, Roots Rock</t>
+  </si>
+  <si>
+    <t>Garage Rock, Proto-Punk</t>
+  </si>
+  <si>
+    <t>Post-Punk - tinged Rock, New Wave - influenced Rock</t>
+  </si>
+  <si>
+    <t>Acoustic Blues, Country Rock</t>
+  </si>
+  <si>
+    <t>Acoustic Blues, Traditional Blues Cover</t>
+  </si>
+  <si>
+    <t>Gospel Rock, Epic Soul Ballad</t>
+  </si>
+  <si>
+    <t>Slow Blues, Atmospheric Ballad</t>
+  </si>
+  <si>
+    <t>Mid-tempo Rock, Rolling Stones Roots</t>
+  </si>
+  <si>
+    <t>Boogie Rock, Classic 70s Stones Rock</t>
+  </si>
+  <si>
+    <t>Disco-Rock, Funk Rock</t>
+  </si>
+  <si>
+    <t>Δυναμικό εναρκτήριο track βασισμένο σε ένα κλασικό Keith Richards open-G κιθαριστικό riff, που πραγματεύεται μια τελματωμένη σχέση γεμάτη εκνευρισμό.</t>
+  </si>
+  <si>
+    <t>Αισθησιακό rock κομμάτι με έντονο brass section και σόλο σαξόφωνο από τον James Carter, ενισχυμένο από το διακριτικό πιάνο του Elton John.</t>
+  </si>
+  <si>
+    <t>Μελωδική country-rock μπαλάντα με pedal steel κιθάρες και έγχορδα, που εστιάζει στην απογοήτευση από την προδομένη εμπιστοσύνη.</t>
+  </si>
+  <si>
+    <t>Ένας garage-punk κεραυνός όπου ο Paul McCartney παίζει ένα παραμορφωμένο, επιθετικό fuzz μπάσο, με τον Jagger να επιτίθεται φωνητικά.</t>
+  </si>
+  <si>
+    <t>Ενεργητικό power-pop/rock κομμάτι με βρετανική post-punk αύρα, όπου ο Jagger αναπολεί τα δύσκολα νεανικά χρόνια στο Λονδίνο.</t>
+  </si>
+  <si>
+    <t>Ακουστικό, country-blues διάλειμμα με slide κιθάρα και φυσαρμόνικα, εκφράζοντας την ανάγκη αποσύνδεσης από τον ψηφιακό θόρυβο.</t>
+  </si>
+  <si>
+    <t>Disco-rock ρυθμός με το αυθεντικό groovy drum track του Charlie Watts, που σχολιάζει την ανθρώπινη τάση για αυτοκαταστροφή.</t>
+  </si>
+  <si>
+    <t>Αυθεντικό 70s Stones boogie με τη rhythm section των Charlie Watts και Bill Wyman να παίζει ξανά μαζί μετά από τρεις δεκαετίες.</t>
+  </si>
+  <si>
+    <t>Χαρακτηριστικός Keith Richards mid-tempo ρυθμός με country-rock αποχρώσεις για την ασφυκτική πίεση μιας σχέσης.</t>
+  </si>
+  <si>
+    <t>Σκοτεινή, ατμοσφαιρική μπαλάντα με κύρια φωνητικά από τον Keith Richards, ο οποίος αναμετράται με τη φθαρτότητα και το άγνωστο μέλλον.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Επικό 7λεπτο gospel/soul κομμάτι με συγκλονιστικό φωνητικό διάλογο Mick Jagger και Lady Gaga, πλαισιωμένο από το πιάνο και Rhodes του Stevie Wonder.
+</t>
+  </si>
+  <si>
+    <t>Λιτή, συγκινητική επιστροφή στις ρίζες με διασκευή του Muddy Waters μόνο από τους Mick Jagger (φυσαρμόνικα/φωνή) και Keith Richards (ακουστική κιθάρα).</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2926,6 +3137,12 @@
     <font>
       <sz val="8"/>
       <color theme="10"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="161"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Tahoma"/>
       <family val="2"/>
       <charset val="161"/>
@@ -2973,7 +3190,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3007,6 +3224,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3313,7 +3533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -4351,6 +4571,70 @@
       </c>
       <c r="J32" s="11" t="s">
         <v>947</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="84" x14ac:dyDescent="0.25">
+      <c r="A33" s="6">
+        <v>33253932</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>956</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>955</v>
+      </c>
+      <c r="D33" s="6">
+        <v>1981</v>
+      </c>
+      <c r="E33" s="10">
+        <v>3.94</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>966</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>967</v>
+      </c>
+      <c r="I33" s="11" t="s">
+        <v>957</v>
+      </c>
+      <c r="J33" s="11" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+      <c r="A34" s="6">
+        <v>28518808</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>982</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>983</v>
+      </c>
+      <c r="D34" s="6">
+        <v>2023</v>
+      </c>
+      <c r="E34" s="10">
+        <v>3.08</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>998</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>999</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>1000</v>
+      </c>
+      <c r="I34" s="11" t="s">
+        <v>984</v>
+      </c>
+      <c r="J34" s="11" t="s">
+        <v>985</v>
       </c>
     </row>
   </sheetData>
@@ -4415,6 +4699,10 @@
     <hyperlink ref="J31" r:id="rId58" xr:uid="{6E83A0B5-25C8-4527-A2C1-368E190DF4BF}"/>
     <hyperlink ref="I32" r:id="rId59" xr:uid="{AC32B278-CEC9-4643-B124-1F81CDC65266}"/>
     <hyperlink ref="J32" r:id="rId60" xr:uid="{CCA851C3-A0FC-424B-8F6D-38C0FDFC9C81}"/>
+    <hyperlink ref="I33" r:id="rId61" xr:uid="{F3AD3E6F-CC74-49B0-ADE8-22126BE46225}"/>
+    <hyperlink ref="J33" r:id="rId62" xr:uid="{3631FC2C-D978-4762-A2EC-CC8A5C60C54C}"/>
+    <hyperlink ref="I34" r:id="rId63" xr:uid="{809285F3-BBBD-48F0-BD7A-A1302B4236FA}"/>
+    <hyperlink ref="J34" r:id="rId64" xr:uid="{2CD14492-8591-4F36-9885-7C3437E6E821}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4422,7 +4710,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I277"/>
+  <dimension ref="A1:I296"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="3" bestFit="1" customWidth="1"/>
@@ -11451,7 +11739,7 @@
       </c>
       <c r="I258" s="6"/>
     </row>
-    <row r="259" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A259" s="6">
         <v>28251457</v>
       </c>
@@ -11967,6 +12255,521 @@
         <v>944</v>
       </c>
       <c r="I277" s="6"/>
+    </row>
+    <row r="278" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A278" s="6">
+        <v>33253932</v>
+      </c>
+      <c r="B278" s="6">
+        <v>1</v>
+      </c>
+      <c r="C278" s="7" t="s">
+        <v>959</v>
+      </c>
+      <c r="D278" s="7" t="s">
+        <v>968</v>
+      </c>
+      <c r="E278" s="8">
+        <v>4.46</v>
+      </c>
+      <c r="F278" s="8">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G278" s="8">
+        <v>4.8</v>
+      </c>
+      <c r="H278" s="9" t="s">
+        <v>969</v>
+      </c>
+      <c r="I278" s="6" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="279" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A279" s="6">
+        <v>33253932</v>
+      </c>
+      <c r="B279" s="6">
+        <v>2</v>
+      </c>
+      <c r="C279" s="7" t="s">
+        <v>960</v>
+      </c>
+      <c r="D279" s="7" t="s">
+        <v>970</v>
+      </c>
+      <c r="E279" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="F279" s="8">
+        <v>4.8</v>
+      </c>
+      <c r="G279" s="8">
+        <v>4.7</v>
+      </c>
+      <c r="H279" s="9" t="s">
+        <v>976</v>
+      </c>
+      <c r="I279" s="6"/>
+    </row>
+    <row r="280" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A280" s="6">
+        <v>33253932</v>
+      </c>
+      <c r="B280" s="6">
+        <v>3</v>
+      </c>
+      <c r="C280" s="7" t="s">
+        <v>961</v>
+      </c>
+      <c r="D280" s="7" t="s">
+        <v>971</v>
+      </c>
+      <c r="E280" s="8">
+        <v>4.41</v>
+      </c>
+      <c r="F280" s="8">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G280" s="8">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H280" s="9" t="s">
+        <v>977</v>
+      </c>
+      <c r="I280" s="6"/>
+    </row>
+    <row r="281" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A281" s="6">
+        <v>33253932</v>
+      </c>
+      <c r="B281" s="6">
+        <v>4</v>
+      </c>
+      <c r="C281" s="7" t="s">
+        <v>962</v>
+      </c>
+      <c r="D281" s="7" t="s">
+        <v>972</v>
+      </c>
+      <c r="E281" s="8">
+        <v>4.33</v>
+      </c>
+      <c r="F281" s="8">
+        <v>4.7</v>
+      </c>
+      <c r="G281" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H281" s="9" t="s">
+        <v>978</v>
+      </c>
+      <c r="I281" s="6"/>
+    </row>
+    <row r="282" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A282" s="6">
+        <v>33253932</v>
+      </c>
+      <c r="B282" s="6">
+        <v>5</v>
+      </c>
+      <c r="C282" s="7" t="s">
+        <v>965</v>
+      </c>
+      <c r="D282" s="7" t="s">
+        <v>973</v>
+      </c>
+      <c r="E282" s="8">
+        <v>4.07</v>
+      </c>
+      <c r="F282" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G282" s="8">
+        <v>4.7</v>
+      </c>
+      <c r="H282" s="9" t="s">
+        <v>979</v>
+      </c>
+      <c r="I282" s="6"/>
+    </row>
+    <row r="283" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A283" s="6">
+        <v>33253932</v>
+      </c>
+      <c r="B283" s="6">
+        <v>6</v>
+      </c>
+      <c r="C283" s="7" t="s">
+        <v>963</v>
+      </c>
+      <c r="D283" s="7" t="s">
+        <v>974</v>
+      </c>
+      <c r="E283" s="8">
+        <v>3.82</v>
+      </c>
+      <c r="F283" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="G283" s="8">
+        <v>4.7</v>
+      </c>
+      <c r="H283" s="9" t="s">
+        <v>980</v>
+      </c>
+      <c r="I283" s="6"/>
+    </row>
+    <row r="284" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A284" s="6">
+        <v>33253932</v>
+      </c>
+      <c r="B284" s="6">
+        <v>7</v>
+      </c>
+      <c r="C284" s="7" t="s">
+        <v>964</v>
+      </c>
+      <c r="D284" s="7" t="s">
+        <v>975</v>
+      </c>
+      <c r="E284" s="8">
+        <v>3.91</v>
+      </c>
+      <c r="F284" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="G284" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H284" s="9" t="s">
+        <v>981</v>
+      </c>
+      <c r="I284" s="6"/>
+    </row>
+    <row r="285" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A285" s="6">
+        <v>28518808</v>
+      </c>
+      <c r="B285" s="6">
+        <v>1</v>
+      </c>
+      <c r="C285" s="7" t="s">
+        <v>986</v>
+      </c>
+      <c r="D285" s="7" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E285" s="8">
+        <v>3.44</v>
+      </c>
+      <c r="F285" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="G285" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="H285" s="9" t="s">
+        <v>1013</v>
+      </c>
+      <c r="I285" s="6"/>
+    </row>
+    <row r="286" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A286" s="6">
+        <v>28518808</v>
+      </c>
+      <c r="B286" s="6">
+        <v>2</v>
+      </c>
+      <c r="C286" s="7" t="s">
+        <v>987</v>
+      </c>
+      <c r="D286" s="7" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E286" s="8">
+        <v>3.39</v>
+      </c>
+      <c r="F286" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="G286" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="H286" s="9" t="s">
+        <v>1014</v>
+      </c>
+      <c r="I286" s="6"/>
+    </row>
+    <row r="287" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A287" s="6">
+        <v>28518808</v>
+      </c>
+      <c r="B287" s="6">
+        <v>3</v>
+      </c>
+      <c r="C287" s="7" t="s">
+        <v>995</v>
+      </c>
+      <c r="D287" s="7" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E287" s="8">
+        <v>3.36</v>
+      </c>
+      <c r="F287" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="G287" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="H287" s="9" t="s">
+        <v>1015</v>
+      </c>
+      <c r="I287" s="6"/>
+    </row>
+    <row r="288" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A288" s="6">
+        <v>28518808</v>
+      </c>
+      <c r="B288" s="6">
+        <v>4</v>
+      </c>
+      <c r="C288" s="7" t="s">
+        <v>988</v>
+      </c>
+      <c r="D288" s="7" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E288" s="8">
+        <v>3.35</v>
+      </c>
+      <c r="F288" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="G288" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="H288" s="9" t="s">
+        <v>1016</v>
+      </c>
+      <c r="I288" s="6"/>
+    </row>
+    <row r="289" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A289" s="6">
+        <v>28518808</v>
+      </c>
+      <c r="B289" s="6">
+        <v>5</v>
+      </c>
+      <c r="C289" s="7" t="s">
+        <v>989</v>
+      </c>
+      <c r="D289" s="7" t="s">
+        <v>1005</v>
+      </c>
+      <c r="E289" s="8">
+        <v>3.34</v>
+      </c>
+      <c r="F289" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="G289" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="H289" s="9" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I289" s="6"/>
+    </row>
+    <row r="290" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A290" s="6">
+        <v>28518808</v>
+      </c>
+      <c r="B290" s="6">
+        <v>6</v>
+      </c>
+      <c r="C290" s="7" t="s">
+        <v>990</v>
+      </c>
+      <c r="D290" s="7" t="s">
+        <v>1006</v>
+      </c>
+      <c r="E290" s="8">
+        <v>3.24</v>
+      </c>
+      <c r="F290" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="G290" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="H290" s="9" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I290" s="6"/>
+    </row>
+    <row r="291" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A291" s="6">
+        <v>28518808</v>
+      </c>
+      <c r="B291" s="6">
+        <v>7</v>
+      </c>
+      <c r="C291" s="7" t="s">
+        <v>991</v>
+      </c>
+      <c r="D291" s="7" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E291" s="8">
+        <v>3.27</v>
+      </c>
+      <c r="F291" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="G291" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="H291" s="9" t="s">
+        <v>1019</v>
+      </c>
+      <c r="I291" s="6"/>
+    </row>
+    <row r="292" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A292" s="6">
+        <v>28518808</v>
+      </c>
+      <c r="B292" s="6">
+        <v>8</v>
+      </c>
+      <c r="C292" s="7" t="s">
+        <v>996</v>
+      </c>
+      <c r="D292" s="7" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E292" s="8">
+        <v>3.21</v>
+      </c>
+      <c r="F292" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="G292" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="H292" s="9" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I292" s="6"/>
+    </row>
+    <row r="293" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A293" s="6">
+        <v>28518808</v>
+      </c>
+      <c r="B293" s="6">
+        <v>9</v>
+      </c>
+      <c r="C293" s="7" t="s">
+        <v>992</v>
+      </c>
+      <c r="D293" s="7" t="s">
+        <v>1010</v>
+      </c>
+      <c r="E293" s="8">
+        <v>3.15</v>
+      </c>
+      <c r="F293" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="G293" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="H293" s="9" t="s">
+        <v>1021</v>
+      </c>
+      <c r="I293" s="6"/>
+    </row>
+    <row r="294" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A294" s="6">
+        <v>28518808</v>
+      </c>
+      <c r="B294" s="6">
+        <v>10</v>
+      </c>
+      <c r="C294" s="7" t="s">
+        <v>993</v>
+      </c>
+      <c r="D294" s="7" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E294" s="8">
+        <v>3.07</v>
+      </c>
+      <c r="F294" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="G294" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="H294" s="9" t="s">
+        <v>1022</v>
+      </c>
+      <c r="I294" s="6"/>
+    </row>
+    <row r="295" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A295" s="6">
+        <v>28518808</v>
+      </c>
+      <c r="B295" s="6">
+        <v>11</v>
+      </c>
+      <c r="C295" s="7" t="s">
+        <v>997</v>
+      </c>
+      <c r="D295" s="7" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E295" s="8">
+        <v>3.72</v>
+      </c>
+      <c r="F295" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G295" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H295" s="9" t="s">
+        <v>1023</v>
+      </c>
+      <c r="I295" s="6"/>
+    </row>
+    <row r="296" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A296" s="6">
+        <v>28518808</v>
+      </c>
+      <c r="B296" s="6">
+        <v>12</v>
+      </c>
+      <c r="C296" s="7" t="s">
+        <v>994</v>
+      </c>
+      <c r="D296" s="7" t="s">
+        <v>1007</v>
+      </c>
+      <c r="E296" s="8">
+        <v>3.31</v>
+      </c>
+      <c r="F296" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="G296" s="12">
+        <v>4</v>
+      </c>
+      <c r="H296" s="9" t="s">
+        <v>1024</v>
+      </c>
+      <c r="I296" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E744ACA6-0131-46FB-A453-9E525DC76747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01A0C4F6-1BBC-4C5A-9063-7473DA72F27F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
     <sheet name="tracks" sheetId="1" r:id="rId2"/>
+    <sheet name="info" sheetId="6" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1175" uniqueCount="1025">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="1094">
   <si>
     <t>No</t>
   </si>
@@ -3097,13 +3098,423 @@
   </si>
   <si>
     <t>Λιτή, συγκινητική επιστροφή στις ρίζες με διασκευή του Muddy Waters μόνο από τους Mick Jagger (φυσαρμόνικα/φωνή) και Keith Richards (ακουστική κιθάρα).</t>
+  </si>
+  <si>
+    <t>Darkfighter</t>
+  </si>
+  <si>
+    <t>Mercy</t>
+  </si>
+  <si>
+    <t>Redemption</t>
+  </si>
+  <si>
+    <t>Sweet Life</t>
+  </si>
+  <si>
+    <t>Before The Fire</t>
+  </si>
+  <si>
+    <t>Mosaic</t>
+  </si>
+  <si>
+    <t>Rival Sons</t>
+  </si>
+  <si>
+    <t>Lightbringer</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/28649152-Rival-Sons-Lightbringer</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/Hia-Q4AieKm7vpoWAqRJouyEG16AoRqo9cA3osB0s00/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI4NjQ5/MTUyLTE2OTc4MDc2/NzgtMjc1Mi5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το δεύτερο μέρος του διπλού μουσικού εγχειρήματος του συγκροτήματος για το 2023 (συνέχεια του *Darkfighter*), σε παραγωγή του πιστού συνεργάτη τους Dave Cobb. Ένας δίσκος γεμάτος κινηματογραφική ένταση, θεματική συνοχή και ωμό, αναλογικό ροκ συναίσθημα.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blues Rock, Hard Rock, Classic Rock, Roots Rock, Heavy Psych </t>
+  </si>
+  <si>
+    <t>Έπος 9 λεπτών που ενώνει τα δύο άλμπουμ, ξεκινώντας με 12χορδη ακουστική κιθάρα και φτάνοντας σε μια σαρωτική hard prog κορύφωση. Δυναμική εισαγωγή με βαριά riff, επικό χτίσιμο και την αλάνθαστη, ψυχωμένη ερμηνεία του Jay Buchanan.</t>
+  </si>
+  <si>
+    <t>Heavy Psych, Multi-Part Epic, Art Rock</t>
+  </si>
+  <si>
+    <t>Garage Rock, Soul-infused Hard Rock</t>
+  </si>
+  <si>
+    <t>Ρυθμικό, κοφτό heavy blues κομμάτι που εστιάζει στην ανάγκη επίδειξης ανθρωπιάς και συμπόνιας στις δύσκολες στιγμές.</t>
+  </si>
+  <si>
+    <t>Acoustic Ballad, Gospel-tinged Rock</t>
+  </si>
+  <si>
+    <t>Μελωδική ακουστική μπαλάντα με βαθιές ρίζες στο gospel και στο Southern rock, με θέμα τη συγχώρεση του εαυτού μας.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ένα εξωστρεφές, χορευτικό rock 'n' roll κομμάτι με glam/boogie αισθητική, που υμνεί την απόλαυση της καθημερινότητας.</t>
+  </si>
+  <si>
+    <t>Boogie Rock, 70s Proto-Punk-infused Rock</t>
+  </si>
+  <si>
+    <t>Heavy Blues, Vintage Zeppelin-esque Rock</t>
+  </si>
+  <si>
+    <t>Spiritual Rock, Anthemic Heavy Soul</t>
+  </si>
+  <si>
+    <t>Συγκινητικό κλείσιμο με gospel φωνητικά και επιβλητικά τύμπανα, που πραγματεύεται τη συνένωση των σπασμένων κομματιών της ζωής σε ένα ενιαίο, όμορφο σύνολο.</t>
+  </si>
+  <si>
+    <t>Βαρύ blues-rock με vintage fuzz κιθάρες, άμεση αναφορά στον τίτλο του ντεμπούτου άλμπουμ της μπάντας και αναστοχασμό της διαδρομής τους.</t>
+  </si>
+  <si>
+    <t>Atlantic, Low Country Sound – 075678615024 (LP, Album, Stereo)</t>
+  </si>
+  <si>
+    <t>The Riven</t>
+  </si>
+  <si>
+    <t>Peace And Conflict</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/2Fz_z1dVZaQXaXXMWc4UoGCTIQm5CleXvTqK5a1dPvo/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI1NDEy/MjgxLTE3ODU5MjI5/ODUtMTQzNC5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/25412281-The-Riven-Peace-And-Conflict</t>
+  </si>
+  <si>
+    <t>On Time</t>
+  </si>
+  <si>
+    <t>The Taker</t>
+  </si>
+  <si>
+    <t>La Puerta Del Tiempo</t>
+  </si>
+  <si>
+    <t>On Top Of Evil</t>
+  </si>
+  <si>
+    <t>Fly Free</t>
+  </si>
+  <si>
+    <t>Sundown</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Classic 70s Rock, Twin-Guitar Hard Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Heavy Blues Rock, Power Rock]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Hard Rock [Heavy Soul, Blues Ballad, 70s Proto-Doom]</t>
+  </si>
+  <si>
+    <t>Folk Rock [Spanish Classical, Acoustic Interlude (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Psychedelic Rock [Heavy Psych, Occult Rock, Twin-Lead Metal]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Psychedelic Rock [Heavy Blues, Vintage Doom Rock	]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Classic Rock [Arena Hard Rock, Melodic Retro-Rock]</t>
+  </si>
+  <si>
+    <t>Folk Rock, Blues Rock [Acoustic Blues, Country-tinged Interlude]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Heavy Psych, Proto-Metal, Epic Blues Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Retro-Rock, 70s Classic Rock, Blues Rock]</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το δεύτερο ολοκληρωμένο άλμπουμ της σουηδικής μπάντας (Limited Edition 500 copies σε πορτοκαλί βινύλιο). Ηχογραφήθηκε στο La Cabana Studio (Borrby) από τον Arnau Díaz και έγινε ηχοληψία/mastering από τον Ola Ersfjord. Ένας δίσκος με έντονο vintage 70s χαρακτήρα, αναλογική ζεστασιά και occult ατμόσφαιρα.</t>
+  </si>
+  <si>
+    <t>The Sign Records – CRC 025 (LP, Album, Limited Edition, Orange)</t>
+  </si>
+  <si>
+    <t>Εκρηκτική έναρξη με γρήγορο hard rock τέμπο, διπλά κιθαριστικά σόλο και στίχους για την πίεση του χρόνου και την ανάγκη δράσης.</t>
+  </si>
+  <si>
+    <t>Δυναμικό heavy rock κομμάτι με έντονο rhythm section, που στηλιτεύει τους τοξικούς, ιδιοτελείς ανθρώπους που απομυζούν τους γύρω τους.</t>
+  </si>
+  <si>
+    <t>Το ομώνυμο αργό blues-rock έπος, όπου η Ekebergh δίνει μία από τις πιο συγκλονιστικές και συναισθηματικές ερμηνείες της καριέρας της.</t>
+  </si>
+  <si>
+    <t>Σύντομο, ατμοσφαιρικό ακουστικό ιντερλούδιο με ισπανικές κλασικές κιθάρες, το οποίο λειτουργεί ως γέφυρα για το επόμενο κομμάτι.</t>
+  </si>
+  <si>
+    <t>Αποκορύφωμα του άλμπουμ με heavy psych riffing και επική occult rock ατμόσφαιρα αφιερωμένη σε μια μυθική ουράνια μορφή.</t>
+  </si>
+  <si>
+    <t>Σκοτεινό heavy blues με αργόσυρτο ρυθμό και proto-doom υπόβαθρο, επικεντρωμένο στην ανθρώπινη διαφθορά.</t>
+  </si>
+  <si>
+    <t>Εξωστρεφής, ρυθμικός 70s classic rock rocker με εξαιρετικά sing-along φωνητικά και μήνυμα απελευθέρωσης.</t>
+  </si>
+  <si>
+    <t>Ακουστική folk-blues ανάπαυλα με μελαγχολική μελωδία και ατμόσφαιρα ηλιοβασιλέματος.</t>
+  </si>
+  <si>
+    <t>Επιβλητικό 6λεπτο φινάλε που κλιμακώνεται από σκοτεινό blues σε ένα σαρωτικό heavy metal κρεσέντο για την αποδοχή της θνητότητας.</t>
+  </si>
+  <si>
+    <t>Sorceress Of The Sky</t>
+  </si>
+  <si>
+    <t>1. Compositional_Value (Συνθετική Αξία)</t>
+  </si>
+  <si>
+    <r>
+      <t>Τι μετράμε:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Την ίδια την καλλιτεχνική και εσωτερική αξία της μουσικής και στιχουργικής σύνθεσης. Εξετάζουμε τη δομή του κομματιού, την έμπνευση στα riff και τις μελωδίες, την αρμονική εξέλιξη, την ενορχηστρωτική μαεστρία, τη συναισθηματική φόρτιση και το πόσο "γεμάτο" και άρτιο είναι το δημιούργημα καθαυτό, ανεξάρτητα από το πώς έχει ηχογραφηθεί.</t>
+    </r>
+  </si>
+  <si>
+    <t>Τι βαθμολογούμε (Κριτήρια):</t>
+  </si>
+  <si>
+    <r>
+      <t>Δομή &amp; Ροή:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Πώς εξελίσσεται το κομμάτι από την αρχή μέχρι το τέλος (π.χ. αν έχει έξυπνες εναλλαγές, χτισίματα, κορυφώσεις ή αν είναι επαναλαμβανόμενο).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Ερμηνεία &amp; Πάθος:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Η εκτελεστική δεινότητα και η ψυχή που βγάζουν τα φωνητικά και τα όργανα (π.χ. η θεατρικότητα ή η δραματικότητα σε ένα έπος ή μια μπαλάντα).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Μουσική Ταυτότητα:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Πόσο μοναδικό, χαρακτηριστικό ή στιβαρό είναι το αποτύπωμα του κομματιού μέσα στον δίσκο.</t>
+    </r>
+  </si>
+  <si>
+    <t>2. Audiophile_Interest (Ακουστικό / Ηχητικό Ενδιαφέρον)</t>
+  </si>
+  <si>
+    <r>
+      <t>Τι μετράμε:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Την ποιότητα της παραγωγής, της μίξης, του mastering και το πώς αποδίδεται ηχητικά το βινύλιο πάνω στο αναλογικό σου σύστημα (πικάπ Technics με Sumiko cartridge και ενισχυτή Rotel). Εδώ δεν κρίνουμε αν η σύνθεση είναι καλή, αλλά </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>πώς ακούγεται</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> στο αυτί: το ηχητικό βάθος, η διαύγεια των οργάνων, η αναπνοή του χώρου, η δυναμική περιοχή και η ζεστασιά της αναλογικής αποτύπωσης.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Δυναμικό Εύρος (Dynamic Range):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Η ικανότητα του κομμάτιού να αναπνέει από τα χαμηλόφωνα στα δυνατά σημεία χωρίς υπερσυμπίεση (brickwalling).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Διαχωρισμός Οργάνων &amp; Στερεοφωνική Εικόνα:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Πόσο καθαρά διακρίνονται οι δίδυμες κιθάρες, το μπάσο και τα τύμπανα στο στερεοφωνικό πεδίο (soundstage) ή αν η μίξη είναι θολή και "λασπωμένη".</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Αναλογική Συμπεριφορά στο Βινύλιο:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Πώς αντιδρά η αυλάκωση του δίσκου στις συχνότητες του συγκεκριμένου κομματιού (π.χ. αν τα μπάσα είναι γεμάτα και οι ψηλές συχνότητες δεν ξυρίζουν).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Με λίγα λόγια, το </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Compositional_Value</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> αφορά το </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>τι γράφτηκε</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (η ψυχή και η τέχνη της σύνθεσης), ενώ το </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Audiophile_Interest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> αφορά το </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>πως γράφτηκε και αποδίδεται</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (η τεχνική της ηχογράφησης και η ηχητική απόλαυση στο πικάπ σου).</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3146,6 +3557,30 @@
       <name val="Tahoma"/>
       <family val="2"/>
       <charset val="161"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -3190,7 +3625,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3227,6 +3662,21 @@
     </xf>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3533,7 +3983,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -4635,6 +5085,70 @@
       </c>
       <c r="J34" s="11" t="s">
         <v>985</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+      <c r="A35" s="6">
+        <v>28649152</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D35" s="6">
+        <v>2023</v>
+      </c>
+      <c r="E35" s="10">
+        <v>3.47</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>1036</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>1035</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>1049</v>
+      </c>
+      <c r="I35" s="11" t="s">
+        <v>1033</v>
+      </c>
+      <c r="J35" s="11" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+      <c r="A36" s="6">
+        <v>25412281</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D36" s="6">
+        <v>2022</v>
+      </c>
+      <c r="E36" s="10">
+        <v>3.41</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>1069</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>1070</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>1071</v>
+      </c>
+      <c r="I36" s="11" t="s">
+        <v>1053</v>
+      </c>
+      <c r="J36" s="11" t="s">
+        <v>1052</v>
       </c>
     </row>
   </sheetData>
@@ -4703,6 +5217,10 @@
     <hyperlink ref="J33" r:id="rId62" xr:uid="{3631FC2C-D978-4762-A2EC-CC8A5C60C54C}"/>
     <hyperlink ref="I34" r:id="rId63" xr:uid="{809285F3-BBBD-48F0-BD7A-A1302B4236FA}"/>
     <hyperlink ref="J34" r:id="rId64" xr:uid="{2CD14492-8591-4F36-9885-7C3437E6E821}"/>
+    <hyperlink ref="I35" r:id="rId65" xr:uid="{3089CEA5-B4D3-4CF8-8369-656AF5B6317D}"/>
+    <hyperlink ref="J35" r:id="rId66" xr:uid="{9D002A99-727C-4388-B0E6-A0286BC1AB53}"/>
+    <hyperlink ref="J36" r:id="rId67" xr:uid="{2575D056-1912-4177-AEBE-B4E01DCEF8FA}"/>
+    <hyperlink ref="I36" r:id="rId68" xr:uid="{209C362D-EC30-4A00-A0B8-501F369CD679}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4710,7 +5228,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I296"/>
+  <dimension ref="A1:I311"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="3" bestFit="1" customWidth="1"/>
@@ -12771,8 +13289,530 @@
       </c>
       <c r="I296" s="6"/>
     </row>
+    <row r="297" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A297" s="6">
+        <v>28649152</v>
+      </c>
+      <c r="B297" s="6">
+        <v>1</v>
+      </c>
+      <c r="C297" s="7" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D297" s="7" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E297" s="8">
+        <v>3.66</v>
+      </c>
+      <c r="F297" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G297" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H297" s="9" t="s">
+        <v>1037</v>
+      </c>
+      <c r="I297" s="6"/>
+    </row>
+    <row r="298" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A298" s="6">
+        <v>28649152</v>
+      </c>
+      <c r="B298" s="6">
+        <v>2</v>
+      </c>
+      <c r="C298" s="7" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D298" s="7" t="s">
+        <v>1039</v>
+      </c>
+      <c r="E298" s="8">
+        <v>3.51</v>
+      </c>
+      <c r="F298" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="G298" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="H298" s="9" t="s">
+        <v>1040</v>
+      </c>
+      <c r="I298" s="6"/>
+    </row>
+    <row r="299" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A299" s="6">
+        <v>28649152</v>
+      </c>
+      <c r="B299" s="6">
+        <v>3</v>
+      </c>
+      <c r="C299" s="7" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D299" s="7" t="s">
+        <v>1041</v>
+      </c>
+      <c r="E299" s="8">
+        <v>3.43</v>
+      </c>
+      <c r="F299" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="G299" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="H299" s="9" t="s">
+        <v>1042</v>
+      </c>
+      <c r="I299" s="6"/>
+    </row>
+    <row r="300" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A300" s="6">
+        <v>28649152</v>
+      </c>
+      <c r="B300" s="6">
+        <v>4</v>
+      </c>
+      <c r="C300" s="7" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D300" s="7" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E300" s="8">
+        <v>3.51</v>
+      </c>
+      <c r="F300" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="G300" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="H300" s="9" t="s">
+        <v>1043</v>
+      </c>
+      <c r="I300" s="6"/>
+    </row>
+    <row r="301" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A301" s="6">
+        <v>28649152</v>
+      </c>
+      <c r="B301" s="6">
+        <v>5</v>
+      </c>
+      <c r="C301" s="7" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D301" s="7" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E301" s="8">
+        <v>3.48</v>
+      </c>
+      <c r="F301" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="G301" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="H301" s="9" t="s">
+        <v>1048</v>
+      </c>
+      <c r="I301" s="6"/>
+    </row>
+    <row r="302" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A302" s="6">
+        <v>28649152</v>
+      </c>
+      <c r="B302" s="6">
+        <v>6</v>
+      </c>
+      <c r="C302" s="7" t="s">
+        <v>1030</v>
+      </c>
+      <c r="D302" s="7" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E302" s="8">
+        <v>3.59</v>
+      </c>
+      <c r="F302" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="G302" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H302" s="9" t="s">
+        <v>1047</v>
+      </c>
+      <c r="I302" s="6"/>
+    </row>
+    <row r="303" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A303" s="6">
+        <v>25412281</v>
+      </c>
+      <c r="B303" s="6">
+        <v>1</v>
+      </c>
+      <c r="C303" s="7" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D303" s="7" t="s">
+        <v>1060</v>
+      </c>
+      <c r="E303" s="8">
+        <v>3.81</v>
+      </c>
+      <c r="F303" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="G303" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="H303" s="9" t="s">
+        <v>1072</v>
+      </c>
+      <c r="I303" s="6"/>
+    </row>
+    <row r="304" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A304" s="6">
+        <v>25412281</v>
+      </c>
+      <c r="B304" s="6">
+        <v>2</v>
+      </c>
+      <c r="C304" s="7" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D304" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E304" s="8">
+        <v>3.82</v>
+      </c>
+      <c r="F304" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="G304" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="H304" s="9" t="s">
+        <v>1073</v>
+      </c>
+      <c r="I304" s="6"/>
+    </row>
+    <row r="305" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A305" s="6">
+        <v>25412281</v>
+      </c>
+      <c r="B305" s="6">
+        <v>3</v>
+      </c>
+      <c r="C305" s="7" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D305" s="7" t="s">
+        <v>1062</v>
+      </c>
+      <c r="E305" s="8">
+        <v>3.81</v>
+      </c>
+      <c r="F305" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G305" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H305" s="9" t="s">
+        <v>1074</v>
+      </c>
+      <c r="I305" s="6"/>
+    </row>
+    <row r="306" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A306" s="6">
+        <v>25412281</v>
+      </c>
+      <c r="B306" s="6">
+        <v>4</v>
+      </c>
+      <c r="C306" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D306" s="7" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E306" s="8">
+        <v>3</v>
+      </c>
+      <c r="F306" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="G306" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="H306" s="9" t="s">
+        <v>1075</v>
+      </c>
+      <c r="I306" s="6"/>
+    </row>
+    <row r="307" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A307" s="6">
+        <v>25412281</v>
+      </c>
+      <c r="B307" s="6">
+        <v>5</v>
+      </c>
+      <c r="C307" s="7" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D307" s="7" t="s">
+        <v>1064</v>
+      </c>
+      <c r="E307" s="8">
+        <v>3.82</v>
+      </c>
+      <c r="F307" s="8">
+        <v>4</v>
+      </c>
+      <c r="G307" s="12">
+        <v>4</v>
+      </c>
+      <c r="H307" s="9" t="s">
+        <v>1076</v>
+      </c>
+      <c r="I307" s="6"/>
+    </row>
+    <row r="308" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A308" s="6">
+        <v>25412281</v>
+      </c>
+      <c r="B308" s="6">
+        <v>6</v>
+      </c>
+      <c r="C308" s="7" t="s">
+        <v>1057</v>
+      </c>
+      <c r="D308" s="7" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E308" s="8">
+        <v>3.86</v>
+      </c>
+      <c r="F308" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="G308" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="H308" s="9" t="s">
+        <v>1077</v>
+      </c>
+      <c r="I308" s="6"/>
+    </row>
+    <row r="309" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A309" s="6">
+        <v>25412281</v>
+      </c>
+      <c r="B309" s="6">
+        <v>7</v>
+      </c>
+      <c r="C309" s="7" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D309" s="7" t="s">
+        <v>1066</v>
+      </c>
+      <c r="E309" s="8">
+        <v>3.65</v>
+      </c>
+      <c r="F309" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="G309" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="H309" s="9" t="s">
+        <v>1078</v>
+      </c>
+      <c r="I309" s="6"/>
+    </row>
+    <row r="310" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A310" s="6">
+        <v>25412281</v>
+      </c>
+      <c r="B310" s="6">
+        <v>8</v>
+      </c>
+      <c r="C310" s="7" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D310" s="7" t="s">
+        <v>1067</v>
+      </c>
+      <c r="E310" s="8">
+        <v>3.28</v>
+      </c>
+      <c r="F310" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="G310" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="H310" s="9" t="s">
+        <v>1079</v>
+      </c>
+      <c r="I310" s="6"/>
+    </row>
+    <row r="311" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A311" s="6">
+        <v>25412281</v>
+      </c>
+      <c r="B311" s="6">
+        <v>9</v>
+      </c>
+      <c r="C311" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D311" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="E311" s="8">
+        <v>3.74</v>
+      </c>
+      <c r="F311" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="G311" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H311" s="9" t="s">
+        <v>1080</v>
+      </c>
+      <c r="I311" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8399EA5-E4D0-4141-B53B-8BEA60D97B6A}">
+  <dimension ref="A1:A29"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="14"/>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="14"/>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="14"/>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="14"/>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="16"/>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="17" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="16"/>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="17" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="16"/>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="17" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" ht="18" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="14"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="15" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="14"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="15" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="14"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="14"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="16"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="17" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="16"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="17" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="16"/>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="17" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01A0C4F6-1BBC-4C5A-9063-7473DA72F27F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58ABF085-9A7F-4236-ABE7-8F4FEE892DE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -207,9 +207,6 @@
     <t>RYM_Rating</t>
   </si>
   <si>
-    <t>Genres_Subgenres</t>
-  </si>
-  <si>
     <t>Notes_Hard_Facts</t>
   </si>
   <si>
@@ -3018,49 +3015,10 @@
     <t>Sweet Sounds of Heaven [with Lady Gaga (vocals)]</t>
   </si>
   <si>
-    <t>Classic Rock, Hard Rock, Roots Rock</t>
-  </si>
-  <si>
     <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το πρώτο στούντιο άλμπουμ των Rolling Stones με πρωτότυπο υλικό μετά από 18 χρόνια (από το A Bigger Bang του 2005). Σε παραγωγή του Andrew Watt, περιλαμβάνει τις τελευταίες ηχογραφήσεις του θρυλικού ντράμερ Charlie Watts σε δύο κομμάτια, καθώς και τεράστιες συμμετοχές (Lady Gaga, Stevie Wonder, Paul McCartney, Elton John).</t>
   </si>
   <si>
     <t>Geffen Records, Polydor – 00602458393529 (LP, Album, Stereo, Gatefold)</t>
-  </si>
-  <si>
-    <t>Classic Rock, Glam-Rock - infused Pop Rock</t>
-  </si>
-  <si>
-    <t>Funk Rock, Saxophone-driven Rock</t>
-  </si>
-  <si>
-    <t>Rock Ballad, Roots Rock</t>
-  </si>
-  <si>
-    <t>Garage Rock, Proto-Punk</t>
-  </si>
-  <si>
-    <t>Post-Punk - tinged Rock, New Wave - influenced Rock</t>
-  </si>
-  <si>
-    <t>Acoustic Blues, Country Rock</t>
-  </si>
-  <si>
-    <t>Acoustic Blues, Traditional Blues Cover</t>
-  </si>
-  <si>
-    <t>Gospel Rock, Epic Soul Ballad</t>
-  </si>
-  <si>
-    <t>Slow Blues, Atmospheric Ballad</t>
-  </si>
-  <si>
-    <t>Mid-tempo Rock, Rolling Stones Roots</t>
-  </si>
-  <si>
-    <t>Boogie Rock, Classic 70s Stones Rock</t>
-  </si>
-  <si>
-    <t>Disco-Rock, Funk Rock</t>
   </si>
   <si>
     <t>Δυναμικό εναρκτήριο track βασισμένο σε ένα κλασικό Keith Richards open-G κιθαριστικό riff, που πραγματεύεται μια τελματωμένη σχέση γεμάτη εκνευρισμό.</t>
@@ -3133,37 +3091,16 @@
     <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το δεύτερο μέρος του διπλού μουσικού εγχειρήματος του συγκροτήματος για το 2023 (συνέχεια του *Darkfighter*), σε παραγωγή του πιστού συνεργάτη τους Dave Cobb. Ένας δίσκος γεμάτος κινηματογραφική ένταση, θεματική συνοχή και ωμό, αναλογικό ροκ συναίσθημα.</t>
   </si>
   <si>
-    <t xml:space="preserve">Blues Rock, Hard Rock, Classic Rock, Roots Rock, Heavy Psych </t>
-  </si>
-  <si>
     <t>Έπος 9 λεπτών που ενώνει τα δύο άλμπουμ, ξεκινώντας με 12χορδη ακουστική κιθάρα και φτάνοντας σε μια σαρωτική hard prog κορύφωση. Δυναμική εισαγωγή με βαριά riff, επικό χτίσιμο και την αλάνθαστη, ψυχωμένη ερμηνεία του Jay Buchanan.</t>
   </si>
   <si>
-    <t>Heavy Psych, Multi-Part Epic, Art Rock</t>
-  </si>
-  <si>
-    <t>Garage Rock, Soul-infused Hard Rock</t>
-  </si>
-  <si>
     <t>Ρυθμικό, κοφτό heavy blues κομμάτι που εστιάζει στην ανάγκη επίδειξης ανθρωπιάς και συμπόνιας στις δύσκολες στιγμές.</t>
   </si>
   <si>
-    <t>Acoustic Ballad, Gospel-tinged Rock</t>
-  </si>
-  <si>
     <t>Μελωδική ακουστική μπαλάντα με βαθιές ρίζες στο gospel και στο Southern rock, με θέμα τη συγχώρεση του εαυτού μας.</t>
   </si>
   <si>
     <t xml:space="preserve"> Ένα εξωστρεφές, χορευτικό rock 'n' roll κομμάτι με glam/boogie αισθητική, που υμνεί την απόλαυση της καθημερινότητας.</t>
-  </si>
-  <si>
-    <t>Boogie Rock, 70s Proto-Punk-infused Rock</t>
-  </si>
-  <si>
-    <t>Heavy Blues, Vintage Zeppelin-esque Rock</t>
-  </si>
-  <si>
-    <t>Spiritual Rock, Anthemic Heavy Soul</t>
   </si>
   <si>
     <t>Συγκινητικό κλείσιμο με gospel φωνητικά και επιβλητικά τύμπανα, που πραγματεύεται τη συνένωση των σπασμένων κομματιών της ζωής σε ένα ενιαίο, όμορφο σύνολο.</t>
@@ -3508,6 +3445,69 @@
       </rPr>
       <t xml:space="preserve"> (η τεχνική της ηχογράφησης και η ηχητική απόλαυση στο πικάπ σου).</t>
     </r>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Roots Rock, Heavy Psych, Classic Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Progressive Rock [Heavy Psych, Multi-Part Epic, Art Rock]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Hard Rock [Garage Rock, Soul-infused Hard Rock]</t>
+  </si>
+  <si>
+    <t>Folk Rock, Blues Rock [Acoustic Ballad, Gospel-tinged Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Glam Rock [Boogie Rock, 70s Proto-Punk-infused Rock]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Hard Rock [Heavy Blues, Vintage Zeppelin-esque Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Gospel [	Spiritual Rock, Anthemic Heavy Soul]</t>
+  </si>
+  <si>
+    <t>Genres_Subgenres_Styles</t>
+  </si>
+  <si>
+    <t>Blues Rock, Pop Rock [Classic Rock, Hard Rock, Roots Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Classic Rock, Glam-Rock-infused Pop Rock]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Pop Rock [Funk Rock, Saxophone-driven Rock]</t>
+  </si>
+  <si>
+    <t>Pop Rock, Country Rock [Rock Ballad, Roots Rock]</t>
+  </si>
+  <si>
+    <t>Punk Rock, Hard Rock [Garage Rock, Proto-Punk]</t>
+  </si>
+  <si>
+    <t>Power Pop, Pop Rock [Post-Punk-tinged Rock, New Wave-influenced Rock]</t>
+  </si>
+  <si>
+    <t>Country Blues, Folk Rock [Acoustic Blues, Country Rock]</t>
+  </si>
+  <si>
+    <t>Dance-Rock, Pop Rock [Disco-Rock, Funk Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Boogie Rock, Classic 70s Stones Rock]</t>
+  </si>
+  <si>
+    <t>Pop Rock, Country Rock [Mid-tempo Rock, Rolling Stones Roots]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Art Rock [Slow Blues, Atmospheric Ballad]</t>
+  </si>
+  <si>
+    <t>Gospel, Soul Blues [Gospel Rock, Epic Soul Ballad]</t>
+  </si>
+  <si>
+    <t>Country Blues, Delta Blues [Acoustic Blues, Traditional Blues Cover]</t>
   </si>
 </sst>
 </file>
@@ -4016,19 +4016,19 @@
         <v>60</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>1080</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="J1" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="63" x14ac:dyDescent="0.25">
@@ -4054,13 +4054,13 @@
         <v>38</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="42" x14ac:dyDescent="0.25">
@@ -4086,13 +4086,13 @@
         <v>37</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="42" x14ac:dyDescent="0.25">
@@ -4100,10 +4100,10 @@
         <v>37452171</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D4" s="6">
         <v>2026</v>
@@ -4112,19 +4112,19 @@
         <v>3.73</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G4" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="H4" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="I4" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="J4" s="11" t="s">
         <v>75</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="42" x14ac:dyDescent="0.25">
@@ -4132,10 +4132,10 @@
         <v>33790944</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>125</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>126</v>
       </c>
       <c r="D5" s="6">
         <v>2025</v>
@@ -4144,19 +4144,19 @@
         <v>3.11</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G5" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I5" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="H5" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="I5" s="11" t="s">
+      <c r="J5" s="11" t="s">
         <v>128</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
@@ -4164,10 +4164,10 @@
         <v>926332</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>172</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>173</v>
       </c>
       <c r="D6" s="6">
         <v>1976</v>
@@ -4176,19 +4176,19 @@
         <v>3.29</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G6" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="I6" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="H6" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="I6" s="11" t="s">
+      <c r="J6" s="11" t="s">
         <v>176</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="63" x14ac:dyDescent="0.25">
@@ -4196,10 +4196,10 @@
         <v>10079558</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>178</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>179</v>
       </c>
       <c r="D7" s="6">
         <v>1978</v>
@@ -4208,19 +4208,19 @@
         <v>3.6</v>
       </c>
       <c r="F7" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="H7" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="I7" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="H7" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="I7" s="11" t="s">
+      <c r="J7" s="11" t="s">
         <v>183</v>
-      </c>
-      <c r="J7" s="11" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="63" x14ac:dyDescent="0.25">
@@ -4228,10 +4228,10 @@
         <v>2027786</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>210</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>211</v>
       </c>
       <c r="D8" s="6">
         <v>1976</v>
@@ -4240,19 +4240,19 @@
         <v>3.45</v>
       </c>
       <c r="F8" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="G8" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="H8" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="I8" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="I8" s="11" t="s">
+      <c r="J8" s="11" t="s">
         <v>215</v>
-      </c>
-      <c r="J8" s="11" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="63" x14ac:dyDescent="0.25">
@@ -4260,10 +4260,10 @@
         <v>35339929</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>240</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>241</v>
       </c>
       <c r="D9" s="6">
         <v>1977</v>
@@ -4272,19 +4272,19 @@
         <v>2.84</v>
       </c>
       <c r="F9" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="H9" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="I9" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="J9" s="11" t="s">
         <v>245</v>
-      </c>
-      <c r="J9" s="11" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="63" x14ac:dyDescent="0.25">
@@ -4292,10 +4292,10 @@
         <v>31106519</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D10" s="6">
         <v>1975</v>
@@ -4304,19 +4304,19 @@
         <v>3.69</v>
       </c>
       <c r="F10" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="G10" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="H10" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="I10" s="11" t="s">
         <v>274</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="J10" s="11" t="s">
         <v>275</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="63" x14ac:dyDescent="0.25">
@@ -4324,31 +4324,31 @@
         <v>21229427</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E11" s="10">
         <v>3.8</v>
       </c>
       <c r="F11" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="H11" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="H11" s="6" t="s">
-        <v>288</v>
-      </c>
       <c r="I11" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="J11" s="11" t="s">
         <v>290</v>
-      </c>
-      <c r="J11" s="11" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="73.5" x14ac:dyDescent="0.25">
@@ -4356,31 +4356,31 @@
         <v>24362534</v>
       </c>
       <c r="B12" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>314</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="D12" s="6" t="s">
         <v>315</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>316</v>
       </c>
       <c r="E12" s="10">
         <v>3.08</v>
       </c>
       <c r="F12" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="H12" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="I12" s="11" t="s">
         <v>319</v>
       </c>
-      <c r="H12" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="I12" s="11" t="s">
+      <c r="J12" s="11" t="s">
         <v>320</v>
-      </c>
-      <c r="J12" s="11" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="73.5" x14ac:dyDescent="0.25">
@@ -4388,31 +4388,31 @@
         <v>24831386</v>
       </c>
       <c r="B13" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="D13" s="6" t="s">
         <v>359</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>360</v>
       </c>
       <c r="E13" s="10">
         <v>4.1399999999999997</v>
       </c>
       <c r="F13" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="H13" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="G13" s="7" t="s">
-        <v>389</v>
-      </c>
-      <c r="H13" s="6" t="s">
+      <c r="I13" s="11" t="s">
         <v>362</v>
       </c>
-      <c r="I13" s="11" t="s">
+      <c r="J13" s="11" t="s">
         <v>363</v>
-      </c>
-      <c r="J13" s="11" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="63" x14ac:dyDescent="0.25">
@@ -4420,10 +4420,10 @@
         <v>6503426</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D14" s="6">
         <v>1973</v>
@@ -4432,19 +4432,19 @@
         <v>3.66</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="G14" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="I14" s="11" t="s">
         <v>404</v>
       </c>
-      <c r="H14" s="6" t="s">
-        <v>403</v>
-      </c>
-      <c r="I14" s="11" t="s">
+      <c r="J14" s="11" t="s">
         <v>405</v>
-      </c>
-      <c r="J14" s="11" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="63" x14ac:dyDescent="0.25">
@@ -4452,10 +4452,10 @@
         <v>920311</v>
       </c>
       <c r="B15" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>407</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>408</v>
       </c>
       <c r="D15" s="6">
         <v>1981</v>
@@ -4464,19 +4464,19 @@
         <v>3.45</v>
       </c>
       <c r="F15" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="G15" s="7" t="s">
         <v>425</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="H15" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="I15" s="11" t="s">
         <v>426</v>
       </c>
-      <c r="H15" s="6" t="s">
-        <v>409</v>
-      </c>
-      <c r="I15" s="11" t="s">
+      <c r="J15" s="11" t="s">
         <v>427</v>
-      </c>
-      <c r="J15" s="11" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="73.5" x14ac:dyDescent="0.25">
@@ -4484,10 +4484,10 @@
         <v>2138840</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D16" s="6">
         <v>1983</v>
@@ -4496,19 +4496,19 @@
         <v>3.48</v>
       </c>
       <c r="F16" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="H16" s="6" t="s">
         <v>440</v>
       </c>
-      <c r="G16" s="7" t="s">
-        <v>444</v>
-      </c>
-      <c r="H16" s="6" t="s">
+      <c r="I16" s="11" t="s">
         <v>441</v>
       </c>
-      <c r="I16" s="11" t="s">
+      <c r="J16" s="11" t="s">
         <v>442</v>
-      </c>
-      <c r="J16" s="11" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="84" x14ac:dyDescent="0.25">
@@ -4516,10 +4516,10 @@
         <v>10867099</v>
       </c>
       <c r="B17" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>466</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>467</v>
       </c>
       <c r="D17" s="6">
         <v>1992</v>
@@ -4528,19 +4528,19 @@
         <v>3.67</v>
       </c>
       <c r="F17" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="G17" s="7" t="s">
         <v>468</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="H17" s="6" t="s">
         <v>469</v>
       </c>
-      <c r="H17" s="6" t="s">
+      <c r="I17" s="11" t="s">
         <v>470</v>
       </c>
-      <c r="I17" s="11" t="s">
+      <c r="J17" s="11" t="s">
         <v>471</v>
-      </c>
-      <c r="J17" s="11" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="84" x14ac:dyDescent="0.25">
@@ -4548,10 +4548,10 @@
         <v>2797526</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D18" s="6">
         <v>1990</v>
@@ -4560,19 +4560,19 @@
         <v>3.55</v>
       </c>
       <c r="F18" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>536</v>
+      </c>
+      <c r="H18" s="6" t="s">
         <v>518</v>
       </c>
-      <c r="G18" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>519</v>
-      </c>
       <c r="I18" s="11" t="s">
+        <v>520</v>
+      </c>
+      <c r="J18" s="11" t="s">
         <v>521</v>
-      </c>
-      <c r="J18" s="11" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="63" x14ac:dyDescent="0.25">
@@ -4580,10 +4580,10 @@
         <v>28270285</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D19" s="6">
         <v>2023</v>
@@ -4592,19 +4592,19 @@
         <v>3.56</v>
       </c>
       <c r="F19" s="9" t="s">
+        <v>541</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>540</v>
+      </c>
+      <c r="H19" s="6" t="s">
         <v>542</v>
       </c>
-      <c r="G19" s="7" t="s">
-        <v>541</v>
-      </c>
-      <c r="H19" s="6" t="s">
+      <c r="I19" s="11" t="s">
         <v>543</v>
       </c>
-      <c r="I19" s="11" t="s">
+      <c r="J19" s="11" t="s">
         <v>544</v>
-      </c>
-      <c r="J19" s="11" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="63" x14ac:dyDescent="0.25">
@@ -4612,10 +4612,10 @@
         <v>24184766</v>
       </c>
       <c r="B20" s="7" t="s">
+        <v>581</v>
+      </c>
+      <c r="C20" s="7" t="s">
         <v>582</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>583</v>
       </c>
       <c r="D20" s="6">
         <v>2020</v>
@@ -4624,19 +4624,19 @@
         <v>3.51</v>
       </c>
       <c r="F20" s="9" t="s">
+        <v>583</v>
+      </c>
+      <c r="G20" s="7" t="s">
         <v>584</v>
       </c>
-      <c r="G20" s="7" t="s">
+      <c r="H20" s="6" t="s">
         <v>585</v>
       </c>
-      <c r="H20" s="6" t="s">
+      <c r="I20" s="11" t="s">
         <v>586</v>
       </c>
-      <c r="I20" s="11" t="s">
+      <c r="J20" s="11" t="s">
         <v>587</v>
-      </c>
-      <c r="J20" s="11" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
@@ -4644,10 +4644,10 @@
         <v>28074505</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D21" s="6">
         <v>2023</v>
@@ -4656,19 +4656,19 @@
         <v>3.57</v>
       </c>
       <c r="F21" s="9" t="s">
+        <v>618</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>621</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>622</v>
+      </c>
+      <c r="I21" s="11" t="s">
         <v>619</v>
       </c>
-      <c r="G21" s="7" t="s">
-        <v>622</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>623</v>
-      </c>
-      <c r="I21" s="11" t="s">
+      <c r="J21" s="11" t="s">
         <v>620</v>
-      </c>
-      <c r="J21" s="11" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="63" x14ac:dyDescent="0.25">
@@ -4676,10 +4676,10 @@
         <v>25695898</v>
       </c>
       <c r="B22" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>628</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>629</v>
       </c>
       <c r="D22" s="6">
         <v>1974</v>
@@ -4688,19 +4688,19 @@
         <v>3.8</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="G22" s="7" t="s">
+        <v>623</v>
+      </c>
+      <c r="H22" s="6" t="s">
         <v>624</v>
       </c>
-      <c r="H22" s="6" t="s">
+      <c r="I22" s="11" t="s">
         <v>625</v>
       </c>
-      <c r="I22" s="11" t="s">
+      <c r="J22" s="11" t="s">
         <v>626</v>
-      </c>
-      <c r="J22" s="11" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -4708,10 +4708,10 @@
         <v>11981817</v>
       </c>
       <c r="B23" s="7" t="s">
+        <v>662</v>
+      </c>
+      <c r="C23" s="7" t="s">
         <v>663</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>664</v>
       </c>
       <c r="D23" s="6">
         <v>1996</v>
@@ -4720,19 +4720,19 @@
         <v>3.94</v>
       </c>
       <c r="F23" s="9" t="s">
+        <v>666</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>709</v>
+      </c>
+      <c r="H23" s="6" t="s">
         <v>667</v>
       </c>
-      <c r="G23" s="7" t="s">
-        <v>710</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>668</v>
-      </c>
       <c r="I23" s="11" t="s">
+        <v>664</v>
+      </c>
+      <c r="J23" s="11" t="s">
         <v>665</v>
-      </c>
-      <c r="J23" s="11" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="42" x14ac:dyDescent="0.25">
@@ -4740,10 +4740,10 @@
         <v>29264422</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="D24" s="6">
         <v>1973</v>
@@ -4752,19 +4752,19 @@
         <v>3.58</v>
       </c>
       <c r="F24" s="9" t="s">
+        <v>707</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>725</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>708</v>
       </c>
-      <c r="G24" s="7" t="s">
-        <v>726</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>709</v>
-      </c>
       <c r="I24" s="11" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="42" x14ac:dyDescent="0.25">
@@ -4772,10 +4772,10 @@
         <v>28667458</v>
       </c>
       <c r="B25" s="7" t="s">
+        <v>735</v>
+      </c>
+      <c r="C25" s="7" t="s">
         <v>736</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>737</v>
       </c>
       <c r="D25" s="6">
         <v>2019</v>
@@ -4784,19 +4784,19 @@
         <v>3.49</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="G25" s="7" t="s">
+        <v>739</v>
+      </c>
+      <c r="H25" s="6" t="s">
         <v>740</v>
       </c>
-      <c r="H25" s="6" t="s">
-        <v>741</v>
-      </c>
       <c r="I25" s="11" t="s">
+        <v>737</v>
+      </c>
+      <c r="J25" s="11" t="s">
         <v>738</v>
-      </c>
-      <c r="J25" s="11" t="s">
-        <v>739</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="42" x14ac:dyDescent="0.25">
@@ -4804,10 +4804,10 @@
         <v>26857331</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="D26" s="6">
         <v>2023</v>
@@ -4816,19 +4816,19 @@
         <v>3.48</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="63" x14ac:dyDescent="0.25">
@@ -4836,10 +4836,10 @@
         <v>22420804</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="D27" s="6">
         <v>1970</v>
@@ -4848,19 +4848,19 @@
         <v>3.66</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="I27" s="11" t="s">
+        <v>784</v>
+      </c>
+      <c r="J27" s="11" t="s">
         <v>785</v>
-      </c>
-      <c r="J27" s="11" t="s">
-        <v>786</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
@@ -4868,10 +4868,10 @@
         <v>31880233</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="D28" s="6">
         <v>1976</v>
@@ -4880,19 +4880,19 @@
         <v>3.5</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="I28" s="11" t="s">
+        <v>809</v>
+      </c>
+      <c r="J28" s="11" t="s">
         <v>810</v>
-      </c>
-      <c r="J28" s="11" t="s">
-        <v>811</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="63" x14ac:dyDescent="0.25">
@@ -4900,10 +4900,10 @@
         <v>31700342</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="D29" s="6">
         <v>2019</v>
@@ -4912,19 +4912,19 @@
         <v>3.73</v>
       </c>
       <c r="F29" s="9" t="s">
+        <v>838</v>
+      </c>
+      <c r="G29" s="7" t="s">
         <v>839</v>
       </c>
-      <c r="G29" s="7" t="s">
+      <c r="H29" s="6" t="s">
         <v>840</v>
       </c>
-      <c r="H29" s="6" t="s">
-        <v>841</v>
-      </c>
       <c r="I29" s="11" t="s">
+        <v>836</v>
+      </c>
+      <c r="J29" s="11" t="s">
         <v>837</v>
-      </c>
-      <c r="J29" s="11" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="42" x14ac:dyDescent="0.25">
@@ -4932,10 +4932,10 @@
         <v>28251457</v>
       </c>
       <c r="B30" s="7" t="s">
+        <v>858</v>
+      </c>
+      <c r="C30" s="7" t="s">
         <v>859</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>860</v>
       </c>
       <c r="D30" s="6">
         <v>2023</v>
@@ -4944,19 +4944,19 @@
         <v>3.61</v>
       </c>
       <c r="F30" s="9" t="s">
+        <v>870</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>871</v>
       </c>
-      <c r="G30" s="7" t="s">
-        <v>873</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>872</v>
-      </c>
       <c r="I30" s="11" t="s">
+        <v>860</v>
+      </c>
+      <c r="J30" s="11" t="s">
         <v>861</v>
-      </c>
-      <c r="J30" s="11" t="s">
-        <v>862</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="42" x14ac:dyDescent="0.25">
@@ -4964,10 +4964,10 @@
         <v>26207852</v>
       </c>
       <c r="B31" s="7" t="s">
+        <v>887</v>
+      </c>
+      <c r="C31" s="7" t="s">
         <v>888</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>889</v>
       </c>
       <c r="D31" s="6">
         <v>2023</v>
@@ -4976,19 +4976,19 @@
         <v>3.29</v>
       </c>
       <c r="F31" s="9" t="s">
+        <v>902</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>904</v>
+      </c>
+      <c r="H31" s="6" t="s">
         <v>903</v>
       </c>
-      <c r="G31" s="7" t="s">
-        <v>905</v>
-      </c>
-      <c r="H31" s="6" t="s">
-        <v>904</v>
-      </c>
       <c r="I31" s="11" t="s">
+        <v>900</v>
+      </c>
+      <c r="J31" s="11" t="s">
         <v>901</v>
-      </c>
-      <c r="J31" s="11" t="s">
-        <v>902</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="42" x14ac:dyDescent="0.25">
@@ -4996,10 +4996,10 @@
         <v>3507697</v>
       </c>
       <c r="B32" s="7" t="s">
+        <v>933</v>
+      </c>
+      <c r="C32" s="7" t="s">
         <v>934</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>935</v>
       </c>
       <c r="D32" s="6">
         <v>1973</v>
@@ -5008,19 +5008,19 @@
         <v>3.29</v>
       </c>
       <c r="F32" s="9" t="s">
+        <v>935</v>
+      </c>
+      <c r="G32" s="7" t="s">
         <v>936</v>
       </c>
-      <c r="G32" s="7" t="s">
-        <v>937</v>
-      </c>
       <c r="H32" s="6" t="s">
+        <v>944</v>
+      </c>
+      <c r="I32" s="11" t="s">
         <v>945</v>
       </c>
-      <c r="I32" s="11" t="s">
+      <c r="J32" s="11" t="s">
         <v>946</v>
-      </c>
-      <c r="J32" s="11" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="84" x14ac:dyDescent="0.25">
@@ -5028,10 +5028,10 @@
         <v>33253932</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="D33" s="6">
         <v>1981</v>
@@ -5040,19 +5040,19 @@
         <v>3.94</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G33" s="7" t="s">
+        <v>965</v>
+      </c>
+      <c r="H33" s="6" t="s">
         <v>966</v>
       </c>
-      <c r="H33" s="6" t="s">
-        <v>967</v>
-      </c>
       <c r="I33" s="11" t="s">
+        <v>956</v>
+      </c>
+      <c r="J33" s="11" t="s">
         <v>957</v>
-      </c>
-      <c r="J33" s="11" t="s">
-        <v>958</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="42" x14ac:dyDescent="0.25">
@@ -5060,10 +5060,10 @@
         <v>28518808</v>
       </c>
       <c r="B34" s="7" t="s">
+        <v>981</v>
+      </c>
+      <c r="C34" s="7" t="s">
         <v>982</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>983</v>
       </c>
       <c r="D34" s="6">
         <v>2023</v>
@@ -5072,19 +5072,19 @@
         <v>3.08</v>
       </c>
       <c r="F34" s="9" t="s">
+        <v>1081</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>997</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>998</v>
       </c>
-      <c r="G34" s="7" t="s">
-        <v>999</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>1000</v>
-      </c>
       <c r="I34" s="11" t="s">
+        <v>983</v>
+      </c>
+      <c r="J34" s="11" t="s">
         <v>984</v>
-      </c>
-      <c r="J34" s="11" t="s">
-        <v>985</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="42" x14ac:dyDescent="0.25">
@@ -5092,10 +5092,10 @@
         <v>28649152</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>1031</v>
+        <v>1017</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>1032</v>
+        <v>1018</v>
       </c>
       <c r="D35" s="6">
         <v>2023</v>
@@ -5104,19 +5104,19 @@
         <v>3.47</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>1036</v>
+        <v>1073</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>1035</v>
+        <v>1021</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>1049</v>
+        <v>1028</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>1033</v>
+        <v>1019</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>1034</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="42" x14ac:dyDescent="0.25">
@@ -5124,10 +5124,10 @@
         <v>25412281</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>1050</v>
+        <v>1029</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>1051</v>
+        <v>1030</v>
       </c>
       <c r="D36" s="6">
         <v>2022</v>
@@ -5136,19 +5136,19 @@
         <v>3.41</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>1069</v>
+        <v>1048</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>1070</v>
+        <v>1049</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>1071</v>
+        <v>1050</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>1053</v>
+        <v>1032</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>1052</v>
+        <v>1031</v>
       </c>
     </row>
   </sheetData>
@@ -5251,25 +5251,25 @@
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>61</v>
+        <v>1080</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>60</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="H1" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="21" x14ac:dyDescent="0.25">
@@ -5739,13 +5739,13 @@
         <v>1</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F19" s="8">
         <v>3.5</v>
@@ -5754,7 +5754,7 @@
         <v>3.7</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I19" s="6"/>
     </row>
@@ -5766,13 +5766,13 @@
         <v>2</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F20" s="8">
         <v>3</v>
@@ -5781,7 +5781,7 @@
         <v>3.4</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I20" s="6"/>
     </row>
@@ -5793,13 +5793,13 @@
         <v>3</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F21" s="8">
         <v>3.5</v>
@@ -5808,7 +5808,7 @@
         <v>3.8</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I21" s="6"/>
     </row>
@@ -5820,13 +5820,13 @@
         <v>4</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F22" s="8">
         <v>3.5</v>
@@ -5835,7 +5835,7 @@
         <v>3.6</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I22" s="6"/>
     </row>
@@ -5847,13 +5847,13 @@
         <v>5</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F23" s="8">
         <v>4</v>
@@ -5862,7 +5862,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I23" s="6"/>
     </row>
@@ -5874,13 +5874,13 @@
         <v>6</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F24" s="8">
         <v>3</v>
@@ -5889,7 +5889,7 @@
         <v>3.5</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I24" s="6"/>
     </row>
@@ -5901,13 +5901,13 @@
         <v>7</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F25" s="8">
         <v>4</v>
@@ -5916,7 +5916,7 @@
         <v>4.2</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I25" s="6"/>
     </row>
@@ -5928,13 +5928,13 @@
         <v>8</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F26" s="8">
         <v>3.5</v>
@@ -5943,7 +5943,7 @@
         <v>3.7</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I26" s="6"/>
     </row>
@@ -5955,13 +5955,13 @@
         <v>9</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F27" s="8">
         <v>3</v>
@@ -5970,7 +5970,7 @@
         <v>3.4</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I27" s="6"/>
     </row>
@@ -5982,13 +5982,13 @@
         <v>10</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F28" s="8">
         <v>3</v>
@@ -5997,7 +5997,7 @@
         <v>3.5</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I28" s="6"/>
     </row>
@@ -6009,13 +6009,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D29" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="E29" s="8" t="s">
         <v>101</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>102</v>
       </c>
       <c r="F29" s="8">
         <v>3.5</v>
@@ -6024,7 +6024,7 @@
         <v>3.9</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I29" s="6"/>
     </row>
@@ -6036,10 +6036,10 @@
         <v>1</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E30" s="8">
         <v>3.63</v>
@@ -6051,7 +6051,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I30" s="6"/>
     </row>
@@ -6063,10 +6063,10 @@
         <v>2</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E31" s="8">
         <v>3.72</v>
@@ -6078,7 +6078,7 @@
         <v>4.5</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I31" s="6"/>
     </row>
@@ -6090,10 +6090,10 @@
         <v>3</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E32" s="8">
         <v>3.65</v>
@@ -6105,7 +6105,7 @@
         <v>4</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I32" s="6"/>
     </row>
@@ -6117,10 +6117,10 @@
         <v>4</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E33" s="8">
         <v>3.15</v>
@@ -6132,7 +6132,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I33" s="6"/>
     </row>
@@ -6144,10 +6144,10 @@
         <v>5</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E34" s="8">
         <v>3.35</v>
@@ -6159,7 +6159,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I34" s="6"/>
     </row>
@@ -6171,10 +6171,10 @@
         <v>6</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E35" s="8">
         <v>3.21</v>
@@ -6186,7 +6186,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I35" s="6"/>
     </row>
@@ -6198,10 +6198,10 @@
         <v>7</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E36" s="8">
         <v>3.12</v>
@@ -6213,7 +6213,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I36" s="6"/>
     </row>
@@ -6225,10 +6225,10 @@
         <v>8</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E37" s="8">
         <v>3.43</v>
@@ -6240,7 +6240,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I37" s="6"/>
     </row>
@@ -6252,10 +6252,10 @@
         <v>9</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E38" s="8">
         <v>3.62</v>
@@ -6267,7 +6267,7 @@
         <v>4.7</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I38" s="6"/>
     </row>
@@ -6279,10 +6279,10 @@
         <v>10</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E39" s="8">
         <v>3.15</v>
@@ -6294,7 +6294,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I39" s="6"/>
     </row>
@@ -6306,10 +6306,10 @@
         <v>1</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E40" s="8">
         <v>3.41</v>
@@ -6321,7 +6321,7 @@
         <v>4.2</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I40" s="6"/>
     </row>
@@ -6333,10 +6333,10 @@
         <v>2</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E41" s="8">
         <v>3.29</v>
@@ -6348,7 +6348,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I41" s="6"/>
     </row>
@@ -6360,10 +6360,10 @@
         <v>3</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E42" s="8">
         <v>3.03</v>
@@ -6375,7 +6375,7 @@
         <v>4.2</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I42" s="6"/>
     </row>
@@ -6387,10 +6387,10 @@
         <v>4</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E43" s="8">
         <v>3.08</v>
@@ -6402,7 +6402,7 @@
         <v>3.8</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I43" s="6"/>
     </row>
@@ -6414,10 +6414,10 @@
         <v>5</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E44" s="8">
         <v>3.28</v>
@@ -6429,7 +6429,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I44" s="6"/>
     </row>
@@ -6441,10 +6441,10 @@
         <v>6</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E45" s="8">
         <v>3.04</v>
@@ -6456,7 +6456,7 @@
         <v>4.3</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I45" s="6"/>
     </row>
@@ -6468,10 +6468,10 @@
         <v>7</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E46" s="8">
         <v>3.45</v>
@@ -6483,10 +6483,10 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="42" x14ac:dyDescent="0.25">
@@ -6497,10 +6497,10 @@
         <v>1</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E47" s="8">
         <v>3.91</v>
@@ -6512,10 +6512,10 @@
         <v>4.8</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -6526,10 +6526,10 @@
         <v>2</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E48" s="8">
         <v>3.63</v>
@@ -6541,7 +6541,7 @@
         <v>4.3</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I48" s="6"/>
     </row>
@@ -6553,10 +6553,10 @@
         <v>3</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E49" s="8">
         <v>4.04</v>
@@ -6568,7 +6568,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I49" s="6"/>
     </row>
@@ -6580,10 +6580,10 @@
         <v>4</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E50" s="8">
         <v>3.63</v>
@@ -6595,7 +6595,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I50" s="6"/>
     </row>
@@ -6607,10 +6607,10 @@
         <v>5</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E51" s="8">
         <v>3.67</v>
@@ -6622,10 +6622,10 @@
         <v>4.3</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -6636,10 +6636,10 @@
         <v>6</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E52" s="8">
         <v>4.03</v>
@@ -6651,7 +6651,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I52" s="6"/>
     </row>
@@ -6663,10 +6663,10 @@
         <v>7</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E53" s="8">
         <v>3.58</v>
@@ -6678,7 +6678,7 @@
         <v>4.3</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I53" s="6"/>
     </row>
@@ -6690,10 +6690,10 @@
         <v>8</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E54" s="8">
         <v>3.66</v>
@@ -6705,7 +6705,7 @@
         <v>4.7</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I54" s="6"/>
     </row>
@@ -6717,10 +6717,10 @@
         <v>9</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E55" s="8">
         <v>3.73</v>
@@ -6732,7 +6732,7 @@
         <v>4.5</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I55" s="6"/>
     </row>
@@ -6744,10 +6744,10 @@
         <v>1</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E56" s="8">
         <v>3.6</v>
@@ -6759,10 +6759,10 @@
         <v>4.2</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -6773,10 +6773,10 @@
         <v>2</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E57" s="8">
         <v>3.42</v>
@@ -6788,7 +6788,7 @@
         <v>4.5</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I57" s="6"/>
     </row>
@@ -6800,10 +6800,10 @@
         <v>3</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E58" s="8">
         <v>3.05</v>
@@ -6815,7 +6815,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I58" s="6"/>
     </row>
@@ -6827,10 +6827,10 @@
         <v>4</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E59" s="8">
         <v>3.44</v>
@@ -6842,7 +6842,7 @@
         <v>4.5</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I59" s="6"/>
     </row>
@@ -6854,10 +6854,10 @@
         <v>5</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E60" s="8">
         <v>3.34</v>
@@ -6869,7 +6869,7 @@
         <v>4.2</v>
       </c>
       <c r="H60" s="9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I60" s="6"/>
     </row>
@@ -6881,10 +6881,10 @@
         <v>6</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E61" s="8">
         <v>3.31</v>
@@ -6896,7 +6896,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I61" s="6"/>
     </row>
@@ -6908,10 +6908,10 @@
         <v>7</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E62" s="8">
         <v>2.97</v>
@@ -6923,7 +6923,7 @@
         <v>4</v>
       </c>
       <c r="H62" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I62" s="6"/>
     </row>
@@ -6935,10 +6935,10 @@
         <v>8</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E63" s="8">
         <v>2.96</v>
@@ -6950,7 +6950,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I63" s="6"/>
     </row>
@@ -6962,10 +6962,10 @@
         <v>9</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E64" s="8">
         <v>2.99</v>
@@ -6977,7 +6977,7 @@
         <v>4.7</v>
       </c>
       <c r="H64" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I64" s="6"/>
     </row>
@@ -6989,10 +6989,10 @@
         <v>1</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E65" s="8">
         <v>3.07</v>
@@ -7004,10 +7004,10 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -7018,10 +7018,10 @@
         <v>2</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E66" s="8">
         <v>2.81</v>
@@ -7033,7 +7033,7 @@
         <v>4.3</v>
       </c>
       <c r="H66" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I66" s="6"/>
     </row>
@@ -7045,10 +7045,10 @@
         <v>3</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E67" s="8">
         <v>3.31</v>
@@ -7060,7 +7060,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I67" s="6"/>
     </row>
@@ -7072,10 +7072,10 @@
         <v>4</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E68" s="8">
         <v>3.24</v>
@@ -7087,7 +7087,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H68" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I68" s="6"/>
     </row>
@@ -7099,10 +7099,10 @@
         <v>5</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E69" s="8">
         <v>3.27</v>
@@ -7114,7 +7114,7 @@
         <v>4.3</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I69" s="6"/>
     </row>
@@ -7126,10 +7126,10 @@
         <v>6</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E70" s="8">
         <v>3.51</v>
@@ -7141,7 +7141,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H70" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="I70" s="6"/>
     </row>
@@ -7153,10 +7153,10 @@
         <v>1</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E71" s="8">
         <v>4.17</v>
@@ -7168,10 +7168,10 @@
         <v>4.7</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -7182,10 +7182,10 @@
         <v>2</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E72" s="8">
         <v>3.52</v>
@@ -7197,10 +7197,10 @@
         <v>4.3</v>
       </c>
       <c r="H72" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I72" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -7211,10 +7211,10 @@
         <v>3</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E73" s="8">
         <v>2.91</v>
@@ -7226,7 +7226,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I73" s="6"/>
     </row>
@@ -7238,10 +7238,10 @@
         <v>4</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E74" s="8">
         <v>3.38</v>
@@ -7253,10 +7253,10 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H74" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I74" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="42" x14ac:dyDescent="0.25">
@@ -7267,10 +7267,10 @@
         <v>5</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E75" s="8">
         <v>3.67</v>
@@ -7282,7 +7282,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I75" s="6"/>
     </row>
@@ -7294,10 +7294,10 @@
         <v>6</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E76" s="8">
         <v>3.04</v>
@@ -7309,10 +7309,10 @@
         <v>4.5</v>
       </c>
       <c r="H76" s="9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I76" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="42" x14ac:dyDescent="0.25">
@@ -7323,10 +7323,10 @@
         <v>1</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E77" s="8">
         <v>3.86</v>
@@ -7338,7 +7338,7 @@
         <v>4.5</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="I77" s="6"/>
     </row>
@@ -7350,10 +7350,10 @@
         <v>2</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E78" s="8">
         <v>3.96</v>
@@ -7365,7 +7365,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H78" s="9" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="I78" s="6"/>
     </row>
@@ -7377,10 +7377,10 @@
         <v>3</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E79" s="8">
         <v>3.84</v>
@@ -7392,7 +7392,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="I79" s="6"/>
     </row>
@@ -7404,10 +7404,10 @@
         <v>4</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E80" s="8">
         <v>3.78</v>
@@ -7419,7 +7419,7 @@
         <v>4.5</v>
       </c>
       <c r="H80" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="I80" s="6"/>
     </row>
@@ -7431,10 +7431,10 @@
         <v>5</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E81" s="8">
         <v>3.67</v>
@@ -7446,7 +7446,7 @@
         <v>4.3</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="I81" s="6"/>
     </row>
@@ -7458,10 +7458,10 @@
         <v>6</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E82" s="8">
         <v>3.9</v>
@@ -7473,7 +7473,7 @@
         <v>4.8</v>
       </c>
       <c r="H82" s="9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I82" s="6"/>
     </row>
@@ -7485,10 +7485,10 @@
         <v>7</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E83" s="8">
         <v>4.34</v>
@@ -7500,10 +7500,10 @@
         <v>4.8</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="I83" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -7514,10 +7514,10 @@
         <v>1</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E84" s="8">
         <v>3.98</v>
@@ -7529,7 +7529,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H84" s="9" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="I84" s="6"/>
     </row>
@@ -7541,10 +7541,10 @@
         <v>2</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E85" s="8">
         <v>3.96</v>
@@ -7556,7 +7556,7 @@
         <v>4.5</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="I85" s="6"/>
     </row>
@@ -7568,10 +7568,10 @@
         <v>3</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E86" s="8">
         <v>3.22</v>
@@ -7583,7 +7583,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H86" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I86" s="6"/>
     </row>
@@ -7595,10 +7595,10 @@
         <v>4</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E87" s="8">
         <v>3.56</v>
@@ -7610,7 +7610,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I87" s="6"/>
     </row>
@@ -7622,10 +7622,10 @@
         <v>5</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E88" s="8">
         <v>2.93</v>
@@ -7637,7 +7637,7 @@
         <v>4.2</v>
       </c>
       <c r="H88" s="9" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="I88" s="6"/>
     </row>
@@ -7649,10 +7649,10 @@
         <v>6</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E89" s="8">
         <v>3.46</v>
@@ -7664,7 +7664,7 @@
         <v>4.5</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I89" s="6"/>
     </row>
@@ -7676,10 +7676,10 @@
         <v>7</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E90" s="8">
         <v>2.97</v>
@@ -7691,7 +7691,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H90" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="I90" s="6"/>
     </row>
@@ -7703,10 +7703,10 @@
         <v>8</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D91" s="7" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E91" s="8">
         <v>3.26</v>
@@ -7718,7 +7718,7 @@
         <v>4.5</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="I91" s="6"/>
     </row>
@@ -7730,10 +7730,10 @@
         <v>9</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E92" s="8">
         <v>3.7</v>
@@ -7745,7 +7745,7 @@
         <v>4.5</v>
       </c>
       <c r="H92" s="9" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="I92" s="6"/>
     </row>
@@ -7757,10 +7757,10 @@
         <v>10</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E93" s="8">
         <v>3.47</v>
@@ -7772,7 +7772,7 @@
         <v>4.3</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="I93" s="6"/>
     </row>
@@ -7784,10 +7784,10 @@
         <v>11</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E94" s="8">
         <v>3.47</v>
@@ -7799,7 +7799,7 @@
         <v>4.7</v>
       </c>
       <c r="H94" s="9" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I94" s="6"/>
     </row>
@@ -7811,10 +7811,10 @@
         <v>12</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E95" s="8">
         <v>3.4</v>
@@ -7826,7 +7826,7 @@
         <v>4.75</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="I95" s="6"/>
     </row>
@@ -7838,10 +7838,10 @@
         <v>1</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D96" s="7" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E96" s="8">
         <v>4.47</v>
@@ -7853,10 +7853,10 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H96" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -7867,10 +7867,10 @@
         <v>2</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D97" s="7" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E97" s="8">
         <v>4.1900000000000004</v>
@@ -7882,7 +7882,7 @@
         <v>4.5</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I97" s="6"/>
     </row>
@@ -7894,10 +7894,10 @@
         <v>3</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D98" s="7" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E98" s="8">
         <v>3.63</v>
@@ -7909,7 +7909,7 @@
         <v>4.3</v>
       </c>
       <c r="H98" s="9" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="I98" s="6"/>
     </row>
@@ -7921,10 +7921,10 @@
         <v>4</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D99" s="7" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E99" s="8">
         <v>4.58</v>
@@ -7936,10 +7936,10 @@
         <v>4.8</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I99" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -7950,10 +7950,10 @@
         <v>5</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E100" s="8">
         <v>3.86</v>
@@ -7965,7 +7965,7 @@
         <v>4.5</v>
       </c>
       <c r="H100" s="9" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I100" s="6"/>
     </row>
@@ -7977,10 +7977,10 @@
         <v>6</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E101" s="8">
         <v>4.2699999999999996</v>
@@ -7992,7 +7992,7 @@
         <v>4.7</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="I101" s="6"/>
     </row>
@@ -8004,10 +8004,10 @@
         <v>7</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E102" s="8">
         <v>4.0999999999999996</v>
@@ -8019,7 +8019,7 @@
         <v>4.75</v>
       </c>
       <c r="H102" s="9" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="I102" s="6"/>
     </row>
@@ -8031,10 +8031,10 @@
         <v>8</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E103" s="8">
         <v>4.49</v>
@@ -8046,10 +8046,10 @@
         <v>4.8499999999999996</v>
       </c>
       <c r="H103" s="9" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="I103" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -8060,10 +8060,10 @@
         <v>1</v>
       </c>
       <c r="C104" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="D104" s="7" t="s">
         <v>390</v>
-      </c>
-      <c r="D104" s="7" t="s">
-        <v>391</v>
       </c>
       <c r="E104" s="8">
         <v>3.87</v>
@@ -8075,7 +8075,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H104" s="9" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="I104" s="6"/>
     </row>
@@ -8087,10 +8087,10 @@
         <v>2</v>
       </c>
       <c r="C105" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="D105" s="7" t="s">
         <v>393</v>
-      </c>
-      <c r="D105" s="7" t="s">
-        <v>394</v>
       </c>
       <c r="E105" s="8">
         <v>3.82</v>
@@ -8102,7 +8102,7 @@
         <v>4.5</v>
       </c>
       <c r="H105" s="9" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I105" s="6"/>
     </row>
@@ -8114,10 +8114,10 @@
         <v>3</v>
       </c>
       <c r="C106" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="D106" s="7" t="s">
         <v>396</v>
-      </c>
-      <c r="D106" s="7" t="s">
-        <v>397</v>
       </c>
       <c r="E106" s="8">
         <v>3.65</v>
@@ -8129,10 +8129,10 @@
         <v>4.45</v>
       </c>
       <c r="H106" s="9" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="I106" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -8143,10 +8143,10 @@
         <v>4</v>
       </c>
       <c r="C107" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="D107" s="7" t="s">
         <v>399</v>
-      </c>
-      <c r="D107" s="7" t="s">
-        <v>400</v>
       </c>
       <c r="E107" s="8">
         <v>3.57</v>
@@ -8158,7 +8158,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H107" s="9" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="I107" s="6"/>
     </row>
@@ -8170,10 +8170,10 @@
         <v>1</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D108" s="7" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E108" s="8">
         <v>4.25</v>
@@ -8185,7 +8185,7 @@
         <v>3.7</v>
       </c>
       <c r="H108" s="9" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="I108" s="6"/>
     </row>
@@ -8197,10 +8197,10 @@
         <v>2</v>
       </c>
       <c r="C109" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="D109" s="7" t="s">
         <v>411</v>
-      </c>
-      <c r="D109" s="7" t="s">
-        <v>412</v>
       </c>
       <c r="E109" s="8">
         <v>4.25</v>
@@ -8212,10 +8212,10 @@
         <v>3.6</v>
       </c>
       <c r="H109" s="9" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="I109" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="21" x14ac:dyDescent="0.25">
@@ -8226,10 +8226,10 @@
         <v>3</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E110" s="8">
         <v>3.5</v>
@@ -8241,7 +8241,7 @@
         <v>3.45</v>
       </c>
       <c r="H110" s="9" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I110" s="6"/>
     </row>
@@ -8253,10 +8253,10 @@
         <v>4</v>
       </c>
       <c r="C111" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="D111" s="7" t="s">
         <v>414</v>
-      </c>
-      <c r="D111" s="7" t="s">
-        <v>415</v>
       </c>
       <c r="E111" s="8">
         <v>3.5</v>
@@ -8268,7 +8268,7 @@
         <v>3.6</v>
       </c>
       <c r="H111" s="9" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="I111" s="6"/>
     </row>
@@ -8280,10 +8280,10 @@
         <v>5</v>
       </c>
       <c r="C112" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="D112" s="7" t="s">
         <v>416</v>
-      </c>
-      <c r="D112" s="7" t="s">
-        <v>417</v>
       </c>
       <c r="E112" s="8">
         <v>4.33</v>
@@ -8295,7 +8295,7 @@
         <v>3.8</v>
       </c>
       <c r="H112" s="9" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I112" s="6"/>
     </row>
@@ -8307,10 +8307,10 @@
         <v>6</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E113" s="8">
         <v>4</v>
@@ -8322,7 +8322,7 @@
         <v>3.7</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="I113" s="6"/>
     </row>
@@ -8334,10 +8334,10 @@
         <v>7</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D114" s="7" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E114" s="8">
         <v>4.25</v>
@@ -8349,7 +8349,7 @@
         <v>3.55</v>
       </c>
       <c r="H114" s="9" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="I114" s="6"/>
     </row>
@@ -8361,10 +8361,10 @@
         <v>8</v>
       </c>
       <c r="C115" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="D115" s="7" t="s">
         <v>420</v>
-      </c>
-      <c r="D115" s="7" t="s">
-        <v>421</v>
       </c>
       <c r="E115" s="8">
         <v>4</v>
@@ -8376,7 +8376,7 @@
         <v>3.9</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="I115" s="6"/>
     </row>
@@ -8388,10 +8388,10 @@
         <v>9</v>
       </c>
       <c r="C116" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="D116" s="7" t="s">
         <v>422</v>
-      </c>
-      <c r="D116" s="7" t="s">
-        <v>423</v>
       </c>
       <c r="E116" s="8">
         <v>3.5</v>
@@ -8403,7 +8403,7 @@
         <v>3.2</v>
       </c>
       <c r="H116" s="9" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I116" s="6"/>
     </row>
@@ -8415,10 +8415,10 @@
         <v>10</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D117" s="7" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E117" s="8">
         <v>3.75</v>
@@ -8430,7 +8430,7 @@
         <v>3.6</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="I117" s="6"/>
     </row>
@@ -8442,10 +8442,10 @@
         <v>1</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D118" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E118" s="8">
         <v>3.59</v>
@@ -8457,10 +8457,10 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H118" s="9" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="I118" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="21" x14ac:dyDescent="0.25">
@@ -8471,10 +8471,10 @@
         <v>2</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D119" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E119" s="8">
         <v>3.38</v>
@@ -8486,7 +8486,7 @@
         <v>4</v>
       </c>
       <c r="H119" s="9" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="I119" s="6"/>
     </row>
@@ -8498,10 +8498,10 @@
         <v>3</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D120" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E120" s="8">
         <v>3.27</v>
@@ -8513,7 +8513,7 @@
         <v>4.05</v>
       </c>
       <c r="H120" s="9" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="I120" s="6"/>
     </row>
@@ -8525,10 +8525,10 @@
         <v>4</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D121" s="7" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E121" s="8">
         <v>3.58</v>
@@ -8540,10 +8540,10 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="H121" s="9" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="I121" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="122" spans="1:9" ht="21" x14ac:dyDescent="0.25">
@@ -8554,10 +8554,10 @@
         <v>5</v>
       </c>
       <c r="C122" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D122" s="7" t="s">
         <v>453</v>
-      </c>
-      <c r="D122" s="7" t="s">
-        <v>454</v>
       </c>
       <c r="E122" s="8">
         <v>3.49</v>
@@ -8569,7 +8569,7 @@
         <v>4</v>
       </c>
       <c r="H122" s="9" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="I122" s="6"/>
     </row>
@@ -8581,10 +8581,10 @@
         <v>6</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D123" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E123" s="8">
         <v>3.48</v>
@@ -8596,7 +8596,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H123" s="9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="I123" s="6"/>
     </row>
@@ -8608,10 +8608,10 @@
         <v>7</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D124" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E124" s="8">
         <v>3.34</v>
@@ -8623,7 +8623,7 @@
         <v>3.95</v>
       </c>
       <c r="H124" s="9" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="I124" s="6"/>
     </row>
@@ -8635,10 +8635,10 @@
         <v>8</v>
       </c>
       <c r="C125" s="7" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D125" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E125" s="8">
         <v>3.65</v>
@@ -8650,10 +8650,10 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="H125" s="9" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="I125" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="21" x14ac:dyDescent="0.25">
@@ -8664,10 +8664,10 @@
         <v>9</v>
       </c>
       <c r="C126" s="7" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D126" s="7" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E126" s="8">
         <v>3.21</v>
@@ -8679,7 +8679,7 @@
         <v>3.9</v>
       </c>
       <c r="H126" s="9" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="I126" s="6"/>
     </row>
@@ -8691,10 +8691,10 @@
         <v>10</v>
       </c>
       <c r="C127" s="7" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D127" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E127" s="8">
         <v>3.35</v>
@@ -8706,7 +8706,7 @@
         <v>4.2</v>
       </c>
       <c r="H127" s="9" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I127" s="6"/>
     </row>
@@ -8718,10 +8718,10 @@
         <v>1</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D128" s="7" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E128" s="8">
         <v>4.0999999999999996</v>
@@ -8733,7 +8733,7 @@
         <v>4.25</v>
       </c>
       <c r="H128" s="9" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="I128" s="6"/>
     </row>
@@ -8745,10 +8745,10 @@
         <v>2</v>
       </c>
       <c r="C129" s="7" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D129" s="7" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E129" s="8">
         <v>3.72</v>
@@ -8760,7 +8760,7 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="I129" s="6"/>
     </row>
@@ -8772,10 +8772,10 @@
         <v>3</v>
       </c>
       <c r="C130" s="7" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D130" s="7" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E130" s="8">
         <v>3.81</v>
@@ -8787,7 +8787,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H130" s="9" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="I130" s="6"/>
     </row>
@@ -8799,10 +8799,10 @@
         <v>4</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D131" s="7" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E131" s="8">
         <v>3.57</v>
@@ -8814,7 +8814,7 @@
         <v>4.3</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="I131" s="6"/>
     </row>
@@ -8826,10 +8826,10 @@
         <v>5</v>
       </c>
       <c r="C132" s="7" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D132" s="7" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E132" s="8">
         <v>3.98</v>
@@ -8841,7 +8841,7 @@
         <v>4.05</v>
       </c>
       <c r="H132" s="9" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="I132" s="6"/>
     </row>
@@ -8853,10 +8853,10 @@
         <v>6</v>
       </c>
       <c r="C133" s="7" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D133" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E133" s="8">
         <v>3.7</v>
@@ -8868,7 +8868,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="I133" s="6"/>
     </row>
@@ -8880,10 +8880,10 @@
         <v>7</v>
       </c>
       <c r="C134" s="7" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D134" s="7" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E134" s="8">
         <v>3.55</v>
@@ -8895,7 +8895,7 @@
         <v>4.2</v>
       </c>
       <c r="H134" s="9" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="I134" s="6"/>
     </row>
@@ -8907,10 +8907,10 @@
         <v>8</v>
       </c>
       <c r="C135" s="7" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D135" s="7" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E135" s="8">
         <v>3.55</v>
@@ -8922,7 +8922,7 @@
         <v>4.45</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="I135" s="6"/>
     </row>
@@ -8934,10 +8934,10 @@
         <v>9</v>
       </c>
       <c r="C136" s="7" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D136" s="7" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E136" s="8">
         <v>3.55</v>
@@ -8949,7 +8949,7 @@
         <v>4.25</v>
       </c>
       <c r="H136" s="9" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="I136" s="6"/>
     </row>
@@ -8961,10 +8961,10 @@
         <v>10</v>
       </c>
       <c r="C137" s="7" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D137" s="7" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E137" s="8">
         <v>3.68</v>
@@ -8976,7 +8976,7 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="I137" s="6"/>
     </row>
@@ -8988,10 +8988,10 @@
         <v>11</v>
       </c>
       <c r="C138" s="7" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D138" s="7" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E138" s="8">
         <v>3.89</v>
@@ -9003,7 +9003,7 @@
         <v>4.3499999999999996</v>
       </c>
       <c r="H138" s="9" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="I138" s="6"/>
     </row>
@@ -9015,10 +9015,10 @@
         <v>12</v>
       </c>
       <c r="C139" s="7" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D139" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E139" s="8">
         <v>3.87</v>
@@ -9030,7 +9030,7 @@
         <v>4.3</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="I139" s="6"/>
     </row>
@@ -9042,10 +9042,10 @@
         <v>1</v>
       </c>
       <c r="C140" s="7" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D140" s="7" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E140" s="8">
         <v>3.87</v>
@@ -9057,7 +9057,7 @@
         <v>4.3</v>
       </c>
       <c r="H140" s="9" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="I140" s="6"/>
     </row>
@@ -9069,10 +9069,10 @@
         <v>2</v>
       </c>
       <c r="C141" s="7" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D141" s="7" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E141" s="8">
         <v>3.91</v>
@@ -9084,7 +9084,7 @@
         <v>4.25</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I141" s="6"/>
     </row>
@@ -9096,10 +9096,10 @@
         <v>3</v>
       </c>
       <c r="C142" s="7" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D142" s="7" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E142" s="8">
         <v>3.97</v>
@@ -9111,7 +9111,7 @@
         <v>4.45</v>
       </c>
       <c r="H142" s="9" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="I142" s="6"/>
     </row>
@@ -9123,10 +9123,10 @@
         <v>4</v>
       </c>
       <c r="C143" s="7" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D143" s="7" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E143" s="8">
         <v>3.87</v>
@@ -9138,7 +9138,7 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="I143" s="6"/>
     </row>
@@ -9150,10 +9150,10 @@
         <v>5</v>
       </c>
       <c r="C144" s="7" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D144" s="7" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E144" s="8">
         <v>3.76</v>
@@ -9165,7 +9165,7 @@
         <v>4.2</v>
       </c>
       <c r="H144" s="9" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="I144" s="6"/>
     </row>
@@ -9177,10 +9177,10 @@
         <v>6</v>
       </c>
       <c r="C145" s="7" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D145" s="7" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="E145" s="8">
         <v>2.3199999999999998</v>
@@ -9192,7 +9192,7 @@
         <v>4</v>
       </c>
       <c r="H145" s="9" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="I145" s="6"/>
     </row>
@@ -9204,10 +9204,10 @@
         <v>7</v>
       </c>
       <c r="C146" s="7" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D146" s="7" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E146" s="8">
         <v>3.54</v>
@@ -9219,7 +9219,7 @@
         <v>4.2</v>
       </c>
       <c r="H146" s="9" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="I146" s="6"/>
     </row>
@@ -9231,10 +9231,10 @@
         <v>8</v>
       </c>
       <c r="C147" s="7" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D147" s="7" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E147" s="8">
         <v>3.69</v>
@@ -9246,7 +9246,7 @@
         <v>4.3</v>
       </c>
       <c r="H147" s="9" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I147" s="6"/>
     </row>
@@ -9258,10 +9258,10 @@
         <v>9</v>
       </c>
       <c r="C148" s="7" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D148" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E148" s="8">
         <v>3.65</v>
@@ -9273,7 +9273,7 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="H148" s="9" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I148" s="6"/>
     </row>
@@ -9285,10 +9285,10 @@
         <v>10</v>
       </c>
       <c r="C149" s="7" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D149" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E149" s="8">
         <v>3.64</v>
@@ -9300,7 +9300,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H149" s="9" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="I149" s="6"/>
     </row>
@@ -9312,10 +9312,10 @@
         <v>11</v>
       </c>
       <c r="C150" s="7" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D150" s="7" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E150" s="8">
         <v>3.77</v>
@@ -9327,7 +9327,7 @@
         <v>4.5</v>
       </c>
       <c r="H150" s="9" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="I150" s="6"/>
     </row>
@@ -9339,10 +9339,10 @@
         <v>1</v>
       </c>
       <c r="C151" s="7" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D151" s="7" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E151" s="8">
         <v>3.31</v>
@@ -9354,7 +9354,7 @@
         <v>4.3499999999999996</v>
       </c>
       <c r="H151" s="9" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="I151" s="6"/>
     </row>
@@ -9366,10 +9366,10 @@
         <v>2</v>
       </c>
       <c r="C152" s="7" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D152" s="7" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="E152" s="8">
         <v>3.7</v>
@@ -9381,7 +9381,7 @@
         <v>4.25</v>
       </c>
       <c r="H152" s="9" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="I152" s="6"/>
     </row>
@@ -9393,10 +9393,10 @@
         <v>3</v>
       </c>
       <c r="C153" s="7" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D153" s="7" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E153" s="8">
         <v>4.07</v>
@@ -9408,7 +9408,7 @@
         <v>4.7</v>
       </c>
       <c r="H153" s="9" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="I153" s="6"/>
     </row>
@@ -9420,7 +9420,7 @@
         <v>4</v>
       </c>
       <c r="C154" s="7" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D154" s="7" t="s">
         <v>15</v>
@@ -9435,7 +9435,7 @@
         <v>4.3499999999999996</v>
       </c>
       <c r="H154" s="9" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="I154" s="6"/>
     </row>
@@ -9447,10 +9447,10 @@
         <v>5</v>
       </c>
       <c r="C155" s="7" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D155" s="7" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E155" s="8">
         <v>3.73</v>
@@ -9462,7 +9462,7 @@
         <v>4.55</v>
       </c>
       <c r="H155" s="9" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="I155" s="6"/>
     </row>
@@ -9474,10 +9474,10 @@
         <v>6</v>
       </c>
       <c r="C156" s="7" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D156" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E156" s="8">
         <v>3.65</v>
@@ -9489,7 +9489,7 @@
         <v>4.45</v>
       </c>
       <c r="H156" s="9" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="I156" s="6"/>
     </row>
@@ -9501,10 +9501,10 @@
         <v>1</v>
       </c>
       <c r="C157" s="7" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D157" s="7" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E157" s="8">
         <v>3.77</v>
@@ -9516,7 +9516,7 @@
         <v>3.7</v>
       </c>
       <c r="H157" s="9" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="I157" s="6"/>
     </row>
@@ -9528,10 +9528,10 @@
         <v>2</v>
       </c>
       <c r="C158" s="7" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D158" s="7" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E158" s="8">
         <v>3.53</v>
@@ -9543,7 +9543,7 @@
         <v>3.4</v>
       </c>
       <c r="H158" s="9" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="I158" s="6"/>
     </row>
@@ -9555,10 +9555,10 @@
         <v>3</v>
       </c>
       <c r="C159" s="7" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D159" s="7" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E159" s="8">
         <v>3.7</v>
@@ -9570,7 +9570,7 @@
         <v>3.5</v>
       </c>
       <c r="H159" s="9" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I159" s="6"/>
     </row>
@@ -9582,10 +9582,10 @@
         <v>4</v>
       </c>
       <c r="C160" s="7" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D160" s="7" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E160" s="8">
         <v>3.71</v>
@@ -9597,7 +9597,7 @@
         <v>3.6</v>
       </c>
       <c r="H160" s="9" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="I160" s="6"/>
     </row>
@@ -9609,10 +9609,10 @@
         <v>5</v>
       </c>
       <c r="C161" s="7" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D161" s="7" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E161" s="8">
         <v>3.67</v>
@@ -9624,7 +9624,7 @@
         <v>3.6</v>
       </c>
       <c r="H161" s="9" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="I161" s="6"/>
     </row>
@@ -9636,10 +9636,10 @@
         <v>6</v>
       </c>
       <c r="C162" s="7" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D162" s="7" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E162" s="8">
         <v>3.57</v>
@@ -9651,7 +9651,7 @@
         <v>3.4</v>
       </c>
       <c r="H162" s="9" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="I162" s="6"/>
     </row>
@@ -9663,10 +9663,10 @@
         <v>7</v>
       </c>
       <c r="C163" s="7" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D163" s="7" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E163" s="8">
         <v>3.96</v>
@@ -9678,7 +9678,7 @@
         <v>3.8</v>
       </c>
       <c r="H163" s="9" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="I163" s="6"/>
     </row>
@@ -9690,10 +9690,10 @@
         <v>1</v>
       </c>
       <c r="C164" s="7" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D164" s="7" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E164" s="8">
         <v>4.1399999999999997</v>
@@ -9705,7 +9705,7 @@
         <v>4.3</v>
       </c>
       <c r="H164" s="9" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="I164" s="6"/>
     </row>
@@ -9717,10 +9717,10 @@
         <v>2</v>
       </c>
       <c r="C165" s="7" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D165" s="7" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E165" s="8">
         <v>4.13</v>
@@ -9732,7 +9732,7 @@
         <v>4.25</v>
       </c>
       <c r="H165" s="9" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="I165" s="6"/>
     </row>
@@ -9744,10 +9744,10 @@
         <v>3</v>
       </c>
       <c r="C166" s="7" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D166" s="7" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E166" s="8">
         <v>3.88</v>
@@ -9759,7 +9759,7 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="H166" s="9" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="I166" s="6"/>
     </row>
@@ -9771,10 +9771,10 @@
         <v>4</v>
       </c>
       <c r="C167" s="7" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D167" s="7" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E167" s="8">
         <v>4.1900000000000004</v>
@@ -9786,7 +9786,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H167" s="9" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="I167" s="6"/>
     </row>
@@ -9798,10 +9798,10 @@
         <v>5</v>
       </c>
       <c r="C168" s="7" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D168" s="7" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E168" s="8">
         <v>4.0999999999999996</v>
@@ -9813,7 +9813,7 @@
         <v>4.3499999999999996</v>
       </c>
       <c r="H168" s="9" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="I168" s="6"/>
     </row>
@@ -9825,10 +9825,10 @@
         <v>6</v>
       </c>
       <c r="C169" s="7" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D169" s="7" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E169" s="8">
         <v>4.12</v>
@@ -9840,7 +9840,7 @@
         <v>4.45</v>
       </c>
       <c r="H169" s="9" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="I169" s="6"/>
     </row>
@@ -9852,10 +9852,10 @@
         <v>7</v>
       </c>
       <c r="C170" s="7" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D170" s="7" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E170" s="8">
         <v>3.56</v>
@@ -9867,7 +9867,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H170" s="9" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="I170" s="6"/>
     </row>
@@ -9879,10 +9879,10 @@
         <v>8</v>
       </c>
       <c r="C171" s="7" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D171" s="7" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E171" s="8">
         <v>3.8</v>
@@ -9894,7 +9894,7 @@
         <v>4.2</v>
       </c>
       <c r="H171" s="9" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="I171" s="6"/>
     </row>
@@ -9906,10 +9906,10 @@
         <v>9</v>
       </c>
       <c r="C172" s="7" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D172" s="7" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E172" s="8">
         <v>3.71</v>
@@ -9921,7 +9921,7 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="H172" s="9" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="I172" s="6"/>
     </row>
@@ -9933,10 +9933,10 @@
         <v>10</v>
       </c>
       <c r="C173" s="7" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D173" s="7" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="E173" s="8">
         <v>3.83</v>
@@ -9948,7 +9948,7 @@
         <v>4.3</v>
       </c>
       <c r="H173" s="9" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="I173" s="6"/>
     </row>
@@ -9960,10 +9960,10 @@
         <v>1</v>
       </c>
       <c r="C174" s="7" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D174" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E174" s="8">
         <v>4.2</v>
@@ -9975,7 +9975,7 @@
         <v>4.5</v>
       </c>
       <c r="H174" s="9" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="I174" s="6"/>
     </row>
@@ -9987,10 +9987,10 @@
         <v>2</v>
       </c>
       <c r="C175" s="7" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D175" s="7" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="E175" s="8">
         <v>4.12</v>
@@ -10002,10 +10002,10 @@
         <v>4.75</v>
       </c>
       <c r="H175" s="9" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="I175" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="176" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -10016,10 +10016,10 @@
         <v>3</v>
       </c>
       <c r="C176" s="7" t="s">
+        <v>632</v>
+      </c>
+      <c r="D176" s="7" t="s">
         <v>633</v>
-      </c>
-      <c r="D176" s="7" t="s">
-        <v>634</v>
       </c>
       <c r="E176" s="8">
         <v>3.82</v>
@@ -10031,7 +10031,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H176" s="9" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="I176" s="6"/>
     </row>
@@ -10043,10 +10043,10 @@
         <v>4</v>
       </c>
       <c r="C177" s="7" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D177" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E177" s="8">
         <v>3.94</v>
@@ -10058,7 +10058,7 @@
         <v>4.3</v>
       </c>
       <c r="H177" s="9" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="I177" s="6"/>
     </row>
@@ -10070,10 +10070,10 @@
         <v>5</v>
       </c>
       <c r="C178" s="7" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D178" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E178" s="8">
         <v>4.1399999999999997</v>
@@ -10085,7 +10085,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H178" s="9" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="I178" s="6"/>
     </row>
@@ -10097,7 +10097,7 @@
         <v>6</v>
       </c>
       <c r="C179" s="7" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D179" s="7" t="s">
         <v>13</v>
@@ -10112,7 +10112,7 @@
         <v>4.3499999999999996</v>
       </c>
       <c r="H179" s="9" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="I179" s="6"/>
     </row>
@@ -10124,10 +10124,10 @@
         <v>7</v>
       </c>
       <c r="C180" s="7" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D180" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E180" s="8">
         <v>3.85</v>
@@ -10139,7 +10139,7 @@
         <v>4.3</v>
       </c>
       <c r="H180" s="9" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="I180" s="6"/>
     </row>
@@ -10151,10 +10151,10 @@
         <v>8</v>
       </c>
       <c r="C181" s="7" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D181" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E181" s="8">
         <v>3.87</v>
@@ -10166,7 +10166,7 @@
         <v>4.45</v>
       </c>
       <c r="H181" s="9" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="I181" s="6"/>
     </row>
@@ -10178,10 +10178,10 @@
         <v>1</v>
       </c>
       <c r="C182" s="7" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D182" s="7" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="E182" s="8">
         <v>4.5</v>
@@ -10193,7 +10193,7 @@
         <v>4.2</v>
       </c>
       <c r="H182" s="9" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="I182" s="6"/>
     </row>
@@ -10205,10 +10205,10 @@
         <v>2</v>
       </c>
       <c r="C183" s="7" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D183" s="7" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="E183" s="8">
         <v>4.37</v>
@@ -10220,7 +10220,7 @@
         <v>4.7</v>
       </c>
       <c r="H183" s="9" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="I183" s="6"/>
     </row>
@@ -10232,10 +10232,10 @@
         <v>3</v>
       </c>
       <c r="C184" s="7" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D184" s="7" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="E184" s="8">
         <v>4.25</v>
@@ -10247,7 +10247,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H184" s="9" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="I184" s="6"/>
     </row>
@@ -10259,10 +10259,10 @@
         <v>4</v>
       </c>
       <c r="C185" s="7" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D185" s="7" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="E185" s="8">
         <v>3.01</v>
@@ -10274,7 +10274,7 @@
         <v>3</v>
       </c>
       <c r="H185" s="9" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="I185" s="6"/>
     </row>
@@ -10286,10 +10286,10 @@
         <v>5</v>
       </c>
       <c r="C186" s="7" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D186" s="7" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="E186" s="8">
         <v>4.5</v>
@@ -10301,7 +10301,7 @@
         <v>4.8</v>
       </c>
       <c r="H186" s="9" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="I186" s="6"/>
     </row>
@@ -10313,10 +10313,10 @@
         <v>6</v>
       </c>
       <c r="C187" s="7" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D187" s="7" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="E187" s="8">
         <v>3.18</v>
@@ -10328,7 +10328,7 @@
         <v>3.5</v>
       </c>
       <c r="H187" s="9" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="I187" s="6"/>
     </row>
@@ -10340,10 +10340,10 @@
         <v>7</v>
       </c>
       <c r="C188" s="7" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D188" s="7" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E188" s="8">
         <v>4.04</v>
@@ -10355,7 +10355,7 @@
         <v>4</v>
       </c>
       <c r="H188" s="9" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="I188" s="6"/>
     </row>
@@ -10367,10 +10367,10 @@
         <v>8</v>
       </c>
       <c r="C189" s="7" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D189" s="7" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="E189" s="8">
         <v>3.41</v>
@@ -10382,7 +10382,7 @@
         <v>3</v>
       </c>
       <c r="H189" s="9" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="I189" s="6"/>
     </row>
@@ -10394,10 +10394,10 @@
         <v>9</v>
       </c>
       <c r="C190" s="7" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D190" s="7" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="E190" s="8">
         <v>4.0199999999999996</v>
@@ -10409,7 +10409,7 @@
         <v>4</v>
       </c>
       <c r="H190" s="9" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="I190" s="6"/>
     </row>
@@ -10421,10 +10421,10 @@
         <v>10</v>
       </c>
       <c r="C191" s="7" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D191" s="7" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="E191" s="8">
         <v>3.27</v>
@@ -10436,7 +10436,7 @@
         <v>3.5</v>
       </c>
       <c r="H191" s="9" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="I191" s="6"/>
     </row>
@@ -10448,10 +10448,10 @@
         <v>11</v>
       </c>
       <c r="C192" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="D192" s="7" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="E192" s="8">
         <v>4.1500000000000004</v>
@@ -10463,7 +10463,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H192" s="9" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="I192" s="6"/>
     </row>
@@ -10475,10 +10475,10 @@
         <v>12</v>
       </c>
       <c r="C193" s="7" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D193" s="7" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="E193" s="8">
         <v>2.73</v>
@@ -10490,7 +10490,7 @@
         <v>3</v>
       </c>
       <c r="H193" s="9" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="I193" s="6"/>
     </row>
@@ -10502,10 +10502,10 @@
         <v>13</v>
       </c>
       <c r="C194" s="7" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D194" s="7" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="E194" s="8">
         <v>4.43</v>
@@ -10517,7 +10517,7 @@
         <v>4.7</v>
       </c>
       <c r="H194" s="9" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="I194" s="6"/>
     </row>
@@ -10529,10 +10529,10 @@
         <v>14</v>
       </c>
       <c r="C195" s="7" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D195" s="7" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="E195" s="8">
         <v>2.99</v>
@@ -10544,7 +10544,7 @@
         <v>3.5</v>
       </c>
       <c r="H195" s="9" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="I195" s="6"/>
     </row>
@@ -10556,10 +10556,10 @@
         <v>15</v>
       </c>
       <c r="C196" s="7" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="D196" s="7" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="E196" s="8">
         <v>4.24</v>
@@ -10571,7 +10571,7 @@
         <v>4.8</v>
       </c>
       <c r="H196" s="9" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="I196" s="6"/>
     </row>
@@ -10583,10 +10583,10 @@
         <v>1</v>
       </c>
       <c r="C197" s="7" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D197" s="7" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E197" s="8">
         <v>4.01</v>
@@ -10598,7 +10598,7 @@
         <v>4.7</v>
       </c>
       <c r="H197" s="9" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="I197" s="6"/>
     </row>
@@ -10610,10 +10610,10 @@
         <v>2</v>
       </c>
       <c r="C198" s="7" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D198" s="7" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E198" s="8">
         <v>3.64</v>
@@ -10625,7 +10625,7 @@
         <v>4</v>
       </c>
       <c r="H198" s="9" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="I198" s="6"/>
     </row>
@@ -10637,10 +10637,10 @@
         <v>3</v>
       </c>
       <c r="C199" s="7" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D199" s="7" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E199" s="8">
         <v>3.69</v>
@@ -10652,7 +10652,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H199" s="9" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="I199" s="6"/>
     </row>
@@ -10664,10 +10664,10 @@
         <v>4</v>
       </c>
       <c r="C200" s="7" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="D200" s="7" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="E200" s="8">
         <v>3.34</v>
@@ -10679,7 +10679,7 @@
         <v>4</v>
       </c>
       <c r="H200" s="9" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="I200" s="6"/>
     </row>
@@ -10691,10 +10691,10 @@
         <v>5</v>
       </c>
       <c r="C201" s="7" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="D201" s="7" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="E201" s="8">
         <v>3.73</v>
@@ -10706,7 +10706,7 @@
         <v>4.2</v>
       </c>
       <c r="H201" s="9" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="I201" s="6"/>
     </row>
@@ -10718,10 +10718,10 @@
         <v>6</v>
       </c>
       <c r="C202" s="7" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D202" s="7" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="E202" s="8">
         <v>4.01</v>
@@ -10733,7 +10733,7 @@
         <v>4.5</v>
       </c>
       <c r="H202" s="9" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="I202" s="6"/>
     </row>
@@ -10745,10 +10745,10 @@
         <v>7</v>
       </c>
       <c r="C203" s="7" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D203" s="7" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E203" s="8">
         <v>3.81</v>
@@ -10760,7 +10760,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H203" s="9" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="I203" s="6"/>
     </row>
@@ -10772,10 +10772,10 @@
         <v>8</v>
       </c>
       <c r="C204" s="7" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="D204" s="7" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E204" s="8">
         <v>3.54</v>
@@ -10787,7 +10787,7 @@
         <v>3.9</v>
       </c>
       <c r="H204" s="9" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="I204" s="6"/>
     </row>
@@ -10799,10 +10799,10 @@
         <v>9</v>
       </c>
       <c r="C205" s="7" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D205" s="7" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E205" s="8">
         <v>3.46</v>
@@ -10814,7 +10814,7 @@
         <v>4</v>
       </c>
       <c r="H205" s="9" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="I205" s="6"/>
     </row>
@@ -10826,10 +10826,10 @@
         <v>10</v>
       </c>
       <c r="C206" s="7" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="D206" s="7" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E206" s="8">
         <v>3.56</v>
@@ -10841,7 +10841,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H206" s="9" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="I206" s="6"/>
     </row>
@@ -10853,10 +10853,10 @@
         <v>1</v>
       </c>
       <c r="C207" s="7" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D207" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E207" s="8">
         <v>3.91</v>
@@ -10868,7 +10868,7 @@
         <v>4.3</v>
       </c>
       <c r="H207" s="9" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="I207" s="6"/>
     </row>
@@ -10880,10 +10880,10 @@
         <v>2</v>
       </c>
       <c r="C208" s="7" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="D208" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E208" s="8">
         <v>3.61</v>
@@ -10895,7 +10895,7 @@
         <v>3.9</v>
       </c>
       <c r="H208" s="9" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="I208" s="6"/>
     </row>
@@ -10907,10 +10907,10 @@
         <v>3</v>
       </c>
       <c r="C209" s="7" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D209" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E209" s="8">
         <v>3.55</v>
@@ -10922,7 +10922,7 @@
         <v>4</v>
       </c>
       <c r="H209" s="9" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="I209" s="6"/>
     </row>
@@ -10934,10 +10934,10 @@
         <v>4</v>
       </c>
       <c r="C210" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D210" s="7" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="E210" s="8">
         <v>3.54</v>
@@ -10949,7 +10949,7 @@
         <v>3.8</v>
       </c>
       <c r="H210" s="9" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="I210" s="6"/>
     </row>
@@ -10961,10 +10961,10 @@
         <v>5</v>
       </c>
       <c r="C211" s="7" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="D211" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E211" s="8">
         <v>3.46</v>
@@ -10976,7 +10976,7 @@
         <v>3.9</v>
       </c>
       <c r="H211" s="9" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="I211" s="6"/>
     </row>
@@ -10988,10 +10988,10 @@
         <v>6</v>
       </c>
       <c r="C212" s="7" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D212" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E212" s="8">
         <v>3.41</v>
@@ -11003,7 +11003,7 @@
         <v>3.7</v>
       </c>
       <c r="H212" s="9" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="I212" s="6"/>
     </row>
@@ -11015,10 +11015,10 @@
         <v>7</v>
       </c>
       <c r="C213" s="7" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D213" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E213" s="8">
         <v>3.61</v>
@@ -11030,7 +11030,7 @@
         <v>4</v>
       </c>
       <c r="H213" s="9" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="I213" s="6"/>
     </row>
@@ -11042,10 +11042,10 @@
         <v>8</v>
       </c>
       <c r="C214" s="7" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D214" s="7" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="E214" s="8">
         <v>3.65</v>
@@ -11057,7 +11057,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H214" s="9" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="I214" s="6"/>
     </row>
@@ -11069,10 +11069,10 @@
         <v>9</v>
       </c>
       <c r="C215" s="7" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D215" s="7" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="E215" s="8">
         <v>3.43</v>
@@ -11084,7 +11084,7 @@
         <v>3.6</v>
       </c>
       <c r="H215" s="9" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="I215" s="6"/>
     </row>
@@ -11096,10 +11096,10 @@
         <v>1</v>
       </c>
       <c r="C216" s="7" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D216" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E216" s="8">
         <v>3.6</v>
@@ -11111,7 +11111,7 @@
         <v>4.3</v>
       </c>
       <c r="H216" s="9" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="I216" s="6"/>
     </row>
@@ -11123,10 +11123,10 @@
         <v>2</v>
       </c>
       <c r="C217" s="7" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="D217" s="7" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="E217" s="8">
         <v>3.26</v>
@@ -11138,7 +11138,7 @@
         <v>3.7</v>
       </c>
       <c r="H217" s="9" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="I217" s="6"/>
     </row>
@@ -11150,10 +11150,10 @@
         <v>3</v>
       </c>
       <c r="C218" s="7" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="D218" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E218" s="8">
         <v>3.81</v>
@@ -11165,7 +11165,7 @@
         <v>4.2</v>
       </c>
       <c r="H218" s="9" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="I218" s="6"/>
     </row>
@@ -11177,10 +11177,10 @@
         <v>4</v>
       </c>
       <c r="C219" s="7" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="D219" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E219" s="8">
         <v>3.45</v>
@@ -11192,7 +11192,7 @@
         <v>3.8</v>
       </c>
       <c r="H219" s="9" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="I219" s="6"/>
     </row>
@@ -11204,10 +11204,10 @@
         <v>5</v>
       </c>
       <c r="C220" s="7" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="D220" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E220" s="8">
         <v>3.53</v>
@@ -11219,7 +11219,7 @@
         <v>3.9</v>
       </c>
       <c r="H220" s="9" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="I220" s="6"/>
     </row>
@@ -11231,10 +11231,10 @@
         <v>6</v>
       </c>
       <c r="C221" s="7" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D221" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E221" s="8">
         <v>3.19</v>
@@ -11246,7 +11246,7 @@
         <v>3.6</v>
       </c>
       <c r="H221" s="9" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="I221" s="6"/>
     </row>
@@ -11258,10 +11258,10 @@
         <v>7</v>
       </c>
       <c r="C222" s="7" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D222" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E222" s="8">
         <v>3.41</v>
@@ -11273,7 +11273,7 @@
         <v>3.9</v>
       </c>
       <c r="H222" s="9" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="I222" s="6"/>
     </row>
@@ -11285,10 +11285,10 @@
         <v>8</v>
       </c>
       <c r="C223" s="7" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D223" s="7" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="E223" s="8">
         <v>3.14</v>
@@ -11300,7 +11300,7 @@
         <v>3.6</v>
       </c>
       <c r="H223" s="9" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="I223" s="6"/>
     </row>
@@ -11312,10 +11312,10 @@
         <v>9</v>
       </c>
       <c r="C224" s="7" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D224" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E224" s="8">
         <v>3.52</v>
@@ -11327,7 +11327,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H224" s="9" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="I224" s="6"/>
     </row>
@@ -11339,10 +11339,10 @@
         <v>1</v>
       </c>
       <c r="C225" s="7" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="D225" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E225" s="8">
         <v>3.63</v>
@@ -11354,7 +11354,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H225" s="9" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="I225" s="6"/>
     </row>
@@ -11366,10 +11366,10 @@
         <v>2</v>
       </c>
       <c r="C226" s="7" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="D226" s="7" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E226" s="8">
         <v>3.66</v>
@@ -11381,7 +11381,7 @@
         <v>4</v>
       </c>
       <c r="H226" s="9" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="I226" s="6"/>
     </row>
@@ -11393,10 +11393,10 @@
         <v>3</v>
       </c>
       <c r="C227" s="7" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="D227" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E227" s="8">
         <v>3.8</v>
@@ -11408,10 +11408,10 @@
         <v>4.3</v>
       </c>
       <c r="H227" s="9" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="I227" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="228" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -11422,10 +11422,10 @@
         <v>4</v>
       </c>
       <c r="C228" s="7" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="D228" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E228" s="8">
         <v>3.49</v>
@@ -11437,7 +11437,7 @@
         <v>3.8</v>
       </c>
       <c r="H228" s="9" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="I228" s="6"/>
     </row>
@@ -11449,10 +11449,10 @@
         <v>5</v>
       </c>
       <c r="C229" s="7" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="D229" s="7" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E229" s="8">
         <v>3.29</v>
@@ -11464,7 +11464,7 @@
         <v>3.7</v>
       </c>
       <c r="H229" s="9" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="I229" s="6"/>
     </row>
@@ -11476,10 +11476,10 @@
         <v>6</v>
       </c>
       <c r="C230" s="7" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="D230" s="7" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="E230" s="8">
         <v>3.45</v>
@@ -11491,7 +11491,7 @@
         <v>4</v>
       </c>
       <c r="H230" s="9" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="I230" s="6"/>
     </row>
@@ -11503,10 +11503,10 @@
         <v>7</v>
       </c>
       <c r="C231" s="7" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="D231" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E231" s="8">
         <v>3.51</v>
@@ -11518,7 +11518,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H231" s="9" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="I231" s="6"/>
     </row>
@@ -11530,10 +11530,10 @@
         <v>1</v>
       </c>
       <c r="C232" s="7" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="D232" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E232" s="8">
         <v>3.76</v>
@@ -11545,10 +11545,10 @@
         <v>4.2</v>
       </c>
       <c r="H232" s="9" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="I232" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="233" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
@@ -11559,10 +11559,10 @@
         <v>2</v>
       </c>
       <c r="C233" s="7" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D233" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E233" s="8">
         <v>3.65</v>
@@ -11574,10 +11574,10 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H233" s="9" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="I233" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="234" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -11588,10 +11588,10 @@
         <v>3</v>
       </c>
       <c r="C234" s="7" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="D234" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="E234" s="8">
         <v>3.52</v>
@@ -11603,7 +11603,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H234" s="9" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="I234" s="6"/>
     </row>
@@ -11615,10 +11615,10 @@
         <v>4</v>
       </c>
       <c r="C235" s="7" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="D235" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E235" s="8">
         <v>3.41</v>
@@ -11630,7 +11630,7 @@
         <v>3.9</v>
       </c>
       <c r="H235" s="9" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="I235" s="6"/>
     </row>
@@ -11642,10 +11642,10 @@
         <v>5</v>
       </c>
       <c r="C236" s="7" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="D236" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E236" s="8">
         <v>3.68</v>
@@ -11657,7 +11657,7 @@
         <v>3.8</v>
       </c>
       <c r="H236" s="9" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="I236" s="6"/>
     </row>
@@ -11669,10 +11669,10 @@
         <v>6</v>
       </c>
       <c r="C237" s="7" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="D237" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E237" s="8">
         <v>3.62</v>
@@ -11684,7 +11684,7 @@
         <v>4</v>
       </c>
       <c r="H237" s="9" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="I237" s="6"/>
     </row>
@@ -11696,10 +11696,10 @@
         <v>7</v>
       </c>
       <c r="C238" s="7" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="D238" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E238" s="8">
         <v>3.58</v>
@@ -11711,7 +11711,7 @@
         <v>3.9</v>
       </c>
       <c r="H238" s="9" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="I238" s="6"/>
     </row>
@@ -11723,10 +11723,10 @@
         <v>8</v>
       </c>
       <c r="C239" s="7" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="D239" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="E239" s="8">
         <v>3.45</v>
@@ -11738,10 +11738,10 @@
         <v>4.5</v>
       </c>
       <c r="H239" s="9" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="I239" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="240" spans="1:9" ht="21" x14ac:dyDescent="0.25">
@@ -11752,10 +11752,10 @@
         <v>1</v>
       </c>
       <c r="C240" s="7" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="D240" s="7" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E240" s="8">
         <v>3.5</v>
@@ -11767,7 +11767,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H240" s="9" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="I240" s="6"/>
     </row>
@@ -11779,10 +11779,10 @@
         <v>2</v>
       </c>
       <c r="C241" s="7" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="D241" s="7" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E241" s="8">
         <v>3.16</v>
@@ -11794,7 +11794,7 @@
         <v>3.7</v>
       </c>
       <c r="H241" s="9" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="I241" s="6"/>
     </row>
@@ -11806,10 +11806,10 @@
         <v>3</v>
       </c>
       <c r="C242" s="7" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="D242" s="7" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="E242" s="8">
         <v>3.16</v>
@@ -11821,7 +11821,7 @@
         <v>3.6</v>
       </c>
       <c r="H242" s="9" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="I242" s="6"/>
     </row>
@@ -11833,10 +11833,10 @@
         <v>4</v>
       </c>
       <c r="C243" s="7" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="D243" s="7" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E243" s="8">
         <v>3.31</v>
@@ -11848,7 +11848,7 @@
         <v>3.8</v>
       </c>
       <c r="H243" s="9" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="I243" s="6"/>
     </row>
@@ -11860,10 +11860,10 @@
         <v>5</v>
       </c>
       <c r="C244" s="7" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="D244" s="7" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="E244" s="8">
         <v>3.5</v>
@@ -11875,7 +11875,7 @@
         <v>3.9</v>
       </c>
       <c r="H244" s="9" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="I244" s="6"/>
     </row>
@@ -11887,10 +11887,10 @@
         <v>6</v>
       </c>
       <c r="C245" s="7" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="D245" s="7" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E245" s="8">
         <v>3.41</v>
@@ -11902,7 +11902,7 @@
         <v>3.9</v>
       </c>
       <c r="H245" s="9" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="I245" s="6"/>
     </row>
@@ -11914,10 +11914,10 @@
         <v>7</v>
       </c>
       <c r="C246" s="7" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="D246" s="7" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="E246" s="8">
         <v>3.75</v>
@@ -11929,7 +11929,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H246" s="9" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="I246" s="6"/>
     </row>
@@ -11941,10 +11941,10 @@
         <v>8</v>
       </c>
       <c r="C247" s="7" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="D247" s="7" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E247" s="8">
         <v>2.9</v>
@@ -11956,7 +11956,7 @@
         <v>3.5</v>
       </c>
       <c r="H247" s="9" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="I247" s="6"/>
     </row>
@@ -11968,10 +11968,10 @@
         <v>9</v>
       </c>
       <c r="C248" s="7" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="D248" s="7" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="E248" s="8">
         <v>3.17</v>
@@ -11983,7 +11983,7 @@
         <v>3.8</v>
       </c>
       <c r="H248" s="9" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="I248" s="6"/>
     </row>
@@ -11995,10 +11995,10 @@
         <v>10</v>
       </c>
       <c r="C249" s="7" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="D249" s="7" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E249" s="8">
         <v>3.61</v>
@@ -12010,7 +12010,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H249" s="9" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="I249" s="6"/>
     </row>
@@ -12022,10 +12022,10 @@
         <v>11</v>
       </c>
       <c r="C250" s="7" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="D250" s="7" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E250" s="8">
         <v>3.4</v>
@@ -12037,7 +12037,7 @@
         <v>3.8</v>
       </c>
       <c r="H250" s="9" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="I250" s="6"/>
     </row>
@@ -12049,10 +12049,10 @@
         <v>12</v>
       </c>
       <c r="C251" s="7" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="D251" s="7" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="E251" s="8">
         <v>3.39</v>
@@ -12064,7 +12064,7 @@
         <v>3.7</v>
       </c>
       <c r="H251" s="9" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="I251" s="6"/>
     </row>
@@ -12076,10 +12076,10 @@
         <v>1</v>
       </c>
       <c r="C252" s="7" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="D252" s="7" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="E252" s="8">
         <v>4.3099999999999996</v>
@@ -12091,7 +12091,7 @@
         <v>4.3</v>
       </c>
       <c r="H252" s="9" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="I252" s="6"/>
     </row>
@@ -12103,10 +12103,10 @@
         <v>2</v>
       </c>
       <c r="C253" s="7" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="D253" s="7" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="E253" s="8">
         <v>3.79</v>
@@ -12118,7 +12118,7 @@
         <v>3.8</v>
       </c>
       <c r="H253" s="9" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="I253" s="6"/>
     </row>
@@ -12130,10 +12130,10 @@
         <v>3</v>
       </c>
       <c r="C254" s="7" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="D254" s="7" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="E254" s="8">
         <v>3.86</v>
@@ -12145,7 +12145,7 @@
         <v>3.9</v>
       </c>
       <c r="H254" s="9" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="I254" s="6"/>
     </row>
@@ -12157,10 +12157,10 @@
         <v>4</v>
       </c>
       <c r="C255" s="7" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="D255" s="7" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="E255" s="8">
         <v>4.22</v>
@@ -12172,7 +12172,7 @@
         <v>4.2</v>
       </c>
       <c r="H255" s="9" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="I255" s="6"/>
     </row>
@@ -12184,10 +12184,10 @@
         <v>5</v>
       </c>
       <c r="C256" s="7" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="D256" s="7" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="E256" s="8">
         <v>4.32</v>
@@ -12199,7 +12199,7 @@
         <v>4.3</v>
       </c>
       <c r="H256" s="9" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="I256" s="6"/>
     </row>
@@ -12211,10 +12211,10 @@
         <v>6</v>
       </c>
       <c r="C257" s="7" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="D257" s="7" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E257" s="8">
         <v>3.7</v>
@@ -12226,7 +12226,7 @@
         <v>3.8</v>
       </c>
       <c r="H257" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="I257" s="6"/>
     </row>
@@ -12238,10 +12238,10 @@
         <v>7</v>
       </c>
       <c r="C258" s="7" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="D258" s="7" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="E258" s="8">
         <v>4</v>
@@ -12253,7 +12253,7 @@
         <v>4</v>
       </c>
       <c r="H258" s="9" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="I258" s="6"/>
     </row>
@@ -12265,10 +12265,10 @@
         <v>8</v>
       </c>
       <c r="C259" s="7" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="D259" s="7" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="E259" s="8">
         <v>3.86</v>
@@ -12280,7 +12280,7 @@
         <v>3.9</v>
       </c>
       <c r="H259" s="9" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="I259" s="6"/>
     </row>
@@ -12292,10 +12292,10 @@
         <v>1</v>
       </c>
       <c r="C260" s="7" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="D260" s="7" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="E260" s="8">
         <v>3.76</v>
@@ -12307,7 +12307,7 @@
         <v>4</v>
       </c>
       <c r="H260" s="9" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="I260" s="6"/>
     </row>
@@ -12319,10 +12319,10 @@
         <v>2</v>
       </c>
       <c r="C261" s="7" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="D261" s="7" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="E261" s="8">
         <v>3.67</v>
@@ -12334,7 +12334,7 @@
         <v>3.8</v>
       </c>
       <c r="H261" s="9" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="I261" s="6"/>
     </row>
@@ -12346,10 +12346,10 @@
         <v>3</v>
       </c>
       <c r="C262" s="7" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="D262" s="7" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E262" s="8">
         <v>3.5</v>
@@ -12361,7 +12361,7 @@
         <v>3.7</v>
       </c>
       <c r="H262" s="9" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="I262" s="6"/>
     </row>
@@ -12373,10 +12373,10 @@
         <v>4</v>
       </c>
       <c r="C263" s="7" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="D263" s="7" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="E263" s="8">
         <v>3.33</v>
@@ -12388,7 +12388,7 @@
         <v>3.7</v>
       </c>
       <c r="H263" s="9" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="I263" s="6"/>
     </row>
@@ -12400,10 +12400,10 @@
         <v>5</v>
       </c>
       <c r="C264" s="7" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="D264" s="7" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="E264" s="8">
         <v>3.33</v>
@@ -12415,7 +12415,7 @@
         <v>3.8</v>
       </c>
       <c r="H264" s="9" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="I264" s="6"/>
     </row>
@@ -12427,10 +12427,10 @@
         <v>6</v>
       </c>
       <c r="C265" s="7" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="D265" s="7" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="E265" s="8">
         <v>3.33</v>
@@ -12442,7 +12442,7 @@
         <v>3.6</v>
       </c>
       <c r="H265" s="9" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="I265" s="6"/>
     </row>
@@ -12454,10 +12454,10 @@
         <v>7</v>
       </c>
       <c r="C266" s="7" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="D266" s="7" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="E266" s="8">
         <v>3.33</v>
@@ -12469,7 +12469,7 @@
         <v>3.7</v>
       </c>
       <c r="H266" s="9" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="I266" s="6"/>
     </row>
@@ -12481,10 +12481,10 @@
         <v>8</v>
       </c>
       <c r="C267" s="7" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="D267" s="7" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="E267" s="8">
         <v>3.33</v>
@@ -12496,7 +12496,7 @@
         <v>3.7</v>
       </c>
       <c r="H267" s="9" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="I267" s="6"/>
     </row>
@@ -12508,10 +12508,10 @@
         <v>9</v>
       </c>
       <c r="C268" s="7" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="D268" s="7" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="E268" s="8">
         <v>3.33</v>
@@ -12523,7 +12523,7 @@
         <v>3.7</v>
       </c>
       <c r="H268" s="9" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="I268" s="6"/>
     </row>
@@ -12535,10 +12535,10 @@
         <v>10</v>
       </c>
       <c r="C269" s="7" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="D269" s="7" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="E269" s="8">
         <v>3.5</v>
@@ -12550,7 +12550,7 @@
         <v>3.9</v>
       </c>
       <c r="H269" s="9" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="I269" s="6"/>
     </row>
@@ -12562,10 +12562,10 @@
         <v>11</v>
       </c>
       <c r="C270" s="7" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="D270" s="7" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="E270" s="8">
         <v>3.91</v>
@@ -12577,7 +12577,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H270" s="9" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="I270" s="6"/>
     </row>
@@ -12589,10 +12589,10 @@
         <v>1</v>
       </c>
       <c r="C271" s="7" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="D271" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="E271" s="8">
         <v>3.52</v>
@@ -12604,7 +12604,7 @@
         <v>3.9</v>
       </c>
       <c r="H271" s="9" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="I271" s="6"/>
     </row>
@@ -12616,10 +12616,10 @@
         <v>2</v>
       </c>
       <c r="C272" s="7" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="D272" s="7" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="E272" s="8">
         <v>3.35</v>
@@ -12631,7 +12631,7 @@
         <v>3.8</v>
       </c>
       <c r="H272" s="9" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="I272" s="6"/>
     </row>
@@ -12643,10 +12643,10 @@
         <v>3</v>
       </c>
       <c r="C273" s="7" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D273" s="7" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="E273" s="8">
         <v>3.66</v>
@@ -12658,10 +12658,10 @@
         <v>4.7</v>
       </c>
       <c r="H273" s="9" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="I273" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="274" spans="1:9" ht="21" x14ac:dyDescent="0.25">
@@ -12672,10 +12672,10 @@
         <v>4</v>
       </c>
       <c r="C274" s="7" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="D274" s="7" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="E274" s="8">
         <v>3.18</v>
@@ -12687,7 +12687,7 @@
         <v>3.7</v>
       </c>
       <c r="H274" s="9" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="I274" s="6"/>
     </row>
@@ -12699,10 +12699,10 @@
         <v>5</v>
       </c>
       <c r="C275" s="7" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="D275" s="7" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="E275" s="8">
         <v>3.49</v>
@@ -12714,10 +12714,10 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H275" s="9" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="I275" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="276" spans="1:9" ht="21" x14ac:dyDescent="0.25">
@@ -12728,10 +12728,10 @@
         <v>6</v>
       </c>
       <c r="C276" s="7" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="D276" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E276" s="8">
         <v>3.45</v>
@@ -12743,7 +12743,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H276" s="9" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="I276" s="6"/>
     </row>
@@ -12755,10 +12755,10 @@
         <v>7</v>
       </c>
       <c r="C277" s="7" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="D277" s="7" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E277" s="8">
         <v>3.61</v>
@@ -12770,7 +12770,7 @@
         <v>4.3</v>
       </c>
       <c r="H277" s="9" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="I277" s="6"/>
     </row>
@@ -12782,10 +12782,10 @@
         <v>1</v>
       </c>
       <c r="C278" s="7" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="D278" s="7" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="E278" s="8">
         <v>4.46</v>
@@ -12797,10 +12797,10 @@
         <v>4.8</v>
       </c>
       <c r="H278" s="9" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="I278" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="279" spans="1:9" ht="42" x14ac:dyDescent="0.25">
@@ -12811,10 +12811,10 @@
         <v>2</v>
       </c>
       <c r="C279" s="7" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="D279" s="7" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E279" s="8">
         <v>4.2</v>
@@ -12826,7 +12826,7 @@
         <v>4.7</v>
       </c>
       <c r="H279" s="9" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="I279" s="6"/>
     </row>
@@ -12838,10 +12838,10 @@
         <v>3</v>
       </c>
       <c r="C280" s="7" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="D280" s="7" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E280" s="8">
         <v>4.41</v>
@@ -12853,7 +12853,7 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="H280" s="9" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="I280" s="6"/>
     </row>
@@ -12865,10 +12865,10 @@
         <v>4</v>
       </c>
       <c r="C281" s="7" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="D281" s="7" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="E281" s="8">
         <v>4.33</v>
@@ -12880,7 +12880,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H281" s="9" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="I281" s="6"/>
     </row>
@@ -12892,10 +12892,10 @@
         <v>5</v>
       </c>
       <c r="C282" s="7" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="D282" s="7" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="E282" s="8">
         <v>4.07</v>
@@ -12907,7 +12907,7 @@
         <v>4.7</v>
       </c>
       <c r="H282" s="9" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="I282" s="6"/>
     </row>
@@ -12919,10 +12919,10 @@
         <v>6</v>
       </c>
       <c r="C283" s="7" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="D283" s="7" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="E283" s="8">
         <v>3.82</v>
@@ -12934,7 +12934,7 @@
         <v>4.7</v>
       </c>
       <c r="H283" s="9" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="I283" s="6"/>
     </row>
@@ -12946,10 +12946,10 @@
         <v>7</v>
       </c>
       <c r="C284" s="7" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="D284" s="7" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="E284" s="8">
         <v>3.91</v>
@@ -12961,7 +12961,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H284" s="9" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="I284" s="6"/>
     </row>
@@ -12973,10 +12973,10 @@
         <v>1</v>
       </c>
       <c r="C285" s="7" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="D285" s="7" t="s">
-        <v>1001</v>
+        <v>1082</v>
       </c>
       <c r="E285" s="8">
         <v>3.44</v>
@@ -12988,7 +12988,7 @@
         <v>3.7</v>
       </c>
       <c r="H285" s="9" t="s">
-        <v>1013</v>
+        <v>999</v>
       </c>
       <c r="I285" s="6"/>
     </row>
@@ -13000,10 +13000,10 @@
         <v>2</v>
       </c>
       <c r="C286" s="7" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="D286" s="7" t="s">
-        <v>1002</v>
+        <v>1083</v>
       </c>
       <c r="E286" s="8">
         <v>3.39</v>
@@ -13015,7 +13015,7 @@
         <v>3.5</v>
       </c>
       <c r="H286" s="9" t="s">
-        <v>1014</v>
+        <v>1000</v>
       </c>
       <c r="I286" s="6"/>
     </row>
@@ -13027,10 +13027,10 @@
         <v>3</v>
       </c>
       <c r="C287" s="7" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="D287" s="7" t="s">
-        <v>1003</v>
+        <v>1084</v>
       </c>
       <c r="E287" s="8">
         <v>3.36</v>
@@ -13042,7 +13042,7 @@
         <v>3.6</v>
       </c>
       <c r="H287" s="9" t="s">
-        <v>1015</v>
+        <v>1001</v>
       </c>
       <c r="I287" s="6"/>
     </row>
@@ -13054,10 +13054,10 @@
         <v>4</v>
       </c>
       <c r="C288" s="7" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="D288" s="7" t="s">
-        <v>1004</v>
+        <v>1085</v>
       </c>
       <c r="E288" s="8">
         <v>3.35</v>
@@ -13069,7 +13069,7 @@
         <v>3.7</v>
       </c>
       <c r="H288" s="9" t="s">
-        <v>1016</v>
+        <v>1002</v>
       </c>
       <c r="I288" s="6"/>
     </row>
@@ -13081,10 +13081,10 @@
         <v>5</v>
       </c>
       <c r="C289" s="7" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="D289" s="7" t="s">
-        <v>1005</v>
+        <v>1086</v>
       </c>
       <c r="E289" s="8">
         <v>3.34</v>
@@ -13096,7 +13096,7 @@
         <v>3.7</v>
       </c>
       <c r="H289" s="9" t="s">
-        <v>1017</v>
+        <v>1003</v>
       </c>
       <c r="I289" s="6"/>
     </row>
@@ -13108,10 +13108,10 @@
         <v>6</v>
       </c>
       <c r="C290" s="7" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="D290" s="7" t="s">
-        <v>1006</v>
+        <v>1087</v>
       </c>
       <c r="E290" s="8">
         <v>3.24</v>
@@ -13123,7 +13123,7 @@
         <v>3.8</v>
       </c>
       <c r="H290" s="9" t="s">
-        <v>1018</v>
+        <v>1004</v>
       </c>
       <c r="I290" s="6"/>
     </row>
@@ -13135,10 +13135,10 @@
         <v>7</v>
       </c>
       <c r="C291" s="7" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="D291" s="7" t="s">
-        <v>1012</v>
+        <v>1088</v>
       </c>
       <c r="E291" s="8">
         <v>3.27</v>
@@ -13150,7 +13150,7 @@
         <v>3.5</v>
       </c>
       <c r="H291" s="9" t="s">
-        <v>1019</v>
+        <v>1005</v>
       </c>
       <c r="I291" s="6"/>
     </row>
@@ -13162,10 +13162,10 @@
         <v>8</v>
       </c>
       <c r="C292" s="7" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="D292" s="7" t="s">
-        <v>1011</v>
+        <v>1089</v>
       </c>
       <c r="E292" s="8">
         <v>3.21</v>
@@ -13177,7 +13177,7 @@
         <v>3.7</v>
       </c>
       <c r="H292" s="9" t="s">
-        <v>1020</v>
+        <v>1006</v>
       </c>
       <c r="I292" s="6"/>
     </row>
@@ -13189,10 +13189,10 @@
         <v>9</v>
       </c>
       <c r="C293" s="7" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="D293" s="7" t="s">
-        <v>1010</v>
+        <v>1090</v>
       </c>
       <c r="E293" s="8">
         <v>3.15</v>
@@ -13204,7 +13204,7 @@
         <v>3.5</v>
       </c>
       <c r="H293" s="9" t="s">
-        <v>1021</v>
+        <v>1007</v>
       </c>
       <c r="I293" s="6"/>
     </row>
@@ -13216,10 +13216,10 @@
         <v>10</v>
       </c>
       <c r="C294" s="7" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="D294" s="7" t="s">
-        <v>1009</v>
+        <v>1091</v>
       </c>
       <c r="E294" s="8">
         <v>3.07</v>
@@ -13231,7 +13231,7 @@
         <v>3.7</v>
       </c>
       <c r="H294" s="9" t="s">
-        <v>1022</v>
+        <v>1008</v>
       </c>
       <c r="I294" s="6"/>
     </row>
@@ -13243,10 +13243,10 @@
         <v>11</v>
       </c>
       <c r="C295" s="7" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="D295" s="7" t="s">
-        <v>1008</v>
+        <v>1092</v>
       </c>
       <c r="E295" s="8">
         <v>3.72</v>
@@ -13258,7 +13258,7 @@
         <v>4.2</v>
       </c>
       <c r="H295" s="9" t="s">
-        <v>1023</v>
+        <v>1009</v>
       </c>
       <c r="I295" s="6"/>
     </row>
@@ -13270,10 +13270,10 @@
         <v>12</v>
       </c>
       <c r="C296" s="7" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="D296" s="7" t="s">
-        <v>1007</v>
+        <v>1093</v>
       </c>
       <c r="E296" s="8">
         <v>3.31</v>
@@ -13285,7 +13285,7 @@
         <v>4</v>
       </c>
       <c r="H296" s="9" t="s">
-        <v>1024</v>
+        <v>1010</v>
       </c>
       <c r="I296" s="6"/>
     </row>
@@ -13297,10 +13297,10 @@
         <v>1</v>
       </c>
       <c r="C297" s="7" t="s">
-        <v>1025</v>
+        <v>1011</v>
       </c>
       <c r="D297" s="7" t="s">
-        <v>1038</v>
+        <v>1074</v>
       </c>
       <c r="E297" s="8">
         <v>3.66</v>
@@ -13312,7 +13312,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H297" s="9" t="s">
-        <v>1037</v>
+        <v>1022</v>
       </c>
       <c r="I297" s="6"/>
     </row>
@@ -13324,10 +13324,10 @@
         <v>2</v>
       </c>
       <c r="C298" s="7" t="s">
-        <v>1026</v>
+        <v>1012</v>
       </c>
       <c r="D298" s="7" t="s">
-        <v>1039</v>
+        <v>1075</v>
       </c>
       <c r="E298" s="8">
         <v>3.51</v>
@@ -13339,7 +13339,7 @@
         <v>3.8</v>
       </c>
       <c r="H298" s="9" t="s">
-        <v>1040</v>
+        <v>1023</v>
       </c>
       <c r="I298" s="6"/>
     </row>
@@ -13351,10 +13351,10 @@
         <v>3</v>
       </c>
       <c r="C299" s="7" t="s">
-        <v>1027</v>
+        <v>1013</v>
       </c>
       <c r="D299" s="7" t="s">
-        <v>1041</v>
+        <v>1076</v>
       </c>
       <c r="E299" s="8">
         <v>3.43</v>
@@ -13366,7 +13366,7 @@
         <v>3.9</v>
       </c>
       <c r="H299" s="9" t="s">
-        <v>1042</v>
+        <v>1024</v>
       </c>
       <c r="I299" s="6"/>
     </row>
@@ -13378,10 +13378,10 @@
         <v>4</v>
       </c>
       <c r="C300" s="7" t="s">
-        <v>1028</v>
+        <v>1014</v>
       </c>
       <c r="D300" s="7" t="s">
-        <v>1044</v>
+        <v>1077</v>
       </c>
       <c r="E300" s="8">
         <v>3.51</v>
@@ -13393,7 +13393,7 @@
         <v>3.7</v>
       </c>
       <c r="H300" s="9" t="s">
-        <v>1043</v>
+        <v>1025</v>
       </c>
       <c r="I300" s="6"/>
     </row>
@@ -13405,10 +13405,10 @@
         <v>5</v>
       </c>
       <c r="C301" s="7" t="s">
-        <v>1029</v>
+        <v>1015</v>
       </c>
       <c r="D301" s="7" t="s">
-        <v>1045</v>
+        <v>1078</v>
       </c>
       <c r="E301" s="8">
         <v>3.48</v>
@@ -13420,7 +13420,7 @@
         <v>3.9</v>
       </c>
       <c r="H301" s="9" t="s">
-        <v>1048</v>
+        <v>1027</v>
       </c>
       <c r="I301" s="6"/>
     </row>
@@ -13432,10 +13432,10 @@
         <v>6</v>
       </c>
       <c r="C302" s="7" t="s">
-        <v>1030</v>
+        <v>1016</v>
       </c>
       <c r="D302" s="7" t="s">
-        <v>1046</v>
+        <v>1079</v>
       </c>
       <c r="E302" s="8">
         <v>3.59</v>
@@ -13447,7 +13447,7 @@
         <v>4.2</v>
       </c>
       <c r="H302" s="9" t="s">
-        <v>1047</v>
+        <v>1026</v>
       </c>
       <c r="I302" s="6"/>
     </row>
@@ -13459,10 +13459,10 @@
         <v>1</v>
       </c>
       <c r="C303" s="7" t="s">
-        <v>1054</v>
+        <v>1033</v>
       </c>
       <c r="D303" s="7" t="s">
-        <v>1060</v>
+        <v>1039</v>
       </c>
       <c r="E303" s="8">
         <v>3.81</v>
@@ -13474,7 +13474,7 @@
         <v>3.8</v>
       </c>
       <c r="H303" s="9" t="s">
-        <v>1072</v>
+        <v>1051</v>
       </c>
       <c r="I303" s="6"/>
     </row>
@@ -13486,10 +13486,10 @@
         <v>2</v>
       </c>
       <c r="C304" s="7" t="s">
-        <v>1055</v>
+        <v>1034</v>
       </c>
       <c r="D304" s="7" t="s">
-        <v>1061</v>
+        <v>1040</v>
       </c>
       <c r="E304" s="8">
         <v>3.82</v>
@@ -13501,7 +13501,7 @@
         <v>3.7</v>
       </c>
       <c r="H304" s="9" t="s">
-        <v>1073</v>
+        <v>1052</v>
       </c>
       <c r="I304" s="6"/>
     </row>
@@ -13513,10 +13513,10 @@
         <v>3</v>
       </c>
       <c r="C305" s="7" t="s">
-        <v>1051</v>
+        <v>1030</v>
       </c>
       <c r="D305" s="7" t="s">
-        <v>1062</v>
+        <v>1041</v>
       </c>
       <c r="E305" s="8">
         <v>3.81</v>
@@ -13528,7 +13528,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H305" s="9" t="s">
-        <v>1074</v>
+        <v>1053</v>
       </c>
       <c r="I305" s="6"/>
     </row>
@@ -13540,10 +13540,10 @@
         <v>4</v>
       </c>
       <c r="C306" s="7" t="s">
-        <v>1056</v>
+        <v>1035</v>
       </c>
       <c r="D306" s="7" t="s">
-        <v>1063</v>
+        <v>1042</v>
       </c>
       <c r="E306" s="8">
         <v>3</v>
@@ -13555,7 +13555,7 @@
         <v>3.8</v>
       </c>
       <c r="H306" s="9" t="s">
-        <v>1075</v>
+        <v>1054</v>
       </c>
       <c r="I306" s="6"/>
     </row>
@@ -13567,10 +13567,10 @@
         <v>5</v>
       </c>
       <c r="C307" s="7" t="s">
-        <v>1081</v>
+        <v>1060</v>
       </c>
       <c r="D307" s="7" t="s">
-        <v>1064</v>
+        <v>1043</v>
       </c>
       <c r="E307" s="8">
         <v>3.82</v>
@@ -13582,7 +13582,7 @@
         <v>4</v>
       </c>
       <c r="H307" s="9" t="s">
-        <v>1076</v>
+        <v>1055</v>
       </c>
       <c r="I307" s="6"/>
     </row>
@@ -13594,10 +13594,10 @@
         <v>6</v>
       </c>
       <c r="C308" s="7" t="s">
-        <v>1057</v>
+        <v>1036</v>
       </c>
       <c r="D308" s="7" t="s">
-        <v>1065</v>
+        <v>1044</v>
       </c>
       <c r="E308" s="8">
         <v>3.86</v>
@@ -13609,7 +13609,7 @@
         <v>3.7</v>
       </c>
       <c r="H308" s="9" t="s">
-        <v>1077</v>
+        <v>1056</v>
       </c>
       <c r="I308" s="6"/>
     </row>
@@ -13621,10 +13621,10 @@
         <v>7</v>
       </c>
       <c r="C309" s="7" t="s">
-        <v>1058</v>
+        <v>1037</v>
       </c>
       <c r="D309" s="7" t="s">
-        <v>1066</v>
+        <v>1045</v>
       </c>
       <c r="E309" s="8">
         <v>3.65</v>
@@ -13636,7 +13636,7 @@
         <v>3.8</v>
       </c>
       <c r="H309" s="9" t="s">
-        <v>1078</v>
+        <v>1057</v>
       </c>
       <c r="I309" s="6"/>
     </row>
@@ -13648,10 +13648,10 @@
         <v>8</v>
       </c>
       <c r="C310" s="7" t="s">
-        <v>1059</v>
+        <v>1038</v>
       </c>
       <c r="D310" s="7" t="s">
-        <v>1067</v>
+        <v>1046</v>
       </c>
       <c r="E310" s="8">
         <v>3.28</v>
@@ -13663,7 +13663,7 @@
         <v>3.6</v>
       </c>
       <c r="H310" s="9" t="s">
-        <v>1079</v>
+        <v>1058</v>
       </c>
       <c r="I310" s="6"/>
     </row>
@@ -13678,7 +13678,7 @@
         <v>34</v>
       </c>
       <c r="D311" s="7" t="s">
-        <v>1068</v>
+        <v>1047</v>
       </c>
       <c r="E311" s="8">
         <v>3.74</v>
@@ -13690,7 +13690,7 @@
         <v>4.2</v>
       </c>
       <c r="H311" s="9" t="s">
-        <v>1080</v>
+        <v>1059</v>
       </c>
       <c r="I311" s="6"/>
     </row>
@@ -13707,7 +13707,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
-        <v>1082</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -13715,7 +13715,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>1083</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -13723,7 +13723,7 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>1084</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
@@ -13737,7 +13737,7 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
-        <v>1085</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
@@ -13745,7 +13745,7 @@
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
-        <v>1086</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
@@ -13753,12 +13753,12 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
-        <v>1087</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="18" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>1088</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
@@ -13766,7 +13766,7 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
-        <v>1089</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -13774,7 +13774,7 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="15" t="s">
-        <v>1084</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
@@ -13788,7 +13788,7 @@
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
-        <v>1090</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
@@ -13796,7 +13796,7 @@
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
-        <v>1091</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
@@ -13804,12 +13804,12 @@
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="s">
-        <v>1092</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1093</v>
+        <v>1072</v>
       </c>
     </row>
   </sheetData>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58ABF085-9A7F-4236-ABE7-8F4FEE892DE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7CD2429-4790-45FD-9E2C-802C7498F1D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3468,9 +3468,6 @@
     <t>Hard Rock, Gospel [	Spiritual Rock, Anthemic Heavy Soul]</t>
   </si>
   <si>
-    <t>Genres_Subgenres_Styles</t>
-  </si>
-  <si>
     <t>Blues Rock, Pop Rock [Classic Rock, Hard Rock, Roots Rock]</t>
   </si>
   <si>
@@ -3508,6 +3505,9 @@
   </si>
   <si>
     <t>Country Blues, Delta Blues [Acoustic Blues, Traditional Blues Cover]</t>
+  </si>
+  <si>
+    <t>Genres_Subgenres</t>
   </si>
 </sst>
 </file>
@@ -4016,7 +4016,7 @@
         <v>60</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>1080</v>
+        <v>1093</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>61</v>
@@ -5072,7 +5072,7 @@
         <v>3.08</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="G34" s="7" t="s">
         <v>997</v>
@@ -5254,7 +5254,7 @@
         <v>64</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>1080</v>
+        <v>1093</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>60</v>
@@ -12976,7 +12976,7 @@
         <v>985</v>
       </c>
       <c r="D285" s="7" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="E285" s="8">
         <v>3.44</v>
@@ -13003,7 +13003,7 @@
         <v>986</v>
       </c>
       <c r="D286" s="7" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="E286" s="8">
         <v>3.39</v>
@@ -13030,7 +13030,7 @@
         <v>994</v>
       </c>
       <c r="D287" s="7" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="E287" s="8">
         <v>3.36</v>
@@ -13057,7 +13057,7 @@
         <v>987</v>
       </c>
       <c r="D288" s="7" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="E288" s="8">
         <v>3.35</v>
@@ -13084,7 +13084,7 @@
         <v>988</v>
       </c>
       <c r="D289" s="7" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="E289" s="8">
         <v>3.34</v>
@@ -13111,7 +13111,7 @@
         <v>989</v>
       </c>
       <c r="D290" s="7" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E290" s="8">
         <v>3.24</v>
@@ -13138,7 +13138,7 @@
         <v>990</v>
       </c>
       <c r="D291" s="7" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="E291" s="8">
         <v>3.27</v>
@@ -13165,7 +13165,7 @@
         <v>995</v>
       </c>
       <c r="D292" s="7" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="E292" s="8">
         <v>3.21</v>
@@ -13192,7 +13192,7 @@
         <v>991</v>
       </c>
       <c r="D293" s="7" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="E293" s="8">
         <v>3.15</v>
@@ -13219,7 +13219,7 @@
         <v>992</v>
       </c>
       <c r="D294" s="7" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="E294" s="8">
         <v>3.07</v>
@@ -13246,7 +13246,7 @@
         <v>996</v>
       </c>
       <c r="D295" s="7" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="E295" s="8">
         <v>3.72</v>
@@ -13273,7 +13273,7 @@
         <v>993</v>
       </c>
       <c r="D296" s="7" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E296" s="8">
         <v>3.31</v>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7CD2429-4790-45FD-9E2C-802C7498F1D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CB944DF-8033-4968-A670-FFF7FC771AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="1094">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="1096">
   <si>
     <t>No</t>
   </si>
@@ -2730,45 +2730,12 @@
     <t>https://i.discogs.com/q0_IeQSpoqAEwU3gC1gL7-pq6csIBpHACJg3CT7piF0/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI2MjA3/ODUyLTE2NzcyMzMx/MjUtNTE2MS5qcGVn.jpeg</t>
   </si>
   <si>
-    <t>Blues Rock, Hard Rock, Psychedelic Rock, Roots Rock</t>
-  </si>
-  <si>
     <t>Atomic Fire – AFR0076V (LP, Album, Limited Edition, Clear Vinyl, 2023)</t>
   </si>
   <si>
     <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Κυκλοφόρησε το 2023 σε περιορισμένη έκδοση 1000 αντιτύπων σε διάφανο βινύλιο από την Atomic Fire. Ηχογραφημένο με αναλογική φιλοσοφία και vintage εξοπλισμό, αποτυπώνει αυθεντικά την ατμόσφαιρα του 70s hard rock και blues-rock.</t>
   </si>
   <si>
-    <t>Classic Heavy Rock / Organ-driven Psych</t>
-  </si>
-  <si>
-    <t>Heavy Psych</t>
-  </si>
-  <si>
-    <t>Classic Rock, Boogie Rock</t>
-  </si>
-  <si>
-    <t>Roots Rock</t>
-  </si>
-  <si>
-    <t>Dark Folk, Blues, Appalachian Rock</t>
-  </si>
-  <si>
-    <t>Nordic Folk, Pagan Folk [Instrumental]</t>
-  </si>
-  <si>
-    <t>Folk Psych, Instrumental</t>
-  </si>
-  <si>
-    <t>Acoustic Ballad, Folk Rock</t>
-  </si>
-  <si>
-    <t>Eastern Psych, Indo-Rock, Instrumental Jam</t>
-  </si>
-  <si>
-    <t>Heavy Blues Rock</t>
-  </si>
-  <si>
     <t>Δυναμικό ξεκίνημα με fuzz κιθάρες, βαρύ rhythm section και στίχους για την ευθραυστότητα της ζωής και τον φόβο του θανάτου.</t>
   </si>
   <si>
@@ -2829,9 +2796,6 @@
     <t>Next…</t>
   </si>
   <si>
-    <t>Art Rock, Glam Rock, Hard Rock, Blues Rock</t>
-  </si>
-  <si>
     <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το τρίτο στούντιο άλμπουμ του συγκροτήματος και ένα από τα πιο πρωτοποριακά δείγματα του βρετανικού art/glam rock. Σε παραγωγή του David Batchelor, το άλμπουμ συνδυάζει θεατρικότητα, cabaret στοιχεία, βαριά blues riff και την εκκεντρική, επιβλητική προσωπικότητα του Alex Harvey.</t>
   </si>
   <si>
@@ -2865,27 +2829,6 @@
     <t>https://i.discogs.com/IzxpGXhfn0nzI-5F5piMx3K2n2tgy8s1unE74VzwIcU/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTM1MDc2/OTctMTUyMjU4NDAz/MS0zOTYwLmpwZWc.jpeg</t>
   </si>
   <si>
-    <t>Glam Rock, Heavy Funk Rock</t>
-  </si>
-  <si>
-    <t>Pub Rock, Boogie Rock</t>
-  </si>
-  <si>
-    <t>50s Rockabilly Revival, Hard Boogie</t>
-  </si>
-  <si>
-    <t>Dark Cabaret, Theatrical Rock, Tango</t>
-  </si>
-  <si>
-    <t>Heavy Metal, Heavy Prog, Glam</t>
-  </si>
-  <si>
-    <t>Multi-Part Suite, Glam Rock, Doo-Wop Parody</t>
-  </si>
-  <si>
-    <t>Heavy Psych, Proto-Industrial, Art Rock</t>
-  </si>
-  <si>
     <t>Moving Pictures</t>
   </si>
   <si>
@@ -2925,28 +2868,7 @@
     <t>Mercury – B00223080-01, Universal Music Enterprises – B00223080-01, Anthem (5) – B00223080-01 (LP, Album, Reissue, Stereo, 150g, DMM, Europe, 2015)</t>
   </si>
   <si>
-    <t>Synth-Rock, Classic Rock</t>
-  </si>
-  <si>
     <t>Ο απόλυτος ύμνος του συγκροτήματος, με το χαρακτηριστικό Oberheim synth sweep, το πολυρυθμικό σόλο τυμπάνων του Peart και στίχους για το αδάμαστο, ελεύθερο πνεύμα.</t>
-  </si>
-  <si>
-    <t>Sci-Fi Rock, Narrative Prog</t>
-  </si>
-  <si>
-    <t>Heavy Prog, Instrumental Virtuoso</t>
-  </si>
-  <si>
-    <t>Arena Rock, Melodic Hard Rock</t>
-  </si>
-  <si>
-    <t>Epic Progressive Rock, Synth-Prog</t>
-  </si>
-  <si>
-    <t>Heavy Prog, Dark Art Rock</t>
-  </si>
-  <si>
-    <t>Reggae-Rock, Post-Punk - Influenced Rock</t>
   </si>
   <si>
     <t>Φουτουριστική αφήγηση εμπνευσμένη από το διήγημα «A Nice Morning Drive», που περιγράφει μια παράνομη διαδρομή με ένα κλασικό σπορ αυτοκίνητο σε έναν δυστοπικό κόσμο αυστηρού ελέγχου.</t>
@@ -3508,6 +3430,90 @@
   </si>
   <si>
     <t>Genres_Subgenres</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Hard Rock [Art Rock, Synth-Rock, New Wave-influenced Prog]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Progressive Rock [Synth-Rock, Classic Rock]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Hard Rock [Sci-Fi Rock, Narrative Prog]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Jazz Fusion [Heavy Prog, Instrumental Virtuoso (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Progressive Rock [Arena Rock, Melodic Hard Rock]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Art Rock [Epic Progressive Rock, Synth-Prog]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Hard Rock [Heavy Prog, Dark Art Rock]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, New Wave [Reggae-Rock, Post-Punk-influenced Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Glam Rock [Art Rock, Blues Rock, Theatrical Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Glam Rock, Heavy Funk Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Pub Rock, Boogie Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Krautrock [Heavy Psych, Proto-Industrial, Art Rock]</t>
+  </si>
+  <si>
+    <t>Rock &amp; Roll, Glam Rock [50s Rockabilly Revival, Hard Boogie]</t>
+  </si>
+  <si>
+    <t>Art Rock, Chanson [Dark Cabaret, Theatrical Rock, Tango]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Psych [Heavy Metal, Heavy Prog, Glam]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Rock &amp; Roll [Multi-Part Suite, Glam Rock, Doo-Wop Parody]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Psychedelic Rock [Retro-Rock, Folk Rock, Blues Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Heavy Psych, Vintage 70s Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Classic Rock, Boogie Rock]</t>
+  </si>
+  <si>
+    <t>Folk Rock, Blues Rock [Acoustic Rock, Acoustic Blues]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Psychedelic Rock [Dynamic Roots Rock]</t>
+  </si>
+  <si>
+    <t>Folk Rock, Blues Rock [Dark Folk, Blues, Appalachian Rock]</t>
+  </si>
+  <si>
+    <t>Folk Rock, Acoustic [Nordic Folk, Pagan Folk (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Psychedelic Rock, Folk Rock [Folk Psych, Raga-influenced Instrumental]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Psychedelic Rock [Classic Heavy Rock, Organ-driven Psych]</t>
+  </si>
+  <si>
+    <t>Folk Rock, Hard Rock [Acoustic Ballad, Woodsy Folk Rock]</t>
+  </si>
+  <si>
+    <t>Psychedelic Rock, Raga Rock [Eastern Psych, Indo-Rock, Instrumental Jam]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Classic Rock [Dynamic Heavy Blues Rock, Epilogue]</t>
   </si>
 </sst>
 </file>
@@ -3983,7 +3989,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -3991,9 +3997,9 @@
     <col min="3" max="3" width="25.7109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="12.7109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="10.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="31.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.7109375" style="1" customWidth="1"/>
     <col min="7" max="7" width="96.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.7109375" style="1" customWidth="1"/>
     <col min="9" max="9" width="35" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="50.42578125" style="1" customWidth="1"/>
     <col min="11" max="16384" width="9.140625" style="1"/>
@@ -4016,7 +4022,7 @@
         <v>60</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>1093</v>
+        <v>1067</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>61</v>
@@ -4479,7 +4485,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="73.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="63" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>2138840</v>
       </c>
@@ -4511,7 +4517,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="84" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="73.5" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>10867099</v>
       </c>
@@ -4831,7 +4837,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>22420804</v>
       </c>
@@ -4976,13 +4982,13 @@
         <v>3.29</v>
       </c>
       <c r="F31" s="9" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>903</v>
+      </c>
+      <c r="H31" s="6" t="s">
         <v>902</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>904</v>
-      </c>
-      <c r="H31" s="6" t="s">
-        <v>903</v>
       </c>
       <c r="I31" s="11" t="s">
         <v>900</v>
@@ -4996,10 +5002,10 @@
         <v>3507697</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>933</v>
+        <v>922</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>934</v>
+        <v>923</v>
       </c>
       <c r="D32" s="6">
         <v>1973</v>
@@ -5008,30 +5014,30 @@
         <v>3.29</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>935</v>
+        <v>1076</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>936</v>
+        <v>924</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>944</v>
+        <v>932</v>
       </c>
       <c r="I32" s="11" t="s">
-        <v>945</v>
+        <v>933</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="84" x14ac:dyDescent="0.25">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="63" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>33253932</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>955</v>
+        <v>936</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>954</v>
+        <v>935</v>
       </c>
       <c r="D33" s="6">
         <v>1981</v>
@@ -5040,19 +5046,19 @@
         <v>3.94</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>256</v>
+        <v>1068</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>965</v>
+        <v>946</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>966</v>
+        <v>947</v>
       </c>
       <c r="I33" s="11" t="s">
-        <v>956</v>
+        <v>937</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>957</v>
+        <v>938</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="42" x14ac:dyDescent="0.25">
@@ -5060,10 +5066,10 @@
         <v>28518808</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>981</v>
+        <v>955</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>982</v>
+        <v>956</v>
       </c>
       <c r="D34" s="6">
         <v>2023</v>
@@ -5072,19 +5078,19 @@
         <v>3.08</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>1080</v>
+        <v>1054</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>997</v>
+        <v>971</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>998</v>
+        <v>972</v>
       </c>
       <c r="I34" s="11" t="s">
-        <v>983</v>
+        <v>957</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>984</v>
+        <v>958</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="42" x14ac:dyDescent="0.25">
@@ -5092,10 +5098,10 @@
         <v>28649152</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>1017</v>
+        <v>991</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>1018</v>
+        <v>992</v>
       </c>
       <c r="D35" s="6">
         <v>2023</v>
@@ -5104,19 +5110,19 @@
         <v>3.47</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>1073</v>
+        <v>1047</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>1021</v>
+        <v>995</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>1028</v>
+        <v>1002</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>1019</v>
+        <v>993</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>1020</v>
+        <v>994</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="42" x14ac:dyDescent="0.25">
@@ -5124,10 +5130,10 @@
         <v>25412281</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>1029</v>
+        <v>1003</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>1030</v>
+        <v>1004</v>
       </c>
       <c r="D36" s="6">
         <v>2022</v>
@@ -5136,20 +5142,32 @@
         <v>3.41</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>1048</v>
+        <v>1022</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>1049</v>
+        <v>1023</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>1050</v>
+        <v>1024</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>1032</v>
+        <v>1006</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>1031</v>
-      </c>
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="6"/>
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="7"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="11"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -5228,7 +5246,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I311"/>
+  <dimension ref="A1:I312"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="3" bestFit="1" customWidth="1"/>
@@ -5254,7 +5272,7 @@
         <v>64</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>1093</v>
+        <v>1067</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>60</v>
@@ -12295,7 +12313,7 @@
         <v>889</v>
       </c>
       <c r="D260" s="7" t="s">
-        <v>906</v>
+        <v>1085</v>
       </c>
       <c r="E260" s="8">
         <v>3.76</v>
@@ -12307,7 +12325,7 @@
         <v>4</v>
       </c>
       <c r="H260" s="9" t="s">
-        <v>915</v>
+        <v>904</v>
       </c>
       <c r="I260" s="6"/>
     </row>
@@ -12322,7 +12340,7 @@
         <v>890</v>
       </c>
       <c r="D261" s="7" t="s">
-        <v>907</v>
+        <v>1086</v>
       </c>
       <c r="E261" s="8">
         <v>3.67</v>
@@ -12334,7 +12352,7 @@
         <v>3.8</v>
       </c>
       <c r="H261" s="9" t="s">
-        <v>916</v>
+        <v>905</v>
       </c>
       <c r="I261" s="6"/>
     </row>
@@ -12349,7 +12367,7 @@
         <v>891</v>
       </c>
       <c r="D262" s="7" t="s">
-        <v>793</v>
+        <v>1087</v>
       </c>
       <c r="E262" s="8">
         <v>3.5</v>
@@ -12361,7 +12379,7 @@
         <v>3.7</v>
       </c>
       <c r="H262" s="9" t="s">
-        <v>917</v>
+        <v>906</v>
       </c>
       <c r="I262" s="6"/>
     </row>
@@ -12376,7 +12394,7 @@
         <v>892</v>
       </c>
       <c r="D263" s="7" t="s">
-        <v>908</v>
+        <v>1088</v>
       </c>
       <c r="E263" s="8">
         <v>3.33</v>
@@ -12388,7 +12406,7 @@
         <v>3.7</v>
       </c>
       <c r="H263" s="9" t="s">
-        <v>918</v>
+        <v>907</v>
       </c>
       <c r="I263" s="6"/>
     </row>
@@ -12403,7 +12421,7 @@
         <v>893</v>
       </c>
       <c r="D264" s="7" t="s">
-        <v>909</v>
+        <v>1089</v>
       </c>
       <c r="E264" s="8">
         <v>3.33</v>
@@ -12415,7 +12433,7 @@
         <v>3.8</v>
       </c>
       <c r="H264" s="9" t="s">
-        <v>919</v>
+        <v>908</v>
       </c>
       <c r="I264" s="6"/>
     </row>
@@ -12430,7 +12448,7 @@
         <v>894</v>
       </c>
       <c r="D265" s="7" t="s">
-        <v>910</v>
+        <v>1090</v>
       </c>
       <c r="E265" s="8">
         <v>3.33</v>
@@ -12442,7 +12460,7 @@
         <v>3.6</v>
       </c>
       <c r="H265" s="9" t="s">
-        <v>920</v>
+        <v>909</v>
       </c>
       <c r="I265" s="6"/>
     </row>
@@ -12457,7 +12475,7 @@
         <v>895</v>
       </c>
       <c r="D266" s="7" t="s">
-        <v>911</v>
+        <v>1091</v>
       </c>
       <c r="E266" s="8">
         <v>3.33</v>
@@ -12469,7 +12487,7 @@
         <v>3.7</v>
       </c>
       <c r="H266" s="9" t="s">
-        <v>921</v>
+        <v>910</v>
       </c>
       <c r="I266" s="6"/>
     </row>
@@ -12484,7 +12502,7 @@
         <v>896</v>
       </c>
       <c r="D267" s="7" t="s">
-        <v>905</v>
+        <v>1092</v>
       </c>
       <c r="E267" s="8">
         <v>3.33</v>
@@ -12496,7 +12514,7 @@
         <v>3.7</v>
       </c>
       <c r="H267" s="9" t="s">
-        <v>922</v>
+        <v>911</v>
       </c>
       <c r="I267" s="6"/>
     </row>
@@ -12511,7 +12529,7 @@
         <v>897</v>
       </c>
       <c r="D268" s="7" t="s">
-        <v>912</v>
+        <v>1093</v>
       </c>
       <c r="E268" s="8">
         <v>3.33</v>
@@ -12523,7 +12541,7 @@
         <v>3.7</v>
       </c>
       <c r="H268" s="9" t="s">
-        <v>923</v>
+        <v>912</v>
       </c>
       <c r="I268" s="6"/>
     </row>
@@ -12538,7 +12556,7 @@
         <v>898</v>
       </c>
       <c r="D269" s="7" t="s">
-        <v>913</v>
+        <v>1094</v>
       </c>
       <c r="E269" s="8">
         <v>3.5</v>
@@ -12550,7 +12568,7 @@
         <v>3.9</v>
       </c>
       <c r="H269" s="9" t="s">
-        <v>924</v>
+        <v>913</v>
       </c>
       <c r="I269" s="6"/>
     </row>
@@ -12565,7 +12583,7 @@
         <v>899</v>
       </c>
       <c r="D270" s="7" t="s">
-        <v>914</v>
+        <v>1095</v>
       </c>
       <c r="E270" s="8">
         <v>3.91</v>
@@ -12577,7 +12595,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H270" s="9" t="s">
-        <v>925</v>
+        <v>914</v>
       </c>
       <c r="I270" s="6"/>
     </row>
@@ -12589,10 +12607,10 @@
         <v>1</v>
       </c>
       <c r="C271" s="7" t="s">
-        <v>926</v>
+        <v>915</v>
       </c>
       <c r="D271" s="7" t="s">
-        <v>947</v>
+        <v>1077</v>
       </c>
       <c r="E271" s="8">
         <v>3.52</v>
@@ -12604,7 +12622,7 @@
         <v>3.9</v>
       </c>
       <c r="H271" s="9" t="s">
-        <v>937</v>
+        <v>925</v>
       </c>
       <c r="I271" s="6"/>
     </row>
@@ -12616,10 +12634,10 @@
         <v>2</v>
       </c>
       <c r="C272" s="7" t="s">
-        <v>927</v>
+        <v>916</v>
       </c>
       <c r="D272" s="7" t="s">
-        <v>948</v>
+        <v>1078</v>
       </c>
       <c r="E272" s="8">
         <v>3.35</v>
@@ -12631,7 +12649,7 @@
         <v>3.8</v>
       </c>
       <c r="H272" s="9" t="s">
-        <v>938</v>
+        <v>926</v>
       </c>
       <c r="I272" s="6"/>
     </row>
@@ -12643,10 +12661,10 @@
         <v>3</v>
       </c>
       <c r="C273" s="7" t="s">
-        <v>928</v>
+        <v>917</v>
       </c>
       <c r="D273" s="7" t="s">
-        <v>953</v>
+        <v>1079</v>
       </c>
       <c r="E273" s="8">
         <v>3.66</v>
@@ -12658,7 +12676,7 @@
         <v>4.7</v>
       </c>
       <c r="H273" s="9" t="s">
-        <v>939</v>
+        <v>927</v>
       </c>
       <c r="I273" s="6" t="s">
         <v>312</v>
@@ -12672,10 +12690,10 @@
         <v>4</v>
       </c>
       <c r="C274" s="7" t="s">
-        <v>929</v>
+        <v>918</v>
       </c>
       <c r="D274" s="7" t="s">
-        <v>949</v>
+        <v>1080</v>
       </c>
       <c r="E274" s="8">
         <v>3.18</v>
@@ -12687,7 +12705,7 @@
         <v>3.7</v>
       </c>
       <c r="H274" s="9" t="s">
-        <v>940</v>
+        <v>928</v>
       </c>
       <c r="I274" s="6"/>
     </row>
@@ -12699,10 +12717,10 @@
         <v>5</v>
       </c>
       <c r="C275" s="7" t="s">
-        <v>930</v>
+        <v>919</v>
       </c>
       <c r="D275" s="7" t="s">
-        <v>950</v>
+        <v>1081</v>
       </c>
       <c r="E275" s="8">
         <v>3.49</v>
@@ -12714,7 +12732,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H275" s="9" t="s">
-        <v>942</v>
+        <v>930</v>
       </c>
       <c r="I275" s="6" t="s">
         <v>312</v>
@@ -12728,10 +12746,10 @@
         <v>6</v>
       </c>
       <c r="C276" s="7" t="s">
-        <v>931</v>
+        <v>920</v>
       </c>
       <c r="D276" s="7" t="s">
-        <v>951</v>
+        <v>1082</v>
       </c>
       <c r="E276" s="8">
         <v>3.45</v>
@@ -12743,7 +12761,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H276" s="9" t="s">
-        <v>941</v>
+        <v>929</v>
       </c>
       <c r="I276" s="6"/>
     </row>
@@ -12755,10 +12773,10 @@
         <v>7</v>
       </c>
       <c r="C277" s="7" t="s">
-        <v>932</v>
+        <v>921</v>
       </c>
       <c r="D277" s="7" t="s">
-        <v>952</v>
+        <v>1083</v>
       </c>
       <c r="E277" s="8">
         <v>3.61</v>
@@ -12770,7 +12788,7 @@
         <v>4.3</v>
       </c>
       <c r="H277" s="9" t="s">
-        <v>943</v>
+        <v>931</v>
       </c>
       <c r="I277" s="6"/>
     </row>
@@ -12782,10 +12800,10 @@
         <v>1</v>
       </c>
       <c r="C278" s="7" t="s">
-        <v>958</v>
+        <v>939</v>
       </c>
       <c r="D278" s="7" t="s">
-        <v>967</v>
+        <v>1069</v>
       </c>
       <c r="E278" s="8">
         <v>4.46</v>
@@ -12797,7 +12815,7 @@
         <v>4.8</v>
       </c>
       <c r="H278" s="9" t="s">
-        <v>968</v>
+        <v>948</v>
       </c>
       <c r="I278" s="6" t="s">
         <v>312</v>
@@ -12811,10 +12829,10 @@
         <v>2</v>
       </c>
       <c r="C279" s="7" t="s">
-        <v>959</v>
+        <v>940</v>
       </c>
       <c r="D279" s="7" t="s">
-        <v>969</v>
+        <v>1070</v>
       </c>
       <c r="E279" s="8">
         <v>4.2</v>
@@ -12826,7 +12844,7 @@
         <v>4.7</v>
       </c>
       <c r="H279" s="9" t="s">
-        <v>975</v>
+        <v>949</v>
       </c>
       <c r="I279" s="6"/>
     </row>
@@ -12838,10 +12856,10 @@
         <v>3</v>
       </c>
       <c r="C280" s="7" t="s">
-        <v>960</v>
+        <v>941</v>
       </c>
       <c r="D280" s="7" t="s">
-        <v>970</v>
+        <v>1071</v>
       </c>
       <c r="E280" s="8">
         <v>4.41</v>
@@ -12853,7 +12871,7 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="H280" s="9" t="s">
-        <v>976</v>
+        <v>950</v>
       </c>
       <c r="I280" s="6"/>
     </row>
@@ -12865,10 +12883,10 @@
         <v>4</v>
       </c>
       <c r="C281" s="7" t="s">
-        <v>961</v>
+        <v>942</v>
       </c>
       <c r="D281" s="7" t="s">
-        <v>971</v>
+        <v>1072</v>
       </c>
       <c r="E281" s="8">
         <v>4.33</v>
@@ -12880,7 +12898,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H281" s="9" t="s">
-        <v>977</v>
+        <v>951</v>
       </c>
       <c r="I281" s="6"/>
     </row>
@@ -12892,10 +12910,10 @@
         <v>5</v>
       </c>
       <c r="C282" s="7" t="s">
-        <v>964</v>
+        <v>945</v>
       </c>
       <c r="D282" s="7" t="s">
-        <v>972</v>
+        <v>1073</v>
       </c>
       <c r="E282" s="8">
         <v>4.07</v>
@@ -12907,7 +12925,7 @@
         <v>4.7</v>
       </c>
       <c r="H282" s="9" t="s">
-        <v>978</v>
+        <v>952</v>
       </c>
       <c r="I282" s="6"/>
     </row>
@@ -12919,10 +12937,10 @@
         <v>6</v>
       </c>
       <c r="C283" s="7" t="s">
-        <v>962</v>
+        <v>943</v>
       </c>
       <c r="D283" s="7" t="s">
-        <v>973</v>
+        <v>1074</v>
       </c>
       <c r="E283" s="8">
         <v>3.82</v>
@@ -12934,7 +12952,7 @@
         <v>4.7</v>
       </c>
       <c r="H283" s="9" t="s">
-        <v>979</v>
+        <v>953</v>
       </c>
       <c r="I283" s="6"/>
     </row>
@@ -12946,10 +12964,10 @@
         <v>7</v>
       </c>
       <c r="C284" s="7" t="s">
-        <v>963</v>
+        <v>944</v>
       </c>
       <c r="D284" s="7" t="s">
-        <v>974</v>
+        <v>1075</v>
       </c>
       <c r="E284" s="8">
         <v>3.91</v>
@@ -12961,7 +12979,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H284" s="9" t="s">
-        <v>980</v>
+        <v>954</v>
       </c>
       <c r="I284" s="6"/>
     </row>
@@ -12973,10 +12991,10 @@
         <v>1</v>
       </c>
       <c r="C285" s="7" t="s">
-        <v>985</v>
+        <v>959</v>
       </c>
       <c r="D285" s="7" t="s">
-        <v>1081</v>
+        <v>1055</v>
       </c>
       <c r="E285" s="8">
         <v>3.44</v>
@@ -12988,7 +13006,7 @@
         <v>3.7</v>
       </c>
       <c r="H285" s="9" t="s">
-        <v>999</v>
+        <v>973</v>
       </c>
       <c r="I285" s="6"/>
     </row>
@@ -13000,10 +13018,10 @@
         <v>2</v>
       </c>
       <c r="C286" s="7" t="s">
-        <v>986</v>
+        <v>960</v>
       </c>
       <c r="D286" s="7" t="s">
-        <v>1082</v>
+        <v>1056</v>
       </c>
       <c r="E286" s="8">
         <v>3.39</v>
@@ -13015,7 +13033,7 @@
         <v>3.5</v>
       </c>
       <c r="H286" s="9" t="s">
-        <v>1000</v>
+        <v>974</v>
       </c>
       <c r="I286" s="6"/>
     </row>
@@ -13027,10 +13045,10 @@
         <v>3</v>
       </c>
       <c r="C287" s="7" t="s">
-        <v>994</v>
+        <v>968</v>
       </c>
       <c r="D287" s="7" t="s">
-        <v>1083</v>
+        <v>1057</v>
       </c>
       <c r="E287" s="8">
         <v>3.36</v>
@@ -13042,7 +13060,7 @@
         <v>3.6</v>
       </c>
       <c r="H287" s="9" t="s">
-        <v>1001</v>
+        <v>975</v>
       </c>
       <c r="I287" s="6"/>
     </row>
@@ -13054,10 +13072,10 @@
         <v>4</v>
       </c>
       <c r="C288" s="7" t="s">
-        <v>987</v>
+        <v>961</v>
       </c>
       <c r="D288" s="7" t="s">
-        <v>1084</v>
+        <v>1058</v>
       </c>
       <c r="E288" s="8">
         <v>3.35</v>
@@ -13069,7 +13087,7 @@
         <v>3.7</v>
       </c>
       <c r="H288" s="9" t="s">
-        <v>1002</v>
+        <v>976</v>
       </c>
       <c r="I288" s="6"/>
     </row>
@@ -13081,10 +13099,10 @@
         <v>5</v>
       </c>
       <c r="C289" s="7" t="s">
-        <v>988</v>
+        <v>962</v>
       </c>
       <c r="D289" s="7" t="s">
-        <v>1085</v>
+        <v>1059</v>
       </c>
       <c r="E289" s="8">
         <v>3.34</v>
@@ -13096,7 +13114,7 @@
         <v>3.7</v>
       </c>
       <c r="H289" s="9" t="s">
-        <v>1003</v>
+        <v>977</v>
       </c>
       <c r="I289" s="6"/>
     </row>
@@ -13108,10 +13126,10 @@
         <v>6</v>
       </c>
       <c r="C290" s="7" t="s">
-        <v>989</v>
+        <v>963</v>
       </c>
       <c r="D290" s="7" t="s">
-        <v>1086</v>
+        <v>1060</v>
       </c>
       <c r="E290" s="8">
         <v>3.24</v>
@@ -13123,7 +13141,7 @@
         <v>3.8</v>
       </c>
       <c r="H290" s="9" t="s">
-        <v>1004</v>
+        <v>978</v>
       </c>
       <c r="I290" s="6"/>
     </row>
@@ -13135,10 +13153,10 @@
         <v>7</v>
       </c>
       <c r="C291" s="7" t="s">
-        <v>990</v>
+        <v>964</v>
       </c>
       <c r="D291" s="7" t="s">
-        <v>1087</v>
+        <v>1061</v>
       </c>
       <c r="E291" s="8">
         <v>3.27</v>
@@ -13150,7 +13168,7 @@
         <v>3.5</v>
       </c>
       <c r="H291" s="9" t="s">
-        <v>1005</v>
+        <v>979</v>
       </c>
       <c r="I291" s="6"/>
     </row>
@@ -13162,10 +13180,10 @@
         <v>8</v>
       </c>
       <c r="C292" s="7" t="s">
-        <v>995</v>
+        <v>969</v>
       </c>
       <c r="D292" s="7" t="s">
-        <v>1088</v>
+        <v>1062</v>
       </c>
       <c r="E292" s="8">
         <v>3.21</v>
@@ -13177,7 +13195,7 @@
         <v>3.7</v>
       </c>
       <c r="H292" s="9" t="s">
-        <v>1006</v>
+        <v>980</v>
       </c>
       <c r="I292" s="6"/>
     </row>
@@ -13189,10 +13207,10 @@
         <v>9</v>
       </c>
       <c r="C293" s="7" t="s">
-        <v>991</v>
+        <v>965</v>
       </c>
       <c r="D293" s="7" t="s">
-        <v>1089</v>
+        <v>1063</v>
       </c>
       <c r="E293" s="8">
         <v>3.15</v>
@@ -13204,7 +13222,7 @@
         <v>3.5</v>
       </c>
       <c r="H293" s="9" t="s">
-        <v>1007</v>
+        <v>981</v>
       </c>
       <c r="I293" s="6"/>
     </row>
@@ -13216,10 +13234,10 @@
         <v>10</v>
       </c>
       <c r="C294" s="7" t="s">
-        <v>992</v>
+        <v>966</v>
       </c>
       <c r="D294" s="7" t="s">
-        <v>1090</v>
+        <v>1064</v>
       </c>
       <c r="E294" s="8">
         <v>3.07</v>
@@ -13231,7 +13249,7 @@
         <v>3.7</v>
       </c>
       <c r="H294" s="9" t="s">
-        <v>1008</v>
+        <v>982</v>
       </c>
       <c r="I294" s="6"/>
     </row>
@@ -13243,10 +13261,10 @@
         <v>11</v>
       </c>
       <c r="C295" s="7" t="s">
-        <v>996</v>
+        <v>970</v>
       </c>
       <c r="D295" s="7" t="s">
-        <v>1091</v>
+        <v>1065</v>
       </c>
       <c r="E295" s="8">
         <v>3.72</v>
@@ -13258,7 +13276,7 @@
         <v>4.2</v>
       </c>
       <c r="H295" s="9" t="s">
-        <v>1009</v>
+        <v>983</v>
       </c>
       <c r="I295" s="6"/>
     </row>
@@ -13270,10 +13288,10 @@
         <v>12</v>
       </c>
       <c r="C296" s="7" t="s">
-        <v>993</v>
+        <v>967</v>
       </c>
       <c r="D296" s="7" t="s">
-        <v>1092</v>
+        <v>1066</v>
       </c>
       <c r="E296" s="8">
         <v>3.31</v>
@@ -13285,7 +13303,7 @@
         <v>4</v>
       </c>
       <c r="H296" s="9" t="s">
-        <v>1010</v>
+        <v>984</v>
       </c>
       <c r="I296" s="6"/>
     </row>
@@ -13297,10 +13315,10 @@
         <v>1</v>
       </c>
       <c r="C297" s="7" t="s">
-        <v>1011</v>
+        <v>985</v>
       </c>
       <c r="D297" s="7" t="s">
-        <v>1074</v>
+        <v>1048</v>
       </c>
       <c r="E297" s="8">
         <v>3.66</v>
@@ -13312,7 +13330,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H297" s="9" t="s">
-        <v>1022</v>
+        <v>996</v>
       </c>
       <c r="I297" s="6"/>
     </row>
@@ -13324,10 +13342,10 @@
         <v>2</v>
       </c>
       <c r="C298" s="7" t="s">
-        <v>1012</v>
+        <v>986</v>
       </c>
       <c r="D298" s="7" t="s">
-        <v>1075</v>
+        <v>1049</v>
       </c>
       <c r="E298" s="8">
         <v>3.51</v>
@@ -13339,7 +13357,7 @@
         <v>3.8</v>
       </c>
       <c r="H298" s="9" t="s">
-        <v>1023</v>
+        <v>997</v>
       </c>
       <c r="I298" s="6"/>
     </row>
@@ -13351,10 +13369,10 @@
         <v>3</v>
       </c>
       <c r="C299" s="7" t="s">
-        <v>1013</v>
+        <v>987</v>
       </c>
       <c r="D299" s="7" t="s">
-        <v>1076</v>
+        <v>1050</v>
       </c>
       <c r="E299" s="8">
         <v>3.43</v>
@@ -13366,7 +13384,7 @@
         <v>3.9</v>
       </c>
       <c r="H299" s="9" t="s">
-        <v>1024</v>
+        <v>998</v>
       </c>
       <c r="I299" s="6"/>
     </row>
@@ -13378,10 +13396,10 @@
         <v>4</v>
       </c>
       <c r="C300" s="7" t="s">
-        <v>1014</v>
+        <v>988</v>
       </c>
       <c r="D300" s="7" t="s">
-        <v>1077</v>
+        <v>1051</v>
       </c>
       <c r="E300" s="8">
         <v>3.51</v>
@@ -13393,7 +13411,7 @@
         <v>3.7</v>
       </c>
       <c r="H300" s="9" t="s">
-        <v>1025</v>
+        <v>999</v>
       </c>
       <c r="I300" s="6"/>
     </row>
@@ -13405,10 +13423,10 @@
         <v>5</v>
       </c>
       <c r="C301" s="7" t="s">
-        <v>1015</v>
+        <v>989</v>
       </c>
       <c r="D301" s="7" t="s">
-        <v>1078</v>
+        <v>1052</v>
       </c>
       <c r="E301" s="8">
         <v>3.48</v>
@@ -13420,7 +13438,7 @@
         <v>3.9</v>
       </c>
       <c r="H301" s="9" t="s">
-        <v>1027</v>
+        <v>1001</v>
       </c>
       <c r="I301" s="6"/>
     </row>
@@ -13432,10 +13450,10 @@
         <v>6</v>
       </c>
       <c r="C302" s="7" t="s">
-        <v>1016</v>
+        <v>990</v>
       </c>
       <c r="D302" s="7" t="s">
-        <v>1079</v>
+        <v>1053</v>
       </c>
       <c r="E302" s="8">
         <v>3.59</v>
@@ -13447,7 +13465,7 @@
         <v>4.2</v>
       </c>
       <c r="H302" s="9" t="s">
-        <v>1026</v>
+        <v>1000</v>
       </c>
       <c r="I302" s="6"/>
     </row>
@@ -13459,10 +13477,10 @@
         <v>1</v>
       </c>
       <c r="C303" s="7" t="s">
-        <v>1033</v>
+        <v>1007</v>
       </c>
       <c r="D303" s="7" t="s">
-        <v>1039</v>
+        <v>1013</v>
       </c>
       <c r="E303" s="8">
         <v>3.81</v>
@@ -13474,7 +13492,7 @@
         <v>3.8</v>
       </c>
       <c r="H303" s="9" t="s">
-        <v>1051</v>
+        <v>1025</v>
       </c>
       <c r="I303" s="6"/>
     </row>
@@ -13486,10 +13504,10 @@
         <v>2</v>
       </c>
       <c r="C304" s="7" t="s">
-        <v>1034</v>
+        <v>1008</v>
       </c>
       <c r="D304" s="7" t="s">
-        <v>1040</v>
+        <v>1014</v>
       </c>
       <c r="E304" s="8">
         <v>3.82</v>
@@ -13501,7 +13519,7 @@
         <v>3.7</v>
       </c>
       <c r="H304" s="9" t="s">
-        <v>1052</v>
+        <v>1026</v>
       </c>
       <c r="I304" s="6"/>
     </row>
@@ -13513,10 +13531,10 @@
         <v>3</v>
       </c>
       <c r="C305" s="7" t="s">
-        <v>1030</v>
+        <v>1004</v>
       </c>
       <c r="D305" s="7" t="s">
-        <v>1041</v>
+        <v>1015</v>
       </c>
       <c r="E305" s="8">
         <v>3.81</v>
@@ -13528,7 +13546,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H305" s="9" t="s">
-        <v>1053</v>
+        <v>1027</v>
       </c>
       <c r="I305" s="6"/>
     </row>
@@ -13540,10 +13558,10 @@
         <v>4</v>
       </c>
       <c r="C306" s="7" t="s">
-        <v>1035</v>
+        <v>1009</v>
       </c>
       <c r="D306" s="7" t="s">
-        <v>1042</v>
+        <v>1016</v>
       </c>
       <c r="E306" s="8">
         <v>3</v>
@@ -13555,7 +13573,7 @@
         <v>3.8</v>
       </c>
       <c r="H306" s="9" t="s">
-        <v>1054</v>
+        <v>1028</v>
       </c>
       <c r="I306" s="6"/>
     </row>
@@ -13567,10 +13585,10 @@
         <v>5</v>
       </c>
       <c r="C307" s="7" t="s">
-        <v>1060</v>
+        <v>1034</v>
       </c>
       <c r="D307" s="7" t="s">
-        <v>1043</v>
+        <v>1017</v>
       </c>
       <c r="E307" s="8">
         <v>3.82</v>
@@ -13582,7 +13600,7 @@
         <v>4</v>
       </c>
       <c r="H307" s="9" t="s">
-        <v>1055</v>
+        <v>1029</v>
       </c>
       <c r="I307" s="6"/>
     </row>
@@ -13594,10 +13612,10 @@
         <v>6</v>
       </c>
       <c r="C308" s="7" t="s">
-        <v>1036</v>
+        <v>1010</v>
       </c>
       <c r="D308" s="7" t="s">
-        <v>1044</v>
+        <v>1018</v>
       </c>
       <c r="E308" s="8">
         <v>3.86</v>
@@ -13609,7 +13627,7 @@
         <v>3.7</v>
       </c>
       <c r="H308" s="9" t="s">
-        <v>1056</v>
+        <v>1030</v>
       </c>
       <c r="I308" s="6"/>
     </row>
@@ -13621,10 +13639,10 @@
         <v>7</v>
       </c>
       <c r="C309" s="7" t="s">
-        <v>1037</v>
+        <v>1011</v>
       </c>
       <c r="D309" s="7" t="s">
-        <v>1045</v>
+        <v>1019</v>
       </c>
       <c r="E309" s="8">
         <v>3.65</v>
@@ -13636,7 +13654,7 @@
         <v>3.8</v>
       </c>
       <c r="H309" s="9" t="s">
-        <v>1057</v>
+        <v>1031</v>
       </c>
       <c r="I309" s="6"/>
     </row>
@@ -13648,10 +13666,10 @@
         <v>8</v>
       </c>
       <c r="C310" s="7" t="s">
-        <v>1038</v>
+        <v>1012</v>
       </c>
       <c r="D310" s="7" t="s">
-        <v>1046</v>
+        <v>1020</v>
       </c>
       <c r="E310" s="8">
         <v>3.28</v>
@@ -13663,7 +13681,7 @@
         <v>3.6</v>
       </c>
       <c r="H310" s="9" t="s">
-        <v>1058</v>
+        <v>1032</v>
       </c>
       <c r="I310" s="6"/>
     </row>
@@ -13678,7 +13696,7 @@
         <v>34</v>
       </c>
       <c r="D311" s="7" t="s">
-        <v>1047</v>
+        <v>1021</v>
       </c>
       <c r="E311" s="8">
         <v>3.74</v>
@@ -13690,9 +13708,20 @@
         <v>4.2</v>
       </c>
       <c r="H311" s="9" t="s">
-        <v>1059</v>
+        <v>1033</v>
       </c>
       <c r="I311" s="6"/>
+    </row>
+    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A312" s="6"/>
+      <c r="B312" s="6"/>
+      <c r="C312" s="7"/>
+      <c r="D312" s="7"/>
+      <c r="E312" s="8"/>
+      <c r="F312" s="8"/>
+      <c r="G312" s="12"/>
+      <c r="H312" s="9"/>
+      <c r="I312" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13707,7 +13736,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
-        <v>1061</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -13715,7 +13744,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>1062</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -13723,7 +13752,7 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>1063</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
@@ -13737,7 +13766,7 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
-        <v>1064</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
@@ -13745,7 +13774,7 @@
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
-        <v>1065</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
@@ -13753,12 +13782,12 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
-        <v>1066</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="18" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>1067</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
@@ -13766,7 +13795,7 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
-        <v>1068</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -13774,7 +13803,7 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="15" t="s">
-        <v>1063</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
@@ -13788,7 +13817,7 @@
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
-        <v>1069</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
@@ -13796,7 +13825,7 @@
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
-        <v>1070</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
@@ -13804,12 +13833,12 @@
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="s">
-        <v>1071</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1072</v>
+        <v>1046</v>
       </c>
     </row>
   </sheetData>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CB944DF-8033-4968-A670-FFF7FC771AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{960DAB0E-DAD9-4832-9A25-EEAB8FCE6E5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="1096">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1282" uniqueCount="1129">
   <si>
     <t>No</t>
   </si>
@@ -3514,6 +3514,105 @@
   </si>
   <si>
     <t>Hard Rock, Classic Rock [Dynamic Heavy Blues Rock, Epilogue]</t>
+  </si>
+  <si>
+    <t>2019 (reissue 2023, Black White Splatter, Limited 500 copies)</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Retro-Rock, Heavy Psych, 70s Proto-Metal]</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/25950673-The-Riven-The-Riven</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/W3zAuVUGPKDvtWnM9nu_aID_qp_vOf4NjGNqtZEs85U/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI1OTUw/NjczLTE3ODQ5MTEy/MzItODg1Mi5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το πρώτο ομότιτλο άλμπουμ της σουηδικής μπάντας. Έκδοση 180g σε Black White Splatter βινύλιο (Limited 500 copies) από την The Sign Records (CRC014). Ωμή, δυνατή παραγωγή με έντονο 70s hard-blues χαρακτήρα και ταξιδιάρικη occult ατμόσφαιρα.</t>
+  </si>
+  <si>
+    <t>The Sign Records – CRC014 (LP, Album, Limited Edition, Reissue, Black White Splatter)</t>
+  </si>
+  <si>
+    <t>The Serpent</t>
+  </si>
+  <si>
+    <t>Far Beyond</t>
+  </si>
+  <si>
+    <t>Edge Of Time</t>
+  </si>
+  <si>
+    <t>Shadow Man</t>
+  </si>
+  <si>
+    <t>Finnish Woods</t>
+  </si>
+  <si>
+    <t>Fortune Teller</t>
+  </si>
+  <si>
+    <t>I Remember</t>
+  </si>
+  <si>
+    <t>Leap Of Faith</t>
+  </si>
+  <si>
+    <t>Sweet Child</t>
+  </si>
+  <si>
+    <t>Δυναμικό ξεκίνημα με κοφτά proto-metal riffs, μυστικιστική αύρα και στίχους για τους πειρασμούς και την απώλεια του ελέγχου.</t>
+  </si>
+  <si>
+    <t>Κλασικός 70s hard rock ρυθμός με έντονο blues swing στο rhythm section και θέμα την υπέρβαση των προσωπικών ορίων.</t>
+  </si>
+  <si>
+    <t>Γρήγορο, αδυσώπητο heavy rock κομμάτι με επιθετικό drumming και στίχους για την αγωνία της φθοράς του χρόνου.</t>
+  </si>
+  <si>
+    <t>Σκοτεινό heavy blues με αργόσυρτο ρυθμό, που πραγματεύεται τις κρυφές πτυχές και τους εσωτερικούς δαίμονες της ανθρώπινης ψυχής.</t>
+  </si>
+  <si>
+    <t>Το ατμοσφαιρικό αποκορύφωμα του δίσκου (διάρκειας 5,5 λεπτών), με ψυχεδελικά περάσματα και μυσταγωγία εμπνευσμένη από τα παρθένα σκανδιναβικά δάση.</t>
+  </si>
+  <si>
+    <t>Το πρώτο επίσημο single του δίσκου, ένα εξαιρετικό vintage hard rock κομμάτι με κολλητικό ρεφρέν για την ψευδαίσθηση της πρόβλεψης του μέλλοντος.</t>
+  </si>
+  <si>
+    <t>Συναισθηματική, βαριά blues/soul μπαλάντα όπου η Totta Ekebergh ξεδιπλώνει όλο το εύρος της φωνής της πάνω σε ένα θέμα νοσταλγίας και απώλειας.</t>
+  </si>
+  <si>
+    <t>Ευθύβολο, ρυθμικό hard rock κομμάτι που εξυμνεί το ρίσκο και την τόλμη απέναντι στο άγνωστο.</t>
+  </si>
+  <si>
+    <t>Heavy psych επικός επίλογος με vintage blues κλιμάκωση, αφιερωμένος στην αθωότητα και την αναγέννηση.</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Heavy Psych, Occult-tinged Hard Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Classic 70s Rock, Groovy Hard Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Proto-Metal, Speed Rock, Fast Boogie]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Hard Rock [Heavy Blues, Dark Hard Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Psychedelic Rock [Nordic Psych, Heavy Prog, Atmospheric Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Vintage Hard Rock, Dynamic Blues Rock]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Soul [Heavy Soul Ballad, Blues Rock Ballad]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Classic Hard Rock, Twin-Riff Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Psychedelic Rock [70s Heavy Rock, Epic Heavy Psych, Epilogue]</t>
   </si>
 </sst>
 </file>
@@ -5157,17 +5256,37 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="6"/>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="11"/>
-      <c r="J37" s="11"/>
+    <row r="37" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A37" s="6">
+        <v>25950673</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>1096</v>
+      </c>
+      <c r="E37" s="10">
+        <v>3.13</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>1097</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>1100</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>1101</v>
+      </c>
+      <c r="I37" s="11" t="s">
+        <v>1098</v>
+      </c>
+      <c r="J37" s="11" t="s">
+        <v>1099</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -5239,6 +5358,8 @@
     <hyperlink ref="J35" r:id="rId66" xr:uid="{9D002A99-727C-4388-B0E6-A0286BC1AB53}"/>
     <hyperlink ref="J36" r:id="rId67" xr:uid="{2575D056-1912-4177-AEBE-B4E01DCEF8FA}"/>
     <hyperlink ref="I36" r:id="rId68" xr:uid="{209C362D-EC30-4A00-A0B8-501F369CD679}"/>
+    <hyperlink ref="I37" r:id="rId69" xr:uid="{E5F32912-DA70-4F56-BFA1-AD945B01A5B7}"/>
+    <hyperlink ref="J37" r:id="rId70" xr:uid="{7EE8F5E1-FCE9-4B2E-8ABD-58D13EC6925F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5246,7 +5367,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I312"/>
+  <dimension ref="A1:I320"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="3" bestFit="1" customWidth="1"/>
@@ -13712,16 +13833,248 @@
       </c>
       <c r="I311" s="6"/>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A312" s="6"/>
-      <c r="B312" s="6"/>
-      <c r="C312" s="7"/>
-      <c r="D312" s="7"/>
-      <c r="E312" s="8"/>
-      <c r="F312" s="8"/>
-      <c r="G312" s="12"/>
-      <c r="H312" s="9"/>
+    <row r="312" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A312" s="6">
+        <v>25950673</v>
+      </c>
+      <c r="B312" s="6">
+        <v>1</v>
+      </c>
+      <c r="C312" s="7" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D312" s="7" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E312" s="8">
+        <v>3.35</v>
+      </c>
+      <c r="F312" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="G312" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="H312" s="9" t="s">
+        <v>1111</v>
+      </c>
       <c r="I312" s="6"/>
+    </row>
+    <row r="313" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A313" s="6">
+        <v>25950673</v>
+      </c>
+      <c r="B313" s="6">
+        <v>2</v>
+      </c>
+      <c r="C313" s="7" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D313" s="7" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E313" s="8">
+        <v>4.38</v>
+      </c>
+      <c r="F313" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="G313" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="H313" s="9" t="s">
+        <v>1112</v>
+      </c>
+      <c r="I313" s="6"/>
+    </row>
+    <row r="314" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A314" s="6">
+        <v>25950673</v>
+      </c>
+      <c r="B314" s="6">
+        <v>3</v>
+      </c>
+      <c r="C314" s="7" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D314" s="7" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E314" s="8">
+        <v>3.47</v>
+      </c>
+      <c r="F314" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="G314" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="H314" s="9" t="s">
+        <v>1113</v>
+      </c>
+      <c r="I314" s="6"/>
+    </row>
+    <row r="315" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A315" s="6">
+        <v>25950673</v>
+      </c>
+      <c r="B315" s="6">
+        <v>4</v>
+      </c>
+      <c r="C315" s="7" t="s">
+        <v>1105</v>
+      </c>
+      <c r="D315" s="7" t="s">
+        <v>1123</v>
+      </c>
+      <c r="E315" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="F315" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="G315" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="H315" s="9" t="s">
+        <v>1114</v>
+      </c>
+      <c r="I315" s="6"/>
+    </row>
+    <row r="316" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A316" s="6">
+        <v>25950673</v>
+      </c>
+      <c r="B316" s="6">
+        <v>5</v>
+      </c>
+      <c r="C316" s="7" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D316" s="7" t="s">
+        <v>1124</v>
+      </c>
+      <c r="E316" s="8">
+        <v>3.81</v>
+      </c>
+      <c r="F316" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="G316" s="12">
+        <v>4</v>
+      </c>
+      <c r="H316" s="9" t="s">
+        <v>1115</v>
+      </c>
+      <c r="I316" s="6"/>
+    </row>
+    <row r="317" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A317" s="6">
+        <v>25950673</v>
+      </c>
+      <c r="B317" s="6">
+        <v>6</v>
+      </c>
+      <c r="C317" s="7" t="s">
+        <v>1107</v>
+      </c>
+      <c r="D317" s="7" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E317" s="8">
+        <v>3.33</v>
+      </c>
+      <c r="F317" s="8">
+        <v>4</v>
+      </c>
+      <c r="G317" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="H317" s="9" t="s">
+        <v>1116</v>
+      </c>
+      <c r="I317" s="6"/>
+    </row>
+    <row r="318" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A318" s="6">
+        <v>25950673</v>
+      </c>
+      <c r="B318" s="6">
+        <v>7</v>
+      </c>
+      <c r="C318" s="7" t="s">
+        <v>1108</v>
+      </c>
+      <c r="D318" s="7" t="s">
+        <v>1126</v>
+      </c>
+      <c r="E318" s="8">
+        <v>2.73</v>
+      </c>
+      <c r="F318" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="G318" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="H318" s="9" t="s">
+        <v>1117</v>
+      </c>
+      <c r="I318" s="6"/>
+    </row>
+    <row r="319" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A319" s="6">
+        <v>25950673</v>
+      </c>
+      <c r="B319" s="6">
+        <v>8</v>
+      </c>
+      <c r="C319" s="7" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D319" s="7" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E319" s="8">
+        <v>3.15</v>
+      </c>
+      <c r="F319" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="G319" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="H319" s="9" t="s">
+        <v>1118</v>
+      </c>
+      <c r="I319" s="6"/>
+    </row>
+    <row r="320" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A320" s="6">
+        <v>25950673</v>
+      </c>
+      <c r="B320" s="6">
+        <v>9</v>
+      </c>
+      <c r="C320" s="7" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D320" s="7" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E320" s="8">
+        <v>3.08</v>
+      </c>
+      <c r="F320" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="G320" s="12">
+        <v>4</v>
+      </c>
+      <c r="H320" s="9" t="s">
+        <v>1119</v>
+      </c>
+      <c r="I320" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{960DAB0E-DAD9-4832-9A25-EEAB8FCE6E5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77EF45D8-8C29-423F-82B0-D323E124CCBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1282" uniqueCount="1129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1281" uniqueCount="1128">
   <si>
     <t>No</t>
   </si>
@@ -3516,9 +3516,6 @@
     <t>Hard Rock, Classic Rock [Dynamic Heavy Blues Rock, Epilogue]</t>
   </si>
   <si>
-    <t>2019 (reissue 2023, Black White Splatter, Limited 500 copies)</t>
-  </si>
-  <si>
     <t>Hard Rock, Blues Rock [Retro-Rock, Heavy Psych, 70s Proto-Metal]</t>
   </si>
   <si>
@@ -3528,9 +3525,6 @@
     <t>https://i.discogs.com/W3zAuVUGPKDvtWnM9nu_aID_qp_vOf4NjGNqtZEs85U/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI1OTUw/NjczLTE3ODQ5MTEy/MzItODg1Mi5qcGVn.jpeg</t>
   </si>
   <si>
-    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το πρώτο ομότιτλο άλμπουμ της σουηδικής μπάντας. Έκδοση 180g σε Black White Splatter βινύλιο (Limited 500 copies) από την The Sign Records (CRC014). Ωμή, δυνατή παραγωγή με έντονο 70s hard-blues χαρακτήρα και ταξιδιάρικη occult ατμόσφαιρα.</t>
-  </si>
-  <si>
     <t>The Sign Records – CRC014 (LP, Album, Limited Edition, Reissue, Black White Splatter)</t>
   </si>
   <si>
@@ -3613,6 +3607,9 @@
   </si>
   <si>
     <t>Hard Rock, Psychedelic Rock [70s Heavy Rock, Epic Heavy Psych, Epilogue]</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το πρώτο ομότιτλο άλμπουμ της σουηδικής μπάντας. Reissue 2023. Έκδοση 180g σε Black White Splatter βινύλιο (Limited 500 copies) από την The Sign Records (CRC014). Ωμή, δυνατή παραγωγή με έντονο 70s hard-blues χαρακτήρα και ταξιδιάρικη occult ατμόσφαιρα.</t>
   </si>
 </sst>
 </file>
@@ -5256,7 +5253,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" ht="42" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>25950673</v>
       </c>
@@ -5266,26 +5263,26 @@
       <c r="C37" s="7" t="s">
         <v>1003</v>
       </c>
-      <c r="D37" s="6" t="s">
-        <v>1096</v>
+      <c r="D37" s="6">
+        <v>2019</v>
       </c>
       <c r="E37" s="10">
         <v>3.13</v>
       </c>
       <c r="F37" s="9" t="s">
+        <v>1096</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>1127</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>1099</v>
+      </c>
+      <c r="I37" s="11" t="s">
         <v>1097</v>
       </c>
-      <c r="G37" s="7" t="s">
-        <v>1100</v>
-      </c>
-      <c r="H37" s="6" t="s">
-        <v>1101</v>
-      </c>
-      <c r="I37" s="11" t="s">
+      <c r="J37" s="11" t="s">
         <v>1098</v>
-      </c>
-      <c r="J37" s="11" t="s">
-        <v>1099</v>
       </c>
     </row>
   </sheetData>
@@ -13841,10 +13838,10 @@
         <v>1</v>
       </c>
       <c r="C312" s="7" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="D312" s="7" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="E312" s="8">
         <v>3.35</v>
@@ -13856,7 +13853,7 @@
         <v>3.8</v>
       </c>
       <c r="H312" s="9" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="I312" s="6"/>
     </row>
@@ -13868,10 +13865,10 @@
         <v>2</v>
       </c>
       <c r="C313" s="7" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="D313" s="7" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="E313" s="8">
         <v>4.38</v>
@@ -13883,7 +13880,7 @@
         <v>3.7</v>
       </c>
       <c r="H313" s="9" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="I313" s="6"/>
     </row>
@@ -13895,10 +13892,10 @@
         <v>3</v>
       </c>
       <c r="C314" s="7" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="D314" s="7" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="E314" s="8">
         <v>3.47</v>
@@ -13910,7 +13907,7 @@
         <v>3.8</v>
       </c>
       <c r="H314" s="9" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="I314" s="6"/>
     </row>
@@ -13922,10 +13919,10 @@
         <v>4</v>
       </c>
       <c r="C315" s="7" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="D315" s="7" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="E315" s="8">
         <v>3.5</v>
@@ -13937,7 +13934,7 @@
         <v>3.6</v>
       </c>
       <c r="H315" s="9" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="I315" s="6"/>
     </row>
@@ -13949,10 +13946,10 @@
         <v>5</v>
       </c>
       <c r="C316" s="7" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="D316" s="7" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="E316" s="8">
         <v>3.81</v>
@@ -13964,7 +13961,7 @@
         <v>4</v>
       </c>
       <c r="H316" s="9" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="I316" s="6"/>
     </row>
@@ -13976,10 +13973,10 @@
         <v>6</v>
       </c>
       <c r="C317" s="7" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="D317" s="7" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="E317" s="8">
         <v>3.33</v>
@@ -13991,7 +13988,7 @@
         <v>3.8</v>
       </c>
       <c r="H317" s="9" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="I317" s="6"/>
     </row>
@@ -14003,10 +14000,10 @@
         <v>7</v>
       </c>
       <c r="C318" s="7" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="D318" s="7" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="E318" s="8">
         <v>2.73</v>
@@ -14018,7 +14015,7 @@
         <v>3.7</v>
       </c>
       <c r="H318" s="9" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="I318" s="6"/>
     </row>
@@ -14030,10 +14027,10 @@
         <v>8</v>
       </c>
       <c r="C319" s="7" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="D319" s="7" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="E319" s="8">
         <v>3.15</v>
@@ -14045,7 +14042,7 @@
         <v>3.8</v>
       </c>
       <c r="H319" s="9" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="I319" s="6"/>
     </row>
@@ -14057,10 +14054,10 @@
         <v>9</v>
       </c>
       <c r="C320" s="7" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="D320" s="7" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="E320" s="8">
         <v>3.08</v>
@@ -14072,7 +14069,7 @@
         <v>4</v>
       </c>
       <c r="H320" s="9" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="I320" s="6"/>
     </row>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77EF45D8-8C29-423F-82B0-D323E124CCBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CDEB314-A8AE-4C9B-8915-129C145A6DF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1281" uniqueCount="1128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1320" uniqueCount="1164">
   <si>
     <t>No</t>
   </si>
@@ -3610,6 +3610,114 @@
   </si>
   <si>
     <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το πρώτο ομότιτλο άλμπουμ της σουηδικής μπάντας. Reissue 2023. Έκδοση 180g σε Black White Splatter βινύλιο (Limited 500 copies) από την The Sign Records (CRC014). Ωμή, δυνατή παραγωγή με έντονο 70s hard-blues χαρακτήρα και ταξιδιάρικη occult ατμόσφαιρα.</t>
+  </si>
+  <si>
+    <t>Gerry Rafferty</t>
+  </si>
+  <si>
+    <t>The Ark</t>
+  </si>
+  <si>
+    <t>Baker Street</t>
+  </si>
+  <si>
+    <t>Right Down The Line</t>
+  </si>
+  <si>
+    <t>City To City</t>
+  </si>
+  <si>
+    <t>Stealin' Time</t>
+  </si>
+  <si>
+    <t>Mattie's Rag</t>
+  </si>
+  <si>
+    <t>Whatever's Written In Your Heart</t>
+  </si>
+  <si>
+    <t>Home And Dry</t>
+  </si>
+  <si>
+    <t>Island</t>
+  </si>
+  <si>
+    <t>Waiting For The Day</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/28117261-Gerry-Rafferty-City-To-City</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/7ayJ1GvPlsLfGDD7Fl17-_Vhd1nB_PFjCnEg0nQEe4g/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI4MTE3/MjYxLTE3MDY3NDA4/MjMtNTMwNC5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Η κορυφαία solo δουλειά του Σκωτσέζου τραγουδοποιού μετά τη διάλυση των Stealers Wheel. Ηχογραφήθηκε κυρίως στα Chipping Norton Studios με παραγωγούς τους Hugh Murphy και Gerry Rafferty. Η συγκεκριμένη έκδοση είναι **2LP Special Edition, Half-Speed Mastered στο Abbey Road Studios από τον Miles Showell**, κομμένη στις 45/33rpm ανάλογα με το Format, με χαραγμένη (etched) την 4η πλευρά.</t>
+  </si>
+  <si>
+    <t>Soft Rock, Folk Rock [Cinematic Soft Rock, Singer-Songwriter]</t>
+  </si>
+  <si>
+    <t>Soft Rock, Pop Rock [Saxophone-driven Rock, Classic Rock]</t>
+  </si>
+  <si>
+    <t>Pop Rock, Blue-Eyed Soul [Soulful Pop, Soft Rock]</t>
+  </si>
+  <si>
+    <t>Soft Rock, Pop Rock [Narrative Pop Rock, Singer-Songwriter]</t>
+  </si>
+  <si>
+    <t>Folk Rock, Soft Rock [Acoustic Folk Rock, Celtic Folk]</t>
+  </si>
+  <si>
+    <t>Folk Rock, Pop Rock [Folk Pop, Instrumental-leaning Acoustic Rock]</t>
+  </si>
+  <si>
+    <t>Soft Rock, Blue-Eyed Soul [Gospel-inflected Soft Rock, Soul Ballad]</t>
+  </si>
+  <si>
+    <t>Soft Rock, Pop Rock [Adult Contemporary, Melodic Pop Rock]</t>
+  </si>
+  <si>
+    <t>Folk Rock, Soft Rock [Acoustic Folk, Maritime Folk Rock]</t>
+  </si>
+  <si>
+    <t>Soft Rock, Singer-Songwriter [Orchestral Soft Rock, Reflective Pop Ballad]</t>
+  </si>
+  <si>
+    <t>Το κομμάτι σύμβολο του Rafferty, με το ασύγκριτο σαξοφωνικό θέμα του Raphael Ravenscroft να εκφράζει σχεδόν μόνο του τη νυχτερινή μοναξιά του Λονδίνου. Πίσω από το αναγνωρίσιμο hook βρίσκεται ένα τραγούδι για αναμονή, αμφιβολία, αυτοπαγίδευση και την ελπίδα μιας καθαρής επανεκκίνησης.</t>
+  </si>
+  <si>
+    <t>Ατμοσφαιρικό και διακριτικά προοδευτικό άνοιγμα, χτισμένο σαν κάλεσμα φυγής από την αποξένωση της πόλης προς μια πιο εσωτερική, ασφαλή "κιβωτό". Το σκοτσέζικο folk υπόστρωμα, η μελαγχολική αρμονία και η σταδιακή ανάπτυξη της ενορχήστρωσης λειτουργούν ως προοίμιο για τον κεντρικό άξονα του δίσκου: την αντιπαράθεση αστικής πίεσης και ανάγκης για καταφύγιο.</t>
+  </si>
+  <si>
+    <t>Ζεστό, ρυθμικό soft-rock τραγούδι με blue-eyed soul αίσθηση και γεμάτες backing vocals. Είναι μια άμεση, ώριμη ερωτική δήλωση αφοσίωσης προς τη σύζυγο του Rafferty, Carla, και ξεχωρίζει επειδή μετατρέπει τη συζυγική σταθερότητα σε μεγάλη, αβίαστη pop μελωδία.</t>
+  </si>
+  <si>
+    <t>Πιο νευρικό και κινητικό κομμάτι, με ρυθμό που θυμίζει διαδρομή ή τρένο σε συνεχή κίνηση. Ο Rafferty αποτυπώνει την κούραση των μετακινήσεων, της περιοδείας και της ζωής που εξελίσσεται ανάμεσα σε πόλεις, ενώ το τραγούδι κρατά μια ζωηρή, σχεδόν αισιόδοξη μουσική ορμή αντί να βυθίζεται στη μελαγχολία.</t>
+  </si>
+  <si>
+    <t>Μια πιο εσωστρεφής folk-rock σύνθεση, με ακουστικά στοιχεία και αίσθηση Σκωτίας στον τρόπο που κυλά η μελωδία. Εξετάζει τον χρόνο ως κάτι που διαρρέει διαρκώς από τα χέρια μας: τις χαμένες ευκαιρίες, τις απαιτήσεις της ζωής και την αδυναμία να κρατήσεις πραγματικά όσα έχουν σημασία.</t>
+  </si>
+  <si>
+    <t>Φωτεινό, χαριτωμένο και σχεδόν παιδικό folk-pop κομμάτι, γραμμένο για την κόρη του Rafferty, Martha (“Mattie”). Το δυνατό fade-in, το dobro του Hughie Cole και το fiddle/strings κλείσιμο δίνουν έναν παιχνιδιάρικο, οικογενειακό χαρακτήρα που σπάει δημιουργικά τη σοβαρότητα του υπόλοιπου άλμπουμ.</t>
+  </si>
+  <si>
+    <t>Από τις πιο πλούσια ενορχηστρωμένες στιγμές του δίσκου: gospel-χρωματισμένο soft rock με πιάνo, έγχορδα, διακριτικά πνευστά και έντονη συναισθηματική κλιμάκωση. Στον πυρήνα του βρίσκεται μια ώριμη αποδοχή: η αγάπη δεν ελέγχεται ούτε επιβάλλεται· ό,τι είναι αληθινό αποκαλύπτεται τελικά "γραμμένο στην καρδιά".</t>
+  </si>
+  <si>
+    <t>Γήινο και μελωδικό mid-tempo pop-rock, που επαναφέρει το μοτίβο της επιστροφής στο σπίτι. Η αίσθηση δεν είναι θριαμβευτική αλλά ανακουφισμένη: μετά την ταραχή, τη διαδρομή και τις παγίδες της πόλης, η εγγύτητα και η οικειότητα εμφανίζονται ως το ουσιαστικό αντίβαρο.</t>
+  </si>
+  <si>
+    <t>Ακουστικό, στοχαστικό τραγούδι με folk χροιά, όπου η «νησίδα» λειτουργεί ως εικόνα απομόνωσης αλλά και ως πιθανός χώρος προστασίας. Ο Rafferty διατηρεί σκόπιμα μια αμφισημία: η απομάκρυνση από τον κόσμο μπορεί να προσφέρει ηρεμία, όμως μπορεί επίσης να εξελιχθεί σε συναισθηματική αποκοπή.</t>
+  </si>
+  <si>
+    <t>Μεγαλοπρεπές και μελαγχολικό κλείσιμο, βασισμένο σε αργή οικοδόμηση, πλούσια ενορχήστρωση και την χαρακτηριστική φωνητική συγκράτηση του Rafferty. Το τραγούδι επιστρέφει στην κεντρική ιδέα της αναμονής, της προσδοκίας για μια μέρα εσωτερικής διαύγειας, συμφιλίωσης ή επιστροφής και ολοκληρώνει τον δίσκο χωρίς εύκολη κάθαρση, αλλά με ήρεμη ελπίδα.</t>
+  </si>
+  <si>
+    <t>Soft Rock, Singer-Songwriter [Pop Rock, Folk Rock, Blue-Eyed Soul]</t>
+  </si>
+  <si>
+    <t>Parlophone – 0190296375682 / 2LP, Half-Speed Mastered, Etched</t>
   </si>
 </sst>
 </file>
@@ -4085,7 +4193,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -5283,6 +5391,38 @@
       </c>
       <c r="J37" s="11" t="s">
         <v>1098</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+      <c r="A38" s="6">
+        <v>28117261</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D38" s="6">
+        <v>1978</v>
+      </c>
+      <c r="E38" s="10">
+        <v>3.48</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>1162</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>1141</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>1163</v>
+      </c>
+      <c r="I38" s="11" t="s">
+        <v>1139</v>
+      </c>
+      <c r="J38" s="11" t="s">
+        <v>1140</v>
       </c>
     </row>
   </sheetData>
@@ -5357,6 +5497,8 @@
     <hyperlink ref="I36" r:id="rId68" xr:uid="{209C362D-EC30-4A00-A0B8-501F369CD679}"/>
     <hyperlink ref="I37" r:id="rId69" xr:uid="{E5F32912-DA70-4F56-BFA1-AD945B01A5B7}"/>
     <hyperlink ref="J37" r:id="rId70" xr:uid="{7EE8F5E1-FCE9-4B2E-8ABD-58D13EC6925F}"/>
+    <hyperlink ref="I38" r:id="rId71" xr:uid="{E39EA436-D938-4A1F-B12C-BC75152F540A}"/>
+    <hyperlink ref="J38" r:id="rId72" xr:uid="{434446FF-52A2-4990-B9E8-4AC6733C6C33}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5364,7 +5506,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I320"/>
+  <dimension ref="A1:I361"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="3" bestFit="1" customWidth="1"/>
@@ -14073,6 +14215,621 @@
       </c>
       <c r="I320" s="6"/>
     </row>
+    <row r="321" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A321" s="6">
+        <v>28117261</v>
+      </c>
+      <c r="B321" s="6">
+        <v>1</v>
+      </c>
+      <c r="C321" s="7" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D321" s="7" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E321" s="8">
+        <v>3.61</v>
+      </c>
+      <c r="F321" s="8">
+        <v>4</v>
+      </c>
+      <c r="G321" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H321" s="9" t="s">
+        <v>1153</v>
+      </c>
+      <c r="I321" s="6"/>
+    </row>
+    <row r="322" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A322" s="6">
+        <v>28117261</v>
+      </c>
+      <c r="B322" s="6">
+        <v>2</v>
+      </c>
+      <c r="C322" s="7" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D322" s="7" t="s">
+        <v>1143</v>
+      </c>
+      <c r="E322" s="8">
+        <v>4.24</v>
+      </c>
+      <c r="F322" s="8">
+        <v>4.8</v>
+      </c>
+      <c r="G322" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H322" s="9" t="s">
+        <v>1152</v>
+      </c>
+      <c r="I322" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="323" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A323" s="6">
+        <v>28117261</v>
+      </c>
+      <c r="B323" s="6">
+        <v>3</v>
+      </c>
+      <c r="C323" s="7" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D323" s="7" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E323" s="8">
+        <v>4</v>
+      </c>
+      <c r="F323" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="G323" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H323" s="9" t="s">
+        <v>1154</v>
+      </c>
+      <c r="I323" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="324" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A324" s="6">
+        <v>28117261</v>
+      </c>
+      <c r="B324" s="6">
+        <v>4</v>
+      </c>
+      <c r="C324" s="7" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D324" s="7" t="s">
+        <v>1145</v>
+      </c>
+      <c r="E324" s="8">
+        <v>3.35</v>
+      </c>
+      <c r="F324" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="G324" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="H324" s="9" t="s">
+        <v>1155</v>
+      </c>
+      <c r="I324" s="6"/>
+    </row>
+    <row r="325" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A325" s="6">
+        <v>28117261</v>
+      </c>
+      <c r="B325" s="6">
+        <v>5</v>
+      </c>
+      <c r="C325" s="7" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D325" s="7" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E325" s="8">
+        <v>3.14</v>
+      </c>
+      <c r="F325" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="G325" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="H325" s="9" t="s">
+        <v>1156</v>
+      </c>
+      <c r="I325" s="6"/>
+    </row>
+    <row r="326" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A326" s="6">
+        <v>28117261</v>
+      </c>
+      <c r="B326" s="6">
+        <v>6</v>
+      </c>
+      <c r="C326" s="7" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D326" s="7" t="s">
+        <v>1147</v>
+      </c>
+      <c r="E326" s="8">
+        <v>3.33</v>
+      </c>
+      <c r="F326" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="G326" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="H326" s="9" t="s">
+        <v>1157</v>
+      </c>
+      <c r="I326" s="6"/>
+    </row>
+    <row r="327" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A327" s="6">
+        <v>28117261</v>
+      </c>
+      <c r="B327" s="6">
+        <v>7</v>
+      </c>
+      <c r="C327" s="7" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D327" s="7" t="s">
+        <v>1148</v>
+      </c>
+      <c r="E327" s="8">
+        <v>3.33</v>
+      </c>
+      <c r="F327" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="G327" s="12">
+        <v>4</v>
+      </c>
+      <c r="H327" s="9" t="s">
+        <v>1158</v>
+      </c>
+      <c r="I327" s="6"/>
+    </row>
+    <row r="328" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A328" s="6">
+        <v>28117261</v>
+      </c>
+      <c r="B328" s="6">
+        <v>8</v>
+      </c>
+      <c r="C328" s="7" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D328" s="7" t="s">
+        <v>1149</v>
+      </c>
+      <c r="E328" s="8">
+        <v>3.37</v>
+      </c>
+      <c r="F328" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="G328" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="H328" s="9" t="s">
+        <v>1159</v>
+      </c>
+      <c r="I328" s="6"/>
+    </row>
+    <row r="329" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A329" s="6">
+        <v>28117261</v>
+      </c>
+      <c r="B329" s="6">
+        <v>9</v>
+      </c>
+      <c r="C329" s="7" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D329" s="7" t="s">
+        <v>1150</v>
+      </c>
+      <c r="E329" s="8">
+        <v>3.11</v>
+      </c>
+      <c r="F329" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="G329" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="H329" s="9" t="s">
+        <v>1160</v>
+      </c>
+      <c r="I329" s="6"/>
+    </row>
+    <row r="330" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A330" s="6">
+        <v>28117261</v>
+      </c>
+      <c r="B330" s="6">
+        <v>10</v>
+      </c>
+      <c r="C330" s="7" t="s">
+        <v>1138</v>
+      </c>
+      <c r="D330" s="7" t="s">
+        <v>1151</v>
+      </c>
+      <c r="E330" s="8">
+        <v>3.23</v>
+      </c>
+      <c r="F330" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="G330" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="H330" s="9" t="s">
+        <v>1161</v>
+      </c>
+      <c r="I330" s="6"/>
+    </row>
+    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A331" s="6"/>
+      <c r="B331" s="6"/>
+      <c r="C331" s="7"/>
+      <c r="D331" s="7"/>
+      <c r="E331" s="8"/>
+      <c r="F331" s="8"/>
+      <c r="G331" s="12"/>
+      <c r="H331" s="9"/>
+      <c r="I331" s="6"/>
+    </row>
+    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A332" s="6"/>
+      <c r="B332" s="6"/>
+      <c r="C332" s="7"/>
+      <c r="D332" s="7"/>
+      <c r="E332" s="8"/>
+      <c r="F332" s="8"/>
+      <c r="G332" s="12"/>
+      <c r="H332" s="9"/>
+      <c r="I332" s="6"/>
+    </row>
+    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A333" s="6"/>
+      <c r="B333" s="6"/>
+      <c r="C333" s="7"/>
+      <c r="D333" s="7"/>
+      <c r="E333" s="8"/>
+      <c r="F333" s="8"/>
+      <c r="G333" s="12"/>
+      <c r="H333" s="9"/>
+      <c r="I333" s="6"/>
+    </row>
+    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A334" s="6"/>
+      <c r="B334" s="6"/>
+      <c r="C334" s="7"/>
+      <c r="D334" s="7"/>
+      <c r="E334" s="8"/>
+      <c r="F334" s="8"/>
+      <c r="G334" s="12"/>
+      <c r="H334" s="9"/>
+      <c r="I334" s="6"/>
+    </row>
+    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A335" s="6"/>
+      <c r="B335" s="6"/>
+      <c r="C335" s="7"/>
+      <c r="D335" s="7"/>
+      <c r="E335" s="8"/>
+      <c r="F335" s="8"/>
+      <c r="G335" s="12"/>
+      <c r="H335" s="9"/>
+      <c r="I335" s="6"/>
+    </row>
+    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A336" s="6"/>
+      <c r="B336" s="6"/>
+      <c r="C336" s="7"/>
+      <c r="D336" s="7"/>
+      <c r="E336" s="8"/>
+      <c r="F336" s="8"/>
+      <c r="G336" s="12"/>
+      <c r="H336" s="9"/>
+      <c r="I336" s="6"/>
+    </row>
+    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A337" s="6"/>
+      <c r="B337" s="6"/>
+      <c r="C337" s="7"/>
+      <c r="D337" s="7"/>
+      <c r="E337" s="8"/>
+      <c r="F337" s="8"/>
+      <c r="G337" s="12"/>
+      <c r="H337" s="9"/>
+      <c r="I337" s="6"/>
+    </row>
+    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A338" s="6"/>
+      <c r="B338" s="6"/>
+      <c r="C338" s="7"/>
+      <c r="D338" s="7"/>
+      <c r="E338" s="8"/>
+      <c r="F338" s="8"/>
+      <c r="G338" s="12"/>
+      <c r="H338" s="9"/>
+      <c r="I338" s="6"/>
+    </row>
+    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A339" s="6"/>
+      <c r="B339" s="6"/>
+      <c r="C339" s="7"/>
+      <c r="D339" s="7"/>
+      <c r="E339" s="8"/>
+      <c r="F339" s="8"/>
+      <c r="G339" s="12"/>
+      <c r="H339" s="9"/>
+      <c r="I339" s="6"/>
+    </row>
+    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A340" s="6"/>
+      <c r="B340" s="6"/>
+      <c r="C340" s="7"/>
+      <c r="D340" s="7"/>
+      <c r="E340" s="8"/>
+      <c r="F340" s="8"/>
+      <c r="G340" s="12"/>
+      <c r="H340" s="9"/>
+      <c r="I340" s="6"/>
+    </row>
+    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A341" s="6"/>
+      <c r="B341" s="6"/>
+      <c r="C341" s="7"/>
+      <c r="D341" s="7"/>
+      <c r="E341" s="8"/>
+      <c r="F341" s="8"/>
+      <c r="G341" s="12"/>
+      <c r="H341" s="9"/>
+      <c r="I341" s="6"/>
+    </row>
+    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A342" s="6"/>
+      <c r="B342" s="6"/>
+      <c r="C342" s="7"/>
+      <c r="D342" s="7"/>
+      <c r="E342" s="8"/>
+      <c r="F342" s="8"/>
+      <c r="G342" s="12"/>
+      <c r="H342" s="9"/>
+      <c r="I342" s="6"/>
+    </row>
+    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A343" s="6"/>
+      <c r="B343" s="6"/>
+      <c r="C343" s="7"/>
+      <c r="D343" s="7"/>
+      <c r="E343" s="8"/>
+      <c r="F343" s="8"/>
+      <c r="G343" s="12"/>
+      <c r="H343" s="9"/>
+      <c r="I343" s="6"/>
+    </row>
+    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A344" s="6"/>
+      <c r="B344" s="6"/>
+      <c r="C344" s="7"/>
+      <c r="D344" s="7"/>
+      <c r="E344" s="8"/>
+      <c r="F344" s="8"/>
+      <c r="G344" s="12"/>
+      <c r="H344" s="9"/>
+      <c r="I344" s="6"/>
+    </row>
+    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A345" s="6"/>
+      <c r="B345" s="6"/>
+      <c r="C345" s="7"/>
+      <c r="D345" s="7"/>
+      <c r="E345" s="8"/>
+      <c r="F345" s="8"/>
+      <c r="G345" s="12"/>
+      <c r="H345" s="9"/>
+      <c r="I345" s="6"/>
+    </row>
+    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A346" s="6"/>
+      <c r="B346" s="6"/>
+      <c r="C346" s="7"/>
+      <c r="D346" s="7"/>
+      <c r="E346" s="8"/>
+      <c r="F346" s="8"/>
+      <c r="G346" s="12"/>
+      <c r="H346" s="9"/>
+      <c r="I346" s="6"/>
+    </row>
+    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A347" s="6"/>
+      <c r="B347" s="6"/>
+      <c r="C347" s="7"/>
+      <c r="D347" s="7"/>
+      <c r="E347" s="8"/>
+      <c r="F347" s="8"/>
+      <c r="G347" s="12"/>
+      <c r="H347" s="9"/>
+      <c r="I347" s="6"/>
+    </row>
+    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A348" s="6"/>
+      <c r="B348" s="6"/>
+      <c r="C348" s="7"/>
+      <c r="D348" s="7"/>
+      <c r="E348" s="8"/>
+      <c r="F348" s="8"/>
+      <c r="G348" s="12"/>
+      <c r="H348" s="9"/>
+      <c r="I348" s="6"/>
+    </row>
+    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A349" s="6"/>
+      <c r="B349" s="6"/>
+      <c r="C349" s="7"/>
+      <c r="D349" s="7"/>
+      <c r="E349" s="8"/>
+      <c r="F349" s="8"/>
+      <c r="G349" s="12"/>
+      <c r="H349" s="9"/>
+      <c r="I349" s="6"/>
+    </row>
+    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A350" s="6"/>
+      <c r="B350" s="6"/>
+      <c r="C350" s="7"/>
+      <c r="D350" s="7"/>
+      <c r="E350" s="8"/>
+      <c r="F350" s="8"/>
+      <c r="G350" s="12"/>
+      <c r="H350" s="9"/>
+      <c r="I350" s="6"/>
+    </row>
+    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A351" s="6"/>
+      <c r="B351" s="6"/>
+      <c r="C351" s="7"/>
+      <c r="D351" s="7"/>
+      <c r="E351" s="8"/>
+      <c r="F351" s="8"/>
+      <c r="G351" s="12"/>
+      <c r="H351" s="9"/>
+      <c r="I351" s="6"/>
+    </row>
+    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A352" s="6"/>
+      <c r="B352" s="6"/>
+      <c r="C352" s="7"/>
+      <c r="D352" s="7"/>
+      <c r="E352" s="8"/>
+      <c r="F352" s="8"/>
+      <c r="G352" s="12"/>
+      <c r="H352" s="9"/>
+      <c r="I352" s="6"/>
+    </row>
+    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A353" s="6"/>
+      <c r="B353" s="6"/>
+      <c r="C353" s="7"/>
+      <c r="D353" s="7"/>
+      <c r="E353" s="8"/>
+      <c r="F353" s="8"/>
+      <c r="G353" s="12"/>
+      <c r="H353" s="9"/>
+      <c r="I353" s="6"/>
+    </row>
+    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A354" s="6"/>
+      <c r="B354" s="6"/>
+      <c r="C354" s="7"/>
+      <c r="D354" s="7"/>
+      <c r="E354" s="8"/>
+      <c r="F354" s="8"/>
+      <c r="G354" s="12"/>
+      <c r="H354" s="9"/>
+      <c r="I354" s="6"/>
+    </row>
+    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A355" s="6"/>
+      <c r="B355" s="6"/>
+      <c r="C355" s="7"/>
+      <c r="D355" s="7"/>
+      <c r="E355" s="8"/>
+      <c r="F355" s="8"/>
+      <c r="G355" s="12"/>
+      <c r="H355" s="9"/>
+      <c r="I355" s="6"/>
+    </row>
+    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A356" s="6"/>
+      <c r="B356" s="6"/>
+      <c r="C356" s="7"/>
+      <c r="D356" s="7"/>
+      <c r="E356" s="8"/>
+      <c r="F356" s="8"/>
+      <c r="G356" s="12"/>
+      <c r="H356" s="9"/>
+      <c r="I356" s="6"/>
+    </row>
+    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A357" s="6"/>
+      <c r="B357" s="6"/>
+      <c r="C357" s="7"/>
+      <c r="D357" s="7"/>
+      <c r="E357" s="8"/>
+      <c r="F357" s="8"/>
+      <c r="G357" s="12"/>
+      <c r="H357" s="9"/>
+      <c r="I357" s="6"/>
+    </row>
+    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A358" s="6"/>
+      <c r="B358" s="6"/>
+      <c r="C358" s="7"/>
+      <c r="D358" s="7"/>
+      <c r="E358" s="8"/>
+      <c r="F358" s="8"/>
+      <c r="G358" s="12"/>
+      <c r="H358" s="9"/>
+      <c r="I358" s="6"/>
+    </row>
+    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A359" s="6"/>
+      <c r="B359" s="6"/>
+      <c r="C359" s="7"/>
+      <c r="D359" s="7"/>
+      <c r="E359" s="8"/>
+      <c r="F359" s="8"/>
+      <c r="G359" s="12"/>
+      <c r="H359" s="9"/>
+      <c r="I359" s="6"/>
+    </row>
+    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A360" s="6"/>
+      <c r="B360" s="6"/>
+      <c r="C360" s="7"/>
+      <c r="D360" s="7"/>
+      <c r="E360" s="8"/>
+      <c r="F360" s="8"/>
+      <c r="G360" s="12"/>
+      <c r="H360" s="9"/>
+      <c r="I360" s="6"/>
+    </row>
+    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A361" s="6"/>
+      <c r="B361" s="6"/>
+      <c r="C361" s="7"/>
+      <c r="D361" s="7"/>
+      <c r="E361" s="8"/>
+      <c r="F361" s="8"/>
+      <c r="G361" s="12"/>
+      <c r="H361" s="9"/>
+      <c r="I361" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CDEB314-A8AE-4C9B-8915-129C145A6DF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E794F6A1-BD1A-487A-9679-3B0EB20F53B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1320" uniqueCount="1164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1425" uniqueCount="1265">
   <si>
     <t>No</t>
   </si>
@@ -3718,6 +3718,309 @@
   </si>
   <si>
     <t>Parlophone – 0190296375682 / 2LP, Half-Speed Mastered, Etched</t>
+  </si>
+  <si>
+    <t>Death Alley Driver</t>
+  </si>
+  <si>
+    <t>Stone Cold</t>
+  </si>
+  <si>
+    <t>Bring On The Night (Dream Chaser)</t>
+  </si>
+  <si>
+    <t>Tite Squeeze</t>
+  </si>
+  <si>
+    <t>Tearin' Out My Heart</t>
+  </si>
+  <si>
+    <t>Power</t>
+  </si>
+  <si>
+    <t>Miss Mistreated</t>
+  </si>
+  <si>
+    <t>Rock Fever</t>
+  </si>
+  <si>
+    <t>Eyes Of Fire</t>
+  </si>
+  <si>
+    <t>Straight Between The Eyes</t>
+  </si>
+  <si>
+    <t>Rainbow</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/KRJMWZApMLctQDRbn7JLbDgJMOm7wGuvdsHwQvuU7E4/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTE1NjIw/ODYtMTQyMzgzNjk4/Ny0yMTE2LmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/1562086-Rainbow-Straight-Between-The-Eyes</t>
+  </si>
+  <si>
+    <t>Hard Rock, AOR [Melodic Hard Rock, Arena Rock, Pop Metal]</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Η έκτη δισκογραφική δουλειά των Rainbow με τον Joe Lynn Turner στα φωνητικά και την παραγωγή του Roger Glover. Ηχογραφήθηκε στα Le Studio (Morin Heights, Canada) και έγινε το mastering στη Νέα Υόρκη (Sterling Sound). Η συγκεκριμένη γερμανική έκδοση (Polydor 2391 542) διακρίνεται για την καθαρή, γυαλισμένη 80s hard rock παραγωγή της.</t>
+  </si>
+  <si>
+    <t>Polydor – 2391 542 / LP, Album, Stereo (Germany Pressing)</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Speed Rock, Driving Hard Rock]</t>
+  </si>
+  <si>
+    <t>Αστραπιαίο εναρκτήριο hard rock κομμάτι, με racing ρυθμό και επιθετικό riff του Blackmore. Η αφήγηση χρησιμοποιεί την εικόνα της επικίνδυνης νυχτερινής οδήγησης ως μεταφορά για την έλξη προς το ρίσκο και την αυτοκαταστροφή.</t>
+  </si>
+  <si>
+    <t>AOR, Hard Rock [Power Ballad, Melodic Hard Rock]</t>
+  </si>
+  <si>
+    <t>Η μεγάλη power ballad των Rainbow. Με πιάνο keys, δραματική μελωδική κίνηση και εξαιρετικά ελεγχόμενη ερμηνεία του Turner, αποτυπώνει τη στιγμή κατά την οποία μια σχέση παγώνει συναισθηματικά και η αποχώρηση γίνεται αναπόφευκτη.</t>
+  </si>
+  <si>
+    <t>AOR, Hard Rock [Arena Rock, Melodic Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Boogie Rock, Barroom Rock]</t>
+  </si>
+  <si>
+    <t>Μελωδικό AOR με ανοιχτό, νυχτερινό χαρακτήρα και δυνατό chorus. Η θεματική περιστρέφεται γύρω από την αναζήτηση διαφυγής, έντασης και μιας ιδανικής εμπειρίας που μοιάζει διαρκώς να βρίσκεται λίγο πιο πέρα.</t>
+  </si>
+  <si>
+    <t>Σύντομο, ευθύ boogie rock κομμάτι με σαφές barroom attitude. Εδώ οι Rainbow αφήνουν προσωρινά τη δραματικότητα και λειτουργούν πιο απλά, με χιούμορ, riff οικονομία και rock ’n’ roll αμεσότητα.</t>
+  </si>
+  <si>
+    <t>AOR, Hard Rock [Melodic Hard Rock, Pop Metal]</t>
+  </si>
+  <si>
+    <t>Anthemic hard rock με κεντρικό θέμα την επιθυμία για έλεγχο, αυτοπεποίθηση και προσωπική κυριαρχία. Είναι από τα κομμάτια όπου η σκληρή κιθάρα του Blackmore και η AOR προσβασιμότητα του Turner συνυπάρχουν πιο ισορροπημένα.</t>
+  </si>
+  <si>
+    <t>Κοφτερό melodic hard rock, με τον τίτλο να παίζει ειρωνικά με το Mistreated των Deep Purple χωρίς να αποτελεί συνέχεια ή διασκευή του. Το τραγούδι εστιάζει στη συναισθηματική απόσταση, στην παρεξήγηση και στην αμφίδρομη φθορά μιας σχέσης. Η γραφή του David Rosenthal ενισχύει τον keyboard-driven χαρακτήρα του.</t>
+  </si>
+  <si>
+    <t>Γρήγορη, σχεδόν ανέμελη ωδή στη σωματική ενέργεια του rock ’n’ roll και της συναυλιακής εμπειρίας. Δεν είναι το πιο σύνθετο κομμάτι του άλμπουμ, αλλά λειτουργεί ως σφιχτός, party rock καθαρισμός πριν από το μεγάλο φινάλε.</t>
+  </si>
+  <si>
+    <t>Σκοτεινό, μακρύτερο και πιο δραματικό κλείσιμο, με βαριά riffs, επιβλητικά keyboards και πιο επικό φωνητικό ύφος. Η εικόνα των "ματιών της φωτιάς" δημιουργεί μια απειλητική, σχεδόν μοιραία ατμόσφαιρα για μια έλξη που καίει, σαγηνεύει και ταυτόχρονα προειδοποιεί.</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Epic Hard Rock, Dark Melodic Metal]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Rock &amp; Roll [Boogie Rock, Party Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, AOR [Melodic Hard Rock, Keyboard-driven Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, AOR [Arena Rock, Anthemic Hard Rock]</t>
+  </si>
+  <si>
+    <t>Μελωδικό hard rock με έντονο pop metal περίγραμμα. Ο αφηγητής μιλά για μια σχέση που φθείρει και διαλύει συναισθηματικά, ενώ η παραγωγή δίνει έμφαση σε hooks, keyboards και ένα ραδιοφωνικά σχεδιασμένο ρεφρέν. Από τις πιο αδικημένες στιγμές του δίσκου, με βαρύ blues υπόβαθρο, ανατολίτικες κλίμακες στην κιθάρα και τεράστιο συναισθηματικό δυναμισμό.</t>
+  </si>
+  <si>
+    <t>Coming Up To Consciousness</t>
+  </si>
+  <si>
+    <t>Dig Till You Die</t>
+  </si>
+  <si>
+    <t>Betrayal</t>
+  </si>
+  <si>
+    <t>The Gallows</t>
+  </si>
+  <si>
+    <t>Useless Animal</t>
+  </si>
+  <si>
+    <t>Worship</t>
+  </si>
+  <si>
+    <t>Bend The Earth</t>
+  </si>
+  <si>
+    <t>Lifeless Creature</t>
+  </si>
+  <si>
+    <t>As We Disappear</t>
+  </si>
+  <si>
+    <t>Pure Reason Revolution</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/1c2IMLDbQRN6GBQWq1WJZOoagVOpzLiilcdlPV5cgCw/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTMxNjgz/MjMwLTE3MjU3OTIx/NjEtODQ4NC5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/31683230-Pure-Reason-Revolution-Coming-Up-To-Consciousness</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Alternative Rock [Progressive Pop, Art Rock, Electronica]</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το έκτο στούντιο άλμπουμ των Pure Reason Revolution. Ηχογραφήθηκε με τη συμμετοχή των Guy Pratt, Bruce Soord και Jon Sykes. Mastering από τον Steve Kitch, κοπή lacquers από τον KR στα Optimal Media Studios (BO15550). Limited Gatefold Blue ReVinyl έκδοση.</t>
+  </si>
+  <si>
+    <t>Inside Out Music, Sony Music – IOM710, 19658871441 / LP, Album, Limited Edition, Gatefold, Blue ReVinyl</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Alternative Rock [Progressive Pop, Electronic Rock]</t>
+  </si>
+  <si>
+    <t>Η πρώτη πλήρης σύνθεση συνδυάζει κοφτές κιθάρες, ψηφιακές υφές και χαρακτηριστικές εναλλαγές φωνητικών Courtney Alper. Το θέμα του είναι η καταναγκαστική αναζήτηση απαντήσεων, η επίμονη "ανασκαφή" στον εαυτό μέχρι αυτή να γίνει εξαντλητική.</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Alternative Rock [Art Rock, Electronic Prog, Melancholic Rock]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Μελαγχολικό αλλά ρυθμικά δραστήριο art rock κομμάτι για τη ρήξη εμπιστοσύνης, είτε προς έναν άλλον άνθρωπο είτε προς τον ίδιο τον εαυτό. Η αντίθεση των φωνών δημιουργεί μια δραματική αμφισημία ανάμεσα στην κατηγορία και την αυτοκριτική.</t>
+  </si>
+  <si>
+    <t>Από τα βαρύτερα και πιο απειλητικά σημεία του δίσκου, με αυστηρό riffing, ηλεκτρονικά layers και αίσθηση κλιμακούμενης πίεσης. Η αγχόνη λειτουργεί ως εικόνα ψυχολογικού εγκλωβισμού και τιμωρίας πριν από την πιθανότητα λύτρωσης.</t>
+  </si>
+  <si>
+    <t>Περισσότερο εσωστρεφές και synth-βαρύ, χτίζεται γύρω από την αμφιβολία για την αξία και τον έλεγχο του ανθρώπου πάνω στον εαυτό του. Η pop σαφήνεια της μελωδίας αντισταθμίζεται από ένα υποβόσκον αίσθημα αποσύνδεσης.</t>
+  </si>
+  <si>
+    <t>Πολυεπίπεδο progressive pop κομμάτι με έντονο συναίσθημα και ηλεκτρονική κίνηση. Εξετάζει την τάση να εξιδανικεύουμε πρόσωπα, σχέσεις ή ιδέες μέχρι η αφοσίωση να μετατρέπεται σε υποταγή.</t>
+  </si>
+  <si>
+    <t>Μία από τις δύο μεγάλες κορυφές του δίσκου. Η σύνθεση αναπτύσσεται πιο υπομονετικά, συνδυάζοντας cinematic κιθάρες, επαναλαμβανόμενα μοτίβα και φωνητική κλιμάκωση. Η εικόνα του τίτλου υποδηλώνει την απελπισμένη ανάγκη να αλλάξει κανείς κάτι θεμελιώδες, ακόμη και αν αυτό μοιάζει αδύνατο.</t>
+  </si>
+  <si>
+    <t>Σκοτεινό και δραματικό progressive rock, με πιο βαριά κιθαριστική υπόσταση και σχεδόν αποκαλυπτική ατμόσφαιρα. Ασχολείται με την ψυχική ακινησία, την αποξένωση και το αίσθημα ότι κάποιος παρακολουθεί τη ζωή του αντί να τη ζει.</t>
+  </si>
+  <si>
+    <t>Μελαγχολικό αλλά λυτρωτικό φινάλε. Οι PRR συγκεντρώνουν εδώ τη μελωδική τους πλευρά και μετατρέπουν την ιδέα της εξαφάνισης σε στοχασμό πάνω στην παροδικότητα, τη μνήμη και τη δυνατότητα συμφιλίωσης με όσα δεν ελέγχουμε.</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Alternative Rock [Melancholic Prog Pop, Art Rock]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Alternative Rock [Dark Progressive Rock, Electronic Rock]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Post-Rock [Cinematic Prog, Alternative Rock]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Alternative Rock [Progressive Pop, Electronic Art Rock]</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Progressive Rock [Art Rock, Synth Rock, Dreamy Prog]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Alternative Rock [Heavy Prog, Dark Art Rock]</t>
+  </si>
+  <si>
+    <t>Primordial</t>
+  </si>
+  <si>
+    <t>How It Ends</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/28426390-Primordial-How-It-Ends?redirected=true</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/qCz6uniUHjv95qfb6WbEAhCVe7rRimRhtQG0w7j1EPA/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI4NDI2/MzkwLTE2OTU5Mzk4/MDItOTM3Ni5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Ploughs To Rust, Swords To Dust</t>
+  </si>
+  <si>
+    <t>We Shall Not Serve</t>
+  </si>
+  <si>
+    <t>Traidisiunta</t>
+  </si>
+  <si>
+    <t>Pilgrimage To The World’s End</t>
+  </si>
+  <si>
+    <t>Nothing New Under The Sun</t>
+  </si>
+  <si>
+    <t>Call To Cernunnos</t>
+  </si>
+  <si>
+    <t>All Against All</t>
+  </si>
+  <si>
+    <t>Death Holy Death</t>
+  </si>
+  <si>
+    <t>Victory Has 1000 Fathers, Defeat Is An Orphan</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το δέκατο στούντιο άλμπουμ των Ιρλανδών Primordial. Κυκλοφόρησε στις 29 Σεπτεμβρίου 2023 από τη Metal Blade Records σε διπλό LP (180g black vinyl) με gatefold εξώφυλλο και insert στίχων. Τα runouts φέρουν την υπογραφή κοπής της SST (SST).</t>
+  </si>
+  <si>
+    <t>Metal Blade Records – 3984-16061-1 / 2 x Vinyl, LP, Album, 180g</t>
+  </si>
+  <si>
+    <t>Black Metal, Folk Metal [Celtic Metal, Epic Metal, Doom Metal]</t>
+  </si>
+  <si>
+    <t>Black Metal, Folk Metal [Epic Black Metal, Celtic Metal, Melancholic Metal]</t>
+  </si>
+  <si>
+    <t>Black Metal, Heavy Metal [Epic Metal, Celtic Metal, Martial Metal]</t>
+  </si>
+  <si>
+    <t>Black Metal, Heavy Metal [Pagan Metal, Defiant Black Metal]</t>
+  </si>
+  <si>
+    <t>Folk, Ambient [Irish Traditional Folk, Acoustic Interlude (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Black Metal, Folk Metal [Epic Black Metal, Doom-tinged Metal]</t>
+  </si>
+  <si>
+    <t>Black Metal, Heavy Metal [Dark Epic Metal, Celtic Metal]</t>
+  </si>
+  <si>
+    <t>Folk Metal, Black Metal [Celtic Metal, Ritual Metal, Heavy Metal]</t>
+  </si>
+  <si>
+    <t>Black Metal, Doom Metal [Epic Doom Metal, Atmospheric Black Metal]</t>
+  </si>
+  <si>
+    <t>Black Metal, Doom Metal [Funeral Epic Metal, Celtic Metal]</t>
+  </si>
+  <si>
+    <t>Black Metal, Heavy Metal [Epic Metal, Celtic Folk Metal, Closing Anthem]</t>
+  </si>
+  <si>
+    <t>Το ομώνυμο άνοιγμα θέτει αμέσως τον τόνο με μελαγχολικές folk μελωδίες, βαριά riffs και μια σταδιακή, τελετουργική κλιμάκωση. Η φράση του τίτλου λειτουργεί ως ερώτηση για την ιστορική φθορά και τη στιγμή που μια κοινωνία αναγκάζεται να κοιτάξει κατάματα τις συνέπειες των επιλογών της.</t>
+  </si>
+  <si>
+    <t>Από τα πιο άμεσα πολεμικά τραγούδια του δίσκου. Η αντιπαράθεση ανάμεσα στο αλέτρι και το σπαθί, εργασία ζωή απέναντι σε βία κατάκτηση, μετατρέπεται σε πικρό σχόλιο για το πώς η ιστορία φθείρει και τις δύο πλευρές. Η heavy-metal μελωδία και το martial drumming του δίνουν χαρακτήρα θρήνου ύμνου.</t>
+  </si>
+  <si>
+    <t>Μανιφέστο άρνησης υποταγής, που επιστρέφει στη ρητορική αξιοπρέπειας και αντίστασης η οποία διατρέχει ολόκληρη τη δισκογραφία των Primordial. Οι σκληρές κιθάρες και η επιτακτική ερμηνεία του Nemtheanga δίνουν στο κομμάτι τον χαρακτήρα συλλογικού όρκου.</t>
+  </si>
+  <si>
+    <t>Σύντομο οργανικό ακουστικό interlude με σαφή αναφορά στην ιρλανδική παράδοση. Λειτουργεί ως τελετουργική παύση και ως υπενθύμιση ότι η folk κληρονομιά των Primordial δεν είναι διακοσμητική, αλλά οργανικό μέρος της αφήγησής τους.</t>
+  </si>
+  <si>
+    <t>Μακρόσυρτη, καταθλιπτικά επική σύνθεση για ένα ταξίδι προς τα όρια, γεωγραφικά, ηθικά και πνευματικά. Η doom αίσθηση, τα αργά χτισίματα και οι μεγάλες μελωδικές γραμμές εντείνουν την εικόνα μιας πορείας όπου η λύτρωση παραμένει αβέβαιη.</t>
+  </si>
+  <si>
+    <t>Σκοτεινή διαπίστωση για την κυκλική φύση της ανθρώπινης βίας και της ιστορίας. Η σύνθεση ισορροπεί ανάμεσα σε black-metal ένταση και βαριά epic-rock ανάπτυξη, υπογραμμίζοντας ότι η πρόοδος συχνά μοιάζει επιφανειακή μπροστά στην επανάληψη των ίδιων καταστροφών.</t>
+  </si>
+  <si>
+    <t>Το πιο άμεσα τελετουργικό και παγανιστικό κομμάτι του άλμπουμ. Η επίκληση στον Cernunnos —κελτική θεότητα που συνδέεται με την άγρια φύση και τα ζώα— γίνεται τρόπος να αντιπαρατεθεί η φυσική αρχέγονη τάξη με την κοινωνική και ιστορική παρακμή.</t>
+  </si>
+  <si>
+    <t>Από τις κορυφαίες και πιο συντριπτικές στιγμές. Το αργό, doom-βαρύ βάδισμα και η πυκνή ατμόσφαιρα απεικονίζουν τον κόσμο ως πεδίο γενικευμένης σύγκρουσης, όπου κάθε μορφή αλληλεγγύης απειλείται από φόβο, εξουσία και ανταγωνισμό.</t>
+  </si>
+  <si>
+    <t>Μεγάλη, μελαγχολική και δραματική σύνθεση, με αξιοσημείωτο build-up που έχει ξεχωρίσει στις κριτικές. Δεν εξιδανικεύει τον θάνατο· τον αντιμετωπίζει ως βαριά, αναπόφευκτη παρουσία που αγιάζεται μόνο μέσα από μνήμη, απώλεια και αξιοπρέπεια.</t>
+  </si>
+  <si>
+    <t>Επίλογος με τον αφορισμό του τίτλου να συνοψίζει το ηθικό σύμπαν του δίσκου: η νίκη διεκδικείται από πολλούς, ενώ η ήττα εγκαταλείπεται στους λίγους. Η σύνθεση κλείνει σαν πικρός πολιτικός και ανθρώπινος απολογισμός, χωρίς θριαμβολογία αλλά με επιμονή στη μνήμη των ηττημένων.</t>
   </si>
 </sst>
 </file>
@@ -4193,7 +4496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -5423,6 +5726,102 @@
       </c>
       <c r="J38" s="11" t="s">
         <v>1140</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+      <c r="A39" s="6">
+        <v>1562086</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>1173</v>
+      </c>
+      <c r="D39" s="6">
+        <v>1982</v>
+      </c>
+      <c r="E39" s="10">
+        <v>3.16</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>1177</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>1178</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>1179</v>
+      </c>
+      <c r="I39" s="11" t="s">
+        <v>1176</v>
+      </c>
+      <c r="J39" s="11" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A40" s="6">
+        <v>31683230</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>1198</v>
+      </c>
+      <c r="D40" s="6">
+        <v>2024</v>
+      </c>
+      <c r="E40" s="10">
+        <v>3.33</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>1210</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>1211</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>1212</v>
+      </c>
+      <c r="I40" s="11" t="s">
+        <v>1209</v>
+      </c>
+      <c r="J40" s="11" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+      <c r="A41" s="6">
+        <v>28426390</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D41" s="6">
+        <v>2023</v>
+      </c>
+      <c r="E41" s="10">
+        <v>3.42</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>1244</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>1242</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>1243</v>
+      </c>
+      <c r="I41" s="11" t="s">
+        <v>1231</v>
+      </c>
+      <c r="J41" s="11" t="s">
+        <v>1232</v>
       </c>
     </row>
   </sheetData>
@@ -5499,6 +5898,12 @@
     <hyperlink ref="J37" r:id="rId70" xr:uid="{7EE8F5E1-FCE9-4B2E-8ABD-58D13EC6925F}"/>
     <hyperlink ref="I38" r:id="rId71" xr:uid="{E39EA436-D938-4A1F-B12C-BC75152F540A}"/>
     <hyperlink ref="J38" r:id="rId72" xr:uid="{434446FF-52A2-4990-B9E8-4AC6733C6C33}"/>
+    <hyperlink ref="J39" r:id="rId73" xr:uid="{5DC2641E-2387-4BA6-9A88-B4A6B827B909}"/>
+    <hyperlink ref="I39" r:id="rId74" xr:uid="{91790331-D35E-4067-B038-263AEF6060A9}"/>
+    <hyperlink ref="J40" r:id="rId75" xr:uid="{F738125C-E6C4-4EEB-8C06-4A5232B3EE11}"/>
+    <hyperlink ref="I40" r:id="rId76" xr:uid="{B1E3FDF7-1E6A-4CD0-9059-589E76913A9D}"/>
+    <hyperlink ref="I41" r:id="rId77" xr:uid="{DD98C381-1D2F-4129-BF2B-416B9F6B51C6}"/>
+    <hyperlink ref="J41" r:id="rId78" xr:uid="{61899882-82A0-4494-9A50-48D3406AC8FA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -14489,301 +14894,739 @@
       </c>
       <c r="I330" s="6"/>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A331" s="6"/>
-      <c r="B331" s="6"/>
-      <c r="C331" s="7"/>
-      <c r="D331" s="7"/>
-      <c r="E331" s="8"/>
-      <c r="F331" s="8"/>
-      <c r="G331" s="12"/>
-      <c r="H331" s="9"/>
-      <c r="I331" s="6"/>
-    </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A332" s="6"/>
-      <c r="B332" s="6"/>
-      <c r="C332" s="7"/>
-      <c r="D332" s="7"/>
-      <c r="E332" s="8"/>
-      <c r="F332" s="8"/>
-      <c r="G332" s="12"/>
-      <c r="H332" s="9"/>
-      <c r="I332" s="6"/>
-    </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A333" s="6"/>
-      <c r="B333" s="6"/>
-      <c r="C333" s="7"/>
-      <c r="D333" s="7"/>
-      <c r="E333" s="8"/>
-      <c r="F333" s="8"/>
-      <c r="G333" s="12"/>
-      <c r="H333" s="9"/>
+    <row r="331" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A331" s="6">
+        <v>1562086</v>
+      </c>
+      <c r="B331" s="6">
+        <v>1</v>
+      </c>
+      <c r="C331" s="7" t="s">
+        <v>1164</v>
+      </c>
+      <c r="D331" s="7" t="s">
+        <v>1180</v>
+      </c>
+      <c r="E331" s="8">
+        <v>3.83</v>
+      </c>
+      <c r="F331" s="8">
+        <v>4</v>
+      </c>
+      <c r="G331" s="12">
+        <v>4</v>
+      </c>
+      <c r="H331" s="9" t="s">
+        <v>1181</v>
+      </c>
+      <c r="I331" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="332" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A332" s="6">
+        <v>1562086</v>
+      </c>
+      <c r="B332" s="6">
+        <v>2</v>
+      </c>
+      <c r="C332" s="7" t="s">
+        <v>1165</v>
+      </c>
+      <c r="D332" s="7" t="s">
+        <v>1182</v>
+      </c>
+      <c r="E332" s="8">
+        <v>3.73</v>
+      </c>
+      <c r="F332" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="G332" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H332" s="9" t="s">
+        <v>1183</v>
+      </c>
+      <c r="I332" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="333" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A333" s="6">
+        <v>1562086</v>
+      </c>
+      <c r="B333" s="6">
+        <v>3</v>
+      </c>
+      <c r="C333" s="7" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D333" s="7" t="s">
+        <v>1184</v>
+      </c>
+      <c r="E333" s="8">
+        <v>3.37</v>
+      </c>
+      <c r="F333" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="G333" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="H333" s="9" t="s">
+        <v>1186</v>
+      </c>
       <c r="I333" s="6"/>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A334" s="6"/>
-      <c r="B334" s="6"/>
-      <c r="C334" s="7"/>
-      <c r="D334" s="7"/>
-      <c r="E334" s="8"/>
-      <c r="F334" s="8"/>
-      <c r="G334" s="12"/>
-      <c r="H334" s="9"/>
+    <row r="334" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A334" s="6">
+        <v>1562086</v>
+      </c>
+      <c r="B334" s="6">
+        <v>4</v>
+      </c>
+      <c r="C334" s="7" t="s">
+        <v>1167</v>
+      </c>
+      <c r="D334" s="7" t="s">
+        <v>1185</v>
+      </c>
+      <c r="E334" s="8">
+        <v>2.99</v>
+      </c>
+      <c r="F334" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="G334" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="H334" s="9" t="s">
+        <v>1187</v>
+      </c>
       <c r="I334" s="6"/>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A335" s="6"/>
-      <c r="B335" s="6"/>
-      <c r="C335" s="7"/>
-      <c r="D335" s="7"/>
-      <c r="E335" s="8"/>
-      <c r="F335" s="8"/>
-      <c r="G335" s="12"/>
-      <c r="H335" s="9"/>
-      <c r="I335" s="6"/>
-    </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A336" s="6"/>
-      <c r="B336" s="6"/>
-      <c r="C336" s="7"/>
-      <c r="D336" s="7"/>
-      <c r="E336" s="8"/>
-      <c r="F336" s="8"/>
-      <c r="G336" s="12"/>
-      <c r="H336" s="9"/>
+    <row r="335" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A335" s="6">
+        <v>1562086</v>
+      </c>
+      <c r="B335" s="6">
+        <v>5</v>
+      </c>
+      <c r="C335" s="7" t="s">
+        <v>1168</v>
+      </c>
+      <c r="D335" s="7" t="s">
+        <v>1188</v>
+      </c>
+      <c r="E335" s="8">
+        <v>3.47</v>
+      </c>
+      <c r="F335" s="8">
+        <v>4</v>
+      </c>
+      <c r="G335" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="H335" s="9" t="s">
+        <v>1197</v>
+      </c>
+      <c r="I335" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="336" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A336" s="6">
+        <v>1562086</v>
+      </c>
+      <c r="B336" s="6">
+        <v>6</v>
+      </c>
+      <c r="C336" s="7" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D336" s="7" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E336" s="8">
+        <v>3.23</v>
+      </c>
+      <c r="F336" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="G336" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="H336" s="9" t="s">
+        <v>1189</v>
+      </c>
       <c r="I336" s="6"/>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A337" s="6"/>
-      <c r="B337" s="6"/>
-      <c r="C337" s="7"/>
-      <c r="D337" s="7"/>
-      <c r="E337" s="8"/>
-      <c r="F337" s="8"/>
-      <c r="G337" s="12"/>
-      <c r="H337" s="9"/>
+    <row r="337" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A337" s="6">
+        <v>1562086</v>
+      </c>
+      <c r="B337" s="6">
+        <v>7</v>
+      </c>
+      <c r="C337" s="7" t="s">
+        <v>1170</v>
+      </c>
+      <c r="D337" s="7" t="s">
+        <v>1195</v>
+      </c>
+      <c r="E337" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="F337" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="G337" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="H337" s="9" t="s">
+        <v>1190</v>
+      </c>
       <c r="I337" s="6"/>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A338" s="6"/>
-      <c r="B338" s="6"/>
-      <c r="C338" s="7"/>
-      <c r="D338" s="7"/>
-      <c r="E338" s="8"/>
-      <c r="F338" s="8"/>
-      <c r="G338" s="12"/>
-      <c r="H338" s="9"/>
+    <row r="338" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A338" s="6">
+        <v>1562086</v>
+      </c>
+      <c r="B338" s="6">
+        <v>8</v>
+      </c>
+      <c r="C338" s="7" t="s">
+        <v>1171</v>
+      </c>
+      <c r="D338" s="7" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E338" s="8">
+        <v>3.12</v>
+      </c>
+      <c r="F338" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="G338" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="H338" s="9" t="s">
+        <v>1191</v>
+      </c>
       <c r="I338" s="6"/>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A339" s="6"/>
-      <c r="B339" s="6"/>
-      <c r="C339" s="7"/>
-      <c r="D339" s="7"/>
-      <c r="E339" s="8"/>
-      <c r="F339" s="8"/>
-      <c r="G339" s="12"/>
-      <c r="H339" s="9"/>
+    <row r="339" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A339" s="6">
+        <v>1562086</v>
+      </c>
+      <c r="B339" s="6">
+        <v>9</v>
+      </c>
+      <c r="C339" s="7" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D339" s="7" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E339" s="8">
+        <v>3.65</v>
+      </c>
+      <c r="F339" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="G339" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H339" s="9" t="s">
+        <v>1192</v>
+      </c>
       <c r="I339" s="6"/>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A340" s="6"/>
-      <c r="B340" s="6"/>
-      <c r="C340" s="7"/>
-      <c r="D340" s="7"/>
-      <c r="E340" s="8"/>
-      <c r="F340" s="8"/>
-      <c r="G340" s="12"/>
-      <c r="H340" s="9"/>
+    <row r="340" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A340" s="6">
+        <v>31683230</v>
+      </c>
+      <c r="B340" s="6">
+        <v>1</v>
+      </c>
+      <c r="C340" s="7" t="s">
+        <v>1199</v>
+      </c>
+      <c r="D340" s="7" t="s">
+        <v>1213</v>
+      </c>
+      <c r="E340" s="8">
+        <v>3.69</v>
+      </c>
+      <c r="F340" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G340" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H340" s="9" t="s">
+        <v>1214</v>
+      </c>
       <c r="I340" s="6"/>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A341" s="6"/>
-      <c r="B341" s="6"/>
-      <c r="C341" s="7"/>
-      <c r="D341" s="7"/>
-      <c r="E341" s="8"/>
-      <c r="F341" s="8"/>
-      <c r="G341" s="12"/>
-      <c r="H341" s="9"/>
+    <row r="341" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A341" s="6">
+        <v>31683230</v>
+      </c>
+      <c r="B341" s="6">
+        <v>2</v>
+      </c>
+      <c r="C341" s="7" t="s">
+        <v>1200</v>
+      </c>
+      <c r="D341" s="7" t="s">
+        <v>1215</v>
+      </c>
+      <c r="E341" s="8">
+        <v>3.75</v>
+      </c>
+      <c r="F341" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="G341" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="H341" s="9" t="s">
+        <v>1216</v>
+      </c>
       <c r="I341" s="6"/>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A342" s="6"/>
-      <c r="B342" s="6"/>
-      <c r="C342" s="7"/>
-      <c r="D342" s="7"/>
-      <c r="E342" s="8"/>
-      <c r="F342" s="8"/>
-      <c r="G342" s="12"/>
-      <c r="H342" s="9"/>
+    <row r="342" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A342" s="6">
+        <v>31683230</v>
+      </c>
+      <c r="B342" s="6">
+        <v>3</v>
+      </c>
+      <c r="C342" s="7" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D342" s="7" t="s">
+        <v>1228</v>
+      </c>
+      <c r="E342" s="8">
+        <v>3.68</v>
+      </c>
+      <c r="F342" s="8">
+        <v>4</v>
+      </c>
+      <c r="G342" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H342" s="9" t="s">
+        <v>1217</v>
+      </c>
       <c r="I342" s="6"/>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A343" s="6"/>
-      <c r="B343" s="6"/>
-      <c r="C343" s="7"/>
-      <c r="D343" s="7"/>
-      <c r="E343" s="8"/>
-      <c r="F343" s="8"/>
-      <c r="G343" s="12"/>
-      <c r="H343" s="9"/>
+    <row r="343" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A343" s="6">
+        <v>31683230</v>
+      </c>
+      <c r="B343" s="6">
+        <v>4</v>
+      </c>
+      <c r="C343" s="7" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D343" s="7" t="s">
+        <v>1227</v>
+      </c>
+      <c r="E343" s="8">
+        <v>3.77</v>
+      </c>
+      <c r="F343" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="G343" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="H343" s="9" t="s">
+        <v>1218</v>
+      </c>
       <c r="I343" s="6"/>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A344" s="6"/>
-      <c r="B344" s="6"/>
-      <c r="C344" s="7"/>
-      <c r="D344" s="7"/>
-      <c r="E344" s="8"/>
-      <c r="F344" s="8"/>
-      <c r="G344" s="12"/>
-      <c r="H344" s="9"/>
+    <row r="344" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A344" s="6">
+        <v>31683230</v>
+      </c>
+      <c r="B344" s="6">
+        <v>5</v>
+      </c>
+      <c r="C344" s="7" t="s">
+        <v>1203</v>
+      </c>
+      <c r="D344" s="7" t="s">
+        <v>1226</v>
+      </c>
+      <c r="E344" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="F344" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="G344" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H344" s="9" t="s">
+        <v>1219</v>
+      </c>
       <c r="I344" s="6"/>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A345" s="6"/>
-      <c r="B345" s="6"/>
-      <c r="C345" s="7"/>
-      <c r="D345" s="7"/>
-      <c r="E345" s="8"/>
-      <c r="F345" s="8"/>
-      <c r="G345" s="12"/>
-      <c r="H345" s="9"/>
+    <row r="345" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A345" s="6">
+        <v>31683230</v>
+      </c>
+      <c r="B345" s="6">
+        <v>6</v>
+      </c>
+      <c r="C345" s="7" t="s">
+        <v>1204</v>
+      </c>
+      <c r="D345" s="7" t="s">
+        <v>1225</v>
+      </c>
+      <c r="E345" s="8">
+        <v>3.57</v>
+      </c>
+      <c r="F345" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="G345" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H345" s="9" t="s">
+        <v>1220</v>
+      </c>
       <c r="I345" s="6"/>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A346" s="6"/>
-      <c r="B346" s="6"/>
-      <c r="C346" s="7"/>
-      <c r="D346" s="7"/>
-      <c r="E346" s="8"/>
-      <c r="F346" s="8"/>
-      <c r="G346" s="12"/>
-      <c r="H346" s="9"/>
+    <row r="346" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A346" s="6">
+        <v>31683230</v>
+      </c>
+      <c r="B346" s="6">
+        <v>7</v>
+      </c>
+      <c r="C346" s="7" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D346" s="7" t="s">
+        <v>1224</v>
+      </c>
+      <c r="E346" s="8">
+        <v>3.77</v>
+      </c>
+      <c r="F346" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="G346" s="12">
+        <v>4</v>
+      </c>
+      <c r="H346" s="9" t="s">
+        <v>1221</v>
+      </c>
       <c r="I346" s="6"/>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A347" s="6"/>
-      <c r="B347" s="6"/>
-      <c r="C347" s="7"/>
-      <c r="D347" s="7"/>
-      <c r="E347" s="8"/>
-      <c r="F347" s="8"/>
-      <c r="G347" s="12"/>
-      <c r="H347" s="9"/>
+    <row r="347" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A347" s="6">
+        <v>31683230</v>
+      </c>
+      <c r="B347" s="6">
+        <v>8</v>
+      </c>
+      <c r="C347" s="7" t="s">
+        <v>1206</v>
+      </c>
+      <c r="D347" s="7" t="s">
+        <v>1223</v>
+      </c>
+      <c r="E347" s="8">
+        <v>3.82</v>
+      </c>
+      <c r="F347" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="G347" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H347" s="9" t="s">
+        <v>1222</v>
+      </c>
       <c r="I347" s="6"/>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A348" s="6"/>
-      <c r="B348" s="6"/>
-      <c r="C348" s="7"/>
-      <c r="D348" s="7"/>
-      <c r="E348" s="8"/>
-      <c r="F348" s="8"/>
-      <c r="G348" s="12"/>
-      <c r="H348" s="9"/>
+    <row r="348" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A348" s="6">
+        <v>28426390</v>
+      </c>
+      <c r="B348" s="6">
+        <v>1</v>
+      </c>
+      <c r="C348" s="7" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D348" s="7" t="s">
+        <v>1245</v>
+      </c>
+      <c r="E348" s="8">
+        <v>3.78</v>
+      </c>
+      <c r="F348" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="G348" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H348" s="9" t="s">
+        <v>1255</v>
+      </c>
       <c r="I348" s="6"/>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A349" s="6"/>
-      <c r="B349" s="6"/>
-      <c r="C349" s="7"/>
-      <c r="D349" s="7"/>
-      <c r="E349" s="8"/>
-      <c r="F349" s="8"/>
-      <c r="G349" s="12"/>
-      <c r="H349" s="9"/>
+    <row r="349" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A349" s="6">
+        <v>28426390</v>
+      </c>
+      <c r="B349" s="6">
+        <v>2</v>
+      </c>
+      <c r="C349" s="7" t="s">
+        <v>1233</v>
+      </c>
+      <c r="D349" s="7" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E349" s="8">
+        <v>3.52</v>
+      </c>
+      <c r="F349" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G349" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H349" s="9" t="s">
+        <v>1256</v>
+      </c>
       <c r="I349" s="6"/>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A350" s="6"/>
-      <c r="B350" s="6"/>
-      <c r="C350" s="7"/>
-      <c r="D350" s="7"/>
-      <c r="E350" s="8"/>
-      <c r="F350" s="8"/>
-      <c r="G350" s="12"/>
-      <c r="H350" s="9"/>
+    <row r="350" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A350" s="6">
+        <v>28426390</v>
+      </c>
+      <c r="B350" s="6">
+        <v>3</v>
+      </c>
+      <c r="C350" s="7" t="s">
+        <v>1234</v>
+      </c>
+      <c r="D350" s="7" t="s">
+        <v>1247</v>
+      </c>
+      <c r="E350" s="8">
+        <v>3.74</v>
+      </c>
+      <c r="F350" s="8">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="G350" s="12">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="H350" s="9" t="s">
+        <v>1257</v>
+      </c>
       <c r="I350" s="6"/>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A351" s="6"/>
-      <c r="B351" s="6"/>
-      <c r="C351" s="7"/>
-      <c r="D351" s="7"/>
-      <c r="E351" s="8"/>
-      <c r="F351" s="8"/>
-      <c r="G351" s="12"/>
-      <c r="H351" s="9"/>
+    <row r="351" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A351" s="6">
+        <v>28426390</v>
+      </c>
+      <c r="B351" s="6">
+        <v>4</v>
+      </c>
+      <c r="C351" s="7" t="s">
+        <v>1235</v>
+      </c>
+      <c r="D351" s="7" t="s">
+        <v>1248</v>
+      </c>
+      <c r="E351" s="8">
+        <v>3.39</v>
+      </c>
+      <c r="F351" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="G351" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="H351" s="9" t="s">
+        <v>1258</v>
+      </c>
       <c r="I351" s="6"/>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A352" s="6"/>
-      <c r="B352" s="6"/>
-      <c r="C352" s="7"/>
-      <c r="D352" s="7"/>
-      <c r="E352" s="8"/>
-      <c r="F352" s="8"/>
-      <c r="G352" s="12"/>
-      <c r="H352" s="9"/>
+    <row r="352" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A352" s="6">
+        <v>28426390</v>
+      </c>
+      <c r="B352" s="6">
+        <v>5</v>
+      </c>
+      <c r="C352" s="7" t="s">
+        <v>1236</v>
+      </c>
+      <c r="D352" s="7" t="s">
+        <v>1249</v>
+      </c>
+      <c r="E352" s="8">
+        <v>3.59</v>
+      </c>
+      <c r="F352" s="8">
+        <v>4.25</v>
+      </c>
+      <c r="G352" s="12">
+        <v>4.25</v>
+      </c>
+      <c r="H352" s="9" t="s">
+        <v>1259</v>
+      </c>
       <c r="I352" s="6"/>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A353" s="6"/>
-      <c r="B353" s="6"/>
-      <c r="C353" s="7"/>
-      <c r="D353" s="7"/>
-      <c r="E353" s="8"/>
-      <c r="F353" s="8"/>
-      <c r="G353" s="12"/>
-      <c r="H353" s="9"/>
+    <row r="353" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A353" s="6">
+        <v>28426390</v>
+      </c>
+      <c r="B353" s="6">
+        <v>6</v>
+      </c>
+      <c r="C353" s="7" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D353" s="7" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E353" s="8">
+        <v>3.64</v>
+      </c>
+      <c r="F353" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G353" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H353" s="9" t="s">
+        <v>1260</v>
+      </c>
       <c r="I353" s="6"/>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A354" s="6"/>
-      <c r="B354" s="6"/>
-      <c r="C354" s="7"/>
-      <c r="D354" s="7"/>
-      <c r="E354" s="8"/>
-      <c r="F354" s="8"/>
-      <c r="G354" s="12"/>
-      <c r="H354" s="9"/>
+    <row r="354" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A354" s="6">
+        <v>28426390</v>
+      </c>
+      <c r="B354" s="6">
+        <v>7</v>
+      </c>
+      <c r="C354" s="7" t="s">
+        <v>1238</v>
+      </c>
+      <c r="D354" s="7" t="s">
+        <v>1251</v>
+      </c>
+      <c r="E354" s="8">
+        <v>3.42</v>
+      </c>
+      <c r="F354" s="8">
+        <v>4</v>
+      </c>
+      <c r="G354" s="12">
+        <v>4</v>
+      </c>
+      <c r="H354" s="9" t="s">
+        <v>1261</v>
+      </c>
       <c r="I354" s="6"/>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A355" s="6"/>
-      <c r="B355" s="6"/>
-      <c r="C355" s="7"/>
-      <c r="D355" s="7"/>
-      <c r="E355" s="8"/>
-      <c r="F355" s="8"/>
-      <c r="G355" s="12"/>
-      <c r="H355" s="9"/>
+    <row r="355" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A355" s="6">
+        <v>28426390</v>
+      </c>
+      <c r="B355" s="6">
+        <v>8</v>
+      </c>
+      <c r="C355" s="7" t="s">
+        <v>1239</v>
+      </c>
+      <c r="D355" s="7" t="s">
+        <v>1252</v>
+      </c>
+      <c r="E355" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="F355" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G355" s="12">
+        <v>4</v>
+      </c>
+      <c r="H355" s="9" t="s">
+        <v>1262</v>
+      </c>
       <c r="I355" s="6"/>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A356" s="6"/>
-      <c r="B356" s="6"/>
-      <c r="C356" s="7"/>
-      <c r="D356" s="7"/>
-      <c r="E356" s="8"/>
-      <c r="F356" s="8"/>
-      <c r="G356" s="12"/>
-      <c r="H356" s="9"/>
+    <row r="356" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A356" s="6">
+        <v>28426390</v>
+      </c>
+      <c r="B356" s="6">
+        <v>9</v>
+      </c>
+      <c r="C356" s="7" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D356" s="7" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E356" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="F356" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G356" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H356" s="9" t="s">
+        <v>1263</v>
+      </c>
       <c r="I356" s="6"/>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A357" s="6"/>
-      <c r="B357" s="6"/>
-      <c r="C357" s="7"/>
-      <c r="D357" s="7"/>
-      <c r="E357" s="8"/>
-      <c r="F357" s="8"/>
-      <c r="G357" s="12"/>
-      <c r="H357" s="9"/>
+    <row r="357" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A357" s="6">
+        <v>28426390</v>
+      </c>
+      <c r="B357" s="6">
+        <v>10</v>
+      </c>
+      <c r="C357" s="7" t="s">
+        <v>1241</v>
+      </c>
+      <c r="D357" s="7" t="s">
+        <v>1254</v>
+      </c>
+      <c r="E357" s="8">
+        <v>3.68</v>
+      </c>
+      <c r="F357" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G357" s="12">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="H357" s="9" t="s">
+        <v>1264</v>
+      </c>
       <c r="I357" s="6"/>
     </row>
     <row r="358" spans="1:9" x14ac:dyDescent="0.25">

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E794F6A1-BD1A-487A-9679-3B0EB20F53B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C560DB9E-8A5C-4147-8276-C0B089217B48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1425" uniqueCount="1265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1450" uniqueCount="1286">
   <si>
     <t>No</t>
   </si>
@@ -4021,6 +4021,69 @@
   </si>
   <si>
     <t>Επίλογος με τον αφορισμό του τίτλου να συνοψίζει το ηθικό σύμπαν του δίσκου: η νίκη διεκδικείται από πολλούς, ενώ η ήττα εγκαταλείπεται στους λίγους. Η σύνθεση κλείνει σαν πικρός πολιτικός και ανθρώπινος απολογισμός, χωρίς θριαμβολογία αλλά με επιμονή στη μνήμη των ηττημένων.</t>
+  </si>
+  <si>
+    <t>Pink Floyd</t>
+  </si>
+  <si>
+    <t>Wish You Were Here</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/25885156-Pink-Floyd-Wish-You-Were-Here</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/tKTkJZ2iBIpRjl6TK3Ls3a3qCwzD9aQXtIyCt8uT1Ck/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI1ODg1/MTU2LTE2OTUyMDA1/ODgtMTk1NS5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Welcome to the Machine</t>
+  </si>
+  <si>
+    <t>Have a Cigar</t>
+  </si>
+  <si>
+    <t>Shine On You Crazy Diamond (Parts 1–5)</t>
+  </si>
+  <si>
+    <t>Shine On You Crazy Diamond (Parts 6–9)</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Art Rock [Concept Album, Space Rock, Psychedelic Rock]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Art Rock [Space Rock, Ambient Prog, Symphonic Prog]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Art Rock [Electronic Rock, Industrial-tinged Prog, Dystopian Rock]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Hard Rock [Funk Rock, Satirical Art Rock]</t>
+  </si>
+  <si>
+    <t>Folk Rock, Progressive Rock [Acoustic Rock, Folk Ballad, Classic Rock]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Art Rock [Space Rock, Jazz Rock, Symphonic Prog]</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το ένατο στούντιο άλμπουμ των Pink Floyd. Ευρωπαϊκή remastered έκδοση του 2016 σε heavyweight βινύλιο 180g (Pink Floyd Records, PFRLP9). Remastering από τους James Guthrie, Joel Plante και Bernie Grundman. Η κοπή έγινε στα Optimal Media (BG24222). Περιέχει μαύρο shrink-wrap, postcard και τυπωμένο εσωτερικό φάκελο.</t>
+  </si>
+  <si>
+    <t>Pink Floyd Records – PFRLP9, 5099902988016 / Vinyl, LP, Album, Reissue, Remastered, Stereo, 180 Gram</t>
+  </si>
+  <si>
+    <t>Αργή, σχεδόν τελετουργική είσοδος μέσα από synth drone, organ και την εμβληματική τετράφωνη κιθαριστική φράση του Gilmour. Αποτελεί τον πυρήνα της αφιέρωσης στον Syd Barrett. Μια θλιμμένη αναγνώριση του χαρισματικού "τρελού διαμαντιού" που χάθηκε μέσα στις συνέπειες της ψυχικής του κατάρρευσης και της πίεσης της φήμης.</t>
+  </si>
+  <si>
+    <t>Ψυχρό, μηχανικό και σχεδόν δυστοπικό κομμάτι, με συνθεσάιζερ, processed acoustic guitar και ηχητικά εφέ που μοιάζουν να σε εγκλωβίζουν σε εργοστάσιο. Οι στίχοι του Waters σατιρίζουν τη μουσική βιομηχανία ως μηχανισμό που σχεδιάζει, κατευθύνει και τελικά καταναλώνει τον καλλιτέχνη.</t>
+  </si>
+  <si>
+    <t>Το πιο άμεσο και δηκτικό rock τραγούδι του δίσκου. Με funky bass line, σκληρό guitar groove και την ειρωνική ερμηνεία του Roy Harper, δίνει φωνή σε έναν ανώνυμο δισκογραφικό executive που μιλά στον μουσικό με κενές φιλοφρονήσεις, χωρίς καν να γνωρίζει βασικά στοιχεία της μπάντας.</t>
+  </si>
+  <si>
+    <t>Η ακουστική καρδιά του δίσκου. Με την εσκεμμένα "ραδιοφωνική" εισαγωγή, το 12-string acoustic μοτίβο και το λιτό solo του Gilmour, μετατρέπει τη νοσταλγία σε καθολική ερώτηση: μπορείς ακόμη να διακρίνεις το αληθινό από το ψεύτικο, την ελευθερία από μια χρυσή φυλακή; Απευθύνεται στον Barrett, αλλά η δύναμή του βρίσκεται ακριβώς στο ότι μπορεί να ακουστεί ως τραγούδι για κάθε απώντα άνθρωπο.</t>
+  </si>
+  <si>
+    <t>Η δεύτερη ενότητα επιστρέφει στο θέμα με πιο bluesy, jazz-rock και τελικά λυρική διάθεση. Το σαξόφωνο του Parry, το electric piano του Wright και η βραδυφλεγής κιθάρα του Gilmour προσφέρουν μια αίσθηση αποδοχής αντί καθαρής θλίψης. Η τελική αναφορά στο παλαιότερο Floyd κομμάτι See Emily Play λειτουργεί ως λεπτή, συγκινητική μνήμη του Barrett.</t>
   </si>
 </sst>
 </file>
@@ -4496,7 +4559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -5822,6 +5885,38 @@
       </c>
       <c r="J41" s="11" t="s">
         <v>1232</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A42" s="6">
+        <v>25885156</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>1266</v>
+      </c>
+      <c r="D42" s="6">
+        <v>1975</v>
+      </c>
+      <c r="E42" s="10">
+        <v>4.37</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>1273</v>
+      </c>
+      <c r="G42" s="7" t="s">
+        <v>1279</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>1280</v>
+      </c>
+      <c r="I42" s="11" t="s">
+        <v>1267</v>
+      </c>
+      <c r="J42" s="11" t="s">
+        <v>1268</v>
       </c>
     </row>
   </sheetData>
@@ -5904,6 +5999,8 @@
     <hyperlink ref="I40" r:id="rId76" xr:uid="{B1E3FDF7-1E6A-4CD0-9059-589E76913A9D}"/>
     <hyperlink ref="I41" r:id="rId77" xr:uid="{DD98C381-1D2F-4129-BF2B-416B9F6B51C6}"/>
     <hyperlink ref="J41" r:id="rId78" xr:uid="{61899882-82A0-4494-9A50-48D3406AC8FA}"/>
+    <hyperlink ref="I42" r:id="rId79" xr:uid="{1A7FCE72-5D02-4E89-93C9-DE53A362CFED}"/>
+    <hyperlink ref="J42" r:id="rId80" xr:uid="{0E5A0CB2-B773-4C6B-B1DB-498BA4E6F6E5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5911,7 +6008,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I361"/>
+  <dimension ref="A1:I362"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="3" bestFit="1" customWidth="1"/>
@@ -15629,49 +15726,146 @@
       </c>
       <c r="I357" s="6"/>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A358" s="6"/>
-      <c r="B358" s="6"/>
-      <c r="C358" s="7"/>
-      <c r="D358" s="7"/>
-      <c r="E358" s="8"/>
-      <c r="F358" s="8"/>
-      <c r="G358" s="12"/>
-      <c r="H358" s="9"/>
-      <c r="I358" s="6"/>
-    </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A359" s="6"/>
-      <c r="B359" s="6"/>
-      <c r="C359" s="7"/>
-      <c r="D359" s="7"/>
-      <c r="E359" s="8"/>
-      <c r="F359" s="8"/>
-      <c r="G359" s="12"/>
-      <c r="H359" s="9"/>
+    <row r="358" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A358" s="6">
+        <v>25885156</v>
+      </c>
+      <c r="B358" s="6">
+        <v>1</v>
+      </c>
+      <c r="C358" s="7" t="s">
+        <v>1271</v>
+      </c>
+      <c r="D358" s="7" t="s">
+        <v>1274</v>
+      </c>
+      <c r="E358" s="8">
+        <v>4.72</v>
+      </c>
+      <c r="F358" s="8">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G358" s="12">
+        <v>4.95</v>
+      </c>
+      <c r="H358" s="9" t="s">
+        <v>1281</v>
+      </c>
+      <c r="I358" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="359" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A359" s="6">
+        <v>25885156</v>
+      </c>
+      <c r="B359" s="6">
+        <v>2</v>
+      </c>
+      <c r="C359" s="7" t="s">
+        <v>1269</v>
+      </c>
+      <c r="D359" s="7" t="s">
+        <v>1275</v>
+      </c>
+      <c r="E359" s="8">
+        <v>4.32</v>
+      </c>
+      <c r="F359" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G359" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H359" s="9" t="s">
+        <v>1282</v>
+      </c>
       <c r="I359" s="6"/>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A360" s="6"/>
-      <c r="B360" s="6"/>
-      <c r="C360" s="7"/>
-      <c r="D360" s="7"/>
-      <c r="E360" s="8"/>
-      <c r="F360" s="8"/>
-      <c r="G360" s="12"/>
-      <c r="H360" s="9"/>
-      <c r="I360" s="6"/>
-    </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A361" s="6"/>
-      <c r="B361" s="6"/>
-      <c r="C361" s="7"/>
-      <c r="D361" s="7"/>
-      <c r="E361" s="8"/>
-      <c r="F361" s="8"/>
-      <c r="G361" s="12"/>
-      <c r="H361" s="9"/>
-      <c r="I361" s="6"/>
+    <row r="360" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A360" s="6">
+        <v>25885156</v>
+      </c>
+      <c r="B360" s="6">
+        <v>3</v>
+      </c>
+      <c r="C360" s="7" t="s">
+        <v>1270</v>
+      </c>
+      <c r="D360" s="7" t="s">
+        <v>1276</v>
+      </c>
+      <c r="E360" s="8">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="F360" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="G360" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H360" s="9" t="s">
+        <v>1283</v>
+      </c>
+      <c r="I360" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="361" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A361" s="6">
+        <v>25885156</v>
+      </c>
+      <c r="B361" s="6">
+        <v>4</v>
+      </c>
+      <c r="C361" s="7" t="s">
+        <v>1266</v>
+      </c>
+      <c r="D361" s="7" t="s">
+        <v>1277</v>
+      </c>
+      <c r="E361" s="8">
+        <v>4.6900000000000004</v>
+      </c>
+      <c r="F361" s="8">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G361" s="12">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H361" s="9" t="s">
+        <v>1284</v>
+      </c>
+      <c r="I361" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="362" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A362" s="6">
+        <v>25885156</v>
+      </c>
+      <c r="B362" s="6">
+        <v>5</v>
+      </c>
+      <c r="C362" s="7" t="s">
+        <v>1272</v>
+      </c>
+      <c r="D362" s="7" t="s">
+        <v>1278</v>
+      </c>
+      <c r="E362" s="8">
+        <v>4.55</v>
+      </c>
+      <c r="F362" s="8">
+        <v>4.8</v>
+      </c>
+      <c r="G362" s="12">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="H362" s="9" t="s">
+        <v>1285</v>
+      </c>
+      <c r="I362" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C560DB9E-8A5C-4147-8276-C0B089217B48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A33BADDB-6501-4412-958D-2032634FC7A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1450" uniqueCount="1286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1481" uniqueCount="1316">
   <si>
     <t>No</t>
   </si>
@@ -4084,6 +4084,96 @@
   </si>
   <si>
     <t>Η δεύτερη ενότητα επιστρέφει στο θέμα με πιο bluesy, jazz-rock και τελικά λυρική διάθεση. Το σαξόφωνο του Parry, το electric piano του Wright και η βραδυφλεγής κιθάρα του Gilmour προσφέρουν μια αίσθηση αποδοχής αντί καθαρής θλίψης. Η τελική αναφορά στο παλαιότερο Floyd κομμάτι See Emily Play λειτουργεί ως λεπτή, συγκινητική μνήμη του Barrett.</t>
+  </si>
+  <si>
+    <t>Immortal's Requiem</t>
+  </si>
+  <si>
+    <t>Dawn Of Mind</t>
+  </si>
+  <si>
+    <t>Seven Sided Mirror</t>
+  </si>
+  <si>
+    <t>Up The Tower</t>
+  </si>
+  <si>
+    <t>Black Spire Course</t>
+  </si>
+  <si>
+    <t>Blood Becomes Sand</t>
+  </si>
+  <si>
+    <t>Moonchild</t>
+  </si>
+  <si>
+    <t>Keep On Running (Alternate Version)</t>
+  </si>
+  <si>
+    <t>Phantom Spell</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/nRIpRMcnZrwYHVNAg7NFYzf1sqmklvNkgN7zMw01XCk/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI1ODk1/NjM1LTE2NzQ3NjMy/NzEtMjQzMi5wbmc.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/25895635-Phantom-Spell-Immortals-Requiem</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το δεύτερο full-length άλμπουμ του project Phantom Spell, πίσω από το οποίο βρίσκεται ο πολυοργανίστας Kyle McNeill (των Seven Sisters). Ηχογραφήθηκε στα Wizard Gower Studios. Ευρωπαϊκή έκδοση σε μαύρο βινύλιο από τη Cruz Del Sur Music (CRUZ611). Περιέχει αφίσα (poster), ένθετο (insert) και κωδικό λήψης (download code).</t>
+  </si>
+  <si>
+    <t>Cruz Del Sur Music – CRUZ611 / Vinyl, LP, Album</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Heavy Metal [Retro Prog, Traditional Heavy Metal, Hard Rock]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Hard Rock [Organ-driven Retro Prog, Fantasy Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Progressive Rock [NWOTHM, Melodic Heavy Metal, Keyboard Prog]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Hard Rock [Symphonic Prog, Fantasy Hard Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Traditional Heavy Metal, 70s Hard Rock]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Heavy Metal [Instrumental Prog Metal, Organ Rock (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Heavy Metal [Epic Heavy Prog, Doom-tinged Hard Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Heavy Rock Cover, Blues Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Progressive Rock [Melodic Hard Rock, Retro Prog]</t>
+  </si>
+  <si>
+    <t>Σύντομη αλλά επιβλητική έναρξη, με σχεδόν εκκλησιαστική χορωδιακή αίσθηση και organ-driven ατμόσφαιρα. Εισάγει τον κεντρικό μύθο: μια φιγούρα που αναζητά αιωνιότητα, μόνο για να συνειδητοποιήσει το βάρος της ακινησίας και της λησμονιάς.</t>
+  </si>
+  <si>
+    <t>Ένα από τα πιο άμεσα και δυνατά κομμάτια του δίσκου. Τα galloping riffs και τα προσεκτικά τοποθετημένα keyboards φέρνουν στο νου Maiden-ική ορμή, αλλά με πιο prog αρμονική ευαισθησία. Θεματικά, μιλά για μια εσωτερική αφύπνιση —τη δύσκολη στιγμή που η συνείδηση επιστρέφει και δεν επιτρέπει πλέον την άνεση της άγνοιας.</t>
+  </si>
+  <si>
+    <t>Πιο ατμοσφαιρικό και πολυφωνικά χτισμένο, μετατρέπει τον "επτάπλευρο καθρέφτη" σε σύμβολο διασπασμένης ταυτότητας και διαφορετικών οπτικών του ίδιου προσώπου. Οι αρμονίες, οι κιθάρες και το διακριτικό synth/organ υπόστρωμα προσεγγίζουν περισσότερο το symphonic prog.</t>
+  </si>
+  <si>
+    <t>Ευθύ, γρήγορο και φιλικό προς τον classic-metal ακροατή. Η εικόνα της ανάβασης στον πύργο λειτουργεί ως αλληγορία μιας αναζήτησης γνώσης ή σωτηρίας που απαιτεί ρίσκο, με τη μουσική να ακολουθεί την ίδια ανηφορική, αποφασιστική κίνηση.</t>
+  </si>
+  <si>
+    <t>Οργανικό κομμάτι και εξαιρετικό δείγμα της ισορροπίας του McNeill. Οι κιθάρες και τα πλήκτρα συνομιλούν χωρίς να ανταγωνίζονται, χτίζοντας μια μυστικιστική, σκοτεινή διαδρομή γύρω από την "κατάρα του μαύρου κωδωνοστασίου".</t>
+  </si>
+  <si>
+    <t>Η κορυφαία στιγμή του άλμπουμ και το ουσιαστικό αφηγηματικό φινάλε. Σε επτά λεπτά, ενώνει heavy riffs, μελαγχολική prog ανάπτυξη, επιβλητικά keyboards και ένα αίσθημα αργής καταστροφής. Η άμμος ως εικόνα του αίματος μιλά για θυσία, απώλεια και για την ιστορία που σβήνει ακόμη και τις πιο βίαιες πράξεις.</t>
+  </si>
+  <si>
+    <t>Διασκευή στο τραγούδι του Rory Gallagher. Ο McNeill διατηρεί την blues-rock ψυχή του πρωτοτύπου, αλλά την ντύνει με πυκνότερες κιθάρες και heavy-rock ενορχήστρωση. Είναι καλοδουλεμένο bonus, όμως βρίσκεται έξω από τον βασικό fantasy/prog κόσμο των έξι πρώτων συνθέσεων.</t>
+  </si>
+  <si>
+    <t>Εναλλακτική εκδοχή παλαιότερου τραγουδιού του project. Έχει μελωδικό hard-rock προσανατολισμό και λειτουργεί ως ευχάριστο bonus epilogue, όχι ως αναγκαίο κεφάλαιο του Immortal’s Requiem.</t>
   </si>
 </sst>
 </file>
@@ -4559,7 +4649,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -5917,6 +6007,38 @@
       </c>
       <c r="J42" s="11" t="s">
         <v>1268</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+      <c r="A43" s="6">
+        <v>25895635</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="D43" s="6">
+        <v>2022</v>
+      </c>
+      <c r="E43" s="10">
+        <v>3.58</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>1299</v>
+      </c>
+      <c r="G43" s="7" t="s">
+        <v>1297</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>1298</v>
+      </c>
+      <c r="I43" s="11" t="s">
+        <v>1296</v>
+      </c>
+      <c r="J43" s="11" t="s">
+        <v>1295</v>
       </c>
     </row>
   </sheetData>
@@ -6001,6 +6123,8 @@
     <hyperlink ref="J41" r:id="rId78" xr:uid="{61899882-82A0-4494-9A50-48D3406AC8FA}"/>
     <hyperlink ref="I42" r:id="rId79" xr:uid="{1A7FCE72-5D02-4E89-93C9-DE53A362CFED}"/>
     <hyperlink ref="J42" r:id="rId80" xr:uid="{0E5A0CB2-B773-4C6B-B1DB-498BA4E6F6E5}"/>
+    <hyperlink ref="J43" r:id="rId81" xr:uid="{39E05B2F-F184-40CE-87F6-5680777D3441}"/>
+    <hyperlink ref="I43" r:id="rId82" xr:uid="{A866AB9A-F5F8-4F0F-BEC5-94DAC48A3202}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6008,7 +6132,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I362"/>
+  <dimension ref="A1:I370"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="3" bestFit="1" customWidth="1"/>
@@ -15867,6 +15991,222 @@
       </c>
       <c r="I362" s="6"/>
     </row>
+    <row r="363" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A363" s="6">
+        <v>25895635</v>
+      </c>
+      <c r="B363" s="6">
+        <v>1</v>
+      </c>
+      <c r="C363" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="D363" s="7" t="s">
+        <v>1300</v>
+      </c>
+      <c r="E363" s="8">
+        <v>3.05</v>
+      </c>
+      <c r="F363" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="G363" s="12">
+        <v>4</v>
+      </c>
+      <c r="H363" s="9" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I363" s="6"/>
+    </row>
+    <row r="364" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A364" s="6">
+        <v>25895635</v>
+      </c>
+      <c r="B364" s="6">
+        <v>2</v>
+      </c>
+      <c r="C364" s="7" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D364" s="7" t="s">
+        <v>1301</v>
+      </c>
+      <c r="E364" s="8">
+        <v>4.16</v>
+      </c>
+      <c r="F364" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="G364" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H364" s="9" t="s">
+        <v>1309</v>
+      </c>
+      <c r="I364" s="6"/>
+    </row>
+    <row r="365" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A365" s="6">
+        <v>25895635</v>
+      </c>
+      <c r="B365" s="6">
+        <v>3</v>
+      </c>
+      <c r="C365" s="7" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D365" s="7" t="s">
+        <v>1302</v>
+      </c>
+      <c r="E365" s="8">
+        <v>4.25</v>
+      </c>
+      <c r="F365" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="G365" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H365" s="9" t="s">
+        <v>1310</v>
+      </c>
+      <c r="I365" s="6"/>
+    </row>
+    <row r="366" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A366" s="6">
+        <v>25895635</v>
+      </c>
+      <c r="B366" s="6">
+        <v>4</v>
+      </c>
+      <c r="C366" s="7" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D366" s="7" t="s">
+        <v>1303</v>
+      </c>
+      <c r="E366" s="8">
+        <v>3.85</v>
+      </c>
+      <c r="F366" s="8">
+        <v>4</v>
+      </c>
+      <c r="G366" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H366" s="9" t="s">
+        <v>1311</v>
+      </c>
+      <c r="I366" s="6"/>
+    </row>
+    <row r="367" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A367" s="6">
+        <v>25895635</v>
+      </c>
+      <c r="B367" s="6">
+        <v>5</v>
+      </c>
+      <c r="C367" s="7" t="s">
+        <v>1290</v>
+      </c>
+      <c r="D367" s="7" t="s">
+        <v>1304</v>
+      </c>
+      <c r="E367" s="8">
+        <v>3.74</v>
+      </c>
+      <c r="F367" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G367" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H367" s="9" t="s">
+        <v>1312</v>
+      </c>
+      <c r="I367" s="6"/>
+    </row>
+    <row r="368" spans="1:9" ht="66.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A368" s="6">
+        <v>25895635</v>
+      </c>
+      <c r="B368" s="6">
+        <v>6</v>
+      </c>
+      <c r="C368" s="7" t="s">
+        <v>1291</v>
+      </c>
+      <c r="D368" s="7" t="s">
+        <v>1305</v>
+      </c>
+      <c r="E368" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="F368" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="G368" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H368" s="9" t="s">
+        <v>1313</v>
+      </c>
+      <c r="I368" s="6"/>
+    </row>
+    <row r="369" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A369" s="6">
+        <v>25895635</v>
+      </c>
+      <c r="B369" s="6">
+        <v>7</v>
+      </c>
+      <c r="C369" s="7" t="s">
+        <v>1292</v>
+      </c>
+      <c r="D369" s="7" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E369" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="F369" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G369" s="12">
+        <v>4</v>
+      </c>
+      <c r="H369" s="9" t="s">
+        <v>1314</v>
+      </c>
+      <c r="I369" s="6"/>
+    </row>
+    <row r="370" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A370" s="6">
+        <v>25895635</v>
+      </c>
+      <c r="B370" s="6">
+        <v>8</v>
+      </c>
+      <c r="C370" s="7" t="s">
+        <v>1293</v>
+      </c>
+      <c r="D370" s="7" t="s">
+        <v>1307</v>
+      </c>
+      <c r="E370" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="F370" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="G370" s="12">
+        <v>4</v>
+      </c>
+      <c r="H370" s="9" t="s">
+        <v>1315</v>
+      </c>
+      <c r="I370" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A33BADDB-6501-4412-958D-2032634FC7A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB40DF0E-679A-417A-9D3D-8D213501781C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1481" uniqueCount="1316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1521" uniqueCount="1355">
   <si>
     <t>No</t>
   </si>
@@ -4174,6 +4174,123 @@
   </si>
   <si>
     <t>Εναλλακτική εκδοχή παλαιότερου τραγουδιού του project. Έχει μελωδικό hard-rock προσανατολισμό και λειτουργεί ως ευχάριστο bonus epilogue, όχι ως αναγκαίο κεφάλαιο του Immortal’s Requiem.</t>
+  </si>
+  <si>
+    <t>Driptorch</t>
+  </si>
+  <si>
+    <t>Sugar Maple</t>
+  </si>
+  <si>
+    <t>In Green / We Dream</t>
+  </si>
+  <si>
+    <t>West Memphis</t>
+  </si>
+  <si>
+    <t>Flowers For Sharon</t>
+  </si>
+  <si>
+    <t>Parlor Strut</t>
+  </si>
+  <si>
+    <t>The Ripper</t>
+  </si>
+  <si>
+    <t>Steam Presser</t>
+  </si>
+  <si>
+    <t>The Jelly Roll</t>
+  </si>
+  <si>
+    <t>Irish Goodbye</t>
+  </si>
+  <si>
+    <t>My Sweet Lord</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/sETo-sHQa4dOpbm1PUrxHJM3s_D170KW4xPU-gq6FUc/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTMxMjE2/NzM4LTE3MjczMTQy/MTAtNzA5Mi5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/31216738-Parlor-Greens-In-Green-We-Dream</t>
+  </si>
+  <si>
+    <t>Parlor Greens</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το ντεμπούτο άλμπουμ του organ jazz supergroup της Colemine Records. Ηχογράφηση και παραγωγή από τον Leroi Conroy. Mastered από τον Doug Kress. Lacquers cut στα Well Made Music και pressed στα Gotta Groove Records. Κυκλοφορία σε πράσινο βινύλιο με hype sticker.</t>
+  </si>
+  <si>
+    <t>Colemine Records – CLMN-12062 / Vinyl, LP, Album, Limited Edition, Green</t>
+  </si>
+  <si>
+    <t>Soul Jazz, Instrumental Funk [Hammond B3 Organ Trio, Deep Funk, Jazz Funk]</t>
+  </si>
+  <si>
+    <t>Instrumental Funk, Soul Jazz [Deep Funk, Organ Funk (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Soul Jazz, Jazz Funk [Organ Jazz, Soulful Groove (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Instrumental Funk, Soul Jazz [Hammond Funk, Soul Jazz (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Soul Jazz, Rhythm &amp; Blues [Memphis Soul, Organ R&amp;B (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Soul Jazz, Jazz Funk [Minor-key Organ Soul, Cinematic Soul Jazz (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Instrumental Funk, Soul Jazz [Strutting Organ Funk, Guitar-Organ Jam (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Jazz Funk, Instrumental Funk [Fast Organ Funk, Soul Jazz Burner (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Soul Jazz, Blues [Organ Blues, Slow-Burn Jazz Funk (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Instrumental Funk, Rhythm &amp; Blues [New Orleans R&amp;B, Hammond Groove (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Soul Jazz, Jazz Funk [Laid-back Organ Soul, Jazz-Funk (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Soul Jazz, Gospel [Gospel Soul, Hammond Instrumental Cover (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Ανοίγει με άμεσο, βαρύ organ-funk groove, όπου το Hammond B3 ορίζει το μπάσο και η κιθάρα του Jimmy James κόβει με καθαρές, κοφτές φράσεις. Έχει τη δραματική, νυχτερινή αίσθηση χαμένου crime-film soundtrack, αλλά με αρκετή ενέργεια ώστε να λειτουργεί ως ξεκάθαρη δήλωση προθέσεων.</t>
+  </si>
+  <si>
+    <t>Πιο γλυκό και χαλαρό, αφήνει το organ να αναπτύξει ζεστά chord voicings πάνω σε σταθερό pocket. Δεν κυνηγά κορύφωση· προτιμά μια αίσθηση άνεσης και αργής μελωδικής ροής, γι’ αυτό και λειτουργεί ως ιδανικό αντιστάθμισμα στο δυναμικό opener.</t>
+  </si>
+  <si>
+    <t>Το title track είναι compact Hammond workout, με σφιχτό ρυθμό, δυνατές αλλαγές συγχορδιών και εξαιρετική εναλλαγή κιθάρας–οργάνου. Η ομορφιά του βρίσκεται στο πόσο γρήγορα η μπάντα χτίζει ένταση χωρίς να θυσιάζει το relaxed feel του groove.</t>
+  </si>
+  <si>
+    <t>Φέρνει ευδιάκριτη Memphis soul αίσθηση, με clean, Steve Cropper-όμοια κιθαριστική γραμμή και βαθύ shuffle από τον Carman. Το κομμάτι τιμά την οικονομία της Stax αισθητικής: λίγες νότες, σωστή τοποθέτηση και μέγιστη ρυθμική αποτελεσματικότητα.</t>
+  </si>
+  <si>
+    <t>Η πιο μελαγχολική και κινηματογραφική στιγμή της πρώτης πλευράς. Το minor-key χρώμα και η πιο ανοιχτή χρονική ανάπτυξη επιτρέπουν στο trio να αφήσει χώρο για συναισθηματική αφήγηση, χωρίς να εγκαταλείπει το soul-jazz λεξιλόγιο.</t>
+  </si>
+  <si>
+    <t>Το πιο «σβέλτο» ensemble track, βασισμένο σε swaggering ρυθμό και σε διαρκή διάλογο των τριών παικτών. Δεν είναι απλώς jam: ο Scone, ο James και ο Carman περνούν ο ένας στον άλλο μικρές φράσεις, δείχνοντας γιατί η οικονομία ενός organ trio μπορεί να είναι πιο εκρηκτική από μια πολυμελή funk μπάντα.</t>
+  </si>
+  <si>
+    <t>Γρήγορος soul-jazz burner, με επιθετικό groove και άμεσες σόλο παρεμβάσεις. Εδώ η κιθάρα και το Hammond ανεβάζουν ταχύτητα, αλλά το drumming παραμένει απόλυτα μέσα στο pocket, διατηρώντας μια vintage club αίσθηση αντί για jazz-fusion επίδειξη δεξιοτεχνίας.</t>
+  </si>
+  <si>
+    <t>Από τις βαθύτερες στιγμές του άλμπουμ: ένα bluesy, slow-burn organ workout με βάρος στο χαμηλό register και στο σταδιακό χτίσιμο έντασης. Η μπάντα αποδεικνύει ότι μπορεί να είναι εξίσου πειστική όταν χαμηλώνει ταχύτητα και αφήνει το tone να μιλήσει.</t>
+  </si>
+  <si>
+    <t>Πιο ανάλαφρο και παιχνιδιάρικο, πατά σε New Orleans R&amp;B ρυθμούς και σε bouncing Hammond μοτίβα. Η αίσθηση είναι ανοιχτή, γιορτινή και σχεδόν χορευτική, χωρίς να χάνει την οργανική αμεσότητα της ηχογράφησης.</t>
+  </si>
+  <si>
+    <t>Υποτονικό και γοητευτικά λοξό, λειτουργεί σαν late-night ανάσα πριν από το κλείσιμο. Τα μελωδικά του στοιχεία αφήνουν μια μικρή αίσθηση αποχώρησης και ανεπίλυτης διάθεσης, κατάλληλη για τον τίτλο του.</t>
+  </si>
+  <si>
+    <t>Η μοναδική διασκευή του δίσκου μεταφέρει το τραγούδι του George Harrison σε gospel-soul οργανικό πλαίσιο. Αντί να προσπαθήσει να αντικαταστήσει το πνευματικό βάρος των στίχων, το Hammond αναλαμβάνει τον μελωδικό και σχεδόν φωνητικό ρόλο, οδηγώντας ένα θερμό, σεβαστικό φινάλε.</t>
   </si>
 </sst>
 </file>
@@ -4649,7 +4766,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -6039,6 +6156,38 @@
       </c>
       <c r="J43" s="11" t="s">
         <v>1295</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+      <c r="A44" s="6">
+        <v>31216738</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D44" s="6">
+        <v>2024</v>
+      </c>
+      <c r="E44" s="10">
+        <v>3.44</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>1332</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>1330</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>1331</v>
+      </c>
+      <c r="I44" s="11" t="s">
+        <v>1328</v>
+      </c>
+      <c r="J44" s="11" t="s">
+        <v>1327</v>
       </c>
     </row>
   </sheetData>
@@ -6125,6 +6274,8 @@
     <hyperlink ref="J42" r:id="rId80" xr:uid="{0E5A0CB2-B773-4C6B-B1DB-498BA4E6F6E5}"/>
     <hyperlink ref="J43" r:id="rId81" xr:uid="{39E05B2F-F184-40CE-87F6-5680777D3441}"/>
     <hyperlink ref="I43" r:id="rId82" xr:uid="{A866AB9A-F5F8-4F0F-BEC5-94DAC48A3202}"/>
+    <hyperlink ref="J44" r:id="rId83" xr:uid="{FB2A51A6-1F57-4CB7-9467-FEECDE5EA7F8}"/>
+    <hyperlink ref="I44" r:id="rId84" xr:uid="{2E158044-3989-4614-A77D-7F99C6C2356D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6132,7 +6283,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I370"/>
+  <dimension ref="A1:I381"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="3" bestFit="1" customWidth="1"/>
@@ -16207,6 +16358,303 @@
       </c>
       <c r="I370" s="6"/>
     </row>
+    <row r="371" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A371" s="6">
+        <v>31216738</v>
+      </c>
+      <c r="B371" s="6">
+        <v>1</v>
+      </c>
+      <c r="C371" s="7" t="s">
+        <v>1316</v>
+      </c>
+      <c r="D371" s="7" t="s">
+        <v>1333</v>
+      </c>
+      <c r="E371" s="8">
+        <v>4.16</v>
+      </c>
+      <c r="F371" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="G371" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H371" s="9" t="s">
+        <v>1344</v>
+      </c>
+      <c r="I371" s="6"/>
+    </row>
+    <row r="372" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A372" s="6">
+        <v>31216738</v>
+      </c>
+      <c r="B372" s="6">
+        <v>2</v>
+      </c>
+      <c r="C372" s="7" t="s">
+        <v>1317</v>
+      </c>
+      <c r="D372" s="7" t="s">
+        <v>1334</v>
+      </c>
+      <c r="E372" s="8">
+        <v>4</v>
+      </c>
+      <c r="F372" s="8">
+        <v>4</v>
+      </c>
+      <c r="G372" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H372" s="9" t="s">
+        <v>1345</v>
+      </c>
+      <c r="I372" s="6"/>
+    </row>
+    <row r="373" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A373" s="6">
+        <v>31216738</v>
+      </c>
+      <c r="B373" s="6">
+        <v>3</v>
+      </c>
+      <c r="C373" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D373" s="7" t="s">
+        <v>1335</v>
+      </c>
+      <c r="E373" s="8">
+        <v>4.12</v>
+      </c>
+      <c r="F373" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="G373" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H373" s="9" t="s">
+        <v>1346</v>
+      </c>
+      <c r="I373" s="6"/>
+    </row>
+    <row r="374" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A374" s="6">
+        <v>31216738</v>
+      </c>
+      <c r="B374" s="6">
+        <v>4</v>
+      </c>
+      <c r="C374" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="D374" s="7" t="s">
+        <v>1336</v>
+      </c>
+      <c r="E374" s="8">
+        <v>4</v>
+      </c>
+      <c r="F374" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G374" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H374" s="9" t="s">
+        <v>1347</v>
+      </c>
+      <c r="I374" s="6"/>
+    </row>
+    <row r="375" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A375" s="6">
+        <v>31216738</v>
+      </c>
+      <c r="B375" s="6">
+        <v>5</v>
+      </c>
+      <c r="C375" s="7" t="s">
+        <v>1320</v>
+      </c>
+      <c r="D375" s="7" t="s">
+        <v>1337</v>
+      </c>
+      <c r="E375" s="8">
+        <v>3.84</v>
+      </c>
+      <c r="F375" s="8">
+        <v>4</v>
+      </c>
+      <c r="G375" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H375" s="9" t="s">
+        <v>1348</v>
+      </c>
+      <c r="I375" s="6"/>
+    </row>
+    <row r="376" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A376" s="6">
+        <v>31216738</v>
+      </c>
+      <c r="B376" s="6">
+        <v>6</v>
+      </c>
+      <c r="C376" s="7" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D376" s="7" t="s">
+        <v>1338</v>
+      </c>
+      <c r="E376" s="8">
+        <v>4</v>
+      </c>
+      <c r="F376" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="G376" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H376" s="9" t="s">
+        <v>1349</v>
+      </c>
+      <c r="I376" s="6"/>
+    </row>
+    <row r="377" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A377" s="6">
+        <v>31216738</v>
+      </c>
+      <c r="B377" s="6">
+        <v>7</v>
+      </c>
+      <c r="C377" s="7" t="s">
+        <v>1322</v>
+      </c>
+      <c r="D377" s="7" t="s">
+        <v>1339</v>
+      </c>
+      <c r="E377" s="8">
+        <v>4</v>
+      </c>
+      <c r="F377" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G377" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H377" s="9" t="s">
+        <v>1350</v>
+      </c>
+      <c r="I377" s="6"/>
+    </row>
+    <row r="378" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A378" s="6">
+        <v>31216738</v>
+      </c>
+      <c r="B378" s="6">
+        <v>8</v>
+      </c>
+      <c r="C378" s="7" t="s">
+        <v>1323</v>
+      </c>
+      <c r="D378" s="7" t="s">
+        <v>1340</v>
+      </c>
+      <c r="E378" s="8">
+        <v>4</v>
+      </c>
+      <c r="F378" s="8">
+        <v>4</v>
+      </c>
+      <c r="G378" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H378" s="9" t="s">
+        <v>1351</v>
+      </c>
+      <c r="I378" s="6"/>
+    </row>
+    <row r="379" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A379" s="6">
+        <v>31216738</v>
+      </c>
+      <c r="B379" s="6">
+        <v>9</v>
+      </c>
+      <c r="C379" s="7" t="s">
+        <v>1324</v>
+      </c>
+      <c r="D379" s="7" t="s">
+        <v>1341</v>
+      </c>
+      <c r="E379" s="8">
+        <v>4</v>
+      </c>
+      <c r="F379" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G379" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H379" s="9" t="s">
+        <v>1352</v>
+      </c>
+      <c r="I379" s="6"/>
+    </row>
+    <row r="380" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A380" s="6">
+        <v>31216738</v>
+      </c>
+      <c r="B380" s="6">
+        <v>10</v>
+      </c>
+      <c r="C380" s="7" t="s">
+        <v>1325</v>
+      </c>
+      <c r="D380" s="7" t="s">
+        <v>1342</v>
+      </c>
+      <c r="E380" s="8">
+        <v>4</v>
+      </c>
+      <c r="F380" s="8">
+        <v>4</v>
+      </c>
+      <c r="G380" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H380" s="9" t="s">
+        <v>1353</v>
+      </c>
+      <c r="I380" s="6"/>
+    </row>
+    <row r="381" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A381" s="6">
+        <v>31216738</v>
+      </c>
+      <c r="B381" s="6">
+        <v>11</v>
+      </c>
+      <c r="C381" s="7" t="s">
+        <v>1326</v>
+      </c>
+      <c r="D381" s="7" t="s">
+        <v>1343</v>
+      </c>
+      <c r="E381" s="8">
+        <v>3.81</v>
+      </c>
+      <c r="F381" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="G381" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H381" s="9" t="s">
+        <v>1354</v>
+      </c>
+      <c r="I381" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB40DF0E-679A-417A-9D3D-8D213501781C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0386E251-AA9B-415E-BB96-695581B74795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1521" uniqueCount="1355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="1387">
   <si>
     <t>No</t>
   </si>
@@ -4218,9 +4218,6 @@
     <t>Parlor Greens</t>
   </si>
   <si>
-    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το ντεμπούτο άλμπουμ του organ jazz supergroup της Colemine Records. Ηχογράφηση και παραγωγή από τον Leroi Conroy. Mastered από τον Doug Kress. Lacquers cut στα Well Made Music και pressed στα Gotta Groove Records. Κυκλοφορία σε πράσινο βινύλιο με hype sticker.</t>
-  </si>
-  <si>
     <t>Colemine Records – CLMN-12062 / Vinyl, LP, Album, Limited Edition, Green</t>
   </si>
   <si>
@@ -4291,6 +4288,105 @@
   </si>
   <si>
     <t>Η μοναδική διασκευή του δίσκου μεταφέρει το τραγούδι του George Harrison σε gospel-soul οργανικό πλαίσιο. Αντί να προσπαθήσει να αντικαταστήσει το πνευματικό βάρος των στίχων, το Hammond αναλαμβάνει τον μελωδικό και σχεδόν φωνητικό ρόλο, οδηγώντας ένα θερμό, σεβαστικό φινάλε.</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το ντεμπούτο άλμπουμ του organ jazz supergroup της Colemine Records (Tim Carman, Jimmy James, Adam Scone). Παραγωγή από τον Leroi Conroy. Mastered από τον Doug Kress. Lacquers cut στα Well Made Music και pressed στα Gotta Groove Records. Κυκλοφορία σε πράσινο βινύλιο με hype sticker.</t>
+  </si>
+  <si>
+    <t>Paice Ashton Lord</t>
+  </si>
+  <si>
+    <t>Malice In Wonderland</t>
+  </si>
+  <si>
+    <t>Ghost Story</t>
+  </si>
+  <si>
+    <t>Remember The Good Times</t>
+  </si>
+  <si>
+    <t>Silas &amp; Jerome</t>
+  </si>
+  <si>
+    <t>Dance With Me Baby</t>
+  </si>
+  <si>
+    <t>On The Road Again, Again</t>
+  </si>
+  <si>
+    <t>Sneaky Private Lee</t>
+  </si>
+  <si>
+    <t>I'm Gonna Stop Drinking</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/4418939-Paice-Ashton-Lord-Malice-In-Wonderland</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/xwtLvyUV7uE0Z3t6IfGcDlzGg315Sv-jqpJMZpzL8tU/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTQ0MTg5/MzktMTM2NDQyMzg3/NS04OTIzLmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το μοναδικό στούντιο άλμπουμ του βραχύβιου supergroup των Ian Paice, Jon Lord (από τους Deep Purple) και Tony Ashton. Ηχογραφήθηκε στα Musicland Studios του Μονάχου (Σεπτέμβριος-Οκτώβριος 1976). Γαλλική έκδοση της Polydor (Oyster – 2391 269), pressed από την C.I.D.I.S. Mastered στο Master Room με χάραξη από τον BilBo (Denis Blackham). Gatefold εξώφυλλο με πίνακα του Graham Ovenden.</t>
+  </si>
+  <si>
+    <t>Polydor – 2391 269, Oyster – 2391 269 / Vinyl, LP, Album, Stereo, Gatefold, France, 1977</t>
+  </si>
+  <si>
+    <t>Blues Rock, Rhythm &amp; Blues [Jazz Rock, Funk Rock, British Soul Rock]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Rhythm &amp; Blues [Jazz Rock, Organ-led Hard Rock]</t>
+  </si>
+  <si>
+    <t>Σκοτεινό, βαρύ και ατμοσφαιρικό άνοιγμα με τον Jon Lord να δίνει οργανικό βάθος και τον Ian Paice να κρατά ένταση χωρίς υπερβολική επίδειξη. Η αφήγηση της "ιστορίας φαντάσματος" λειτουργεί ως δραματικό πλαίσιο για ένα blues-rock κομμάτι με αρκετή mystique και κινηματογραφική κλιμάκωση.</t>
+  </si>
+  <si>
+    <t>Rhythm &amp; Blues, Blues Rock [Funk Rock, Blue-Eyed Soul]</t>
+  </si>
+  <si>
+    <t>Funky R&amp;B με πλούσιο rhythm section, γήινες κιθάρες και blue-eyed soul φωνητικό ύφος από τον Tony Ashton. Είναι νοσταλγικό χωρίς να γίνεται γλυκανάλατο, η μνήμη των καλών καιρών αντιπαραβάλλεται με την αναπόφευκτη απόσταση που επιβάλλει ο χρόνος.</t>
+  </si>
+  <si>
+    <t>Μελωδικό, piano-led soul-rock τραγούδι. Ο Ashton βρίσκεται στο επίκεντρο με την τραχιά, ανθρώπινη φωνή του, ενώ το Hammond και τα πνευστά δίνουν χρώμα χωρίς να επιβαρύνουν τη μελωδία. Η “Arabella” είναι η απρόσιτη μορφή προς την οποία απευθύνεται ο αφηγητής, αναζητώντας εξήγηση και ανταπόκριση.</t>
+  </si>
+  <si>
+    <t>Ενότητα με πιο jazz-rock λογική, όπου το playing υπερισχύει της συμβατικής pop φόρμας. Η σύνθεση επιτρέπει στα πλήκτρα, στην κιθάρα και στο ρυθμικό δίδυμο Paice–Martinez να αναπτύξουν συνομιλία, με τον τίτλο να δημιουργεί την αίσθηση δύο χαρακτήρων σε μια ιδιόρρυθμη αστική ιστορία.</t>
+  </si>
+  <si>
+    <t>Πιο απλό και εξωστρεφές funk/boogie track, φτιαγμένο για κίνηση και άμεση επικοινωνία. Η μπάντα αποφεύγει τη βαριά prog ανάπτυξη και λειτουργεί σαν R&amp;B revue, με τον Paice να κρατά ελαφρύ αλλά ακριβές groove.</t>
+  </si>
+  <si>
+    <t>Road-song με blues-rock πυρήνα και περιπλανώμενη αίσθηση. Οι στίχοι επαναφέρουν την κούραση αλλά και τη γοητεία της διαδρομής, ενώ η κιθάρα του Marsden και η φωνή του Ashton το κρατούν συνδεδεμένο με την βρετανική pub-rock/soul παράδοση.</t>
+  </si>
+  <si>
+    <t>Μία από τις κορυφές του δίσκου και η πιο ανοιχτά jam-oriented στιγμή του. Σε πάνω από έξι λεπτά, το κομμάτι χτίζεται πάνω σε blues-funk groove και αφήνει χώρο για τα πλήκτρα του Lord και την κιθάρα του Marsden. Ο τίτλος σκιαγραφεί μια πονηρή, αμφίσημη φιγούρα, αλλά η πραγματική ιστορία λέγεται από το interplay της μπάντας.</t>
+  </si>
+  <si>
+    <t>Πικρόγλυκο, χιουμοριστικό piano-R&amp;B κομμάτι που μετατρέπει την υπόσχεση της αποχής σε επαναλαμβανόμενη ανθρώπινη αποτυχία. Ο Ashton παίζει με την αυτοειρωνεία, ενώ η μπάντα προσφέρει στρογγυλό, χορευτικό groove αντί ηθικολογίας.</t>
+  </si>
+  <si>
+    <t>Το μεγάλο, σύνθετο φινάλε. Συνδυάζει blues-rock βάρος, theatrical διάθεση, μεγαλύτερες οργανικές αναπτύξεις και πιο progressive κίνηση στα keyboards. Ο τίτλος αντιστρέφει ειρωνικά το Alice in Wonderland, ο φανταστικός κόσμος δεν είναι αθώος, αλλά γεμάτος παγίδες, καχυποψία και σκοτεινή φαντασία.</t>
+  </si>
+  <si>
+    <t>Blues Rock, Soul [Soul Rock, Piano Rock]</t>
+  </si>
+  <si>
+    <t>Jazz Rock, Blues Rock [Jazz-Blues Rock, Instrumental-leaning Organ Rock]</t>
+  </si>
+  <si>
+    <t>Rhythm &amp; Blues, Funk Rock [Funky R&amp;B, Boogie Rock]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Rhythm &amp; Blues [Road Rock, Soulful Blues Rock]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Jazz Rock [Extended Jam, Organ Blues, Funk Rock]</t>
+  </si>
+  <si>
+    <t>Rhythm &amp; Blues, Blues Rock [Pub Rock, Piano-led R&amp;B]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Jazz Rock [Epic Organ Rock, Progressive Blues Rock]</t>
   </si>
 </sst>
 </file>
@@ -4766,7 +4862,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -6175,19 +6271,51 @@
         <v>3.44</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="G44" s="7" t="s">
+        <v>1354</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>1330</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>1331</v>
       </c>
       <c r="I44" s="11" t="s">
         <v>1328</v>
       </c>
       <c r="J44" s="11" t="s">
         <v>1327</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+      <c r="A45" s="6">
+        <v>4418939</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D45" s="6">
+        <v>1977</v>
+      </c>
+      <c r="E45" s="10">
+        <v>3.55</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G45" s="7" t="s">
+        <v>1366</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>1367</v>
+      </c>
+      <c r="I45" s="11" t="s">
+        <v>1364</v>
+      </c>
+      <c r="J45" s="11" t="s">
+        <v>1365</v>
       </c>
     </row>
   </sheetData>
@@ -6276,6 +6404,8 @@
     <hyperlink ref="I43" r:id="rId82" xr:uid="{A866AB9A-F5F8-4F0F-BEC5-94DAC48A3202}"/>
     <hyperlink ref="J44" r:id="rId83" xr:uid="{FB2A51A6-1F57-4CB7-9467-FEECDE5EA7F8}"/>
     <hyperlink ref="I44" r:id="rId84" xr:uid="{2E158044-3989-4614-A77D-7F99C6C2356D}"/>
+    <hyperlink ref="I45" r:id="rId85" xr:uid="{9EF8A064-D187-433B-89BB-274CB08879EF}"/>
+    <hyperlink ref="J45" r:id="rId86" xr:uid="{EABAADF0-EDBF-4DA8-9418-3D6076A68A9D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6283,7 +6413,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I381"/>
+  <dimension ref="A1:I390"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="3" bestFit="1" customWidth="1"/>
@@ -16369,7 +16499,7 @@
         <v>1316</v>
       </c>
       <c r="D371" s="7" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="E371" s="8">
         <v>4.16</v>
@@ -16381,7 +16511,7 @@
         <v>4.3</v>
       </c>
       <c r="H371" s="9" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="I371" s="6"/>
     </row>
@@ -16396,7 +16526,7 @@
         <v>1317</v>
       </c>
       <c r="D372" s="7" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="E372" s="8">
         <v>4</v>
@@ -16408,7 +16538,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H372" s="9" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="I372" s="6"/>
     </row>
@@ -16423,7 +16553,7 @@
         <v>1318</v>
       </c>
       <c r="D373" s="7" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="E373" s="8">
         <v>4.12</v>
@@ -16435,7 +16565,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H373" s="9" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="I373" s="6"/>
     </row>
@@ -16450,7 +16580,7 @@
         <v>1319</v>
       </c>
       <c r="D374" s="7" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="E374" s="8">
         <v>4</v>
@@ -16462,7 +16592,7 @@
         <v>4.2</v>
       </c>
       <c r="H374" s="9" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="I374" s="6"/>
     </row>
@@ -16477,7 +16607,7 @@
         <v>1320</v>
       </c>
       <c r="D375" s="7" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="E375" s="8">
         <v>3.84</v>
@@ -16489,7 +16619,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H375" s="9" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="I375" s="6"/>
     </row>
@@ -16504,7 +16634,7 @@
         <v>1321</v>
       </c>
       <c r="D376" s="7" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="E376" s="8">
         <v>4</v>
@@ -16516,7 +16646,7 @@
         <v>4.3</v>
       </c>
       <c r="H376" s="9" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="I376" s="6"/>
     </row>
@@ -16531,7 +16661,7 @@
         <v>1322</v>
       </c>
       <c r="D377" s="7" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="E377" s="8">
         <v>4</v>
@@ -16543,7 +16673,7 @@
         <v>4.2</v>
       </c>
       <c r="H377" s="9" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="I377" s="6"/>
     </row>
@@ -16558,7 +16688,7 @@
         <v>1323</v>
       </c>
       <c r="D378" s="7" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="E378" s="8">
         <v>4</v>
@@ -16570,7 +16700,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H378" s="9" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="I378" s="6"/>
     </row>
@@ -16585,7 +16715,7 @@
         <v>1324</v>
       </c>
       <c r="D379" s="7" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="E379" s="8">
         <v>4</v>
@@ -16597,7 +16727,7 @@
         <v>4.2</v>
       </c>
       <c r="H379" s="9" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="I379" s="6"/>
     </row>
@@ -16612,7 +16742,7 @@
         <v>1325</v>
       </c>
       <c r="D380" s="7" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="E380" s="8">
         <v>4</v>
@@ -16624,7 +16754,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H380" s="9" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="I380" s="6"/>
     </row>
@@ -16639,7 +16769,7 @@
         <v>1326</v>
       </c>
       <c r="D381" s="7" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="E381" s="8">
         <v>3.81</v>
@@ -16651,9 +16781,254 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H381" s="9" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="I381" s="6"/>
+    </row>
+    <row r="382" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A382" s="6">
+        <v>4418939</v>
+      </c>
+      <c r="B382" s="6">
+        <v>1</v>
+      </c>
+      <c r="C382" s="7" t="s">
+        <v>1357</v>
+      </c>
+      <c r="D382" s="7" t="s">
+        <v>1369</v>
+      </c>
+      <c r="E382" s="8">
+        <v>3.61</v>
+      </c>
+      <c r="F382" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G382" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H382" s="9" t="s">
+        <v>1370</v>
+      </c>
+      <c r="I382" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="383" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A383" s="6">
+        <v>4418939</v>
+      </c>
+      <c r="B383" s="6">
+        <v>2</v>
+      </c>
+      <c r="C383" s="7" t="s">
+        <v>1358</v>
+      </c>
+      <c r="D383" s="7" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E383" s="8">
+        <v>3.74</v>
+      </c>
+      <c r="F383" s="8">
+        <v>4</v>
+      </c>
+      <c r="G383" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H383" s="9" t="s">
+        <v>1372</v>
+      </c>
+      <c r="I383" s="6"/>
+    </row>
+    <row r="384" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A384" s="6">
+        <v>4418939</v>
+      </c>
+      <c r="B384" s="6">
+        <v>3</v>
+      </c>
+      <c r="C384" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="D384" s="7" t="s">
+        <v>1380</v>
+      </c>
+      <c r="E384" s="8">
+        <v>3.35</v>
+      </c>
+      <c r="F384" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="G384" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="H384" s="9" t="s">
+        <v>1373</v>
+      </c>
+      <c r="I384" s="6"/>
+    </row>
+    <row r="385" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A385" s="6">
+        <v>4418939</v>
+      </c>
+      <c r="B385" s="6">
+        <v>4</v>
+      </c>
+      <c r="C385" s="7" t="s">
+        <v>1359</v>
+      </c>
+      <c r="D385" s="7" t="s">
+        <v>1381</v>
+      </c>
+      <c r="E385" s="8">
+        <v>3.25</v>
+      </c>
+      <c r="F385" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="G385" s="12">
+        <v>4</v>
+      </c>
+      <c r="H385" s="9" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I385" s="6"/>
+    </row>
+    <row r="386" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A386" s="6">
+        <v>4418939</v>
+      </c>
+      <c r="B386" s="6">
+        <v>5</v>
+      </c>
+      <c r="C386" s="7" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D386" s="7" t="s">
+        <v>1382</v>
+      </c>
+      <c r="E386" s="8">
+        <v>3.12</v>
+      </c>
+      <c r="F386" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="G386" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="H386" s="9" t="s">
+        <v>1375</v>
+      </c>
+      <c r="I386" s="6"/>
+    </row>
+    <row r="387" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A387" s="6">
+        <v>4418939</v>
+      </c>
+      <c r="B387" s="6">
+        <v>6</v>
+      </c>
+      <c r="C387" s="7" t="s">
+        <v>1361</v>
+      </c>
+      <c r="D387" s="7" t="s">
+        <v>1383</v>
+      </c>
+      <c r="E387" s="8">
+        <v>3.21</v>
+      </c>
+      <c r="F387" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="G387" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="H387" s="9" t="s">
+        <v>1376</v>
+      </c>
+      <c r="I387" s="6"/>
+    </row>
+    <row r="388" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A388" s="6">
+        <v>4418939</v>
+      </c>
+      <c r="B388" s="6">
+        <v>7</v>
+      </c>
+      <c r="C388" s="7" t="s">
+        <v>1362</v>
+      </c>
+      <c r="D388" s="7" t="s">
+        <v>1384</v>
+      </c>
+      <c r="E388" s="8">
+        <v>3.21</v>
+      </c>
+      <c r="F388" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G388" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H388" s="9" t="s">
+        <v>1377</v>
+      </c>
+      <c r="I388" s="6"/>
+    </row>
+    <row r="389" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A389" s="6">
+        <v>4418939</v>
+      </c>
+      <c r="B389" s="6">
+        <v>8</v>
+      </c>
+      <c r="C389" s="7" t="s">
+        <v>1363</v>
+      </c>
+      <c r="D389" s="7" t="s">
+        <v>1385</v>
+      </c>
+      <c r="E389" s="8">
+        <v>3.25</v>
+      </c>
+      <c r="F389" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="G389" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="H389" s="9" t="s">
+        <v>1378</v>
+      </c>
+      <c r="I389" s="6"/>
+    </row>
+    <row r="390" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A390" s="6">
+        <v>4418939</v>
+      </c>
+      <c r="B390" s="6">
+        <v>9</v>
+      </c>
+      <c r="C390" s="7" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D390" s="7" t="s">
+        <v>1386</v>
+      </c>
+      <c r="E390" s="8">
+        <v>3.39</v>
+      </c>
+      <c r="F390" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="G390" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H390" s="9" t="s">
+        <v>1379</v>
+      </c>
+      <c r="I390" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0386E251-AA9B-415E-BB96-695581B74795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C6D0130-2461-4C12-97FB-03A292251978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4326,9 +4326,6 @@
     <t>https://i.discogs.com/xwtLvyUV7uE0Z3t6IfGcDlzGg315Sv-jqpJMZpzL8tU/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTQ0MTg5/MzktMTM2NDQyMzg3/NS04OTIzLmpwZWc.jpeg</t>
   </si>
   <si>
-    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το μοναδικό στούντιο άλμπουμ του βραχύβιου supergroup των Ian Paice, Jon Lord (από τους Deep Purple) και Tony Ashton. Ηχογραφήθηκε στα Musicland Studios του Μονάχου (Σεπτέμβριος-Οκτώβριος 1976). Γαλλική έκδοση της Polydor (Oyster – 2391 269), pressed από την C.I.D.I.S. Mastered στο Master Room με χάραξη από τον BilBo (Denis Blackham). Gatefold εξώφυλλο με πίνακα του Graham Ovenden.</t>
-  </si>
-  <si>
     <t>Polydor – 2391 269, Oyster – 2391 269 / Vinyl, LP, Album, Stereo, Gatefold, France, 1977</t>
   </si>
   <si>
@@ -4387,6 +4384,9 @@
   </si>
   <si>
     <t>Blues Rock, Jazz Rock [Epic Organ Rock, Progressive Blues Rock]</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το μοναδικό στούντιο άλμπουμ του supergroup των Ian Paice, Jon Lord και Tony Ashton. Ηχογραφήθηκε στα Musicland Studios του Μονάχου (Σεπτέμβριος-Οκτώβριος 1976). Γαλλική έκδοση της Polydor (Oyster – 2391 269), pressed από την C.I.D.I.S. Mastered στο Master Room με χάραξη από τον BilBo (Denis Blackham). Gatefold εξώφυλλο με πίνακα του Graham Ovenden. **Special Feature:** Φέρει χαραγμένη/ανάγλυφη την προσωπική υπογραφή του Tony Ashton πάνω στην πορτοκαλί ετικέτα της Oyster, καθώς και τυπογραφική παράλειψη (λείπει το δεύτερο "Again" στον τίτλο του A1/B1).</t>
   </si>
 </sst>
 </file>
@@ -6286,7 +6286,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>4418939</v>
       </c>
@@ -6303,13 +6303,13 @@
         <v>3.55</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="G45" s="7" t="s">
+        <v>1386</v>
+      </c>
+      <c r="H45" s="6" t="s">
         <v>1366</v>
-      </c>
-      <c r="H45" s="6" t="s">
-        <v>1367</v>
       </c>
       <c r="I45" s="11" t="s">
         <v>1364</v>
@@ -16796,7 +16796,7 @@
         <v>1357</v>
       </c>
       <c r="D382" s="7" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="E382" s="8">
         <v>3.61</v>
@@ -16808,7 +16808,7 @@
         <v>4.2</v>
       </c>
       <c r="H382" s="9" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="I382" s="6" t="s">
         <v>312</v>
@@ -16825,7 +16825,7 @@
         <v>1358</v>
       </c>
       <c r="D383" s="7" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="E383" s="8">
         <v>3.74</v>
@@ -16837,7 +16837,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H383" s="9" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="I383" s="6"/>
     </row>
@@ -16852,7 +16852,7 @@
         <v>324</v>
       </c>
       <c r="D384" s="7" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="E384" s="8">
         <v>3.35</v>
@@ -16864,7 +16864,7 @@
         <v>3.9</v>
       </c>
       <c r="H384" s="9" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="I384" s="6"/>
     </row>
@@ -16879,7 +16879,7 @@
         <v>1359</v>
       </c>
       <c r="D385" s="7" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="E385" s="8">
         <v>3.25</v>
@@ -16891,7 +16891,7 @@
         <v>4</v>
       </c>
       <c r="H385" s="9" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="I385" s="6"/>
     </row>
@@ -16906,7 +16906,7 @@
         <v>1360</v>
       </c>
       <c r="D386" s="7" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="E386" s="8">
         <v>3.12</v>
@@ -16918,7 +16918,7 @@
         <v>3.7</v>
       </c>
       <c r="H386" s="9" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="I386" s="6"/>
     </row>
@@ -16933,7 +16933,7 @@
         <v>1361</v>
       </c>
       <c r="D387" s="7" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="E387" s="8">
         <v>3.21</v>
@@ -16945,7 +16945,7 @@
         <v>3.8</v>
       </c>
       <c r="H387" s="9" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="I387" s="6"/>
     </row>
@@ -16960,7 +16960,7 @@
         <v>1362</v>
       </c>
       <c r="D388" s="7" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="E388" s="8">
         <v>3.21</v>
@@ -16972,7 +16972,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H388" s="9" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="I388" s="6"/>
     </row>
@@ -16987,7 +16987,7 @@
         <v>1363</v>
       </c>
       <c r="D389" s="7" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="E389" s="8">
         <v>3.25</v>
@@ -16999,7 +16999,7 @@
         <v>3.9</v>
       </c>
       <c r="H389" s="9" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="I389" s="6"/>
     </row>
@@ -17014,7 +17014,7 @@
         <v>1356</v>
       </c>
       <c r="D390" s="7" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="E390" s="8">
         <v>3.39</v>
@@ -17026,7 +17026,7 @@
         <v>4.3</v>
       </c>
       <c r="H390" s="9" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="I390" s="6"/>
     </row>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C6D0130-2461-4C12-97FB-03A292251978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{547CD7C8-C5D8-4058-B955-F3D1275E9C09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="1387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1590" uniqueCount="1421">
   <si>
     <t>No</t>
   </si>
@@ -4387,6 +4387,108 @@
   </si>
   <si>
     <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το μοναδικό στούντιο άλμπουμ του supergroup των Ian Paice, Jon Lord και Tony Ashton. Ηχογραφήθηκε στα Musicland Studios του Μονάχου (Σεπτέμβριος-Οκτώβριος 1976). Γαλλική έκδοση της Polydor (Oyster – 2391 269), pressed από την C.I.D.I.S. Mastered στο Master Room με χάραξη από τον BilBo (Denis Blackham). Gatefold εξώφυλλο με πίνακα του Graham Ovenden. **Special Feature:** Φέρει χαραγμένη/ανάγλυφη την προσωπική υπογραφή του Tony Ashton πάνω στην πορτοκαλί ετικέτα της Oyster, καθώς και τυπογραφική παράλειψη (λείπει το δεύτερο "Again" στον τίτλο του A1/B1).</t>
+  </si>
+  <si>
+    <t>Orions Belte</t>
+  </si>
+  <si>
+    <t>Mint</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/gJzEMp8d2Sd88ZJiGfZsvJzkG5kc_vtk0IAobLAR-mY/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI2OTA5/Njc4LTE2ODI2ODY2/OTktMjcxNy5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/26909678-Orions-Belte-Mint</t>
+  </si>
+  <si>
+    <t>New Years Eve #2</t>
+  </si>
+  <si>
+    <t>Papillon</t>
+  </si>
+  <si>
+    <t>Delmonte</t>
+  </si>
+  <si>
+    <t>Joe Frazier</t>
+  </si>
+  <si>
+    <t>Moving Back Again</t>
+  </si>
+  <si>
+    <t>Le Mans</t>
+  </si>
+  <si>
+    <t>Picturephone Blues</t>
+  </si>
+  <si>
+    <t>Atlantic Surfing</t>
+  </si>
+  <si>
+    <t>Alnitak</t>
+  </si>
+  <si>
+    <t>Psychedelic Rock, Instrumental Rock [Krautrock-Blues, Surf Rock, Cosmic Americana]</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Ευρωπαϊκή επανέκδοση του 2023 σε κίτρινο διαφανές βινύλιο (Yellow Transparent) από την Jansen Records (JANSEN101LP). Direct Metal Mastering (DMM) από τον H.P. στα Pauler Acoustics, pressed στη Γερμανία από την Schallplattenfabrik Pallas GmbH. Περιέχει την τρυφερή σημείωση στο οπισθόφυλλο: "Since we’re family guys we would like to share our love and devotion to our ladies and kids."</t>
+  </si>
+  <si>
+    <t>Jansen Records – JANSEN101LP / Vinyl, LP, Album, Reissue, Repress, Yellow Transparent, Europe, 2023</t>
+  </si>
+  <si>
+    <t>Psychedelic Rock, Instrumental Rock [Cosmic Surf, Desert Rock (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Ambient, Psychedelic Rock [Cosmic Ambient, Post-Rock Epilogue (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Psychedelic Rock, Blues Rock [Dreamy Psych Rock, Cosmic Americana]</t>
+  </si>
+  <si>
+    <t>Instrumental Rock, Ambient [Guitar Interlude, Cinematic Soundscape (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Psychedelic Rock, Blues Rock [Krautrock-Blues, Heavy Instrumental Jam (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Psychedelic Rock, Instrumental Rock [Cosmic Americana, Motorik Psych (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Instrumental Rock, Jazz Rock [Downtempo Groove, Cinematic Jazz-Psych (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Psychedelic Rock [Twangy Psych Blues, Desert Rock (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Psychedelic Rock, Surf Rock [Space Surf, Krautrock, Extended Jam (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Ανοίγει τον δίσκο με σιωπηλή ένταση και μια χλωμή, νυχτερινή κιθαριστική μελωδία. Το κομμάτι δίνει την αίσθηση μιας πόλης μετά τα μεσάνυχτα, όπου η γιορτινή ενέργεια έχει ήδη φύγει και μένει μόνο η αναμονή ενός νέου ξεκινήματος.</t>
+  </si>
+  <si>
+    <t>Πιο ανοιχτό και αέρινο, βασίζεται σε λεπτές κιθάρες και ήπια rhythm section. Ο τίτλος παραπέμπει σε κίνηση και ελαφρότητα, ενώ η μουσική αναπτύσσεται σαν αργή πτήση πάνω από ένα ζεστό, ψυχεδελικό τοπίο.</t>
+  </si>
+  <si>
+    <t>Μικρό, κινηματογραφικό interlude. Δουλεύει με ηχητικά χρώματα και λιτές κιθαριστικές χειρονομίες, σαν σύντομο cutaway σε ταινία δρόμου πριν η αφήγηση επιστρέψει στην κύρια ένταση.</t>
+  </si>
+  <si>
+    <t>Το πιο βαρύ και δραματικό track της πρώτης πλευράς. Η έμπνευση από τον αγώνα Frazier–Ali του 1971 δίνει στο κομμάτι μια αίσθηση ιδρώτα, πίεσης και σωματικής σύγκρουσης. Το bluesy riffing και η επίμονη ρυθμική κίνηση μετατρέπουν το θέμα σε σχεδόν κινηματογραφικό pugilist jam.</t>
+  </si>
+  <si>
+    <t>Αργόσυρτο, motorik-επηρεασμένο groove με μια μελωδία που μοιάζει να κοιτά προς τα πίσω. Η «επιστροφή» του τίτλου αποδίδεται μουσικά ως κύκλος: το trio επαναλαμβάνει μικρές ιδέες μέχρι αυτές να αποκτήσουν νοσταλγικό βάρος.</t>
+  </si>
+  <si>
+    <t>Από τις πιο κομψές συνθέσεις του άλμπουμ. Τα retro drums, οι reverb-heavy jazz κιθάρες και το χαλαρό tempo θυμίζουν μια νυχτερινή βόλτα με αυτοκίνητο περισσότερο παρά αγώνα ταχύτητας. Είναι ένα μοντέρνο downtempo instrumental με παλιάς κοπής lounge/soundtrack ευαισθησία.</t>
+  </si>
+  <si>
+    <t>Επιστροφή στο twang και το blues, με πιο φωτεινό αλλά ελαφρώς απομονωμένο χαρακτήρα. Η κιθάρα ακούγεται σαν να μεταδίδεται μέσα από παλιό τηλεφωνικό δίκτυο, ενώ η μπάντα χτίζει ένα restrained desert-blues κλίμα.</t>
+  </si>
+  <si>
+    <t>Η μεγάλη κορύφωση του δίσκου. Στα επτάμισι λεπτά, οι Orions Belte αξιοποιούν την υπομονή του krautrock, το surf tremolo και τη space-rock ατμόσφαιρα για να δημιουργήσουν ένα αργό κύμα έντασης. Δεν επιδιώκει θεαματική κορύφωση· η δύναμή του βρίσκεται στην παρατεταμένη αιώρηση.</t>
+  </si>
+  <si>
+    <t>Σύντομος και μοναχικός επίλογος, ονομασμένος από αστέρι στη ζώνη του Ωρίωνα. Η μουσική αφήνει την αίσθηση ότι η προηγούμενη θαλάσσια διαδρομή απομακρύνεται και γίνεται κοσμική, κλείνοντας το άλμπουμ με σιωπηλή, ambient μελαγχολία.</t>
   </si>
 </sst>
 </file>
@@ -4862,7 +4964,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -6316,6 +6418,38 @@
       </c>
       <c r="J45" s="11" t="s">
         <v>1365</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A46" s="6">
+        <v>26909678</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>1388</v>
+      </c>
+      <c r="D46" s="6">
+        <v>2018</v>
+      </c>
+      <c r="E46" s="10">
+        <v>3.24</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>1400</v>
+      </c>
+      <c r="G46" s="7" t="s">
+        <v>1401</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>1402</v>
+      </c>
+      <c r="I46" s="11" t="s">
+        <v>1390</v>
+      </c>
+      <c r="J46" s="11" t="s">
+        <v>1389</v>
       </c>
     </row>
   </sheetData>
@@ -6406,6 +6540,8 @@
     <hyperlink ref="I44" r:id="rId84" xr:uid="{2E158044-3989-4614-A77D-7F99C6C2356D}"/>
     <hyperlink ref="I45" r:id="rId85" xr:uid="{9EF8A064-D187-433B-89BB-274CB08879EF}"/>
     <hyperlink ref="J45" r:id="rId86" xr:uid="{EABAADF0-EDBF-4DA8-9418-3D6076A68A9D}"/>
+    <hyperlink ref="J46" r:id="rId87" xr:uid="{398D0B82-5507-4F19-8987-F81B81EABEEA}"/>
+    <hyperlink ref="I46" r:id="rId88" xr:uid="{CD08D7F6-9889-458F-B1D7-B11EC371B1DB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6413,7 +6549,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I390"/>
+  <dimension ref="A1:I399"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="3" bestFit="1" customWidth="1"/>
@@ -17030,6 +17166,249 @@
       </c>
       <c r="I390" s="6"/>
     </row>
+    <row r="391" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A391" s="6">
+        <v>26909678</v>
+      </c>
+      <c r="B391" s="6">
+        <v>1</v>
+      </c>
+      <c r="C391" s="7" t="s">
+        <v>1391</v>
+      </c>
+      <c r="D391" s="7" t="s">
+        <v>1403</v>
+      </c>
+      <c r="E391" s="8">
+        <v>3.67</v>
+      </c>
+      <c r="F391" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G391" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H391" s="9" t="s">
+        <v>1412</v>
+      </c>
+      <c r="I391" s="6"/>
+    </row>
+    <row r="392" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A392" s="6">
+        <v>26909678</v>
+      </c>
+      <c r="B392" s="6">
+        <v>2</v>
+      </c>
+      <c r="C392" s="7" t="s">
+        <v>1392</v>
+      </c>
+      <c r="D392" s="7" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E392" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="F392" s="8">
+        <v>4</v>
+      </c>
+      <c r="G392" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H392" s="9" t="s">
+        <v>1413</v>
+      </c>
+      <c r="I392" s="6"/>
+    </row>
+    <row r="393" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A393" s="6">
+        <v>26909678</v>
+      </c>
+      <c r="B393" s="6">
+        <v>3</v>
+      </c>
+      <c r="C393" s="7" t="s">
+        <v>1393</v>
+      </c>
+      <c r="D393" s="7" t="s">
+        <v>1406</v>
+      </c>
+      <c r="E393" s="8">
+        <v>3.17</v>
+      </c>
+      <c r="F393" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="G393" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="H393" s="9" t="s">
+        <v>1414</v>
+      </c>
+      <c r="I393" s="6"/>
+    </row>
+    <row r="394" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A394" s="6">
+        <v>26909678</v>
+      </c>
+      <c r="B394" s="6">
+        <v>4</v>
+      </c>
+      <c r="C394" s="7" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D394" s="7" t="s">
+        <v>1407</v>
+      </c>
+      <c r="E394" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="F394" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="G394" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H394" s="9" t="s">
+        <v>1415</v>
+      </c>
+      <c r="I394" s="6"/>
+    </row>
+    <row r="395" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A395" s="6">
+        <v>26909678</v>
+      </c>
+      <c r="B395" s="6">
+        <v>5</v>
+      </c>
+      <c r="C395" s="7" t="s">
+        <v>1395</v>
+      </c>
+      <c r="D395" s="7" t="s">
+        <v>1408</v>
+      </c>
+      <c r="E395" s="8">
+        <v>3.33</v>
+      </c>
+      <c r="F395" s="8">
+        <v>4</v>
+      </c>
+      <c r="G395" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H395" s="9" t="s">
+        <v>1416</v>
+      </c>
+      <c r="I395" s="6"/>
+    </row>
+    <row r="396" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A396" s="6">
+        <v>26909678</v>
+      </c>
+      <c r="B396" s="6">
+        <v>6</v>
+      </c>
+      <c r="C396" s="7" t="s">
+        <v>1396</v>
+      </c>
+      <c r="D396" s="7" t="s">
+        <v>1409</v>
+      </c>
+      <c r="E396" s="8">
+        <v>3.83</v>
+      </c>
+      <c r="F396" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="G396" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H396" s="9" t="s">
+        <v>1417</v>
+      </c>
+      <c r="I396" s="6"/>
+    </row>
+    <row r="397" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A397" s="6">
+        <v>26909678</v>
+      </c>
+      <c r="B397" s="6">
+        <v>7</v>
+      </c>
+      <c r="C397" s="7" t="s">
+        <v>1397</v>
+      </c>
+      <c r="D397" s="7" t="s">
+        <v>1410</v>
+      </c>
+      <c r="E397" s="8">
+        <v>3.67</v>
+      </c>
+      <c r="F397" s="8">
+        <v>4</v>
+      </c>
+      <c r="G397" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H397" s="9" t="s">
+        <v>1418</v>
+      </c>
+      <c r="I397" s="6"/>
+    </row>
+    <row r="398" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A398" s="6">
+        <v>26909678</v>
+      </c>
+      <c r="B398" s="6">
+        <v>8</v>
+      </c>
+      <c r="C398" s="7" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D398" s="7" t="s">
+        <v>1411</v>
+      </c>
+      <c r="E398" s="8">
+        <v>3.83</v>
+      </c>
+      <c r="F398" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="G398" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H398" s="9" t="s">
+        <v>1419</v>
+      </c>
+      <c r="I398" s="6"/>
+    </row>
+    <row r="399" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A399" s="6">
+        <v>26909678</v>
+      </c>
+      <c r="B399" s="6">
+        <v>9</v>
+      </c>
+      <c r="C399" s="7" t="s">
+        <v>1399</v>
+      </c>
+      <c r="D399" s="7" t="s">
+        <v>1404</v>
+      </c>
+      <c r="E399" s="8">
+        <v>3.33</v>
+      </c>
+      <c r="F399" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G399" s="12">
+        <v>4</v>
+      </c>
+      <c r="H399" s="9" t="s">
+        <v>1420</v>
+      </c>
+      <c r="I399" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{547CD7C8-C5D8-4058-B955-F3D1275E9C09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{334F36AD-9FF2-4015-B24F-6F18BB3AEDBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1590" uniqueCount="1421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1624" uniqueCount="1455">
   <si>
     <t>No</t>
   </si>
@@ -4489,6 +4489,108 @@
   </si>
   <si>
     <t>Σύντομος και μοναχικός επίλογος, ονομασμένος από αστέρι στη ζώνη του Ωρίωνα. Η μουσική αφήνει την αίσθηση ότι η προηγούμενη θαλάσσια διαδρομή απομακρύνεται και γίνεται κοσμική, κλείνοντας το άλμπουμ με σιωπηλή, ambient μελαγχολία.</t>
+  </si>
+  <si>
+    <t>Orgōne</t>
+  </si>
+  <si>
+    <t>Chimera</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/tR1l6vZefdo45-3Jctm5hUcYdzNkFACOGtBM7p6p-d0/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI5NzA0/NTYxLTE3MDg2ODI2/NzctNzQyMS5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/29704561-Org%C5%8Dne-Chimera</t>
+  </si>
+  <si>
+    <t>Hallowed Dreams</t>
+  </si>
+  <si>
+    <t>Lies And Games</t>
+  </si>
+  <si>
+    <t>Basilisk</t>
+  </si>
+  <si>
+    <t>Peace For You</t>
+  </si>
+  <si>
+    <t>Parasols</t>
+  </si>
+  <si>
+    <t>Zum Zum</t>
+  </si>
+  <si>
+    <t>Running Low</t>
+  </si>
+  <si>
+    <t>The Husk</t>
+  </si>
+  <si>
+    <t>Tula Muisi (Dance Like Them)</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Κυκλοφορία του 2024 από τη 3 Palm Records (TPR-013) σε περιορισμένο κίτρινο αδιαφανές βινύλιο (Opaque Yellow). Ηχογραφήθηκε από τον Sergio Rios στα Killonsound Studios στο North Hollywood της Καλιφόρνια. Το mastering έγινε από τον θρυλικό JJ Golden στα Golden Mastering (Ventura, CA), διασφαλίζοντας κορυφαία αναλογική ζεστασιά και δυναμικό εύρος.</t>
+  </si>
+  <si>
+    <t>3 Palm Records – TPR-013 / Vinyl, LP, Album, Limited Edition, Stereo, Yellow Opaque, US, Feb 2, 2024</t>
+  </si>
+  <si>
+    <t>Funk, Soul [Afrobeat, Psychedelic Soul, Instrumental Funk]</t>
+  </si>
+  <si>
+    <t>Instrumental Funk, Psychedelic Rock [Afro-Psych, Dub-Funk, Cinematic Instrumental (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Soul, Funk [Modern Soul, Psychedelic Soul]</t>
+  </si>
+  <si>
+    <t>Instrumental Funk, Afrobeat [Afro-Funk, Psychedelic Funk (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Soul, Rhythm &amp; Blues [Deep Soul, Spiritual Soul]</t>
+  </si>
+  <si>
+    <t>Funk, Rhythm &amp; Blues [New Orleans Funk, Second-Line Groove]</t>
+  </si>
+  <si>
+    <t>Afrobeat, Funk [Afro-Funk, Dancefloor Funk]</t>
+  </si>
+  <si>
+    <t>Soul, Funk [Soul-Funk, West Coast Funk]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Psychedelic Rock, Instrumental Funk [Psychedelic Funk, Dub Rock, Extended Jam (Instrumental)]	</t>
+  </si>
+  <si>
+    <t>Afrobeat, Funk [Congolese Funk, Afro-Psych, Dance Groove]</t>
+  </si>
+  <si>
+    <t>Εισαγωγικό instrumental με spacey keys, boom-bap influenced drums, πνευστά και αργές αλλαγές ύφους. Λειτουργεί σαν μικρή χαρτογράφηση του άλμπουμ: Afrobeat παλμός, ψυχεδελική κιθάρα, dub διάθεση και funk ενορχηστρωτική πυκνότητα συνυπάρχουν χωρίς να ακολουθούν αυστηρή ποπ φόρμα.</t>
+  </si>
+  <si>
+    <t>Soul-funk τραγούδι με φωνητικά της Terin Ector και στιχουργικό πυρήνα τις ψευδαισθήσεις, τους χειρισμούς και τη συναισθηματική αβεβαιότητα μιας σχέσης. Το groove είναι σφιχτό, όμως η παραγωγή αφήνει χώρο στις φωνές και στις κιθάρες να δημιουργήσουν ψυχεδελικό βάθος.</t>
+  </si>
+  <si>
+    <t>Instrumental Afro-funk με ορμητικά κρουστά, βρώμικο μπάσο και κιθάρες που κινούνται ανάμεσα σε wah-funk και desert psych. Ο μυθολογικός τίτλος ταιριάζει στην ελαφρώς απειλητική, ερπετική κίνηση του riff.</t>
+  </si>
+  <si>
+    <t>Αργό, πνευματικό deep-soul κομμάτι, με τη φωνή της Ector να αναζητά ηρεμία και συναισθηματική αποκατάσταση. Η διαφορετική μίξη του Benjamin Spitzmueller δίνει πιο ανοιχτό χώρο στη φωνή και τονίζει τη λεπτομέρεια των keys και των πνευστών.</t>
+  </si>
+  <si>
+    <t>Φωτεινό, χορευτικό New Orleans funk, με second-line ελαστικότητα στα τύμπανα και πνευστά που απαντούν στα κιθαριστικά stabs. Είναι ένα από τα πιο άμεσα, σωματικά tracks του άλμπουμ και σκόπιμη αναφορά στις μουσικές ρίζες της αμερικανικής funk παράδοσης.</t>
+  </si>
+  <si>
+    <t>Από τις κεντρικές κορυφές του δίσκου. Το Afro-funk dance groove, τα φωνητικά του Mermans Mosengo και οι επαναληπτικές κιθαριστικές/κρουστικές γραμμές δημιουργούν κομμάτι φτιαγμένο για κίνηση χωρίς να καταφεύγει σε απλό revivalism.</t>
+  </si>
+  <si>
+    <t>Funk-soul σύνθεση με τον Jamie Allensworth στα φωνητικά, πιο άμεση και τραχιά από τα κομμάτια της Ector. Η φωνητική ερμηνεία μεταφέρει εξάντληση, ανάγκη και επιμονή, πάνω σε ένα West Coast groove που παραμένει σταθερά γειωμένο.</t>
+  </si>
+  <si>
+    <t>Μεγάλο instrumental ταξίδι, σχεδόν dub-psych suite. Οι Orgōne μειώνουν την ταχύτητα και δίνουν χώρο σε echo, distortion, πνευστά και σταδιακά χτισίματα. Ο τίτλος παραπέμπει σε ένα άδειο περίβλημα· η μουσική αντίθετα είναι γεμάτη μικρές υφές και ελεγχόμενη ένταση.</t>
+  </si>
+  <si>
+    <t>Επιστρέφει στο αφρικανικό στοιχείο με Mermans Mosengo σε φωνητική/ρυθμική καθοδήγηση. Το κομμάτι είναι γιορτινό, πολυρυθμικό και συλλογικό, αποφεύγοντας τη δυτική «εξωτικοποίηση» επειδή η συνεργασία είναι πραγματικά ενσωματωμένη στην ενορχήστρωση και όχι διακοσμητική.</t>
   </si>
 </sst>
 </file>
@@ -4964,7 +5066,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -6450,6 +6552,38 @@
       </c>
       <c r="J46" s="11" t="s">
         <v>1389</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A47" s="6">
+        <v>29704561</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>1421</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>1422</v>
+      </c>
+      <c r="D47" s="6">
+        <v>2024</v>
+      </c>
+      <c r="E47" s="10">
+        <v>3.25</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>1436</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>1434</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>1435</v>
+      </c>
+      <c r="I47" s="11" t="s">
+        <v>1424</v>
+      </c>
+      <c r="J47" s="11" t="s">
+        <v>1423</v>
       </c>
     </row>
   </sheetData>
@@ -6542,6 +6676,8 @@
     <hyperlink ref="J45" r:id="rId86" xr:uid="{EABAADF0-EDBF-4DA8-9418-3D6076A68A9D}"/>
     <hyperlink ref="J46" r:id="rId87" xr:uid="{398D0B82-5507-4F19-8987-F81B81EABEEA}"/>
     <hyperlink ref="I46" r:id="rId88" xr:uid="{CD08D7F6-9889-458F-B1D7-B11EC371B1DB}"/>
+    <hyperlink ref="J47" r:id="rId89" xr:uid="{F8E2C3AC-0723-47E2-B70F-5BE2142A8C3F}"/>
+    <hyperlink ref="I47" r:id="rId90" xr:uid="{3F7A8B1D-1B9A-44F4-AFFC-EB39B6A43F6E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6549,7 +6685,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I399"/>
+  <dimension ref="A1:I408"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="3" bestFit="1" customWidth="1"/>
@@ -17409,6 +17545,249 @@
       </c>
       <c r="I399" s="6"/>
     </row>
+    <row r="400" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A400" s="6">
+        <v>29704561</v>
+      </c>
+      <c r="B400" s="6">
+        <v>1</v>
+      </c>
+      <c r="C400" s="7" t="s">
+        <v>1425</v>
+      </c>
+      <c r="D400" s="7" t="s">
+        <v>1437</v>
+      </c>
+      <c r="E400" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="F400" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G400" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H400" s="9" t="s">
+        <v>1446</v>
+      </c>
+      <c r="I400" s="6"/>
+    </row>
+    <row r="401" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A401" s="6">
+        <v>29704561</v>
+      </c>
+      <c r="B401" s="6">
+        <v>2</v>
+      </c>
+      <c r="C401" s="7" t="s">
+        <v>1426</v>
+      </c>
+      <c r="D401" s="7" t="s">
+        <v>1438</v>
+      </c>
+      <c r="E401" s="8">
+        <v>4</v>
+      </c>
+      <c r="F401" s="8">
+        <v>4</v>
+      </c>
+      <c r="G401" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H401" s="9" t="s">
+        <v>1447</v>
+      </c>
+      <c r="I401" s="6"/>
+    </row>
+    <row r="402" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A402" s="6">
+        <v>29704561</v>
+      </c>
+      <c r="B402" s="6">
+        <v>3</v>
+      </c>
+      <c r="C402" s="7" t="s">
+        <v>1427</v>
+      </c>
+      <c r="D402" s="7" t="s">
+        <v>1439</v>
+      </c>
+      <c r="E402" s="8">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="F402" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="G402" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H402" s="9" t="s">
+        <v>1448</v>
+      </c>
+      <c r="I402" s="6"/>
+    </row>
+    <row r="403" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A403" s="6">
+        <v>29704561</v>
+      </c>
+      <c r="B403" s="6">
+        <v>4</v>
+      </c>
+      <c r="C403" s="7" t="s">
+        <v>1428</v>
+      </c>
+      <c r="D403" s="7" t="s">
+        <v>1440</v>
+      </c>
+      <c r="E403" s="8">
+        <v>4</v>
+      </c>
+      <c r="F403" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G403" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H403" s="9" t="s">
+        <v>1449</v>
+      </c>
+      <c r="I403" s="6"/>
+    </row>
+    <row r="404" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A404" s="6">
+        <v>29704561</v>
+      </c>
+      <c r="B404" s="6">
+        <v>5</v>
+      </c>
+      <c r="C404" s="7" t="s">
+        <v>1429</v>
+      </c>
+      <c r="D404" s="7" t="s">
+        <v>1441</v>
+      </c>
+      <c r="E404" s="8">
+        <v>3.33</v>
+      </c>
+      <c r="F404" s="8">
+        <v>4</v>
+      </c>
+      <c r="G404" s="12">
+        <v>4</v>
+      </c>
+      <c r="H404" s="9" t="s">
+        <v>1450</v>
+      </c>
+      <c r="I404" s="6"/>
+    </row>
+    <row r="405" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A405" s="6">
+        <v>29704561</v>
+      </c>
+      <c r="B405" s="6">
+        <v>6</v>
+      </c>
+      <c r="C405" s="7" t="s">
+        <v>1430</v>
+      </c>
+      <c r="D405" s="7" t="s">
+        <v>1442</v>
+      </c>
+      <c r="E405" s="8">
+        <v>3.67</v>
+      </c>
+      <c r="F405" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="G405" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H405" s="9" t="s">
+        <v>1451</v>
+      </c>
+      <c r="I405" s="6"/>
+    </row>
+    <row r="406" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A406" s="6">
+        <v>29704561</v>
+      </c>
+      <c r="B406" s="6">
+        <v>7</v>
+      </c>
+      <c r="C406" s="7" t="s">
+        <v>1431</v>
+      </c>
+      <c r="D406" s="7" t="s">
+        <v>1443</v>
+      </c>
+      <c r="E406" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="F406" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="G406" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H406" s="9" t="s">
+        <v>1452</v>
+      </c>
+      <c r="I406" s="6"/>
+    </row>
+    <row r="407" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A407" s="6">
+        <v>29704561</v>
+      </c>
+      <c r="B407" s="6">
+        <v>8</v>
+      </c>
+      <c r="C407" s="7" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D407" s="7" t="s">
+        <v>1444</v>
+      </c>
+      <c r="E407" s="8">
+        <v>3.75</v>
+      </c>
+      <c r="F407" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="G407" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H407" s="9" t="s">
+        <v>1453</v>
+      </c>
+      <c r="I407" s="6"/>
+    </row>
+    <row r="408" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A408" s="6">
+        <v>29704561</v>
+      </c>
+      <c r="B408" s="6">
+        <v>9</v>
+      </c>
+      <c r="C408" s="7" t="s">
+        <v>1433</v>
+      </c>
+      <c r="D408" s="7" t="s">
+        <v>1445</v>
+      </c>
+      <c r="E408" s="8">
+        <v>3.67</v>
+      </c>
+      <c r="F408" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="G408" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H408" s="9" t="s">
+        <v>1454</v>
+      </c>
+      <c r="I408" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{334F36AD-9FF2-4015-B24F-6F18BB3AEDBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73FFF5F7-E8D6-4907-B751-54D3FEF6F102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1624" uniqueCount="1455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1659" uniqueCount="1487">
   <si>
     <t>No</t>
   </si>
@@ -4591,6 +4591,102 @@
   </si>
   <si>
     <t>Επιστρέφει στο αφρικανικό στοιχείο με Mermans Mosengo σε φωνητική/ρυθμική καθοδήγηση. Το κομμάτι είναι γιορτινό, πολυρυθμικό και συλλογικό, αποφεύγοντας τη δυτική «εξωτικοποίηση» επειδή η συνεργασία είναι πραγματικά ενσωματωμένη στην ενορχήστρωση και όχι διακοσμητική.</t>
+  </si>
+  <si>
+    <t>Razamanaz</t>
+  </si>
+  <si>
+    <t>Nazareth</t>
+  </si>
+  <si>
+    <t>Alcatraz</t>
+  </si>
+  <si>
+    <t>Vigilante Man</t>
+  </si>
+  <si>
+    <t>Woke Up This Morning</t>
+  </si>
+  <si>
+    <t>Night Woman</t>
+  </si>
+  <si>
+    <t>Bad, Bad Boy</t>
+  </si>
+  <si>
+    <t>Sold My Soul</t>
+  </si>
+  <si>
+    <t>Too Bad, Too Sad</t>
+  </si>
+  <si>
+    <t>Broken Down Angel</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/23803544-Nazareth-Razamanaz</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/qcurFeeUfVUgMcN1mNonar9Lr-tjQ_Ty3nedloSz6hg/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTIzODAz/NTQ0LTE2NTcxMzEw/ODUtMzA2OS5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Proto-Metal, Boogie Rock, Classic Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Proto-Metal, Boogie Rock, Glam-tinged Hard Rock]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Hard Rock [Heavy Blues Rock, Leon Russell Cover]</t>
+  </si>
+  <si>
+    <t>Folk Rock, Blues Rock [Country Blues, Folk Rock Cover]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Heavy Boogie, Proto-Metal]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Rock &amp; Roll [Glam Rock, Boogie Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Dark Heavy Rock, Proto-Metal]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Rock &amp; Roll [Up-tempo Blues Rock, Pub Rock]</t>
+  </si>
+  <si>
+    <t>Soft Rock, Blues Rock [Power Ballad, Blue-Eyed Soul]</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Ευρωπαϊκή επανέκδοση του 2022 σε κίτρινο βινύλιο (Yellow Vinyl) από την BMG / Salvo (BMGCAT192LPX / SALVO 381 LP). Χρησιμοποιεί το remastered audio του 2009. Παραγωγή από τον Roger Glover.</t>
+  </si>
+  <si>
+    <t>BMG, Salvo – BMGCAT192LPX, SALVO 381 LP / Vinyl, LP, Album, Reissue, Remastered, Yellow Vinyl, Europe, Jul 6, 2022</t>
+  </si>
+  <si>
+    <t>Εκρηκτικό άνοιγμα, βασισμένο σε κοφτό riff, απειλητικό groove και την ωμή ερμηνεία του McCafferty. Ο παράξενος τίτλος λειτουργεί κυρίως ως φωνητικό σύνθημα: ένα rock ’n’ roll κάλεσμα, με ζωντανή ενέργεια και proto-metal βάρος.</t>
+  </si>
+  <si>
+    <t>Διασκευή του Leon Russell που οι Nazareth απογυμνώνουν από κάθε χαλαρότητα και μετατρέπουν σε heavy blues-rock ιστορία εγκλεισμού και απελπισίας. Η κιθάρα του Charlton και η τραχιά φωνή του McCafferty κάνουν τη φυλακή του τίτλου να ακούγεται τόσο κυριολεκτική όσο και ψυχολογική.</t>
+  </si>
+  <si>
+    <t>Η σύνθεση του Woody Guthrie μεταφέρεται από το folk/blues πεδίο σε πιο βαριά, rural-rock εκτέλεση. Το κομμάτι διατηρεί την κοινωνική σκιά του πρωτοτύπου, εξουσία, φτώχεια, έλεγχος αλλά αποκτά σκόνη, slide κιθάρα και σκληρότερο βηματισμό.</t>
+  </si>
+  <si>
+    <t>Νέα, βαρύτερη εκδοχή τραγουδιού που είχε εμφανιστεί στο προηγούμενο άλμπουμ Exercises. Εδώ το slide, ο boogie ρυθμός και η πιο αποφασιστική παραγωγή του Glover το μετατρέπουν σε καθαρό hard-rock statement: η καθημερινή ερωτική/υπαρξιακή δυσφορία γίνεται riff-driven εφόρμηση.</t>
+  </si>
+  <si>
+    <t>Σφιχτό, νυχτερινό heavy boogie με άμεση ρυθμική επίθεση. Ο αφηγητής έλκεται από μια επικίνδυνη, μυστηριώδη γυναικεία μορφή και η μπάντα αποδίδει το θέμα χωρίς ποιητική υπεκφυγή: μπάσο, drums και riff λειτουργούν σαν μηχανή.</t>
+  </si>
+  <si>
+    <t>Ένα από τα μεγαλύτερα hooks της μπάντας, με glam-rock αμεσότητα και χορευτικό boogie. Παρά τον ανάλαφρο τίτλο, το τραγούδι έχει πραγματικό riff punch και συμπυκνώνει την ικανότητα των Nazareth να παντρεύουν σκληρό rock με single-friendly μελωδία.</t>
+  </si>
+  <si>
+    <t>Από τα πιο σκοτεινά τραγούδια του άλμπουμ. Το μοτίβο της "πώλησης της ψυχής" γίνεται εικόνα ενοχής, εξάντλησης και ηθικού συμβιβασμού, με πιο βαριά κιθαριστική διάθεση και ένα riff που πλησιάζει το πρώιμο heavy metal.</t>
+  </si>
+  <si>
+    <t>Σύντομο, γρήγορο blues-rock κομμάτι με pub-rock αίσθηση. Η φράση του τίτλου μετατρέπει την απογοήτευση σε ειρωνικό, σχεδόν χορευτικό ξέσπασμα· είναι λιγότερο σύνθετο από τα κεντρικά τραγούδια, αλλά ταιριάζει στον ρυθμό της δεύτερης πλευράς.</t>
+  </si>
+  <si>
+    <t>Μεγάλη μελωδική μπαλάντα και πιο ευάλωτη πλευρά των Nazareth. Ο McCafferty περιορίζει τη φωνητική του αγριότητα και τραγουδά για μια πληγωμένη, εγκαταλελειμμένη γυναίκα, ενώ η ενορχήστρωση κρατά blues-rock βάθος χωρίς να βουλιάζει σε υπερβολική γλυκύτητα. Είναι το τραγούδι που απέδειξε ότι το συγκρότημα μπορούσε να γράψει επιτυχίες με πραγματικό συναίσθημα.</t>
   </si>
 </sst>
 </file>
@@ -4708,7 +4804,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -4760,6 +4856,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5066,7 +5165,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -6584,6 +6683,38 @@
       </c>
       <c r="J47" s="11" t="s">
         <v>1423</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+      <c r="A48" s="6">
+        <v>23803544</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>1456</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>1455</v>
+      </c>
+      <c r="D48" s="6">
+        <v>1973</v>
+      </c>
+      <c r="E48" s="10">
+        <v>3.63</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>1467</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>1476</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>1477</v>
+      </c>
+      <c r="I48" s="11" t="s">
+        <v>1465</v>
+      </c>
+      <c r="J48" s="11" t="s">
+        <v>1466</v>
       </c>
     </row>
   </sheetData>
@@ -6678,6 +6809,8 @@
     <hyperlink ref="I46" r:id="rId88" xr:uid="{CD08D7F6-9889-458F-B1D7-B11EC371B1DB}"/>
     <hyperlink ref="J47" r:id="rId89" xr:uid="{F8E2C3AC-0723-47E2-B70F-5BE2142A8C3F}"/>
     <hyperlink ref="I47" r:id="rId90" xr:uid="{3F7A8B1D-1B9A-44F4-AFFC-EB39B6A43F6E}"/>
+    <hyperlink ref="I48" r:id="rId91" xr:uid="{BA233FB6-5839-41E1-AC06-8D9949B461AC}"/>
+    <hyperlink ref="J48" r:id="rId92" xr:uid="{B7D5820B-1F3D-4D0E-A47D-20072EB8BBBE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6685,7 +6818,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I408"/>
+  <dimension ref="A1:I417"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="3" bestFit="1" customWidth="1"/>
@@ -17788,6 +17921,251 @@
       </c>
       <c r="I408" s="6"/>
     </row>
+    <row r="409" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A409" s="6">
+        <v>23803544</v>
+      </c>
+      <c r="B409" s="6">
+        <v>1</v>
+      </c>
+      <c r="C409" s="7" t="s">
+        <v>1455</v>
+      </c>
+      <c r="D409" s="18" t="s">
+        <v>1468</v>
+      </c>
+      <c r="E409" s="8">
+        <v>3.98</v>
+      </c>
+      <c r="F409" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G409" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="H409" s="9" t="s">
+        <v>1478</v>
+      </c>
+      <c r="I409" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="410" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A410" s="6">
+        <v>23803544</v>
+      </c>
+      <c r="B410" s="6">
+        <v>2</v>
+      </c>
+      <c r="C410" s="7" t="s">
+        <v>1457</v>
+      </c>
+      <c r="D410" s="18" t="s">
+        <v>1469</v>
+      </c>
+      <c r="E410" s="8">
+        <v>3.86</v>
+      </c>
+      <c r="F410" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G410" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="H410" s="9" t="s">
+        <v>1479</v>
+      </c>
+      <c r="I410" s="6"/>
+    </row>
+    <row r="411" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A411" s="6">
+        <v>23803544</v>
+      </c>
+      <c r="B411" s="6">
+        <v>3</v>
+      </c>
+      <c r="C411" s="7" t="s">
+        <v>1458</v>
+      </c>
+      <c r="D411" s="18" t="s">
+        <v>1470</v>
+      </c>
+      <c r="E411" s="8">
+        <v>3.44</v>
+      </c>
+      <c r="F411" s="12">
+        <v>4</v>
+      </c>
+      <c r="G411" s="12">
+        <v>3.85</v>
+      </c>
+      <c r="H411" s="9" t="s">
+        <v>1480</v>
+      </c>
+      <c r="I411" s="6"/>
+    </row>
+    <row r="412" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A412" s="6">
+        <v>23803544</v>
+      </c>
+      <c r="B412" s="6">
+        <v>4</v>
+      </c>
+      <c r="C412" s="7" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D412" s="18" t="s">
+        <v>1470</v>
+      </c>
+      <c r="E412" s="8">
+        <v>3.67</v>
+      </c>
+      <c r="F412" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G412" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="H412" s="9" t="s">
+        <v>1481</v>
+      </c>
+      <c r="I412" s="6"/>
+    </row>
+    <row r="413" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A413" s="6">
+        <v>23803544</v>
+      </c>
+      <c r="B413" s="6">
+        <v>5</v>
+      </c>
+      <c r="C413" s="7" t="s">
+        <v>1460</v>
+      </c>
+      <c r="D413" s="18" t="s">
+        <v>1471</v>
+      </c>
+      <c r="E413" s="8">
+        <v>3.58</v>
+      </c>
+      <c r="F413" s="12">
+        <v>4</v>
+      </c>
+      <c r="G413" s="12">
+        <v>3.75</v>
+      </c>
+      <c r="H413" s="9" t="s">
+        <v>1482</v>
+      </c>
+      <c r="I413" s="6"/>
+    </row>
+    <row r="414" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A414" s="6">
+        <v>23803544</v>
+      </c>
+      <c r="B414" s="6">
+        <v>6</v>
+      </c>
+      <c r="C414" s="7" t="s">
+        <v>1461</v>
+      </c>
+      <c r="D414" s="18" t="s">
+        <v>1472</v>
+      </c>
+      <c r="E414" s="8">
+        <v>3.57</v>
+      </c>
+      <c r="F414" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G414" s="12">
+        <v>4</v>
+      </c>
+      <c r="H414" s="9" t="s">
+        <v>1483</v>
+      </c>
+      <c r="I414" s="6"/>
+    </row>
+    <row r="415" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A415" s="6">
+        <v>23803544</v>
+      </c>
+      <c r="B415" s="6">
+        <v>7</v>
+      </c>
+      <c r="C415" s="7" t="s">
+        <v>1462</v>
+      </c>
+      <c r="D415" s="18" t="s">
+        <v>1473</v>
+      </c>
+      <c r="E415" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="F415" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G415" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="H415" s="9" t="s">
+        <v>1484</v>
+      </c>
+      <c r="I415" s="6"/>
+    </row>
+    <row r="416" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A416" s="6">
+        <v>23803544</v>
+      </c>
+      <c r="B416" s="6">
+        <v>8</v>
+      </c>
+      <c r="C416" s="7" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D416" s="18" t="s">
+        <v>1474</v>
+      </c>
+      <c r="E416" s="8">
+        <v>3.46</v>
+      </c>
+      <c r="F416" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="G416" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="H416" s="9" t="s">
+        <v>1485</v>
+      </c>
+      <c r="I416" s="6"/>
+    </row>
+    <row r="417" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A417" s="6">
+        <v>23803544</v>
+      </c>
+      <c r="B417" s="6">
+        <v>9</v>
+      </c>
+      <c r="C417" s="7" t="s">
+        <v>1464</v>
+      </c>
+      <c r="D417" s="18" t="s">
+        <v>1475</v>
+      </c>
+      <c r="E417" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="F417" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G417" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="H417" s="9" t="s">
+        <v>1486</v>
+      </c>
+      <c r="I417" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73FFF5F7-E8D6-4907-B751-54D3FEF6F102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6B1096F-AC8B-48E6-9DA0-16F2C29F104F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1659" uniqueCount="1487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1728" uniqueCount="1554">
   <si>
     <t>No</t>
   </si>
@@ -4687,6 +4687,207 @@
   </si>
   <si>
     <t>Μεγάλη μελωδική μπαλάντα και πιο ευάλωτη πλευρά των Nazareth. Ο McCafferty περιορίζει τη φωνητική του αγριότητα και τραγουδά για μια πληγωμένη, εγκαταλελειμμένη γυναίκα, ενώ η ενορχήστρωση κρατά blues-rock βάθος χωρίς να βουλιάζει σε υπερβολική γλυκύτητα. Είναι το τραγούδι που απέδειξε ότι το συγκρότημα μπορούσε να γράψει επιτυχίες με πραγματικό συναίσθημα.</t>
+  </si>
+  <si>
+    <t>First Two Pages Of Frankenstein</t>
+  </si>
+  <si>
+    <t>The National</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/26832221-The-National-First-Two-Pages-Of-Frankenstein</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/tkwjeF2564kS1bN5xvBaaSU4yguJE9aDr92HxchAaqo/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI2ODMy/MjIxLTE2ODU4MjU0/ODUtMzAzMy5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Eucalyptus</t>
+  </si>
+  <si>
+    <t>New Order T-Shirt</t>
+  </si>
+  <si>
+    <t>Tropic Morning News</t>
+  </si>
+  <si>
+    <t>Alien</t>
+  </si>
+  <si>
+    <t>Grease In Your Hair</t>
+  </si>
+  <si>
+    <t>Ice Machines</t>
+  </si>
+  <si>
+    <t>Send For Me</t>
+  </si>
+  <si>
+    <t>Once Upon A Poolside Featuring [Feat.] – Sufjan Stevens</t>
+  </si>
+  <si>
+    <t>This Isn't Helping Featuring [Feat.] – Phoebe Bridgers</t>
+  </si>
+  <si>
+    <t>The Alcott Featuring [Feat.] – Taylor Swift</t>
+  </si>
+  <si>
+    <t>Your Mind Is Not Your Friend Featuring [Feat.] – Phoebe Bridgers</t>
+  </si>
+  <si>
+    <t>Indie Rock, Chamber Pop [Indietronica, Indie Folk, Post-Punk Revival]</t>
+  </si>
+  <si>
+    <t>Πιάνο, σχεδόν ψιθυριστή ερμηνεία και διακριτική παρουσία του Sufjan Stevens ανοίγουν τον δίσκο σαν καταγραφή αποπροσανατολισμού. Ο Berninger αναρωτιέται αν η μπάντα μπορεί ακόμη να λειτουργήσει και αν η επαφή με τους άλλους παραμένει εφικτή.</t>
+  </si>
+  <si>
+    <t>Indie Rock, Chamber Pop [Slowcore, Piano Ballad, Indie Folk]</t>
+  </si>
+  <si>
+    <t>Indie Rock, Alternative Rock [Post-Punk Revival, Baritone Indie Rock]</t>
+  </si>
+  <si>
+    <t>Από τα πιο δυνατά τραγούδια του άλμπουμ. Η ιδέα του να μοιράζεις τα αντικείμενα ενός σπιτιού μετά από έναν χωρισμό μετατρέπεται σε σειρά από μικρές, πρακτικές και τελικά συντριπτικές παραχωρήσεις. Το χτίσιμο της κιθάρας και το επαναλαμβανόμενο "You should take it" προσδίδουν ένταση που σπάνια ξεσπά, αλλά διαρκώς αυξάνεται.</t>
+  </si>
+  <si>
+    <t>Η Phoebe Bridgers δίνει λεπτή, φαντασματική αντιφωνία σε ένα κομμάτι για τη συναισθηματική εξάντληση μιας σχέσης. Η φράση του τίτλου είναι η παραδοχή ότι ο τρόπος που δύο άνθρωποι προσπαθούν να βοηθήσουν ο ένας τον άλλο μπορεί τελικά να συντηρεί την απόσταση.</t>
+  </si>
+  <si>
+    <t>Η πιο άμεση, νευρική και σχεδόν χορευτική στιγμή του δίσκου. Τα synths, το σταθερό motorik pulse και το ανεβασμένο tempo συνοδεύουν την αίσθηση υπερφόρτωσης από πληροφορία, κοινωνική ένταση και πρωινή ανησυχία.</t>
+  </si>
+  <si>
+    <t>Εσωτερικό αλλά πιο κιθαριστικό track, για το να νιώθεις ξένος μέσα σε μια σχέση, σε ένα δωμάτιο ή ακόμη και μέσα στο ίδιο σου το σώμα. Η μελωδική οικονομία των National υπηρετεί την αίσθηση αποξένωσης χωρίς να την κάνει θεατρική.</t>
+  </si>
+  <si>
+    <t>Η Taylor Swift και ο Berninger τραγουδούν σαν δύο άνθρωποι που ανταλλάσσουν γράμματα ή σκέψεις τις οποίες δεν μπορούν να πουν πρόσωπο με πρόσωπο. Η σύνθεση αποφεύγει το pop-duet κλισέ: είναι λιτή, πιανιστική και γεμάτη αμφιβολία για το αν μια σύνδεση μπορεί να ξαναρχίσει.</t>
+  </si>
+  <si>
+    <t>Από τα πιο παλιομοδίτικα National κομμάτια του δίσκου, με κιθάρες, ρυθμική κίνηση και στίχους που μπλέκουν οικειότητα, μικρές εικόνες της καθημερινότητας και τη δυσκολία να ζητήσεις καθαρά αυτό που χρειάζεσαι.</t>
+  </si>
+  <si>
+    <t>Πιο υποτονικό και electronic-tinged, λειτουργεί σαν αϋπνική σκέψη σε αργή επανάληψη. Η ψυχρή εικόνα των "ice machines" αποδίδει τη μηχανική επανάληψη του άγχους και την επιθυμία για μια συναισθηματική παύση.</t>
+  </si>
+  <si>
+    <t>Η δεύτερη συμμετοχή της Phoebe Bridgers και ένας από τους πιο καθαρούς στιχουργικούς πυρήνες του δίσκου. Ο τίτλος συνοψίζει τη μάχη με τις καταστροφικές σκέψεις: το μυαλό μπορεί να κατασκευάζει εχθρικές αφηγήσεις, ακόμη και όταν εξωτερικά δεν υπάρχει άμεση απειλή.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ήπιο αλλά συγκινητικό κλείσιμο, χτισμένο σαν υπόσχεση διαθεσιμότητας και αλληλεγγύης. Μετά τη δυσπιστία, την αποσύνδεση και το βάρος των προηγούμενων κομματιών, ο Berninger δεν υπόσχεται λύση· προσφέρει απλώς την παρουσία του όταν χρειαστεί.</t>
+  </si>
+  <si>
+    <t>Indie Rock, Indietronica [Synth-driven Indie Rock, Nostalgic Alternative Rock]</t>
+  </si>
+  <si>
+    <t>Indie Rock, Chamber Pop [Melancholic Indie Pop, Vocal Duet]</t>
+  </si>
+  <si>
+    <t>Indie Rock, Indietronica [Synth Rock, Post-Punk Revival]</t>
+  </si>
+  <si>
+    <t>Indie Rock, Alternative Rock [Driving Indie Rock, Art Rock]</t>
+  </si>
+  <si>
+    <t>Chamber Pop, Indie Rock [Piano Duet, Indie Ballad]</t>
+  </si>
+  <si>
+    <t>Indie Rock, Alternative Rock [Guitar-driven Indie Rock, Post-Punk Revival]</t>
+  </si>
+  <si>
+    <t>Indietronica, Chamber Pop [Ambient Pop, Electronic Indie Ballad]</t>
+  </si>
+  <si>
+    <t>Τραγούδι για τη νοσταλγία, το σώμα που κουβαλά αναμνήσεις και τη συναισθηματική αξία καθημερινών αντικειμένων. Οι αναφορές στην indie κουλτούρα δεν λειτουργούν ως trivia· είναι ο τρόπος με τον οποίο ο αφηγητής προσπαθεί να κρατήσει ζωντανό ένα παρελθόν που έχει ήδη αλλάξει.</t>
+  </si>
+  <si>
+    <t>Indie Rock, Chamber Pop [Slowcore, Indie Folk, Dark Indie Pop]</t>
+  </si>
+  <si>
+    <t>Indie Rock, Chamber Pop [Orchestral Indie Rock, Closing Ballad]</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Ευρωπαϊκή limited έκδοση σε κόκκινο βινύλιο (Red Vinyl) κομμένη στο Optimal Media. Lacquer cut από τον JN-H στη Sterling Sound. Συμμετέχουν οι Sufjan Stevens, Phoebe Bridgers και Taylor Swift.</t>
+  </si>
+  <si>
+    <t>4AD – 4AD0566LPE / Vinyl, LP, Album, Limited Edition, Red, Optimal Pressing, Europe, Apr 28, 2023</t>
+  </si>
+  <si>
+    <t>Mother's Finest</t>
+  </si>
+  <si>
+    <t>Fire</t>
+  </si>
+  <si>
+    <t>Give You All The Love (Inside Of Me)</t>
+  </si>
+  <si>
+    <t>Niggizz Can't Sang Rock &amp; Roll</t>
+  </si>
+  <si>
+    <t>My Baby</t>
+  </si>
+  <si>
+    <t>Fly With Me (Feel The Love)</t>
+  </si>
+  <si>
+    <t>Dontcha Wanna Love Me</t>
+  </si>
+  <si>
+    <t>Rain</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/lAUL7LLXU51geHXlOFZrQYjEF6eeIX7XkHFVpQEmNXI/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTc2NjAw/OTctMTQ0NjE1MDk4/Ni0zMjY3LmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/7660097-Mothers-Finest-Mothers-Finest</t>
+  </si>
+  <si>
+    <t>Funk Rock, Hard Rock [Soul Rock, Funk Metal, Heavy Funk]</t>
+  </si>
+  <si>
+    <t>Funk Rock, Hard Rock [Heavy Funk, Soul Rock]</t>
+  </si>
+  <si>
+    <t>Funk Rock, Soul [Extended Soul-Funk, Psychedelic Funk]</t>
+  </si>
+  <si>
+    <t>Funk Rock, Hard Rock [Proto-Funk Metal, Satirical Rock]</t>
+  </si>
+  <si>
+    <t>Soul, Funk Rock [Blue-Eyed Soul, Funk Ballad]</t>
+  </si>
+  <si>
+    <t>Funk Rock, Hard Rock [Psychedelic Soul Rock, Slow-Burn Funk</t>
+  </si>
+  <si>
+    <t>Funk, Rhythm &amp; Blues [Funk Soul, Danceable R&amp;B]</t>
+  </si>
+  <si>
+    <t>Funk Rock, Soul [Soul Rock, Melodic Funk</t>
+  </si>
+  <si>
+    <t>Σκληρό, γρήγορο funk-rock opener με riff που θα μπορούσε να σταθεί σε hard-rock δίσκο, αλλά με rhythm section που αρνείται να εγκαταλείψει το pocket. Η φωνή της Kennedy εμφανίζεται με πλήρη δύναμη και δηλώνει αμέσως ότι η μπάντα δεν διαλέγει ανάμεσα σε rock και soul.</t>
+  </si>
+  <si>
+    <t>Το επτάλεπτο κέντρο βάρους του άλμπουμ. Αρχίζει σαν αισθησιακό soul-funk, επεκτείνεται σε ψυχεδελικό groove και επιτρέπει στο συγκρότημα να αναπτύξει δυναμικές, φωνητικές εναλλαγές και κρουστική ένταση χωρίς να χάνει τη συνοχή του. Η συμμετοχή του Joe Lala ενισχύει το πολυρυθμικό βάθος.</t>
+  </si>
+  <si>
+    <t>Η πιο πολιτικά φορτισμένη στιγμή του δίσκου. Με τίτλο που χρησιμοποιείται ειρωνικά ως αναστροφή ενός ρατσιστικού ισχυρισμού, το κομμάτι έχει σατιρική και διεκδικητική λειτουργία: η μπάντα αποδεικνύει την άνεσή της στο σκληρό riffing με έναν τρόπο που δεν ζητά άδεια από κανέναν.</t>
+  </si>
+  <si>
+    <t>Πιο λυρικό και soulful, χαμηλώνει το tempo χωρίς να χάνει το groove. Το κομμάτι στηρίζεται στην εκφραστική χημεία Kennedy–Murdock και αναδεικνύει ότι η μπάντα μπορεί να γράψει αισθησιακή R&amp;B μπαλάντα χωρίς να ακούγεται ως συμβατικό soul act.</t>
+  </si>
+  <si>
+    <t>Το πιο χορευτικό και άμεσο cut της δεύτερης πλευράς. Το groove είναι σταθερό, οι φωνές γίνονται call-and-response και η μπάντα επιλέγει οικονομία αντί για hard-rock μεγαλοπρέπεια.</t>
+  </si>
+  <si>
+    <t>Μελωδικό, ανοιχτό soul-rock κομμάτι, με ανέβασμα στο ρεφρέν και αίσθηση φυγής/ένωσης. Η κιθάρα και τα keys δημιουργούν ένα πιο "αέρινο" πεδίο πάνω από τον σταθερό funk ρυθμό.</t>
+  </si>
+  <si>
+    <t>Αργόσυρτο, ψυχεδελικό και βαρύτερο φινάλε. Η ατμόσφαιρα του τίτλου αποδίδεται με υπομονετικό build-up, μελαγχολικές φωνητικές γραμμές και κιθάρες που αφήνουν τη σύνθεση να τελειώσει περισσότερο ως διάθεση παρά ως συμβατική κορύφωση.</t>
+  </si>
+  <si>
+    <t>Epic – EPC 32112 (Europe, 1982, Dark Blue Labels, Price Code CB 231)</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Ευρωπαϊκή επανέκδοση (1982, Made in Holland) με τα σκούρα μπλε labels της Epic (Catalog No: EPC 32112, Price Code: CB 231). Χρησιμοποιεί τις αυθεντικές μεταλλικές μήτρες (stampers) του Sterling Sound (S-81595), εξασφαλίζοντας εξαιρετική δυναμική και αναλογικό punch.</t>
   </si>
 </sst>
 </file>
@@ -5165,7 +5366,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -6715,6 +6916,70 @@
       </c>
       <c r="J48" s="11" t="s">
         <v>1466</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+      <c r="A49" s="6">
+        <v>26832221</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>1488</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>1487</v>
+      </c>
+      <c r="D49" s="6">
+        <v>2023</v>
+      </c>
+      <c r="E49" s="10">
+        <v>2.82</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>1502</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>1525</v>
+      </c>
+      <c r="H49" s="6" t="s">
+        <v>1526</v>
+      </c>
+      <c r="I49" s="11" t="s">
+        <v>1489</v>
+      </c>
+      <c r="J49" s="11" t="s">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+      <c r="A50" s="6">
+        <v>7660097</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>1527</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>1527</v>
+      </c>
+      <c r="D50" s="6">
+        <v>1976</v>
+      </c>
+      <c r="E50" s="10">
+        <v>3.63</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>1537</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>1553</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>1552</v>
+      </c>
+      <c r="I50" s="11" t="s">
+        <v>1536</v>
+      </c>
+      <c r="J50" s="11" t="s">
+        <v>1535</v>
       </c>
     </row>
   </sheetData>
@@ -6811,6 +7076,10 @@
     <hyperlink ref="I47" r:id="rId90" xr:uid="{3F7A8B1D-1B9A-44F4-AFFC-EB39B6A43F6E}"/>
     <hyperlink ref="I48" r:id="rId91" xr:uid="{BA233FB6-5839-41E1-AC06-8D9949B461AC}"/>
     <hyperlink ref="J48" r:id="rId92" xr:uid="{B7D5820B-1F3D-4D0E-A47D-20072EB8BBBE}"/>
+    <hyperlink ref="I49" r:id="rId93" xr:uid="{0AECC585-C22C-466A-9DD8-680618CE482C}"/>
+    <hyperlink ref="J49" r:id="rId94" xr:uid="{C3A3F0A6-33F1-4328-BF10-E113DBBEF38F}"/>
+    <hyperlink ref="J50" r:id="rId95" xr:uid="{68B72E20-33B9-4DEC-9ED1-60B37506BCDD}"/>
+    <hyperlink ref="I50" r:id="rId96" xr:uid="{C736AAB1-9716-4350-A6EB-A381CE4E7CCD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6818,7 +7087,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I417"/>
+  <dimension ref="A1:I435"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="3" bestFit="1" customWidth="1"/>
@@ -18166,6 +18435,480 @@
       </c>
       <c r="I417" s="6"/>
     </row>
+    <row r="418" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A418" s="6">
+        <v>26832221</v>
+      </c>
+      <c r="B418" s="6">
+        <v>1</v>
+      </c>
+      <c r="C418" s="7" t="s">
+        <v>1498</v>
+      </c>
+      <c r="D418" s="18" t="s">
+        <v>1504</v>
+      </c>
+      <c r="E418" s="8">
+        <v>3.35</v>
+      </c>
+      <c r="F418" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G418" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H418" s="9" t="s">
+        <v>1503</v>
+      </c>
+      <c r="I418" s="6"/>
+    </row>
+    <row r="419" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A419" s="6">
+        <v>26832221</v>
+      </c>
+      <c r="B419" s="6">
+        <v>2</v>
+      </c>
+      <c r="C419" s="7" t="s">
+        <v>1491</v>
+      </c>
+      <c r="D419" s="18" t="s">
+        <v>1505</v>
+      </c>
+      <c r="E419" s="8">
+        <v>3.31</v>
+      </c>
+      <c r="F419" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G419" s="12">
+        <v>4</v>
+      </c>
+      <c r="H419" s="9" t="s">
+        <v>1506</v>
+      </c>
+      <c r="I419" s="6"/>
+    </row>
+    <row r="420" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A420" s="6">
+        <v>26832221</v>
+      </c>
+      <c r="B420" s="6">
+        <v>3</v>
+      </c>
+      <c r="C420" s="7" t="s">
+        <v>1492</v>
+      </c>
+      <c r="D420" s="18" t="s">
+        <v>1515</v>
+      </c>
+      <c r="E420" s="8">
+        <v>3.22</v>
+      </c>
+      <c r="F420" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G420" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H420" s="9" t="s">
+        <v>1522</v>
+      </c>
+      <c r="I420" s="6"/>
+    </row>
+    <row r="421" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A421" s="6">
+        <v>26832221</v>
+      </c>
+      <c r="B421" s="6">
+        <v>4</v>
+      </c>
+      <c r="C421" s="7" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D421" s="18" t="s">
+        <v>1516</v>
+      </c>
+      <c r="E421" s="8">
+        <v>3.08</v>
+      </c>
+      <c r="F421" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G421" s="12">
+        <v>4.05</v>
+      </c>
+      <c r="H421" s="9" t="s">
+        <v>1507</v>
+      </c>
+      <c r="I421" s="6"/>
+    </row>
+    <row r="422" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A422" s="6">
+        <v>26832221</v>
+      </c>
+      <c r="B422" s="6">
+        <v>5</v>
+      </c>
+      <c r="C422" s="7" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D422" s="18" t="s">
+        <v>1517</v>
+      </c>
+      <c r="E422" s="8">
+        <v>3.66</v>
+      </c>
+      <c r="F422" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G422" s="12">
+        <v>4.25</v>
+      </c>
+      <c r="H422" s="9" t="s">
+        <v>1508</v>
+      </c>
+      <c r="I422" s="6"/>
+    </row>
+    <row r="423" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A423" s="6">
+        <v>26832221</v>
+      </c>
+      <c r="B423" s="6">
+        <v>6</v>
+      </c>
+      <c r="C423" s="7" t="s">
+        <v>1494</v>
+      </c>
+      <c r="D423" s="18" t="s">
+        <v>1518</v>
+      </c>
+      <c r="E423" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="F423" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G423" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="H423" s="9" t="s">
+        <v>1509</v>
+      </c>
+      <c r="I423" s="6"/>
+    </row>
+    <row r="424" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A424" s="6">
+        <v>26832221</v>
+      </c>
+      <c r="B424" s="6">
+        <v>7</v>
+      </c>
+      <c r="C424" s="7" t="s">
+        <v>1500</v>
+      </c>
+      <c r="D424" s="18" t="s">
+        <v>1519</v>
+      </c>
+      <c r="E424" s="8">
+        <v>3.22</v>
+      </c>
+      <c r="F424" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G424" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H424" s="9" t="s">
+        <v>1510</v>
+      </c>
+      <c r="I424" s="6"/>
+    </row>
+    <row r="425" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A425" s="6">
+        <v>26832221</v>
+      </c>
+      <c r="B425" s="6">
+        <v>8</v>
+      </c>
+      <c r="C425" s="7" t="s">
+        <v>1495</v>
+      </c>
+      <c r="D425" s="18" t="s">
+        <v>1520</v>
+      </c>
+      <c r="E425" s="8">
+        <v>3.23</v>
+      </c>
+      <c r="F425" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G425" s="12">
+        <v>4</v>
+      </c>
+      <c r="H425" s="9" t="s">
+        <v>1511</v>
+      </c>
+      <c r="I425" s="6"/>
+    </row>
+    <row r="426" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A426" s="6">
+        <v>26832221</v>
+      </c>
+      <c r="B426" s="6">
+        <v>9</v>
+      </c>
+      <c r="C426" s="7" t="s">
+        <v>1496</v>
+      </c>
+      <c r="D426" s="18" t="s">
+        <v>1521</v>
+      </c>
+      <c r="E426" s="8">
+        <v>2.92</v>
+      </c>
+      <c r="F426" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="G426" s="12">
+        <v>3.95</v>
+      </c>
+      <c r="H426" s="9" t="s">
+        <v>1512</v>
+      </c>
+      <c r="I426" s="6"/>
+    </row>
+    <row r="427" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A427" s="6">
+        <v>26832221</v>
+      </c>
+      <c r="B427" s="6">
+        <v>10</v>
+      </c>
+      <c r="C427" s="7" t="s">
+        <v>1501</v>
+      </c>
+      <c r="D427" s="18" t="s">
+        <v>1523</v>
+      </c>
+      <c r="E427" s="8">
+        <v>3.25</v>
+      </c>
+      <c r="F427" s="12">
+        <v>4</v>
+      </c>
+      <c r="G427" s="12">
+        <v>4.05</v>
+      </c>
+      <c r="H427" s="9" t="s">
+        <v>1513</v>
+      </c>
+      <c r="I427" s="6"/>
+    </row>
+    <row r="428" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A428" s="6">
+        <v>26832221</v>
+      </c>
+      <c r="B428" s="6">
+        <v>11</v>
+      </c>
+      <c r="C428" s="7" t="s">
+        <v>1497</v>
+      </c>
+      <c r="D428" s="18" t="s">
+        <v>1524</v>
+      </c>
+      <c r="E428" s="8">
+        <v>2.8</v>
+      </c>
+      <c r="F428" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G428" s="12">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="H428" s="9" t="s">
+        <v>1514</v>
+      </c>
+      <c r="I428" s="6"/>
+    </row>
+    <row r="429" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A429" s="6">
+        <v>7660097</v>
+      </c>
+      <c r="B429" s="6">
+        <v>1</v>
+      </c>
+      <c r="C429" s="7" t="s">
+        <v>1528</v>
+      </c>
+      <c r="D429" s="18" t="s">
+        <v>1538</v>
+      </c>
+      <c r="E429" s="8">
+        <v>4.12</v>
+      </c>
+      <c r="F429" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G429" s="12"/>
+      <c r="H429" s="9" t="s">
+        <v>1545</v>
+      </c>
+      <c r="I429" s="6"/>
+    </row>
+    <row r="430" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A430" s="6">
+        <v>7660097</v>
+      </c>
+      <c r="B430" s="6">
+        <v>2</v>
+      </c>
+      <c r="C430" s="7" t="s">
+        <v>1529</v>
+      </c>
+      <c r="D430" s="18" t="s">
+        <v>1539</v>
+      </c>
+      <c r="E430" s="8">
+        <v>4.16</v>
+      </c>
+      <c r="F430" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G430" s="12"/>
+      <c r="H430" s="9" t="s">
+        <v>1546</v>
+      </c>
+      <c r="I430" s="6"/>
+    </row>
+    <row r="431" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A431" s="6">
+        <v>7660097</v>
+      </c>
+      <c r="B431" s="6">
+        <v>3</v>
+      </c>
+      <c r="C431" s="7" t="s">
+        <v>1530</v>
+      </c>
+      <c r="D431" s="18" t="s">
+        <v>1540</v>
+      </c>
+      <c r="E431" s="8">
+        <v>4.07</v>
+      </c>
+      <c r="F431" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G431" s="12"/>
+      <c r="H431" s="9" t="s">
+        <v>1547</v>
+      </c>
+      <c r="I431" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="432" spans="1:9" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A432" s="6">
+        <v>7660097</v>
+      </c>
+      <c r="B432" s="6">
+        <v>4</v>
+      </c>
+      <c r="C432" s="7" t="s">
+        <v>1531</v>
+      </c>
+      <c r="D432" s="18" t="s">
+        <v>1541</v>
+      </c>
+      <c r="E432" s="8">
+        <v>3.76</v>
+      </c>
+      <c r="F432" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G432" s="12"/>
+      <c r="H432" s="9" t="s">
+        <v>1548</v>
+      </c>
+      <c r="I432" s="6"/>
+    </row>
+    <row r="433" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A433" s="6">
+        <v>7660097</v>
+      </c>
+      <c r="B433" s="6">
+        <v>5</v>
+      </c>
+      <c r="C433" s="7" t="s">
+        <v>1532</v>
+      </c>
+      <c r="D433" s="18" t="s">
+        <v>1544</v>
+      </c>
+      <c r="E433" s="8">
+        <v>3.69</v>
+      </c>
+      <c r="F433" s="12">
+        <v>4</v>
+      </c>
+      <c r="G433" s="12"/>
+      <c r="H433" s="9" t="s">
+        <v>1550</v>
+      </c>
+      <c r="I433" s="6"/>
+    </row>
+    <row r="434" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A434" s="6">
+        <v>7660097</v>
+      </c>
+      <c r="B434" s="6">
+        <v>6</v>
+      </c>
+      <c r="C434" s="7" t="s">
+        <v>1533</v>
+      </c>
+      <c r="D434" s="18" t="s">
+        <v>1543</v>
+      </c>
+      <c r="E434" s="8">
+        <v>3.86</v>
+      </c>
+      <c r="F434" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G434" s="12"/>
+      <c r="H434" s="9" t="s">
+        <v>1549</v>
+      </c>
+      <c r="I434" s="6"/>
+    </row>
+    <row r="435" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A435" s="6">
+        <v>7660097</v>
+      </c>
+      <c r="B435" s="6">
+        <v>7</v>
+      </c>
+      <c r="C435" s="7" t="s">
+        <v>1534</v>
+      </c>
+      <c r="D435" s="18" t="s">
+        <v>1542</v>
+      </c>
+      <c r="E435" s="8">
+        <v>3.76</v>
+      </c>
+      <c r="F435" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G435" s="12"/>
+      <c r="H435" s="9" t="s">
+        <v>1551</v>
+      </c>
+      <c r="I435" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6B1096F-AC8B-48E6-9DA0-16F2C29F104F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{200EEDF8-6E96-41DB-B6CB-3C902B284A06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1728" uniqueCount="1554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="1602">
   <si>
     <t>No</t>
   </si>
@@ -4888,6 +4888,150 @@
   </si>
   <si>
     <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Ευρωπαϊκή επανέκδοση (1982, Made in Holland) με τα σκούρα μπλε labels της Epic (Catalog No: EPC 32112, Price Code: CB 231). Χρησιμοποιεί τις αυθεντικές μεταλλικές μήτρες (stampers) του Sterling Sound (S-81595), εξασφαλίζοντας εξαιρετική δυναμική και αναλογικό punch.</t>
+  </si>
+  <si>
+    <t>A Hard Road</t>
+  </si>
+  <si>
+    <t>It's Over</t>
+  </si>
+  <si>
+    <t>You Don't Love Me</t>
+  </si>
+  <si>
+    <t>The Stumble</t>
+  </si>
+  <si>
+    <t>Another Kinda Love</t>
+  </si>
+  <si>
+    <t>Hit The Highway</t>
+  </si>
+  <si>
+    <t>Leaping Christine</t>
+  </si>
+  <si>
+    <t>Dust My Blues</t>
+  </si>
+  <si>
+    <t>There's Always Work</t>
+  </si>
+  <si>
+    <t>The Same Way</t>
+  </si>
+  <si>
+    <t>The Supernatural</t>
+  </si>
+  <si>
+    <t>Top Of The Hill</t>
+  </si>
+  <si>
+    <t>Someday After Awhile (You'll Be Sorry)</t>
+  </si>
+  <si>
+    <t>Living Alone</t>
+  </si>
+  <si>
+    <t>De Agostini – none, Italy, 2015 (Series: Blues In Vinile – 01, 180 gram, Reissue)</t>
+  </si>
+  <si>
+    <t>John Mayall &amp; The Bluesbreakers</t>
+  </si>
+  <si>
+    <t>British Blues, Blues Rock [Electric Blues, Chicago Blues Revival, Blues Instrumental]</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Ιταλική επανέκδοση 180 γραμμαρίων του 2015 από τη σειρά Blues In Vinile της De Agostini (No. 01). Ηχογραφημένο στα West Hampstead Studios τον Οκτώβριο και Νοέμβριο του 1966, με την ανεπανάληπτη παρουσία του Peter Green στις κιθάρες και τον John McVie στο μπάσο. Η κοπή φέρει χαραγμένα τα αρχικά MW (SST Brüggemann GmbH / lacquered by Morrow) και διαθέτει το αυθεντικό ιταλικό αυτοκόλλητο ασφαλείας της SIAE (RE001).</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/sej4PZVcgR1UHs-jaisyi0k1P5Mmf52RszgP-XrB3SQ/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTc1OTgw/NjAtMTcwMjEzNjQ5/MC03NDA5LmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/7598060-John-Mayall-And-The-Bluesbreakers-A-Hard-Road</t>
+  </si>
+  <si>
+    <t>British Blues, Blues Rock [Electric Blues, Chicago Blues Revival]</t>
+  </si>
+  <si>
+    <t>British Blues, Blues [Slow Blues, Soul Blues]</t>
+  </si>
+  <si>
+    <t>Blues Rock, British Blues [Chicago Blues, Electric Blues Cover]</t>
+  </si>
+  <si>
+    <t>British Blues, Blues Rock [Up-tempo Electric Blues, Blues Shuffle]</t>
+  </si>
+  <si>
+    <t>British Blues, Rhythm &amp; Blues [Piano Blues, R&amp;B]</t>
+  </si>
+  <si>
+    <t>Blues, Blues Rock [Electric Slide Blues, Elmore James Cover]</t>
+  </si>
+  <si>
+    <t>British Blues, Rhythm &amp; Blues [Piano R&amp;B, Jump Blues]</t>
+  </si>
+  <si>
+    <t>British Blues, Blues Rock [Chicago Blues, Peter Green Vocal]</t>
+  </si>
+  <si>
+    <t>British Blues, Blues Rock [Electric Blues, Piano-led Blues Rock]</t>
+  </si>
+  <si>
+    <t>Blues, Blues Rock [Freddie King Blues, Electric Slow Blues]</t>
+  </si>
+  <si>
+    <t>British Blues, Blues [Piano Blues, Closing Slow Blues]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Rhythm &amp; Blues [Freddie King-style Instrumental (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Blues Rock, British Blues [Guitar Instrumental, Blues Shuffle (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Instrumental Rock [Atmospheric Blues Instrumental, Slow Blues (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Λιτός επίλογος με θέμα τη μοναξιά ως τελική κατάσταση μετά την απώλεια και την περιπλάνηση. Η blues γλώσσα είναι παραδοσιακή, όμως ο τρόπος που ο Mayall και ο Green αφήνουν χώρο μεταξύ των φράσεων κλείνει τον δίσκο με πραγματική αίσθηση απομόνωσης.</t>
+  </si>
+  <si>
+    <t>Freddie King/Sonny Thompson slow blues, με τη μπάντα να παίζει με βαριά, νυχτερινή υπομονή. Η ερμηνεία αναβάλλει τη δικαίωση για το μέλλον, αφήνοντας το παράπονο να λειτουργήσει ως δύναμη.</t>
+  </si>
+  <si>
+    <t>Mid-tempo blues rock με πιάνο, φωνητικά Mayall και κιθαριστική απάντηση του Green. Η ανάβαση του τίτλου παρουσιάζεται περισσότερο ως δύσκολη διεκδίκηση παρά ως εγγυημένη επιτυχία.</t>
+  </si>
+  <si>
+    <t>Ομότιτλο electric blues με μετρημένη ένταση και αίσθηση διαρκούς κίνησης. Ο Mayall παρουσιάζει τον δρόμο ως εμπειρία σκληρής βιοπάλης, ενώ ο Green απαντά με κιθαριστικές φράσεις που περισσότερο «τραγουδούν» παρά επιδεικνύουν δεξιοτεχνία.</t>
+  </si>
+  <si>
+    <t>Αργό, πικρό blues για το τέλος μιας σχέσης. Η ερμηνεία κρατά την απογοήτευση χαμηλά, χωρίς μελοδραματισμό, και η κιθάρα του Green γεμίζει τα κενά με σχεδόν φωνητικά bends.</t>
+  </si>
+  <si>
+    <t>Διασκευή του Willie Cobbs σε σφιχτό Chicago-blues πλαίσιο. Ο Peter Green αναλαμβάνει τα κύρια φωνητικά, αποδεικνύοντας ότι η ήσυχη, ελαφρώς τραχιά φωνή του ταιριάζει ιδανικά στην παραιτημένη θλίψη του τραγουδιού.</t>
+  </si>
+  <si>
+    <t>Instrumental του Freddie King και του Sonny Thompson, παιγμένο με swing, ακρίβεια και καθαρό κιθαριστικό articulation. Ο Green αποφεύγει την αντιγραφή και δίνει πιο κομψή, less-is-more εκδοχή της αμερικανικής R&amp;B/blue instrumental παράδοσης.</t>
+  </si>
+  <si>
+    <t>Γρήγορο shuffle για ένα είδος αγάπης που δεν ακολουθεί τους συμβατικούς κανόνες. Η μπάντα λειτουργεί σαν tight club ensemble, με το πιάνο και τα drums να δίνουν επιθετική, χορευτική κίνηση.</t>
+  </si>
+  <si>
+    <t>Πιο λιτό piano-R&amp;B τραγούδι για την ανάγκη φυγής και το ταξίδι ως λύση ή απόδραση. Λειτουργεί σαν σύντομη, καθημερινή σκηνή μέσα στο μεγαλύτερο blues ταξίδι του δίσκου.</t>
+  </si>
+  <si>
+    <t>Ζωντανό instrumental shuffle, σχεδόν σαν soundtrack σε χορευτικό club set. Η κιθάρα έχει πρωταγωνιστικό ρόλο, όμως ο Green και η μπάντα παραμένουν αφοσιωμένοι στο groove, όχι στην επίδειξη σόλο.</t>
+  </si>
+  <si>
+    <t>Η Elmore James/“Dust My Broom” παράδοση περνά από το φίλτρο των Bluesbreakers με ηλεκτρισμό, slide/blues αίσθηση και έντονη ρυθμική βάση. Είναι μια ωμή, γειωμένη στιγμή που συνδέει τον δίσκο απευθείας με το μεταπολεμικό Chicago blues.</t>
+  </si>
+  <si>
+    <t>Σύντομο, χιουμοριστικό και πιο ανάλαφρο piano R&amp;B. Ο τίτλος λέει πολλά για τον κόσμο του Mayall: η εργασία εμφανίζεται ως σταθερά, ακόμη και όταν η ζωή και οι σχέσεις βρίσκονται σε χάος.</t>
+  </si>
+  <si>
+    <t>Peter Green composition και μία από τις κρίσιμες συνθέσεις του δίσκου. Με τον Green στα φωνητικά, το τραγούδι έχει προσωπική, λιγότερο «τυπική» blues διάθεση και προαναγγέλλει τον τρόπο που θα έγραφε αργότερα στους πρώιμους Fleetwood Mac.</t>
+  </si>
+  <si>
+    <t>Η κορυφαία στιγμή του άλμπουμ. Οργανικό slow blues με υπνωτική οικονομία, sustained notes, εκτεταμένο vibrato και σχεδόν υπερβατική αίσθηση χώρου. Δεν είναι «σόλο επίδειξης»· είναι μάθημα για το πώς η μία σωστή νότα μπορεί να έχει μεγαλύτερη δύναμη από δεκάδες γρήγορες φράσεις.</t>
   </si>
 </sst>
 </file>
@@ -4977,7 +5121,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -5000,12 +5144,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF002060"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF002060"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF002060"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF002060"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -5060,6 +5219,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5366,7 +5528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -6980,6 +7142,38 @@
       </c>
       <c r="J50" s="11" t="s">
         <v>1535</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+      <c r="A51" s="6">
+        <v>7598060</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D51" s="6">
+        <v>1967</v>
+      </c>
+      <c r="E51" s="10">
+        <v>3.65</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>1570</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>1571</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>1568</v>
+      </c>
+      <c r="I51" s="11" t="s">
+        <v>1573</v>
+      </c>
+      <c r="J51" s="11" t="s">
+        <v>1572</v>
       </c>
     </row>
   </sheetData>
@@ -7080,6 +7274,8 @@
     <hyperlink ref="J49" r:id="rId94" xr:uid="{C3A3F0A6-33F1-4328-BF10-E113DBBEF38F}"/>
     <hyperlink ref="J50" r:id="rId95" xr:uid="{68B72E20-33B9-4DEC-9ED1-60B37506BCDD}"/>
     <hyperlink ref="I50" r:id="rId96" xr:uid="{C736AAB1-9716-4350-A6EB-A381CE4E7CCD}"/>
+    <hyperlink ref="J51" r:id="rId97" xr:uid="{752C2683-11F4-4130-9245-211B37841510}"/>
+    <hyperlink ref="I51" r:id="rId98" xr:uid="{EA51E579-73B3-4A35-B724-480050ED921C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7087,7 +7283,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I435"/>
+  <dimension ref="A1:I449"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="3" bestFit="1" customWidth="1"/>
@@ -18909,6 +19105,386 @@
       </c>
       <c r="I435" s="6"/>
     </row>
+    <row r="436" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A436" s="6">
+        <v>7598060</v>
+      </c>
+      <c r="B436" s="6">
+        <v>1</v>
+      </c>
+      <c r="C436" s="7" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D436" s="19" t="s">
+        <v>1574</v>
+      </c>
+      <c r="E436" s="8">
+        <v>3.79</v>
+      </c>
+      <c r="F436" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G436" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H436" s="9" t="s">
+        <v>1591</v>
+      </c>
+      <c r="I436" s="6"/>
+    </row>
+    <row r="437" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A437" s="6">
+        <v>7598060</v>
+      </c>
+      <c r="B437" s="6">
+        <v>2</v>
+      </c>
+      <c r="C437" s="7" t="s">
+        <v>1555</v>
+      </c>
+      <c r="D437" s="19" t="s">
+        <v>1575</v>
+      </c>
+      <c r="E437" s="8">
+        <v>3.53</v>
+      </c>
+      <c r="F437" s="12">
+        <v>4</v>
+      </c>
+      <c r="G437" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="H437" s="9" t="s">
+        <v>1592</v>
+      </c>
+      <c r="I437" s="6"/>
+    </row>
+    <row r="438" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A438" s="6">
+        <v>7598060</v>
+      </c>
+      <c r="B438" s="6">
+        <v>3</v>
+      </c>
+      <c r="C438" s="7" t="s">
+        <v>1556</v>
+      </c>
+      <c r="D438" s="19" t="s">
+        <v>1576</v>
+      </c>
+      <c r="E438" s="8">
+        <v>3.63</v>
+      </c>
+      <c r="F438" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G438" s="12">
+        <v>4</v>
+      </c>
+      <c r="H438" s="9" t="s">
+        <v>1593</v>
+      </c>
+      <c r="I438" s="6"/>
+    </row>
+    <row r="439" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A439" s="6">
+        <v>7598060</v>
+      </c>
+      <c r="B439" s="6">
+        <v>4</v>
+      </c>
+      <c r="C439" s="7" t="s">
+        <v>1557</v>
+      </c>
+      <c r="D439" s="19" t="s">
+        <v>1585</v>
+      </c>
+      <c r="E439" s="8">
+        <v>3.78</v>
+      </c>
+      <c r="F439" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G439" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H439" s="9" t="s">
+        <v>1594</v>
+      </c>
+      <c r="I439" s="6"/>
+    </row>
+    <row r="440" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A440" s="6">
+        <v>7598060</v>
+      </c>
+      <c r="B440" s="6">
+        <v>5</v>
+      </c>
+      <c r="C440" s="7" t="s">
+        <v>1558</v>
+      </c>
+      <c r="D440" s="19" t="s">
+        <v>1577</v>
+      </c>
+      <c r="E440" s="8">
+        <v>3.69</v>
+      </c>
+      <c r="F440" s="12">
+        <v>4</v>
+      </c>
+      <c r="G440" s="12">
+        <v>3.85</v>
+      </c>
+      <c r="H440" s="9" t="s">
+        <v>1595</v>
+      </c>
+      <c r="I440" s="6"/>
+    </row>
+    <row r="441" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A441" s="6">
+        <v>7598060</v>
+      </c>
+      <c r="B441" s="6">
+        <v>6</v>
+      </c>
+      <c r="C441" s="7" t="s">
+        <v>1559</v>
+      </c>
+      <c r="D441" s="19" t="s">
+        <v>1578</v>
+      </c>
+      <c r="E441" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="F441" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G441" s="12">
+        <v>3.95</v>
+      </c>
+      <c r="H441" s="9" t="s">
+        <v>1596</v>
+      </c>
+      <c r="I441" s="6"/>
+    </row>
+    <row r="442" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A442" s="6">
+        <v>7598060</v>
+      </c>
+      <c r="B442" s="6">
+        <v>7</v>
+      </c>
+      <c r="C442" s="7" t="s">
+        <v>1560</v>
+      </c>
+      <c r="D442" s="19" t="s">
+        <v>1586</v>
+      </c>
+      <c r="E442" s="8">
+        <v>3.43</v>
+      </c>
+      <c r="F442" s="12">
+        <v>4</v>
+      </c>
+      <c r="G442" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="H442" s="9" t="s">
+        <v>1597</v>
+      </c>
+      <c r="I442" s="6"/>
+    </row>
+    <row r="443" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A443" s="6">
+        <v>7598060</v>
+      </c>
+      <c r="B443" s="6">
+        <v>8</v>
+      </c>
+      <c r="C443" s="7" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D443" s="19" t="s">
+        <v>1579</v>
+      </c>
+      <c r="E443" s="8">
+        <v>3.62</v>
+      </c>
+      <c r="F443" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G443" s="12">
+        <v>4.05</v>
+      </c>
+      <c r="H443" s="9" t="s">
+        <v>1598</v>
+      </c>
+      <c r="I443" s="6"/>
+    </row>
+    <row r="444" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A444" s="6">
+        <v>7598060</v>
+      </c>
+      <c r="B444" s="6">
+        <v>9</v>
+      </c>
+      <c r="C444" s="7" t="s">
+        <v>1562</v>
+      </c>
+      <c r="D444" s="19" t="s">
+        <v>1580</v>
+      </c>
+      <c r="E444" s="8">
+        <v>2.97</v>
+      </c>
+      <c r="F444" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="G444" s="12">
+        <v>3.75</v>
+      </c>
+      <c r="H444" s="9" t="s">
+        <v>1599</v>
+      </c>
+      <c r="I444" s="6"/>
+    </row>
+    <row r="445" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A445" s="6">
+        <v>7598060</v>
+      </c>
+      <c r="B445" s="6">
+        <v>10</v>
+      </c>
+      <c r="C445" s="7" t="s">
+        <v>1563</v>
+      </c>
+      <c r="D445" s="19" t="s">
+        <v>1581</v>
+      </c>
+      <c r="E445" s="8">
+        <v>3.27</v>
+      </c>
+      <c r="F445" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G445" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="H445" s="9" t="s">
+        <v>1600</v>
+      </c>
+      <c r="I445" s="6"/>
+    </row>
+    <row r="446" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A446" s="6">
+        <v>7598060</v>
+      </c>
+      <c r="B446" s="6">
+        <v>11</v>
+      </c>
+      <c r="C446" s="7" t="s">
+        <v>1564</v>
+      </c>
+      <c r="D446" s="19" t="s">
+        <v>1587</v>
+      </c>
+      <c r="E446" s="8">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="F446" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="G446" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H446" s="9" t="s">
+        <v>1601</v>
+      </c>
+      <c r="I446" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="447" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A447" s="6">
+        <v>7598060</v>
+      </c>
+      <c r="B447" s="6">
+        <v>12</v>
+      </c>
+      <c r="C447" s="7" t="s">
+        <v>1565</v>
+      </c>
+      <c r="D447" s="19" t="s">
+        <v>1582</v>
+      </c>
+      <c r="E447" s="8">
+        <v>3.38</v>
+      </c>
+      <c r="F447" s="12">
+        <v>4</v>
+      </c>
+      <c r="G447" s="12">
+        <v>3.95</v>
+      </c>
+      <c r="H447" s="9" t="s">
+        <v>1590</v>
+      </c>
+      <c r="I447" s="6"/>
+    </row>
+    <row r="448" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A448" s="6">
+        <v>7598060</v>
+      </c>
+      <c r="B448" s="6">
+        <v>13</v>
+      </c>
+      <c r="C448" s="7" t="s">
+        <v>1566</v>
+      </c>
+      <c r="D448" s="19" t="s">
+        <v>1583</v>
+      </c>
+      <c r="E448" s="8">
+        <v>3.68</v>
+      </c>
+      <c r="F448" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G448" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H448" s="9" t="s">
+        <v>1589</v>
+      </c>
+      <c r="I448" s="6"/>
+    </row>
+    <row r="449" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A449" s="6">
+        <v>7598060</v>
+      </c>
+      <c r="B449" s="6">
+        <v>14</v>
+      </c>
+      <c r="C449" s="7" t="s">
+        <v>1567</v>
+      </c>
+      <c r="D449" s="19" t="s">
+        <v>1584</v>
+      </c>
+      <c r="E449" s="8">
+        <v>3.47</v>
+      </c>
+      <c r="F449" s="12">
+        <v>4</v>
+      </c>
+      <c r="G449" s="12">
+        <v>3.85</v>
+      </c>
+      <c r="H449" s="9" t="s">
+        <v>1588</v>
+      </c>
+      <c r="I449" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{200EEDF8-6E96-41DB-B6CB-3C902B284A06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26053D71-C0A0-4953-A270-F34E4B78D974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="1602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1818" uniqueCount="1634">
   <si>
     <t>No</t>
   </si>
@@ -5032,6 +5032,104 @@
   </si>
   <si>
     <t>Η κορυφαία στιγμή του άλμπουμ. Οργανικό slow blues με υπνωτική οικονομία, sustained notes, εκτεταμένο vibrato και σχεδόν υπερβατική αίσθηση χώρου. Δεν είναι «σόλο επίδειξης»· είναι μάθημα για το πώς η μία σωστή νότα μπορεί να έχει μεγαλύτερη δύναμη από δεκάδες γρήγορες φράσεις.</t>
+  </si>
+  <si>
+    <t>Sheila C.</t>
+  </si>
+  <si>
+    <t>This Time</t>
+  </si>
+  <si>
+    <t>The Dreamer</t>
+  </si>
+  <si>
+    <t>Till He Mentioned Your Name</t>
+  </si>
+  <si>
+    <t>Baby Don't</t>
+  </si>
+  <si>
+    <t>Treat You Right</t>
+  </si>
+  <si>
+    <t>I'm Not Gonna Cry Anymore</t>
+  </si>
+  <si>
+    <t>Oh Me Oh My</t>
+  </si>
+  <si>
+    <t>Benny Mardones</t>
+  </si>
+  <si>
+    <t>Too Much To Lose</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/amJLJ134MDR91bNIvfiyROE-LlWaMkPYwzr_S7Rs_2U/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTMyMjk4/NDEtMTMyMTQ1NDE3/NS5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/3229841-Benny-Mardones-Too-Much-To-Lose</t>
+  </si>
+  <si>
+    <t>AOR, Pop Rock [Blue-Eyed Soul, Soft Rock, Melodic Rock]</t>
+  </si>
+  <si>
+    <t>AOR, Pop Rock [Melodic Rock, Piano-led AOR]</t>
+  </si>
+  <si>
+    <t>AOR, Soft Rock [Power Ballad, Blue-Eyed Soul]</t>
+  </si>
+  <si>
+    <t>Pop Rock, AOR [Melodic Rock, Heartland Rock]</t>
+  </si>
+  <si>
+    <t>AOR, Soft Rock [Adult Contemporary, Soul Ballad]</t>
+  </si>
+  <si>
+    <t>Pop Rock, AOR [Up-tempo Melodic Rock]</t>
+  </si>
+  <si>
+    <t>AOR, Blue-Eyed Soul [Soulful AOR, Slow-Burn Rock]</t>
+  </si>
+  <si>
+    <t>Soft Rock, Blue-Eyed Soul [Soul Pop, Heartbreak Ballad]</t>
+  </si>
+  <si>
+    <t>AOR, Pop Rock [Epic Soft Rock, Extended Closing Ballad]</t>
+  </si>
+  <si>
+    <t>Polydor – PD-1-6336, US, 1981 (LP, Album, Presswell Pressing)</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Αμερικανική πρώτη έκδοση του 1981, τυπωμένη στο εργοστάσιο της Presswell (με την ένδειξη PR στο runout και 18 στο rimtext). Η ηχογράφηση φέρει τη σφραγίδα του θρυλικού mastering από το Sterling Sound, προσφέροντας εξαιρετική δυναμική, καθαρότητα στα πρίμα και γεμάτο μπάσο σε αυτό το κλασικό AOR/rock άλμπουμ.</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Δυναμικό ξεκίνημα με piano-led AOR δομή και αφηγηματική φωνητική ερμηνεία. Το τραγούδι σκιαγραφεί μια γυναικεία φιγούρα που λειτουργεί ταυτόχρονα ως ανάμνηση, πειρασμός και συναισθηματικό σημείο αναφοράς.</t>
+  </si>
+  <si>
+    <t>Mid-tempo melodic rock για τον άνθρωπο που επιμένει να ζει μέσα σε όνειρα και προσδοκίες, ακόμη κι όταν η πραγματικότητα τον διαψεύδει. Το κομμάτι έχει πιο ανοιχτή, heartland-rock διάθεση και σταθερό rhythm section.</t>
+  </si>
+  <si>
+    <t>Συναισθηματική μπαλάντα με αφηγηματικό κέντρο μια ξαφνική αναφορά σε ένα όνομα που επαναφέρει παλιό τραύμα. Η ενορχήστρωση είναι συγκρατημένη, αφήνοντας το βάρος στη φωνή και στη μελωδική γραμμή.</t>
+  </si>
+  <si>
+    <t>Πιο σύντομο, εξωστρεφές και ρυθμικό AOR cut. Ο αφηγητής προσπαθεί να σταματήσει μια φυγή ή μια ρήξη πριν αυτή γίνει οριστική, με πιο έντονα guitar/keyboard hooks.</t>
+  </si>
+  <si>
+    <t>Slow-burn soul-rock τραγούδι που βασίζεται στην υπόσχεση φροντίδας και επανόρθωσης. Η blue-eyed soul ερμηνεία του Mardones και η παρουσία σαξοφώνου του Mark Rivera ενισχύουν τη νυχτερινή ατμόσφαιρα.</t>
+  </si>
+  <si>
+    <t>Soul-pop μπαλάντα με θέμα τη συναισθηματική αυτάρκεια μετά από επανειλημμένες απογοητεύσεις. Παρά τον τίτλο αποφασιστικότητας, η ερμηνεία του Mardones διατηρεί την ευαλωτότητα που κάνει το κομμάτι πειστικό.</t>
+  </si>
+  <si>
+    <t>Επτάλεπτο φινάλε που δίνει στον δίσκο μεγαλύτερη δραματική κλίμακα. Η σύνθεση κινείται από soft-rock εσωστρέφεια σε πιο εκτεταμένη AOR ανάπτυξη και συνοψίζει το βασικό συναισθηματικό πλαίσιο του άλμπουμ: σύγχυση, απώλεια και η αδυναμία να αποκοπεί κανείς πλήρως από μια σχέση.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ένα από τα πιο δυνατά και υποτιμημένα κομμάτια του Too Much to Lose, γραμμένο από τους Benny Mardones και Robert Tepper. Παρότι ο τίτλος αρχικά υπονοεί μια προσπάθεια επανασύνδεσης, το τραγούδι είναι στην πραγματικότητα μια οριστική απόφαση αποχώρησης μετά από προδοσία. Ο αφηγητής έχει ακούσει τα ψέματα που ειπώθηκαν εις βάρος του και γνωρίζει πως η σύντροφός του τον πρόδωσε με έναν φίλο του. Το επαναλαμβανόμενο “Where’s your heart now, baby?” δεν λειτουργεί απλώς ως hook, αλλά ως κατηγορητήριο και ως αδυναμία να κατανοήσει την ψυχρότητα ενός ανθρώπου που κάποτε αγαπούσε.
+ Η κρίσιμη ανατροπή βρίσκεται στο refrain: “This time, I’m gonna walk away all right / Not like the last time / When I cried every night.” Ο Mardones δεν υπόσχεται πως θα σώσει τη σχέση· υπόσχεται ότι θα σώσει τον εαυτό του από την επανάληψη της ίδιας πληγής. Η απόφαση δεν ακούγεται θριαμβευτική ούτε εκδικητική. Είναι εύθραυστη, βαριά και τελεσίδικη —η φωνή του διατηρεί την ανάμνηση της προηγούμενης αποτυχίας, άρα η αυτοπροστασία ακούγεται ως κάτι που κερδήθηκε με μεγάλο προσωπικό κόστος.
+ Μουσικά, η μεγάλη διάρκεια των 6:16 επιτρέπει στη σύνθεση να λειτουργήσει σαν ολοκληρωμένη AOR/soul δραματουργία και όχι σαν τυπική power ballad. Οι στίχοι ξεκινούν σχεδόν εξομολογητικά, το πιάνο και τα keyboards χτίζουν σταδιακά ατμόσφαιρα, και το chorus δεν έρχεται ως εύκολη pop λύτρωση αλλά σαν επαναλαμβανόμενη δήλωση επιβίωσης. Η παραγωγή του Barry Mraz αφήνει επαρκή χώρο στη βραχνή, blue-eyed soul φωνή του Mardones, ενώ τα διακριτικά synth textures και η rock ενορχήστρωση εντείνουν την αίσθηση νυχτερινής μοναξιάς. Ο Mardones δεν τραγουδά σαν στιλπνός AOR frontman της εποχής. Αφήνει τις ρωγμές, τη σκληράδα και την εσωτερική κόπωση να περάσουν στην ερμηνεία. Γι’ αυτό το “This Time” ξεφεύγει από τα όρια ενός απλού τραγουδιού χωρισμού: είναι μια blue-eyed soul εξομολόγηση για το σημείο όπου η αγάπη παύει να δικαιολογεί την παραμονή και η αξιοπρέπεια επιβάλλει τη φυγή. Αποτελεί κρυφό διαμάντι της early-’80s AOR/rock σκηνής και μία από τις πιο ολοκληρωμένες φωνητικές ερμηνείες του Mardones.</t>
   </si>
 </sst>
 </file>
@@ -5164,7 +5262,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -5222,6 +5320,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5528,7 +5629,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -7174,6 +7275,38 @@
       </c>
       <c r="J51" s="11" t="s">
         <v>1572</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+      <c r="A52" s="6">
+        <v>3229841</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>1610</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>1611</v>
+      </c>
+      <c r="D52" s="6">
+        <v>1981</v>
+      </c>
+      <c r="E52" s="10">
+        <v>3.38</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>1614</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>1624</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>1623</v>
+      </c>
+      <c r="I52" s="11" t="s">
+        <v>1613</v>
+      </c>
+      <c r="J52" s="11" t="s">
+        <v>1612</v>
       </c>
     </row>
   </sheetData>
@@ -7276,6 +7409,8 @@
     <hyperlink ref="I50" r:id="rId96" xr:uid="{C736AAB1-9716-4350-A6EB-A381CE4E7CCD}"/>
     <hyperlink ref="J51" r:id="rId97" xr:uid="{752C2683-11F4-4130-9245-211B37841510}"/>
     <hyperlink ref="I51" r:id="rId98" xr:uid="{EA51E579-73B3-4A35-B724-480050ED921C}"/>
+    <hyperlink ref="J52" r:id="rId99" xr:uid="{3C9E633D-16AC-41F4-9319-FDDB83D97349}"/>
+    <hyperlink ref="I52" r:id="rId100" xr:uid="{3E32E8C7-A58A-4A22-A76D-04BAE7EC648B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7283,7 +7418,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I449"/>
+  <dimension ref="A1:I457"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="3" bestFit="1" customWidth="1"/>
@@ -19485,6 +19620,224 @@
       </c>
       <c r="I449" s="6"/>
     </row>
+    <row r="450" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A450" s="6">
+        <v>3229841</v>
+      </c>
+      <c r="B450" s="6">
+        <v>1</v>
+      </c>
+      <c r="C450" s="7" t="s">
+        <v>1602</v>
+      </c>
+      <c r="D450" s="7" t="s">
+        <v>1615</v>
+      </c>
+      <c r="E450" s="20" t="s">
+        <v>1625</v>
+      </c>
+      <c r="F450" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="G450" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H450" s="9" t="s">
+        <v>1626</v>
+      </c>
+      <c r="I450" s="6"/>
+    </row>
+    <row r="451" spans="1:9" ht="399.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A451" s="6">
+        <v>3229841</v>
+      </c>
+      <c r="B451" s="6">
+        <v>2</v>
+      </c>
+      <c r="C451" s="7" t="s">
+        <v>1603</v>
+      </c>
+      <c r="D451" s="7" t="s">
+        <v>1616</v>
+      </c>
+      <c r="E451" s="20" t="s">
+        <v>1625</v>
+      </c>
+      <c r="F451" s="12">
+        <v>4</v>
+      </c>
+      <c r="G451" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H451" s="9" t="s">
+        <v>1633</v>
+      </c>
+      <c r="I451" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="452" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A452" s="6">
+        <v>3229841</v>
+      </c>
+      <c r="B452" s="6">
+        <v>3</v>
+      </c>
+      <c r="C452" s="7" t="s">
+        <v>1604</v>
+      </c>
+      <c r="D452" s="7" t="s">
+        <v>1617</v>
+      </c>
+      <c r="E452" s="20" t="s">
+        <v>1625</v>
+      </c>
+      <c r="F452" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="G452" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H452" s="9" t="s">
+        <v>1627</v>
+      </c>
+      <c r="I452" s="6"/>
+    </row>
+    <row r="453" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A453" s="6">
+        <v>3229841</v>
+      </c>
+      <c r="B453" s="6">
+        <v>4</v>
+      </c>
+      <c r="C453" s="7" t="s">
+        <v>1605</v>
+      </c>
+      <c r="D453" s="7" t="s">
+        <v>1618</v>
+      </c>
+      <c r="E453" s="20" t="s">
+        <v>1625</v>
+      </c>
+      <c r="F453" s="12">
+        <v>3.4</v>
+      </c>
+      <c r="G453" s="12">
+        <v>4.25</v>
+      </c>
+      <c r="H453" s="9" t="s">
+        <v>1628</v>
+      </c>
+      <c r="I453" s="6"/>
+    </row>
+    <row r="454" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A454" s="6">
+        <v>3229841</v>
+      </c>
+      <c r="B454" s="6">
+        <v>5</v>
+      </c>
+      <c r="C454" s="7" t="s">
+        <v>1606</v>
+      </c>
+      <c r="D454" s="7" t="s">
+        <v>1619</v>
+      </c>
+      <c r="E454" s="20" t="s">
+        <v>1625</v>
+      </c>
+      <c r="F454" s="12">
+        <v>3.4</v>
+      </c>
+      <c r="G454" s="12">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="H454" s="9" t="s">
+        <v>1629</v>
+      </c>
+      <c r="I454" s="6"/>
+    </row>
+    <row r="455" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A455" s="6">
+        <v>3229841</v>
+      </c>
+      <c r="B455" s="6">
+        <v>6</v>
+      </c>
+      <c r="C455" s="7" t="s">
+        <v>1607</v>
+      </c>
+      <c r="D455" s="7" t="s">
+        <v>1620</v>
+      </c>
+      <c r="E455" s="20" t="s">
+        <v>1625</v>
+      </c>
+      <c r="F455" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="G455" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H455" s="9" t="s">
+        <v>1630</v>
+      </c>
+      <c r="I455" s="6"/>
+    </row>
+    <row r="456" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A456" s="6">
+        <v>3229841</v>
+      </c>
+      <c r="B456" s="6">
+        <v>7</v>
+      </c>
+      <c r="C456" s="7" t="s">
+        <v>1608</v>
+      </c>
+      <c r="D456" s="7" t="s">
+        <v>1621</v>
+      </c>
+      <c r="E456" s="20" t="s">
+        <v>1625</v>
+      </c>
+      <c r="F456" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="G456" s="12">
+        <v>4.05</v>
+      </c>
+      <c r="H456" s="9" t="s">
+        <v>1631</v>
+      </c>
+      <c r="I456" s="6"/>
+    </row>
+    <row r="457" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A457" s="6">
+        <v>3229841</v>
+      </c>
+      <c r="B457" s="6">
+        <v>8</v>
+      </c>
+      <c r="C457" s="7" t="s">
+        <v>1609</v>
+      </c>
+      <c r="D457" s="7" t="s">
+        <v>1622</v>
+      </c>
+      <c r="E457" s="20" t="s">
+        <v>1625</v>
+      </c>
+      <c r="F457" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G457" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H457" s="9" t="s">
+        <v>1632</v>
+      </c>
+      <c r="I457" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26053D71-C0A0-4953-A270-F34E4B78D974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D14BF46E-8E8F-4A2C-9539-DFBBC9C92399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1818" uniqueCount="1634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1872" uniqueCount="1686">
   <si>
     <t>No</t>
   </si>
@@ -5131,12 +5131,281 @@
  Η κρίσιμη ανατροπή βρίσκεται στο refrain: “This time, I’m gonna walk away all right / Not like the last time / When I cried every night.” Ο Mardones δεν υπόσχεται πως θα σώσει τη σχέση· υπόσχεται ότι θα σώσει τον εαυτό του από την επανάληψη της ίδιας πληγής. Η απόφαση δεν ακούγεται θριαμβευτική ούτε εκδικητική. Είναι εύθραυστη, βαριά και τελεσίδικη —η φωνή του διατηρεί την ανάμνηση της προηγούμενης αποτυχίας, άρα η αυτοπροστασία ακούγεται ως κάτι που κερδήθηκε με μεγάλο προσωπικό κόστος.
  Μουσικά, η μεγάλη διάρκεια των 6:16 επιτρέπει στη σύνθεση να λειτουργήσει σαν ολοκληρωμένη AOR/soul δραματουργία και όχι σαν τυπική power ballad. Οι στίχοι ξεκινούν σχεδόν εξομολογητικά, το πιάνο και τα keyboards χτίζουν σταδιακά ατμόσφαιρα, και το chorus δεν έρχεται ως εύκολη pop λύτρωση αλλά σαν επαναλαμβανόμενη δήλωση επιβίωσης. Η παραγωγή του Barry Mraz αφήνει επαρκή χώρο στη βραχνή, blue-eyed soul φωνή του Mardones, ενώ τα διακριτικά synth textures και η rock ενορχήστρωση εντείνουν την αίσθηση νυχτερινής μοναξιάς. Ο Mardones δεν τραγουδά σαν στιλπνός AOR frontman της εποχής. Αφήνει τις ρωγμές, τη σκληράδα και την εσωτερική κόπωση να περάσουν στην ερμηνεία. Γι’ αυτό το “This Time” ξεφεύγει από τα όρια ενός απλού τραγουδιού χωρισμού: είναι μια blue-eyed soul εξομολόγηση για το σημείο όπου η αγάπη παύει να δικαιολογεί την παραμονή και η αξιοπρέπεια επιβάλλει τη φυγή. Αποτελεί κρυφό διαμάντι της early-’80s AOR/rock σκηνής και μία από τις πιο ολοκληρωμένες φωνητικές ερμηνείες του Mardones.</t>
   </si>
+  <si>
+    <t>Mad Season</t>
+  </si>
+  <si>
+    <t>Above</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/7GeMIFjv_d1L-1dLNlJqGMEvzBCg_jnS47wPmWlqpT4/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTMwNjMw/NTUzLTE3MTUyNDk3/MjYtOTA0NS5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/30630553-Mad-Season-Above</t>
+  </si>
+  <si>
+    <t>Wake Up</t>
+  </si>
+  <si>
+    <t>X-Ray Mind</t>
+  </si>
+  <si>
+    <t>River Of Deceit</t>
+  </si>
+  <si>
+    <t>I'm Above</t>
+  </si>
+  <si>
+    <t>Artificial Red</t>
+  </si>
+  <si>
+    <t>Lifeless Dead</t>
+  </si>
+  <si>
+    <t>I Don't Know Anything</t>
+  </si>
+  <si>
+    <t>Long Gone Day</t>
+  </si>
+  <si>
+    <t>November Hotel</t>
+  </si>
+  <si>
+    <t>All Alone</t>
+  </si>
+  <si>
+    <t>Interlude</t>
+  </si>
+  <si>
+    <t>Locomotive</t>
+  </si>
+  <si>
+    <t>Black Book Of Fear</t>
+  </si>
+  <si>
+    <t>Slip Away</t>
+  </si>
+  <si>
+    <t>I Don't Wanna Be A Soldier (Remix)</t>
+  </si>
+  <si>
+    <t>Music On Vinyl – MOVLP169, Legacy, Columbia, Monkeywrench Records – MOVLP169, Europe, Reissue, Remastered, 180 gr (2xLP)</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Ευρωπαϊκή remastered επανέκδοση 180 γραμμαρίων (2xLP) από τη Music On Vinyl (MOVLP169), η οποία συχνά περιλαμβάνει και επιπλέον κομμάτια (όπως τα bonus tracks των sessions). Η ηχητική αποτύπωση διακρίνεται για το τεράστιο δυναμικό εύρος, την υποδειγματική κατανομή στο διπλό βινύλιο (που αποτρέπει το inner groove distortion σε δίσκους μεγαλύτερης διάρκειας) και τη βαθιά, ατμοσφαιρική απόδοση των σκοτεινών blues συνθέσεων.</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Grunge [Blues Rock, Psychedelic Rock, Dark Rock]</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Blues Rock [Slow-Burn Grunge, Dark Blues Rock]</t>
+  </si>
+  <si>
+    <t>Grunge, Hard Rock [Psychedelic Grunge, Heavy Alternative]</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Blues Rock [Acoustic Grunge, Dark Folk Rock]</t>
+  </si>
+  <si>
+    <t>Grunge, Alternative Rock [Psychedelic Blues Rock, Dark Grunge]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Grunge [Stoner Blues, Psychedelic Rock]</t>
+  </si>
+  <si>
+    <t>Grunge, Alternative Rock [Dark Rock, Heavy Blues Grunge]</t>
+  </si>
+  <si>
+    <t>Grunge, Hard Rock [Heavy Grunge, Alternative Metal]</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Jazz Rock [Psychedelic Blues, Jazz-Grunge]</t>
+  </si>
+  <si>
+    <t>Psychedelic Rock, Jazz Rock [Instrumental Grunge, Hendrixian Jam (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Blues Rock [Acoustic Grunge, Dark Folk Ballad]</t>
+  </si>
+  <si>
+    <t>Ambient, Instrumental Rock [Atmospheric Guitar Interlude (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Blues Rock [Dark Blues Rock, Post-Grunge]</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Psychedelic Rock [Dark Psych Rock, Blues Rock]</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Blues Rock [Melancholic Rock, Acoustic-leaning Grunge]</t>
+  </si>
+  <si>
+    <t>Rock, Psychedelic Rock [John Lennon Cover, Dark Blues Rock]</t>
+  </si>
+  <si>
+    <t>Το πιο άμεσο heavy-grunge τραγούδι του δίσκου. Η επαναλαμβανόμενη φράση του τίτλου λειτουργεί ως ωμή ομολογία σύγχυσης και απώλειας ελέγχου. Η μπάντα παίζει με live ένστικτο, δίνοντας στην αδυναμία του αφηγητή όχι έναν θεωρητικό αλλά έναν σωματικό, σχεδόν βίαιο χαρακτήρα.</t>
+  </si>
+  <si>
+    <t>Αργό, βαρύ και σχεδόν τελετουργικό άνοιγμα. Η επαναλαμβανόμενη κιθάρα του Mike McCready και ο υπνωτικός ρυθμός των Barrett Martin και John Baker Saunders χτίζουν την αίσθηση μιας αφύπνισης που δεν φέρνει ανακούφιση. Η φωνή του Layne Staley ακούγεται σαν άνθρωπος που αναγκάζεται να κοιτάξει την πραγματικότητά του χωρίς την αναισθησία της άρνησης.</t>
+  </si>
+  <si>
+    <t>Η συναισθηματική καρδιά του δίσκου και η πιο εμβληματική σύνθεση των Mad Season. Με ακουστική κιθάρα, μελαγχολική μελωδία και γυμνή ερμηνεία, περιγράφει την αυτοεξαπάτηση όχι ως εξωτερική παγίδα αλλά ως πορεία στην οποία ο άνθρωπος έχει ήδη συναινέσει. Το «ποτάμι» της απάτης είναι ταυτόχρονα η εξάρτηση, η ενοχή και η συνειδητή κάθοδος προς κάτι που γνωρίζεις ότι θα σε καταστρέψει.</t>
+  </si>
+  <si>
+    <t>Πιο άμεσο και νευρικό grunge hard-rock ξέσπασμα, με αιχμηρό riffing και ασφυκτική φωνητική ερμηνεία. Ο τίτλος παραπέμπει σε ένα μυαλό εκτεθειμένο σε αδιάκριτο ψυχικό έλεγχο: δεν μπορεί να κρυφτεί τίποτα, ούτε από τους άλλους ούτε από τον ίδιο τον εαυτό.</t>
+  </si>
+  <si>
+    <t>Instrumental έκταση επτά λεπτών, όπου ο McCready δίνει μία από τις πιο ελεύθερες, Hendrix-ικές ερμηνείες του. Τα drums και τα πρόσθετα όργανα του Barrett Martin ανοίγουν τον χώρο πέρα από το τυπικό grunge, δημιουργώντας έναν σκοτεινό, κινηματογραφικό τόπο. Το «ξενοδοχείο του Νοεμβρίου» ακούγεται σαν τόπος προσωρινής διαμονής, παγωνιάς και εσωτερικής περιπλάνησης.</t>
+  </si>
+  <si>
+    <t>Σύντομο, μέχρι τότε αδημοσίευτο οργανικό πέρασμα του McCready. Δεν επιδιώκει πλήρη μορφή τραγουδιού· λειτουργεί ως ατμοσφαιρική ανάσα ανάμεσα στο original album και στα μεταγενέστερα υλικά. Η finger-picked κιθάρα μεταφέρει μια ήρεμη, εύθραυστη μελαγχολία.</t>
+  </si>
+  <si>
+    <t>Σκοτεινό ψυχεδελικό blues-rock με φωνητικά και στίχους του Lanegan. Αποτελεί επίσης υλικό του ανολοκλήρωτου δεύτερου δίσκου και έχει τον χαρακτήρα αποσπασματικής, υπόγειας εξομολόγησης. Το «μαύρο βιβλίο του φόβου» λειτουργεί ως κατάλογος ενοχών, εσωτερικών απειλών και αναμνήσεων που ο αφηγητής κουβαλά αλλά δεν μπορεί να εξημερώσει.</t>
+  </si>
+  <si>
+    <t>Το τρίτο Lanegan-led τραγούδι από τις ηχογραφήσεις του ανεκπλήρωτου δεύτερου άλμπουμ. Είναι μελαγχολικό, βραδυφλεγές και περισσότερο υπαινικτικό από τα βαριά κομμάτια του αρχικού δίσκου. Οι στίχοι κινούνται γύρω από γέννηση, θνητότητα, έλξη προς την εξαφάνιση και τη δυσκολία να κρατηθεί κανείς παρών στον κόσμο.</t>
+  </si>
+  <si>
+    <t>Η διασκευή του John Lennon δεν είναι απλή tribute εκτέλεση. Οι Mad Season την προσεγγίζουν σαν σκοτεινό, αργόσυρτο blues-rock mantra, διατηρώντας το αντιπολεμικό/αντιεξουσιαστικό βάρος του πρωτοτύπου αλλά μεταφέροντάς το σε έναν πιο άγριο, Seattle-session χώρο. Η remix εκδοχή λειτουργεί ως raw appendix: λιγότερο ολοκληρωμένη από τα βασικά tracks, αλλά αποκαλυπτική για τη βαριά, αυτοσχεδιαστική πλευρά της μπάντας.</t>
+  </si>
+  <si>
+    <t>Artificial Red: Αργό, πυκνό και σχεδόν υπνωτικό blues με stoner-rock βάρος. Το riff κυλά σαν βαρύ υγρό, ενώ η φωνή του Staley μετατρέπει την εικόνα του «τεχνητού κόκκινου» σε αίσθηση χημικής θολούρας, τεχνητής διέγερσης και ψυχικής αποξένωσης. Από τα πιο σκοτεινά και σωματικά tracks του άλμπουμ.</t>
+  </si>
+  <si>
+    <t>Lifeless Dead: Κλειστοφοβικό, απειλητικό κομμάτι όπου η ένταση δεν προέρχεται από την ταχύτητα αλλά από τη σταθερή πίεση. Οι στίχοι και το βαρύ groove παραπέμπουν σε πνευματική ακινησία: το να κινείσαι μέσα στη ζωή χωρίς πραγματική παρουσία, σαν να είσαι ήδη νεκρός συναισθηματικά.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I'm Above: Ψυχεδελικό blues-rock με ανοιχτό, αιωρούμενο χώρο και φωνητικά του </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Mark Lanegan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> στην expanded tracklist credit της έκδοσής σου. Η παρουσία του Lanegan φέρνει μια χαμηλή, καπνισμένη αντίστιξη στην εύθραυστη ένταση του Staley. Ο τίτλος μοιάζει με δήλωση υπέρβασης, όμως η μουσική τον αντιμετωπίζει ως αμφίβολη στιγμή καθαρότητας, όχι ως οριστική νίκη απέναντι στην εξάρτηση ή την κατάρρευση.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Το αυθεντικό φινάλε του άλμπουμ του 1995. Ακουστικό, λιτό και απομονωμένο, συμπυκνώνει τον πυρήνα του </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Above,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> μετά την ένταση, τις ουσίες, τα riffs και τις εξομολογήσεις, μένει ο άνθρωπος μόνος απέναντι στις επιλογές του. Δεν δίνει εύκολη λύση· μετατρέπει τη μοναξιά σε γυμνή παραδοχή.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ένα από τα τρία κομμάτια που προορίζονταν για το ανολοκλήρωτο δεύτερο άλμπουμ, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Disinformation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve">. Ο </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Mark Lanegan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> έγραψε τους στίχους και ανέλαβε τα φωνητικά, μετατρέποντας τη σύνθεση σε πιο βαριά, γειωμένη και post-grunge μπλουζική εμπειρία. Η εικόνα της αργής ατμομηχανής παραπέμπει σε αναπόφευκτη κίνηση προς τη φθορά: ακόμη κι όταν το σώμα και ο νους εξαντλούνται, η πορεία συνεχίζεται.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Από τις πιο ιδιαίτερες συνθέσεις της εποχής Seattle. Με σαξόφωνο από τον </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Nalgas Sin Carne</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> και φωνητικό διάλογο Staley–Lanegan, κινείται ανάμεσα σε jazz, blues και grunge με νυχτερινή, smoky ατμόσφαιρα. Η "μέρα που χάθηκε" αφορά όσα δεν μπορούν να επιστραφούν, μια παλιά ζωή, μια σχέση ή μια εκδοχή του εαυτού που έχει ήδη φύγει.</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5203,6 +5472,22 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="161"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="161"/>
     </font>
   </fonts>
   <fills count="3">
@@ -5629,7 +5914,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -7307,6 +7592,38 @@
       </c>
       <c r="J52" s="11" t="s">
         <v>1612</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+      <c r="A53" s="6">
+        <v>30630553</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>1634</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>1635</v>
+      </c>
+      <c r="D53" s="6">
+        <v>1995</v>
+      </c>
+      <c r="E53" s="10">
+        <v>3.76</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>1655</v>
+      </c>
+      <c r="G53" s="7" t="s">
+        <v>1654</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>1653</v>
+      </c>
+      <c r="I53" s="11" t="s">
+        <v>1637</v>
+      </c>
+      <c r="J53" s="11" t="s">
+        <v>1636</v>
       </c>
     </row>
   </sheetData>
@@ -7411,6 +7728,8 @@
     <hyperlink ref="I51" r:id="rId98" xr:uid="{EA51E579-73B3-4A35-B724-480050ED921C}"/>
     <hyperlink ref="J52" r:id="rId99" xr:uid="{3C9E633D-16AC-41F4-9319-FDDB83D97349}"/>
     <hyperlink ref="I52" r:id="rId100" xr:uid="{3E32E8C7-A58A-4A22-A76D-04BAE7EC648B}"/>
+    <hyperlink ref="J53" r:id="rId101" xr:uid="{78696536-2EE3-4E1E-BE35-3104DCC74F14}"/>
+    <hyperlink ref="I53" r:id="rId102" xr:uid="{1357F0CA-ED11-4C8F-A624-FF42D1B7FDB5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7418,16 +7737,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I457"/>
+  <dimension ref="A1:I472"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="3" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.140625" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="33.7109375" style="5" customWidth="1"/>
     <col min="4" max="4" width="32.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.5703125" style="4" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="50.7109375" style="3" customWidth="1"/>
     <col min="9" max="9" width="12.7109375" style="4" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="9.140625" style="3"/>
@@ -16486,7 +16805,7 @@
       </c>
       <c r="I333" s="6"/>
     </row>
-    <row r="334" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A334" s="6">
         <v>1562086</v>
       </c>
@@ -17304,7 +17623,7 @@
       </c>
       <c r="I363" s="6"/>
     </row>
-    <row r="364" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A364" s="6">
         <v>25895635</v>
       </c>
@@ -17412,7 +17731,7 @@
       </c>
       <c r="I367" s="6"/>
     </row>
-    <row r="368" spans="1:9" ht="66.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A368" s="6">
         <v>25895635</v>
       </c>
@@ -17655,7 +17974,7 @@
       </c>
       <c r="I376" s="6"/>
     </row>
-    <row r="377" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A377" s="6">
         <v>31216738</v>
       </c>
@@ -17819,7 +18138,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="383" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A383" s="6">
         <v>4418939</v>
       </c>
@@ -17954,7 +18273,7 @@
       </c>
       <c r="I387" s="6"/>
     </row>
-    <row r="388" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A388" s="6">
         <v>4418939</v>
       </c>
@@ -18143,7 +18462,7 @@
       </c>
       <c r="I394" s="6"/>
     </row>
-    <row r="395" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A395" s="6">
         <v>26909678</v>
       </c>
@@ -18467,7 +18786,7 @@
       </c>
       <c r="I406" s="6"/>
     </row>
-    <row r="407" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A407" s="6">
         <v>29704561</v>
       </c>
@@ -18766,7 +19085,7 @@
       </c>
       <c r="I417" s="6"/>
     </row>
-    <row r="418" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A418" s="6">
         <v>26832221</v>
       </c>
@@ -18793,7 +19112,7 @@
       </c>
       <c r="I418" s="6"/>
     </row>
-    <row r="419" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A419" s="6">
         <v>26832221</v>
       </c>
@@ -19140,7 +19459,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="432" spans="1:9" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A432" s="6">
         <v>7660097</v>
       </c>
@@ -19647,7 +19966,7 @@
       </c>
       <c r="I450" s="6"/>
     </row>
-    <row r="451" spans="1:9" ht="399.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:9" ht="357" x14ac:dyDescent="0.25">
       <c r="A451" s="6">
         <v>3229841</v>
       </c>
@@ -19837,6 +20156,411 @@
         <v>1632</v>
       </c>
       <c r="I457" s="6"/>
+    </row>
+    <row r="458" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A458" s="6">
+        <v>30630553</v>
+      </c>
+      <c r="B458" s="6">
+        <v>1</v>
+      </c>
+      <c r="C458" s="7" t="s">
+        <v>1638</v>
+      </c>
+      <c r="D458" s="7" t="s">
+        <v>1656</v>
+      </c>
+      <c r="E458" s="20">
+        <v>4.32</v>
+      </c>
+      <c r="F458" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G458" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H458" s="9" t="s">
+        <v>1672</v>
+      </c>
+      <c r="I458" s="6"/>
+    </row>
+    <row r="459" spans="1:9" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A459" s="6">
+        <v>30630553</v>
+      </c>
+      <c r="B459" s="6">
+        <v>2</v>
+      </c>
+      <c r="C459" s="7" t="s">
+        <v>1639</v>
+      </c>
+      <c r="D459" s="7" t="s">
+        <v>1657</v>
+      </c>
+      <c r="E459" s="20">
+        <v>3.89</v>
+      </c>
+      <c r="F459" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G459" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H459" s="9" t="s">
+        <v>1674</v>
+      </c>
+      <c r="I459" s="6"/>
+    </row>
+    <row r="460" spans="1:9" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A460" s="6">
+        <v>30630553</v>
+      </c>
+      <c r="B460" s="6">
+        <v>3</v>
+      </c>
+      <c r="C460" s="7" t="s">
+        <v>1640</v>
+      </c>
+      <c r="D460" s="7" t="s">
+        <v>1658</v>
+      </c>
+      <c r="E460" s="20">
+        <v>4.22</v>
+      </c>
+      <c r="F460" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="G460" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H460" s="9" t="s">
+        <v>1673</v>
+      </c>
+      <c r="I460" s="6"/>
+    </row>
+    <row r="461" spans="1:9" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A461" s="6">
+        <v>30630553</v>
+      </c>
+      <c r="B461" s="6">
+        <v>4</v>
+      </c>
+      <c r="C461" s="7" t="s">
+        <v>1641</v>
+      </c>
+      <c r="D461" s="7" t="s">
+        <v>1659</v>
+      </c>
+      <c r="E461" s="20">
+        <v>4.04</v>
+      </c>
+      <c r="F461" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G461" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H461" s="9" t="s">
+        <v>1682</v>
+      </c>
+      <c r="I461" s="6"/>
+    </row>
+    <row r="462" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A462" s="6">
+        <v>30630553</v>
+      </c>
+      <c r="B462" s="6">
+        <v>5</v>
+      </c>
+      <c r="C462" s="7" t="s">
+        <v>1642</v>
+      </c>
+      <c r="D462" s="7" t="s">
+        <v>1660</v>
+      </c>
+      <c r="E462" s="20">
+        <v>3.67</v>
+      </c>
+      <c r="F462" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G462" s="12">
+        <v>4.75</v>
+      </c>
+      <c r="H462" s="9" t="s">
+        <v>1680</v>
+      </c>
+      <c r="I462" s="6"/>
+    </row>
+    <row r="463" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A463" s="6">
+        <v>30630553</v>
+      </c>
+      <c r="B463" s="6">
+        <v>6</v>
+      </c>
+      <c r="C463" s="7" t="s">
+        <v>1643</v>
+      </c>
+      <c r="D463" s="7" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E463" s="20">
+        <v>3.85</v>
+      </c>
+      <c r="F463" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G463" s="12">
+        <v>4.45</v>
+      </c>
+      <c r="H463" s="9" t="s">
+        <v>1681</v>
+      </c>
+      <c r="I463" s="6"/>
+    </row>
+    <row r="464" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A464" s="6">
+        <v>30630553</v>
+      </c>
+      <c r="B464" s="6">
+        <v>7</v>
+      </c>
+      <c r="C464" s="7" t="s">
+        <v>1644</v>
+      </c>
+      <c r="D464" s="7" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E464" s="20">
+        <v>3.93</v>
+      </c>
+      <c r="F464" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G464" s="12">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="H464" s="9" t="s">
+        <v>1671</v>
+      </c>
+      <c r="I464" s="6"/>
+    </row>
+    <row r="465" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A465" s="6">
+        <v>30630553</v>
+      </c>
+      <c r="B465" s="6">
+        <v>8</v>
+      </c>
+      <c r="C465" s="7" t="s">
+        <v>1645</v>
+      </c>
+      <c r="D465" s="7" t="s">
+        <v>1663</v>
+      </c>
+      <c r="E465" s="20">
+        <v>4.08</v>
+      </c>
+      <c r="F465" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G465" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H465" s="9" t="s">
+        <v>1685</v>
+      </c>
+      <c r="I465" s="6"/>
+    </row>
+    <row r="466" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A466" s="6">
+        <v>30630553</v>
+      </c>
+      <c r="B466" s="6">
+        <v>9</v>
+      </c>
+      <c r="C466" s="7" t="s">
+        <v>1646</v>
+      </c>
+      <c r="D466" s="7" t="s">
+        <v>1664</v>
+      </c>
+      <c r="E466" s="20">
+        <v>3.86</v>
+      </c>
+      <c r="F466" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G466" s="12">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="H466" s="9" t="s">
+        <v>1675</v>
+      </c>
+      <c r="I466" s="6"/>
+    </row>
+    <row r="467" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A467" s="6">
+        <v>30630553</v>
+      </c>
+      <c r="B467" s="6">
+        <v>10</v>
+      </c>
+      <c r="C467" s="7" t="s">
+        <v>1647</v>
+      </c>
+      <c r="D467" s="7" t="s">
+        <v>1665</v>
+      </c>
+      <c r="E467" s="20">
+        <v>3.59</v>
+      </c>
+      <c r="F467" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G467" s="12">
+        <v>4.55</v>
+      </c>
+      <c r="H467" s="9" t="s">
+        <v>1683</v>
+      </c>
+      <c r="I467" s="6"/>
+    </row>
+    <row r="468" spans="1:9" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A468" s="6">
+        <v>30630553</v>
+      </c>
+      <c r="B468" s="6">
+        <v>11</v>
+      </c>
+      <c r="C468" s="7" t="s">
+        <v>1648</v>
+      </c>
+      <c r="D468" s="7" t="s">
+        <v>1666</v>
+      </c>
+      <c r="E468" s="20" t="s">
+        <v>1625</v>
+      </c>
+      <c r="F468" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="G468" s="12">
+        <v>4</v>
+      </c>
+      <c r="H468" s="9" t="s">
+        <v>1676</v>
+      </c>
+      <c r="I468" s="6"/>
+    </row>
+    <row r="469" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A469" s="6">
+        <v>30630553</v>
+      </c>
+      <c r="B469" s="6">
+        <v>12</v>
+      </c>
+      <c r="C469" s="7" t="s">
+        <v>1649</v>
+      </c>
+      <c r="D469" s="7" t="s">
+        <v>1667</v>
+      </c>
+      <c r="E469" s="20">
+        <v>3.75</v>
+      </c>
+      <c r="F469" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G469" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H469" s="9" t="s">
+        <v>1684</v>
+      </c>
+      <c r="I469" s="6"/>
+    </row>
+    <row r="470" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A470" s="6">
+        <v>30630553</v>
+      </c>
+      <c r="B470" s="6">
+        <v>13</v>
+      </c>
+      <c r="C470" s="7" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D470" s="7" t="s">
+        <v>1668</v>
+      </c>
+      <c r="E470" s="20">
+        <v>3.55</v>
+      </c>
+      <c r="F470" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G470" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H470" s="9" t="s">
+        <v>1677</v>
+      </c>
+      <c r="I470" s="6"/>
+    </row>
+    <row r="471" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A471" s="6">
+        <v>30630553</v>
+      </c>
+      <c r="B471" s="6">
+        <v>14</v>
+      </c>
+      <c r="C471" s="7" t="s">
+        <v>1651</v>
+      </c>
+      <c r="D471" s="7" t="s">
+        <v>1669</v>
+      </c>
+      <c r="E471" s="20" t="s">
+        <v>1625</v>
+      </c>
+      <c r="F471" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G471" s="12">
+        <v>4.55</v>
+      </c>
+      <c r="H471" s="9" t="s">
+        <v>1678</v>
+      </c>
+      <c r="I471" s="6"/>
+    </row>
+    <row r="472" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A472" s="6">
+        <v>30630553</v>
+      </c>
+      <c r="B472" s="6">
+        <v>15</v>
+      </c>
+      <c r="C472" s="7" t="s">
+        <v>1652</v>
+      </c>
+      <c r="D472" s="7" t="s">
+        <v>1670</v>
+      </c>
+      <c r="E472" s="20">
+        <v>3.96</v>
+      </c>
+      <c r="F472" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G472" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H472" s="9" t="s">
+        <v>1679</v>
+      </c>
+      <c r="I472" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D14BF46E-8E8F-4A2C-9539-DFBBC9C92399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98CE0183-666E-42CC-8651-911FE277A347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1872" uniqueCount="1686">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1936" uniqueCount="1741">
   <si>
     <t>No</t>
   </si>
@@ -5399,6 +5399,171 @@
       </rPr>
       <t xml:space="preserve"> και φωνητικό διάλογο Staley–Lanegan, κινείται ανάμεσα σε jazz, blues και grunge με νυχτερινή, smoky ατμόσφαιρα. Η "μέρα που χάθηκε" αφορά όσα δεν μπορούν να επιστραφούν, μια παλιά ζωή, μια σχέση ή μια εκδοχή του εαυτού που έχει ήδη φύγει.</t>
     </r>
+  </si>
+  <si>
+    <t>Lynyrd Skynyrd</t>
+  </si>
+  <si>
+    <t>Gold &amp; Platinum</t>
+  </si>
+  <si>
+    <t>MCA Records – 250 413-1, Europe, Reissue, Gatefold (2xLP)</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Ευρωπαϊκή έκδοση της δεκαετίας του '80 (με barcode 0 2292-50413-1 και γαλλικό price code WE 332), τυπωμένη και κομμένη στη Γερμανία από την R/S Alsdorf. Η συγκεκριμένη κοπή φέρει τις χαρακτηριστικές μήτρες χαραγμένες στο runout (250413-1), προσφέροντας εξαιρετική δυναμική, καθαρότητα στα διπλά κιθαριστικά σόλο και συμπαγή απόδοση στις χαμηλές συχνότητες του κλασικού Southern Rock.</t>
+  </si>
+  <si>
+    <t>Down South Jukin'</t>
+  </si>
+  <si>
+    <t>Saturday Night Special</t>
+  </si>
+  <si>
+    <t>Gimme Three Steps (Live)</t>
+  </si>
+  <si>
+    <t>What's Your Name</t>
+  </si>
+  <si>
+    <t>You Got That Right</t>
+  </si>
+  <si>
+    <t>Gimme Back My Bullets</t>
+  </si>
+  <si>
+    <t>Sweet Home Alabama</t>
+  </si>
+  <si>
+    <t>Free Bird (Live)</t>
+  </si>
+  <si>
+    <t>That Smell</t>
+  </si>
+  <si>
+    <t>On The Hunt</t>
+  </si>
+  <si>
+    <t>I Ain't The One (Live)</t>
+  </si>
+  <si>
+    <t>Whiskey Rock-A Roller</t>
+  </si>
+  <si>
+    <t>Simple Man</t>
+  </si>
+  <si>
+    <t>I Know A Little</t>
+  </si>
+  <si>
+    <t>Tuesday's Gone</t>
+  </si>
+  <si>
+    <t>Comin' Home</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/9EGyY07SJSO8SnLHdMRUHxnzDKbbbyA3dehWfmZjFnM/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTEzNzk1/ODE4LTE1NjEzMTAy/MDEtNTE4MS5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/13795818-Lynyrd-Skynyrd-Band-Gold-Platinum</t>
+  </si>
+  <si>
+    <t>Southern Rock, Blues Rock [Classic Rock, Boogie Rock, Country Rock]</t>
+  </si>
+  <si>
+    <t>Southern Rock, Blues Rock [Boogie Rock, Early Southern Rock]</t>
+  </si>
+  <si>
+    <t>Southern Rock, Hard Rock [Hard Southern Rock, Political Rock]</t>
+  </si>
+  <si>
+    <t>Southern Rock, Blues Rock [Live Boogie Rock, Barroom Rock]</t>
+  </si>
+  <si>
+    <t>Southern Rock, Pop Rock [Radio-friendly Southern Rock, Boogie Rock]</t>
+  </si>
+  <si>
+    <t>Southern Rock, Blues Rock [Piano-driven Southern Rock, Duet Rock]</t>
+  </si>
+  <si>
+    <t>Southern Rock, Hard Rock [Hard Southern Rock, Defiant Rock]</t>
+  </si>
+  <si>
+    <t>Southern Rock, Country Rock [Southern Rock Anthem, Blues Rock]</t>
+  </si>
+  <si>
+    <t>Southern Rock, Blues Rock [Epic Southern Rock, Live Guitar Jam]</t>
+  </si>
+  <si>
+    <t>Southern Rock, Hard Rock [Dark Southern Rock, Cautionary Rock]</t>
+  </si>
+  <si>
+    <t>Southern Rock, Blues Rock [Hard Southern Rock, Boogie Rock]</t>
+  </si>
+  <si>
+    <t>Southern Rock, Blues Rock [Live Boogie Rock, Early Southern Rock]</t>
+  </si>
+  <si>
+    <t>Southern Rock, Hard Rock [Boogie Rock, Road Rock]</t>
+  </si>
+  <si>
+    <t>Southern Rock, Folk Rock [Southern Rock Ballad, Acoustic Rock]</t>
+  </si>
+  <si>
+    <t>Southern Rock, Blues Rock [Piano Rock, Boogie Rock, Steve Gaines Showcase]</t>
+  </si>
+  <si>
+    <t>Southern Rock, Country Rock [Southern Rock Ballad, Piano-led Epic]</t>
+  </si>
+  <si>
+    <t>Southern Rock, Blues Rock [Roots Rock, Guitar-driven Southern Rock]</t>
+  </si>
+  <si>
+    <t>Πρώιμο, ζωηρό boogie track που συστήνει την μπάντα πριν αποκτήσει πλήρως το μυθικό της status. Μιλά για την τοπική ζωή, τη διασκέδαση και τη Southern ταυτότητα με χαλαρό groove και ωμή bar-band αμεσότητα.</t>
+  </si>
+  <si>
+    <t>Βαρύ hard-Southern-rock κομμάτι με έναν από τους πιο ξεκάθαρους κοινωνικούς στίχους του Van Zant. Η προειδοποίηση απέναντι στην εύκολη πρόσβαση σε όπλα και στη βία έρχεται μέσα από riff που έχει σχεδόν metal punch, αποδεικνύοντας ότι οι Skynyrd δεν ήταν μόνο party road band.</t>
+  </si>
+  <si>
+    <t>Η live εκτέλεση ενισχύει το χιούμορ και την ταχύτητα της ιστορίας: ένας αφηγητής προσπαθεί να ξεφύγει από έναν οργισμένο σύζυγο ζητώντας μόνο «τρία βήματα» προς την έξοδο. Η μπάντα μετατρέπει το barroom anecdote σε ξέφρενο boogie sing-along.</t>
+  </si>
+  <si>
+    <t>Εξωστρεφές, ραδιοφωνικά άμεσο Southern Rock με σαρκασμό για τις περιστασιακές, ανώνυμες συναντήσεις της περιοδείας. Κάτω από το ανάλαφρο hook υπάρχει η κούραση της διαρκούς μετακίνησης και μιας ζωής όπου οι σχέσεις συχνά μένουν μόνο ονόματα.</t>
+  </si>
+  <si>
+    <t>Η χαρακτηριστική συνεργασία Ronnie Van Zant–Steve Gaines. Το πιάνο, οι αλληλοσυμπληρούμενες φωνές και το αποφασιστικό riff κάνουν το κομμάτι δήλωση αυτοπεποίθησης, αλλά και ένα συγκινητικό ντοκουμέντο της τελευταίας μεγάλης δημιουργικής περιόδου του συγκροτήματος.</t>
+  </si>
+  <si>
+    <t>Τελικό roots-rock κομμάτι που δίνει στη συλλογή μια αίσθηση επιστροφής μετά από όλη την ένταση, τη βία, την περιπλάνηση και την απώλεια. Η «επιστροφή» δεν είναι απλώς γεωγραφική· είναι η επιθυμία να ξαναβρείς σταθερότητα έπειτα από μια ζωή στον δρόμο.</t>
+  </si>
+  <si>
+    <t>Μεγάλη, μελαγχολική μπαλάντα για αναχώρηση, απώλεια και την αναπόφευκτη κίνηση του χρόνου. Η σταδιακή ανάπτυξη των πλήκτρων, των κιθάρων και της φωνής του Van Zant δείχνει την ικανότητα της μπάντας να δημιουργεί ατμόσφαιρα χωρίς να χάνει τη γείωσή της στο blues.</t>
+  </si>
+  <si>
+    <t>Η πιο ξεκάθαρη βιτρίνα του Steve Gaines ως κιθαρίστα, τραγουδιστή και συνθέτη. Το title hook είναι παιχνιδιάρικο, το piano/boogie groove καταιγιστικό, ενώ τα solos δείχνουν πώς ο Gaines έφερε νέα, πιο κοφτερή ενέργεια στους Skynyrd λίγο πριν από την τραγωδία.</t>
+  </si>
+  <si>
+    <t>Μία από τις πιο καθαρές ηθικές διατυπώσεις του Ronnie Van Zant. Η μητρική συμβουλή να ζεις με τιμιότητα, ταπεινότητα και αυτογνωσία μετατρέπεται σε διαχρονική Southern Rock μπαλάντα. Η δύναμή της βρίσκεται στην απλότητα, ακουστική κιθάρα, πιάνο και σταδιακή συγκινησιακή κορύφωση.</t>
+  </si>
+  <si>
+    <t>Road-rock κομμάτι για τον τρόπο ζωής του μουσικού που ζει για το βράδυ, το ποτό, την περιοδεία και την ένταση της σκηνής. Είναι λιγότερο περίπλοκο στιχουργικά, αλλά αποτυπώνει άριστα την κινητική, boogie πλευρά της μπάντας.</t>
+  </si>
+  <si>
+    <t>Επιστροφή στο πρώιμο Skynyrd boogie, με live attack και βρώμικο Southern swagger. Ο αφηγητής απορρίπτει την ιδέα ότι θα γίνει ο εύκολος στόχος ή ο άνθρωπος που θα δεχτεί παθητικά τη μεταχείριση των άλλων.</t>
+  </si>
+  <si>
+    <t>Δυναμικό, riff-driven Southern rocker με κυνηγητική ενέργεια. Αντλεί από blues και hard rock για να αφηγηθεί μια ζωή όπου η επιθυμία, ο ανταγωνισμός και η ανάγκη επιβίωσης λειτουργούν σαν μόνιμη καταδίωξη.</t>
+  </si>
+  <si>
+    <t>κοτεινή, απειλητική προειδοποίηση για την αυτοκαταστροφή από υπερβολές και ουσίες. Το χαρακτηριστικό riff κινείται σαν αργό, μοιραίο βήμα, ενώ η φράση “the smell of death surrounds you” δίνει στο τραγούδι τραγική βαρύτητα, ιδιαίτερα μετά τα γεγονότα του 1977.</t>
+  </si>
+  <si>
+    <t>Η live εκδοχή συλλαμβάνει την μπάντα στο φυσικό της πεδίο, μια μπαλάντα για την αδυναμία δέσμευσης μετατρέπεται σε πολυκιθαριστικό, κλιμακούμενο jam. Το σημείο όπου το τραγούδι περνά από την ευάλωτη εξομολόγηση στην κιθαριστική καταιγίδα είναι ο πυρήνας της Skynyrd μυθολογίας.</t>
+  </si>
+  <si>
+    <t>Ο απόλυτος Southern Rock ύμνος, με το piano hook, τις κιθάρες και τις αντιπαραθέσεις/αναφορές προς Neil Young να δημιουργούν ένα τραγούδι ταυτότητας. Παρά την ενίοτε απλουστευτική πρόσληψή του, μουσικά είναι αριστοτεχνικό κράμα country, blues και rock: κάθε όργανο υπηρετεί το groove χωρίς περιττή επίδειξη.</t>
+  </si>
+  <si>
+    <t>Σκληρό, επιθετικό τραγούδι για την ανάγκη να πάρεις πίσω τη δύναμή σου μετά από ήττα ή αμφισβήτηση. Οι "σφαίρες" είναι μεταφορικές, η μπάντα ζητά πίσω το δικαίωμα να απαντήσει, να επιστρέψει και να μην παραμείνει στόχος.</t>
   </si>
 </sst>
 </file>
@@ -5914,7 +6079,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -7624,6 +7789,38 @@
       </c>
       <c r="J53" s="11" t="s">
         <v>1636</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+      <c r="A54" s="6">
+        <v>13795818</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>1686</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>1687</v>
+      </c>
+      <c r="D54" s="6">
+        <v>1979</v>
+      </c>
+      <c r="E54" s="10">
+        <v>3.96</v>
+      </c>
+      <c r="F54" s="9" t="s">
+        <v>1708</v>
+      </c>
+      <c r="G54" s="7" t="s">
+        <v>1689</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>1688</v>
+      </c>
+      <c r="I54" s="11" t="s">
+        <v>1707</v>
+      </c>
+      <c r="J54" s="11" t="s">
+        <v>1706</v>
       </c>
     </row>
   </sheetData>
@@ -7730,6 +7927,8 @@
     <hyperlink ref="I52" r:id="rId100" xr:uid="{3E32E8C7-A58A-4A22-A76D-04BAE7EC648B}"/>
     <hyperlink ref="J53" r:id="rId101" xr:uid="{78696536-2EE3-4E1E-BE35-3104DCC74F14}"/>
     <hyperlink ref="I53" r:id="rId102" xr:uid="{1357F0CA-ED11-4C8F-A624-FF42D1B7FDB5}"/>
+    <hyperlink ref="J54" r:id="rId103" xr:uid="{F0EEEEEF-EBE5-4544-B8BA-8E931925B446}"/>
+    <hyperlink ref="I54" r:id="rId104" xr:uid="{4334CF94-C610-4B1A-A4D2-6CD9050589CA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7737,7 +7936,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I472"/>
+  <dimension ref="A1:I488"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -20562,6 +20761,456 @@
       </c>
       <c r="I472" s="6"/>
     </row>
+    <row r="473" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A473" s="6">
+        <v>13795818</v>
+      </c>
+      <c r="B473" s="6">
+        <v>1</v>
+      </c>
+      <c r="C473" s="5" t="s">
+        <v>1690</v>
+      </c>
+      <c r="D473" s="7" t="s">
+        <v>1709</v>
+      </c>
+      <c r="E473" s="20">
+        <v>3.31</v>
+      </c>
+      <c r="F473" s="12">
+        <v>4</v>
+      </c>
+      <c r="G473" s="12">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="H473" s="7" t="s">
+        <v>1725</v>
+      </c>
+      <c r="I473" s="6"/>
+    </row>
+    <row r="474" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A474" s="6">
+        <v>13795818</v>
+      </c>
+      <c r="B474" s="6">
+        <v>2</v>
+      </c>
+      <c r="C474" s="7" t="s">
+        <v>1691</v>
+      </c>
+      <c r="D474" s="7" t="s">
+        <v>1710</v>
+      </c>
+      <c r="E474" s="20">
+        <v>3.97</v>
+      </c>
+      <c r="F474" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G474" s="12">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="H474" s="7" t="s">
+        <v>1726</v>
+      </c>
+      <c r="I474" s="6"/>
+    </row>
+    <row r="475" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A475" s="6">
+        <v>13795818</v>
+      </c>
+      <c r="B475" s="6">
+        <v>3</v>
+      </c>
+      <c r="C475" s="7" t="s">
+        <v>1692</v>
+      </c>
+      <c r="D475" s="7" t="s">
+        <v>1711</v>
+      </c>
+      <c r="E475" s="20">
+        <v>3.78</v>
+      </c>
+      <c r="F475" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G475" s="12">
+        <v>4.25</v>
+      </c>
+      <c r="H475" s="7" t="s">
+        <v>1727</v>
+      </c>
+      <c r="I475" s="6"/>
+    </row>
+    <row r="476" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A476" s="6">
+        <v>13795818</v>
+      </c>
+      <c r="B476" s="6">
+        <v>4</v>
+      </c>
+      <c r="C476" s="7" t="s">
+        <v>1693</v>
+      </c>
+      <c r="D476" s="7" t="s">
+        <v>1712</v>
+      </c>
+      <c r="E476" s="20">
+        <v>3.67</v>
+      </c>
+      <c r="F476" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G476" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H476" s="7" t="s">
+        <v>1728</v>
+      </c>
+      <c r="I476" s="6"/>
+    </row>
+    <row r="477" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A477" s="6">
+        <v>13795818</v>
+      </c>
+      <c r="B477" s="6">
+        <v>5</v>
+      </c>
+      <c r="C477" s="7" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D477" s="7" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E477" s="20">
+        <v>3.65</v>
+      </c>
+      <c r="F477" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G477" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H477" s="7" t="s">
+        <v>1729</v>
+      </c>
+      <c r="I477" s="6"/>
+    </row>
+    <row r="478" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A478" s="6">
+        <v>13795818</v>
+      </c>
+      <c r="B478" s="6">
+        <v>6</v>
+      </c>
+      <c r="C478" s="7" t="s">
+        <v>1695</v>
+      </c>
+      <c r="D478" s="7" t="s">
+        <v>1714</v>
+      </c>
+      <c r="E478" s="20">
+        <v>3.86</v>
+      </c>
+      <c r="F478" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G478" s="12">
+        <v>4.25</v>
+      </c>
+      <c r="H478" s="7" t="s">
+        <v>1740</v>
+      </c>
+      <c r="I478" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="479" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A479" s="6">
+        <v>13795818</v>
+      </c>
+      <c r="B479" s="6">
+        <v>7</v>
+      </c>
+      <c r="C479" s="7" t="s">
+        <v>1696</v>
+      </c>
+      <c r="D479" s="7" t="s">
+        <v>1715</v>
+      </c>
+      <c r="E479" s="20">
+        <v>4.07</v>
+      </c>
+      <c r="F479" s="12">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G479" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H479" s="7" t="s">
+        <v>1739</v>
+      </c>
+      <c r="I479" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="480" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A480" s="6">
+        <v>13795818</v>
+      </c>
+      <c r="B480" s="6">
+        <v>8</v>
+      </c>
+      <c r="C480" s="7" t="s">
+        <v>1697</v>
+      </c>
+      <c r="D480" s="7" t="s">
+        <v>1716</v>
+      </c>
+      <c r="E480" s="20">
+        <v>4.6100000000000003</v>
+      </c>
+      <c r="F480" s="12">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G480" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H480" s="7" t="s">
+        <v>1738</v>
+      </c>
+      <c r="I480" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="481" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A481" s="6">
+        <v>13795818</v>
+      </c>
+      <c r="B481" s="6">
+        <v>9</v>
+      </c>
+      <c r="C481" s="7" t="s">
+        <v>1698</v>
+      </c>
+      <c r="D481" s="7" t="s">
+        <v>1717</v>
+      </c>
+      <c r="E481" s="20">
+        <v>4.07</v>
+      </c>
+      <c r="F481" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G481" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H481" s="7" t="s">
+        <v>1737</v>
+      </c>
+      <c r="I481" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="482" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A482" s="6">
+        <v>13795818</v>
+      </c>
+      <c r="B482" s="6">
+        <v>10</v>
+      </c>
+      <c r="C482" s="7" t="s">
+        <v>1699</v>
+      </c>
+      <c r="D482" s="7" t="s">
+        <v>1718</v>
+      </c>
+      <c r="E482" s="20">
+        <v>3.83</v>
+      </c>
+      <c r="F482" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G482" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H482" s="7" t="s">
+        <v>1736</v>
+      </c>
+      <c r="I482" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="483" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A483" s="6">
+        <v>13795818</v>
+      </c>
+      <c r="B483" s="6">
+        <v>11</v>
+      </c>
+      <c r="C483" s="7" t="s">
+        <v>1700</v>
+      </c>
+      <c r="D483" s="7" t="s">
+        <v>1719</v>
+      </c>
+      <c r="E483" s="20">
+        <v>3.79</v>
+      </c>
+      <c r="F483" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G483" s="12">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="H483" s="7" t="s">
+        <v>1735</v>
+      </c>
+      <c r="I483" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="484" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A484" s="6">
+        <v>13795818</v>
+      </c>
+      <c r="B484" s="6">
+        <v>12</v>
+      </c>
+      <c r="C484" s="7" t="s">
+        <v>1701</v>
+      </c>
+      <c r="D484" s="7" t="s">
+        <v>1720</v>
+      </c>
+      <c r="E484" s="20">
+        <v>3.55</v>
+      </c>
+      <c r="F484" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G484" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H484" s="7" t="s">
+        <v>1734</v>
+      </c>
+      <c r="I484" s="6"/>
+    </row>
+    <row r="485" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A485" s="6">
+        <v>13795818</v>
+      </c>
+      <c r="B485" s="6">
+        <v>13</v>
+      </c>
+      <c r="C485" s="7" t="s">
+        <v>1702</v>
+      </c>
+      <c r="D485" s="7" t="s">
+        <v>1721</v>
+      </c>
+      <c r="E485" s="20">
+        <v>4.37</v>
+      </c>
+      <c r="F485" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="G485" s="12">
+        <v>4.45</v>
+      </c>
+      <c r="H485" s="7" t="s">
+        <v>1733</v>
+      </c>
+      <c r="I485" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="486" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A486" s="6">
+        <v>13795818</v>
+      </c>
+      <c r="B486" s="6">
+        <v>14</v>
+      </c>
+      <c r="C486" s="7" t="s">
+        <v>1703</v>
+      </c>
+      <c r="D486" s="7" t="s">
+        <v>1722</v>
+      </c>
+      <c r="E486" s="20">
+        <v>3.68</v>
+      </c>
+      <c r="F486" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G486" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H486" s="7" t="s">
+        <v>1732</v>
+      </c>
+      <c r="I486" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="487" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A487" s="6">
+        <v>13795818</v>
+      </c>
+      <c r="B487" s="6">
+        <v>15</v>
+      </c>
+      <c r="C487" s="7" t="s">
+        <v>1704</v>
+      </c>
+      <c r="D487" s="7" t="s">
+        <v>1723</v>
+      </c>
+      <c r="E487" s="20">
+        <v>4.28</v>
+      </c>
+      <c r="F487" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="G487" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H487" s="7" t="s">
+        <v>1731</v>
+      </c>
+      <c r="I487" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="488" spans="1:9" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A488" s="6">
+        <v>13795818</v>
+      </c>
+      <c r="B488" s="6">
+        <v>16</v>
+      </c>
+      <c r="C488" s="7" t="s">
+        <v>1705</v>
+      </c>
+      <c r="D488" s="7" t="s">
+        <v>1724</v>
+      </c>
+      <c r="E488" s="20">
+        <v>3.8</v>
+      </c>
+      <c r="F488" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G488" s="12">
+        <v>4.25</v>
+      </c>
+      <c r="H488" s="7" t="s">
+        <v>1730</v>
+      </c>
+      <c r="I488" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98CE0183-666E-42CC-8651-911FE277A347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{203FEB17-8E28-4348-A49F-13BF1F0DA95A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1936" uniqueCount="1741">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2008" uniqueCount="1810">
   <si>
     <t>No</t>
   </si>
@@ -5410,9 +5410,6 @@
     <t>MCA Records – 250 413-1, Europe, Reissue, Gatefold (2xLP)</t>
   </si>
   <si>
-    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Ευρωπαϊκή έκδοση της δεκαετίας του '80 (με barcode 0 2292-50413-1 και γαλλικό price code WE 332), τυπωμένη και κομμένη στη Γερμανία από την R/S Alsdorf. Η συγκεκριμένη κοπή φέρει τις χαρακτηριστικές μήτρες χαραγμένες στο runout (250413-1), προσφέροντας εξαιρετική δυναμική, καθαρότητα στα διπλά κιθαριστικά σόλο και συμπαγή απόδοση στις χαμηλές συχνότητες του κλασικού Southern Rock.</t>
-  </si>
-  <si>
     <t>Down South Jukin'</t>
   </si>
   <si>
@@ -5564,6 +5561,246 @@
   </si>
   <si>
     <t>Σκληρό, επιθετικό τραγούδι για την ανάγκη να πάρεις πίσω τη δύναμή σου μετά από ήττα ή αμφισβήτηση. Οι "σφαίρες" είναι μεταφορικές, η μπάντα ζητά πίσω το δικαίωμα να απαντήσει, να επιστρέψει και να μην παραμείνει στόχος.</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Ευρωπαϊκή έκδοση κυκλοφορίας 1984 (με barcode 0 2292-50413-1 και γαλλικό price code WE 332), τυπωμένη και κομμένη στη Γερμανία από την R/S Alsdorf. Η συγκεκριμένη κοπή φέρει τις χαρακτηριστικές μήτρες χαραγμένες στο runout (250413-1), προσφέροντας εξαιρετική δυναμική, καθαρότητα στα διπλά κιθαριστικά σόλο και συμπαγή απόδοση στις χαμηλές συχνότητες του κλασικού Southern Rock.</t>
+  </si>
+  <si>
+    <t>Krokus</t>
+  </si>
+  <si>
+    <t>Pay It In Metal</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/Pl0q3jrIM9ytxphf_YazmZUpMyRvHBBXVo5Fy7FOCYo/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTExMDA3/MTA2LTE1MDgxMDMz/NjItODc4OS5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/11007106-Krokus-Pay-It-In-Metal</t>
+  </si>
+  <si>
+    <t>Mercury – 6367 012, Netherlands, LP, Album, Reissue (Banana Cover), 1978</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Ολλανδική έκδοση του 1978 με το εμβληματικό "banana" εξώφυλλο (μεταγενέστερη παραλλαγή μετά την αρχική κυκλοφορία του Pain Killer με τον κωδικό 6326 800). Κομμένο και τυπωμένο στην Ολλανδία (Phonogram), διαθέτει ωμή, δυναμική hard rock/heavy metal παραγωγή της εποχής, γεμάτη ενέργεια και αυθεντικό αναλογικό χαρακτήρα.</t>
+  </si>
+  <si>
+    <t>Werewolf</t>
+  </si>
+  <si>
+    <t>Rock Ladies</t>
+  </si>
+  <si>
+    <t>Bad Love</t>
+  </si>
+  <si>
+    <t>Get Out of My Mind</t>
+  </si>
+  <si>
+    <t>Rock Me, Rock You</t>
+  </si>
+  <si>
+    <t>Deadline</t>
+  </si>
+  <si>
+    <t>Susie</t>
+  </si>
+  <si>
+    <t>Pay It</t>
+  </si>
+  <si>
+    <t>Bye Bye Baby</t>
+  </si>
+  <si>
+    <t>Σφιχτό εναρκτήριο hard-rock κομμάτι, χτισμένο πάνω σε ευθύ riff και κοφτές ρυθμικές αλλαγές. Ο τίτλος λειτουργεί ως εικόνα μιας επικίνδυνης δύναμης ή προσώπου που έλκει και απειλεί ταυτόχρονα, ενώ η μπάντα εισάγει τον proto-metal τόνο του δίσκου.</t>
+  </si>
+  <si>
+    <t>Πιο σκοτεινό και θεατρικό, χρησιμοποιεί τον λυκάνθρωπο ως σύμβολο ανεξέλεγκτης επιθυμίας και νυχτερινής μεταμόρφωσης. Η κιθάρα και το πιο βαριά τονισμένο rhythm section δίνουν στο κομμάτι early-metal ένταση, χωρίς να χάνει το 70s hard-rock swing.</t>
+  </si>
+  <si>
+    <t>Ανάλαφρο, boogie-driven τραγούδι για τη rock ’n’ roll κοινωνικότητα, τη σκηνή και την ερωτική ενέργεια του δρόμου. Είναι από τις πιο απλές συνθέσεις του δίσκου, με glam/party-rock πνεύμα και άμεσο sing-along χαρακτήρα.</t>
+  </si>
+  <si>
+    <t>Γρήγορο hard-rock ξέσπασμα για την αδυναμία να αποβάλεις μια επίμονη σκέψη ή πρόσωπο. Ο ρυθμός είναι πιο επιθετικός και λειτουργεί σαν άμεση προσπάθεια ψυχικής εκτόνωσης.</t>
+  </si>
+  <si>
+    <t>Τυπικό boogie/party-rock cut, με λιτό hook και ρυθμό σχεδιασμένο για ζωντανή εκτέλεση. Δεν έχει τη σκοτεινή χροιά των πιο βαριών κομματιών, αλλά δείχνει την προδιάθεση των Krokus για ευθύ, crowd-oriented hard rock.</t>
+  </si>
+  <si>
+    <t>Σύντομη, κοφτή σύνθεση με αίσθηση βιασύνης και πίεσης. Ο τίτλος γίνεται μεταφορά για τον χρόνο που τελειώνει και για μια κατάσταση όπου η απόφαση δεν μπορεί πλέον να αναβληθεί.</t>
+  </si>
+  <si>
+    <t>Μελαγχολικότερο και πιο bluesy φινάλε. Η αποχαιρετιστήρια ιστορία του τίτλου επιτρέπει στη μπάντα να κλείσει με περισσότερο συναίσθημα και λιγότερη καθαρή επίθεση, αφήνοντας ανοιχτό το πέρασμα από το hard-rock party κλίμα σε πιο ώριμη, βαριά ερμηνεία.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve">Heavy rock με proto-metal προσανατολισμό, όπου η έννοια του τίτλου παραπέμπει στο τίμημα πράξεων και επιλογών. Είναι η σύνθεση που έδωσε το εναλλακτικό διεθνές όνομα </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Pay It in Metal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> στο άλμπουμ, κάτι που ταιριάζει στην πιο σκληρή, metallic πλευρά του υλικού.</t>
+    </r>
+  </si>
+  <si>
+    <t>Μελωδικότερο, blues-χρωματισμένο hard-rock τραγούδι, που χρησιμοποιεί ένα γυναικείο όνομα για να σκιαγραφήσει ερωτική έλξη και συναισθηματική αστάθεια. Το πιο light groove του προσφέρει ανάσα πριν από το βαρύτερο κλείσιμο.</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Proto-Metal, Boogie Rock, Swiss Hard Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Proto-Metal, Riff-driven Hard Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Dark Hard Rock, Early Heavy Metal]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Rock &amp; Roll [Boogie Rock, Glam-tinged Hard Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Heavy Blues Rock, Slow-Burn Hard Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Fast Hard Rock, Proto-Metal]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Short Heavy Rock, Proto-Punk-tinged Metal]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Melodic Hard Rock, Blues Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Proto-Metal, Heavy Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Heavy Blues Ballad, Closing Hard Rock]</t>
+  </si>
+  <si>
+    <t>Η μεγάλη εξαίρεση μέσα στο ωμό, riff-driven περιβάλλον του Pain Killer. Εκεί όπου τα περισσότερα κομμάτια του δίσκου κινούνται με boogie επιθετικότητα και proto-metal αμεσότητα, το Bad Love χαμηλώνει τον ρυθμό και μετατρέπει το hard rock σε μια αίσθηση συναισθηματικού εγκλωβισμού. Δεν είναι κλασική power ballad, ο όρος δεν είχε ακόμη αποκτήσει τη μεταγενέστερη, γυαλισμένη μορφή του, αλλά ένα slow-burn blues-rock δράμα, στο οποίο κάθε κιθαριστική φράση και κάθε παύση έχουν περισσότερο βάρος από ένα εύκολο, μεγάλο chorus. Η μουσική στήνεται πάνω σε αργό, βαρύ groove. Το rhythm section δεν προσπαθεί να γεμίσει κάθε διαθέσιμο χώρο· λειτουργεί σαν σταθερή, σχεδόν μοιραία κίνηση, αφήνοντας την κιθάρα του Fernando von Arb να εκτεθεί. Ο von Arb δεν ποντάρει στην ταχύτητα ή στη βιρτουοζιτέ. Χρησιμοποιεί μακρόσυρτα bends, sustain και blues φράσεις που ακούγονται σαν απαντήσεις σε μια φωνή που δεν μπορεί να βρει διέξοδο. Η κιθάρα δεν «σολάρει πάνω» από το τραγούδι· μιλά μαζί του. Η σύνθεση έχει μια πολύ συγκεκριμένη εσωτερική ένταση: από τη μία η ανάγκη για σύνδεση, από την άλλη η επίγνωση ότι αυτή η σύνδεση είναι δηλητηριώδης. Αυτό είναι το ουσιαστικό νόημα του τίτλου “Bad Love”. Δεν πρόκειται απλώς για έναν αποτυχημένο έρωτα ή μια συνηθισμένη ρήξη. Είναι μια σχέση που ασκεί έλξη ακριβώς επειδή είναι επιβλαβής, μια αγάπη που παραμένει ισχυρή, ενώ ταυτόχρονα αποδυναμώνει, απομονώνει και τραυματίζει. Ο Chris von Rohr, με την τραχιά και λιγότερο "γυαλισμένη" φωνή του σε σχέση με τον μετέπειτα Marc Storace, δίνει στο κομμάτι σημαντικό μέρος της ταυτότητάς του. Η ερμηνεία δεν ακούγεται σαν θεατρικός θρήνος· ακούγεται σαν ένας άνθρωπος που έχει ήδη κουραστεί από την ίδια σύγκρουση και δεν είναι βέβαιος αν έχει τη δύναμη να φύγει. Αυτή η αστάθεια, ανάμεσα στην οργή, τη λαχτάρα και την παραίτηση, κάνει το τραγούδι πολύ πιο ανθρώπινο από αρκετές hard-rock μπαλάντες της περιόδου. Το Bad Love ανήκει στην ευρύτερη 70s blues-hard-rock παράδοση όπου η αργή ένταση είναι σημαντικότερη από την εντυπωσιακή κορύφωση: μπορεί να σταθεί δίπλα σε πιο βαριές στιγμές των UFO, Nazareth, Scorpions της προ-’80s περιόδου ή ακόμη και σε bluesier Deep Purple/Rainbow πλευρές, χωρίς να μιμείται κάποιο από αυτά τα σχήματα. Η δύναμή του είναι ότι παραμένει καθαρά Krokus του 1978: λιγότερο στιλπνό από το μετέπειτα mainstream heavy rock τους, αλλά πιο εύθραυστο και πιο ανεπεξέργαστο. Είναι επίσης κομβικό τραγούδι για να καταλάβει κανείς τι χάθηκε όταν η μπάντα, στα επόμενα άλμπουμ, κατευθύνθηκε σε πιο σαφές, AC/DC-συγγενές hard-rock μοντέλο. Εκείνοι οι δίσκοι μπορεί να είναι πιο συνεπείς σε riffs και singles, όμως το Bad Love αποκαλύπτει μια πιο ανοιχτή πλευρά των Krokus: blues βάρος, αργή δραματουργία και προθυμία να αφήσουν ένα τραγούδι να αναπνέει αντί να το πιέσουν σε άμεση εμπορική φόρμα.</t>
+  </si>
+  <si>
+    <t>Cold As Weiss</t>
+  </si>
+  <si>
+    <t>Delvon Lamarr Organ Trio</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/4bHh8ysHICh9UunuNC8usYoFBl69C02j0N9oQ-h12R0/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTIyMTAw/Mzc3LTE3MTYyMjE5/OTItNTMyMC5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/22100377-Delvon-Lamarr-Organ-Trio-Cold-As-Weiss</t>
+  </si>
+  <si>
+    <t>Colemine Records – CLMN-12029, USA, LP, Album, Gatefold, 2022</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Αμερικανική έκδοση του 2022 σε gatefold εξώφυλλο. Mastered από τον Doug Krebs, lacquer cut από τον mf στο Well Made Music και pressing από τη Gotta Groove Records. Οργανικό soul-jazz / funk υψηλών προδιαγραφών με τεράστιο δυναμικό εύρος και κορυφαία αναλογική πιστότητα.</t>
+  </si>
+  <si>
+    <t>Pull Your Pants Up</t>
+  </si>
+  <si>
+    <t>Don't Worry 'Bout What I Do</t>
+  </si>
+  <si>
+    <t>I Wanna Be Where You Are</t>
+  </si>
+  <si>
+    <t>Big TT's Blues</t>
+  </si>
+  <si>
+    <t>Get Da Steppin'</t>
+  </si>
+  <si>
+    <t>Uncertainty</t>
+  </si>
+  <si>
+    <t>Keep On Keepin' On</t>
+  </si>
+  <si>
+    <t>Slip 'N' Slide</t>
+  </si>
+  <si>
+    <t>This Is Who I Is</t>
+  </si>
+  <si>
+    <t>Soul Jazz, Instrumental Funk [Hammond B3 Organ Trio, Jazz Funk, Deep Funk]</t>
+  </si>
+  <si>
+    <t>Instrumental Funk, Soul Jazz [Hammond Funk, Deep Funk (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Soul Jazz, Jazz Funk [Organ Soul, Melodic Jazz Funk (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Soul Jazz, Instrumental Funk [Soul-Jazz Cover, Hammond R&amp;B (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Blues, Soul Jazz [Organ Blues, Extended Soul-Jazz Jam (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Instrumental Funk, Jazz Funk [Up-tempo Organ Funk, Deep Funk (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Soul Jazz, Jazz Funk [Cinematic Soul-Jazz, Minor-key Organ Groove (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Instrumental Funk, Soul Jazz [Feel-good Organ Funk, R&amp;B Groove (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Instrumental Funk, Rhythm &amp; Blues [New Orleans Funk, Hammond Groove (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Soul Jazz, Blues [Slow-Burn Organ Soul, Bluesy Jazz Funk (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Δυναμικό opening statement με κοφτό Hammond riff, σφιχτά drums και κιθάρα που παρεμβαίνει με μικρές, funk-ακριβείς φράσεις. Ο τίτλος έχει χιουμοριστικό street-funk χαρακτήρα και η μουσική λειτουργεί σαν άμεση πρόσκληση για κίνηση. [Instrumental]</t>
+  </si>
+  <si>
+    <t>Η πιο εκτεταμένη σύνθεση, περίπου έξιμισι λεπτών, και ουσιαστικά το κεντρικό jam του δίσκου. Το αργό, bluesy tempo επιτρέπει στο Hammond να χτίσει χαμηλές γραμμές και γκρίζες αρμονίες, ενώ η κιθάρα του Jimmy James περνά από κοφτά R&amp;B stabs σε πιο εκφραστικές blues φράσεις. Αντί για επίδειξη, το trio δουλεύει με υπομονή και αφήνει το groove να βαθύνει. [Instrumental]</t>
+  </si>
+  <si>
+    <t>Πιο γρήγορο, χορευτικό deep-funk κομμάτι, με επίμονη bass line από το Hammond και drums που σπρώχνουν την κίνηση προς τα εμπρός. Το θέμα είναι λιτό, αλλά οι μικρές αλλαγές έντασης και οι κιθαριστικές απαντήσεις το κρατούν ζωντανό. [Instrumental]</t>
+  </si>
+  <si>
+    <t>Πιο σκοτεινό και στοχαστικό, με minor-key χρώμα και κινηματογραφική ατμόσφαιρα. Η «αβεβαιότητα» δεν εκφράζεται με χαοτική γραφή, αλλά με μελωδίες που δεν λύνονται αμέσως και με ένα groove που μοιάζει να προχωρά προσεκτικά μέσα σε μισοσκόταδο. [Instrumental]</t>
+  </si>
+  <si>
+    <t>Φωτεινό, σταθερό και αισιόδοξο organ-funk. Ο τίτλος εκφράζεται μέσα από την επιμονή του ρυθμού: δεν υπάρχουν δραματικές αλλαγές, μόνο ένα groove που συνεχίζει να βρίσκει νέες λεπτομέρειες όσο προχωρά. [Instrumental]</t>
+  </si>
+  <si>
+    <t>Αργό, μπλουζικό και συναισθηματικά πιο βαρύ κλείσιμο. Το Hammond κινείται σαν ανθρώπινη φωνή, η κιθάρα αποφεύγει την υπερβολή και τα drums κρατούν μια διακριτική, υπομονετική βάση. Ο ανορθόγραφος, προφορικός τίτλος ταιριάζει με το νόημα της μουσικής: μια δήλωση ταυτότητας χωρίς επίδειξη, με αποδοχή της ατέλειας και του προσωπικού ύφους. [Instrumental]</t>
+  </si>
+  <si>
+    <t>Slip 'N' Slide: Γρήγορη, παιχνιδιάρικη σύνθεση με New Orleans/R&amp;B ευελιξία. Η κιθάρα γλιστρά γύρω από το Hammond, ενώ τα drums κρατούν μια ελαφριά, σχεδόν χορευτική κίνηση. Είναι από τα κομμάτια που δείχνουν καλύτερα τη χημεία του trio ως live-like ensemble. [Instrumental]</t>
+  </si>
+  <si>
+    <t>Instrumental προσέγγιση του τραγουδιού των Leon Ware και Arthur “T-Boy” Ross, γνωστού από την εκτέλεση του Michael Jackson. Το trio μεταφέρει το αρχικό soul συναίσθημα σε Hammond R&amp;B γλώσσα, αφήνοντας το B3 να «τραγουδά» τη μελωδία χωρίς να μιμείται το φωνητικό πρωτότυπο. [Instrumental]</t>
+  </si>
+  <si>
+    <t>Από τις πιο μελωδικές στιγμές του δίσκου. Το organ έχει σχεδόν φωνητικό ρόλο, η κιθάρα διαμορφώνει διακριτικά τις αρμονίες και το groove παραμένει ζεστό, χωρίς να βιάζεται. Είναι soul-jazz με αίσθηση προσωπικής αυτοπεποίθησης και ήρεμης ελευθερίας. [Instrumental]</t>
   </si>
 </sst>
 </file>
@@ -5712,7 +5949,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -5773,6 +6010,9 @@
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -6079,7 +6319,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -7808,19 +8048,83 @@
         <v>3.96</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>1689</v>
+        <v>1740</v>
       </c>
       <c r="H54" s="6" t="s">
         <v>1688</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>1706</v>
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+      <c r="A55" s="6">
+        <v>11007106</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>1741</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>1742</v>
+      </c>
+      <c r="D55" s="6">
+        <v>1978</v>
+      </c>
+      <c r="E55" s="10">
+        <v>2.9</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>1765</v>
+      </c>
+      <c r="G55" s="7" t="s">
+        <v>1746</v>
+      </c>
+      <c r="H55" s="6" t="s">
+        <v>1745</v>
+      </c>
+      <c r="I55" s="11" t="s">
+        <v>1744</v>
+      </c>
+      <c r="J55" s="11" t="s">
+        <v>1743</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+      <c r="A56" s="6">
+        <v>22100377</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>1777</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>1776</v>
+      </c>
+      <c r="D56" s="6">
+        <v>2022</v>
+      </c>
+      <c r="E56" s="10">
+        <v>3.39</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>1791</v>
+      </c>
+      <c r="G56" s="7" t="s">
+        <v>1781</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>1780</v>
+      </c>
+      <c r="I56" s="11" t="s">
+        <v>1779</v>
+      </c>
+      <c r="J56" s="11" t="s">
+        <v>1778</v>
       </c>
     </row>
   </sheetData>
@@ -7929,6 +8233,10 @@
     <hyperlink ref="I53" r:id="rId102" xr:uid="{1357F0CA-ED11-4C8F-A624-FF42D1B7FDB5}"/>
     <hyperlink ref="J54" r:id="rId103" xr:uid="{F0EEEEEF-EBE5-4544-B8BA-8E931925B446}"/>
     <hyperlink ref="I54" r:id="rId104" xr:uid="{4334CF94-C610-4B1A-A4D2-6CD9050589CA}"/>
+    <hyperlink ref="J55" r:id="rId105" xr:uid="{36CEEA26-13A0-4AFA-8ED6-B4B6BC4B51BA}"/>
+    <hyperlink ref="I55" r:id="rId106" xr:uid="{D4FD42AF-DC0B-41B1-A1CF-67D8689FA322}"/>
+    <hyperlink ref="J56" r:id="rId107" xr:uid="{879099B2-2A0C-40A7-8A67-6C10CBF856D5}"/>
+    <hyperlink ref="I56" r:id="rId108" xr:uid="{39AA173B-82EA-49C0-AB10-59F5102644AE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7936,7 +8244,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I488"/>
+  <dimension ref="A1:I507"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -7946,7 +8254,7 @@
     <col min="5" max="5" width="11" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.28515625" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="50.7109375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="65.7109375" style="3" customWidth="1"/>
     <col min="9" max="9" width="12.7109375" style="4" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="9.140625" style="3"/>
   </cols>
@@ -20769,10 +21077,10 @@
         <v>1</v>
       </c>
       <c r="C473" s="5" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="D473" s="7" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="E473" s="20">
         <v>3.31</v>
@@ -20784,7 +21092,7 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="H473" s="7" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="I473" s="6"/>
     </row>
@@ -20796,10 +21104,10 @@
         <v>2</v>
       </c>
       <c r="C474" s="7" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="D474" s="7" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="E474" s="20">
         <v>3.97</v>
@@ -20811,7 +21119,7 @@
         <v>4.3499999999999996</v>
       </c>
       <c r="H474" s="7" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="I474" s="6"/>
     </row>
@@ -20823,10 +21131,10 @@
         <v>3</v>
       </c>
       <c r="C475" s="7" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="D475" s="7" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="E475" s="20">
         <v>3.78</v>
@@ -20838,7 +21146,7 @@
         <v>4.25</v>
       </c>
       <c r="H475" s="7" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="I475" s="6"/>
     </row>
@@ -20850,10 +21158,10 @@
         <v>4</v>
       </c>
       <c r="C476" s="7" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="D476" s="7" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="E476" s="20">
         <v>3.67</v>
@@ -20865,7 +21173,7 @@
         <v>4.3</v>
       </c>
       <c r="H476" s="7" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="I476" s="6"/>
     </row>
@@ -20877,10 +21185,10 @@
         <v>5</v>
       </c>
       <c r="C477" s="7" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="D477" s="7" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="E477" s="20">
         <v>3.65</v>
@@ -20892,7 +21200,7 @@
         <v>4.2</v>
       </c>
       <c r="H477" s="7" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="I477" s="6"/>
     </row>
@@ -20904,10 +21212,10 @@
         <v>6</v>
       </c>
       <c r="C478" s="7" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="D478" s="7" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="E478" s="20">
         <v>3.86</v>
@@ -20919,7 +21227,7 @@
         <v>4.25</v>
       </c>
       <c r="H478" s="7" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="I478" s="6" t="s">
         <v>312</v>
@@ -20933,10 +21241,10 @@
         <v>7</v>
       </c>
       <c r="C479" s="7" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="D479" s="7" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="E479" s="20">
         <v>4.07</v>
@@ -20948,7 +21256,7 @@
         <v>4.5</v>
       </c>
       <c r="H479" s="7" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="I479" s="6" t="s">
         <v>312</v>
@@ -20962,10 +21270,10 @@
         <v>8</v>
       </c>
       <c r="C480" s="7" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="D480" s="7" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="E480" s="20">
         <v>4.6100000000000003</v>
@@ -20977,7 +21285,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H480" s="7" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="I480" s="6" t="s">
         <v>312</v>
@@ -20991,10 +21299,10 @@
         <v>9</v>
       </c>
       <c r="C481" s="7" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="D481" s="7" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="E481" s="20">
         <v>4.07</v>
@@ -21006,7 +21314,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H481" s="7" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="I481" s="6" t="s">
         <v>312</v>
@@ -21020,10 +21328,10 @@
         <v>10</v>
       </c>
       <c r="C482" s="7" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="D482" s="7" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="E482" s="20">
         <v>3.83</v>
@@ -21035,7 +21343,7 @@
         <v>4.3</v>
       </c>
       <c r="H482" s="7" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="I482" s="6" t="s">
         <v>312</v>
@@ -21049,10 +21357,10 @@
         <v>11</v>
       </c>
       <c r="C483" s="7" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="D483" s="7" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="E483" s="20">
         <v>3.79</v>
@@ -21064,7 +21372,7 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="H483" s="7" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="I483" s="6" t="s">
         <v>312</v>
@@ -21078,10 +21386,10 @@
         <v>12</v>
       </c>
       <c r="C484" s="7" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="D484" s="7" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="E484" s="20">
         <v>3.55</v>
@@ -21093,7 +21401,7 @@
         <v>4.2</v>
       </c>
       <c r="H484" s="7" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="I484" s="6"/>
     </row>
@@ -21105,10 +21413,10 @@
         <v>13</v>
       </c>
       <c r="C485" s="7" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="D485" s="7" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="E485" s="20">
         <v>4.37</v>
@@ -21120,7 +21428,7 @@
         <v>4.45</v>
       </c>
       <c r="H485" s="7" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="I485" s="6" t="s">
         <v>312</v>
@@ -21134,10 +21442,10 @@
         <v>14</v>
       </c>
       <c r="C486" s="7" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="D486" s="7" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="E486" s="20">
         <v>3.68</v>
@@ -21149,7 +21457,7 @@
         <v>4.3</v>
       </c>
       <c r="H486" s="7" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="I486" s="6" t="s">
         <v>312</v>
@@ -21163,10 +21471,10 @@
         <v>15</v>
       </c>
       <c r="C487" s="7" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="D487" s="7" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="E487" s="20">
         <v>4.28</v>
@@ -21178,7 +21486,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H487" s="7" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="I487" s="6" t="s">
         <v>312</v>
@@ -21192,10 +21500,10 @@
         <v>16</v>
       </c>
       <c r="C488" s="7" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="D488" s="7" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="E488" s="20">
         <v>3.8</v>
@@ -21207,9 +21515,524 @@
         <v>4.25</v>
       </c>
       <c r="H488" s="7" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="I488" s="6"/>
+    </row>
+    <row r="489" spans="1:9" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A489" s="6">
+        <v>11007106</v>
+      </c>
+      <c r="B489" s="6">
+        <v>1</v>
+      </c>
+      <c r="C489" s="7" t="s">
+        <v>803</v>
+      </c>
+      <c r="D489" s="7" t="s">
+        <v>1766</v>
+      </c>
+      <c r="E489" s="20">
+        <v>3.61</v>
+      </c>
+      <c r="F489" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="G489" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H489" s="7" t="s">
+        <v>1756</v>
+      </c>
+      <c r="I489" s="6"/>
+    </row>
+    <row r="490" spans="1:9" ht="53.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A490" s="6">
+        <v>11007106</v>
+      </c>
+      <c r="B490" s="6">
+        <v>2</v>
+      </c>
+      <c r="C490" s="7" t="s">
+        <v>1747</v>
+      </c>
+      <c r="D490" s="7" t="s">
+        <v>1767</v>
+      </c>
+      <c r="E490" s="20">
+        <v>3.55</v>
+      </c>
+      <c r="F490" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="G490" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H490" s="7" t="s">
+        <v>1757</v>
+      </c>
+      <c r="I490" s="6"/>
+    </row>
+    <row r="491" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A491" s="6">
+        <v>11007106</v>
+      </c>
+      <c r="B491" s="6">
+        <v>3</v>
+      </c>
+      <c r="C491" s="7" t="s">
+        <v>1748</v>
+      </c>
+      <c r="D491" s="7" t="s">
+        <v>1768</v>
+      </c>
+      <c r="E491" s="20">
+        <v>3.38</v>
+      </c>
+      <c r="F491" s="12">
+        <v>3.3</v>
+      </c>
+      <c r="G491" s="12">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="H491" s="7" t="s">
+        <v>1758</v>
+      </c>
+      <c r="I491" s="6"/>
+    </row>
+    <row r="492" spans="1:9" ht="408.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A492" s="6">
+        <v>11007106</v>
+      </c>
+      <c r="B492" s="6">
+        <v>4</v>
+      </c>
+      <c r="C492" s="21" t="s">
+        <v>1749</v>
+      </c>
+      <c r="D492" s="7" t="s">
+        <v>1769</v>
+      </c>
+      <c r="E492" s="20">
+        <v>3.6</v>
+      </c>
+      <c r="F492" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G492" s="12">
+        <v>4.25</v>
+      </c>
+      <c r="H492" s="7" t="s">
+        <v>1775</v>
+      </c>
+      <c r="I492" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="493" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A493" s="6">
+        <v>11007106</v>
+      </c>
+      <c r="B493" s="6">
+        <v>5</v>
+      </c>
+      <c r="C493" s="7" t="s">
+        <v>1750</v>
+      </c>
+      <c r="D493" s="7" t="s">
+        <v>1770</v>
+      </c>
+      <c r="E493" s="20">
+        <v>3.08</v>
+      </c>
+      <c r="F493" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="G493" s="12">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="H493" s="7" t="s">
+        <v>1759</v>
+      </c>
+      <c r="I493" s="6"/>
+    </row>
+    <row r="494" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A494" s="6">
+        <v>11007106</v>
+      </c>
+      <c r="B494" s="6">
+        <v>6</v>
+      </c>
+      <c r="C494" s="7" t="s">
+        <v>1751</v>
+      </c>
+      <c r="D494" s="7" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E494" s="20">
+        <v>3.26</v>
+      </c>
+      <c r="F494" s="12">
+        <v>3.4</v>
+      </c>
+      <c r="G494" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H494" s="7" t="s">
+        <v>1760</v>
+      </c>
+      <c r="I494" s="6"/>
+    </row>
+    <row r="495" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A495" s="6">
+        <v>11007106</v>
+      </c>
+      <c r="B495" s="6">
+        <v>7</v>
+      </c>
+      <c r="C495" s="7" t="s">
+        <v>1752</v>
+      </c>
+      <c r="D495" s="7" t="s">
+        <v>1771</v>
+      </c>
+      <c r="E495" s="20">
+        <v>3.18</v>
+      </c>
+      <c r="F495" s="12">
+        <v>3.3</v>
+      </c>
+      <c r="G495" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H495" s="7" t="s">
+        <v>1761</v>
+      </c>
+      <c r="I495" s="6"/>
+    </row>
+    <row r="496" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A496" s="6">
+        <v>11007106</v>
+      </c>
+      <c r="B496" s="6">
+        <v>8</v>
+      </c>
+      <c r="C496" s="7" t="s">
+        <v>1753</v>
+      </c>
+      <c r="D496" s="7" t="s">
+        <v>1772</v>
+      </c>
+      <c r="E496" s="20">
+        <v>3.04</v>
+      </c>
+      <c r="F496" s="12">
+        <v>3.4</v>
+      </c>
+      <c r="G496" s="12">
+        <v>4.25</v>
+      </c>
+      <c r="H496" s="7" t="s">
+        <v>1764</v>
+      </c>
+      <c r="I496" s="6"/>
+    </row>
+    <row r="497" spans="1:9" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A497" s="6">
+        <v>11007106</v>
+      </c>
+      <c r="B497" s="6">
+        <v>9</v>
+      </c>
+      <c r="C497" s="7" t="s">
+        <v>1754</v>
+      </c>
+      <c r="D497" s="7" t="s">
+        <v>1773</v>
+      </c>
+      <c r="E497" s="20">
+        <v>3.3</v>
+      </c>
+      <c r="F497" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="G497" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H497" s="7" t="s">
+        <v>1763</v>
+      </c>
+      <c r="I497" s="6"/>
+    </row>
+    <row r="498" spans="1:9" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A498" s="6">
+        <v>11007106</v>
+      </c>
+      <c r="B498" s="6">
+        <v>10</v>
+      </c>
+      <c r="C498" s="7" t="s">
+        <v>1755</v>
+      </c>
+      <c r="D498" s="7" t="s">
+        <v>1774</v>
+      </c>
+      <c r="E498" s="20">
+        <v>3.34</v>
+      </c>
+      <c r="F498" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G498" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H498" s="7" t="s">
+        <v>1762</v>
+      </c>
+      <c r="I498" s="6"/>
+    </row>
+    <row r="499" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A499" s="6">
+        <v>22100377</v>
+      </c>
+      <c r="B499" s="6">
+        <v>1</v>
+      </c>
+      <c r="C499" s="7" t="s">
+        <v>1782</v>
+      </c>
+      <c r="D499" s="7" t="s">
+        <v>1792</v>
+      </c>
+      <c r="E499" s="20">
+        <v>3.92</v>
+      </c>
+      <c r="F499" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G499" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H499" s="7" t="s">
+        <v>1801</v>
+      </c>
+      <c r="I499" s="6"/>
+    </row>
+    <row r="500" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A500" s="6">
+        <v>22100377</v>
+      </c>
+      <c r="B500" s="6">
+        <v>2</v>
+      </c>
+      <c r="C500" s="7" t="s">
+        <v>1783</v>
+      </c>
+      <c r="D500" s="7" t="s">
+        <v>1793</v>
+      </c>
+      <c r="E500" s="20">
+        <v>3.69</v>
+      </c>
+      <c r="F500" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G500" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H500" s="7" t="s">
+        <v>1809</v>
+      </c>
+      <c r="I500" s="6"/>
+    </row>
+    <row r="501" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A501" s="6">
+        <v>22100377</v>
+      </c>
+      <c r="B501" s="6">
+        <v>3</v>
+      </c>
+      <c r="C501" s="7" t="s">
+        <v>1784</v>
+      </c>
+      <c r="D501" s="7" t="s">
+        <v>1794</v>
+      </c>
+      <c r="E501" s="20">
+        <v>3.55</v>
+      </c>
+      <c r="F501" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G501" s="12">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="H501" s="7" t="s">
+        <v>1808</v>
+      </c>
+      <c r="I501" s="6"/>
+    </row>
+    <row r="502" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A502" s="6">
+        <v>22100377</v>
+      </c>
+      <c r="B502" s="6">
+        <v>4</v>
+      </c>
+      <c r="C502" s="7" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D502" s="7" t="s">
+        <v>1795</v>
+      </c>
+      <c r="E502" s="20">
+        <v>3.37</v>
+      </c>
+      <c r="F502" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G502" s="12">
+        <v>4.45</v>
+      </c>
+      <c r="H502" s="7" t="s">
+        <v>1802</v>
+      </c>
+      <c r="I502" s="6"/>
+    </row>
+    <row r="503" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A503" s="6">
+        <v>22100377</v>
+      </c>
+      <c r="B503" s="6">
+        <v>5</v>
+      </c>
+      <c r="C503" s="7" t="s">
+        <v>1786</v>
+      </c>
+      <c r="D503" s="7" t="s">
+        <v>1796</v>
+      </c>
+      <c r="E503" s="20">
+        <v>3.59</v>
+      </c>
+      <c r="F503" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G503" s="12">
+        <v>4.55</v>
+      </c>
+      <c r="H503" s="7" t="s">
+        <v>1803</v>
+      </c>
+      <c r="I503" s="6"/>
+    </row>
+    <row r="504" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A504" s="6">
+        <v>22100377</v>
+      </c>
+      <c r="B504" s="6">
+        <v>6</v>
+      </c>
+      <c r="C504" s="7" t="s">
+        <v>1787</v>
+      </c>
+      <c r="D504" s="7" t="s">
+        <v>1797</v>
+      </c>
+      <c r="E504" s="20">
+        <v>3.62</v>
+      </c>
+      <c r="F504" s="12">
+        <v>4</v>
+      </c>
+      <c r="G504" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H504" s="7" t="s">
+        <v>1804</v>
+      </c>
+      <c r="I504" s="6"/>
+    </row>
+    <row r="505" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A505" s="6">
+        <v>22100377</v>
+      </c>
+      <c r="B505" s="6">
+        <v>7</v>
+      </c>
+      <c r="C505" s="7" t="s">
+        <v>1788</v>
+      </c>
+      <c r="D505" s="7" t="s">
+        <v>1798</v>
+      </c>
+      <c r="E505" s="20">
+        <v>3.51</v>
+      </c>
+      <c r="F505" s="12">
+        <v>4</v>
+      </c>
+      <c r="G505" s="12">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="H505" s="7" t="s">
+        <v>1805</v>
+      </c>
+      <c r="I505" s="6"/>
+    </row>
+    <row r="506" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A506" s="6">
+        <v>22100377</v>
+      </c>
+      <c r="B506" s="6">
+        <v>8</v>
+      </c>
+      <c r="C506" s="7" t="s">
+        <v>1789</v>
+      </c>
+      <c r="D506" s="7" t="s">
+        <v>1799</v>
+      </c>
+      <c r="E506" s="20">
+        <v>3.79</v>
+      </c>
+      <c r="F506" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G506" s="12">
+        <v>4.45</v>
+      </c>
+      <c r="H506" s="7" t="s">
+        <v>1807</v>
+      </c>
+      <c r="I506" s="6"/>
+    </row>
+    <row r="507" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A507" s="6">
+        <v>22100377</v>
+      </c>
+      <c r="B507" s="6">
+        <v>9</v>
+      </c>
+      <c r="C507" s="7" t="s">
+        <v>1790</v>
+      </c>
+      <c r="D507" s="7" t="s">
+        <v>1800</v>
+      </c>
+      <c r="E507" s="20">
+        <v>3.8</v>
+      </c>
+      <c r="F507" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G507" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H507" s="7" t="s">
+        <v>1806</v>
+      </c>
+      <c r="I507" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{203FEB17-8E28-4348-A49F-13BF1F0DA95A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE83F202-D058-454F-99EF-D0922AD4F10B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2008" uniqueCount="1810">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2039" uniqueCount="1841">
   <si>
     <t>No</t>
   </si>
@@ -5801,6 +5801,145 @@
   </si>
   <si>
     <t>Από τις πιο μελωδικές στιγμές του δίσκου. Το organ έχει σχεδόν φωνητικό ρόλο, η κιθάρα διαμορφώνει διακριτικά τις αρμονίες και το groove παραμένει ζεστό, χωρίς να βιάζεται. Είναι soul-jazz με αίσθηση προσωπικής αυτοπεποίθησης και ήρεμης ελευθερίας. [Instrumental]</t>
+  </si>
+  <si>
+    <t>Petrodragonic Apocalypse; Or, Dawn Of Eternal Night: An Annihilation Of Planet Earth And The Beginning Of Merciless Damnation</t>
+  </si>
+  <si>
+    <t>King Gizzard And The Lizard Wizard</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/27606564-King-Gizzard-And-The-Lizard-Wizard-Petrodragonic-Apocalypse-Or-Dawn-Of-Eternal-Night-An-Annihilation</t>
+  </si>
+  <si>
+    <t>KGLW – KGLW-035, KGLW – KGLW-035-2LP, Europe, 2 x Vinyl, LP, Album, Recycled Black Wax, 2023</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Ευρωπαϊκή έκδοση διπλού βινυλίου (2LP) του 2023 σε Recycled Black Wax (με αυτοκόλλητο "Made in Germany" στο πίσω μέρος). Mastering από τον Joseph Carra, ηχογράφηση από τον Nico Wilson. Heavy, thrash και progressive metal με τεράστιο δυναμικό εύρος, καταιγιστικά πολυρυθμικά τύμπανα και βαριές κιθάρες.</t>
+  </si>
+  <si>
+    <t>Thrash Metal, Progressive Metal [Stoner Metal, Heavy Psych, Concept Metal]</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/L9jF-zgj6YtO2RejTOcI3BwiBCAtbWcAoaxvjsgDMBg/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI3NzYz/MzIwLTE2OTAxNDA2/NDktMjc2Ni5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Motor Spirit</t>
+  </si>
+  <si>
+    <t>Supercell</t>
+  </si>
+  <si>
+    <t>Converge</t>
+  </si>
+  <si>
+    <t>Witchcraft</t>
+  </si>
+  <si>
+    <t>Gila Monster</t>
+  </si>
+  <si>
+    <t>Dragon</t>
+  </si>
+  <si>
+    <t>Flamethrower</t>
+  </si>
+  <si>
+    <t>Dawn of Eternal Night (feat. Leah Senior)</t>
+  </si>
+  <si>
+    <t>Οκτάμισι λεπτά κινητικής thrash τελετουργίας. Το κομμάτι λειτουργεί σαν μηχανή που δεν σταματά: repetitious riffing, πολυρυθμικές μετακινήσεις και η έννοια του “motor spirit” ως πνεύμα της καύσης, της βιομηχανικής λατρείας και της αχαλίνωτης κατανάλωσης. Η μπάντα μετατρέπει την επανάληψη σε υπνωτικό όπλο, συνδέοντας το motorik παρελθόν της με βαρύτερη thrash μορφή.</t>
+  </si>
+  <si>
+    <t>Πιο συμπαγές αλλά εξίσου καταστροφικό, συνδέει το φυσικό φαινόμενο μιας υπερκαταιγίδας με την επερχόμενη περιβαλλοντική αποκάλυψη. Τα βαριά riffs και η σχεδόν doom αίσθηση περιγράφουν έναν ουρανό που μετατρέπεται σε απειλή, ενώ το φωνητικό ύφος είναι πιο κοφτό, εξαγριωμένο και λιγότερο ψυχεδελικό.</t>
+  </si>
+  <si>
+    <t>Τεχνικότερα δομημένο thrash με συνεχείς μεταβολές ρυθμού και έντασης. Η “σύγκλιση” του τίτλου μπορεί να διαβαστεί ως η στιγμή όπου πολλαπλές καταστροφικές δυνάμεις, φωτιά, καιρός, πετρέλαιο, μαγεία, ενώνονται σε ένα σημείο δίχως επιστροφή. Οι κιθάρες λειτουργούν σχεδόν σαν ένα ον που αλλάζει σχήμα.</t>
+  </si>
+  <si>
+    <t>Από τα πιο χαρακτηριστικά Gizzard tracks του δίσκου, επειδή παντρεύει σκληρό riffing με occult ψυχεδελική εικονοποιία. Η μαγεία δεν είναι διακοσμητική: γίνεται η δύναμη που καλείται για να ενεργοποιήσει την καταστροφή και να φέρει το τέρας στον κόσμο. Το ρυθμικό motif είναι απλό και κολλητικό, επιτρέποντας στο τραγούδι να λειτουργεί ως μία από τις πιο άμεσες heavy στιγμές του άλμπουμ.</t>
+  </si>
+  <si>
+    <t>Το πιο άμεσο single και ένα σύγχρονο kaiju-metal anthem. Η Gila monster είναι προάγγελος της μεταμόρφωσης, ένα πλάσμα που δραπετεύει από τον ανθρώπινο έλεγχο και γίνεται σύμβολο της βίας που ο ίδιος ο πολιτισμός γεννά. Το chorus έχει σχεδόν παιχνιδιάρικη, chant-like απλότητα, αλλά τα riffs κρατούν stoner-thrash βάρος.</t>
+  </si>
+  <si>
+    <t>Το δραματικό κέντρο του δίσκου και η πιο επική metal σύνθεση του. Η γέννηση του δράκου συμπυκνώνει το album narrative: καταστροφή, μαγεία, πετρέλαιο, φωτιά και τερατώδης αναγέννηση. Οι αλλαγές ανάμεσα σε thrash καταιγίδες, doom επιβράδυνση και ritual φωνητικά κάνουν το τραγούδι να μοιάζει με πολεμική/αποκαλυπτική τελετή. Η μπάντα αποφεύγει το prog-metal exhibitionism· κάθε αλλαγή υπηρετεί την ιστορία του τέρατος που ξυπνά.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Εννιάλεπτο φινάλε που αρχίζει ως αδυσώπητο thrash assault και καταλήγει σε synth-heavy, σχεδόν ηλεκτρονική κατάρρευση. Η φωτιά του τίτλου είναι κυριολεκτική και μεταφορική: καταστροφή του πλανήτη, καθαρτήριο και η τελική έκρηξη ενός συστήματος που δεν μπορεί να επιβιώσει. Το τελευταίο μεγάλο instrumental πέρασμα δημιουργεί γέφυρα προς τον ηλεκτρονικό κόσμο του επόμενου δίσκου τους, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>The Silver Cord</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Vinyl-exclusive spoken-word epilogue. Η Leah Senior αφηγείται τη συνέχεια της ιστορίας του PetroDragon, με μουσική/ambient υπόκρουση που λειτουργεί ως σκοτεινό audiobook. Δεν διαθέτει την άμεση metal αξία των επτά τραγουδιών, αλλά ως αντικείμενο world-building ολοκληρώνει την έκδοση βινυλίου και επανασυνδέει την μπάντα με τον αφηγηματικό κόσμο του </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Murder of the Universe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Thrash Metal, Progressive Metal [Motorik Thrash, Stoner Metal, Heavy Psych]</t>
+  </si>
+  <si>
+    <t>Thrash Metal, Heavy Metal [Doom-tinged Thrash, Stoner Metal]</t>
+  </si>
+  <si>
+    <t>Thrash Metal, Progressive Metal [Technical Thrash, Progressive Thrash]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Progressive Metal [Occult Metal, Stoner Metal, Heavy Psych]</t>
+  </si>
+  <si>
+    <t>Thrash Metal, Heavy Metal [Stoner Thrash, Kaiju Metal, Proto-Metal]</t>
+  </si>
+  <si>
+    <t>Progressive Metal, Thrash Metal [Epic Thrash, Doom Metal, Concept Metal]</t>
+  </si>
+  <si>
+    <t>Thrash Metal, Progressive Metal [Apocalyptic Thrash, Synth Metal, Heavy Psych]</t>
+  </si>
+  <si>
+    <t>Spoken Word, Ambient [Audiobook, Fantasy Narration, Atmospheric Soundscape]</t>
   </si>
 </sst>
 </file>
@@ -6319,7 +6458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:J57"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -8125,6 +8264,38 @@
       </c>
       <c r="J56" s="11" t="s">
         <v>1778</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A57" s="6">
+        <v>27606564</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>1811</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>1810</v>
+      </c>
+      <c r="D57" s="6">
+        <v>2023</v>
+      </c>
+      <c r="E57" s="10">
+        <v>3.76</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>1815</v>
+      </c>
+      <c r="G57" s="7" t="s">
+        <v>1814</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>1813</v>
+      </c>
+      <c r="I57" s="11" t="s">
+        <v>1812</v>
+      </c>
+      <c r="J57" s="11" t="s">
+        <v>1816</v>
       </c>
     </row>
   </sheetData>
@@ -8237,6 +8408,8 @@
     <hyperlink ref="I55" r:id="rId106" xr:uid="{D4FD42AF-DC0B-41B1-A1CF-67D8689FA322}"/>
     <hyperlink ref="J56" r:id="rId107" xr:uid="{879099B2-2A0C-40A7-8A67-6C10CBF856D5}"/>
     <hyperlink ref="I56" r:id="rId108" xr:uid="{39AA173B-82EA-49C0-AB10-59F5102644AE}"/>
+    <hyperlink ref="I57" r:id="rId109" xr:uid="{AF006A7D-90EE-4043-B23C-FCFA92E4B64D}"/>
+    <hyperlink ref="J57" r:id="rId110" xr:uid="{54C8F634-D910-413C-87D6-1278DAF31A3D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8244,7 +8417,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I507"/>
+  <dimension ref="A1:I515"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -8558,7 +8731,7 @@
       </c>
       <c r="I11" s="6"/>
     </row>
-    <row r="12" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>1739129</v>
       </c>
@@ -8585,7 +8758,7 @@
       </c>
       <c r="I12" s="6"/>
     </row>
-    <row r="13" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>1739129</v>
       </c>
@@ -8639,7 +8812,7 @@
       </c>
       <c r="I14" s="6"/>
     </row>
-    <row r="15" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>1739129</v>
       </c>
@@ -8693,7 +8866,7 @@
       </c>
       <c r="I16" s="6"/>
     </row>
-    <row r="17" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>1739129</v>
       </c>
@@ -8747,7 +8920,7 @@
       </c>
       <c r="I18" s="6"/>
     </row>
-    <row r="19" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>37452171</v>
       </c>
@@ -8882,7 +9055,7 @@
       </c>
       <c r="I23" s="6"/>
     </row>
-    <row r="24" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>37452171</v>
       </c>
@@ -8909,7 +9082,7 @@
       </c>
       <c r="I24" s="6"/>
     </row>
-    <row r="25" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>37452171</v>
       </c>
@@ -9017,7 +9190,7 @@
       </c>
       <c r="I28" s="6"/>
     </row>
-    <row r="29" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>37452171</v>
       </c>
@@ -9044,7 +9217,7 @@
       </c>
       <c r="I29" s="6"/>
     </row>
-    <row r="30" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>33790944</v>
       </c>
@@ -9341,7 +9514,7 @@
       </c>
       <c r="I40" s="6"/>
     </row>
-    <row r="41" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>926332</v>
       </c>
@@ -9368,7 +9541,7 @@
       </c>
       <c r="I41" s="6"/>
     </row>
-    <row r="42" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>926332</v>
       </c>
@@ -9395,7 +9568,7 @@
       </c>
       <c r="I42" s="6"/>
     </row>
-    <row r="43" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>926332</v>
       </c>
@@ -9505,7 +9678,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>10079558</v>
       </c>
@@ -9534,7 +9707,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>10079558</v>
       </c>
@@ -9561,7 +9734,7 @@
       </c>
       <c r="I48" s="6"/>
     </row>
-    <row r="49" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>10079558</v>
       </c>
@@ -9615,7 +9788,7 @@
       </c>
       <c r="I50" s="6"/>
     </row>
-    <row r="51" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>10079558</v>
       </c>
@@ -9644,7 +9817,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>10079558</v>
       </c>
@@ -9671,7 +9844,7 @@
       </c>
       <c r="I52" s="6"/>
     </row>
-    <row r="53" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>10079558</v>
       </c>
@@ -9698,7 +9871,7 @@
       </c>
       <c r="I53" s="6"/>
     </row>
-    <row r="54" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
         <v>10079558</v>
       </c>
@@ -9752,7 +9925,7 @@
       </c>
       <c r="I55" s="6"/>
     </row>
-    <row r="56" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
         <v>2027786</v>
       </c>
@@ -9781,7 +9954,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
         <v>2027786</v>
       </c>
@@ -9808,7 +9981,7 @@
       </c>
       <c r="I57" s="6"/>
     </row>
-    <row r="58" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
         <v>2027786</v>
       </c>
@@ -9835,7 +10008,7 @@
       </c>
       <c r="I58" s="6"/>
     </row>
-    <row r="59" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
         <v>2027786</v>
       </c>
@@ -9916,7 +10089,7 @@
       </c>
       <c r="I61" s="6"/>
     </row>
-    <row r="62" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
         <v>2027786</v>
       </c>
@@ -9970,7 +10143,7 @@
       </c>
       <c r="I63" s="6"/>
     </row>
-    <row r="64" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
         <v>2027786</v>
       </c>
@@ -9997,7 +10170,7 @@
       </c>
       <c r="I64" s="6"/>
     </row>
-    <row r="65" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
         <v>35339929</v>
       </c>
@@ -10026,7 +10199,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
         <v>35339929</v>
       </c>
@@ -10053,7 +10226,7 @@
       </c>
       <c r="I66" s="6"/>
     </row>
-    <row r="67" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>35339929</v>
       </c>
@@ -10107,7 +10280,7 @@
       </c>
       <c r="I68" s="6"/>
     </row>
-    <row r="69" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
         <v>35339929</v>
       </c>
@@ -10134,7 +10307,7 @@
       </c>
       <c r="I69" s="6"/>
     </row>
-    <row r="70" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
         <v>35339929</v>
       </c>
@@ -10161,7 +10334,7 @@
       </c>
       <c r="I70" s="6"/>
     </row>
-    <row r="71" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
         <v>31106519</v>
       </c>
@@ -10190,7 +10363,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
         <v>31106519</v>
       </c>
@@ -10219,7 +10392,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
         <v>31106519</v>
       </c>
@@ -10246,7 +10419,7 @@
       </c>
       <c r="I73" s="6"/>
     </row>
-    <row r="74" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
         <v>31106519</v>
       </c>
@@ -10275,7 +10448,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
         <v>31106519</v>
       </c>
@@ -10302,7 +10475,7 @@
       </c>
       <c r="I75" s="6"/>
     </row>
-    <row r="76" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
         <v>31106519</v>
       </c>
@@ -10331,7 +10504,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
         <v>21229427</v>
       </c>
@@ -10385,7 +10558,7 @@
       </c>
       <c r="I78" s="6"/>
     </row>
-    <row r="79" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
         <v>21229427</v>
       </c>
@@ -10439,7 +10612,7 @@
       </c>
       <c r="I80" s="6"/>
     </row>
-    <row r="81" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
         <v>21229427</v>
       </c>
@@ -10466,7 +10639,7 @@
       </c>
       <c r="I81" s="6"/>
     </row>
-    <row r="82" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
         <v>21229427</v>
       </c>
@@ -10493,7 +10666,7 @@
       </c>
       <c r="I82" s="6"/>
     </row>
-    <row r="83" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
         <v>21229427</v>
       </c>
@@ -10522,7 +10695,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
         <v>24362534</v>
       </c>
@@ -10576,7 +10749,7 @@
       </c>
       <c r="I85" s="6"/>
     </row>
-    <row r="86" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
         <v>24362534</v>
       </c>
@@ -10603,7 +10776,7 @@
       </c>
       <c r="I86" s="6"/>
     </row>
-    <row r="87" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
         <v>24362534</v>
       </c>
@@ -10657,7 +10830,7 @@
       </c>
       <c r="I88" s="6"/>
     </row>
-    <row r="89" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
         <v>24362534</v>
       </c>
@@ -10684,7 +10857,7 @@
       </c>
       <c r="I89" s="6"/>
     </row>
-    <row r="90" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A90" s="6">
         <v>24362534</v>
       </c>
@@ -10711,7 +10884,7 @@
       </c>
       <c r="I90" s="6"/>
     </row>
-    <row r="91" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
         <v>24362534</v>
       </c>
@@ -10738,7 +10911,7 @@
       </c>
       <c r="I91" s="6"/>
     </row>
-    <row r="92" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
         <v>24362534</v>
       </c>
@@ -10819,7 +10992,7 @@
       </c>
       <c r="I94" s="6"/>
     </row>
-    <row r="95" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A95" s="6">
         <v>24362534</v>
       </c>
@@ -10875,7 +11048,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
         <v>24831386</v>
       </c>
@@ -10902,7 +11075,7 @@
       </c>
       <c r="I97" s="6"/>
     </row>
-    <row r="98" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
         <v>24831386</v>
       </c>
@@ -10929,7 +11102,7 @@
       </c>
       <c r="I98" s="6"/>
     </row>
-    <row r="99" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A99" s="6">
         <v>24831386</v>
       </c>
@@ -10958,7 +11131,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A100" s="6">
         <v>24831386</v>
       </c>
@@ -10985,7 +11158,7 @@
       </c>
       <c r="I100" s="6"/>
     </row>
-    <row r="101" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A101" s="6">
         <v>24831386</v>
       </c>
@@ -11012,7 +11185,7 @@
       </c>
       <c r="I101" s="6"/>
     </row>
-    <row r="102" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A102" s="6">
         <v>24831386</v>
       </c>
@@ -11095,7 +11268,7 @@
       </c>
       <c r="I104" s="6"/>
     </row>
-    <row r="105" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A105" s="6">
         <v>6503426</v>
       </c>
@@ -11122,7 +11295,7 @@
       </c>
       <c r="I105" s="6"/>
     </row>
-    <row r="106" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A106" s="6">
         <v>6503426</v>
       </c>
@@ -11178,7 +11351,7 @@
       </c>
       <c r="I107" s="6"/>
     </row>
-    <row r="108" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A108" s="6">
         <v>920311</v>
       </c>
@@ -11205,7 +11378,7 @@
       </c>
       <c r="I108" s="6"/>
     </row>
-    <row r="109" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="6">
         <v>920311</v>
       </c>
@@ -11234,7 +11407,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="6">
         <v>920311</v>
       </c>
@@ -11261,7 +11434,7 @@
       </c>
       <c r="I110" s="6"/>
     </row>
-    <row r="111" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="6">
         <v>920311</v>
       </c>
@@ -11288,7 +11461,7 @@
       </c>
       <c r="I111" s="6"/>
     </row>
-    <row r="112" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="6">
         <v>920311</v>
       </c>
@@ -11450,7 +11623,7 @@
       </c>
       <c r="I117" s="6"/>
     </row>
-    <row r="118" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A118" s="6">
         <v>2138840</v>
       </c>
@@ -11562,7 +11735,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="6">
         <v>2138840</v>
       </c>
@@ -11672,7 +11845,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="6">
         <v>2138840</v>
       </c>
@@ -11699,7 +11872,7 @@
       </c>
       <c r="I126" s="6"/>
     </row>
-    <row r="127" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A127" s="6">
         <v>2138840</v>
       </c>
@@ -11780,7 +11953,7 @@
       </c>
       <c r="I129" s="6"/>
     </row>
-    <row r="130" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="6">
         <v>10867099</v>
       </c>
@@ -11834,7 +12007,7 @@
       </c>
       <c r="I131" s="6"/>
     </row>
-    <row r="132" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="6">
         <v>10867099</v>
       </c>
@@ -12050,7 +12223,7 @@
       </c>
       <c r="I139" s="6"/>
     </row>
-    <row r="140" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A140" s="6">
         <v>2797526</v>
       </c>
@@ -12104,7 +12277,7 @@
       </c>
       <c r="I141" s="6"/>
     </row>
-    <row r="142" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A142" s="6">
         <v>2797526</v>
       </c>
@@ -12131,7 +12304,7 @@
       </c>
       <c r="I142" s="6"/>
     </row>
-    <row r="143" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A143" s="6">
         <v>2797526</v>
       </c>
@@ -12158,7 +12331,7 @@
       </c>
       <c r="I143" s="6"/>
     </row>
-    <row r="144" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A144" s="6">
         <v>2797526</v>
       </c>
@@ -12185,7 +12358,7 @@
       </c>
       <c r="I144" s="6"/>
     </row>
-    <row r="145" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A145" s="6">
         <v>2797526</v>
       </c>
@@ -12212,7 +12385,7 @@
       </c>
       <c r="I145" s="6"/>
     </row>
-    <row r="146" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A146" s="6">
         <v>2797526</v>
       </c>
@@ -12239,7 +12412,7 @@
       </c>
       <c r="I146" s="6"/>
     </row>
-    <row r="147" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A147" s="6">
         <v>2797526</v>
       </c>
@@ -12266,7 +12439,7 @@
       </c>
       <c r="I147" s="6"/>
     </row>
-    <row r="148" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="6">
         <v>2797526</v>
       </c>
@@ -12320,7 +12493,7 @@
       </c>
       <c r="I149" s="6"/>
     </row>
-    <row r="150" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A150" s="6">
         <v>2797526</v>
       </c>
@@ -12347,7 +12520,7 @@
       </c>
       <c r="I150" s="6"/>
     </row>
-    <row r="151" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A151" s="6">
         <v>28270285</v>
       </c>
@@ -12374,7 +12547,7 @@
       </c>
       <c r="I151" s="6"/>
     </row>
-    <row r="152" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A152" s="6">
         <v>28270285</v>
       </c>
@@ -12401,7 +12574,7 @@
       </c>
       <c r="I152" s="6"/>
     </row>
-    <row r="153" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A153" s="6">
         <v>28270285</v>
       </c>
@@ -12509,7 +12682,7 @@
       </c>
       <c r="I156" s="6"/>
     </row>
-    <row r="157" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A157" s="6">
         <v>24184766</v>
       </c>
@@ -12671,7 +12844,7 @@
       </c>
       <c r="I162" s="6"/>
     </row>
-    <row r="163" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A163" s="6">
         <v>24184766</v>
       </c>
@@ -12779,7 +12952,7 @@
       </c>
       <c r="I166" s="6"/>
     </row>
-    <row r="167" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A167" s="6">
         <v>28074505</v>
       </c>
@@ -12860,7 +13033,7 @@
       </c>
       <c r="I169" s="6"/>
     </row>
-    <row r="170" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A170" s="6">
         <v>28074505</v>
       </c>
@@ -12887,7 +13060,7 @@
       </c>
       <c r="I170" s="6"/>
     </row>
-    <row r="171" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A171" s="6">
         <v>28074505</v>
       </c>
@@ -12914,7 +13087,7 @@
       </c>
       <c r="I171" s="6"/>
     </row>
-    <row r="172" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A172" s="6">
         <v>28074505</v>
       </c>
@@ -12941,7 +13114,7 @@
       </c>
       <c r="I172" s="6"/>
     </row>
-    <row r="173" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A173" s="6">
         <v>28074505</v>
       </c>
@@ -12968,7 +13141,7 @@
       </c>
       <c r="I173" s="6"/>
     </row>
-    <row r="174" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A174" s="6">
         <v>25695898</v>
       </c>
@@ -12995,7 +13168,7 @@
       </c>
       <c r="I174" s="6"/>
     </row>
-    <row r="175" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A175" s="6">
         <v>25695898</v>
       </c>
@@ -13024,7 +13197,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="176" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A176" s="6">
         <v>25695898</v>
       </c>
@@ -13186,7 +13359,7 @@
       </c>
       <c r="I181" s="6"/>
     </row>
-    <row r="182" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A182" s="6">
         <v>11981817</v>
       </c>
@@ -13240,7 +13413,7 @@
       </c>
       <c r="I183" s="6"/>
     </row>
-    <row r="184" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A184" s="6">
         <v>11981817</v>
       </c>
@@ -13267,7 +13440,7 @@
       </c>
       <c r="I184" s="6"/>
     </row>
-    <row r="185" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A185" s="6">
         <v>11981817</v>
       </c>
@@ -13321,7 +13494,7 @@
       </c>
       <c r="I186" s="6"/>
     </row>
-    <row r="187" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A187" s="6">
         <v>11981817</v>
       </c>
@@ -13348,7 +13521,7 @@
       </c>
       <c r="I187" s="6"/>
     </row>
-    <row r="188" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A188" s="6">
         <v>11981817</v>
       </c>
@@ -13375,7 +13548,7 @@
       </c>
       <c r="I188" s="6"/>
     </row>
-    <row r="189" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A189" s="6">
         <v>11981817</v>
       </c>
@@ -13429,7 +13602,7 @@
       </c>
       <c r="I190" s="6"/>
     </row>
-    <row r="191" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A191" s="6">
         <v>11981817</v>
       </c>
@@ -13456,7 +13629,7 @@
       </c>
       <c r="I191" s="6"/>
     </row>
-    <row r="192" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A192" s="6">
         <v>11981817</v>
       </c>
@@ -13483,7 +13656,7 @@
       </c>
       <c r="I192" s="6"/>
     </row>
-    <row r="193" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A193" s="6">
         <v>11981817</v>
       </c>
@@ -13510,7 +13683,7 @@
       </c>
       <c r="I193" s="6"/>
     </row>
-    <row r="194" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A194" s="6">
         <v>11981817</v>
       </c>
@@ -13564,7 +13737,7 @@
       </c>
       <c r="I195" s="6"/>
     </row>
-    <row r="196" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A196" s="6">
         <v>11981817</v>
       </c>
@@ -13591,7 +13764,7 @@
       </c>
       <c r="I196" s="6"/>
     </row>
-    <row r="197" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A197" s="6">
         <v>29264422</v>
       </c>
@@ -13618,7 +13791,7 @@
       </c>
       <c r="I197" s="6"/>
     </row>
-    <row r="198" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A198" s="6">
         <v>29264422</v>
       </c>
@@ -13645,7 +13818,7 @@
       </c>
       <c r="I198" s="6"/>
     </row>
-    <row r="199" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A199" s="6">
         <v>29264422</v>
       </c>
@@ -13672,7 +13845,7 @@
       </c>
       <c r="I199" s="6"/>
     </row>
-    <row r="200" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A200" s="6">
         <v>29264422</v>
       </c>
@@ -13699,7 +13872,7 @@
       </c>
       <c r="I200" s="6"/>
     </row>
-    <row r="201" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A201" s="6">
         <v>29264422</v>
       </c>
@@ -13726,7 +13899,7 @@
       </c>
       <c r="I201" s="6"/>
     </row>
-    <row r="202" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A202" s="6">
         <v>29264422</v>
       </c>
@@ -13753,7 +13926,7 @@
       </c>
       <c r="I202" s="6"/>
     </row>
-    <row r="203" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A203" s="6">
         <v>29264422</v>
       </c>
@@ -13807,7 +13980,7 @@
       </c>
       <c r="I204" s="6"/>
     </row>
-    <row r="205" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A205" s="6">
         <v>29264422</v>
       </c>
@@ -13834,7 +14007,7 @@
       </c>
       <c r="I205" s="6"/>
     </row>
-    <row r="206" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A206" s="6">
         <v>29264422</v>
       </c>
@@ -13861,7 +14034,7 @@
       </c>
       <c r="I206" s="6"/>
     </row>
-    <row r="207" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A207" s="6">
         <v>28667458</v>
       </c>
@@ -13888,7 +14061,7 @@
       </c>
       <c r="I207" s="6"/>
     </row>
-    <row r="208" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A208" s="6">
         <v>28667458</v>
       </c>
@@ -13915,7 +14088,7 @@
       </c>
       <c r="I208" s="6"/>
     </row>
-    <row r="209" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A209" s="6">
         <v>28667458</v>
       </c>
@@ -13969,7 +14142,7 @@
       </c>
       <c r="I210" s="6"/>
     </row>
-    <row r="211" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A211" s="6">
         <v>28667458</v>
       </c>
@@ -13996,7 +14169,7 @@
       </c>
       <c r="I211" s="6"/>
     </row>
-    <row r="212" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A212" s="6">
         <v>28667458</v>
       </c>
@@ -14023,7 +14196,7 @@
       </c>
       <c r="I212" s="6"/>
     </row>
-    <row r="213" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A213" s="6">
         <v>28667458</v>
       </c>
@@ -14050,7 +14223,7 @@
       </c>
       <c r="I213" s="6"/>
     </row>
-    <row r="214" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A214" s="6">
         <v>28667458</v>
       </c>
@@ -14077,7 +14250,7 @@
       </c>
       <c r="I214" s="6"/>
     </row>
-    <row r="215" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A215" s="6">
         <v>28667458</v>
       </c>
@@ -14104,7 +14277,7 @@
       </c>
       <c r="I215" s="6"/>
     </row>
-    <row r="216" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A216" s="6">
         <v>26857331</v>
       </c>
@@ -14185,7 +14358,7 @@
       </c>
       <c r="I218" s="6"/>
     </row>
-    <row r="219" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A219" s="6">
         <v>26857331</v>
       </c>
@@ -14212,7 +14385,7 @@
       </c>
       <c r="I219" s="6"/>
     </row>
-    <row r="220" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A220" s="6">
         <v>26857331</v>
       </c>
@@ -14239,7 +14412,7 @@
       </c>
       <c r="I220" s="6"/>
     </row>
-    <row r="221" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A221" s="6">
         <v>26857331</v>
       </c>
@@ -14266,7 +14439,7 @@
       </c>
       <c r="I221" s="6"/>
     </row>
-    <row r="222" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A222" s="6">
         <v>26857331</v>
       </c>
@@ -14320,7 +14493,7 @@
       </c>
       <c r="I223" s="6"/>
     </row>
-    <row r="224" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A224" s="6">
         <v>26857331</v>
       </c>
@@ -14347,7 +14520,7 @@
       </c>
       <c r="I224" s="6"/>
     </row>
-    <row r="225" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A225" s="6">
         <v>22420804</v>
       </c>
@@ -14374,7 +14547,7 @@
       </c>
       <c r="I225" s="6"/>
     </row>
-    <row r="226" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A226" s="6">
         <v>22420804</v>
       </c>
@@ -14401,7 +14574,7 @@
       </c>
       <c r="I226" s="6"/>
     </row>
-    <row r="227" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A227" s="6">
         <v>22420804</v>
       </c>
@@ -14430,7 +14603,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="228" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A228" s="6">
         <v>22420804</v>
       </c>
@@ -14457,7 +14630,7 @@
       </c>
       <c r="I228" s="6"/>
     </row>
-    <row r="229" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A229" s="6">
         <v>22420804</v>
       </c>
@@ -14484,7 +14657,7 @@
       </c>
       <c r="I229" s="6"/>
     </row>
-    <row r="230" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A230" s="6">
         <v>22420804</v>
       </c>
@@ -14511,7 +14684,7 @@
       </c>
       <c r="I230" s="6"/>
     </row>
-    <row r="231" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A231" s="6">
         <v>22420804</v>
       </c>
@@ -14538,7 +14711,7 @@
       </c>
       <c r="I231" s="6"/>
     </row>
-    <row r="232" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A232" s="6">
         <v>31880233</v>
       </c>
@@ -14567,7 +14740,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="233" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A233" s="6">
         <v>31880233</v>
       </c>
@@ -14596,7 +14769,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="234" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A234" s="6">
         <v>31880233</v>
       </c>
@@ -14623,7 +14796,7 @@
       </c>
       <c r="I234" s="6"/>
     </row>
-    <row r="235" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A235" s="6">
         <v>31880233</v>
       </c>
@@ -14677,7 +14850,7 @@
       </c>
       <c r="I236" s="6"/>
     </row>
-    <row r="237" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A237" s="6">
         <v>31880233</v>
       </c>
@@ -14731,7 +14904,7 @@
       </c>
       <c r="I238" s="6"/>
     </row>
-    <row r="239" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A239" s="6">
         <v>31880233</v>
       </c>
@@ -14787,7 +14960,7 @@
       </c>
       <c r="I240" s="6"/>
     </row>
-    <row r="241" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" s="6">
         <v>31700342</v>
       </c>
@@ -14868,7 +15041,7 @@
       </c>
       <c r="I243" s="6"/>
     </row>
-    <row r="244" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" s="6">
         <v>31700342</v>
       </c>
@@ -14895,7 +15068,7 @@
       </c>
       <c r="I244" s="6"/>
     </row>
-    <row r="245" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" s="6">
         <v>31700342</v>
       </c>
@@ -14976,7 +15149,7 @@
       </c>
       <c r="I247" s="6"/>
     </row>
-    <row r="248" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" s="6">
         <v>31700342</v>
       </c>
@@ -15030,7 +15203,7 @@
       </c>
       <c r="I249" s="6"/>
     </row>
-    <row r="250" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" s="6">
         <v>31700342</v>
       </c>
@@ -15057,7 +15230,7 @@
       </c>
       <c r="I250" s="6"/>
     </row>
-    <row r="251" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" s="6">
         <v>31700342</v>
       </c>
@@ -15084,7 +15257,7 @@
       </c>
       <c r="I251" s="6"/>
     </row>
-    <row r="252" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A252" s="6">
         <v>28251457</v>
       </c>
@@ -15111,7 +15284,7 @@
       </c>
       <c r="I252" s="6"/>
     </row>
-    <row r="253" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A253" s="6">
         <v>28251457</v>
       </c>
@@ -15381,7 +15554,7 @@
       </c>
       <c r="I262" s="6"/>
     </row>
-    <row r="263" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A263" s="6">
         <v>26207852</v>
       </c>
@@ -15543,7 +15716,7 @@
       </c>
       <c r="I268" s="6"/>
     </row>
-    <row r="269" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A269" s="6">
         <v>26207852</v>
       </c>
@@ -15597,7 +15770,7 @@
       </c>
       <c r="I270" s="6"/>
     </row>
-    <row r="271" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A271" s="6">
         <v>3507697</v>
       </c>
@@ -15651,7 +15824,7 @@
       </c>
       <c r="I272" s="6"/>
     </row>
-    <row r="273" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A273" s="6">
         <v>3507697</v>
       </c>
@@ -15790,7 +15963,7 @@
       </c>
       <c r="I277" s="6"/>
     </row>
-    <row r="278" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A278" s="6">
         <v>33253932</v>
       </c>
@@ -15819,7 +15992,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="279" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A279" s="6">
         <v>33253932</v>
       </c>
@@ -15873,7 +16046,7 @@
       </c>
       <c r="I280" s="6"/>
     </row>
-    <row r="281" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A281" s="6">
         <v>33253932</v>
       </c>
@@ -15900,7 +16073,7 @@
       </c>
       <c r="I281" s="6"/>
     </row>
-    <row r="282" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A282" s="6">
         <v>33253932</v>
       </c>
@@ -15927,7 +16100,7 @@
       </c>
       <c r="I282" s="6"/>
     </row>
-    <row r="283" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A283" s="6">
         <v>33253932</v>
       </c>
@@ -15954,7 +16127,7 @@
       </c>
       <c r="I283" s="6"/>
     </row>
-    <row r="284" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A284" s="6">
         <v>33253932</v>
       </c>
@@ -15981,7 +16154,7 @@
       </c>
       <c r="I284" s="6"/>
     </row>
-    <row r="285" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A285" s="6">
         <v>28518808</v>
       </c>
@@ -16008,7 +16181,7 @@
       </c>
       <c r="I285" s="6"/>
     </row>
-    <row r="286" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A286" s="6">
         <v>28518808</v>
       </c>
@@ -16062,7 +16235,7 @@
       </c>
       <c r="I287" s="6"/>
     </row>
-    <row r="288" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A288" s="6">
         <v>28518808</v>
       </c>
@@ -16224,7 +16397,7 @@
       </c>
       <c r="I293" s="6"/>
     </row>
-    <row r="294" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A294" s="6">
         <v>28518808</v>
       </c>
@@ -16251,7 +16424,7 @@
       </c>
       <c r="I294" s="6"/>
     </row>
-    <row r="295" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A295" s="6">
         <v>28518808</v>
       </c>
@@ -16278,7 +16451,7 @@
       </c>
       <c r="I295" s="6"/>
     </row>
-    <row r="296" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A296" s="6">
         <v>28518808</v>
       </c>
@@ -16305,7 +16478,7 @@
       </c>
       <c r="I296" s="6"/>
     </row>
-    <row r="297" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A297" s="6">
         <v>28649152</v>
       </c>
@@ -16413,7 +16586,7 @@
       </c>
       <c r="I300" s="6"/>
     </row>
-    <row r="301" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A301" s="6">
         <v>28649152</v>
       </c>
@@ -16440,7 +16613,7 @@
       </c>
       <c r="I301" s="6"/>
     </row>
-    <row r="302" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A302" s="6">
         <v>28649152</v>
       </c>
@@ -16494,7 +16667,7 @@
       </c>
       <c r="I303" s="6"/>
     </row>
-    <row r="304" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A304" s="6">
         <v>25412281</v>
       </c>
@@ -16683,7 +16856,7 @@
       </c>
       <c r="I310" s="6"/>
     </row>
-    <row r="311" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A311" s="6">
         <v>25412281</v>
       </c>
@@ -16791,7 +16964,7 @@
       </c>
       <c r="I314" s="6"/>
     </row>
-    <row r="315" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A315" s="6">
         <v>25950673</v>
       </c>
@@ -16818,7 +16991,7 @@
       </c>
       <c r="I315" s="6"/>
     </row>
-    <row r="316" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A316" s="6">
         <v>25950673</v>
       </c>
@@ -16845,7 +17018,7 @@
       </c>
       <c r="I316" s="6"/>
     </row>
-    <row r="317" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A317" s="6">
         <v>25950673</v>
       </c>
@@ -16872,7 +17045,7 @@
       </c>
       <c r="I317" s="6"/>
     </row>
-    <row r="318" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A318" s="6">
         <v>25950673</v>
       </c>
@@ -16953,7 +17126,7 @@
       </c>
       <c r="I320" s="6"/>
     </row>
-    <row r="321" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A321" s="6">
         <v>28117261</v>
       </c>
@@ -16980,7 +17153,7 @@
       </c>
       <c r="I321" s="6"/>
     </row>
-    <row r="322" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A322" s="6">
         <v>28117261</v>
       </c>
@@ -17009,7 +17182,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="323" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A323" s="6">
         <v>28117261</v>
       </c>
@@ -17038,7 +17211,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="324" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A324" s="6">
         <v>28117261</v>
       </c>
@@ -17065,7 +17238,7 @@
       </c>
       <c r="I324" s="6"/>
     </row>
-    <row r="325" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A325" s="6">
         <v>28117261</v>
       </c>
@@ -17092,7 +17265,7 @@
       </c>
       <c r="I325" s="6"/>
     </row>
-    <row r="326" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A326" s="6">
         <v>28117261</v>
       </c>
@@ -17119,7 +17292,7 @@
       </c>
       <c r="I326" s="6"/>
     </row>
-    <row r="327" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A327" s="6">
         <v>28117261</v>
       </c>
@@ -17146,7 +17319,7 @@
       </c>
       <c r="I327" s="6"/>
     </row>
-    <row r="328" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A328" s="6">
         <v>28117261</v>
       </c>
@@ -17173,7 +17346,7 @@
       </c>
       <c r="I328" s="6"/>
     </row>
-    <row r="329" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A329" s="6">
         <v>28117261</v>
       </c>
@@ -17200,7 +17373,7 @@
       </c>
       <c r="I329" s="6"/>
     </row>
-    <row r="330" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A330" s="6">
         <v>28117261</v>
       </c>
@@ -17227,7 +17400,7 @@
       </c>
       <c r="I330" s="6"/>
     </row>
-    <row r="331" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A331" s="6">
         <v>1562086</v>
       </c>
@@ -17256,7 +17429,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="332" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A332" s="6">
         <v>1562086</v>
       </c>
@@ -17285,7 +17458,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="333" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A333" s="6">
         <v>1562086</v>
       </c>
@@ -17339,7 +17512,7 @@
       </c>
       <c r="I334" s="6"/>
     </row>
-    <row r="335" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A335" s="6">
         <v>1562086</v>
       </c>
@@ -17368,7 +17541,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="336" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A336" s="6">
         <v>1562086</v>
       </c>
@@ -17395,7 +17568,7 @@
       </c>
       <c r="I336" s="6"/>
     </row>
-    <row r="337" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A337" s="6">
         <v>1562086</v>
       </c>
@@ -17422,7 +17595,7 @@
       </c>
       <c r="I337" s="6"/>
     </row>
-    <row r="338" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A338" s="6">
         <v>1562086</v>
       </c>
@@ -17449,7 +17622,7 @@
       </c>
       <c r="I338" s="6"/>
     </row>
-    <row r="339" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A339" s="6">
         <v>1562086</v>
       </c>
@@ -17476,7 +17649,7 @@
       </c>
       <c r="I339" s="6"/>
     </row>
-    <row r="340" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A340" s="6">
         <v>31683230</v>
       </c>
@@ -17503,7 +17676,7 @@
       </c>
       <c r="I340" s="6"/>
     </row>
-    <row r="341" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A341" s="6">
         <v>31683230</v>
       </c>
@@ -17530,7 +17703,7 @@
       </c>
       <c r="I341" s="6"/>
     </row>
-    <row r="342" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A342" s="6">
         <v>31683230</v>
       </c>
@@ -17557,7 +17730,7 @@
       </c>
       <c r="I342" s="6"/>
     </row>
-    <row r="343" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A343" s="6">
         <v>31683230</v>
       </c>
@@ -17611,7 +17784,7 @@
       </c>
       <c r="I344" s="6"/>
     </row>
-    <row r="345" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A345" s="6">
         <v>31683230</v>
       </c>
@@ -17638,7 +17811,7 @@
       </c>
       <c r="I345" s="6"/>
     </row>
-    <row r="346" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A346" s="6">
         <v>31683230</v>
       </c>
@@ -17665,7 +17838,7 @@
       </c>
       <c r="I346" s="6"/>
     </row>
-    <row r="347" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A347" s="6">
         <v>31683230</v>
       </c>
@@ -17692,7 +17865,7 @@
       </c>
       <c r="I347" s="6"/>
     </row>
-    <row r="348" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A348" s="6">
         <v>28426390</v>
       </c>
@@ -17719,7 +17892,7 @@
       </c>
       <c r="I348" s="6"/>
     </row>
-    <row r="349" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A349" s="6">
         <v>28426390</v>
       </c>
@@ -17746,7 +17919,7 @@
       </c>
       <c r="I349" s="6"/>
     </row>
-    <row r="350" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A350" s="6">
         <v>28426390</v>
       </c>
@@ -17773,7 +17946,7 @@
       </c>
       <c r="I350" s="6"/>
     </row>
-    <row r="351" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A351" s="6">
         <v>28426390</v>
       </c>
@@ -17800,7 +17973,7 @@
       </c>
       <c r="I351" s="6"/>
     </row>
-    <row r="352" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A352" s="6">
         <v>28426390</v>
       </c>
@@ -17827,7 +18000,7 @@
       </c>
       <c r="I352" s="6"/>
     </row>
-    <row r="353" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A353" s="6">
         <v>28426390</v>
       </c>
@@ -17854,7 +18027,7 @@
       </c>
       <c r="I353" s="6"/>
     </row>
-    <row r="354" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A354" s="6">
         <v>28426390</v>
       </c>
@@ -17881,7 +18054,7 @@
       </c>
       <c r="I354" s="6"/>
     </row>
-    <row r="355" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A355" s="6">
         <v>28426390</v>
       </c>
@@ -17908,7 +18081,7 @@
       </c>
       <c r="I355" s="6"/>
     </row>
-    <row r="356" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A356" s="6">
         <v>28426390</v>
       </c>
@@ -17935,7 +18108,7 @@
       </c>
       <c r="I356" s="6"/>
     </row>
-    <row r="357" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A357" s="6">
         <v>28426390</v>
       </c>
@@ -17962,7 +18135,7 @@
       </c>
       <c r="I357" s="6"/>
     </row>
-    <row r="358" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A358" s="6">
         <v>25885156</v>
       </c>
@@ -17991,7 +18164,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="359" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A359" s="6">
         <v>25885156</v>
       </c>
@@ -18018,7 +18191,7 @@
       </c>
       <c r="I359" s="6"/>
     </row>
-    <row r="360" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A360" s="6">
         <v>25885156</v>
       </c>
@@ -18047,7 +18220,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="361" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A361" s="6">
         <v>25885156</v>
       </c>
@@ -18076,7 +18249,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="362" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A362" s="6">
         <v>25885156</v>
       </c>
@@ -18103,7 +18276,7 @@
       </c>
       <c r="I362" s="6"/>
     </row>
-    <row r="363" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A363" s="6">
         <v>25895635</v>
       </c>
@@ -18130,7 +18303,7 @@
       </c>
       <c r="I363" s="6"/>
     </row>
-    <row r="364" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A364" s="6">
         <v>25895635</v>
       </c>
@@ -18157,7 +18330,7 @@
       </c>
       <c r="I364" s="6"/>
     </row>
-    <row r="365" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A365" s="6">
         <v>25895635</v>
       </c>
@@ -18184,7 +18357,7 @@
       </c>
       <c r="I365" s="6"/>
     </row>
-    <row r="366" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A366" s="6">
         <v>25895635</v>
       </c>
@@ -18211,7 +18384,7 @@
       </c>
       <c r="I366" s="6"/>
     </row>
-    <row r="367" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A367" s="6">
         <v>25895635</v>
       </c>
@@ -18238,7 +18411,7 @@
       </c>
       <c r="I367" s="6"/>
     </row>
-    <row r="368" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A368" s="6">
         <v>25895635</v>
       </c>
@@ -18265,7 +18438,7 @@
       </c>
       <c r="I368" s="6"/>
     </row>
-    <row r="369" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A369" s="6">
         <v>25895635</v>
       </c>
@@ -18319,7 +18492,7 @@
       </c>
       <c r="I370" s="6"/>
     </row>
-    <row r="371" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A371" s="6">
         <v>31216738</v>
       </c>
@@ -18346,7 +18519,7 @@
       </c>
       <c r="I371" s="6"/>
     </row>
-    <row r="372" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A372" s="6">
         <v>31216738</v>
       </c>
@@ -18373,7 +18546,7 @@
       </c>
       <c r="I372" s="6"/>
     </row>
-    <row r="373" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A373" s="6">
         <v>31216738</v>
       </c>
@@ -18400,7 +18573,7 @@
       </c>
       <c r="I373" s="6"/>
     </row>
-    <row r="374" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A374" s="6">
         <v>31216738</v>
       </c>
@@ -18427,7 +18600,7 @@
       </c>
       <c r="I374" s="6"/>
     </row>
-    <row r="375" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A375" s="6">
         <v>31216738</v>
       </c>
@@ -18454,7 +18627,7 @@
       </c>
       <c r="I375" s="6"/>
     </row>
-    <row r="376" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A376" s="6">
         <v>31216738</v>
       </c>
@@ -18481,7 +18654,7 @@
       </c>
       <c r="I376" s="6"/>
     </row>
-    <row r="377" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A377" s="6">
         <v>31216738</v>
       </c>
@@ -18508,7 +18681,7 @@
       </c>
       <c r="I377" s="6"/>
     </row>
-    <row r="378" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A378" s="6">
         <v>31216738</v>
       </c>
@@ -18535,7 +18708,7 @@
       </c>
       <c r="I378" s="6"/>
     </row>
-    <row r="379" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A379" s="6">
         <v>31216738</v>
       </c>
@@ -18589,7 +18762,7 @@
       </c>
       <c r="I380" s="6"/>
     </row>
-    <row r="381" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A381" s="6">
         <v>31216738</v>
       </c>
@@ -18616,7 +18789,7 @@
       </c>
       <c r="I381" s="6"/>
     </row>
-    <row r="382" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A382" s="6">
         <v>4418939</v>
       </c>
@@ -18645,7 +18818,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="383" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A383" s="6">
         <v>4418939</v>
       </c>
@@ -18672,7 +18845,7 @@
       </c>
       <c r="I383" s="6"/>
     </row>
-    <row r="384" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A384" s="6">
         <v>4418939</v>
       </c>
@@ -18699,7 +18872,7 @@
       </c>
       <c r="I384" s="6"/>
     </row>
-    <row r="385" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A385" s="6">
         <v>4418939</v>
       </c>
@@ -18726,7 +18899,7 @@
       </c>
       <c r="I385" s="6"/>
     </row>
-    <row r="386" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A386" s="6">
         <v>4418939</v>
       </c>
@@ -18753,7 +18926,7 @@
       </c>
       <c r="I386" s="6"/>
     </row>
-    <row r="387" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A387" s="6">
         <v>4418939</v>
       </c>
@@ -18780,7 +18953,7 @@
       </c>
       <c r="I387" s="6"/>
     </row>
-    <row r="388" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A388" s="6">
         <v>4418939</v>
       </c>
@@ -18807,7 +18980,7 @@
       </c>
       <c r="I388" s="6"/>
     </row>
-    <row r="389" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A389" s="6">
         <v>4418939</v>
       </c>
@@ -18834,7 +19007,7 @@
       </c>
       <c r="I389" s="6"/>
     </row>
-    <row r="390" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A390" s="6">
         <v>4418939</v>
       </c>
@@ -18861,7 +19034,7 @@
       </c>
       <c r="I390" s="6"/>
     </row>
-    <row r="391" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A391" s="6">
         <v>26909678</v>
       </c>
@@ -18888,7 +19061,7 @@
       </c>
       <c r="I391" s="6"/>
     </row>
-    <row r="392" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A392" s="6">
         <v>26909678</v>
       </c>
@@ -18942,7 +19115,7 @@
       </c>
       <c r="I393" s="6"/>
     </row>
-    <row r="394" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A394" s="6">
         <v>26909678</v>
       </c>
@@ -18969,7 +19142,7 @@
       </c>
       <c r="I394" s="6"/>
     </row>
-    <row r="395" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A395" s="6">
         <v>26909678</v>
       </c>
@@ -18996,7 +19169,7 @@
       </c>
       <c r="I395" s="6"/>
     </row>
-    <row r="396" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A396" s="6">
         <v>26909678</v>
       </c>
@@ -19023,7 +19196,7 @@
       </c>
       <c r="I396" s="6"/>
     </row>
-    <row r="397" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A397" s="6">
         <v>26909678</v>
       </c>
@@ -19050,7 +19223,7 @@
       </c>
       <c r="I397" s="6"/>
     </row>
-    <row r="398" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A398" s="6">
         <v>26909678</v>
       </c>
@@ -19077,7 +19250,7 @@
       </c>
       <c r="I398" s="6"/>
     </row>
-    <row r="399" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A399" s="6">
         <v>26909678</v>
       </c>
@@ -19104,7 +19277,7 @@
       </c>
       <c r="I399" s="6"/>
     </row>
-    <row r="400" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A400" s="6">
         <v>29704561</v>
       </c>
@@ -19131,7 +19304,7 @@
       </c>
       <c r="I400" s="6"/>
     </row>
-    <row r="401" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A401" s="6">
         <v>29704561</v>
       </c>
@@ -19158,7 +19331,7 @@
       </c>
       <c r="I401" s="6"/>
     </row>
-    <row r="402" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A402" s="6">
         <v>29704561</v>
       </c>
@@ -19185,7 +19358,7 @@
       </c>
       <c r="I402" s="6"/>
     </row>
-    <row r="403" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A403" s="6">
         <v>29704561</v>
       </c>
@@ -19212,7 +19385,7 @@
       </c>
       <c r="I403" s="6"/>
     </row>
-    <row r="404" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A404" s="6">
         <v>29704561</v>
       </c>
@@ -19239,7 +19412,7 @@
       </c>
       <c r="I404" s="6"/>
     </row>
-    <row r="405" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A405" s="6">
         <v>29704561</v>
       </c>
@@ -19266,7 +19439,7 @@
       </c>
       <c r="I405" s="6"/>
     </row>
-    <row r="406" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A406" s="6">
         <v>29704561</v>
       </c>
@@ -19293,7 +19466,7 @@
       </c>
       <c r="I406" s="6"/>
     </row>
-    <row r="407" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A407" s="6">
         <v>29704561</v>
       </c>
@@ -19320,7 +19493,7 @@
       </c>
       <c r="I407" s="6"/>
     </row>
-    <row r="408" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A408" s="6">
         <v>29704561</v>
       </c>
@@ -19347,7 +19520,7 @@
       </c>
       <c r="I408" s="6"/>
     </row>
-    <row r="409" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A409" s="6">
         <v>23803544</v>
       </c>
@@ -19376,7 +19549,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="410" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A410" s="6">
         <v>23803544</v>
       </c>
@@ -19403,7 +19576,7 @@
       </c>
       <c r="I410" s="6"/>
     </row>
-    <row r="411" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A411" s="6">
         <v>23803544</v>
       </c>
@@ -19430,7 +19603,7 @@
       </c>
       <c r="I411" s="6"/>
     </row>
-    <row r="412" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A412" s="6">
         <v>23803544</v>
       </c>
@@ -19457,7 +19630,7 @@
       </c>
       <c r="I412" s="6"/>
     </row>
-    <row r="413" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A413" s="6">
         <v>23803544</v>
       </c>
@@ -19484,7 +19657,7 @@
       </c>
       <c r="I413" s="6"/>
     </row>
-    <row r="414" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A414" s="6">
         <v>23803544</v>
       </c>
@@ -19511,7 +19684,7 @@
       </c>
       <c r="I414" s="6"/>
     </row>
-    <row r="415" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A415" s="6">
         <v>23803544</v>
       </c>
@@ -19538,7 +19711,7 @@
       </c>
       <c r="I415" s="6"/>
     </row>
-    <row r="416" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A416" s="6">
         <v>23803544</v>
       </c>
@@ -19565,7 +19738,7 @@
       </c>
       <c r="I416" s="6"/>
     </row>
-    <row r="417" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A417" s="6">
         <v>23803544</v>
       </c>
@@ -19592,7 +19765,7 @@
       </c>
       <c r="I417" s="6"/>
     </row>
-    <row r="418" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A418" s="6">
         <v>26832221</v>
       </c>
@@ -19619,7 +19792,7 @@
       </c>
       <c r="I418" s="6"/>
     </row>
-    <row r="419" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A419" s="6">
         <v>26832221</v>
       </c>
@@ -19646,7 +19819,7 @@
       </c>
       <c r="I419" s="6"/>
     </row>
-    <row r="420" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A420" s="6">
         <v>26832221</v>
       </c>
@@ -19673,7 +19846,7 @@
       </c>
       <c r="I420" s="6"/>
     </row>
-    <row r="421" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A421" s="6">
         <v>26832221</v>
       </c>
@@ -19700,7 +19873,7 @@
       </c>
       <c r="I421" s="6"/>
     </row>
-    <row r="422" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A422" s="6">
         <v>26832221</v>
       </c>
@@ -19727,7 +19900,7 @@
       </c>
       <c r="I422" s="6"/>
     </row>
-    <row r="423" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A423" s="6">
         <v>26832221</v>
       </c>
@@ -19754,7 +19927,7 @@
       </c>
       <c r="I423" s="6"/>
     </row>
-    <row r="424" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A424" s="6">
         <v>26832221</v>
       </c>
@@ -19781,7 +19954,7 @@
       </c>
       <c r="I424" s="6"/>
     </row>
-    <row r="425" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A425" s="6">
         <v>26832221</v>
       </c>
@@ -19808,7 +19981,7 @@
       </c>
       <c r="I425" s="6"/>
     </row>
-    <row r="426" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A426" s="6">
         <v>26832221</v>
       </c>
@@ -19835,7 +20008,7 @@
       </c>
       <c r="I426" s="6"/>
     </row>
-    <row r="427" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A427" s="6">
         <v>26832221</v>
       </c>
@@ -19862,7 +20035,7 @@
       </c>
       <c r="I427" s="6"/>
     </row>
-    <row r="428" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A428" s="6">
         <v>26832221</v>
       </c>
@@ -19889,7 +20062,7 @@
       </c>
       <c r="I428" s="6"/>
     </row>
-    <row r="429" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A429" s="6">
         <v>7660097</v>
       </c>
@@ -19914,7 +20087,7 @@
       </c>
       <c r="I429" s="6"/>
     </row>
-    <row r="430" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A430" s="6">
         <v>7660097</v>
       </c>
@@ -19939,7 +20112,7 @@
       </c>
       <c r="I430" s="6"/>
     </row>
-    <row r="431" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A431" s="6">
         <v>7660097</v>
       </c>
@@ -19966,7 +20139,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="432" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A432" s="6">
         <v>7660097</v>
       </c>
@@ -20041,7 +20214,7 @@
       </c>
       <c r="I434" s="6"/>
     </row>
-    <row r="435" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A435" s="6">
         <v>7660097</v>
       </c>
@@ -20066,7 +20239,7 @@
       </c>
       <c r="I435" s="6"/>
     </row>
-    <row r="436" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A436" s="6">
         <v>7598060</v>
       </c>
@@ -20093,7 +20266,7 @@
       </c>
       <c r="I436" s="6"/>
     </row>
-    <row r="437" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A437" s="6">
         <v>7598060</v>
       </c>
@@ -20120,7 +20293,7 @@
       </c>
       <c r="I437" s="6"/>
     </row>
-    <row r="438" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A438" s="6">
         <v>7598060</v>
       </c>
@@ -20147,7 +20320,7 @@
       </c>
       <c r="I438" s="6"/>
     </row>
-    <row r="439" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A439" s="6">
         <v>7598060</v>
       </c>
@@ -20201,7 +20374,7 @@
       </c>
       <c r="I440" s="6"/>
     </row>
-    <row r="441" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A441" s="6">
         <v>7598060</v>
       </c>
@@ -20255,7 +20428,7 @@
       </c>
       <c r="I442" s="6"/>
     </row>
-    <row r="443" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A443" s="6">
         <v>7598060</v>
       </c>
@@ -20309,7 +20482,7 @@
       </c>
       <c r="I444" s="6"/>
     </row>
-    <row r="445" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A445" s="6">
         <v>7598060</v>
       </c>
@@ -20336,7 +20509,7 @@
       </c>
       <c r="I445" s="6"/>
     </row>
-    <row r="446" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A446" s="6">
         <v>7598060</v>
       </c>
@@ -20446,7 +20619,7 @@
       </c>
       <c r="I449" s="6"/>
     </row>
-    <row r="450" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A450" s="6">
         <v>3229841</v>
       </c>
@@ -20473,7 +20646,7 @@
       </c>
       <c r="I450" s="6"/>
     </row>
-    <row r="451" spans="1:9" ht="357" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:9" ht="262.5" x14ac:dyDescent="0.25">
       <c r="A451" s="6">
         <v>3229841</v>
       </c>
@@ -20502,7 +20675,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="452" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A452" s="6">
         <v>3229841</v>
       </c>
@@ -20529,7 +20702,7 @@
       </c>
       <c r="I452" s="6"/>
     </row>
-    <row r="453" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A453" s="6">
         <v>3229841</v>
       </c>
@@ -20556,7 +20729,7 @@
       </c>
       <c r="I453" s="6"/>
     </row>
-    <row r="454" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A454" s="6">
         <v>3229841</v>
       </c>
@@ -20583,7 +20756,7 @@
       </c>
       <c r="I454" s="6"/>
     </row>
-    <row r="455" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A455" s="6">
         <v>3229841</v>
       </c>
@@ -20610,7 +20783,7 @@
       </c>
       <c r="I455" s="6"/>
     </row>
-    <row r="456" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A456" s="6">
         <v>3229841</v>
       </c>
@@ -20637,7 +20810,7 @@
       </c>
       <c r="I456" s="6"/>
     </row>
-    <row r="457" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A457" s="6">
         <v>3229841</v>
       </c>
@@ -20664,7 +20837,7 @@
       </c>
       <c r="I457" s="6"/>
     </row>
-    <row r="458" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A458" s="6">
         <v>30630553</v>
       </c>
@@ -20772,7 +20945,7 @@
       </c>
       <c r="I461" s="6"/>
     </row>
-    <row r="462" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A462" s="6">
         <v>30630553</v>
       </c>
@@ -20799,7 +20972,7 @@
       </c>
       <c r="I462" s="6"/>
     </row>
-    <row r="463" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A463" s="6">
         <v>30630553</v>
       </c>
@@ -20826,7 +20999,7 @@
       </c>
       <c r="I463" s="6"/>
     </row>
-    <row r="464" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A464" s="6">
         <v>30630553</v>
       </c>
@@ -20853,7 +21026,7 @@
       </c>
       <c r="I464" s="6"/>
     </row>
-    <row r="465" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A465" s="6">
         <v>30630553</v>
       </c>
@@ -20880,7 +21053,7 @@
       </c>
       <c r="I465" s="6"/>
     </row>
-    <row r="466" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A466" s="6">
         <v>30630553</v>
       </c>
@@ -20907,7 +21080,7 @@
       </c>
       <c r="I466" s="6"/>
     </row>
-    <row r="467" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A467" s="6">
         <v>30630553</v>
       </c>
@@ -20961,7 +21134,7 @@
       </c>
       <c r="I468" s="6"/>
     </row>
-    <row r="469" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A469" s="6">
         <v>30630553</v>
       </c>
@@ -20988,7 +21161,7 @@
       </c>
       <c r="I469" s="6"/>
     </row>
-    <row r="470" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A470" s="6">
         <v>30630553</v>
       </c>
@@ -21015,7 +21188,7 @@
       </c>
       <c r="I470" s="6"/>
     </row>
-    <row r="471" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A471" s="6">
         <v>30630553</v>
       </c>
@@ -21042,7 +21215,7 @@
       </c>
       <c r="I471" s="6"/>
     </row>
-    <row r="472" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:9" ht="63" x14ac:dyDescent="0.25">
       <c r="A472" s="6">
         <v>30630553</v>
       </c>
@@ -21069,7 +21242,7 @@
       </c>
       <c r="I472" s="6"/>
     </row>
-    <row r="473" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A473" s="6">
         <v>13795818</v>
       </c>
@@ -21096,7 +21269,7 @@
       </c>
       <c r="I473" s="6"/>
     </row>
-    <row r="474" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A474" s="6">
         <v>13795818</v>
       </c>
@@ -21123,7 +21296,7 @@
       </c>
       <c r="I474" s="6"/>
     </row>
-    <row r="475" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A475" s="6">
         <v>13795818</v>
       </c>
@@ -21150,7 +21323,7 @@
       </c>
       <c r="I475" s="6"/>
     </row>
-    <row r="476" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A476" s="6">
         <v>13795818</v>
       </c>
@@ -21177,7 +21350,7 @@
       </c>
       <c r="I476" s="6"/>
     </row>
-    <row r="477" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A477" s="6">
         <v>13795818</v>
       </c>
@@ -21204,7 +21377,7 @@
       </c>
       <c r="I477" s="6"/>
     </row>
-    <row r="478" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A478" s="6">
         <v>13795818</v>
       </c>
@@ -21233,7 +21406,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="479" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A479" s="6">
         <v>13795818</v>
       </c>
@@ -21262,7 +21435,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="480" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A480" s="6">
         <v>13795818</v>
       </c>
@@ -21320,7 +21493,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="482" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A482" s="6">
         <v>13795818</v>
       </c>
@@ -21349,7 +21522,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="483" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A483" s="6">
         <v>13795818</v>
       </c>
@@ -21378,7 +21551,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="484" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A484" s="6">
         <v>13795818</v>
       </c>
@@ -21405,7 +21578,7 @@
       </c>
       <c r="I484" s="6"/>
     </row>
-    <row r="485" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A485" s="6">
         <v>13795818</v>
       </c>
@@ -21463,7 +21636,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="487" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A487" s="6">
         <v>13795818</v>
       </c>
@@ -22033,6 +22206,222 @@
         <v>1806</v>
       </c>
       <c r="I507" s="6"/>
+    </row>
+    <row r="508" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A508" s="6">
+        <v>27606564</v>
+      </c>
+      <c r="B508" s="6">
+        <v>1</v>
+      </c>
+      <c r="C508" s="7" t="s">
+        <v>1817</v>
+      </c>
+      <c r="D508" s="7" t="s">
+        <v>1833</v>
+      </c>
+      <c r="E508" s="20">
+        <v>4.22</v>
+      </c>
+      <c r="F508" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G508" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H508" s="7" t="s">
+        <v>1825</v>
+      </c>
+      <c r="I508" s="6"/>
+    </row>
+    <row r="509" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A509" s="6">
+        <v>27606564</v>
+      </c>
+      <c r="B509" s="6">
+        <v>2</v>
+      </c>
+      <c r="C509" s="7" t="s">
+        <v>1818</v>
+      </c>
+      <c r="D509" s="7" t="s">
+        <v>1834</v>
+      </c>
+      <c r="E509" s="20">
+        <v>4.05</v>
+      </c>
+      <c r="F509" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G509" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H509" s="7" t="s">
+        <v>1826</v>
+      </c>
+      <c r="I509" s="6"/>
+    </row>
+    <row r="510" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A510" s="6">
+        <v>27606564</v>
+      </c>
+      <c r="B510" s="6">
+        <v>3</v>
+      </c>
+      <c r="C510" s="7" t="s">
+        <v>1819</v>
+      </c>
+      <c r="D510" s="7" t="s">
+        <v>1835</v>
+      </c>
+      <c r="E510" s="20">
+        <v>3.93</v>
+      </c>
+      <c r="F510" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G510" s="12">
+        <v>4.55</v>
+      </c>
+      <c r="H510" s="7" t="s">
+        <v>1827</v>
+      </c>
+      <c r="I510" s="6"/>
+    </row>
+    <row r="511" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A511" s="6">
+        <v>27606564</v>
+      </c>
+      <c r="B511" s="6">
+        <v>4</v>
+      </c>
+      <c r="C511" s="7" t="s">
+        <v>1820</v>
+      </c>
+      <c r="D511" s="7" t="s">
+        <v>1836</v>
+      </c>
+      <c r="E511" s="20">
+        <v>4.13</v>
+      </c>
+      <c r="F511" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G511" s="12">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="H511" s="7" t="s">
+        <v>1828</v>
+      </c>
+      <c r="I511" s="6"/>
+    </row>
+    <row r="512" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A512" s="6">
+        <v>27606564</v>
+      </c>
+      <c r="B512" s="6">
+        <v>5</v>
+      </c>
+      <c r="C512" s="7" t="s">
+        <v>1821</v>
+      </c>
+      <c r="D512" s="7" t="s">
+        <v>1837</v>
+      </c>
+      <c r="E512" s="20">
+        <v>4.08</v>
+      </c>
+      <c r="F512" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G512" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H512" s="7" t="s">
+        <v>1829</v>
+      </c>
+      <c r="I512" s="6"/>
+    </row>
+    <row r="513" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A513" s="6">
+        <v>27606564</v>
+      </c>
+      <c r="B513" s="6">
+        <v>6</v>
+      </c>
+      <c r="C513" s="7" t="s">
+        <v>1822</v>
+      </c>
+      <c r="D513" s="7" t="s">
+        <v>1838</v>
+      </c>
+      <c r="E513" s="20">
+        <v>4.29</v>
+      </c>
+      <c r="F513" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G513" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H513" s="7" t="s">
+        <v>1830</v>
+      </c>
+      <c r="I513" s="6"/>
+    </row>
+    <row r="514" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A514" s="6">
+        <v>27606564</v>
+      </c>
+      <c r="B514" s="6">
+        <v>7</v>
+      </c>
+      <c r="C514" s="7" t="s">
+        <v>1823</v>
+      </c>
+      <c r="D514" s="7" t="s">
+        <v>1839</v>
+      </c>
+      <c r="E514" s="20">
+        <v>4.21</v>
+      </c>
+      <c r="F514" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G514" s="12">
+        <v>4.55</v>
+      </c>
+      <c r="H514" s="7" t="s">
+        <v>1831</v>
+      </c>
+      <c r="I514" s="6"/>
+    </row>
+    <row r="515" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A515" s="6">
+        <v>27606564</v>
+      </c>
+      <c r="B515" s="6">
+        <v>8</v>
+      </c>
+      <c r="C515" s="7" t="s">
+        <v>1824</v>
+      </c>
+      <c r="D515" s="7" t="s">
+        <v>1840</v>
+      </c>
+      <c r="E515" s="20">
+        <v>3.39</v>
+      </c>
+      <c r="F515" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G515" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H515" s="7" t="s">
+        <v>1832</v>
+      </c>
+      <c r="I515" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76ED57D5-222D-4F63-84E1-87BBD7704D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E378B0F-2897-4187-B4A8-CD2E9A7ACB74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2039" uniqueCount="1844">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2103" uniqueCount="1907">
   <si>
     <t>No</t>
   </si>
@@ -5949,6 +5949,195 @@
   </si>
   <si>
     <t>Psychedelic Rock, Folk Rock [Cosmic Folk, Atmospheric Psych Rock]</t>
+  </si>
+  <si>
+    <t>King Hannah</t>
+  </si>
+  <si>
+    <t>I’m Not Sorry, I Was Just Being Me // Tell Me Your Mind And I'll Tell You Mine</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/26012116-King-Hannah-Im-Not-Sorry-I-Was-Just-Being-Me--Tell-Me-Your-Mind-And-Ill-Tell-You-Mine</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/PCKMe3yWf7C0QdouuoAWY6A-_bi9TD6-jYGS9lJ4Awo/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI2MDEy/MTE2LTE2NzU3MDgx/MzEtMTY1MS5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Indie Rock, Alternative Rock [Slowcore, Dream Pop, Noir Folk, Post-Punk]</t>
+  </si>
+  <si>
+    <t>City Slang – SLANG50329XX, Europe, 2023 (Deluxe Edition, Numbered, White with orange marbling LP &amp; Green with white marbling 12")</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Ευρωπαϊκή περιορισμένη έκδοση 1.700 αριθμημένων αντιτύπων σε gatefold εξώφυλλο (περιλαμβάνει το ντεμπούτο άλμπουμ I’m Not Sorry, I Was Just Being Me σε λευκό/πορτοκαλί marbled βινύλιο και το EP Tell Me Your Mind And I'll Tell You Mine σε πράσινο/λευκό marbled 12". Ταχύτητες: Side A/B/D στις 33⅓ RPM, Side C στις 45 RPM). Dream pop, indie rock και slowcore ατμόσφαιρες με υπνωτικά φωνητικά και κινηματογραφική κιθαριστική παραγωγή.</t>
+  </si>
+  <si>
+    <t>A Well-Made Woman</t>
+  </si>
+  <si>
+    <t>So Much Water So Close to Drone</t>
+  </si>
+  <si>
+    <t>All Being Fine</t>
+  </si>
+  <si>
+    <t>Big Big Baby</t>
+  </si>
+  <si>
+    <t>Ants Crawling On An Apple Stork</t>
+  </si>
+  <si>
+    <t>The Moods That I Get In</t>
+  </si>
+  <si>
+    <t>Foolius Caesar</t>
+  </si>
+  <si>
+    <t>Death Of The House Phone</t>
+  </si>
+  <si>
+    <t>Go-Kart Kid (HELL NO!)</t>
+  </si>
+  <si>
+    <t>I’m Not Sorry, I Was Just Being Me</t>
+  </si>
+  <si>
+    <t>Berenson</t>
+  </si>
+  <si>
+    <t>It’s Me And You, Kid</t>
+  </si>
+  <si>
+    <t>And Then Out Of Nowhere, It Rained</t>
+  </si>
+  <si>
+    <t>Meal Deal</t>
+  </si>
+  <si>
+    <t>Bill Tench</t>
+  </si>
+  <si>
+    <t>Crème Brûlée</t>
+  </si>
+  <si>
+    <t>The Sea Has Stretch Marks</t>
+  </si>
+  <si>
+    <t>Reprise (Moving Day)</t>
+  </si>
+  <si>
+    <t>State Trooper</t>
+  </si>
+  <si>
+    <t>Indie Rock, Alternative Rock [Noir Rock, Desert Rock, Slowcore]</t>
+  </si>
+  <si>
+    <t>Ambient, Indie Rock [Drone Interlude, Atmospheric Transition (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Indie Rock, Alternative Rock [Slowcore, Indie Folk, Confessional Rock]</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Indie Rock [Post-Punk, Grunge-tinged Indie Rock]</t>
+  </si>
+  <si>
+    <t>Indie Rock, Alternative Rock [Gothic Americana, Noir Folk, Slowcore]</t>
+  </si>
+  <si>
+    <t>Indie Rock, Psychedelic Rock [Slow-Burn Psych Rock, Dreamy Alternative]</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Indie Rock [Post-Punk, Dark Indie Rock]</t>
+  </si>
+  <si>
+    <t>Ambient, Indie Rock [Lo-Fi Interlude, Domestic Noir (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Indie Rock [Grunge-tinged Indie Rock, Guitar Rock]</t>
+  </si>
+  <si>
+    <t>Indie Rock, Alternative Rock [Slowcore, Gothic Americana, Indie Ballad]</t>
+  </si>
+  <si>
+    <t>Indie Rock, Dream Pop [Dreamy Indie Rock, Slowcore Closing Ballad]</t>
+  </si>
+  <si>
+    <t>Ambient, Indie Rock [Atmospheric Intro, Dream Pop (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Indie Rock, Alternative Rock [Slowcore, Noir Rock, Desert Blues]</t>
+  </si>
+  <si>
+    <t>Indie Rock, Blues Rock [Desert Blues, Slow-Burn Indie Rock]</t>
+  </si>
+  <si>
+    <t>Indie Rock, Blues Rock [Desert Blues, Noise Rock, Slowcore]</t>
+  </si>
+  <si>
+    <t>Indie Rock, Dream Pop [Dream Pop, Gothic Americana, Slowcore]</t>
+  </si>
+  <si>
+    <t>Ambient, Indie Rock [Ambient Folk, Slowcore Outro]</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Indie Rock [Bruce Springsteen Cover, Minimal Dark Rock]</t>
+  </si>
+  <si>
+    <t>It’s Me And You, Kid: Μελαγχολικό, σχεδόν τρυφερό φινάλε. Η φράση του τίτλου αποδέχεται μια μικρή, ατελή συμμαχία απέναντι στον έξω κόσμο: όχι μεγάλη ρομαντική υπόσχεση, αλλά η επιθυμία δύο ανθρώπων να αντέξουν τον χρόνο, την αμηχανία και τις διαθέσεις τους μαζί.</t>
+  </si>
+  <si>
+    <t>Επιβλητικό άνοιγμα με αργή, βαρύτονη κιθάρα και τη Hannah Merrick να τραγουδά σχεδόν σαν να αφηγείται μια σκοτεινή ιστορία σε άδειο δωμάτιο. Η μορφή της "καλοφτιαγμένης γυναίκας" δεν είναι άψογη ή υποδειγματική· μοιάζει να έχει χτιστεί μέσα από καθημερινές προσδοκίες, άμυνες και μια ήσυχη ανάγκη να μην της επιβληθούν ρόλοι.</t>
+  </si>
+  <si>
+    <t>Σύντομο, ατμοσφαιρικό instrumental που λειτουργεί σαν διάδρομος μεταξύ της εισαγωγικής βαρύτητας και της πιο εξομολογητικής επόμενης σύνθεσης. Η εικόνα του νερού δίπλα στο drone δίνει την αίσθηση μιας μεγάλης συναισθηματικής μάζας που παραμένει ακίνητη αλλά απειλητικά κοντά. [Instrumental]</t>
+  </si>
+  <si>
+    <t>Από τις πιο προσωπικές στιγμές του άλμπουμ. Μέσα από παιδικές μνήμες, αμηχανία και μικρές, σχεδόν ντροπιαστικές λεπτομέρειες, η Merrick αποδομεί το καθησυχαστικό "όλα είναι καλά". Δεν πρόκειται για δραματικό ξέσπασμα, αλλά για μια ήσυχη παραδοχή ότι η κανονικότητα συχνά είναι απλώς ένας τρόπος να κρύβονται πιο δύσκολα πράγματα.</t>
+  </si>
+  <si>
+    <t>Πιο κοφτό και ηλεκτρισμένο, με post-punk/grunge νεύρο. Η μπάντα σχολιάζει την ανωριμότητα, την προσκόλληση και τη συναισθηματική υπερβολή χωρίς να εγκαταλείπει το deadpan χιούμορ της. Το κομμάτι λειτουργεί σαν μικρό ξέσπασμα απέναντι σε κάποιον που απαιτεί διαρκώς προσοχή, επιβεβαίωση ή φροντίδα.</t>
+  </si>
+  <si>
+    <t>Παράξενο, σκοτεινά κινηματογραφικό και γεμάτο surreal εικόνες. Ο τίτλος μοιάζει με παιδικό εφιάλτη, ενώ η μουσική χτίζει αργά μια αίσθηση εισβολής: κάτι μικρό, επαναλαμβανόμενο και ενοχλητικό αρχίζει να κυριεύει το καθημερινό τοπίο.</t>
+  </si>
+  <si>
+    <t>Η μεγάλη slow-burn κορύφωση του πρώτου LP. Σε σχεδόν οκτώ λεπτά, οι King Hannah αφήνουν την κιθάρα να περάσει από υπνωτικό dream-rock σε πιο θορυβώδη ψυχεδελικό ξέσπασμα. Η σύνθεση παρακολουθεί τις διαθέσεις όχι ως τυχαίες μεταβολές, αλλά ως τοπία στα οποία ο άνθρωπος εισέρχεται και πρέπει να μάθει να επιβιώνει.</t>
+  </si>
+  <si>
+    <t>Σαρκαστικό dark indie-rock στιγμιότυπο. Ο τίτλος ενώνει το “fool” με τον Caesar και στοχεύει έναν μικρό τύραννο, έναν άνθρωπο που αντιμετωπίζει τον εαυτό του σαν σπουδαίο ηγέτη ενώ συμπεριφέρεται παιδικά. Η φράση “Stop actin’ like a baby” δίνει στον σαρκασμό καθαρό στόχο.</t>
+  </si>
+  <si>
+    <t>Μικρό instrumental/interlude που παίρνει ένα οικιακό αντικείμενο και το μετατρέπει σε σύμβολο αλλαγής. Το σταθερό τηλέφωνο του σπιτιού υποδηλώνει παλιές μορφές οικειότητας, αναμονής και οικογενειακής επικοινωνίας· η «θάνατός» του αφήνει πίσω ένα ήσυχο, κενό δωμάτιο. [Instrumental]</t>
+  </si>
+  <si>
+    <t>Από τις πιο άμεσες rock συνθέσεις. Η εικόνα του go-kart συνδέεται με παρορμητισμό, παιδική ταχύτητα και άρνηση να μετατραπεί κάποιος σε "σωστό" ενήλικα. Το “HELL NO!” λειτουργεί ως μικρό, θυμωμένο σύνθημα αυτοάμυνας, ενώ οι κιθάρες απαντούν με την πιο επιθετική ένταση του δίσκου.</t>
+  </si>
+  <si>
+    <t>Το title track είναι η ήρεμη αλλά σταθερή ηθική δήλωση του άλμπουμ. Οι καθημερινές αναφορές και η απλή αφήγηση δεν εξυπηρετούν μια πόζα αδιαφορίας: η Merrick υπερασπίζεται το δικαίωμα να είναι ατελής, αμήχανη, μοναχική ή διαφορετική χωρίς να μετατρέπει κάθε πτυχή του εαυτού της σε δημόσια απολογία.</t>
+  </si>
+  <si>
+    <t>Σύντομο οργανικό διάλειμμα με ατμοσφαιρική κιθάρα. Ο τίτλος λειτουργεί περισσότερο σαν κινηματογραφικό όνομα ή σημείο στον χάρτη παρά ως γραμμική αφήγηση. Προετοιμάζει το κλείσιμο, καθαρίζοντας τον χώρο μετά τη λυρική εξομολόγηση του title track. [Instrumental]</t>
+  </si>
+  <si>
+    <t>Σύντομο ambient intro, σαν αλλαγή καιρού που δίνει το σήμα της μετάβασης σε πιο γυμνό και νυχτερινό κόσμο. Η βροχή δεν λειτουργεί ως ρομαντικό σκηνικό, αλλά ως ένα ξαφνικό γεγονός που αλλάζει τον ήχο του δρόμου και τη διάθεση ενός δωματίου. [Instrumental]</t>
+  </si>
+  <si>
+    <t>Η μεγάλη slowcore/noir στιγμή του EP. Ο καθημερινός τίτλος κρύβει μια αίσθηση συναισθηματικής πείνας, ρουτίνας και χαμηλού κόστους επιβίωσης. Η φωνή της Merrick παραμένει αποστασιοποιημένη, ενώ η κιθάρα του Whittle αφήνει το τραγούδι να μεγαλώνει υπομονετικά σε ένα σχεδόν desert-rock τοπίο.</t>
+  </si>
+  <si>
+    <t>Αργό desert-blues character study. Το όνομα του τίτλου μοιάζει να ανήκει σε άνθρωπο που περιπλανιέται ανάμεσα σε μικρές πόλεις, προσωπικά αδιέξοδα και σιωπηλές ενοχές. Η κιθάρα δημιουργεί ξερό, σκονισμένο χώρο, όπου κάθε φράση ακούγεται σαν βήμα σε άδειο parking lot.</t>
+  </si>
+  <si>
+    <t>Από τις καθοριστικές συνθέσεις των King Hannah. Η αντίθεση του γλυκού τίτλου με τη σκοτεινή, παραμορφωμένη κιθάρα συνοψίζει την αισθητική τους, χιούμορ, επιθυμία και απειλή μέσα στο ίδιο τραγούδι. Η μουσική ξεκινά υπομονετικά και καταλήγει σε ένα πυκνό slow-burn noise/blues ξέσπασμα, χωρίς να χάνει ποτέ τη στοιχειωμένη ψυχραιμία της φωνής.</t>
+  </si>
+  <si>
+    <t>Dream-pop/slowcore κομμάτι που μετατρέπει τη θάλασσα σε ανθρώπινο, φθαρτό σώμα. Η μεταφορά αναφέρεται στη μνήμη, στην έκταση, στη φθορά και στις αλλαγές που αφήνουν σημάδια ακόμη και στα πιο απέραντα τοπία. Είναι από τα πιο ποιητικά και ατμοσφαιρικά tracks του set.</t>
+  </si>
+  <si>
+    <t>Λιτό, ambient-folk κλείσιμο του αρχικού EP. Η "ημέρα μετακόμισης" παραπέμπει σε κουτιά, αντικείμενα, αποχωρισμούς και μικρές ζωές που ξετυλίγονται από έναν χώρο. Δεν κλείνει με κάθαρση, αλλά με τη σιωπηλή αποδοχή ότι κάθε μετακίνηση αφήνει ένα κομμάτι σου πίσω. [Instrumental]</t>
+  </si>
+  <si>
+    <t>Μινιμαλιστική διασκευή του Bruce Springsteen και bonus track της deluxe έκδοσής σου. Οι King Hannah αφαιρούν κάθε περιττή κίνηση και κρατούν την παράνοια/φόβο της νυχτερινής οδήγησης: η επανάληψη, ο κενός δρόμος και η υποψία μιας απειλής δημιουργούν ψυχολογικό thriller σε slow-motion.</t>
   </si>
 </sst>
 </file>
@@ -6467,7 +6656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J57"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -6477,7 +6666,7 @@
     <col min="5" max="5" width="10.7109375" style="1" customWidth="1"/>
     <col min="6" max="6" width="35.7109375" style="1" customWidth="1"/>
     <col min="7" max="7" width="96.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="25.7109375" style="1" customWidth="1"/>
     <col min="9" max="9" width="35" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="50.42578125" style="1" customWidth="1"/>
     <col min="11" max="16384" width="9.140625" style="1"/>
@@ -8305,6 +8494,38 @@
       </c>
       <c r="J57" s="11" t="s">
         <v>1797</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A58" s="6">
+        <v>26012116</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>1844</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>1845</v>
+      </c>
+      <c r="D58" s="6">
+        <v>2022</v>
+      </c>
+      <c r="E58" s="10">
+        <v>3.4</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>1848</v>
+      </c>
+      <c r="G58" s="7" t="s">
+        <v>1850</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>1849</v>
+      </c>
+      <c r="I58" s="11" t="s">
+        <v>1846</v>
+      </c>
+      <c r="J58" s="11" t="s">
+        <v>1847</v>
       </c>
     </row>
   </sheetData>
@@ -8419,6 +8640,8 @@
     <hyperlink ref="I56" r:id="rId108" xr:uid="{39AA173B-82EA-49C0-AB10-59F5102644AE}"/>
     <hyperlink ref="I57" r:id="rId109" xr:uid="{AF006A7D-90EE-4043-B23C-FCFA92E4B64D}"/>
     <hyperlink ref="J57" r:id="rId110" xr:uid="{54C8F634-D910-413C-87D6-1278DAF31A3D}"/>
+    <hyperlink ref="I58" r:id="rId111" xr:uid="{0DB723D1-7E83-4837-BD4C-0EE522F370EB}"/>
+    <hyperlink ref="J58" r:id="rId112" xr:uid="{F7626FDC-49F2-48D7-8AB4-747CB4E5205A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8426,7 +8649,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I515"/>
+  <dimension ref="A1:I534"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -22432,6 +22655,519 @@
       </c>
       <c r="I515" s="6"/>
     </row>
+    <row r="516" spans="1:9" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A516" s="6">
+        <v>26012116</v>
+      </c>
+      <c r="B516" s="6">
+        <v>1</v>
+      </c>
+      <c r="C516" s="7" t="s">
+        <v>1851</v>
+      </c>
+      <c r="D516" s="7" t="s">
+        <v>1870</v>
+      </c>
+      <c r="E516" s="20">
+        <v>3.75</v>
+      </c>
+      <c r="F516" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G516" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H516" s="7" t="s">
+        <v>1889</v>
+      </c>
+      <c r="I516" s="6"/>
+    </row>
+    <row r="517" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A517" s="6">
+        <v>26012116</v>
+      </c>
+      <c r="B517" s="6">
+        <v>2</v>
+      </c>
+      <c r="C517" s="7" t="s">
+        <v>1852</v>
+      </c>
+      <c r="D517" s="7" t="s">
+        <v>1871</v>
+      </c>
+      <c r="E517" s="20">
+        <v>3.45</v>
+      </c>
+      <c r="F517" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="G517" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H517" s="7" t="s">
+        <v>1890</v>
+      </c>
+      <c r="I517" s="6"/>
+    </row>
+    <row r="518" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A518" s="6">
+        <v>26012116</v>
+      </c>
+      <c r="B518" s="6">
+        <v>3</v>
+      </c>
+      <c r="C518" s="7" t="s">
+        <v>1853</v>
+      </c>
+      <c r="D518" s="7" t="s">
+        <v>1872</v>
+      </c>
+      <c r="E518" s="20">
+        <v>3.75</v>
+      </c>
+      <c r="F518" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G518" s="12">
+        <v>4.45</v>
+      </c>
+      <c r="H518" s="7" t="s">
+        <v>1891</v>
+      </c>
+      <c r="I518" s="6"/>
+    </row>
+    <row r="519" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A519" s="6">
+        <v>26012116</v>
+      </c>
+      <c r="B519" s="6">
+        <v>4</v>
+      </c>
+      <c r="C519" s="7" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D519" s="7" t="s">
+        <v>1873</v>
+      </c>
+      <c r="E519" s="20">
+        <v>3.62</v>
+      </c>
+      <c r="F519" s="12">
+        <v>4</v>
+      </c>
+      <c r="G519" s="12">
+        <v>4.55</v>
+      </c>
+      <c r="H519" s="7" t="s">
+        <v>1892</v>
+      </c>
+      <c r="I519" s="6"/>
+    </row>
+    <row r="520" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A520" s="6">
+        <v>26012116</v>
+      </c>
+      <c r="B520" s="6">
+        <v>5</v>
+      </c>
+      <c r="C520" s="7" t="s">
+        <v>1855</v>
+      </c>
+      <c r="D520" s="7" t="s">
+        <v>1874</v>
+      </c>
+      <c r="E520" s="20">
+        <v>3.37</v>
+      </c>
+      <c r="F520" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G520" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H520" s="7" t="s">
+        <v>1893</v>
+      </c>
+      <c r="I520" s="6"/>
+    </row>
+    <row r="521" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A521" s="6">
+        <v>26012116</v>
+      </c>
+      <c r="B521" s="6">
+        <v>6</v>
+      </c>
+      <c r="C521" s="7" t="s">
+        <v>1856</v>
+      </c>
+      <c r="D521" s="7" t="s">
+        <v>1875</v>
+      </c>
+      <c r="E521" s="20">
+        <v>3.95</v>
+      </c>
+      <c r="F521" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G521" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H521" s="7" t="s">
+        <v>1894</v>
+      </c>
+      <c r="I521" s="6"/>
+    </row>
+    <row r="522" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A522" s="6">
+        <v>26012116</v>
+      </c>
+      <c r="B522" s="6">
+        <v>7</v>
+      </c>
+      <c r="C522" s="7" t="s">
+        <v>1857</v>
+      </c>
+      <c r="D522" s="7" t="s">
+        <v>1876</v>
+      </c>
+      <c r="E522" s="20">
+        <v>3.72</v>
+      </c>
+      <c r="F522" s="12">
+        <v>4</v>
+      </c>
+      <c r="G522" s="12">
+        <v>4.45</v>
+      </c>
+      <c r="H522" s="7" t="s">
+        <v>1895</v>
+      </c>
+      <c r="I522" s="6"/>
+    </row>
+    <row r="523" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A523" s="6">
+        <v>26012116</v>
+      </c>
+      <c r="B523" s="6">
+        <v>8</v>
+      </c>
+      <c r="C523" s="7" t="s">
+        <v>1858</v>
+      </c>
+      <c r="D523" s="7" t="s">
+        <v>1877</v>
+      </c>
+      <c r="E523" s="20">
+        <v>3.61</v>
+      </c>
+      <c r="F523" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="G523" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H523" s="7" t="s">
+        <v>1896</v>
+      </c>
+      <c r="I523" s="6"/>
+    </row>
+    <row r="524" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A524" s="6">
+        <v>26012116</v>
+      </c>
+      <c r="B524" s="6">
+        <v>9</v>
+      </c>
+      <c r="C524" s="7" t="s">
+        <v>1859</v>
+      </c>
+      <c r="D524" s="7" t="s">
+        <v>1878</v>
+      </c>
+      <c r="E524" s="20">
+        <v>3.66</v>
+      </c>
+      <c r="F524" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G524" s="12">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="H524" s="7" t="s">
+        <v>1897</v>
+      </c>
+      <c r="I524" s="6"/>
+    </row>
+    <row r="525" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A525" s="6">
+        <v>26012116</v>
+      </c>
+      <c r="B525" s="6">
+        <v>10</v>
+      </c>
+      <c r="C525" s="7" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D525" s="7" t="s">
+        <v>1879</v>
+      </c>
+      <c r="E525" s="20">
+        <v>3.26</v>
+      </c>
+      <c r="F525" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G525" s="12">
+        <v>4.55</v>
+      </c>
+      <c r="H525" s="7" t="s">
+        <v>1898</v>
+      </c>
+      <c r="I525" s="6"/>
+    </row>
+    <row r="526" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A526" s="6">
+        <v>26012116</v>
+      </c>
+      <c r="B526" s="6">
+        <v>11</v>
+      </c>
+      <c r="C526" s="7" t="s">
+        <v>1861</v>
+      </c>
+      <c r="D526" s="7" t="s">
+        <v>1648</v>
+      </c>
+      <c r="E526" s="20">
+        <v>3.31</v>
+      </c>
+      <c r="F526" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G526" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H526" s="7" t="s">
+        <v>1899</v>
+      </c>
+      <c r="I526" s="6"/>
+    </row>
+    <row r="527" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A527" s="6">
+        <v>26012116</v>
+      </c>
+      <c r="B527" s="6">
+        <v>12</v>
+      </c>
+      <c r="C527" s="7" t="s">
+        <v>1862</v>
+      </c>
+      <c r="D527" s="7" t="s">
+        <v>1880</v>
+      </c>
+      <c r="E527" s="20">
+        <v>3.73</v>
+      </c>
+      <c r="F527" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G527" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H527" s="7" t="s">
+        <v>1888</v>
+      </c>
+      <c r="I527" s="6"/>
+    </row>
+    <row r="528" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A528" s="6">
+        <v>26012116</v>
+      </c>
+      <c r="B528" s="6">
+        <v>13</v>
+      </c>
+      <c r="C528" s="7" t="s">
+        <v>1863</v>
+      </c>
+      <c r="D528" s="7" t="s">
+        <v>1881</v>
+      </c>
+      <c r="E528" s="20">
+        <v>3.86</v>
+      </c>
+      <c r="F528" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G528" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H528" s="7" t="s">
+        <v>1900</v>
+      </c>
+      <c r="I528" s="6"/>
+    </row>
+    <row r="529" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A529" s="6">
+        <v>26012116</v>
+      </c>
+      <c r="B529" s="6">
+        <v>14</v>
+      </c>
+      <c r="C529" s="7" t="s">
+        <v>1864</v>
+      </c>
+      <c r="D529" s="7" t="s">
+        <v>1882</v>
+      </c>
+      <c r="E529" s="20">
+        <v>3.99</v>
+      </c>
+      <c r="F529" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G529" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H529" s="7" t="s">
+        <v>1901</v>
+      </c>
+      <c r="I529" s="6"/>
+    </row>
+    <row r="530" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A530" s="6">
+        <v>26012116</v>
+      </c>
+      <c r="B530" s="6">
+        <v>15</v>
+      </c>
+      <c r="C530" s="7" t="s">
+        <v>1865</v>
+      </c>
+      <c r="D530" s="7" t="s">
+        <v>1883</v>
+      </c>
+      <c r="E530" s="20">
+        <v>3.96</v>
+      </c>
+      <c r="F530" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G530" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H530" s="7" t="s">
+        <v>1902</v>
+      </c>
+      <c r="I530" s="6"/>
+    </row>
+    <row r="531" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A531" s="6">
+        <v>26012116</v>
+      </c>
+      <c r="B531" s="6">
+        <v>16</v>
+      </c>
+      <c r="C531" s="7" t="s">
+        <v>1866</v>
+      </c>
+      <c r="D531" s="7" t="s">
+        <v>1884</v>
+      </c>
+      <c r="E531" s="20">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="F531" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G531" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H531" s="7" t="s">
+        <v>1903</v>
+      </c>
+      <c r="I531" s="6"/>
+    </row>
+    <row r="532" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A532" s="6">
+        <v>26012116</v>
+      </c>
+      <c r="B532" s="6">
+        <v>17</v>
+      </c>
+      <c r="C532" s="7" t="s">
+        <v>1867</v>
+      </c>
+      <c r="D532" s="7" t="s">
+        <v>1885</v>
+      </c>
+      <c r="E532" s="20">
+        <v>3.96</v>
+      </c>
+      <c r="F532" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G532" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H532" s="7" t="s">
+        <v>1904</v>
+      </c>
+      <c r="I532" s="6"/>
+    </row>
+    <row r="533" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A533" s="6">
+        <v>26012116</v>
+      </c>
+      <c r="B533" s="6">
+        <v>18</v>
+      </c>
+      <c r="C533" s="7" t="s">
+        <v>1868</v>
+      </c>
+      <c r="D533" s="7" t="s">
+        <v>1886</v>
+      </c>
+      <c r="E533" s="20">
+        <v>3.82</v>
+      </c>
+      <c r="F533" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G533" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H533" s="7" t="s">
+        <v>1905</v>
+      </c>
+      <c r="I533" s="6"/>
+    </row>
+    <row r="534" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A534" s="6">
+        <v>26012116</v>
+      </c>
+      <c r="B534" s="6">
+        <v>19</v>
+      </c>
+      <c r="C534" s="7" t="s">
+        <v>1869</v>
+      </c>
+      <c r="D534" s="7" t="s">
+        <v>1887</v>
+      </c>
+      <c r="E534" s="20">
+        <v>2.5</v>
+      </c>
+      <c r="F534" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G534" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H534" s="7" t="s">
+        <v>1906</v>
+      </c>
+      <c r="I534" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E378B0F-2897-4187-B4A8-CD2E9A7ACB74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{853D49D6-B5D3-4B04-8FAC-8AD44F2590C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7152,7 +7152,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>2138840</v>
       </c>
@@ -7184,7 +7184,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="73.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="63" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>10867099</v>
       </c>
@@ -7504,7 +7504,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="42" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>22420804</v>
       </c>
@@ -7536,7 +7536,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="42" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>31880233</v>
       </c>
@@ -7568,7 +7568,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>31700342</v>
       </c>
@@ -7920,7 +7920,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" ht="42" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>31683230</v>
       </c>
@@ -7984,7 +7984,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" ht="42" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>25885156</v>
       </c>
@@ -8112,7 +8112,7 @@
         <v>1347</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" ht="42" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>26909678</v>
       </c>
@@ -8176,7 +8176,7 @@
         <v>1405</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" ht="42" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>23803544</v>
       </c>
@@ -8336,7 +8336,7 @@
         <v>1594</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>30630553</v>
       </c>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{853D49D6-B5D3-4B04-8FAC-8AD44F2590C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9F8CF5C-FE10-4B8A-B4E6-D18C6865653A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2103" uniqueCount="1907">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2143" uniqueCount="1947">
   <si>
     <t>No</t>
   </si>
@@ -6138,6 +6138,126 @@
   </si>
   <si>
     <t>Μινιμαλιστική διασκευή του Bruce Springsteen και bonus track της deluxe έκδοσής σου. Οι King Hannah αφαιρούν κάθε περιττή κίνηση και κρατούν την παράνοια/φόβο της νυχτερινής οδήγησης: η επανάληψη, ο κενός δρόμος και η υποψία μιας απειλής δημιουργούν ψυχολογικό thriller σε slow-motion.</t>
+  </si>
+  <si>
+    <t>Interpol</t>
+  </si>
+  <si>
+    <t>The Other Side Of Make-Believe</t>
+  </si>
+  <si>
+    <t>Toni</t>
+  </si>
+  <si>
+    <t>Fables</t>
+  </si>
+  <si>
+    <t>Into The Night</t>
+  </si>
+  <si>
+    <t>Something Changed</t>
+  </si>
+  <si>
+    <t>Passenger</t>
+  </si>
+  <si>
+    <t>Gran Hotel</t>
+  </si>
+  <si>
+    <t>Big Shot City</t>
+  </si>
+  <si>
+    <t>Go Easy (Palermo)</t>
+  </si>
+  <si>
+    <t>Mr. Credit (Vocals [Guest Vocals] – Flood, Jacob Tresidder, Juliet Seger, Richie Kennedy)</t>
+  </si>
+  <si>
+    <t>Renegade Hearts (Vocals [Guest Vocals] – Juliet Seger)</t>
+  </si>
+  <si>
+    <t>Greenwich (Vocals [Guest Vocals] – Juliet Seger)</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/33564954-Interpol-The-Other-Side-Of-Make-Believe</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/lAJqcWLgT9VCLDDIMPJ2R0tFGGYAPULvcSvdsX2Lc00/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTMzNTY0/OTU0LTE3NDM0MjU0/NzUtNzU3NS5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Post-Punk Revival, Indie Rock [Art Rock, Darkwave, Alternative Rock]</t>
+  </si>
+  <si>
+    <t>Indie Rock, Post-Punk Revival [Darkwave, Cinematic Indie Rock]</t>
+  </si>
+  <si>
+    <t>Post-Punk Revival, Indie Rock [Atmospheric Art Rock, Dark Indie]</t>
+  </si>
+  <si>
+    <t>Indie Rock, Alternative Rock [Nocturnal Rock, Dreamy Post-Punk]</t>
+  </si>
+  <si>
+    <t>Indie Rock, Post-Punk Revival [Bass-driven Dark Rock, Art Rock]</t>
+  </si>
+  <si>
+    <t>Indie Rock, Chamber Pop [Piano-led Art Rock, Baroque Indie]</t>
+  </si>
+  <si>
+    <t>Post-Punk Revival, Indie Rock [Dark Romantic Rock, Atmospheric Indie]</t>
+  </si>
+  <si>
+    <t>Indie Rock, Alternative Rock [Melodic Dark Rock, Post-Punk Ballad]</t>
+  </si>
+  <si>
+    <t>Post-Punk Revival, Indie Rock [Gloomy Art Rock, Minimalist Post-Punk]</t>
+  </si>
+  <si>
+    <t>Indie Rock, Alternative Rock [Noir Rock, Slow-Burn Indie]</t>
+  </si>
+  <si>
+    <t>Post-Punk Revival, Indie Rock [Driving Alternative Rock, Darkwave Rock]</t>
+  </si>
+  <si>
+    <t>Indie Rock, Ambient [Atmospheric Outro, Dream Pop]</t>
+  </si>
+  <si>
+    <t>Matador – OLE1875LP, Europe, Jul 15, 2022, Vinyl, LP, Album, Limited Edition, Red</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Ευρωπαϊκή περιορισμένη έκδοση σε κόκκινο βινύλιο (Red Vinyl) του 2022. Ηχογράφηση στα Battery Studios (Λονδίνο) με παραγωγή από τον Flood και mastering στα Sterling Sound (NJ) από τους Greg Calbi και Steve Fallone. Pressed by Optimal Media GmbH (BM64087). Περιλαμβάνει τυπωμένο εσωτερικό sleeve.</t>
+  </si>
+  <si>
+    <t>Ατμοσφαιρικό opening με κυκλική κιθάρα, σταθερό μπάσο και τον Banks να τραγουδά για μια ερωτική ή ψυχική φυγή. Ο τίτλος λειτουργεί σαν όνομα-σύμβολο, ενώ η μουσική κινείται ανάμεσα σε post-punk πειθαρχία και dreamlike κινηματογραφικότητα.</t>
+  </si>
+  <si>
+    <t>Νυχτερινό και μελωδικό, με έντονη αίσθηση κίνησης. Η νύχτα εδώ δεν είναι απλώς σκηνικό αλλά κατάσταση συνείδησης, ένας χώρος όπου ο αφηγητής μπορεί να απομακρυνθεί από την κοινωνική ταυτότητα και να κινηθεί πιο ελεύθερα.</t>
+  </si>
+  <si>
+    <t>Πιο εσωτερικό και αργό, με κιθάρες που δημιουργούν αίσθηση ομίχλης. Οι "μύθοι" του τίτλου παραπέμπουν στις ιστορίες που λέμε στον εαυτό μας για να αντέξουμε σχέσεις, αναμνήσεις και απογοητεύσεις.</t>
+  </si>
+  <si>
+    <t>Bass-driven, ειρωνικό και πιο νευρικό. Ο τίτλος παραπέμπει σε χρέος, οικονομική πίεση ή σε έναν απρόσωπο μηχανισμό που διεκδικεί συνεχώς κάτι από εσένα. Οι Interpol μετατρέπουν την οικονομική γλώσσα σε σκοτεινό art-rock χαρακτήρα.</t>
+  </si>
+  <si>
+    <t>Πιο ευάλωτο, piano-led κομμάτι με chamber-pop χροιά. Το τραγούδι αποτυπώνει τη στιγμή κατά την οποία μια σχέση ή μια εσωτερική κατάσταση δεν μπορεί πλέον να επιστρέψει στην προηγούμενη μορφή της. Η αλλαγή είναι μικρή στην επιφάνεια αλλά οριστική.</t>
+  </si>
+  <si>
+    <t>Ρομαντικό αλλά όχι αισιόδοξο. Οι "αντάρτικες καρδιές" υποδηλώνουν ανθρώπους που θέλουν σύνδεση αλλά αρνούνται να προσαρμοστούν στους κανόνες της. Η παραγωγή χτίζει αργά ένταση, με σκοτεινό βάθος στα drums και στις κιθάρες.</t>
+  </si>
+  <si>
+    <t>Μελαγχολικό και μελωδικό, μιλά για τη θέση του ανθρώπου που παρατηρεί τη ζωή του από απόσταση. Ο “passenger” δεν κρατά το τιμόνι· μεταφέρεται από γεγονότα, σχέσεις και αποφάσεις που ίσως δεν ελέγχει πλέον.</t>
+  </si>
+  <si>
+    <t>Αστικό, ψυχρό και ατμοσφαιρικό. Ο γεωγραφικός τίτλος προσφέρει συγκεκριμένο τόπο, όμως η μουσική τον μετατρέπει σε ψυχολογικό τοπίο, δρόμοι, χρόνος, απόσταση και ένας άνθρωπος που προσπαθεί να βρει προσανατολισμό.</t>
+  </si>
+  <si>
+    <t>Από τις πιο δυνατές συνθέσεις της δεύτερης πλευράς. Έχει αίσθηση παλιού ξενοδοχείου, προσωρινής ταυτότητας και σχέσεων που συμβαίνουν σε χώρο όπου κανείς δεν μένει για πάντα. Η αργή ανάπτυξη και οι κιθαριστικές σκιές δίνουν στο κομμάτι noir κινηματογραφικότητα.</t>
+  </si>
+  <si>
+    <t>Πιο αποφασιστικό και ρυθμικά κινητικό, με post-punk drive. Η “μεγάλη πόλη” γίνεται χώρος φιλοδοξίας, ανταγωνισμού και ανωνυμίας· το τραγούδι αναγνωρίζει τη γοητεία της, αλλά και το τίμημα του να πρέπει συνεχώς να αποδεικνύεις την αξία σου.</t>
+  </si>
+  <si>
+    <t>Ατμοσφαιρικό closing track, σχεδόν σαν απομάκρυνση από το album. Η αναφορά στο Palermo φέρνει μεσογειακή/ταξιδιωτική εικόνα, αλλά η μουσική παραμένει εσωστρεφής. Το “go easy” ακούγεται σαν συμβουλή προς τον εαυτό: να χαμηλώσεις την ένταση, να δεχτείς την αβεβαιότητα και να φύγεις χωρίς θόρυβο.</t>
   </si>
 </sst>
 </file>
@@ -6656,7 +6776,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -8526,6 +8646,38 @@
       </c>
       <c r="J58" s="11" t="s">
         <v>1847</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+      <c r="A59" s="6">
+        <v>33564954</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>1907</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>1908</v>
+      </c>
+      <c r="D59" s="6">
+        <v>2022</v>
+      </c>
+      <c r="E59" s="10">
+        <v>2.72</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G59" s="7" t="s">
+        <v>1935</v>
+      </c>
+      <c r="H59" s="6" t="s">
+        <v>1934</v>
+      </c>
+      <c r="I59" s="11" t="s">
+        <v>1920</v>
+      </c>
+      <c r="J59" s="11" t="s">
+        <v>1921</v>
       </c>
     </row>
   </sheetData>
@@ -8642,6 +8794,8 @@
     <hyperlink ref="J57" r:id="rId110" xr:uid="{54C8F634-D910-413C-87D6-1278DAF31A3D}"/>
     <hyperlink ref="I58" r:id="rId111" xr:uid="{0DB723D1-7E83-4837-BD4C-0EE522F370EB}"/>
     <hyperlink ref="J58" r:id="rId112" xr:uid="{F7626FDC-49F2-48D7-8AB4-747CB4E5205A}"/>
+    <hyperlink ref="I59" r:id="rId113" xr:uid="{1A6A9BEB-14DD-452B-B093-004CC31CBC62}"/>
+    <hyperlink ref="J59" r:id="rId114" xr:uid="{0352086C-B63D-43D9-94F4-B89DC5E6CD8F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8649,7 +8803,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I534"/>
+  <dimension ref="A1:I545"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -23168,6 +23322,303 @@
       </c>
       <c r="I534" s="6"/>
     </row>
+    <row r="535" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A535" s="6">
+        <v>33564954</v>
+      </c>
+      <c r="B535" s="6">
+        <v>1</v>
+      </c>
+      <c r="C535" s="7" t="s">
+        <v>1909</v>
+      </c>
+      <c r="D535" s="7" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E535" s="20">
+        <v>3.58</v>
+      </c>
+      <c r="F535" s="12">
+        <v>4</v>
+      </c>
+      <c r="G535" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="H535" s="7" t="s">
+        <v>1936</v>
+      </c>
+      <c r="I535" s="6"/>
+    </row>
+    <row r="536" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A536" s="6">
+        <v>33564954</v>
+      </c>
+      <c r="B536" s="6">
+        <v>2</v>
+      </c>
+      <c r="C536" s="7" t="s">
+        <v>1910</v>
+      </c>
+      <c r="D536" s="7" t="s">
+        <v>1924</v>
+      </c>
+      <c r="E536" s="20">
+        <v>3.1</v>
+      </c>
+      <c r="F536" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="G536" s="12">
+        <v>3.4</v>
+      </c>
+      <c r="H536" s="7" t="s">
+        <v>1938</v>
+      </c>
+      <c r="I536" s="6"/>
+    </row>
+    <row r="537" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A537" s="6">
+        <v>33564954</v>
+      </c>
+      <c r="B537" s="6">
+        <v>3</v>
+      </c>
+      <c r="C537" s="7" t="s">
+        <v>1911</v>
+      </c>
+      <c r="D537" s="7" t="s">
+        <v>1925</v>
+      </c>
+      <c r="E537" s="20">
+        <v>3.04</v>
+      </c>
+      <c r="F537" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G537" s="12">
+        <v>3.45</v>
+      </c>
+      <c r="H537" s="7" t="s">
+        <v>1937</v>
+      </c>
+      <c r="I537" s="6"/>
+    </row>
+    <row r="538" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A538" s="6">
+        <v>33564954</v>
+      </c>
+      <c r="B538" s="6">
+        <v>4</v>
+      </c>
+      <c r="C538" s="7" t="s">
+        <v>1917</v>
+      </c>
+      <c r="D538" s="7" t="s">
+        <v>1926</v>
+      </c>
+      <c r="E538" s="20">
+        <v>3.15</v>
+      </c>
+      <c r="F538" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="G538" s="12">
+        <v>3.75</v>
+      </c>
+      <c r="H538" s="7" t="s">
+        <v>1939</v>
+      </c>
+      <c r="I538" s="6"/>
+    </row>
+    <row r="539" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A539" s="6">
+        <v>33564954</v>
+      </c>
+      <c r="B539" s="6">
+        <v>5</v>
+      </c>
+      <c r="C539" s="7" t="s">
+        <v>1912</v>
+      </c>
+      <c r="D539" s="7" t="s">
+        <v>1927</v>
+      </c>
+      <c r="E539" s="20">
+        <v>3.29</v>
+      </c>
+      <c r="F539" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="G539" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="H539" s="7" t="s">
+        <v>1940</v>
+      </c>
+      <c r="I539" s="6"/>
+    </row>
+    <row r="540" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A540" s="6">
+        <v>33564954</v>
+      </c>
+      <c r="B540" s="6">
+        <v>6</v>
+      </c>
+      <c r="C540" s="7" t="s">
+        <v>1918</v>
+      </c>
+      <c r="D540" s="7" t="s">
+        <v>1928</v>
+      </c>
+      <c r="E540" s="20">
+        <v>3.12</v>
+      </c>
+      <c r="F540" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G540" s="12">
+        <v>3.55</v>
+      </c>
+      <c r="H540" s="7" t="s">
+        <v>1941</v>
+      </c>
+      <c r="I540" s="6"/>
+    </row>
+    <row r="541" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A541" s="6">
+        <v>33564954</v>
+      </c>
+      <c r="B541" s="6">
+        <v>7</v>
+      </c>
+      <c r="C541" s="7" t="s">
+        <v>1913</v>
+      </c>
+      <c r="D541" s="7" t="s">
+        <v>1929</v>
+      </c>
+      <c r="E541" s="20">
+        <v>3.25</v>
+      </c>
+      <c r="F541" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="G541" s="12">
+        <v>3.45</v>
+      </c>
+      <c r="H541" s="7" t="s">
+        <v>1942</v>
+      </c>
+      <c r="I541" s="6"/>
+    </row>
+    <row r="542" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A542" s="6">
+        <v>33564954</v>
+      </c>
+      <c r="B542" s="6">
+        <v>8</v>
+      </c>
+      <c r="C542" s="7" t="s">
+        <v>1919</v>
+      </c>
+      <c r="D542" s="7" t="s">
+        <v>1930</v>
+      </c>
+      <c r="E542" s="20">
+        <v>2.76</v>
+      </c>
+      <c r="F542" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G542" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="H542" s="7" t="s">
+        <v>1943</v>
+      </c>
+      <c r="I542" s="6"/>
+    </row>
+    <row r="543" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A543" s="6">
+        <v>33564954</v>
+      </c>
+      <c r="B543" s="6">
+        <v>9</v>
+      </c>
+      <c r="C543" s="7" t="s">
+        <v>1914</v>
+      </c>
+      <c r="D543" s="7" t="s">
+        <v>1931</v>
+      </c>
+      <c r="E543" s="20">
+        <v>3.35</v>
+      </c>
+      <c r="F543" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G543" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="H543" s="7" t="s">
+        <v>1944</v>
+      </c>
+      <c r="I543" s="6"/>
+    </row>
+    <row r="544" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A544" s="6">
+        <v>33564954</v>
+      </c>
+      <c r="B544" s="6">
+        <v>10</v>
+      </c>
+      <c r="C544" s="7" t="s">
+        <v>1915</v>
+      </c>
+      <c r="D544" s="7" t="s">
+        <v>1932</v>
+      </c>
+      <c r="E544" s="20">
+        <v>2.95</v>
+      </c>
+      <c r="F544" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G544" s="12">
+        <v>3.55</v>
+      </c>
+      <c r="H544" s="7" t="s">
+        <v>1945</v>
+      </c>
+      <c r="I544" s="6"/>
+    </row>
+    <row r="545" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A545" s="6">
+        <v>33564954</v>
+      </c>
+      <c r="B545" s="6">
+        <v>11</v>
+      </c>
+      <c r="C545" s="7" t="s">
+        <v>1916</v>
+      </c>
+      <c r="D545" s="7" t="s">
+        <v>1933</v>
+      </c>
+      <c r="E545" s="20">
+        <v>2.88</v>
+      </c>
+      <c r="F545" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G545" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="H545" s="7" t="s">
+        <v>1946</v>
+      </c>
+      <c r="I545" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9F8CF5C-FE10-4B8A-B4E6-D18C6865653A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCDB1FEA-A5A9-471C-B457-AF2C5D1E5C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2143" uniqueCount="1947">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2171" uniqueCount="1975">
   <si>
     <t>No</t>
   </si>
@@ -6258,6 +6258,90 @@
   </si>
   <si>
     <t>Ατμοσφαιρικό closing track, σχεδόν σαν απομάκρυνση από το album. Η αναφορά στο Palermo φέρνει μεσογειακή/ταξιδιωτική εικόνα, αλλά η μουσική παραμένει εσωστρεφής. Το “go easy” ακούγεται σαν συμβουλή προς τον εαυτό: να χαμηλώσεις την ένταση, να δεχτείς την αβεβαιότητα και να φύγεις χωρίς θόρυβο.</t>
+  </si>
+  <si>
+    <t>Ride the Night</t>
+  </si>
+  <si>
+    <t>We Rock the World</t>
+  </si>
+  <si>
+    <t>Walhalla Warriors</t>
+  </si>
+  <si>
+    <t>Angel Dark</t>
+  </si>
+  <si>
+    <t>Slave No More</t>
+  </si>
+  <si>
+    <t>Raven Is Calling</t>
+  </si>
+  <si>
+    <t>Sail Away</t>
+  </si>
+  <si>
+    <t>Heavy Load</t>
+  </si>
+  <si>
+    <t>Riders Of The Ancient Storm</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/28777768-Heavy-Load-Riders-Of-The-Ancient-Storm</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/fHku5npmyYwNPZnFZXwldjOo8g40vi1FJsr3pLhOYws/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI4Nzc3/NzY4LTE2OTg5NDI2/ODMtNjY0Ny5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Thunderload Records – TLP - 2301, No Remorse Records (4) – TLP - 2301, Greece, Nov 6, 2023, Vinyl, LP, Album</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Greek pressing released by No Remorse Records in cooperation with Thunderload Records. Issued in a gatefold sleeve with an 8-page booklet containing lyrics and photos. Mastering / Runout Info: Cut by Lawrie at Curvepusher (LAWRIE@curvepusher).</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Viking Metal [Traditional Heavy Metal, Epic Metal, Hard Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Viking Metal [Traditional Heavy Metal, Epic Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Anthemic Heavy Metal, Classic Metal]</t>
+  </si>
+  <si>
+    <t>Viking Metal, Heavy Metal [Epic Metal, Norse Metal, Traditional Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Dark Heavy Rock, Melodic Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Doom Metal [Epic Doom, Viking Metal, Progressive Heavy Metal]</t>
+  </si>
+  <si>
+    <t>Viking Metal, Heavy Metal [Dark Epic Metal, Traditional Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Folk Rock [Epic Heavy Metal, Nordic Folk Rock, Closing Ballad]</t>
+  </si>
+  <si>
+    <t>Το πρώτο single και ιδανική είσοδος στον κόσμο του δίσκου. Βασίζεται σε σφιχτό traditional-metal riff, ρυθμική ορμή και έναν νυχτερινό, πολεμικό τόνο. Η "νυχτερινή διαδρομή" δεν είναι απλό biker imagery, λειτουργεί σαν πορεία μέσα από αβεβαιότητα, σε αναζήτηση ελευθερίας και προσωπικής δύναμης.</t>
+  </si>
+  <si>
+    <t>Το πιο άμεσο anthem του δίσκου. Οι Heavy Load επιστρέφουν στη rock ’n’ roll πλευρά τους, με φράσεις και ρυθμό που υπηρετούν τη συλλογική ενέργεια μιας συναυλίας. Δεν είναι το πιο σύνθετο κομμάτι, όμως προσφέρει ανάσα ανάμεσα στα πιο βαριά επικά tracks και επιβεβαιώνει ότι η μπάντα δεν έχει χάσει την απλή, απολαυστική πλευρά της.</t>
+  </si>
+  <si>
+    <t>Μία από τις κορυφές. Χτίζει epic traditional metal πάνω σε σκανδιναβική μυθολογική εικόνα, αλλά οι "πολεμιστές της Βαλχάλα" δεν παρουσιάζονται ως fantasy φιγούρες χωρίς βάρος, γίνονται σύμβολα τιμής, μνήμης και αντοχής απέναντι σε έναν κόσμο που απαιτεί υποταγή. Οι κιθάρες έχουν εμβατηριακή μεγαλοπρέπεια και το refrain λειτουργεί σαν παλιός metal ύμνος.</t>
+  </si>
+  <si>
+    <t>Σκοτεινότερο και πιο μελωδικό, συνδέει heavy rock με δραματική, σχεδόν gothic ατμόσφαιρα. Η "σκοτεινή άγγελος" είναι αμφίσημη μορφή, μπορεί να σημαίνει πειρασμό, απώλεια ή προστασία που έρχεται σε επικίνδυνη μορφή. Η σύνθεση προτιμά πιο αργές κιθαριστικές γραμμές και mood αντί για μόνιμη ταχύτητα.</t>
+  </si>
+  <si>
+    <t>Η μεγάλη, οκτάλεπτη κορυφή του δίσκου. Αργό, επικό και doom-χρωματισμένο, χτίζεται σαν ιστορία απελευθέρωσης, από την υποδούλωση προς την αξιοπρέπεια, την απόφαση και την αντίσταση. Τα riffs έχουν μεγάλη βαρύτητα, οι αλλαγές είναι υπομονετικές και η αίσθηση της τελικής λύτρωσης κερδίζεται αντί να χαρίζεται.</t>
+  </si>
+  <si>
+    <t>Σκοτεινό epic metal κομμάτι όπου το κοράκι λειτουργεί ως αγγελιοφόρος μνήμης, θανάτου και πεπρωμένου, σύμβολο βαθιά δεμένο με τη βόρεια μυθολογική φαντασία. Η κιθάρα και η μελωδία χτίζουν αίσθηση απομονωμένου, παγωμένου τοπίου, χωρίς να εγκαταλείπουν την κλασική heavy metal καθαρότητα.</t>
+  </si>
+  <si>
+    <t>Τελικό, μελαγχολικό και ελαφρώς folk χρωματισμένο κομμάτι. Μετά τα πολεμικά και σκοτεινά θέματα, η αναχώρηση στη θάλασσα γίνεται εικόνα αποχαιρετισμού, ελευθερίας και επιστροφής σε κάτι αρχέγονο. Λειτουργεί ως συναισθηματικός επίλογος, όχι ως καθαρή θριαμβολογία.</t>
   </si>
 </sst>
 </file>
@@ -6776,7 +6860,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -8678,6 +8762,38 @@
       </c>
       <c r="J59" s="11" t="s">
         <v>1921</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+      <c r="A60" s="6">
+        <v>28777768</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>1954</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>1955</v>
+      </c>
+      <c r="D60" s="6">
+        <v>2023</v>
+      </c>
+      <c r="E60" s="10">
+        <v>3.18</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>1960</v>
+      </c>
+      <c r="G60" s="7" t="s">
+        <v>1959</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>1958</v>
+      </c>
+      <c r="I60" s="11" t="s">
+        <v>1956</v>
+      </c>
+      <c r="J60" s="11" t="s">
+        <v>1957</v>
       </c>
     </row>
   </sheetData>
@@ -8796,6 +8912,8 @@
     <hyperlink ref="J58" r:id="rId112" xr:uid="{F7626FDC-49F2-48D7-8AB4-747CB4E5205A}"/>
     <hyperlink ref="I59" r:id="rId113" xr:uid="{1A6A9BEB-14DD-452B-B093-004CC31CBC62}"/>
     <hyperlink ref="J59" r:id="rId114" xr:uid="{0352086C-B63D-43D9-94F4-B89DC5E6CD8F}"/>
+    <hyperlink ref="I60" r:id="rId115" xr:uid="{F9FB0BA6-17D5-4EE4-8FFB-18A226B39AE5}"/>
+    <hyperlink ref="J60" r:id="rId116" xr:uid="{C6E3E414-6FFD-4591-BCD5-A87CCCA662DE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8803,7 +8921,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I545"/>
+  <dimension ref="A1:I552"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -23619,6 +23737,195 @@
       </c>
       <c r="I545" s="6"/>
     </row>
+    <row r="546" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A546" s="6">
+        <v>28777768</v>
+      </c>
+      <c r="B546" s="6">
+        <v>1</v>
+      </c>
+      <c r="C546" s="7" t="s">
+        <v>1947</v>
+      </c>
+      <c r="D546" s="7" t="s">
+        <v>1961</v>
+      </c>
+      <c r="E546" s="20">
+        <v>3.7</v>
+      </c>
+      <c r="F546" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G546" s="12">
+        <v>3.85</v>
+      </c>
+      <c r="H546" s="7" t="s">
+        <v>1968</v>
+      </c>
+      <c r="I546" s="6"/>
+    </row>
+    <row r="547" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A547" s="6">
+        <v>28777768</v>
+      </c>
+      <c r="B547" s="6">
+        <v>2</v>
+      </c>
+      <c r="C547" s="7" t="s">
+        <v>1948</v>
+      </c>
+      <c r="D547" s="7" t="s">
+        <v>1962</v>
+      </c>
+      <c r="E547" s="20">
+        <v>2.97</v>
+      </c>
+      <c r="F547" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G547" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="H547" s="7" t="s">
+        <v>1969</v>
+      </c>
+      <c r="I547" s="6"/>
+    </row>
+    <row r="548" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A548" s="6">
+        <v>28777768</v>
+      </c>
+      <c r="B548" s="6">
+        <v>3</v>
+      </c>
+      <c r="C548" s="7" t="s">
+        <v>1949</v>
+      </c>
+      <c r="D548" s="7" t="s">
+        <v>1963</v>
+      </c>
+      <c r="E548" s="20">
+        <v>3.43</v>
+      </c>
+      <c r="F548" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G548" s="12">
+        <v>3.95</v>
+      </c>
+      <c r="H548" s="7" t="s">
+        <v>1970</v>
+      </c>
+      <c r="I548" s="6"/>
+    </row>
+    <row r="549" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A549" s="6">
+        <v>28777768</v>
+      </c>
+      <c r="B549" s="6">
+        <v>4</v>
+      </c>
+      <c r="C549" s="7" t="s">
+        <v>1950</v>
+      </c>
+      <c r="D549" s="7" t="s">
+        <v>1964</v>
+      </c>
+      <c r="E549" s="20">
+        <v>3.32</v>
+      </c>
+      <c r="F549" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G549" s="12">
+        <v>3.75</v>
+      </c>
+      <c r="H549" s="7" t="s">
+        <v>1971</v>
+      </c>
+      <c r="I549" s="6"/>
+    </row>
+    <row r="550" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A550" s="6">
+        <v>28777768</v>
+      </c>
+      <c r="B550" s="6">
+        <v>5</v>
+      </c>
+      <c r="C550" s="7" t="s">
+        <v>1951</v>
+      </c>
+      <c r="D550" s="7" t="s">
+        <v>1965</v>
+      </c>
+      <c r="E550" s="20">
+        <v>3.31</v>
+      </c>
+      <c r="F550" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G550" s="12">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="H550" s="7" t="s">
+        <v>1972</v>
+      </c>
+      <c r="I550" s="6"/>
+    </row>
+    <row r="551" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A551" s="6">
+        <v>28777768</v>
+      </c>
+      <c r="B551" s="6">
+        <v>6</v>
+      </c>
+      <c r="C551" s="7" t="s">
+        <v>1952</v>
+      </c>
+      <c r="D551" s="7" t="s">
+        <v>1966</v>
+      </c>
+      <c r="E551" s="20">
+        <v>3.51</v>
+      </c>
+      <c r="F551" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G551" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="H551" s="7" t="s">
+        <v>1973</v>
+      </c>
+      <c r="I551" s="6"/>
+    </row>
+    <row r="552" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A552" s="6">
+        <v>28777768</v>
+      </c>
+      <c r="B552" s="6">
+        <v>7</v>
+      </c>
+      <c r="C552" s="7" t="s">
+        <v>1953</v>
+      </c>
+      <c r="D552" s="7" t="s">
+        <v>1967</v>
+      </c>
+      <c r="E552" s="20">
+        <v>3.37</v>
+      </c>
+      <c r="F552" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G552" s="12">
+        <v>3.75</v>
+      </c>
+      <c r="H552" s="7" t="s">
+        <v>1974</v>
+      </c>
+      <c r="I552" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCDB1FEA-A5A9-471C-B457-AF2C5D1E5C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27562428-6875-4F74-867D-290BF8EBF7DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2171" uniqueCount="1975">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2206" uniqueCount="2009">
   <si>
     <t>No</t>
   </si>
@@ -6342,6 +6342,138 @@
   </si>
   <si>
     <t>Τελικό, μελαγχολικό και ελαφρώς folk χρωματισμένο κομμάτι. Μετά τα πολεμικά και σκοτεινά θέματα, η αναχώρηση στη θάλασσα γίνεται εικόνα αποχαιρετισμού, ελευθερίας και επιστροφής σε κάτι αρχέγονο. Λειτουργεί ως συναισθηματικός επίλογος, όχι ως καθαρή θριαμβολογία.</t>
+  </si>
+  <si>
+    <t>Unbehagen</t>
+  </si>
+  <si>
+    <t>Nina Hagen Band</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/4216594-Nina-Hagen-Band-Unbehagen</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/_bMuDSFgKD5C1Xthaotn2BKwOajkQUH0wswpc0x84OI/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTQyMTY1/OTQtMTU1MDUxNTg5/NC0zMDA0LmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>Music On Vinyl – MOVLP642, Europe, Nov 12, 2012, Vinyl, LP, Album, Reissue, Remastered</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** European remastered reissue released by Music On Vinyl on November 12, 2012. Manufactured by Music On Vinyl B.V. Original recordings mastered and mixed at Hansa Tonstudios.</t>
+  </si>
+  <si>
+    <t>African Reggae</t>
+  </si>
+  <si>
+    <t>Alptraum</t>
+  </si>
+  <si>
+    <t>Wir Leben Immer... Noch (Lucky Number)</t>
+  </si>
+  <si>
+    <t>Wenn Ich Ein Junge Wär (Live-Version)</t>
+  </si>
+  <si>
+    <t>Herrmann Hieß Er</t>
+  </si>
+  <si>
+    <t>Auf'm Rummel</t>
+  </si>
+  <si>
+    <t>Wau Wau</t>
+  </si>
+  <si>
+    <t>Fall In Love Mit Mir</t>
+  </si>
+  <si>
+    <t>No Way (Instrumental)</t>
+  </si>
+  <si>
+    <t>Neue Deutsche Welle, Post-Punk [New Wave, Dub, Reggae Rock, Art Rock]</t>
+  </si>
+  <si>
+    <t>Reggae Rock, Neue Deutsche Welle [Dub, Post-Punk, New Wave]</t>
+  </si>
+  <si>
+    <t>Post-Punk, Art Rock [Darkwave, Avant-Garde Rock, Nightmare Rock]</t>
+  </si>
+  <si>
+    <t>New Wave, Post-Punk [Neue Deutsche Welle, Synth-Pop, Punk Pop]</t>
+  </si>
+  <si>
+    <t>Punk Rock, Cabaret [Theatrical Punk, Live Art Rock]</t>
+  </si>
+  <si>
+    <t>Post-Punk, Art Rock [Dark New Wave, Theatrical Rock, Avant-Punk]</t>
+  </si>
+  <si>
+    <t>New Wave, Post-Punk [Neue Deutsche Welle, Carnival Rock, Synth Rock]</t>
+  </si>
+  <si>
+    <t>Punk Rock, Neue Deutsche Welle [Art-Punk, New Wave, Satirical Rock]</t>
+  </si>
+  <si>
+    <t>New Wave, Pop Rock [Synth-Pop, Dark Pop, Neue Deutsche Welle]</t>
+  </si>
+  <si>
+    <t>New Wave, Instrumental Rock [Synth Instrumental, Post-Punk Outro (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Εξάλεπτο opening που χρησιμοποιεί reggae dub ρυθμό ως ελαστική βάση για post-punk ένταση. Η Hagen αποφεύγει την ευθεία πολιτισμική αναπαράσταση, η ερμηνεία της είναι νευρική, σχισμένη και θεατρική, ενώ η μπάντα γεμίζει τα κενά με synths και κοφτές κιθάρες. Το αποτέλεσμα είναι περισσότερο γερμανικό new wave dub παρά συμβατικό reggae.</t>
+  </si>
+  <si>
+    <t>Το σκοτεινό κέντρο του δίσκου. Ο τίτλος σημαίνει "εφιάλτης" και η μουσική λειτουργεί σαν υπνωτική βύθιση, βαριά, ασθενική ατμόσφαιρα, ακανόνιστες φωνητικές μεταπτώσεις και art rock ένταση. Η Hagen μετατρέπει τον τρόμο σε performance, πηγαίνοντας από παιδική αφέλεια σε σχεδόν δαιμονική έκρηξη.</t>
+  </si>
+  <si>
+    <t>Γερμανική ανακατασκευή του “Lucky Number” της Lene Lovich. Διατηρεί το new wave hook του πρωτοτύπου, αλλά το κάνει πιο νευρικό, πιο γωνιώδες και πιο σαρκαστικό. Το "ζούμε ακόμη" λειτουργεί ως ειρωνική διακήρυξη επιβίωσης μέσα σε μια πολιτισμική συνθήκη όπου όλα μοιάζουν να καταρρέουν.</t>
+  </si>
+  <si>
+    <t>Θεατρική live διασκευή που φέρνει cabaret, punk και gender bending performance στην ίδια σκηνή. Η φαντασίωση του να ήταν "αγόρι" δεν παρουσιάζεται ως απλό παιχνίδι ρόλων· γίνεται σατιρική παρατήρηση για την ελευθερία, την κοινωνική εξουσία και το τι επιτρέπεται σε κάθε φύλο.</t>
+  </si>
+  <si>
+    <t>Μακρόσυρτο, σκοτεινό post-punk, art-rock narrative. Η Hagen αφηγείται έναν χαρακτήρα με τρόπο σχεδόν κινηματογραφικό, χρησιμοποιώντας τη φωνή της για να μεταφέρει απειλή, ειρωνεία και συμπόνια μαζί. Η μπάντα δημιουργεί υποβόσκον ρυθμό, σαν περιπλάνηση σε γερμανικό αστικό τοπίο μετά τα μεσάνυχτα.</t>
+  </si>
+  <si>
+    <t>Πιο γρήγορο και καρναβαλικό, με τίτλο που παραπέμπει σε λούνα παρκ ή πανηγύρι. Η μουσική μετατρέπει το χώρο διασκέδασης σε τόπο υπερδιέγερσης και αστάθειας, synth hooks, κοφτά rhythms και η Hagen να αλλάζει φωνές σαν να περνά από μία σειρά αλλόκοτων χαρακτήρων.</t>
+  </si>
+  <si>
+    <t>Σύντομο art punk ξέσπασμα, με τον τίτλο να μιμείται γάβγισμα και να υπονομεύει τη σοβαρότητα του rock performance. Πίσω από το χιούμορ υπάρχει σατιρική ένταση, η μπάντα παίζει κοφτά και η Hagen μετατρέπει τον εαυτό της σε ήχο, ζώο και καρικατούρα ταυτόχρονα.</t>
+  </si>
+  <si>
+    <t>Dark pop, new wave κομμάτι όπου η πρόσκληση "ερωτεύσου με" ακούγεται ταυτόχρονα ερωτική και απειλητική. Η synth pop δομή είναι πιο καθαρή, όμως η Hagen αρνείται να την αφήσει να γίνει γυαλισμένη ποπ: αφήνει αμηχανία, ειρωνεία και υπερβολή μέσα στη φωνή της.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve">Σύντομο οργανικό outro με synth bass και post punk υφές. Λειτουργεί σαν τελική έξοδος από τον εφιαλτικό, καρναβαλικό κόσμο του </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Unbehagen,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> δεν προσφέρει λύση, μόνο μια κοφτή άρνηση. [Instrumental]</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -6860,7 +6992,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -8794,6 +8926,38 @@
       </c>
       <c r="J60" s="11" t="s">
         <v>1957</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+      <c r="A61" s="6">
+        <v>4216594</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>1976</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>1975</v>
+      </c>
+      <c r="D61" s="6">
+        <v>1980</v>
+      </c>
+      <c r="E61" s="10">
+        <v>3.39</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>1990</v>
+      </c>
+      <c r="G61" s="7" t="s">
+        <v>1980</v>
+      </c>
+      <c r="H61" s="6" t="s">
+        <v>1979</v>
+      </c>
+      <c r="I61" s="11" t="s">
+        <v>1977</v>
+      </c>
+      <c r="J61" s="11" t="s">
+        <v>1978</v>
       </c>
     </row>
   </sheetData>
@@ -8914,6 +9078,8 @@
     <hyperlink ref="J59" r:id="rId114" xr:uid="{0352086C-B63D-43D9-94F4-B89DC5E6CD8F}"/>
     <hyperlink ref="I60" r:id="rId115" xr:uid="{F9FB0BA6-17D5-4EE4-8FFB-18A226B39AE5}"/>
     <hyperlink ref="J60" r:id="rId116" xr:uid="{C6E3E414-6FFD-4591-BCD5-A87CCCA662DE}"/>
+    <hyperlink ref="I61" r:id="rId117" xr:uid="{721CF701-F1E2-4D7D-BC9E-45C800A11082}"/>
+    <hyperlink ref="J61" r:id="rId118" xr:uid="{578E24F6-6EF4-4106-AC34-2EB032E5DBAC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8921,7 +9087,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I552"/>
+  <dimension ref="A1:I561"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -23926,6 +24092,251 @@
       </c>
       <c r="I552" s="6"/>
     </row>
+    <row r="553" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A553" s="6">
+        <v>4216594</v>
+      </c>
+      <c r="B553" s="6">
+        <v>1</v>
+      </c>
+      <c r="C553" s="7" t="s">
+        <v>1981</v>
+      </c>
+      <c r="D553" s="7" t="s">
+        <v>1991</v>
+      </c>
+      <c r="E553" s="20">
+        <v>3.55</v>
+      </c>
+      <c r="F553" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G553" s="12">
+        <v>3.95</v>
+      </c>
+      <c r="H553" s="7" t="s">
+        <v>2000</v>
+      </c>
+      <c r="I553" s="6" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="554" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A554" s="6">
+        <v>4216594</v>
+      </c>
+      <c r="B554" s="6">
+        <v>2</v>
+      </c>
+      <c r="C554" s="7" t="s">
+        <v>1982</v>
+      </c>
+      <c r="D554" s="7" t="s">
+        <v>1992</v>
+      </c>
+      <c r="E554" s="20">
+        <v>3.53</v>
+      </c>
+      <c r="F554" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G554" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="H554" s="7" t="s">
+        <v>2001</v>
+      </c>
+      <c r="I554" s="6"/>
+    </row>
+    <row r="555" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A555" s="6">
+        <v>4216594</v>
+      </c>
+      <c r="B555" s="6">
+        <v>3</v>
+      </c>
+      <c r="C555" s="7" t="s">
+        <v>1983</v>
+      </c>
+      <c r="D555" s="7" t="s">
+        <v>1993</v>
+      </c>
+      <c r="E555" s="20">
+        <v>3.2</v>
+      </c>
+      <c r="F555" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G555" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="H555" s="7" t="s">
+        <v>2002</v>
+      </c>
+      <c r="I555" s="6"/>
+    </row>
+    <row r="556" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A556" s="6">
+        <v>4216594</v>
+      </c>
+      <c r="B556" s="6">
+        <v>4</v>
+      </c>
+      <c r="C556" s="7" t="s">
+        <v>1984</v>
+      </c>
+      <c r="D556" s="7" t="s">
+        <v>1994</v>
+      </c>
+      <c r="E556" s="20">
+        <v>2.81</v>
+      </c>
+      <c r="F556" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G556" s="12">
+        <v>3.65</v>
+      </c>
+      <c r="H556" s="7" t="s">
+        <v>2003</v>
+      </c>
+      <c r="I556" s="6"/>
+    </row>
+    <row r="557" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A557" s="6">
+        <v>4216594</v>
+      </c>
+      <c r="B557" s="6">
+        <v>5</v>
+      </c>
+      <c r="C557" s="7" t="s">
+        <v>1985</v>
+      </c>
+      <c r="D557" s="7" t="s">
+        <v>1995</v>
+      </c>
+      <c r="E557" s="20">
+        <v>3.15</v>
+      </c>
+      <c r="F557" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G557" s="12">
+        <v>4</v>
+      </c>
+      <c r="H557" s="7" t="s">
+        <v>2004</v>
+      </c>
+      <c r="I557" s="6"/>
+    </row>
+    <row r="558" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A558" s="6">
+        <v>4216594</v>
+      </c>
+      <c r="B558" s="6">
+        <v>6</v>
+      </c>
+      <c r="C558" s="7" t="s">
+        <v>1986</v>
+      </c>
+      <c r="D558" s="7" t="s">
+        <v>1996</v>
+      </c>
+      <c r="E558" s="20">
+        <v>2.9</v>
+      </c>
+      <c r="F558" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G558" s="12">
+        <v>3.85</v>
+      </c>
+      <c r="H558" s="7" t="s">
+        <v>2005</v>
+      </c>
+      <c r="I558" s="6"/>
+    </row>
+    <row r="559" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A559" s="6">
+        <v>4216594</v>
+      </c>
+      <c r="B559" s="6">
+        <v>7</v>
+      </c>
+      <c r="C559" s="7" t="s">
+        <v>1987</v>
+      </c>
+      <c r="D559" s="7" t="s">
+        <v>1997</v>
+      </c>
+      <c r="E559" s="20">
+        <v>3.15</v>
+      </c>
+      <c r="F559" s="12">
+        <v>4</v>
+      </c>
+      <c r="G559" s="12">
+        <v>3.75</v>
+      </c>
+      <c r="H559" s="7" t="s">
+        <v>2006</v>
+      </c>
+      <c r="I559" s="6"/>
+    </row>
+    <row r="560" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A560" s="6">
+        <v>4216594</v>
+      </c>
+      <c r="B560" s="6">
+        <v>8</v>
+      </c>
+      <c r="C560" s="7" t="s">
+        <v>1988</v>
+      </c>
+      <c r="D560" s="7" t="s">
+        <v>1998</v>
+      </c>
+      <c r="E560" s="20">
+        <v>3.21</v>
+      </c>
+      <c r="F560" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G560" s="12">
+        <v>3.85</v>
+      </c>
+      <c r="H560" s="7" t="s">
+        <v>2007</v>
+      </c>
+      <c r="I560" s="6"/>
+    </row>
+    <row r="561" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A561" s="6">
+        <v>4216594</v>
+      </c>
+      <c r="B561" s="6">
+        <v>9</v>
+      </c>
+      <c r="C561" s="7" t="s">
+        <v>1989</v>
+      </c>
+      <c r="D561" s="7" t="s">
+        <v>1999</v>
+      </c>
+      <c r="E561" s="20">
+        <v>2.82</v>
+      </c>
+      <c r="F561" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G561" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="H561" s="7" t="s">
+        <v>2008</v>
+      </c>
+      <c r="I561" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,22 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EE33197-8653-4A25-B42C-807EB688AE16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81CB587A-C11B-4FCF-B23A-D30C7C2437BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
     <sheet name="tracks" sheetId="1" r:id="rId2"/>
-    <sheet name="Φύλλο2" sheetId="8" r:id="rId3"/>
-    <sheet name="info" sheetId="6" r:id="rId4"/>
+    <sheet name="info" sheetId="6" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2241" uniqueCount="2049">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2301" uniqueCount="2106">
   <si>
     <t>No</t>
   </si>
@@ -6495,9 +6494,6 @@
     <t>Σύντομος αλλά θεατρικός επίλογος, όπου η ιδέα του tango γίνεται σύμβολο σχέσης εξάρτησης, έλξης και αποχωρισμού. Η ρυθμική αναφορά στον χορό δεν είναι κυριολεκτική tango pastiche, ενσωματώνεται σε symphonic pop/art rock πλαίσιο, αφήνοντας την αίσθηση μιας τελευταίας περιστροφής πριν τη σιωπή.</t>
   </si>
   <si>
-    <t>B019263-01 A1</t>
-  </si>
-  <si>
     <t>Look Out</t>
   </si>
   <si>
@@ -6595,6 +6591,240 @@
   </si>
   <si>
     <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** European repress released by Warner Music Central Europe on September 27, 2024. Features heavy psych, krautrock, and early prog-rock sounds from the 1970 recordings (the precursor project to Lucifer's Friend).</t>
+  </si>
+  <si>
+    <t>The Beatles</t>
+  </si>
+  <si>
+    <t>Abbey Road</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/14186441-The-Beatles-Abbey-Road</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/mZ2TX8oMAn3F30zIGlYGXsgERFG_x7w2edfM-SZsn8s/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTE0MTg2/NDQxLTE1Njk0ODcx/NjEtNzMxNC5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Apple Records, Universal Music Group International – 0602577915123, Worldwide, Sep 27, 2019, Vinyl, LP, Album, Reissue, Remastered, Stereo, Remix, 50th Anniversary Edition, Optimal Media Pressing, 180g</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** 50th Anniversary Edition 180g LP pressed at Optimal Media in Germany. Features the new stereo album mix by Giles Martin and Sam Okell, half-speed mastered by Miles Showell at Abbey Road Studios (Room 30). Note that the rear sleeve lists tracks up to "The End" (B10) without mentioning "Her Majesty" (B11), while the vinyl includes the hidden track.</t>
+  </si>
+  <si>
+    <t>Come Together</t>
+  </si>
+  <si>
+    <t>Something</t>
+  </si>
+  <si>
+    <t>Maxwell's Silver Hammer</t>
+  </si>
+  <si>
+    <t>Oh! Darling</t>
+  </si>
+  <si>
+    <t>Octopus's Garden</t>
+  </si>
+  <si>
+    <t>I Want You (She's So Heavy)</t>
+  </si>
+  <si>
+    <t>Here Comes the Sun</t>
+  </si>
+  <si>
+    <t>Because</t>
+  </si>
+  <si>
+    <t>You Never Give Me Your Money</t>
+  </si>
+  <si>
+    <t>Sun King</t>
+  </si>
+  <si>
+    <t>Mean Mr. Mustard</t>
+  </si>
+  <si>
+    <t>Polythene Pam</t>
+  </si>
+  <si>
+    <t>She Came In Through the Bathroom Window</t>
+  </si>
+  <si>
+    <t>Golden Slumbers</t>
+  </si>
+  <si>
+    <t>Carry That Weight</t>
+  </si>
+  <si>
+    <t>The End</t>
+  </si>
+  <si>
+    <t>Her Majesty</t>
+  </si>
+  <si>
+    <t>Ανοίγει με swampy μπάσο, χαμηλό drum pulse και τη σχεδόν ψιθυριστή ερμηνεία του Lennon. Οι στίχοι λειτουργούν σαν σουρεαλιστικά πορτρέτα και η φράση “come together” αποκτά υπαινικτική ερωτική και συλλογική διάσταση. Το groove είναι το πραγματικό κέντρο, σκοτεινό, αργό και αδιαπέραστο.</t>
+  </si>
+  <si>
+    <t>Η κορυφαία ερωτική μπαλάντα του Harrison. Η αμφιβολία στους στίχους «I don’t know» κάνει το τραγούδι πιο ανθρώπινο από μια απλή δήλωση λατρείας. Η κιθάρα του Harrison, το μπάσο του McCartney και η ορχηστρική ενορχήστρωση του George Martin συνυπάρχουν με υποδειγματική οικονομία.</t>
+  </si>
+  <si>
+    <t>Παιχνιδιάρικο piano-pop με music-hall αίσθηση και σκόπιμα μαύρο χιούμορ. Η χαρούμενη μελωδία αντιπαραβάλλεται με έναν χαρακτήρα που λύνει κάθε πρόβλημα με βία, δημιουργώντας μία από τις πιο ειρωνικές McCartney συνθέσεις.</t>
+  </si>
+  <si>
+    <t>Η soul/rock ’n’ roll επίδειξη του McCartney. Η φωνητική ερμηνεία δεν επιδιώκει τεχνική καθαρότητα αλλά φθορά: o McCartney τραγουδά σαν old-school R&amp;B singer που βρίσκεται στο όριο κατάρρευσης, ενώ το πιάνο και η κιθάρα κρατούν τη σύνθεση γειωμένη στην προ-Beatles rock παράδοση.</t>
+  </si>
+  <si>
+    <t>Η παιδική, θαλάσσια φαντασία του Ringo προσφέρει αναγκαίο φως στη σκοτεινότερη πρώτη πλευρά. Κάτω από την απλότητα, η παραγωγή είναι γεμάτη μικρά ηχητικά ευρήματα, κιθάρες, bubbles και ψυχεδελικά underwater effects που μετατρέπουν την παιδική επιθυμία για απόδραση σε πλήρες μικρό ηχητικό σύμπαν.</t>
+  </si>
+  <si>
+    <t>Η πιο βαριά, επίμονη και σχεδόν proto-metal στιγμή των Beatles. Η απλή εμμονική φράση του Lennon επαναλαμβάνεται πάνω σε ένα τεράστιο blues-rock riff, ενώ white noise, Moog textures και στρώσεις κιθάρας δημιουργούν ασφυκτική ένταση. Η ξαφνική σιωπή στο τέλος είναι μία από τις πιο τολμηρές αποφάσεις στη δισκογραφία τους.</t>
+  </si>
+  <si>
+    <t>Το αντίβαρο στην ασφυξία του προηγούμενου τραγουδιού. Ο Harrison γράφει ένα ακουστικό τραγούδι αναγέννησης, με ασυνήθιστα μέτρα, Moog χρώματα και αβίαστη μελωδία. Η χαρά του δεν είναι αφελής· έρχεται ως ανακούφιση μετά από μακρύ σκοτάδι.</t>
+  </si>
+  <si>
+    <t>Ονειρική, αιωρούμενη σύνθεση του Lennon με εννεαφωνη χορωδιακή τεχνική. Οι στίχοι συνδέουν τη φυσική τάξη, τη γνώση και την αγάπη με σχεδόν μυστικιστική απλότητα. Η φωνητική αρμονία είναι το βασικό όργανο του κομματιού, ενώ harpsichord-like electric piano και Moog δημιουργούν μεταφυσικό χώρο.</t>
+  </si>
+  <si>
+    <t>Η πιο καθαρή McCartney αναφορά στη διάλυση των Beatles και στις οικονομικές/διοικητικές συγκρούσεις τους. Ξεκινά ως πικρή πιανιστική μπαλάντα, περνά σε upbeat rock και διαλύεται σε ονειρικό tape-loop coda. Αποτελεί το σημείο όπου το medley αρχίζει να μετατρέπει τις ατομικές ιστορίες σε κοινή αποχαιρετιστήρια αφήγηση.</t>
+  </si>
+  <si>
+    <t>Ατμοσφαιρικό διάλειμμα με μακρινές κιθάρες, πλούσια harmonies και νυχτερινή ψυχεδέλεια. Το τραγούδι δημιουργεί ένα τροπικό, υπνωτικό τοπίο, πριν περάσει αβίαστα στον κόσμο των μικρών Lennon χαρακτήρων.</t>
+  </si>
+  <si>
+    <t>Σύντομο character sketch του Lennon για έναν άθλιο αλλά αλλόκοτο αστικό τύπο. Η οικονομία της σύνθεσης είναι μέρος του χιούμορ, λίγες γραμμές, στεγνό rock ’n’ roll και η άμεση μετάβαση στο επόμενο τραγούδι.</t>
+  </si>
+  <si>
+    <t>Γρήγορο, τραχύ και σχεδόν glam πριν τον όρο glam. Η Pam είναι ένας ακόμη Lennon χαρακτήρας, υπερβολικός, ακατέργαστος και θεατρικός. Οι κιθάρες έχουν σκληρή, άμεση ενέργεια που σπάει την ονειρική ατμόσφαιρα του medley.</t>
+  </si>
+  <si>
+    <t>McCartney story-song εμπνευσμένο από πραγματικό περιστατικό με fan που μπήκε στο σπίτι του. Η μελωδία, το μπάσο και η αρμονική σαφήνεια μετατρέπουν μια παραβίαση ορίων σε σύντομη pop αφήγηση με bittersweet χαρακτήρα.</t>
+  </si>
+  <si>
+    <t>Ο McCartney παίρνει ένα παλιό αγγλικό lullaby και το μετατρέπει σε ορχηστρική, δραματική μπαλάντα. Η φωνή του είναι δυνατή και τελετουργική, σαν να προσπαθεί να μετατρέψει την κόπωση, το τέλος και την παιδική μνήμη σε αποχαιρετισμό.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve">Η επανεμφάνιση του μοτίβου από το </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>You Never Give Me Your Money</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> συνδέει το medley κυκλικά. Η φράση «boy, you’re gonna carry that weight a long time» αποκτά ειδικό βάρος ως σχόλιο για τις προσωπικές και επαγγελματικές συνέπειες της διάλυσης της μπάντας.</t>
+    </r>
+  </si>
+  <si>
+    <t>Το πραγματικό κλείσιμο του άλμπουμ. Το μοναδικό drum solo του Ringo, τα εναλλασσόμενα κιθαριστικά solos McCartney–Harrison–Lennon και η τελική φράση συνθέτουν όχι απλώς το τέλος ενός δίσκου, αλλά το πιο καθαρό μουσικό αντίο των Beatles.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve">Εικοσιτριών δευτερολέπτων music-hall epilogue, αρχικά κομμένο από το medley και τυχαία διατηρημένο στο τέλος της ταινίας. Η απότομη είσοδός του μετά το </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>The End</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> λειτουργεί ως μικρό, χιουμοριστικό wink, αντί για βαριά τελεία, οι Beatles αποχωρούν με ένα ατελές, ανάλαφρο τραγουδάκι.</t>
+    </r>
+  </si>
+  <si>
+    <t>Pop Rock, Art Rock [Baroque Pop, Psychedelic Rock, Rock Suite]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Psychedelic Rock [Swamp Rock, Groove Rock, Dark Pop]</t>
+  </si>
+  <si>
+    <t>Pop Rock, Baroque Pop [Rock Ballad, Orchestral Pop, Love Song]</t>
+  </si>
+  <si>
+    <t>Pop Rock, Music Hall [Vaudeville Pop, Dark Satire, Piano Pop]</t>
+  </si>
+  <si>
+    <t>Rock &amp; Roll, Blue-Eyed Soul [Retro Rock, Soul Rock, Vocal Showcase]</t>
+  </si>
+  <si>
+    <t>Pop Rock, Psychedelic Pop [Children's Pop, Music Hall Pop, Underwater Psych]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Psychedelic Rock [Proto-Metal, Drone Rock, Heavy Blues]</t>
+  </si>
+  <si>
+    <t>Folk Rock, Pop Rock [Acoustic Pop, Baroque Folk, Sunshine Pop]</t>
+  </si>
+  <si>
+    <t>Art Rock, Psychedelic Pop [Vocal Harmony Pop, Dream Pop, Chamber Rock]</t>
+  </si>
+  <si>
+    <t>Art Rock, Pop Rock [Rock Suite, Baroque Pop, Progressive Pop]</t>
+  </si>
+  <si>
+    <t>Psychedelic Rock, Pop Rock [Ambient Pop, Latin-tinged Psych, Dream Rock]</t>
+  </si>
+  <si>
+    <t>Rock &amp; Roll, Pop Rock [British Beat, Character Song, Rock Suite]</t>
+  </si>
+  <si>
+    <t>Rock &amp; Roll, Hard Rock [Glam Proto-Rock, Rock Suite]</t>
+  </si>
+  <si>
+    <t>Pop Rock, Rock &amp; Roll [Power Pop, Rock Suite, Story Song]</t>
+  </si>
+  <si>
+    <t>Baroque Pop, Art Rock [Orchestral Ballad, Rock Suite]</t>
+  </si>
+  <si>
+    <t>Pop Rock, Art Rock [Anthemic Rock, Rock Suite, Reprise]</t>
+  </si>
+  <si>
+    <t>Rock &amp; Roll, Art Rock [Guitar Solo Suite, Drum Solo, Album Finale]</t>
+  </si>
+  <si>
+    <t>Music Hall, Pop Rock [Acoustic Miniature, Hidden Track]</t>
   </si>
 </sst>
 </file>
@@ -7113,7 +7343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -9086,10 +9316,10 @@
         <v>31860245</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="D62" s="6">
         <v>1970</v>
@@ -9098,19 +9328,51 @@
         <v>3.4</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="G62" s="7" t="s">
+        <v>2047</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>2046</v>
+      </c>
+      <c r="I62" s="11" t="s">
+        <v>2044</v>
+      </c>
+      <c r="J62" s="11" t="s">
+        <v>2045</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A63" s="6">
+        <v>14186441</v>
+      </c>
+      <c r="B63" s="7" t="s">
         <v>2048</v>
       </c>
-      <c r="H62" s="6" t="s">
-        <v>2047</v>
-      </c>
-      <c r="I62" s="11" t="s">
-        <v>2045</v>
-      </c>
-      <c r="J62" s="11" t="s">
-        <v>2046</v>
+      <c r="C63" s="7" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D63" s="6">
+        <v>1969</v>
+      </c>
+      <c r="E63" s="10">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>2088</v>
+      </c>
+      <c r="G63" s="7" t="s">
+        <v>2053</v>
+      </c>
+      <c r="H63" s="6" t="s">
+        <v>2052</v>
+      </c>
+      <c r="I63" s="11" t="s">
+        <v>2050</v>
+      </c>
+      <c r="J63" s="11" t="s">
+        <v>2051</v>
       </c>
     </row>
   </sheetData>
@@ -9235,6 +9497,8 @@
     <hyperlink ref="J61" r:id="rId118" xr:uid="{578E24F6-6EF4-4106-AC34-2EB032E5DBAC}"/>
     <hyperlink ref="I62" r:id="rId119" xr:uid="{460B13BE-9FBD-4212-989D-A38BF444C977}"/>
     <hyperlink ref="J62" r:id="rId120" xr:uid="{F80F1184-6004-4DE3-A74B-2FA197532CAD}"/>
+    <hyperlink ref="I63" r:id="rId121" xr:uid="{4231DB13-C70E-4D21-B210-8DDD89D2EE71}"/>
+    <hyperlink ref="J63" r:id="rId122" xr:uid="{8AA4738F-FC96-41CA-87DA-4152EF3852B8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9242,7 +9506,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I570"/>
+  <dimension ref="A1:I587"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -24500,10 +24764,10 @@
         <v>1</v>
       </c>
       <c r="C562" s="7" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="D562" s="7" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="E562" s="20">
         <v>3.6</v>
@@ -24515,7 +24779,7 @@
         <v>3.75</v>
       </c>
       <c r="H562" s="7" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="I562" s="6"/>
     </row>
@@ -24527,10 +24791,10 @@
         <v>2</v>
       </c>
       <c r="C563" s="7" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="D563" s="7" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="E563" s="20">
         <v>3.63</v>
@@ -24542,7 +24806,7 @@
         <v>3.65</v>
       </c>
       <c r="H563" s="7" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="I563" s="6"/>
     </row>
@@ -24554,10 +24818,10 @@
         <v>3</v>
       </c>
       <c r="C564" s="7" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="D564" s="7" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="E564" s="20">
         <v>3.56</v>
@@ -24569,7 +24833,7 @@
         <v>3.8</v>
       </c>
       <c r="H564" s="7" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="I564" s="6"/>
     </row>
@@ -24581,10 +24845,10 @@
         <v>4</v>
       </c>
       <c r="C565" s="7" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="D565" s="7" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="E565" s="20">
         <v>3.64</v>
@@ -24596,7 +24860,7 @@
         <v>3.6</v>
       </c>
       <c r="H565" s="7" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="I565" s="6"/>
     </row>
@@ -24608,10 +24872,10 @@
         <v>5</v>
       </c>
       <c r="C566" s="7" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="D566" s="7" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="E566" s="20">
         <v>3.61</v>
@@ -24623,7 +24887,7 @@
         <v>3.7</v>
       </c>
       <c r="H566" s="7" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="I566" s="6"/>
     </row>
@@ -24635,10 +24899,10 @@
         <v>6</v>
       </c>
       <c r="C567" s="7" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="D567" s="7" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="E567" s="20">
         <v>3.55</v>
@@ -24650,7 +24914,7 @@
         <v>3.7</v>
       </c>
       <c r="H567" s="7" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="I567" s="6"/>
     </row>
@@ -24662,10 +24926,10 @@
         <v>7</v>
       </c>
       <c r="C568" s="7" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="D568" s="7" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="E568" s="20">
         <v>3.42</v>
@@ -24677,7 +24941,7 @@
         <v>3.75</v>
       </c>
       <c r="H568" s="7" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="I568" s="6"/>
     </row>
@@ -24689,10 +24953,10 @@
         <v>8</v>
       </c>
       <c r="C569" s="7" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D569" s="7" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="E569" s="20">
         <v>3.63</v>
@@ -24704,7 +24968,7 @@
         <v>3.65</v>
       </c>
       <c r="H569" s="7" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="I569" s="6"/>
     </row>
@@ -24716,10 +24980,10 @@
         <v>9</v>
       </c>
       <c r="C570" s="7" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D570" s="7" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="E570" s="20">
         <v>3.68</v>
@@ -24731,9 +24995,474 @@
         <v>4</v>
       </c>
       <c r="H570" s="7" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="I570" s="6"/>
+    </row>
+    <row r="571" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A571" s="6">
+        <v>14186441</v>
+      </c>
+      <c r="B571" s="6">
+        <v>1</v>
+      </c>
+      <c r="C571" s="7" t="s">
+        <v>2054</v>
+      </c>
+      <c r="D571" s="7" t="s">
+        <v>2089</v>
+      </c>
+      <c r="E571" s="20">
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="F571" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="G571" s="12">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="H571" s="7" t="s">
+        <v>2071</v>
+      </c>
+      <c r="I571" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="572" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A572" s="6">
+        <v>14186441</v>
+      </c>
+      <c r="B572" s="6">
+        <v>2</v>
+      </c>
+      <c r="C572" s="7" t="s">
+        <v>2055</v>
+      </c>
+      <c r="D572" s="7" t="s">
+        <v>2090</v>
+      </c>
+      <c r="E572" s="20">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="F572" s="12">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G572" s="12">
+        <v>4.95</v>
+      </c>
+      <c r="H572" s="7" t="s">
+        <v>2072</v>
+      </c>
+      <c r="I572" s="6"/>
+    </row>
+    <row r="573" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A573" s="6">
+        <v>14186441</v>
+      </c>
+      <c r="B573" s="6">
+        <v>3</v>
+      </c>
+      <c r="C573" s="7" t="s">
+        <v>2056</v>
+      </c>
+      <c r="D573" s="7" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E573" s="20">
+        <v>3.9</v>
+      </c>
+      <c r="F573" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G573" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H573" s="7" t="s">
+        <v>2073</v>
+      </c>
+      <c r="I573" s="6"/>
+    </row>
+    <row r="574" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A574" s="6">
+        <v>14186441</v>
+      </c>
+      <c r="B574" s="6">
+        <v>4</v>
+      </c>
+      <c r="C574" s="7" t="s">
+        <v>2057</v>
+      </c>
+      <c r="D574" s="7" t="s">
+        <v>2092</v>
+      </c>
+      <c r="E574" s="20">
+        <v>4.32</v>
+      </c>
+      <c r="F574" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G574" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H574" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="I574" s="6"/>
+    </row>
+    <row r="575" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A575" s="6">
+        <v>14186441</v>
+      </c>
+      <c r="B575" s="6">
+        <v>5</v>
+      </c>
+      <c r="C575" s="7" t="s">
+        <v>2058</v>
+      </c>
+      <c r="D575" s="7" t="s">
+        <v>2093</v>
+      </c>
+      <c r="E575" s="20">
+        <v>4.17</v>
+      </c>
+      <c r="F575" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G575" s="12">
+        <v>4.75</v>
+      </c>
+      <c r="H575" s="7" t="s">
+        <v>2075</v>
+      </c>
+      <c r="I575" s="6"/>
+    </row>
+    <row r="576" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A576" s="6">
+        <v>14186441</v>
+      </c>
+      <c r="B576" s="6">
+        <v>6</v>
+      </c>
+      <c r="C576" s="7" t="s">
+        <v>2059</v>
+      </c>
+      <c r="D576" s="7" t="s">
+        <v>2094</v>
+      </c>
+      <c r="E576" s="20">
+        <v>4.55</v>
+      </c>
+      <c r="F576" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="G576" s="12">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="H576" s="7" t="s">
+        <v>2076</v>
+      </c>
+      <c r="I576" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="577" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A577" s="6">
+        <v>14186441</v>
+      </c>
+      <c r="B577" s="6">
+        <v>7</v>
+      </c>
+      <c r="C577" s="7" t="s">
+        <v>2060</v>
+      </c>
+      <c r="D577" s="7" t="s">
+        <v>2095</v>
+      </c>
+      <c r="E577" s="20">
+        <v>4.6100000000000003</v>
+      </c>
+      <c r="F577" s="12">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G577" s="12">
+        <v>4.95</v>
+      </c>
+      <c r="H577" s="7" t="s">
+        <v>2077</v>
+      </c>
+      <c r="I577" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="578" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A578" s="6">
+        <v>14186441</v>
+      </c>
+      <c r="B578" s="6">
+        <v>8</v>
+      </c>
+      <c r="C578" s="7" t="s">
+        <v>2061</v>
+      </c>
+      <c r="D578" s="7" t="s">
+        <v>2096</v>
+      </c>
+      <c r="E578" s="20">
+        <v>4.2</v>
+      </c>
+      <c r="F578" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="G578" s="12">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H578" s="7" t="s">
+        <v>2078</v>
+      </c>
+      <c r="I578" s="6"/>
+    </row>
+    <row r="579" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A579" s="6">
+        <v>14186441</v>
+      </c>
+      <c r="B579" s="6">
+        <v>9</v>
+      </c>
+      <c r="C579" s="7" t="s">
+        <v>2062</v>
+      </c>
+      <c r="D579" s="7" t="s">
+        <v>2097</v>
+      </c>
+      <c r="E579" s="20">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="F579" s="12">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G579" s="12">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="H579" s="7" t="s">
+        <v>2079</v>
+      </c>
+      <c r="I579" s="6"/>
+    </row>
+    <row r="580" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A580" s="6">
+        <v>14186441</v>
+      </c>
+      <c r="B580" s="6">
+        <v>10</v>
+      </c>
+      <c r="C580" s="7" t="s">
+        <v>2063</v>
+      </c>
+      <c r="D580" s="7" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E580" s="20">
+        <v>3.96</v>
+      </c>
+      <c r="F580" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G580" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H580" s="7" t="s">
+        <v>2080</v>
+      </c>
+      <c r="I580" s="6"/>
+    </row>
+    <row r="581" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A581" s="6">
+        <v>14186441</v>
+      </c>
+      <c r="B581" s="6">
+        <v>11</v>
+      </c>
+      <c r="C581" s="7" t="s">
+        <v>2064</v>
+      </c>
+      <c r="D581" s="7" t="s">
+        <v>2099</v>
+      </c>
+      <c r="E581" s="20">
+        <v>3.92</v>
+      </c>
+      <c r="F581" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G581" s="12">
+        <v>4.75</v>
+      </c>
+      <c r="H581" s="7" t="s">
+        <v>2081</v>
+      </c>
+      <c r="I581" s="6"/>
+    </row>
+    <row r="582" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A582" s="6">
+        <v>14186441</v>
+      </c>
+      <c r="B582" s="6">
+        <v>12</v>
+      </c>
+      <c r="C582" s="7" t="s">
+        <v>2065</v>
+      </c>
+      <c r="D582" s="7" t="s">
+        <v>2100</v>
+      </c>
+      <c r="E582" s="20">
+        <v>3.94</v>
+      </c>
+      <c r="F582" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G582" s="12">
+        <v>4.75</v>
+      </c>
+      <c r="H582" s="7" t="s">
+        <v>2082</v>
+      </c>
+      <c r="I582" s="6"/>
+    </row>
+    <row r="583" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A583" s="6">
+        <v>14186441</v>
+      </c>
+      <c r="B583" s="6">
+        <v>13</v>
+      </c>
+      <c r="C583" s="7" t="s">
+        <v>2066</v>
+      </c>
+      <c r="D583" s="7" t="s">
+        <v>2101</v>
+      </c>
+      <c r="E583" s="20">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="F583" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G583" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H583" s="7" t="s">
+        <v>2083</v>
+      </c>
+      <c r="I583" s="6"/>
+    </row>
+    <row r="584" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A584" s="6">
+        <v>14186441</v>
+      </c>
+      <c r="B584" s="6">
+        <v>14</v>
+      </c>
+      <c r="C584" s="7" t="s">
+        <v>2067</v>
+      </c>
+      <c r="D584" s="7" t="s">
+        <v>2102</v>
+      </c>
+      <c r="E584" s="20">
+        <v>4.45</v>
+      </c>
+      <c r="F584" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="G584" s="12">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="H584" s="7" t="s">
+        <v>2084</v>
+      </c>
+      <c r="I584" s="6"/>
+    </row>
+    <row r="585" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A585" s="6">
+        <v>14186441</v>
+      </c>
+      <c r="B585" s="6">
+        <v>15</v>
+      </c>
+      <c r="C585" s="7" t="s">
+        <v>2068</v>
+      </c>
+      <c r="D585" s="7" t="s">
+        <v>2103</v>
+      </c>
+      <c r="E585" s="20">
+        <v>4.46</v>
+      </c>
+      <c r="F585" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="G585" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H585" s="7" t="s">
+        <v>2085</v>
+      </c>
+      <c r="I585" s="6"/>
+    </row>
+    <row r="586" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A586" s="6">
+        <v>14186441</v>
+      </c>
+      <c r="B586" s="6">
+        <v>16</v>
+      </c>
+      <c r="C586" s="7" t="s">
+        <v>2069</v>
+      </c>
+      <c r="D586" s="7" t="s">
+        <v>2104</v>
+      </c>
+      <c r="E586" s="20">
+        <v>4.42</v>
+      </c>
+      <c r="F586" s="12">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G586" s="12">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H586" s="7" t="s">
+        <v>2086</v>
+      </c>
+      <c r="I586" s="6"/>
+    </row>
+    <row r="587" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A587" s="6">
+        <v>14186441</v>
+      </c>
+      <c r="B587" s="6">
+        <v>17</v>
+      </c>
+      <c r="C587" s="7" t="s">
+        <v>2070</v>
+      </c>
+      <c r="D587" s="7" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E587" s="20">
+        <v>3.75</v>
+      </c>
+      <c r="F587" s="12">
+        <v>4</v>
+      </c>
+      <c r="G587" s="12">
+        <v>4.75</v>
+      </c>
+      <c r="H587" s="7" t="s">
+        <v>2087</v>
+      </c>
+      <c r="I587" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -24742,21 +25471,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5863FAA0-C722-4C55-9DF4-9AF4C976B70C}">
-  <dimension ref="H17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H17" t="s">
-        <v>2015</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8399EA5-E4D0-4141-B53B-8BEA60D97B6A}">
   <dimension ref="A1:A29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81CB587A-C11B-4FCF-B23A-D30C7C2437BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC0D9E21-6F92-444C-863F-CF0D5113868D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2301" uniqueCount="2106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2329" uniqueCount="2132">
   <si>
     <t>No</t>
   </si>
@@ -6825,6 +6825,84 @@
   </si>
   <si>
     <t>Music Hall, Pop Rock [Acoustic Miniature, Hidden Track]</t>
+  </si>
+  <si>
+    <t>Savoy Brown</t>
+  </si>
+  <si>
+    <t>Hellbound Train</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/33653532-Savoy-Brown-Hellbound-Train</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/dCvEehqzR8cmNONF6xb0rNAA-9PDacje1RkwfzNGzsI/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTMzNjUz/NTMyLTE3NDQ0NTU4/ODItNTEyMy5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Doin’ Fine</t>
+  </si>
+  <si>
+    <t>Lost and Lonely Child</t>
+  </si>
+  <si>
+    <t>I’ll Make Everything Alright</t>
+  </si>
+  <si>
+    <t>Troubled by These Days and Times</t>
+  </si>
+  <si>
+    <t>If I Could See an End</t>
+  </si>
+  <si>
+    <t>It’ll Make You Happy</t>
+  </si>
+  <si>
+    <t>Decca – 753 5412, Europe, April 12, 2025 (Record Store Day, Reissue, Remastered, Stereo, Grey &amp; Purple Marble), Pressed By – GZ Media</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Record Store Day 2025 release. Limited edition pressed on Grey &amp; Purple Marble vinyl. Features a "Made in Czech Republic" sticker on the back. Remastered by Tim Debney. Pressed at GZ Media.</t>
+  </si>
+  <si>
+    <t>Blues Rock, Rock &amp; Roll [Boogie Rock, Up-tempo British Blues]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Soul Rock [Slow Blues, Blues Ballad, British R&amp;B]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Hard Rock [Mid-tempo Heavy Blues, Rock Ballad]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Progressive Rock [Dark Blues, Dramatic Blues Rock]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Soul Rock [Blues Ballad, Gospel-tinged Rock]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Boogie Rock [Upbeat Heavy Blues, Rock &amp; Roll]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Hard Rock [Epic Blues Rock, Boogie, Heavy Blues Suite]</t>
+  </si>
+  <si>
+    <t>Ανοίγει το album με αισιόδοξο boogie groove και άμεσο, κιθαριστικό drive. Ο τίτλος δηλώνει αυτοπεποίθηση, όμως η μουσική κρατά την τραχιά αίσθηση του Savoy Brown blues. Είναι σύντομο, αποτελεσματικό και λειτουργεί σαν άμεση είσοδος στη ζωντανή ενέργεια της μπάντας.</t>
+  </si>
+  <si>
+    <t>Ένα από τα πιο δυνατά τραγούδια της πρώτης πλευράς. Η αίσθηση μοναξιάς δεν αποδίδεται με μελόδραμα αλλά με αργό blues χτίσιμο, έντονη φωνητική ερμηνεία και κιθάρα που σχολιάζει τη μελωδία. Ο Walker δίνει στον χαρακτήρα του τραγουδιού μια σχεδόν τραγική διάσταση.</t>
+  </si>
+  <si>
+    <t>Πιο compact και μελωδικό, με μια προσπάθεια παρηγοριάς που συγκρούεται με την αμφιβολία. Η μπάντα κρατά mid-tempo ρυθμό, αφήνοντας χώρο στα φωνητικά και στην κιθάρα να αναπτύξουν τη συναισθηματική ένταση.</t>
+  </si>
+  <si>
+    <t>Σκοτεινό και στοχαστικό blues-rock κομμάτι. Ο τίτλος παραπέμπει άμεσα στην κοινωνική και προσωπική ανησυχία των αρχών της δεκαετίας του ’70. Τα πλήκτρα και η κιθάρα κάνουν τον ήχο πιο δραματικό, ενώ το τραγούδι ξεφεύγει από το απλό bar-band blues.</t>
+  </si>
+  <si>
+    <t>Μικρή, συναισθηματική blues μπαλάντα. Η ιδέα του “τέλους” μπορεί να αφορά σχέση, ψυχική δοκιμασία ή μια δύσκολη περίοδο που δεν φαίνεται να τελειώνει. Η ενορχήστρωση είναι συγκρατημένη και αφήνει τη φωνή να κρατήσει το βάρος.</t>
+  </si>
+  <si>
+    <t>Επιστροφή σε πιο εξωστρεφή ρυθμό. Το τραγούδι έχει boogie-rock ενέργεια και πιο ανάλαφρο χαρακτήρα, χωρίς να απομακρύνεται από τη βαρύτητα της κιθάρας και το βρετανικό blues ύφος. Είναι από τα tracks που λειτουργούν καλύτερα σε δυνατή ένταση.</t>
+  </si>
+  <si>
+    <t>Η κορυφαία σύνθεση και η φυσική κατάληξη του άλμπουμ. Το εννιάλεπτο κομμάτι ξεκινά ως blues αφήγηση και σταδιακά εξελίσσεται σε βαριά, επαναληπτική blues-rock διαδρομή. Η κιθάρα του Simmonds γίνεται πιο επίμονη και σκληρή, ενώ το rhythm section δημιουργεί την αίσθηση τρένου που κινείται ασταμάτητα. Η δομή του δεν είναι progressive με την κλασική έννοια, αλλά διαθέτει σαφή κλιμάκωση, ατμόσφαιρα και δραματουργία. Στην αμερικανική βινυλιακή έκδοση, το ομώνυμο κομμάτι φέρεται να διακόπτεται απότομα καθώς η βελόνα μπαίνει στο runoff groove, ιδιαιτερότητα της συγκεκριμένης πλευράς και όχι απαραίτητα mastering error.</t>
   </si>
 </sst>
 </file>
@@ -7343,7 +7421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -9373,6 +9451,36 @@
       </c>
       <c r="J63" s="11" t="s">
         <v>2051</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A64" s="6">
+        <v>33653532</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>2106</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>2107</v>
+      </c>
+      <c r="D64" s="6">
+        <v>1972</v>
+      </c>
+      <c r="E64" s="10">
+        <v>3.52</v>
+      </c>
+      <c r="F64" s="9"/>
+      <c r="G64" s="7" t="s">
+        <v>2117</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>2116</v>
+      </c>
+      <c r="I64" s="11" t="s">
+        <v>2108</v>
+      </c>
+      <c r="J64" s="11" t="s">
+        <v>2109</v>
       </c>
     </row>
   </sheetData>
@@ -9499,6 +9607,8 @@
     <hyperlink ref="J62" r:id="rId120" xr:uid="{F80F1184-6004-4DE3-A74B-2FA197532CAD}"/>
     <hyperlink ref="I63" r:id="rId121" xr:uid="{4231DB13-C70E-4D21-B210-8DDD89D2EE71}"/>
     <hyperlink ref="J63" r:id="rId122" xr:uid="{8AA4738F-FC96-41CA-87DA-4152EF3852B8}"/>
+    <hyperlink ref="I64" r:id="rId123" xr:uid="{1DCFFFE2-22E0-443E-BB64-562E9F90ECA3}"/>
+    <hyperlink ref="J64" r:id="rId124" xr:uid="{29F51A9E-C7A9-4814-94D0-D5E6DC71A5C1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9506,7 +9616,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I587"/>
+  <dimension ref="A1:I594"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -25464,6 +25574,197 @@
       </c>
       <c r="I587" s="6"/>
     </row>
+    <row r="588" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A588" s="6">
+        <v>33653532</v>
+      </c>
+      <c r="B588" s="6">
+        <v>1</v>
+      </c>
+      <c r="C588" s="7" t="s">
+        <v>2110</v>
+      </c>
+      <c r="D588" s="7" t="s">
+        <v>2118</v>
+      </c>
+      <c r="E588" s="20">
+        <v>3.82</v>
+      </c>
+      <c r="F588" s="12">
+        <v>4</v>
+      </c>
+      <c r="G588" s="12">
+        <v>4.75</v>
+      </c>
+      <c r="H588" s="7" t="s">
+        <v>2125</v>
+      </c>
+      <c r="I588" s="6"/>
+    </row>
+    <row r="589" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A589" s="6">
+        <v>33653532</v>
+      </c>
+      <c r="B589" s="6">
+        <v>2</v>
+      </c>
+      <c r="C589" s="7" t="s">
+        <v>2111</v>
+      </c>
+      <c r="D589" s="7" t="s">
+        <v>2119</v>
+      </c>
+      <c r="E589" s="20">
+        <v>3.75</v>
+      </c>
+      <c r="F589" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G589" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H589" s="7" t="s">
+        <v>2126</v>
+      </c>
+      <c r="I589" s="6"/>
+    </row>
+    <row r="590" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A590" s="6">
+        <v>33653532</v>
+      </c>
+      <c r="B590" s="6">
+        <v>3</v>
+      </c>
+      <c r="C590" s="7" t="s">
+        <v>2112</v>
+      </c>
+      <c r="D590" s="7" t="s">
+        <v>2120</v>
+      </c>
+      <c r="E590" s="20">
+        <v>3.35</v>
+      </c>
+      <c r="F590" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G590" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H590" s="7" t="s">
+        <v>2127</v>
+      </c>
+      <c r="I590" s="6"/>
+    </row>
+    <row r="591" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A591" s="6">
+        <v>33653532</v>
+      </c>
+      <c r="B591" s="6">
+        <v>4</v>
+      </c>
+      <c r="C591" s="7" t="s">
+        <v>2113</v>
+      </c>
+      <c r="D591" s="7" t="s">
+        <v>2121</v>
+      </c>
+      <c r="E591" s="20">
+        <v>3.49</v>
+      </c>
+      <c r="F591" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G591" s="12">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="H591" s="7" t="s">
+        <v>2128</v>
+      </c>
+      <c r="I591" s="6"/>
+    </row>
+    <row r="592" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A592" s="6">
+        <v>33653532</v>
+      </c>
+      <c r="B592" s="6">
+        <v>5</v>
+      </c>
+      <c r="C592" s="7" t="s">
+        <v>2114</v>
+      </c>
+      <c r="D592" s="7" t="s">
+        <v>2122</v>
+      </c>
+      <c r="E592" s="20">
+        <v>3.46</v>
+      </c>
+      <c r="F592" s="12">
+        <v>4</v>
+      </c>
+      <c r="G592" s="12">
+        <v>4.75</v>
+      </c>
+      <c r="H592" s="7" t="s">
+        <v>2129</v>
+      </c>
+      <c r="I592" s="6"/>
+    </row>
+    <row r="593" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A593" s="6">
+        <v>33653532</v>
+      </c>
+      <c r="B593" s="6">
+        <v>6</v>
+      </c>
+      <c r="C593" s="7" t="s">
+        <v>2115</v>
+      </c>
+      <c r="D593" s="7" t="s">
+        <v>2123</v>
+      </c>
+      <c r="E593" s="20">
+        <v>3.43</v>
+      </c>
+      <c r="F593" s="12">
+        <v>4</v>
+      </c>
+      <c r="G593" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H593" s="7" t="s">
+        <v>2130</v>
+      </c>
+      <c r="I593" s="6"/>
+    </row>
+    <row r="594" spans="1:9" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A594" s="6">
+        <v>33653532</v>
+      </c>
+      <c r="B594" s="6">
+        <v>7</v>
+      </c>
+      <c r="C594" s="7" t="s">
+        <v>2107</v>
+      </c>
+      <c r="D594" s="7" t="s">
+        <v>2124</v>
+      </c>
+      <c r="E594" s="20">
+        <v>4.25</v>
+      </c>
+      <c r="F594" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="G594" s="12">
+        <v>4.95</v>
+      </c>
+      <c r="H594" s="7" t="s">
+        <v>2131</v>
+      </c>
+      <c r="I594" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC0D9E21-6F92-444C-863F-CF0D5113868D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0249289-5665-4656-AC9F-2B38BABBB477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2329" uniqueCount="2132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2360" uniqueCount="2163">
   <si>
     <t>No</t>
   </si>
@@ -6903,6 +6903,99 @@
   </si>
   <si>
     <t>Η κορυφαία σύνθεση και η φυσική κατάληξη του άλμπουμ. Το εννιάλεπτο κομμάτι ξεκινά ως blues αφήγηση και σταδιακά εξελίσσεται σε βαριά, επαναληπτική blues-rock διαδρομή. Η κιθάρα του Simmonds γίνεται πιο επίμονη και σκληρή, ενώ το rhythm section δημιουργεί την αίσθηση τρένου που κινείται ασταμάτητα. Η δομή του δεν είναι progressive με την κλασική έννοια, αλλά διαθέτει σαφή κλιμάκωση, ατμόσφαιρα και δραματουργία. Στην αμερικανική βινυλιακή έκδοση, το ομώνυμο κομμάτι φέρεται να διακόπτεται απότομα καθώς η βελόνα μπαίνει στο runoff groove, ιδιαιτερότητα της συγκεκριμένης πλευράς και όχι απαραίτητα mastering error.</t>
+  </si>
+  <si>
+    <t>Long Black Waves</t>
+  </si>
+  <si>
+    <t>I See You Better in the Dark</t>
+  </si>
+  <si>
+    <t>My Hair Is on Fire (But I’ll Take Your Hand)</t>
+  </si>
+  <si>
+    <t>Lovers Give a Kingdom to Each Other</t>
+  </si>
+  <si>
+    <t>Being with the Dead</t>
+  </si>
+  <si>
+    <t>Until Forever and Again</t>
+  </si>
+  <si>
+    <t>Notes from Underground</t>
+  </si>
+  <si>
+    <t>Between You, God, the Devil and the Dead</t>
+  </si>
+  <si>
+    <t>Between You, God, The Devil And The Dead</t>
+  </si>
+  <si>
+    <t>Avatarium</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/32916789-Avatarium-Between-You-GodDevil-And-The-Dead</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/XLdUCy0mkAjN-_WyRvgIQuOs7XdaTESxIR4txPajdsY/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTMyOTE2/Nzg5LTE3Mzc1NTA4/NzQtNzkxNC5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Doom Metal, Hard Rock [Psychedelic Doom, Gothic Rock, Traditional Heavy Metal]</t>
+  </si>
+  <si>
+    <t>Doom Metal, Hard Rock [Traditional Doom, Epic Doom, Psychedelic Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Doom Metal [Occult Rock, 70s Hard Rock, Gothic Doom]</t>
+  </si>
+  <si>
+    <t>Doom Metal, Psychedelic Rock [Epic Doom, Bluesy Heavy Rock, Occult Rock]</t>
+  </si>
+  <si>
+    <t>Doom Metal, Gothic Rock [Doom Ballad, Dark Romantic Rock, Psychedelic Doom]</t>
+  </si>
+  <si>
+    <t>Doom Metal, Progressive Rock [Epic Doom, Funeral Rock, Symphonic Doom]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Doom Metal [Melodic Doom, Classic Rock, Power Ballad]</t>
+  </si>
+  <si>
+    <t>Doom Metal, Psychedelic Rock [Dark Psych, Occult Doom, Atmospheric Rock]</t>
+  </si>
+  <si>
+    <t>Doom Metal, Progressive Rock [Epic Doom Suite, Gothic Metal, Theatrical Heavy Rock]</t>
+  </si>
+  <si>
+    <t>AFM Records – AFM 894, AFM Records – AFM 894-11, Germany, Jan 24, 2025 (Limited Edition, Orange / White Marbled)</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Limited edition release of 800 copies worldwide, presented in a single jacket featuring a striking embossed sleeve and a dedicated lyric sheet insert. Pressed on heavy, vibrant orange and white marbled vinyl. Mastered specifically for high-fidelity analog playback, capturing the massive, atmospheric doom-metal dynamics and the characteristic heavy low-end presence of the studio sessions at Deep Well Studio and The Cave Drumstudio.</t>
+  </si>
+  <si>
+    <t>Το εναρκτήριο κομμάτι εισάγει αμέσως τον κόσμο του άλμπουμ με βαρύ, αργό riff και μελωδική φωνητική γραμμή. Οι "μαύρες, μακριές κυματιστές" εικόνες παραπέμπουν σε σκοτεινή κίνηση που παρασύρει τον άνθρωπο. Η κιθάρα του Jidell έχει κλασικό doom βάρος, αλλά η μελωδία παραμένει αρκετά ανοιχτή ώστε να λειτουργεί και ως hard rock anthem. Ήταν το πρώτο single του άλμπουμ.</t>
+  </si>
+  <si>
+    <t>Πιο άμεσο και ρυθμικό, με έντονη occult rock αίσθηση. Η ιδέα ότι κάποιος "βλέπει καλύτερα στο σκοτάδι" μετατρέπει το σκοτάδι από απειλή σε χώρο αποκάλυψης. Η φωνή της Smith έχει μεγαλύτερη αυτοπεποίθηση και το riff διαθέτει classic rock δυναμική, χωρίς να χάνει τη doom σκιά.</t>
+  </si>
+  <si>
+    <t>Ένας από τους πιο χαρακτηριστικούς τίτλους του δίσκου, που ενώνει κίνδυνο και αφοσίωση. Η εικόνα είναι σχεδόν παράλογη, αλλά το συναίσθημα είναι σαφές, ακόμη και μέσα στην καταστροφή, υπάρχει η επιλογή της σύνδεσης. Μουσικά, το κομμάτι κινείται ανάμεσα σε bluesy heavy rock, epic doom και ψυχεδελικές κιθάρες.</t>
+  </si>
+  <si>
+    <t>Αργή, σκοτεινή ερωτική σύνθεση. Ο τίτλος παρουσιάζει τον έρωτα ως αμοιβαία παράδοση ολόκληρου κόσμου, όχι ως απλή ρομαντική στιγμή. Η φωνητική μελωδία είναι θεατρική και το riff λειτουργεί σαν τελετουργικό υπόβαθρο, δίνοντας στο κομμάτι gothic και doom ballad χαρακτήρα.</t>
+  </si>
+  <si>
+    <t>Μία από τις πιο βαριές και δραματικές στιγμές. Ο τίτλος μπορεί να διαβαστεί ως σχέση με τη μνήμη, το πένθος ή την αδυναμία να αποχωριστείς τους νεκρούς. Το τραγούδι έχει μεγαλύτερη επική ανάπτυξη και πιο progressive αίσθηση, με δυναμικές κορυφώσεις που δείχνουν την ικανότητα των Avatarium να δημιουργούν doom χωρίς μονοτονία.</t>
+  </si>
+  <si>
+    <t>Πιο μελωδικό και λιγότερο απειλητικό. Η φράση του τίτλου δημιουργεί έναν κύκλο ανάμεσα στο “forever” και στο “again”, σαν σχέση ή υπόσχεση που επαναλαμβάνεται πέρα από τον χρόνο. Η σύνθεση έχει στοιχεία power ballad και classic hard rock, αλλά διατηρεί το σκοτεινό χρώμα της μπάντας.</t>
+  </si>
+  <si>
+    <t>Σκοτεινό, ψυχεδελικό και εσωστρεφές. Ο τίτλος παραπέμπει σε υπόγεια σκέψη, απομόνωση και ανθρώπους που υπάρχουν στο περιθώριο. Η μουσική κινείται πιο ατμοσφαιρικά, με χώρο για φωνητικές αποχρώσεις και κιθαριστικές υφές αντί για διαρκή riff επίθεση.</t>
+  </si>
+  <si>
+    <t>Το ομώνυμο φινάλε συμπυκνώνει όλη τη θεματολογία του άλμπουμ. Ο άνθρωπος βρίσκεται ανάμεσα σε πνευματική επιθυμία, σκοτεινό πειρασμό και αναπόφευκτο θάνατο. Η σύνθεση είναι επική και θεατρική, με αργές μεταβολές, μεγάλες κιθαριστικές κορυφώσεις και φωνητική ερμηνεία που μοιάζει περισσότερο με τελετουργική αφήγηση παρά με απλό metal τραγούδι.</t>
   </si>
 </sst>
 </file>
@@ -7421,7 +7514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -9481,6 +9574,38 @@
       </c>
       <c r="J64" s="11" t="s">
         <v>2109</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+      <c r="A65" s="6">
+        <v>32916789</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>2140</v>
+      </c>
+      <c r="D65" s="6">
+        <v>2025</v>
+      </c>
+      <c r="E65" s="10">
+        <v>3.25</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>2144</v>
+      </c>
+      <c r="G65" s="7" t="s">
+        <v>2154</v>
+      </c>
+      <c r="H65" s="6" t="s">
+        <v>2153</v>
+      </c>
+      <c r="I65" s="11" t="s">
+        <v>2142</v>
+      </c>
+      <c r="J65" s="11" t="s">
+        <v>2143</v>
       </c>
     </row>
   </sheetData>
@@ -9609,6 +9734,8 @@
     <hyperlink ref="J63" r:id="rId122" xr:uid="{8AA4738F-FC96-41CA-87DA-4152EF3852B8}"/>
     <hyperlink ref="I64" r:id="rId123" xr:uid="{1DCFFFE2-22E0-443E-BB64-562E9F90ECA3}"/>
     <hyperlink ref="J64" r:id="rId124" xr:uid="{29F51A9E-C7A9-4814-94D0-D5E6DC71A5C1}"/>
+    <hyperlink ref="I65" r:id="rId125" xr:uid="{5C8F2870-5E10-4B34-8BCC-743C5F27272D}"/>
+    <hyperlink ref="J65" r:id="rId126" xr:uid="{628D75D8-9DA8-4D3C-8F1C-F2FF0AFE9CD7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9616,7 +9743,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I594"/>
+  <dimension ref="A1:I602"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -25765,6 +25892,222 @@
         <v>266</v>
       </c>
     </row>
+    <row r="595" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A595" s="6">
+        <v>32916789</v>
+      </c>
+      <c r="B595" s="6">
+        <v>1</v>
+      </c>
+      <c r="C595" s="7" t="s">
+        <v>2132</v>
+      </c>
+      <c r="D595" s="7" t="s">
+        <v>2145</v>
+      </c>
+      <c r="E595" s="20">
+        <v>3.62</v>
+      </c>
+      <c r="F595" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G595" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H595" s="7" t="s">
+        <v>2155</v>
+      </c>
+      <c r="I595" s="6"/>
+    </row>
+    <row r="596" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A596" s="6">
+        <v>32916789</v>
+      </c>
+      <c r="B596" s="6">
+        <v>2</v>
+      </c>
+      <c r="C596" s="7" t="s">
+        <v>2133</v>
+      </c>
+      <c r="D596" s="7" t="s">
+        <v>2146</v>
+      </c>
+      <c r="E596" s="20">
+        <v>3.61</v>
+      </c>
+      <c r="F596" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G596" s="12">
+        <v>4</v>
+      </c>
+      <c r="H596" s="7" t="s">
+        <v>2156</v>
+      </c>
+      <c r="I596" s="6"/>
+    </row>
+    <row r="597" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A597" s="6">
+        <v>32916789</v>
+      </c>
+      <c r="B597" s="6">
+        <v>3</v>
+      </c>
+      <c r="C597" s="7" t="s">
+        <v>2134</v>
+      </c>
+      <c r="D597" s="7" t="s">
+        <v>2147</v>
+      </c>
+      <c r="E597" s="20">
+        <v>3.49</v>
+      </c>
+      <c r="F597" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G597" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H597" s="7" t="s">
+        <v>2157</v>
+      </c>
+      <c r="I597" s="6"/>
+    </row>
+    <row r="598" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A598" s="6">
+        <v>32916789</v>
+      </c>
+      <c r="B598" s="6">
+        <v>4</v>
+      </c>
+      <c r="C598" s="7" t="s">
+        <v>2135</v>
+      </c>
+      <c r="D598" s="7" t="s">
+        <v>2148</v>
+      </c>
+      <c r="E598" s="20">
+        <v>3.45</v>
+      </c>
+      <c r="F598" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G598" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="H598" s="7" t="s">
+        <v>2158</v>
+      </c>
+      <c r="I598" s="6"/>
+    </row>
+    <row r="599" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A599" s="6">
+        <v>32916789</v>
+      </c>
+      <c r="B599" s="6">
+        <v>5</v>
+      </c>
+      <c r="C599" s="7" t="s">
+        <v>2136</v>
+      </c>
+      <c r="D599" s="7" t="s">
+        <v>2149</v>
+      </c>
+      <c r="E599" s="20">
+        <v>3.34</v>
+      </c>
+      <c r="F599" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G599" s="12">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="H599" s="7" t="s">
+        <v>2159</v>
+      </c>
+      <c r="I599" s="6"/>
+    </row>
+    <row r="600" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A600" s="6">
+        <v>32916789</v>
+      </c>
+      <c r="B600" s="6">
+        <v>6</v>
+      </c>
+      <c r="C600" s="7" t="s">
+        <v>2137</v>
+      </c>
+      <c r="D600" s="7" t="s">
+        <v>2150</v>
+      </c>
+      <c r="E600" s="20">
+        <v>3.37</v>
+      </c>
+      <c r="F600" s="12">
+        <v>4</v>
+      </c>
+      <c r="G600" s="12">
+        <v>3.95</v>
+      </c>
+      <c r="H600" s="7" t="s">
+        <v>2160</v>
+      </c>
+      <c r="I600" s="6"/>
+    </row>
+    <row r="601" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A601" s="6">
+        <v>32916789</v>
+      </c>
+      <c r="B601" s="6">
+        <v>7</v>
+      </c>
+      <c r="C601" s="7" t="s">
+        <v>2138</v>
+      </c>
+      <c r="D601" s="7" t="s">
+        <v>2151</v>
+      </c>
+      <c r="E601" s="20">
+        <v>3.27</v>
+      </c>
+      <c r="F601" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G601" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="H601" s="7" t="s">
+        <v>2161</v>
+      </c>
+      <c r="I601" s="6"/>
+    </row>
+    <row r="602" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A602" s="6">
+        <v>32916789</v>
+      </c>
+      <c r="B602" s="6">
+        <v>8</v>
+      </c>
+      <c r="C602" s="7" t="s">
+        <v>2139</v>
+      </c>
+      <c r="D602" s="7" t="s">
+        <v>2152</v>
+      </c>
+      <c r="E602" s="20">
+        <v>3.51</v>
+      </c>
+      <c r="F602" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G602" s="12">
+        <v>4.05</v>
+      </c>
+      <c r="H602" s="7" t="s">
+        <v>2162</v>
+      </c>
+      <c r="I602" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0249289-5665-4656-AC9F-2B38BABBB477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B10C5EF0-D0D0-40E4-BA65-11D80B80437C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2360" uniqueCount="2163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2392" uniqueCount="2194">
   <si>
     <t>No</t>
   </si>
@@ -6995,7 +6995,167 @@
     <t>Σκοτεινό, ψυχεδελικό και εσωστρεφές. Ο τίτλος παραπέμπει σε υπόγεια σκέψη, απομόνωση και ανθρώπους που υπάρχουν στο περιθώριο. Η μουσική κινείται πιο ατμοσφαιρικά, με χώρο για φωνητικές αποχρώσεις και κιθαριστικές υφές αντί για διαρκή riff επίθεση.</t>
   </si>
   <si>
-    <t>Το ομώνυμο φινάλε συμπυκνώνει όλη τη θεματολογία του άλμπουμ. Ο άνθρωπος βρίσκεται ανάμεσα σε πνευματική επιθυμία, σκοτεινό πειρασμό και αναπόφευκτο θάνατο. Η σύνθεση είναι επική και θεατρική, με αργές μεταβολές, μεγάλες κιθαριστικές κορυφώσεις και φωνητική ερμηνεία που μοιάζει περισσότερο με τελετουργική αφήγηση παρά με απλό metal τραγούδι.</t>
+    <t>Wired</t>
+  </si>
+  <si>
+    <t>Jeff Beck</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/15960193-Jeff-Beck-Wired</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/0Fpp56KhtuoZfJsl7tfq4ZJL3JROSeSuqzAK_hVfh-g/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTE1OTYw/MTkzLTE2MDI0Mjg3/MzUtMTg1NC5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Led Boots</t>
+  </si>
+  <si>
+    <t>Come Dancing</t>
+  </si>
+  <si>
+    <t>Blue Wind</t>
+  </si>
+  <si>
+    <t>Goodbye Pork Pie Hat</t>
+  </si>
+  <si>
+    <t>Love Is Green</t>
+  </si>
+  <si>
+    <t>Head for the Backstage Pass</t>
+  </si>
+  <si>
+    <t>Sophie</t>
+  </si>
+  <si>
+    <t>Play with Me</t>
+  </si>
+  <si>
+    <t>Legacy – 19439792611, Europe, 2020 (Reissue, Remastered, Stereo, Blueberry Coloured Vinyl)</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** European reissue released in 2020 via Legacy / Music On Vinyl. Pressed on translucent blueberry coloured vinyl, featuring a hype sticker on the outer sleeve ("BLUEBERRY COLOURED VINYL"). Mastered and pressed for audiophile standards with dynamic instrumental jazz-rock and fusion arrangements.</t>
+  </si>
+  <si>
+    <t>Jazz Fusion, Jazz-Rock [Instrumental Fusion, Funk Rock, Jazz Guitar]</t>
+  </si>
+  <si>
+    <t>Jazz Fusion, Funk Rock [Up-tempo Fusion, Instrumental Funk, Jazz-Rock]</t>
+  </si>
+  <si>
+    <t>Jazz Fusion, Jazz-Rock [Melodic Fusion, Instrumental Rock, Jazz Guitar]</t>
+  </si>
+  <si>
+    <t>Jazz Fusion, Jazz [Jazz Standard, Fusion Ballad, Instrumental Guitar]</t>
+  </si>
+  <si>
+    <t>Jazz Fusion, Rock [Funk Fusion, Progressive Jazz-Rock, Instrumental Rock]</t>
+  </si>
+  <si>
+    <t>Jazz Fusion, Funk Rock [Electronic Fusion, Jazz-Rock, Instrumental Groove]</t>
+  </si>
+  <si>
+    <t>Jazz Fusion, Jazz [Fusion Ballad, Jazz Guitar, Atmospheric Instrumental]</t>
+  </si>
+  <si>
+    <t>Jazz Fusion, Funk Rock [Up-tempo Fusion, Funk Instrumental, Jazz-Rock]</t>
+  </si>
+  <si>
+    <t>Acoustic, Jazz Fusion [Acoustic Guitar, Ambient Fusion, Instrumental Ballad]</t>
+  </si>
+  <si>
+    <t>Το “Led Boots” είναι ένα από τα πιο δυναμικά ανοίγματα στην ιστορία του instrumental fusion. Η σύνθεση βασίζεται σε ένα σφιχτό, funk-rock riff, πάνω στο οποίο ο Jeff Beck χρησιμοποιεί την κιθάρα σχεδόν σαν φωνητικό όργανο: κοφτές φράσεις, έντονο vibrato, bends και απότομες δυναμικές.</t>
+  </si>
+  <si>
+    <t>Το “Led Boots” είναι ένα από τα πιο δυναμικά ανοίγματα στην ιστορία του instrumental fusion. Η σύνθεση βασίζεται σε ένα σφιχτό, funk-rock riff, πάνω στο οποίο ο Jeff Beck χρησιμοποιεί την κιθάρα σχεδόν σαν φωνητικό όργανο, κοφτές φράσεις, έντονο vibrato, bends και απότομες δυναμικές. Το rhythm section δίνει στο κομμάτι χορευτική αλλά επιθετική κίνηση, ενώ τα πλήκτρα προσθέτουν ηλεκτρική, σχεδόν διαστημική αίσθηση. Δεν είναι απλώς επίδειξη κιθαριστικής δεξιοτεχνίας, είναι σύνθεση με σαφή groove και πολύ καλή αρχιτεκτονική.</t>
+  </si>
+  <si>
+    <t>Το “Come Dancing” είναι πιο μελωδικό και λιγότερο επιθετικό. Ο Beck αφήνει την κιθάρα να “τραγουδήσει” με καθαρές, ευέλικτες φράσεις, ενώ το rhythm section κρατά μια κομψή fusion κίνηση. Η σύνθεση έχει στοιχεία jazz-rock αλλά παραμένει προσιτή, χάρη στην καθαρή μελωδία και στη σχεδόν pop αίσθηση της βασικής ιδέας. Είναι καλό παράδειγμα του τρόπου με τον οποίο ο Beck μετατρέπει ένα instrumental κομμάτι σε τραγούδι χωρίς λόγια.</t>
+  </si>
+  <si>
+    <t>Το “Love Is Green” είναι το πιο ήσυχο και εσωστρεφές κομμάτι της συγκεκριμένης tracklist. Σε αντίθεση με τον ηλεκτρικό και ρυθμικά έντονο χαρακτήρα των προηγούμενων tracks, εδώ κυριαρχεί η ακουστική κιθάρα και η ατμόσφαιρα. Η σύνθεση λειτουργεί σαν επίλογος: μετά την ένταση του fusion, ο Beck κλείνει το άλμπουμ με μια πιο γήινη και ευαίσθητη χειρονομία. Η ερμηνεία είναι λιτή, με έμφαση στην υφή του οργάνου, στη σιωπή ανάμεσα στις νότες και στην αίσθηση ηρεμίας.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Η διασκευή της σύνθεσης του </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Charles Mingus</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> είναι η πιο καθαρά jazz στιγμή της πρώτης πλευράς. Ο Jeff Beck δεν αντιμετωπίζει το κομμάτι ως απλό όχημα για solo, αλλά διατηρεί τη μελαγχολική και στοχαστική φύση της αρχικής μελωδίας. Η κιθάρα του είναι ιδιαίτερα εκφραστική, με μακρές νότες, ελεγχόμενο sustain και bluesy phrasing. Τα πλήκτρα και η ρυθμική βάση λειτουργούν υποστηρικτικά, αφήνοντας χώρο στη βασική μελωδία να αναπνεύσει.</t>
+    </r>
+  </si>
+  <si>
+    <t>Το “Head for the Backstage Pass” είναι πιο έντονο και ρυθμικά σύνθετο. Η βασική ιδέα κινείται ανάμεσα σε funk, progressive jazz-rock και fusion, με την κιθάρα να εναλλάσσεται ανάμεσα σε κοφτό ρυθμικό παίξιμο και πιο ελεύθερες φράσεις. Ο τίτλος παραπέμπει σε συναυλιακή και backstage ατμόσφαιρα, και η μουσική έχει ανάλογη κινητικότητα: είναι νευρική, γρήγορη και γεμάτη αλλαγές. Δεν έχει την άμεση αναγνωρισιμότητα του “Led Boots”, όμως αναδεικνύει καλύτερα την πολυπλοκότητα του ensemble.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Το “Blue Wind” είναι σύνθεση του </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Jan Hammer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> και μία από τις πιο γνωστές στιγμές του </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Wired</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>. Η κιθάρα του Beck και τα πλήκτρα του Hammer βρίσκονται σε συνεχή διάλογο, με το ένα όργανο να απαντά στο άλλο. Η σύνθεση συνδυάζει funk groove, jazz-rock και ηλεκτρονική fusion αισθητική. Τα synthesizers δεν χρησιμοποιούνται απλώς ως φόντο, αλλά ως ισότιμος αντίπαλος της κιθάρας. Το αποτέλεσμα είναι ενεργητικό, μοντέρνο για το 1976 και εξαιρετικά χαρακτηριστικό της συνεργασίας Beck – Hammer.</t>
+    </r>
+  </si>
+  <si>
+    <t>Το “Sophie” είναι πιο ατμοσφαιρικό και μελωδικό. Σε σχέση με τα γρήγορα funk-fusion κομμάτια, εδώ ο Beck χρησιμοποιεί περισσότερο χώρο και αφήνει τις νότες να αποκτήσουν συναισθηματικό βάρος. Η κιθάρα έχει καθαρό, λυρικό χαρακτήρα και η σύνθεση λειτουργεί σαν fusion μπαλάντα χωρίς φωνητικά. Τα πλήκτρα προσθέτουν βάθος, ενώ η ρυθμική βάση παραμένει διακριτική. Είναι κομμάτι που ανταμείβει περισσότερο την προσεκτική ακρόαση παρά την υψηλή ένταση.</t>
+  </si>
+  <si>
+    <t>Το “Play with Me” επαναφέρει την πιο παιχνιδιάρικη και εξωστρεφή πλευρά του άλμπουμ. Η σύνθεση βασίζεται σε funky ρυθμό, με γρήγορες κιθαριστικές γραμμές και έντονη αλληλεπίδραση ανάμεσα στην κιθάρα και τα πλήκτρα. Ο τίτλος αντανακλά τη διάθεση του κομματιού: είναι ελαφρύ, κινητικό και γεμάτο μουσικό παιχνίδι. Παρά την ταχύτητα, ο Beck δεν χάνει τον έλεγχο της φρασεολογίας· κάθε solo παραμένει δεμένο με το groove.</t>
   </si>
 </sst>
 </file>
@@ -7514,7 +7674,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J66"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -9606,6 +9766,38 @@
       </c>
       <c r="J65" s="11" t="s">
         <v>2143</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A66" s="6">
+        <v>15960193</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>2163</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>2162</v>
+      </c>
+      <c r="D66" s="6">
+        <v>1976</v>
+      </c>
+      <c r="E66" s="10">
+        <v>3.72</v>
+      </c>
+      <c r="F66" s="9" t="s">
+        <v>2176</v>
+      </c>
+      <c r="G66" s="7" t="s">
+        <v>2175</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>2174</v>
+      </c>
+      <c r="I66" s="11" t="s">
+        <v>2164</v>
+      </c>
+      <c r="J66" s="11" t="s">
+        <v>2165</v>
       </c>
     </row>
   </sheetData>
@@ -9736,6 +9928,8 @@
     <hyperlink ref="J64" r:id="rId124" xr:uid="{29F51A9E-C7A9-4814-94D0-D5E6DC71A5C1}"/>
     <hyperlink ref="I65" r:id="rId125" xr:uid="{5C8F2870-5E10-4B34-8BCC-743C5F27272D}"/>
     <hyperlink ref="J65" r:id="rId126" xr:uid="{628D75D8-9DA8-4D3C-8F1C-F2FF0AFE9CD7}"/>
+    <hyperlink ref="I66" r:id="rId127" xr:uid="{B71FE562-A9A6-4B3C-AB49-50BB818D223D}"/>
+    <hyperlink ref="J66" r:id="rId128" xr:uid="{48B641A4-17C1-4191-8CED-5E5659D92591}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9743,7 +9937,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I602"/>
+  <dimension ref="A1:I610"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -26081,7 +26275,7 @@
       </c>
       <c r="I601" s="6"/>
     </row>
-    <row r="602" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A602" s="6">
         <v>32916789</v>
       </c>
@@ -26103,10 +26297,228 @@
       <c r="G602" s="12">
         <v>4.05</v>
       </c>
-      <c r="H602" s="7" t="s">
-        <v>2162</v>
+      <c r="H602" s="9" t="s">
+        <v>2185</v>
       </c>
       <c r="I602" s="6"/>
+    </row>
+    <row r="603" spans="1:9" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A603" s="6">
+        <v>15960193</v>
+      </c>
+      <c r="B603" s="6">
+        <v>1</v>
+      </c>
+      <c r="C603" s="7" t="s">
+        <v>2166</v>
+      </c>
+      <c r="D603" s="7" t="s">
+        <v>2177</v>
+      </c>
+      <c r="E603" s="20">
+        <v>3.93</v>
+      </c>
+      <c r="F603" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="G603" s="12">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="H603" s="9" t="s">
+        <v>2186</v>
+      </c>
+      <c r="I603" s="6"/>
+    </row>
+    <row r="604" spans="1:9" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A604" s="6">
+        <v>15960193</v>
+      </c>
+      <c r="B604" s="6">
+        <v>2</v>
+      </c>
+      <c r="C604" s="7" t="s">
+        <v>2167</v>
+      </c>
+      <c r="D604" s="7" t="s">
+        <v>2178</v>
+      </c>
+      <c r="E604" s="20">
+        <v>3.87</v>
+      </c>
+      <c r="F604" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G604" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H604" s="9" t="s">
+        <v>2187</v>
+      </c>
+      <c r="I604" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="605" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A605" s="6">
+        <v>15960193</v>
+      </c>
+      <c r="B605" s="6">
+        <v>3</v>
+      </c>
+      <c r="C605" s="7" t="s">
+        <v>2169</v>
+      </c>
+      <c r="D605" s="7" t="s">
+        <v>2179</v>
+      </c>
+      <c r="E605" s="20">
+        <v>3.81</v>
+      </c>
+      <c r="F605" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="G605" s="12">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H605" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I605" s="6"/>
+    </row>
+    <row r="606" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A606" s="6">
+        <v>15960193</v>
+      </c>
+      <c r="B606" s="6">
+        <v>4</v>
+      </c>
+      <c r="C606" s="7" t="s">
+        <v>2171</v>
+      </c>
+      <c r="D606" s="7" t="s">
+        <v>2180</v>
+      </c>
+      <c r="E606" s="20">
+        <v>3.74</v>
+      </c>
+      <c r="F606" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G606" s="12">
+        <v>4.75</v>
+      </c>
+      <c r="H606" s="9" t="s">
+        <v>2190</v>
+      </c>
+      <c r="I606" s="6"/>
+    </row>
+    <row r="607" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A607" s="6">
+        <v>15960193</v>
+      </c>
+      <c r="B607" s="6">
+        <v>5</v>
+      </c>
+      <c r="C607" s="7" t="s">
+        <v>2168</v>
+      </c>
+      <c r="D607" s="7" t="s">
+        <v>2181</v>
+      </c>
+      <c r="E607" s="20">
+        <v>3.9</v>
+      </c>
+      <c r="F607" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G607" s="12">
+        <v>4.95</v>
+      </c>
+      <c r="H607" s="9" t="s">
+        <v>2191</v>
+      </c>
+      <c r="I607" s="6"/>
+    </row>
+    <row r="608" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A608" s="6">
+        <v>15960193</v>
+      </c>
+      <c r="B608" s="6">
+        <v>6</v>
+      </c>
+      <c r="C608" s="7" t="s">
+        <v>2172</v>
+      </c>
+      <c r="D608" s="7" t="s">
+        <v>2182</v>
+      </c>
+      <c r="E608" s="20">
+        <v>3.85</v>
+      </c>
+      <c r="F608" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G608" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H608" s="9" t="s">
+        <v>2192</v>
+      </c>
+      <c r="I608" s="6"/>
+    </row>
+    <row r="609" spans="1:9" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A609" s="6">
+        <v>15960193</v>
+      </c>
+      <c r="B609" s="6">
+        <v>7</v>
+      </c>
+      <c r="C609" s="7" t="s">
+        <v>2173</v>
+      </c>
+      <c r="D609" s="7" t="s">
+        <v>2183</v>
+      </c>
+      <c r="E609" s="20">
+        <v>3.67</v>
+      </c>
+      <c r="F609" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G609" s="12">
+        <v>4.75</v>
+      </c>
+      <c r="H609" s="9" t="s">
+        <v>2193</v>
+      </c>
+      <c r="I609" s="6"/>
+    </row>
+    <row r="610" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A610" s="6">
+        <v>15960193</v>
+      </c>
+      <c r="B610" s="6">
+        <v>8</v>
+      </c>
+      <c r="C610" s="7" t="s">
+        <v>2170</v>
+      </c>
+      <c r="D610" s="7" t="s">
+        <v>2184</v>
+      </c>
+      <c r="E610" s="20">
+        <v>3.63</v>
+      </c>
+      <c r="F610" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G610" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H610" s="9" t="s">
+        <v>2188</v>
+      </c>
+      <c r="I610" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B10C5EF0-D0D0-40E4-BA65-11D80B80437C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F9FE206-F452-41C6-8F7C-D762072E49AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2392" uniqueCount="2194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2441" uniqueCount="2242">
   <si>
     <t>No</t>
   </si>
@@ -7156,6 +7156,150 @@
   </si>
   <si>
     <t>Το “Play with Me” επαναφέρει την πιο παιχνιδιάρικη και εξωστρεφή πλευρά του άλμπουμ. Η σύνθεση βασίζεται σε funky ρυθμό, με γρήγορες κιθαριστικές γραμμές και έντονη αλληλεπίδραση ανάμεσα στην κιθάρα και τα πλήκτρα. Ο τίτλος αντανακλά τη διάθεση του κομματιού: είναι ελαφρύ, κινητικό και γεμάτο μουσικό παιχνίδι. Παρά την ταχύτητα, ο Beck δεν χάνει τον έλεγχο της φρασεολογίας· κάθε solo παραμένει δεμένο με το groove.</t>
+  </si>
+  <si>
+    <t>Dan Auerbach</t>
+  </si>
+  <si>
+    <t>Keep It Hid</t>
+  </si>
+  <si>
+    <t>Trouble Weighs a Ton</t>
+  </si>
+  <si>
+    <t>I Want Some More</t>
+  </si>
+  <si>
+    <t>Heartbroken, In Disrepair</t>
+  </si>
+  <si>
+    <t>Because I Should</t>
+  </si>
+  <si>
+    <t>Whispered Words (Pretty Lies)</t>
+  </si>
+  <si>
+    <t>Real Desire</t>
+  </si>
+  <si>
+    <t>When the Night Comes</t>
+  </si>
+  <si>
+    <t>Mean Monsoon</t>
+  </si>
+  <si>
+    <t>The Prowl</t>
+  </si>
+  <si>
+    <t>My Last Mistake</t>
+  </si>
+  <si>
+    <t>When I Left the Room</t>
+  </si>
+  <si>
+    <t>Street Walkin’</t>
+  </si>
+  <si>
+    <t>Goin’ Home</t>
+  </si>
+  <si>
+    <t>Blues Rock, Alternative Rock [Lo-Fi Blues, Garage Soul, Psychedelic Folk]</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/28423156-Dan-Auerbach-Keep-It-Hid</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/ypwNUF8Y_VSwCzv9D5HYJV2KJyOli6L-RS3qFJc5Qpc/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI4NDIz/MTU2LTE2OTU5Mzc5/NDktNTMyMC5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Easy Eye Sound – 0088072533288, Easy Eye Sound – EES-019, UK &amp; US, Sep 29, 2023 (Reissue, Stereo, Orange With Black Splatter)</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Limited edition reissue of 700 copies worldwide. Comes shrink wrapped with a front hype sticker and a 'Made In Czech Republic' rear sticker. Pressed on vibrant orange with black splatter vinyl, featuring printed sleeve notes detailing production at Easy Eye Sound Studios, Akron, OH and mixing by Mark Neill at Soil of the South Productions.</t>
+  </si>
+  <si>
+    <t>Blues, Folk Rock [Delta Blues, Lo-Fi Folk, Acoustic Blues]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Soul Rock [Garage Soul, R&amp;B Rock, Vintage Groove]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Garage Rock [Fuzz Blues, Lo-Fi Rock, Broken-Down Soul]</t>
+  </si>
+  <si>
+    <t>Folk, Psychedelic Rock [Lo-Fi Interlude, Acoustic Psych, Sketch Song]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Soul [Slow Blues, Garage Soul, Dark R&amp;B]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Psychedelic Rock [Fuzz Rock, Garage Blues, Heavy Lo-Fi Rock]</t>
+  </si>
+  <si>
+    <t>Folk Rock, Blues Rock [Nocturnal Folk, Blues Ballad, Vintage Pop]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Garage Rock [Raw Blues, Fuzz Garage, Swamp Rock]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Soul Rock [Dark Groove, Garage Soul, R&amp;B Rock]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Alternative Rock [Mid-tempo Garage Blues, Psychedelic Rock]</t>
+  </si>
+  <si>
+    <t>Folk Rock, Blues Rock [Acoustic Blues, Country Soul, Lo-Fi Ballad]</t>
+  </si>
+  <si>
+    <t>Soul Rock, Blues Rock [Vintage R&amp;B, Melodic Garage Soul, Slow Groove]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Garage Rock [Driving Blues, Fuzz Rock, Road Song]</t>
+  </si>
+  <si>
+    <t>Folk Rock, Blues [Acoustic Folk-Blues, Country Blues, Reflective Finale]</t>
+  </si>
+  <si>
+    <t>Λιτό, ακουστικό και βαρύ από την πρώτη νότα. Η βασική εικόνα είναι ότι η στενοχώρια έχει φυσικό βάρος· δεν είναι απλώς συναίσθημα, αλλά φορτίο που κουβαλάς. Η γυμνή ενορχήστρωση και η χαμηλόφωνη ερμηνεία δημιουργούν old-time folk-blues αίσθηση. Είναι ένα σπουδαίο εναρκτήριο κομμάτι και ένα από τα πιο ολοκληρωμένα τραγούδια του δίσκου.</t>
+  </si>
+  <si>
+    <t>Αλλαγή σε ζωηρότερο garage-soul groove. Ο αφηγητής δεν ζητά απλώς περισσότερο έρωτα ή προσοχή· ζητά διέξοδο από συναισθηματική έλλειψη. Τα drums του Bob Cesare και η ακατέργαστη κιθάρα μετατρέπουν την επιθυμία σε κοφτό, βρώμικο R&amp;B rock.</t>
+  </si>
+  <si>
+    <t>Ο τίτλος είναι σαφής: μια καρδιά όχι μόνο ραγισμένη αλλά κυριολεκτικά εκτός λειτουργίας. Fuzz κιθάρα, γκαραζόμορφος ρυθμός και κάπως ασταθής, σχεδόν χαλασμένη υφή υπηρετούν το θέμα. Ο Auerbach χρησιμοποιεί το studio lo-fi ως δραματικό εργαλείο: το τραγούδι ακούγεται “in disrepair”.</t>
+  </si>
+  <si>
+    <t>Σύντομο, 53 δευτερολέπτων interlude, γραμμένο μαζί με τον Mark Neill. Δεν επιχειρεί να γίνει πλήρης σύνθεση· μοιάζει περισσότερο με μισοειπωμένη σκέψη. Αυτή η ατέλεια ταιριάζει στον τίτλο: η πράξη γίνεται όχι από καθαρή επιθυμία, αλλά “because I should”.</t>
+  </si>
+  <si>
+    <t>Αργό, νυχτερινό και σκοτεινά αισθησιακό. Ο τίτλος αντιπαραβάλλει την οικειότητα του ψιθύρου με τη δυσπιστία των "όμορφων ψεμάτων". Η upright bass παρουσία και τα διακριτικά backing vocals δημιουργούν vintage soul/blues περιβάλλον, ενώ ο Auerbach κρατά την ερμηνεία του ελεγχόμενη αντί για θεατρική.</t>
+  </si>
+  <si>
+    <t>Πιο ηλεκτρικό και αδρό, με fuzz και garage-rock ενέργεια. Εδώ η επιθυμία δεν παρουσιάζεται ως ρομαντική λύτρωση, αλλά ως ένστικτο που μπορεί να σε σπρώξει σε ασταθείς αποφάσεις. Η παραγωγή πυκνώνει και η κιθάρα αποκτά πιο επιθετική θέση στο mix.</t>
+  </si>
+  <si>
+    <t>Νυχτερινή folk-blues μπαλάντα, συν-γραμμένη με τον Charles Auerbach και ηχογραφημένη/engineered από τον Mark Neill. Το τραγούδι χρησιμοποιεί τη νύχτα ως χώρο όπου οι άμυνες πέφτουν και οι σκέψεις γίνονται πιο έντονες. Η ενορχήστρωση είναι συγκρατημένη, με τη μελωδία και τη φωνή να κρατούν το βάρος.</t>
+  </si>
+  <si>
+    <t>Η καταιγίδα του τίτλου αποδίδεται με πιο ωμή blues-rock ενέργεια. Το κομμάτι έχει swampy αίσθηση, βρώμικο riffing και μια ατμόσφαιρα επερχόμενης καταστροφής. Είναι από τα tracks όπου η σύνδεση με το πρώιμο Black Keys DNA ακούγεται πιο έντονα.</t>
+  </si>
+  <si>
+    <t>Χαμηλό, σκοτεινό groove με αίσθηση κρυφής κίνησης. Το “prowl” υποδηλώνει περιπλάνηση ή αναζήτηση χωρίς ασφάλεια, κάτι που η μουσική υπηρετεί με r&amp;b pulse και υπόγειες κιθαριστικές φράσεις. Δεν επιδιώκει μεγάλη κορύφωση· προτιμά την ένταση που συσσωρεύεται αργά.</t>
+  </si>
+  <si>
+    <t>Το title track συγκεντρώνει την κεντρική στάση του άλμπουμ: απόκρυψη, επιφυλακτικότητα και έλεγχος της αποκάλυψης. Μουσικά είναι mid-tempo garage blues, με πιο ψυχεδελικά στοιχεία στην κιθάρα και μία μελωδία που μοιάζει εύκολη αλλά αφήνει διαρκώς ένα μικρό αίσθημα ανησυχίας.</t>
+  </si>
+  <si>
+    <t>Πιο ήσυχο, με country-blues και folk χαρακτήρα. Ο τίτλος λειτουργεί σαν υπόσχεση που ακούμε συχνά μετά από μια αποτυχία: «αυτό ήταν το τελευταίο λάθος». Η σύνθεση δεν προσφέρει βεβαιότητα ότι ο αφηγητής την πιστεύει —κι εκεί βρίσκεται η δύναμή της.</t>
+  </si>
+  <si>
+    <t>Μελωδικό slow groove που εξετάζει το κενό που μένει όταν κάποιος φεύγει. Η σύνδεση με classic R&amp;B και soul είναι ιδιαίτερα έντονη, η φωνή και η ρυθμική βάση δεν ξεσπούν, αλλά αφήνουν το τραγούδι να δουλέψει μέσα από τη συγκράτηση.</t>
+  </si>
+  <si>
+    <t>Πιο κινητικό road-blues κομμάτι. Η εικόνα του περπατήματος στον δρόμο υποδηλώνει φυγή, ανησυχία και αναζήτηση. Η κιθάρα και τα drums επαναφέρουν το γκαραζόμορφο drive, ενώ η παραγωγή κρατά τις άκρες τραχιές, χωρίς σύγχρονο γυάλισμα.</t>
+  </si>
+  <si>
+    <t>Το φυσικό κλείσιμο του album. Με ακουστική, folk-blues απλότητα, δεν παρουσιάζει το “σπίτι” ως θριαμβευτική λύση, αλλά ως ανάγκη για επιστροφή μετά από περιπλάνηση και συναισθηματική κούραση. Ο κύκλος του δίσκου κλείνει όπως άρχισε: με λιτότητα, βάρος και ανθρώπινη ευαισθησία.</t>
   </si>
 </sst>
 </file>
@@ -7304,7 +7448,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -7368,6 +7512,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -7674,7 +7821,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -9798,6 +9945,38 @@
       </c>
       <c r="J66" s="11" t="s">
         <v>2165</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A67" s="6">
+        <v>28423156</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>2194</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>2195</v>
+      </c>
+      <c r="D67" s="6">
+        <v>2009</v>
+      </c>
+      <c r="E67" s="10">
+        <v>3.43</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>2209</v>
+      </c>
+      <c r="G67" s="7" t="s">
+        <v>2213</v>
+      </c>
+      <c r="H67" s="6" t="s">
+        <v>2212</v>
+      </c>
+      <c r="I67" s="11" t="s">
+        <v>2210</v>
+      </c>
+      <c r="J67" s="11" t="s">
+        <v>2211</v>
       </c>
     </row>
   </sheetData>
@@ -9930,6 +10109,8 @@
     <hyperlink ref="J65" r:id="rId126" xr:uid="{628D75D8-9DA8-4D3C-8F1C-F2FF0AFE9CD7}"/>
     <hyperlink ref="I66" r:id="rId127" xr:uid="{B71FE562-A9A6-4B3C-AB49-50BB818D223D}"/>
     <hyperlink ref="J66" r:id="rId128" xr:uid="{48B641A4-17C1-4191-8CED-5E5659D92591}"/>
+    <hyperlink ref="I67" r:id="rId129" xr:uid="{BF0EC9E5-8719-4153-9E86-32829F330A56}"/>
+    <hyperlink ref="J67" r:id="rId130" xr:uid="{82F38111-DBC6-4CEB-AC91-8779B5919A35}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9937,7 +10118,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I610"/>
+  <dimension ref="A1:I624"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -26520,6 +26701,384 @@
       </c>
       <c r="I610" s="6"/>
     </row>
+    <row r="611" spans="1:9" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A611" s="6">
+        <v>28423156</v>
+      </c>
+      <c r="B611" s="6">
+        <v>1</v>
+      </c>
+      <c r="C611" s="22" t="s">
+        <v>2196</v>
+      </c>
+      <c r="D611" s="7" t="s">
+        <v>2214</v>
+      </c>
+      <c r="E611" s="20">
+        <v>3.34</v>
+      </c>
+      <c r="F611" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G611" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H611" s="7" t="s">
+        <v>2228</v>
+      </c>
+      <c r="I611" s="6"/>
+    </row>
+    <row r="612" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A612" s="6">
+        <v>28423156</v>
+      </c>
+      <c r="B612" s="6">
+        <v>2</v>
+      </c>
+      <c r="C612" s="22" t="s">
+        <v>2197</v>
+      </c>
+      <c r="D612" s="7" t="s">
+        <v>2215</v>
+      </c>
+      <c r="E612" s="20">
+        <v>3.66</v>
+      </c>
+      <c r="F612" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G612" s="12">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="H612" s="7" t="s">
+        <v>2229</v>
+      </c>
+      <c r="I612" s="6"/>
+    </row>
+    <row r="613" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A613" s="6">
+        <v>28423156</v>
+      </c>
+      <c r="B613" s="6">
+        <v>3</v>
+      </c>
+      <c r="C613" s="22" t="s">
+        <v>2198</v>
+      </c>
+      <c r="D613" s="7" t="s">
+        <v>2216</v>
+      </c>
+      <c r="E613" s="20">
+        <v>3.86</v>
+      </c>
+      <c r="F613" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G613" s="12">
+        <v>4.75</v>
+      </c>
+      <c r="H613" s="7" t="s">
+        <v>2230</v>
+      </c>
+      <c r="I613" s="6"/>
+    </row>
+    <row r="614" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A614" s="6">
+        <v>28423156</v>
+      </c>
+      <c r="B614" s="6">
+        <v>4</v>
+      </c>
+      <c r="C614" s="22" t="s">
+        <v>2199</v>
+      </c>
+      <c r="D614" s="7" t="s">
+        <v>2217</v>
+      </c>
+      <c r="E614" s="20">
+        <v>2.81</v>
+      </c>
+      <c r="F614" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="G614" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H614" s="7" t="s">
+        <v>2231</v>
+      </c>
+      <c r="I614" s="6"/>
+    </row>
+    <row r="615" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A615" s="6">
+        <v>28423156</v>
+      </c>
+      <c r="B615" s="6">
+        <v>5</v>
+      </c>
+      <c r="C615" s="22" t="s">
+        <v>2200</v>
+      </c>
+      <c r="D615" s="7" t="s">
+        <v>2218</v>
+      </c>
+      <c r="E615" s="20">
+        <v>3.6</v>
+      </c>
+      <c r="F615" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G615" s="12">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H615" s="7" t="s">
+        <v>2232</v>
+      </c>
+      <c r="I615" s="6"/>
+    </row>
+    <row r="616" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A616" s="6">
+        <v>28423156</v>
+      </c>
+      <c r="B616" s="6">
+        <v>6</v>
+      </c>
+      <c r="C616" s="22" t="s">
+        <v>2201</v>
+      </c>
+      <c r="D616" s="7" t="s">
+        <v>2219</v>
+      </c>
+      <c r="E616" s="20">
+        <v>3.61</v>
+      </c>
+      <c r="F616" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G616" s="12">
+        <v>4.75</v>
+      </c>
+      <c r="H616" s="7" t="s">
+        <v>2233</v>
+      </c>
+      <c r="I616" s="6"/>
+    </row>
+    <row r="617" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A617" s="6">
+        <v>28423156</v>
+      </c>
+      <c r="B617" s="6">
+        <v>7</v>
+      </c>
+      <c r="C617" s="22" t="s">
+        <v>2202</v>
+      </c>
+      <c r="D617" s="7" t="s">
+        <v>2220</v>
+      </c>
+      <c r="E617" s="20">
+        <v>3.5</v>
+      </c>
+      <c r="F617" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G617" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H617" s="7" t="s">
+        <v>2234</v>
+      </c>
+      <c r="I617" s="6"/>
+    </row>
+    <row r="618" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A618" s="6">
+        <v>28423156</v>
+      </c>
+      <c r="B618" s="6">
+        <v>8</v>
+      </c>
+      <c r="C618" s="22" t="s">
+        <v>2203</v>
+      </c>
+      <c r="D618" s="7" t="s">
+        <v>2221</v>
+      </c>
+      <c r="E618" s="20">
+        <v>3.48</v>
+      </c>
+      <c r="F618" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G618" s="12">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="H618" s="7" t="s">
+        <v>2235</v>
+      </c>
+      <c r="I618" s="6"/>
+    </row>
+    <row r="619" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A619" s="6">
+        <v>28423156</v>
+      </c>
+      <c r="B619" s="6">
+        <v>9</v>
+      </c>
+      <c r="C619" s="22" t="s">
+        <v>2204</v>
+      </c>
+      <c r="D619" s="7" t="s">
+        <v>2222</v>
+      </c>
+      <c r="E619" s="20">
+        <v>3.84</v>
+      </c>
+      <c r="F619" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G619" s="12">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H619" s="7" t="s">
+        <v>2236</v>
+      </c>
+      <c r="I619" s="6"/>
+    </row>
+    <row r="620" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A620" s="6">
+        <v>28423156</v>
+      </c>
+      <c r="B620" s="6">
+        <v>10</v>
+      </c>
+      <c r="C620" s="22" t="s">
+        <v>2195</v>
+      </c>
+      <c r="D620" s="7" t="s">
+        <v>2223</v>
+      </c>
+      <c r="E620" s="20">
+        <v>3.48</v>
+      </c>
+      <c r="F620" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G620" s="12">
+        <v>4.75</v>
+      </c>
+      <c r="H620" s="7" t="s">
+        <v>2237</v>
+      </c>
+      <c r="I620" s="6"/>
+    </row>
+    <row r="621" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A621" s="6">
+        <v>28423156</v>
+      </c>
+      <c r="B621" s="6">
+        <v>11</v>
+      </c>
+      <c r="C621" s="22" t="s">
+        <v>2205</v>
+      </c>
+      <c r="D621" s="7" t="s">
+        <v>2224</v>
+      </c>
+      <c r="E621" s="20">
+        <v>3.34</v>
+      </c>
+      <c r="F621" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G621" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H621" s="7" t="s">
+        <v>2238</v>
+      </c>
+      <c r="I621" s="6"/>
+    </row>
+    <row r="622" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A622" s="6">
+        <v>28423156</v>
+      </c>
+      <c r="B622" s="6">
+        <v>12</v>
+      </c>
+      <c r="C622" s="22" t="s">
+        <v>2206</v>
+      </c>
+      <c r="D622" s="7" t="s">
+        <v>2225</v>
+      </c>
+      <c r="E622" s="20">
+        <v>3.33</v>
+      </c>
+      <c r="F622" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G622" s="12">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="H622" s="7" t="s">
+        <v>2239</v>
+      </c>
+      <c r="I622" s="6"/>
+    </row>
+    <row r="623" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A623" s="6">
+        <v>28423156</v>
+      </c>
+      <c r="B623" s="6">
+        <v>13</v>
+      </c>
+      <c r="C623" s="22" t="s">
+        <v>2207</v>
+      </c>
+      <c r="D623" s="7" t="s">
+        <v>2226</v>
+      </c>
+      <c r="E623" s="20">
+        <v>3.42</v>
+      </c>
+      <c r="F623" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G623" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H623" s="7" t="s">
+        <v>2240</v>
+      </c>
+      <c r="I623" s="6"/>
+    </row>
+    <row r="624" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A624" s="6">
+        <v>28423156</v>
+      </c>
+      <c r="B624" s="6">
+        <v>14</v>
+      </c>
+      <c r="C624" s="22" t="s">
+        <v>2208</v>
+      </c>
+      <c r="D624" s="7" t="s">
+        <v>2227</v>
+      </c>
+      <c r="E624" s="20">
+        <v>3.81</v>
+      </c>
+      <c r="F624" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G624" s="12">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H624" s="7" t="s">
+        <v>2241</v>
+      </c>
+      <c r="I624" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F9FE206-F452-41C6-8F7C-D762072E49AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6303C191-CB1D-4D2E-A3C5-807908C294CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2441" uniqueCount="2242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2478" uniqueCount="2278">
   <si>
     <t>No</t>
   </si>
@@ -7300,6 +7300,114 @@
   </si>
   <si>
     <t>Το φυσικό κλείσιμο του album. Με ακουστική, folk-blues απλότητα, δεν παρουσιάζει το “σπίτι” ως θριαμβευτική λύση, αλλά ως ανάγκη για επιστροφή μετά από περιπλάνηση και συναισθηματική κούραση. Ο κύκλος του δίσκου κλείνει όπως άρχισε: με λιτότητα, βάρος και ανθρώπινη ευαισθησία.</t>
+  </si>
+  <si>
+    <t>Rock and Sing</t>
+  </si>
+  <si>
+    <t>Forgotten Eyes</t>
+  </si>
+  <si>
+    <t>The Toy</t>
+  </si>
+  <si>
+    <t>Two Hands</t>
+  </si>
+  <si>
+    <t>Those Girls</t>
+  </si>
+  <si>
+    <t>Shoulders</t>
+  </si>
+  <si>
+    <t>Not</t>
+  </si>
+  <si>
+    <t>Wolf</t>
+  </si>
+  <si>
+    <t>Replaced</t>
+  </si>
+  <si>
+    <t>Cut My Hair</t>
+  </si>
+  <si>
+    <t>4AD – 4AD0180LP, Europe, 2022 (Repress, Gatefold)</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Black vinyl. Packaged in a gatefold sleeve. Runouts are etched except for Sterling and MPO logo/number which are stamped. Lacquer cut at Sterling Sound by JN-H and pressed at MPO. Recorded at Sonic Ranch Studios and Sound City Studios.</t>
+  </si>
+  <si>
+    <t>Big Thief</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/25766467-Big-Thief-Two-Hands</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/N7sbT8nmyY62bcVQYWc2e_PVvYO0P7xq0mAgwnjQoPY/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI1NzY2/NDY3LTE2NzM3MjIz/MjAtNjgzOS5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Indie Rock, Indie Folk [Alternative Rock, Art Rock, Live-in-Studio Rock]</t>
+  </si>
+  <si>
+    <t>Indie Rock, Indie Folk [Raw Indie Rock, Folk Rock, Live Band Opener]</t>
+  </si>
+  <si>
+    <t>Indie Rock, Indie Folk [Compassionate Folk Rock, Alternative Rock]</t>
+  </si>
+  <si>
+    <t>Indie Folk, Indie Rock [Intimate Folk Rock, Art Rock, Narrative Song]</t>
+  </si>
+  <si>
+    <t>Indie Rock, Alternative Rock [Slow-Burn Rock, Art Rock, Atmospheric Indie]</t>
+  </si>
+  <si>
+    <t>Indie Rock, Indie Folk [Raw Folk Rock, Relationship Song, Alternative Rock]</t>
+  </si>
+  <si>
+    <t>Indie Rock, Alternative Rock [Tense Indie Rock, Noise Rock, Slow Build]</t>
+  </si>
+  <si>
+    <t>Indie Rock, Alternative Rock [Cathartic Rock, Noise Rock, Extended Guitar Finale]</t>
+  </si>
+  <si>
+    <t>Indie Folk, Indie Rock [Dark Folk Rock, Psychedelic Folk, Narrative Rock]</t>
+  </si>
+  <si>
+    <t>Indie Rock, Indie Folk [Experimental Folk Rock, Art Rock, Fragmented Narrative]</t>
+  </si>
+  <si>
+    <t>Indie Folk, Alternative Rock [Intimate Folk, Raw Indie Rock, Minimalist Ballad]</t>
+  </si>
+  <si>
+    <t>Σύντομη αλλά ουσιαστική εισαγωγή. Η Lenker χρησιμοποιεί το rock ’n’ roll όχι ως επιφανειακή διασκέδαση αλλά ως πράξη επιβίωσης και έκφρασης: όταν ο κόσμος είναι δύσκολος, η απάντηση είναι να παίξεις και να τραγουδήσεις. Η μπάντα ακούγεται ζωντανή και τραχιά, προετοιμάζοντας τον γήινο χαρακτήρα του δίσκου.</t>
+  </si>
+  <si>
+    <t>Από τα πιο ανθρώπινα τραγούδια των Big Thief. Παρατηρεί ανθρώπους του δρόμου και ζητά να τους δούμε όχι ως κοινωνικό τοπίο, αλλά ως πρόσωπα με ιστορία και αξιοπρέπεια. Η σύνθεση διατηρεί μια folk-rock απλότητα, όμως η φωνή της Lenker μετατρέπει την παρατήρηση σε σχεδόν πνευματική έκκληση για συμπόνια.</t>
+  </si>
+  <si>
+    <t>Σκοτεινό, προσωπικό και γεμάτο αμφίσημες εικόνες. Ο τίτλος “το παιχνίδι” δεν λειτουργεί ως αθώα παιδική αναφορά· υπονοεί έλεγχο, αντικειμενοποίηση ή μια ασταθή σχέση ανάμεσα σε δύο ανθρώπους. Οι κιθάρες και οι παύσεις δημιουργούν κλειστοφοβική ένταση, χωρίς το κομμάτι να χρειάζεται μεγάλη κλιμάκωση.</t>
+  </si>
+  <si>
+    <t>Το title track μιλά για επαφή, δημιουργία και για την αδυναμία να χωρέσει όλη η εμπειρία μέσα σε δύο ανθρώπινα χέρια. Η αργή ανάπτυξη και οι κιθάρες δημιουργούν ανοιχτό χώρο, ενώ η φωνή της Lenker παραμένει τρυφερή αλλά διεκδικητική. Είναι κομμάτι που δεν εκρήγνυται, αλλά συσσωρεύει συναίσθημα.</t>
+  </si>
+  <si>
+    <t>Τραγούδι σχέσεων και παρατήρησης, όπου οι άνθρωποι δεν περιγράφονται με καθαρούς ηθικούς ρόλους. Η μπάντα διατηρεί ακατέργαστη folk-rock κίνηση, ενώ τα φωνητικά και οι κιθάρες δίνουν στο τραγούδι μια αίσθηση μικρής, ιδιωτικής εξομολόγησης.</t>
+  </si>
+  <si>
+    <t>Χτίζεται πάνω σε αυξανόμενη ένταση. Οι ώμοι του τίτλου συμβολίζουν το βάρος που κουβαλά ένας άνθρωπος και την ανάγκη να στηριχθεί σε κάποιον άλλο. Το παίξιμο είναι πιο αιχμηρό, τα drums πιο επιθετικά και η φωνή της Lenker πλησιάζει τη στιγμή που δεν μπορεί πλέον να κρατηθεί ήσυχη.</t>
+  </si>
+  <si>
+    <t>Η κορυφαία στιγμή του άλμπουμ και μία από τις μεγάλες indie-rock κορυφές της δεκαετίας. Ξεκινά από επαναληπτική, almost mantra φράση, "not the energy, not the power…" και εξελίσσεται σε έξι λεπτά ολοένα μεγαλύτερης απόρριψης της επιφάνειας, του ελέγχου και της ψεύτικης βεβαιότητας. Η τελική κιθαριστική έκρηξη της Lenker δεν είναι “solo” με συμβατική έννοια: είναι σωματική εκτόνωση, με παραμόρφωση, ανατροφοδότηση και αίσθηση ότι το τραγούδι διαλύεται εσωτερικά.</t>
+  </si>
+  <si>
+    <t>Ένα από τα πιο ατμοσφαιρικά και μυστηριώδη κομμάτια. Ο λύκος λειτουργεί ως εικόνα άγριας φύσης, φόβου, μητρικής προστασίας και ανθρώπινου ενστίκτου. Η ενορχήστρωση παραμένει γήινη αλλά αποκτά ψυχεδελικές αποχρώσεις· είναι σαν folk τραγούδι που έχει περάσει μέσα από σκοτεινό όνειρο.</t>
+  </si>
+  <si>
+    <t>Συν-γραμμένο με τον Buck Meek, είναι πιο θρυμματισμένο και ασυνήθιστο στη δομή του. Ο τίτλος υποδηλώνει αντικατάσταση, απώλεια ταυτότητας ή αντικατάσταση ανθρώπων και αναμνήσεων. Η σύνθεση αρνείται μια εύκολη μελωδική λύση, μεταφέροντας τον ακροατή μέσα από ασύνδετες εικόνες και μουσικές μετατοπίσεις.</t>
+  </si>
+  <si>
+    <t>Πολύ προσωπικός και τρυφερός επίλογος. Το κούρεμα λειτουργεί ως μικρή πράξη αλλαγής, φροντίδας ή ανανέωσης. Με μινιμαλιστική folk-rock προσέγγιση, το τραγούδι αφήνει τον δίσκο να κλείσει χωρίς θεαματική λύση: με μια ανθρώπινη χειρονομία που είναι ταυτόχρονα μικρή και σημαντική.</t>
   </si>
 </sst>
 </file>
@@ -7821,7 +7929,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -9977,6 +10085,36 @@
       </c>
       <c r="J67" s="11" t="s">
         <v>2211</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+      <c r="A68" s="6">
+        <v>25766467</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>2254</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>2245</v>
+      </c>
+      <c r="D68" s="6">
+        <v>2019</v>
+      </c>
+      <c r="E68" s="10"/>
+      <c r="F68" s="9" t="s">
+        <v>2257</v>
+      </c>
+      <c r="G68" s="7" t="s">
+        <v>2253</v>
+      </c>
+      <c r="H68" s="6" t="s">
+        <v>2252</v>
+      </c>
+      <c r="I68" s="11" t="s">
+        <v>2255</v>
+      </c>
+      <c r="J68" s="11" t="s">
+        <v>2256</v>
       </c>
     </row>
   </sheetData>
@@ -10111,6 +10249,8 @@
     <hyperlink ref="J66" r:id="rId128" xr:uid="{48B641A4-17C1-4191-8CED-5E5659D92591}"/>
     <hyperlink ref="I67" r:id="rId129" xr:uid="{BF0EC9E5-8719-4153-9E86-32829F330A56}"/>
     <hyperlink ref="J67" r:id="rId130" xr:uid="{82F38111-DBC6-4CEB-AC91-8779B5919A35}"/>
+    <hyperlink ref="I68" r:id="rId131" xr:uid="{1D827E8B-5090-4D3B-8D5D-D405D16061B2}"/>
+    <hyperlink ref="J68" r:id="rId132" xr:uid="{01F1AB04-96C0-4051-9DE9-1884E1425122}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10118,7 +10258,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I624"/>
+  <dimension ref="A1:I634"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -27079,6 +27219,276 @@
       </c>
       <c r="I624" s="6"/>
     </row>
+    <row r="625" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A625" s="6">
+        <v>25766467</v>
+      </c>
+      <c r="B625" s="6">
+        <v>1</v>
+      </c>
+      <c r="C625" s="22" t="s">
+        <v>2242</v>
+      </c>
+      <c r="D625" s="7" t="s">
+        <v>2258</v>
+      </c>
+      <c r="E625" s="20">
+        <v>3.64</v>
+      </c>
+      <c r="F625" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G625" s="12">
+        <v>4.75</v>
+      </c>
+      <c r="H625" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="I625" s="6"/>
+    </row>
+    <row r="626" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A626" s="6">
+        <v>25766467</v>
+      </c>
+      <c r="B626" s="6">
+        <v>2</v>
+      </c>
+      <c r="C626" s="22" t="s">
+        <v>2243</v>
+      </c>
+      <c r="D626" s="7" t="s">
+        <v>2259</v>
+      </c>
+      <c r="E626" s="20">
+        <v>4.16</v>
+      </c>
+      <c r="F626" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G626" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H626" s="7" t="s">
+        <v>2269</v>
+      </c>
+      <c r="I626" s="6"/>
+    </row>
+    <row r="627" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A627" s="6">
+        <v>25766467</v>
+      </c>
+      <c r="B627" s="6">
+        <v>3</v>
+      </c>
+      <c r="C627" s="22" t="s">
+        <v>2244</v>
+      </c>
+      <c r="D627" s="7" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E627" s="20">
+        <v>3.75</v>
+      </c>
+      <c r="F627" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G627" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H627" s="7" t="s">
+        <v>2270</v>
+      </c>
+      <c r="I627" s="6"/>
+    </row>
+    <row r="628" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A628" s="6">
+        <v>25766467</v>
+      </c>
+      <c r="B628" s="6">
+        <v>4</v>
+      </c>
+      <c r="C628" s="22" t="s">
+        <v>2245</v>
+      </c>
+      <c r="D628" s="7" t="s">
+        <v>2261</v>
+      </c>
+      <c r="E628" s="20">
+        <v>3.99</v>
+      </c>
+      <c r="F628" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G628" s="12">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="H628" s="7" t="s">
+        <v>2271</v>
+      </c>
+      <c r="I628" s="6"/>
+    </row>
+    <row r="629" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A629" s="6">
+        <v>25766467</v>
+      </c>
+      <c r="B629" s="6">
+        <v>5</v>
+      </c>
+      <c r="C629" s="22" t="s">
+        <v>2246</v>
+      </c>
+      <c r="D629" s="7" t="s">
+        <v>2262</v>
+      </c>
+      <c r="E629" s="20">
+        <v>3.56</v>
+      </c>
+      <c r="F629" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G629" s="12">
+        <v>4.75</v>
+      </c>
+      <c r="H629" s="7" t="s">
+        <v>2272</v>
+      </c>
+      <c r="I629" s="6"/>
+    </row>
+    <row r="630" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A630" s="6">
+        <v>25766467</v>
+      </c>
+      <c r="B630" s="6">
+        <v>6</v>
+      </c>
+      <c r="C630" s="22" t="s">
+        <v>2247</v>
+      </c>
+      <c r="D630" s="7" t="s">
+        <v>2263</v>
+      </c>
+      <c r="E630" s="20">
+        <v>4.01</v>
+      </c>
+      <c r="F630" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G630" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H630" s="7" t="s">
+        <v>2273</v>
+      </c>
+      <c r="I630" s="6"/>
+    </row>
+    <row r="631" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A631" s="6">
+        <v>25766467</v>
+      </c>
+      <c r="B631" s="6">
+        <v>7</v>
+      </c>
+      <c r="C631" s="22" t="s">
+        <v>2248</v>
+      </c>
+      <c r="D631" s="7" t="s">
+        <v>2264</v>
+      </c>
+      <c r="E631" s="20">
+        <v>4.53</v>
+      </c>
+      <c r="F631" s="12">
+        <v>5</v>
+      </c>
+      <c r="G631" s="12">
+        <v>4.95</v>
+      </c>
+      <c r="H631" s="7" t="s">
+        <v>2274</v>
+      </c>
+      <c r="I631" s="6"/>
+    </row>
+    <row r="632" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A632" s="6">
+        <v>25766467</v>
+      </c>
+      <c r="B632" s="6">
+        <v>8</v>
+      </c>
+      <c r="C632" s="22" t="s">
+        <v>2249</v>
+      </c>
+      <c r="D632" s="7" t="s">
+        <v>2265</v>
+      </c>
+      <c r="E632" s="20">
+        <v>3.74</v>
+      </c>
+      <c r="F632" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G632" s="12">
+        <v>4.75</v>
+      </c>
+      <c r="H632" s="7" t="s">
+        <v>2275</v>
+      </c>
+      <c r="I632" s="6"/>
+    </row>
+    <row r="633" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A633" s="6">
+        <v>25766467</v>
+      </c>
+      <c r="B633" s="6">
+        <v>9</v>
+      </c>
+      <c r="C633" s="22" t="s">
+        <v>2250</v>
+      </c>
+      <c r="D633" s="7" t="s">
+        <v>2266</v>
+      </c>
+      <c r="E633" s="20">
+        <v>3.66</v>
+      </c>
+      <c r="F633" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G633" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H633" s="7" t="s">
+        <v>2276</v>
+      </c>
+      <c r="I633" s="6"/>
+    </row>
+    <row r="634" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A634" s="6">
+        <v>25766467</v>
+      </c>
+      <c r="B634" s="6">
+        <v>10</v>
+      </c>
+      <c r="C634" s="22" t="s">
+        <v>2251</v>
+      </c>
+      <c r="D634" s="7" t="s">
+        <v>2267</v>
+      </c>
+      <c r="E634" s="20">
+        <v>3.48</v>
+      </c>
+      <c r="F634" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G634" s="12">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="H634" s="7" t="s">
+        <v>2277</v>
+      </c>
+      <c r="I634" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6303C191-CB1D-4D2E-A3C5-807908C294CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8791C576-7F8E-40A9-8E62-98B5B337CCCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2478" uniqueCount="2278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2555" uniqueCount="2339">
   <si>
     <t>No</t>
   </si>
@@ -7408,6 +7408,189 @@
   </si>
   <si>
     <t>Πολύ προσωπικός και τρυφερός επίλογος. Το κούρεμα λειτουργεί ως μικρή πράξη αλλαγής, φροντίδας ή ανανέωσης. Με μινιμαλιστική folk-rock προσέγγιση, το τραγούδι αφήνει τον δίσκο να κλείσει χωρίς θεαματική λύση: με μια ανθρώπινη χειρονομία που είναι ταυτόχρονα μικρή και σημαντική.</t>
+  </si>
+  <si>
+    <t>Never Turn Your Back On A Friend</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/18001219-Budgie-Never-Turn-Your-Back-On-A-Friend</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/4J-ZfwRN8kyj73vzYPnYQx4s-DfkOlrtXcjooBw8c0o/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTg0NDIw/MC0xNzU1MjUyODgx/LTIxMzAuanBlZw.jpeg</t>
+  </si>
+  <si>
+    <t>Orange (6) – 70012, France, 2020 (Unofficial Release, Gatefold)</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Released in a gatefold sleeve featuring artwork designed by Roger Dean. Unofficial release / bootleg according to Budgie's management, with copyright notes referencing Orange (Vatel Music Inc., Orange, 84100 France). Includes the classic 1973 tracklist featuring the bonus live track on Side B.</t>
+  </si>
+  <si>
+    <t>Breadfan</t>
+  </si>
+  <si>
+    <t>Baby, Please Don’t Go</t>
+  </si>
+  <si>
+    <t>You Know I’ll Always Love You</t>
+  </si>
+  <si>
+    <t>You’re the Biggest Thing Since Powdered Milk</t>
+  </si>
+  <si>
+    <t>In the Grip of a Tyrefitter’s Hand</t>
+  </si>
+  <si>
+    <t>Riding My Nightmare</t>
+  </si>
+  <si>
+    <t>Parents</t>
+  </si>
+  <si>
+    <t>Το απόλυτο Budgie riff. Η κιθάρα του Bourge ανοίγει με κοφτή, νευρική και εξαιρετικά βαριά φιγούρα, η οποία προαναγγέλλει στοιχεία του speed και του thrash metal. Η αλλαγή σε πιο ήρεμο, μελωδικό middle section είναι καθοριστική: οι Budgie δεν επαναλαμβάνουν απλώς ένα riff, αλλά μετατρέπουν το τραγούδι σε μικρή heavy-rock δραματουργία. Οι Metallica το διασκεύασαν το 1987, κάτι που επιβεβαιώνει την επιρροή του στο metal, αλλά το πρωτότυπο παραμένει πιο ιδιόρρυθμο, νευρικό και απρόβλεπτο. 1056</t>
+  </si>
+  <si>
+    <t>Η διασκευή του Big Joe Williams κρατά τη blues/R&amp;B ρίζα αλλά την ηλεκτρίζει. Το κομμάτι μετατρέπεται σε heavy boogie, με τον Bourge να χρησιμοποιεί βρώμικη κιθάρα και τον Shelley να τραγουδά με μεγαλύτερη ένταση από μια παραδοσιακή blues ερμηνεία. Λειτουργεί ως γείωση του δίσκου στις μουσικές καταβολές του, πριν επιστρέψει στις πιο παράξενες και φιλόδοξες συνθέσεις.</t>
+  </si>
+  <si>
+    <t>Σύντομο και εκπληκτικά μελωδικό τραγούδι. Κάτω από το heavy-rock πλαίσιο υπάρχει μια σχεδόν power-pop ευαισθησία. Η σχέση παρουσιάζεται με άμεση, αφοσιωμένη γλώσσα, ενώ η κιθάρα και τα φωνητικά δίνουν μια φωτεινή ανάσα ανάμεσα στα πιο βαρύγδουπα tracks.</t>
+  </si>
+  <si>
+    <t>Ένα από τα βαρύτερα riffs του άλμπουμ και πιθανότατα η πιο άμεση γέφυρα με το μελλοντικό stoner metal. Η επαναληπτική κιθαριστική φιγούρα έχει βάρος, χαμηλό κέντρο και απειλητικό groove, ενώ ο τίτλος δίνει μια παράξενη, καθημερινή βρετανική εικόνα εξουσίας ή παγίδευσης. Η μπάντα διατηρεί τον ρυθμό αργό και σκληρό, αφήνοντας το riff να λειτουργήσει σαν μηχανή.</t>
+  </si>
+  <si>
+    <t>Το δεκάλεπτο κλείσιμο είναι η πιο δραματική και θεματικά σύνθετη στιγμή του δίσκου. Ξεκινά με την εμπειρία ενός νέου ανθρώπου που ασφυκτιά κάτω από οικογενειακή και κοινωνική εξουσία, ενώ εξελίσσεται σε heavy-rock suite με αλλαγές έντασης και παρατεταμένα κιθαριστικά περάσματα. Οι Budgie δεν προτείνουν μια απλή επανάσταση· δείχνουν τον φαύλο κύκλο όπου η νέα γενιά αντιδρά στους γονείς της και αργότερα μπορεί να αναπαράγει τις ίδιες πιέσεις. Η αρχική βινυλιακή κόπια περιλαμβάνει intro με καμπάνες του Big Ben και απόσπασμα από την ομιλία του Winston Churchill στη Βουλή των Κοινοτήτων το 1940. Αυτό αφαιρέθηκε από μεταγενέστερα pressings λόγω νομικών ζητημάτων και δεν παρέμεινε στις CD επανεκδόσεις.</t>
+  </si>
+  <si>
+    <t>Σύντομο, σκοτεινό και πιο ψυχεδελικό interlude. Η εικόνα του «καβαλάω τον εφιάλτη μου» δηλώνει ότι ο αφηγητής δεν προσπαθεί να ξεφύγει από τον φόβο· βρίσκεται ήδη μέσα σε αυτόν. Το τραγούδι έχει απειλητική ατμόσφαιρα και λειτουργεί σαν μετάβαση προς το μεγάλο φινάλε.</t>
+  </si>
+  <si>
+    <t>Η πιο αλλόκοτη, progressive και ενορχηστρωτικά φιλόδοξη σύνθεση της πρώτης πλευράς. Ο σατιρικός τίτλος συνοδεύεται από αλλαγές ρυθμού, βαριά riff sections, πιο ατμοσφαιρικά περάσματα και κιθαριστική εξερεύνηση. Είναι ένα κλασικό δείγμα του τρόπου με τον οποίο οι Budgie μπορούν να μετατρέψουν μία απλή blues-rock βάση σε heavy-rock suite.</t>
+  </si>
+  <si>
+    <t>Hard Rock, Proto-Metal [Heavy Blues, Progressive Hard Rock, Early Heavy Metal]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Proto-Metal [Heavy Riff Rock, Speed Metal Prototype, British Heavy Rock]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Hard Rock [Heavy Blues, R&amp;B Cover, Boogie Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Power Pop [Heavy Rock Ballad, Melodic Proto-Metal]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Progressive Rock [Heavy Prog, Riff Suite, Psychedelic Hard Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Proto-Metal [Heavy Riff Rock, Stoner-Rock Prototype, Blues Metal]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Psychedelic Rock [Dark Heavy Rock, Proto-Metal, Nightmarish Rock]</t>
+  </si>
+  <si>
+    <t>Progressive Hard Rock, Hard Rock [Epic Hard-Rock Suite, Proto-Metal, Social Commentary]</t>
+  </si>
+  <si>
+    <t>Vertigo – 6366 116, Vertigo – 6641 335, Greece, 1976 (First Greek Pressing, Compilation, Single LP edition tailored for the Greek market)</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:**  1st original pressing with the characteristic 1976 Vertigo Greek market labels. Rim text has two lines (Greek &amp; English), BIEM is placed elsewhere and has 'Made in Greece' printed over it. Printed on front cover (boxed): "Greatest Hits", Incl.: Black Sabbath, Paranoid, Sabbath Bloody Sabbath, 6641 335. Printed by Αδελφοί Ν. Πιτσιλού Ο.Ε.</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/15223559-Black-Sabbath-We-Sold-Our-Soul-For-Rock-N-Roll?redirected=true</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/b3QtdUkmaSGKfvt65XhC-zDdVN3ulHReJrmGvRgS1qU/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTE1MjIz/NTU5LTE1ODgzMzMz/MDUtMzAwMS5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>The Wizard</t>
+  </si>
+  <si>
+    <t>Paranoid</t>
+  </si>
+  <si>
+    <t>War Pigs</t>
+  </si>
+  <si>
+    <t>Iron Man</t>
+  </si>
+  <si>
+    <t>Fairies Wear Boots</t>
+  </si>
+  <si>
+    <t>Children of the Grave</t>
+  </si>
+  <si>
+    <t>Sabbath Bloody Sabbath</t>
+  </si>
+  <si>
+    <t>Am I Going Insane</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Doom Metal, Proto-Metal, Heavy Blues]</t>
+  </si>
+  <si>
+    <t>We Sold Our Soul For Rock 'N' Roll</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Doom Metal [Doom Blues, Proto-Metal, Occult Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Blues Rock [Heavy Blues, Harmonica Rock, Proto-Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Proto-Speed Metal, Heavy Rock, Anthemic Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Doom Metal [Anti-War Metal, Heavy Blues, Progressive Metal Prototype]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Doom Metal [Riff Metal, Proto-Metal, Sci-Fi Doom]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Blues Rock [Heavy Groove, Psychedelic Metal, Riff Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Stoner Rock [Cannabis Doom, Heavy Riff Rock, Proto-Stoner]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Doom Metal [Anti-War Doom, Proto-Thrash, Heavy Riff Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Progressive Rock [Progressive Metal, Doom Metal, Complex Riff Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Progressive Rock [Psychedelic Pop, Keyboard Rock, Dark Art Rock]</t>
+  </si>
+  <si>
+    <t>Η αρχή όλων. Βροχή, καμπάνες, ένα τριτόνιο και μια αργή, απειλητική κίνηση. Οι στίχοι παρουσιάζουν μια υπερφυσική παρουσία που δεν εξηγείται ούτε νικιέται. Το τραγούδι ορίζει τη βασική γλώσσα του doom metal, αργό tempo, δυσαρμονία, κενός χώρος και τρόμος αντί για απλή ένταση.</t>
+  </si>
+  <si>
+    <t>Το harmonica του Ozzy φέρνει την μπάντα πίσω στο blues, αλλά το riff του Iommi και το ευκίνητο μπάσο του Butler δεν επιτρέπουν στο κομμάτι να γίνει συμβατικό blues rock. Ο “μάγος” μοιάζει με περιπλανώμενη, μυθική φιγούρα που προσφέρει γνώση ή απελευθέρωση, ενώ η μπάντα μετατρέπει το θέμα σε γρήγορο, βρώμικο heavy groove.</t>
+  </si>
+  <si>
+    <t>Γραμμένο ως σύντομο filler αλλά εξελίχθηκε στο πιο αναγνωρίσιμο Sabbath hit. Η γρήγορη, σχεδόν punk πριν το punk, κίνηση και η μελωδία του riff δίνουν στο τραγούδι αμεσότητα, ενώ οι στίχοι μετατρέπουν την ερωτική απογοήτευση σε ψυχικό εγκλωβισμό. Είναι ένα proto-speed-metal τραγούδι που διατηρεί blues swing.</t>
+  </si>
+  <si>
+    <t>Η αντιπολεμική κορυφή του καταλόγου τους. Οι “war pigs” δεν είναι οι στρατιώτες αλλά οι ηγέτες που στέλνουν άλλους να πεθάνουν. Η σύνθεση εναλλάσσει αργό, τελετουργικό riffing με γρήγορο outro, ενώ τα drums του Ward δίνουν στα μέρη αυτά νευρική, σχεδόν jazz-rock ένταση. Η πολιτική της ισχύς δεν εξαρτάται από συγκεκριμένο πόλεμο.</t>
+  </si>
+  <si>
+    <t>Το ρομποτικό, υποβλητικό intro οδηγεί σε ένα από τα πιο αναγνωρίσιμα metal riffs. Η ιστορία του χαρακτήρα που ταξιδεύει στο μέλλον, βλέπει καταστροφή και τελικά γίνεται αυτό που προσπαθούσε να αποτρέψει, δίνει στο κομμάτι sci-fi τραγικότητα. Το riff είναι βαρύ αλλά και εξαιρετικά απλό, ιδανικό παράδειγμα του πώς η οικονομία μετατρέπεται σε μύθο.</t>
+  </si>
+  <si>
+    <t>Υποτιθέμενα εμπνευσμένο από skinheads και LSD εμπειρίες, είναι ένα από τα πιο groove-heavy κομμάτια της μπάντας. Το intro εξελίσσεται σε swinging riff, με τον Butler και τον Ward να δίνουν ασυνήθιστη ρευστότητα. Οι σουρεαλιστικοί στίχοι δεν χρειάζονται κυριολεκτική αποκωδικοποίηση· υπηρετούν τη μεθυστική αίσθηση του κομματιού.</t>
+  </si>
+  <si>
+    <t>Σκοτεινό αντιπολεμικό σύνθημα με relentless riff. Σε σχέση με το αργό doom των “War Pigs” και “Black Sabbath”, έχει περισσότερη προωθητική δύναμη και θα μπορούσε να διαβαστεί ως πρώιμη βάση για thrash/doom crossover. Η μπάντα συνδυάζει βαρύτητα με κινητικότητα, κρατώντας το τραγούδι απειλητικό αλλά και επιθετικό.</t>
+  </si>
+  <si>
+    <t>Βήχας, χτύπημα κιθάρας και ένα riff που θεμελιώνει το proto-stoner rock. Το τραγούδι είναι ωδή στην κάνναβη, χωρίς μεταφορικές άμυνες, αλλά ο ρυθμός και το riff το κάνουν κάτι μεγαλύτερο από novelty, είναι σωματικό, ζεστό και σχεδόν υπνωτικό heavy rock.</t>
+  </si>
+  <si>
+    <t>Ένα από τα πιο σύνθετα riffs του Iommi και σημαντικό βήμα προς progressive metal. Με αλλαγές θέματος, απρόσμενες αρμονίες και λεπτομερή ενορχήστρωση, το τραγούδι αποτυπώνει μια μπάντα που προσπαθεί να επιβιώσει από την πίεση της ίδιας της επιτυχίας της. Το refrain έχει ιδιαίτερη δραματική ένταση: επίθεση, κατάρρευση και επιστροφή μαζί.</t>
+  </si>
+  <si>
+    <t>Παράξενο, πλήκτρο-driven κομμάτι με ψυχεδελικό pop χαρακτήρα. Δεν έχει την κλασική Sabbath βαρύτητα, αλλά η ελαφρώς χαλασμένη, ανήσυχη ατμόσφαιρα και η ερμηνεία του Ozzy κάνουν τον τίτλο να ακούγεται σαν πραγματική αποσταθεροποίηση.</t>
   </si>
 </sst>
 </file>
@@ -7929,7 +8112,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -10100,7 +10283,9 @@
       <c r="D68" s="6">
         <v>2019</v>
       </c>
-      <c r="E68" s="10"/>
+      <c r="E68" s="10">
+        <v>3.6</v>
+      </c>
       <c r="F68" s="9" t="s">
         <v>2257</v>
       </c>
@@ -10115,6 +10300,70 @@
       </c>
       <c r="J68" s="11" t="s">
         <v>2256</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+      <c r="A69" s="6">
+        <v>18001219</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>2278</v>
+      </c>
+      <c r="D69" s="6">
+        <v>1973</v>
+      </c>
+      <c r="E69" s="10">
+        <v>3.82</v>
+      </c>
+      <c r="F69" s="9" t="s">
+        <v>2297</v>
+      </c>
+      <c r="G69" s="7" t="s">
+        <v>2282</v>
+      </c>
+      <c r="H69" s="6" t="s">
+        <v>2281</v>
+      </c>
+      <c r="I69" s="11" t="s">
+        <v>2279</v>
+      </c>
+      <c r="J69" s="11" t="s">
+        <v>2280</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A70" s="6">
+        <v>15223559</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>2318</v>
+      </c>
+      <c r="D70" s="6">
+        <v>1976</v>
+      </c>
+      <c r="E70" s="10">
+        <v>4.21</v>
+      </c>
+      <c r="F70" s="9" t="s">
+        <v>2317</v>
+      </c>
+      <c r="G70" s="7" t="s">
+        <v>2306</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>2305</v>
+      </c>
+      <c r="I70" s="11" t="s">
+        <v>2307</v>
+      </c>
+      <c r="J70" s="11" t="s">
+        <v>2308</v>
       </c>
     </row>
   </sheetData>
@@ -10251,6 +10500,10 @@
     <hyperlink ref="J67" r:id="rId130" xr:uid="{82F38111-DBC6-4CEB-AC91-8779B5919A35}"/>
     <hyperlink ref="I68" r:id="rId131" xr:uid="{1D827E8B-5090-4D3B-8D5D-D405D16061B2}"/>
     <hyperlink ref="J68" r:id="rId132" xr:uid="{01F1AB04-96C0-4051-9DE9-1884E1425122}"/>
+    <hyperlink ref="I69" r:id="rId133" xr:uid="{1890E57B-E8F7-4840-9572-DFEA56597C1F}"/>
+    <hyperlink ref="J69" r:id="rId134" xr:uid="{67050336-EA4B-4356-8517-166EC5C5D269}"/>
+    <hyperlink ref="I70" r:id="rId135" xr:uid="{AFDCBC25-6599-4F55-99D2-8913687FB136}"/>
+    <hyperlink ref="J70" r:id="rId136" xr:uid="{411646F0-69D3-4EDF-9126-2F65597A7EFA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10258,7 +10511,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I634"/>
+  <dimension ref="A1:I651"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -27489,6 +27742,489 @@
       </c>
       <c r="I634" s="6"/>
     </row>
+    <row r="635" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A635" s="6">
+        <v>18001219</v>
+      </c>
+      <c r="B635" s="6">
+        <v>1</v>
+      </c>
+      <c r="C635" s="22" t="s">
+        <v>2283</v>
+      </c>
+      <c r="D635" s="7" t="s">
+        <v>2298</v>
+      </c>
+      <c r="E635" s="20">
+        <v>4.34</v>
+      </c>
+      <c r="F635" s="12">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G635" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H635" s="7" t="s">
+        <v>2290</v>
+      </c>
+      <c r="I635" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="636" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A636" s="6">
+        <v>18001219</v>
+      </c>
+      <c r="B636" s="6">
+        <v>2</v>
+      </c>
+      <c r="C636" s="22" t="s">
+        <v>2284</v>
+      </c>
+      <c r="D636" s="7" t="s">
+        <v>2299</v>
+      </c>
+      <c r="E636" s="20">
+        <v>3.76</v>
+      </c>
+      <c r="F636" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G636" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H636" s="7" t="s">
+        <v>2291</v>
+      </c>
+      <c r="I636" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="637" spans="1:9" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A637" s="6">
+        <v>18001219</v>
+      </c>
+      <c r="B637" s="6">
+        <v>3</v>
+      </c>
+      <c r="C637" s="22" t="s">
+        <v>2285</v>
+      </c>
+      <c r="D637" s="7" t="s">
+        <v>2300</v>
+      </c>
+      <c r="E637" s="20">
+        <v>3.53</v>
+      </c>
+      <c r="F637" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G637" s="12">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="H637" s="7" t="s">
+        <v>2292</v>
+      </c>
+      <c r="I637" s="6"/>
+    </row>
+    <row r="638" spans="1:9" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A638" s="6">
+        <v>18001219</v>
+      </c>
+      <c r="B638" s="6">
+        <v>4</v>
+      </c>
+      <c r="C638" s="22" t="s">
+        <v>2286</v>
+      </c>
+      <c r="D638" s="7" t="s">
+        <v>2301</v>
+      </c>
+      <c r="E638" s="20">
+        <v>3.85</v>
+      </c>
+      <c r="F638" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="G638" s="12">
+        <v>4.75</v>
+      </c>
+      <c r="H638" s="7" t="s">
+        <v>2296</v>
+      </c>
+      <c r="I638" s="6"/>
+    </row>
+    <row r="639" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A639" s="6">
+        <v>18001219</v>
+      </c>
+      <c r="B639" s="6">
+        <v>5</v>
+      </c>
+      <c r="C639" s="22" t="s">
+        <v>2287</v>
+      </c>
+      <c r="D639" s="7" t="s">
+        <v>2302</v>
+      </c>
+      <c r="E639" s="20">
+        <v>3.86</v>
+      </c>
+      <c r="F639" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="G639" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H639" s="7" t="s">
+        <v>2293</v>
+      </c>
+      <c r="I639" s="6"/>
+    </row>
+    <row r="640" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A640" s="6">
+        <v>18001219</v>
+      </c>
+      <c r="B640" s="6">
+        <v>6</v>
+      </c>
+      <c r="C640" s="22" t="s">
+        <v>2288</v>
+      </c>
+      <c r="D640" s="7" t="s">
+        <v>2303</v>
+      </c>
+      <c r="E640" s="20">
+        <v>3.36</v>
+      </c>
+      <c r="F640" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G640" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H640" s="7" t="s">
+        <v>2295</v>
+      </c>
+      <c r="I640" s="6"/>
+    </row>
+    <row r="641" spans="1:9" ht="96.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A641" s="6">
+        <v>18001219</v>
+      </c>
+      <c r="B641" s="6">
+        <v>7</v>
+      </c>
+      <c r="C641" s="22" t="s">
+        <v>2289</v>
+      </c>
+      <c r="D641" s="7" t="s">
+        <v>2304</v>
+      </c>
+      <c r="E641" s="20">
+        <v>4.18</v>
+      </c>
+      <c r="F641" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="G641" s="12">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H641" s="7" t="s">
+        <v>2294</v>
+      </c>
+      <c r="I641" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="642" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A642" s="6">
+        <v>15223559</v>
+      </c>
+      <c r="B642" s="6">
+        <v>1</v>
+      </c>
+      <c r="C642" s="22" t="s">
+        <v>311</v>
+      </c>
+      <c r="D642" s="7" t="s">
+        <v>2319</v>
+      </c>
+      <c r="E642" s="20">
+        <v>4.58</v>
+      </c>
+      <c r="F642" s="12">
+        <v>5</v>
+      </c>
+      <c r="G642" s="12">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="H642" s="7" t="s">
+        <v>2329</v>
+      </c>
+      <c r="I642" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="643" spans="1:9" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A643" s="6">
+        <v>15223559</v>
+      </c>
+      <c r="B643" s="6">
+        <v>2</v>
+      </c>
+      <c r="C643" s="22" t="s">
+        <v>2309</v>
+      </c>
+      <c r="D643" s="7" t="s">
+        <v>2320</v>
+      </c>
+      <c r="E643" s="20">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="F643" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G643" s="12">
+        <v>4.75</v>
+      </c>
+      <c r="H643" s="7" t="s">
+        <v>2330</v>
+      </c>
+      <c r="I643" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="644" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A644" s="6">
+        <v>15223559</v>
+      </c>
+      <c r="B644" s="6">
+        <v>3</v>
+      </c>
+      <c r="C644" s="22" t="s">
+        <v>2310</v>
+      </c>
+      <c r="D644" s="7" t="s">
+        <v>2321</v>
+      </c>
+      <c r="E644" s="20">
+        <v>4.59</v>
+      </c>
+      <c r="F644" s="12">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G644" s="12">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H644" s="7" t="s">
+        <v>2331</v>
+      </c>
+      <c r="I644" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="645" spans="1:9" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A645" s="6">
+        <v>15223559</v>
+      </c>
+      <c r="B645" s="6">
+        <v>4</v>
+      </c>
+      <c r="C645" s="22" t="s">
+        <v>2311</v>
+      </c>
+      <c r="D645" s="7" t="s">
+        <v>2322</v>
+      </c>
+      <c r="E645" s="20">
+        <v>4</v>
+      </c>
+      <c r="F645" s="12">
+        <v>5</v>
+      </c>
+      <c r="G645" s="12">
+        <v>4.95</v>
+      </c>
+      <c r="H645" s="7" t="s">
+        <v>2332</v>
+      </c>
+      <c r="I645" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="646" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A646" s="6">
+        <v>15223559</v>
+      </c>
+      <c r="B646" s="6">
+        <v>5</v>
+      </c>
+      <c r="C646" s="22" t="s">
+        <v>2312</v>
+      </c>
+      <c r="D646" s="7" t="s">
+        <v>2323</v>
+      </c>
+      <c r="E646" s="20">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="F646" s="12">
+        <v>5</v>
+      </c>
+      <c r="G646" s="12">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H646" s="7" t="s">
+        <v>2333</v>
+      </c>
+      <c r="I646" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="647" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A647" s="6">
+        <v>15223559</v>
+      </c>
+      <c r="B647" s="6">
+        <v>6</v>
+      </c>
+      <c r="C647" s="22" t="s">
+        <v>2313</v>
+      </c>
+      <c r="D647" s="7" t="s">
+        <v>2324</v>
+      </c>
+      <c r="E647" s="20">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="F647" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="G647" s="12">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="H647" s="7" t="s">
+        <v>2334</v>
+      </c>
+      <c r="I647" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="648" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A648" s="6">
+        <v>15223559</v>
+      </c>
+      <c r="B648" s="6">
+        <v>7</v>
+      </c>
+      <c r="C648" s="22" t="s">
+        <v>318</v>
+      </c>
+      <c r="D648" s="7" t="s">
+        <v>2325</v>
+      </c>
+      <c r="E648" s="20">
+        <v>4.46</v>
+      </c>
+      <c r="F648" s="12">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G648" s="12">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H648" s="7" t="s">
+        <v>2336</v>
+      </c>
+      <c r="I648" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="649" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A649" s="6">
+        <v>15223559</v>
+      </c>
+      <c r="B649" s="6">
+        <v>8</v>
+      </c>
+      <c r="C649" s="22" t="s">
+        <v>2314</v>
+      </c>
+      <c r="D649" s="7" t="s">
+        <v>2326</v>
+      </c>
+      <c r="E649" s="20">
+        <v>4.57</v>
+      </c>
+      <c r="F649" s="12">
+        <v>5</v>
+      </c>
+      <c r="G649" s="12">
+        <v>4.95</v>
+      </c>
+      <c r="H649" s="7" t="s">
+        <v>2335</v>
+      </c>
+      <c r="I649" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="650" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A650" s="6">
+        <v>15223559</v>
+      </c>
+      <c r="B650" s="6">
+        <v>9</v>
+      </c>
+      <c r="C650" s="22" t="s">
+        <v>2315</v>
+      </c>
+      <c r="D650" s="7" t="s">
+        <v>2327</v>
+      </c>
+      <c r="E650" s="20">
+        <v>4.57</v>
+      </c>
+      <c r="F650" s="12">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G650" s="12">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="H650" s="7" t="s">
+        <v>2337</v>
+      </c>
+      <c r="I650" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="651" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A651" s="6">
+        <v>15223559</v>
+      </c>
+      <c r="B651" s="6">
+        <v>10</v>
+      </c>
+      <c r="C651" s="22" t="s">
+        <v>2316</v>
+      </c>
+      <c r="D651" s="7" t="s">
+        <v>2328</v>
+      </c>
+      <c r="E651" s="20">
+        <v>3.46</v>
+      </c>
+      <c r="F651" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G651" s="12">
+        <v>4.75</v>
+      </c>
+      <c r="H651" s="7" t="s">
+        <v>2338</v>
+      </c>
+      <c r="I651" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8791C576-7F8E-40A9-8E62-98B5B337CCCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D536D9B-1E00-468B-8557-EDBABFE9E3A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2555" uniqueCount="2339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2592" uniqueCount="2374">
   <si>
     <t>No</t>
   </si>
@@ -7591,6 +7591,171 @@
   </si>
   <si>
     <t>Παράξενο, πλήκτρο-driven κομμάτι με ψυχεδελικό pop χαρακτήρα. Δεν έχει την κλασική Sabbath βαρύτητα, αλλά η ελαφρώς χαλασμένη, ανήσυχη ατμόσφαιρα και η ερμηνεία του Ozzy κάνουν τον τίτλο να ακούγεται σαν πραγματική αποσταθεροποίηση.</t>
+  </si>
+  <si>
+    <t>Black Pumas</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/21826186-Black-Pumas-Black-Pumas</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/f1zqGfUT2Q1teuJRJ6S4RcohsgEcDnK_nOTRQuK3JpQ/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTIxODI2/MTg2LTE2NDI3NzY0/NTgtNDEyNy5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>ATO Records – ATO0500LPC, ATO Records – ATO0500LP, Europe, 2019 (Optimal Media European Pressing with "KR" lacquer cut)</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:**  European black vinyl pressing. Lacquer cut by "KR" at Optimal Media. Includes download code on a sticker on the inner sleeve. Features the silver hype sticker on the shrink wrap and [PIAS] logo on the lower right of the rear sleeve.</t>
+  </si>
+  <si>
+    <t>Black Moon Rising</t>
+  </si>
+  <si>
+    <t>Colors</t>
+  </si>
+  <si>
+    <t>Know You Better</t>
+  </si>
+  <si>
+    <t>OCT 33</t>
+  </si>
+  <si>
+    <t>Stay Gold</t>
+  </si>
+  <si>
+    <t>Old Man</t>
+  </si>
+  <si>
+    <t>Confines</t>
+  </si>
+  <si>
+    <t>Touch the Sky</t>
+  </si>
+  <si>
+    <t>Sweet Conversations</t>
+  </si>
+  <si>
+    <t>Psychedelic Soul, Neo-Soul [Funk Rock, Retro Soul, Gospel Soul]</t>
+  </si>
+  <si>
+    <t>Psychedelic Soul, Funk Rock [Fuzz Soul, Garage Funk, Soul Rock]</t>
+  </si>
+  <si>
+    <t>Neo-Soul, Psychedelic Soul [Gospel Soul, Soul Ballad, Alternative R&amp;B]</t>
+  </si>
+  <si>
+    <t>Soul Rock, Funk [Psychedelic Funk, Up-tempo Soul, Retro R&amp;B]</t>
+  </si>
+  <si>
+    <t>Psychedelic Soul, Rock [Soul Rock, Fuzz Rock, Garage Soul]</t>
+  </si>
+  <si>
+    <t>Neo-Soul, Psychedelic Rock [Dream Soul, Psychedelic Ballad, Atmospheric R&amp;B]</t>
+  </si>
+  <si>
+    <t>Soul, Folk Rock [Acoustic Soul, Gospel Folk, Reflective Ballad]</t>
+  </si>
+  <si>
+    <t>Soul Rock, Blues Rock [Slow Groove, Southern Soul, Psychedelic Blues]</t>
+  </si>
+  <si>
+    <t>Neo-Soul, Psychedelic Soul [Dark Soul, Atmospheric R&amp;B, Art Soul]</t>
+  </si>
+  <si>
+    <t>Psychedelic Soul, Funk [Upbeat Soul, Funk Pop, Gospel-tinged R&amp;B]</t>
+  </si>
+  <si>
+    <t>Soul, Pop [Retro Soul, Soft Funk, Warm Soul Pop]</t>
+  </si>
+  <si>
+    <t>Το πιο άμεσο statement του δίσκου. Fuzz κιθάρες, βαρύ bass groove και η φωνή του Burton που ανεβαίνει με ένταση δημιουργούν psychedelic soul-rock με πραγματική απειλή. Ο «μαύρος ανερχόμενος φεγγάρι» λειτουργεί σαν εικόνα μιας σκοτεινής δύναμης, ερωτικής, ψυχικής ή κοινωνικής— που πλησιάζει. Το κομμάτι είχε αρχικά εμφανιστεί ως 7-inch single το 2018 μέσω Karma Chief, sub-label της Colemine Records.</t>
+  </si>
+  <si>
+    <t>Η κορυφαία σύνθεση του άλμπουμ. Ξεκινά ως ευάλωτη soul μπαλάντα και ανοίγει σταδιακά σε gospel-soul κορύφωση. Η φωνή του Burton κρατά την ένταση χωρίς να χάνει την τρυφερότητα, ενώ η παραγωγή αφήνει χώρο ώστε κάθε στροφή να αυξάνει το συναισθηματικό βάρος. Το τραγούδι λειτουργεί ως ύμνος για την ανθρώπινη πολυπλοκότητα, την ομορφιά της διαφορετικότητας και την άρνηση της απλοϊκής κατηγοριοποίησης.</t>
+  </si>
+  <si>
+    <t>Πιο ρυθμικό, με funk κίνηση και άμεση soul-pop δομή. Εξετάζει την απόσταση ανάμεσα στην επιθυμία να γνωρίσεις πραγματικά κάποιον και στη συνειδητοποίηση ότι η οικειότητα δεν κατακτιέται γρήγορα. Η κιθάρα και τα drums κρατούν το track ζωηρό, χωρίς να υποχωρεί η ψυχεδελική χροιά.</t>
+  </si>
+  <si>
+    <t>Γρήγορο, βρώμικο soul-rock με χαρακτήρα live set. Η φωτιά λειτουργεί ως εικόνα για έλξη, κίνδυνο και ανεξέλεγκτη αλλαγή. Το riff και η vocal ερμηνεία δίνουν στο κομμάτι garage-soul άμεση ενέργεια. Όπως και το “Black Moon Rising”, είχε εμφανιστεί αρχικά ως 7-inch single το 2018.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve">Στην inner sleeve της δικής σου έκδοσης αναγράφεται ως </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>“October 33”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>, ενώ στο label/tracklist εμφανίζεται ως “OCT 33”. Είναι ατμοσφαιρικό, ονειρικό και πιο εσωστρεφές: ένα psychedelic soul τοπίο όπου η παραγωγή αποκτά μεγάλη σημασία. Η ασυνήθιστη ημερομηνία του τίτλου υπονοεί χρόνο εκτός κανονικής πραγματικότητας —μια συναισθηματική στιγμή που δεν χωρά σε ημερολόγιο. 1113</t>
+    </r>
+  </si>
+  <si>
+    <t>Η πιο ακουστική και τρυφερή στιγμή του δίσκου. Ο τίτλος παραπέμπει στην προσπάθεια να διατηρήσεις ακεραιότητα, αθωότητα ή εσωτερικό φως μέσα σε συνθήκες που σε σκληραίνουν. Η ερμηνεία του Burton είναι συγκρατημένη, και η folk-soul ενορχήστρωση λειτουργεί σαν αναγκαία παύση μετά την πυκνότητα της πρώτης πλευράς.</t>
+  </si>
+  <si>
+    <t>Εσωτερικό και ατμοσφαιρικό τραγούδι για περιορισμούς —του εαυτού, μιας σχέσης ή κοινωνικής πραγματικότητας. Η σύνθεση δεν στηρίζεται σε μεγάλο riff, αλλά σε στρωματοποιημένα φωνητικά, space και αίσθηση ανησυχίας. Είναι από τα πιο art-soul κομμάτια του album.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve">Ζεστό, χαλαρό κλείσιμο με retro-soul και soft-funk χρώμα. Είναι το μόνο track της LP όπου η Discogs καταχώρηση αποδίδει συνθετική συμμετοχή και στον </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>J. Blue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>, μαζί με τον Burton. Μετά τις μεγάλες κορυφώσεις του album, το κομμάτι επιλέγει οικειότητα και ηρεμία αντί για θεαματικό φινάλε.</t>
+    </r>
+  </si>
+  <si>
+    <t>Επιστροφή σε πιο φωτεινή, gospel-tinged funk διάθεση. Η εικόνα της επαφής με τον ουρανό δεν προτείνει κυριολεκτική υπέρβαση· εκφράζει τη στιγμή όπου μια σχέση ή μια προσωπική απόφαση δίνει αίσθηση ελευθερίας. Η ενορχήστρωση είναι πιο ανοιχτή, με ρυθμό που λειτουργεί ιδανικά ως late-album lift.</t>
+  </si>
+  <si>
+    <t>Μεσαίου tempo, υπόγειο και σκοτεινότερο groove. Η μορφή του “old man” λειτουργεί σαν φωνή εμπειρίας, φθοράς ή προειδοποίησης. Η κιθάρα και το rhythm section κρατούν μια southern-soul/blues ένταση, ενώ η παραγωγή προσθέτει ψυχεδελικές σκιές.</t>
   </si>
 </sst>
 </file>
@@ -8112,7 +8277,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J71"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -10364,6 +10529,38 @@
       </c>
       <c r="J70" s="11" t="s">
         <v>2308</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+      <c r="A71" s="6">
+        <v>21826186</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>2339</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>2339</v>
+      </c>
+      <c r="D71" s="6">
+        <v>2019</v>
+      </c>
+      <c r="E71" s="10">
+        <v>3.46</v>
+      </c>
+      <c r="F71" s="9" t="s">
+        <v>2353</v>
+      </c>
+      <c r="G71" s="7" t="s">
+        <v>2343</v>
+      </c>
+      <c r="H71" s="6" t="s">
+        <v>2342</v>
+      </c>
+      <c r="I71" s="11" t="s">
+        <v>2340</v>
+      </c>
+      <c r="J71" s="11" t="s">
+        <v>2341</v>
       </c>
     </row>
   </sheetData>
@@ -10504,6 +10701,8 @@
     <hyperlink ref="J69" r:id="rId134" xr:uid="{67050336-EA4B-4356-8517-166EC5C5D269}"/>
     <hyperlink ref="I70" r:id="rId135" xr:uid="{AFDCBC25-6599-4F55-99D2-8913687FB136}"/>
     <hyperlink ref="J70" r:id="rId136" xr:uid="{411646F0-69D3-4EDF-9126-2F65597A7EFA}"/>
+    <hyperlink ref="I71" r:id="rId137" xr:uid="{5E8073D0-D198-4EF7-B401-0DAE1D13CFF4}"/>
+    <hyperlink ref="J71" r:id="rId138" xr:uid="{2B75F78E-758A-4053-AE75-07DCB5BE6D3E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10511,7 +10710,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I651"/>
+  <dimension ref="A1:I661"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -28225,6 +28424,276 @@
       </c>
       <c r="I651" s="6"/>
     </row>
+    <row r="652" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A652" s="6">
+        <v>21826186</v>
+      </c>
+      <c r="B652" s="6">
+        <v>1</v>
+      </c>
+      <c r="C652" s="22" t="s">
+        <v>2344</v>
+      </c>
+      <c r="D652" s="7" t="s">
+        <v>2354</v>
+      </c>
+      <c r="E652" s="20">
+        <v>3.73</v>
+      </c>
+      <c r="F652" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G652" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H652" s="7" t="s">
+        <v>2364</v>
+      </c>
+      <c r="I652" s="6"/>
+    </row>
+    <row r="653" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A653" s="6">
+        <v>21826186</v>
+      </c>
+      <c r="B653" s="6">
+        <v>2</v>
+      </c>
+      <c r="C653" s="22" t="s">
+        <v>2345</v>
+      </c>
+      <c r="D653" s="7" t="s">
+        <v>2355</v>
+      </c>
+      <c r="E653" s="20">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="F653" s="12">
+        <v>5</v>
+      </c>
+      <c r="G653" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H653" s="7" t="s">
+        <v>2365</v>
+      </c>
+      <c r="I653" s="6"/>
+    </row>
+    <row r="654" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A654" s="6">
+        <v>21826186</v>
+      </c>
+      <c r="B654" s="6">
+        <v>3</v>
+      </c>
+      <c r="C654" s="22" t="s">
+        <v>2346</v>
+      </c>
+      <c r="D654" s="7" t="s">
+        <v>2356</v>
+      </c>
+      <c r="E654" s="20">
+        <v>3.56</v>
+      </c>
+      <c r="F654" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G654" s="12">
+        <v>4</v>
+      </c>
+      <c r="H654" s="7" t="s">
+        <v>2366</v>
+      </c>
+      <c r="I654" s="6"/>
+    </row>
+    <row r="655" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A655" s="6">
+        <v>21826186</v>
+      </c>
+      <c r="B655" s="6">
+        <v>4</v>
+      </c>
+      <c r="C655" s="22" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D655" s="7" t="s">
+        <v>2357</v>
+      </c>
+      <c r="E655" s="20">
+        <v>3.65</v>
+      </c>
+      <c r="F655" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G655" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H655" s="7" t="s">
+        <v>2367</v>
+      </c>
+      <c r="I655" s="6"/>
+    </row>
+    <row r="656" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A656" s="6">
+        <v>21826186</v>
+      </c>
+      <c r="B656" s="6">
+        <v>5</v>
+      </c>
+      <c r="C656" s="22" t="s">
+        <v>2347</v>
+      </c>
+      <c r="D656" s="7" t="s">
+        <v>2358</v>
+      </c>
+      <c r="E656" s="20">
+        <v>3.76</v>
+      </c>
+      <c r="F656" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G656" s="12">
+        <v>4</v>
+      </c>
+      <c r="H656" s="7" t="s">
+        <v>2368</v>
+      </c>
+      <c r="I656" s="6"/>
+    </row>
+    <row r="657" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A657" s="6">
+        <v>21826186</v>
+      </c>
+      <c r="B657" s="6">
+        <v>6</v>
+      </c>
+      <c r="C657" s="22" t="s">
+        <v>2348</v>
+      </c>
+      <c r="D657" s="7" t="s">
+        <v>2359</v>
+      </c>
+      <c r="E657" s="20">
+        <v>3.46</v>
+      </c>
+      <c r="F657" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G657" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H657" s="7" t="s">
+        <v>2369</v>
+      </c>
+      <c r="I657" s="6"/>
+    </row>
+    <row r="658" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A658" s="6">
+        <v>21826186</v>
+      </c>
+      <c r="B658" s="6">
+        <v>7</v>
+      </c>
+      <c r="C658" s="22" t="s">
+        <v>2349</v>
+      </c>
+      <c r="D658" s="7" t="s">
+        <v>2360</v>
+      </c>
+      <c r="E658" s="20">
+        <v>3.56</v>
+      </c>
+      <c r="F658" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G658" s="12">
+        <v>4</v>
+      </c>
+      <c r="H658" s="7" t="s">
+        <v>2373</v>
+      </c>
+      <c r="I658" s="6"/>
+    </row>
+    <row r="659" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A659" s="6">
+        <v>21826186</v>
+      </c>
+      <c r="B659" s="6">
+        <v>8</v>
+      </c>
+      <c r="C659" s="22" t="s">
+        <v>2350</v>
+      </c>
+      <c r="D659" s="7" t="s">
+        <v>2361</v>
+      </c>
+      <c r="E659" s="20">
+        <v>3.53</v>
+      </c>
+      <c r="F659" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G659" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="H659" s="7" t="s">
+        <v>2370</v>
+      </c>
+      <c r="I659" s="6"/>
+    </row>
+    <row r="660" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A660" s="6">
+        <v>21826186</v>
+      </c>
+      <c r="B660" s="6">
+        <v>9</v>
+      </c>
+      <c r="C660" s="22" t="s">
+        <v>2351</v>
+      </c>
+      <c r="D660" s="7" t="s">
+        <v>2362</v>
+      </c>
+      <c r="E660" s="20">
+        <v>3.68</v>
+      </c>
+      <c r="F660" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G660" s="12">
+        <v>4</v>
+      </c>
+      <c r="H660" s="7" t="s">
+        <v>2372</v>
+      </c>
+      <c r="I660" s="6"/>
+    </row>
+    <row r="661" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A661" s="6">
+        <v>21826186</v>
+      </c>
+      <c r="B661" s="6">
+        <v>10</v>
+      </c>
+      <c r="C661" s="22" t="s">
+        <v>2352</v>
+      </c>
+      <c r="D661" s="7" t="s">
+        <v>2363</v>
+      </c>
+      <c r="E661" s="20">
+        <v>3.22</v>
+      </c>
+      <c r="F661" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G661" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H661" s="7" t="s">
+        <v>2371</v>
+      </c>
+      <c r="I661" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D536D9B-1E00-468B-8557-EDBABFE9E3A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AF463F9-0506-4631-AF75-3B90D17E3806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2592" uniqueCount="2374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2629" uniqueCount="2408">
   <si>
     <t>No</t>
   </si>
@@ -7756,6 +7756,108 @@
   </si>
   <si>
     <t>Μεσαίου tempo, υπόγειο και σκοτεινότερο groove. Η μορφή του “old man” λειτουργεί σαν φωνή εμπειρίας, φθοράς ή προειδοποίησης. Η κιθάρα και το rhythm section κρατούν μια southern-soul/blues ένταση, ενώ η παραγωγή προσθέτει ψυχεδελικές σκιές.</t>
+  </si>
+  <si>
+    <t>More Than A Love Song</t>
+  </si>
+  <si>
+    <t>Ice Cream (Pay Phone)</t>
+  </si>
+  <si>
+    <t>Mrs. Postman</t>
+  </si>
+  <si>
+    <t>Chronicles Of A Diamond</t>
+  </si>
+  <si>
+    <t>Hello</t>
+  </si>
+  <si>
+    <t>Sauvignon</t>
+  </si>
+  <si>
+    <t>Tomorrow</t>
+  </si>
+  <si>
+    <t>Gemini Sun</t>
+  </si>
+  <si>
+    <t>Rock And Roll</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/28699510-Black-Pumas-Chronicles-Of-A-Diamond</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/j4XeE1mEQUcsI1y58oJXQRnnd_8BgxZqTA8mTovANz0/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI4Njk5/NTEwLTE2OTg0MTM2/NzYtODg4MC5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>ATO Records – ATO0854LP, [PIAS] – ATO0854LP, UK &amp; Europe, 2023 (Optimal Media European Pressing)</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** European pressing for UK &amp; Europe featuring the [PIAS] logo. Pressed by Optimal Media GmbH. Runouts are etched. Some copies include an art print in addition to the poster.</t>
+  </si>
+  <si>
+    <t>Psychedelic Soul, Alternative R&amp;B [Art Soul, Funk Rock, Gospel Soul]</t>
+  </si>
+  <si>
+    <t>Psychedelic Soul, Soul Rock [Epic Soul, Gospel Rock, Cinematic R&amp;B]</t>
+  </si>
+  <si>
+    <t>Alternative R&amp;B, Neo-Soul [Minimal Soul, Psychedelic R&amp;B]</t>
+  </si>
+  <si>
+    <t>Soul Rock, Psychedelic Soul [Retro Soul, Funk Rock]</t>
+  </si>
+  <si>
+    <t>Psychedelic Soul, Art Rock [Art Soul, Cinematic Rock]</t>
+  </si>
+  <si>
+    <t>Soul, Gospel Soul [Soul Ballad, Spiritual R&amp;B]</t>
+  </si>
+  <si>
+    <t>Alternative R&amp;B, Psychedelic Soul [Dream Soul, Art Pop]</t>
+  </si>
+  <si>
+    <t>Neo-Soul, Funk [Late-Night Soul, Funk Groove]</t>
+  </si>
+  <si>
+    <t>Psychedelic Soul, Art Rock [Cinematic Soul, Orchestral R&amp;B]</t>
+  </si>
+  <si>
+    <t>Soul Rock, Psychedelic Rock [Guitar Soul, Cosmic Rock]</t>
+  </si>
+  <si>
+    <t>Soul Rock, Funk Rock [Psychedelic Rock, Soul Rock Finale]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Το μεγάλο άνοιγμα του δίσκου. Αρχίζει με ένταση και χώρο, πριν εξελιχθεί σε gospel-soul κορύφωση. Ο τίτλος δηλώνει ότι η αγάπη εδώ δεν είναι απλώς ρομαντική ιστορία αλλά δύναμη υπέρβασης. Η φωνή του Burton έχει δραματικό εύρος, ενώ η παραγωγή συνδυάζει ηλεκτρική κιθάρα, ρυθμική ώθηση και πολυεπίπεδα φωνητικά. Ήταν το lead single και περιγράφει με ακρίβεια τον πιο φιλόδοξο ήχο του δεύτερου album. </t>
+  </si>
+  <si>
+    <t>Μικρότερης κλίμακας και πιο υπαινικτικό. Ο παράξενος συνδυασμός του τίτλου, παγωτό και τηλεφωνικός θάλαμος, δημιουργεί αίσθηση μνήμης, νοσταλγίας ή στιγμιαίας απόδρασης. Η μουσική δεν εκρήγνυται: κρατά χαμηλό, ελαφρώς υπνωτικό R&amp;B groove, πάνω στο οποίο ο Burton λειτουργεί πιο κοντά στον ψίθυρο παρά στη gospel κραυγή.</t>
+  </si>
+  <si>
+    <t>Character song με retro-soul κίνηση και ευκίνητο funk ρυθμό. Η φιγούρα της “Mrs. Postman” συνδέεται με την προσμονή ενός μηνύματος, μιας επιστροφής ή μιας επιβεβαίωσης από κάποιον απόντα. Η μπάντα μετατρέπει αυτό το μικρό, καθημερινό μοτίβο σε ψυχεδελικό soul ταξίδι με κιθάρες και πιο θεατρική φωνητική γραμμή.</t>
+  </si>
+  <si>
+    <t>Το title track είναι περισσότερο ατμόσφαιρα παρά άμεσο single. Οι Black Pumas το χρησιμοποιούν για να εκφράσουν την έννοια της μεταμόρφωσης: πίεση, αλλαγή, επιβίωση και λάμψη. Η παραγωγή δίνει χώρο στις υφές, τα φωνητικά και τα αρμονικά περάσματα, δημιουργώντας art-soul αισθητική που μοιάζει να αιωρείται ανάμεσα σε rock και R&amp;B.</t>
+  </si>
+  <si>
+    <t>Αργή soul gospel μπαλάντα και μία από τις πιο συναισθηματικά άμεσες στιγμές. Η “angel” φιγούρα μπορεί να είναι ερωτικό πρόσωπο, προστάτης ή εσωτερική επιθυμία για σωτηρία. Η φωνή του Burton έχει μεγάλη τρυφερότητα, χωρίς να γίνεται υπερβολική, και η σύνθεση χτίζει σταδιακά μια βαθιά, πνευματική ένταση.</t>
+  </si>
+  <si>
+    <t>Σχεδόν ψυχεδελικό dream-R&amp;B κομμάτι. Το “hello” λειτουργεί ως πρώτη επαφή μετά από απόσταση ή ως απόπειρα να επικοινωνήσεις με κάποιον που ίσως δεν είναι πλέον προσβάσιμος. Τα φωνητικά, οι ηχητικές ουρές και οι αρμονικές ανατροπές δίνουν στο κομμάτι αίσθηση συνομιλίας μέσα από ομίχλη.</t>
+  </si>
+  <si>
+    <t>Late night soul track με σχετικά χαλαρή funk βάση. Ο τίτλος, που παραπέμπει σε κρασί, δημιουργεί ατμόσφαιρα νυχτερινής οικειότητας και ελεγχόμενης μέθης. Η σύνθεση είναι λιγότερο επιβλητική από τα μεγάλα tracks, αλλά προσθέτει στο album απαραίτητη υλικότητα και groove.</t>
+  </si>
+  <si>
+    <t>Από τις πιο κινηματογραφικές και στοχαστικές συνθέσεις. Το “αύριο” δεν παρουσιάζεται ως σίγουρη λύση, αλλά ως ανοιχτή δυνατότητα: κάτι που μπορεί να φέρει αλλαγή, επανόρθωση ή νέα αμφιβολία. Η ενορχήστρωση προχωρά σε κύματα, με την παραγωγή να ενώνει rock, soul και orchestral στοιχεία.</t>
+  </si>
+  <si>
+    <t>Κοσμικό psychedelic soul τραγούδι με κιθαριστικό κέντρο. Η διττή εικόνα του Gemini, δύο όψεις, δύο ταυτότητες, δύο δυνάμεις, ταιριάζει στην εναλλαγή ανάμεσα σε groove και πιο ανοιχτά rock περάσματα. Ο Burton τραγουδά με μεγαλύτερη ένταση, ενώ ο Quesada αφήνει την κιθάρα να προσθέσει χρώμα και κίνηση.</t>
+  </si>
+  <si>
+    <t>Το φινάλε λειτουργεί ως δήλωση καλλιτεχνικής ελευθερίας. Ο τίτλος μπορεί να ακούγεται απλός, όμως οι Black Pumas τον χρησιμοποιούν όχι ως νοσταλγία για το παλιό rock αλλά ως χώρο όπου soul, fuzz κιθάρες, gospel ένταση και ψυχεδελική παραγωγή μπορούν να συνυπάρξουν. Το τραγούδι κλείνει τον δίσκο με αίσθηση συνέχειας, όχι τελικής λύσης.</t>
   </si>
 </sst>
 </file>
@@ -8277,7 +8379,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J71"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -10561,6 +10663,38 @@
       </c>
       <c r="J71" s="11" t="s">
         <v>2341</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+      <c r="A72" s="6">
+        <v>28699510</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>2339</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>2377</v>
+      </c>
+      <c r="D72" s="6">
+        <v>2023</v>
+      </c>
+      <c r="E72" s="10">
+        <v>3.33</v>
+      </c>
+      <c r="F72" s="9" t="s">
+        <v>2387</v>
+      </c>
+      <c r="G72" s="7" t="s">
+        <v>2386</v>
+      </c>
+      <c r="H72" s="6" t="s">
+        <v>2385</v>
+      </c>
+      <c r="I72" s="11" t="s">
+        <v>2383</v>
+      </c>
+      <c r="J72" s="11" t="s">
+        <v>2384</v>
       </c>
     </row>
   </sheetData>
@@ -10703,6 +10837,8 @@
     <hyperlink ref="J70" r:id="rId136" xr:uid="{411646F0-69D3-4EDF-9126-2F65597A7EFA}"/>
     <hyperlink ref="I71" r:id="rId137" xr:uid="{5E8073D0-D198-4EF7-B401-0DAE1D13CFF4}"/>
     <hyperlink ref="J71" r:id="rId138" xr:uid="{2B75F78E-758A-4053-AE75-07DCB5BE6D3E}"/>
+    <hyperlink ref="I72" r:id="rId139" xr:uid="{BD740605-5FB0-4AEE-B015-353A212878C4}"/>
+    <hyperlink ref="J72" r:id="rId140" xr:uid="{C15841C1-57C4-460F-B85E-70AD289D0DB2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10710,7 +10846,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I661"/>
+  <dimension ref="A1:I671"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -28694,6 +28830,276 @@
       </c>
       <c r="I661" s="6"/>
     </row>
+    <row r="662" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A662" s="6">
+        <v>28699510</v>
+      </c>
+      <c r="B662" s="6">
+        <v>1</v>
+      </c>
+      <c r="C662" s="22" t="s">
+        <v>2374</v>
+      </c>
+      <c r="D662" s="7" t="s">
+        <v>2388</v>
+      </c>
+      <c r="E662" s="20">
+        <v>3.83</v>
+      </c>
+      <c r="F662" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G662" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H662" s="7" t="s">
+        <v>2398</v>
+      </c>
+      <c r="I662" s="6"/>
+    </row>
+    <row r="663" spans="1:9" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A663" s="6">
+        <v>28699510</v>
+      </c>
+      <c r="B663" s="6">
+        <v>2</v>
+      </c>
+      <c r="C663" s="22" t="s">
+        <v>2375</v>
+      </c>
+      <c r="D663" s="7" t="s">
+        <v>2389</v>
+      </c>
+      <c r="E663" s="20">
+        <v>3.5</v>
+      </c>
+      <c r="F663" s="12">
+        <v>3.4</v>
+      </c>
+      <c r="G663" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="H663" s="7" t="s">
+        <v>2399</v>
+      </c>
+      <c r="I663" s="6"/>
+    </row>
+    <row r="664" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A664" s="6">
+        <v>28699510</v>
+      </c>
+      <c r="B664" s="6">
+        <v>3</v>
+      </c>
+      <c r="C664" s="22" t="s">
+        <v>2376</v>
+      </c>
+      <c r="D664" s="7" t="s">
+        <v>2390</v>
+      </c>
+      <c r="E664" s="20">
+        <v>3.95</v>
+      </c>
+      <c r="F664" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="G664" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H664" s="7" t="s">
+        <v>2400</v>
+      </c>
+      <c r="I664" s="6"/>
+    </row>
+    <row r="665" spans="1:9" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A665" s="6">
+        <v>28699510</v>
+      </c>
+      <c r="B665" s="6">
+        <v>4</v>
+      </c>
+      <c r="C665" s="22" t="s">
+        <v>2377</v>
+      </c>
+      <c r="D665" s="7" t="s">
+        <v>2391</v>
+      </c>
+      <c r="E665" s="20">
+        <v>3.58</v>
+      </c>
+      <c r="F665" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="G665" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H665" s="7" t="s">
+        <v>2401</v>
+      </c>
+      <c r="I665" s="6"/>
+    </row>
+    <row r="666" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A666" s="6">
+        <v>28699510</v>
+      </c>
+      <c r="B666" s="6">
+        <v>5</v>
+      </c>
+      <c r="C666" s="22" t="s">
+        <v>372</v>
+      </c>
+      <c r="D666" s="7" t="s">
+        <v>2392</v>
+      </c>
+      <c r="E666" s="20">
+        <v>3.63</v>
+      </c>
+      <c r="F666" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G666" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H666" s="7" t="s">
+        <v>2402</v>
+      </c>
+      <c r="I666" s="6"/>
+    </row>
+    <row r="667" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A667" s="6">
+        <v>28699510</v>
+      </c>
+      <c r="B667" s="6">
+        <v>6</v>
+      </c>
+      <c r="C667" s="22" t="s">
+        <v>2378</v>
+      </c>
+      <c r="D667" s="7" t="s">
+        <v>2393</v>
+      </c>
+      <c r="E667" s="20">
+        <v>3.47</v>
+      </c>
+      <c r="F667" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="G667" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="H667" s="7" t="s">
+        <v>2403</v>
+      </c>
+      <c r="I667" s="6"/>
+    </row>
+    <row r="668" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A668" s="6">
+        <v>28699510</v>
+      </c>
+      <c r="B668" s="6">
+        <v>7</v>
+      </c>
+      <c r="C668" s="22" t="s">
+        <v>2379</v>
+      </c>
+      <c r="D668" s="7" t="s">
+        <v>2394</v>
+      </c>
+      <c r="E668" s="20">
+        <v>3.61</v>
+      </c>
+      <c r="F668" s="12">
+        <v>3.4</v>
+      </c>
+      <c r="G668" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="H668" s="7" t="s">
+        <v>2404</v>
+      </c>
+      <c r="I668" s="6"/>
+    </row>
+    <row r="669" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A669" s="6">
+        <v>28699510</v>
+      </c>
+      <c r="B669" s="6">
+        <v>8</v>
+      </c>
+      <c r="C669" s="22" t="s">
+        <v>2380</v>
+      </c>
+      <c r="D669" s="7" t="s">
+        <v>2395</v>
+      </c>
+      <c r="E669" s="20">
+        <v>3.61</v>
+      </c>
+      <c r="F669" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G669" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H669" s="7" t="s">
+        <v>2405</v>
+      </c>
+      <c r="I669" s="6"/>
+    </row>
+    <row r="670" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A670" s="6">
+        <v>28699510</v>
+      </c>
+      <c r="B670" s="6">
+        <v>9</v>
+      </c>
+      <c r="C670" s="22" t="s">
+        <v>2381</v>
+      </c>
+      <c r="D670" s="7" t="s">
+        <v>2396</v>
+      </c>
+      <c r="E670" s="20">
+        <v>3.65</v>
+      </c>
+      <c r="F670" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G670" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H670" s="7" t="s">
+        <v>2406</v>
+      </c>
+      <c r="I670" s="6"/>
+    </row>
+    <row r="671" spans="1:9" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A671" s="6">
+        <v>28699510</v>
+      </c>
+      <c r="B671" s="6">
+        <v>10</v>
+      </c>
+      <c r="C671" s="22" t="s">
+        <v>2382</v>
+      </c>
+      <c r="D671" s="7" t="s">
+        <v>2397</v>
+      </c>
+      <c r="E671" s="20">
+        <v>3.37</v>
+      </c>
+      <c r="F671" s="12">
+        <v>4</v>
+      </c>
+      <c r="G671" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H671" s="7" t="s">
+        <v>2407</v>
+      </c>
+      <c r="I671" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C9F4043-0631-4755-BC8C-B62AAAFAFBDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C6AAC74-C2C0-4D52-B83A-87666C17328F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2629" uniqueCount="2408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2668" uniqueCount="2444">
   <si>
     <t>No</t>
   </si>
@@ -7858,6 +7858,144 @@
   </si>
   <si>
     <t>Rocksteady, Roots Reggae [Reprise, Dubby Outro, Rocksteady Coda]</t>
+  </si>
+  <si>
+    <t>The Dave Brubeck Quartet</t>
+  </si>
+  <si>
+    <t>Time Out</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/11898961-The-Dave-Brubeck-Quartet-Time-Out</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/AR9luXU_tvIB7if2YyfwlAKOuodu1PuIMMEi66_Gwb8/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTExODk4/OTYxLTE1MjQzNTUx/NTMtNjgzMS5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Blue Rondo A La Turk</t>
+  </si>
+  <si>
+    <t>Strange Meadow Lark</t>
+  </si>
+  <si>
+    <t>Take Five</t>
+  </si>
+  <si>
+    <t>Three To Get Ready</t>
+  </si>
+  <si>
+    <t>Kathy's Waltz</t>
+  </si>
+  <si>
+    <t>Everybody's Jumpin'</t>
+  </si>
+  <si>
+    <t>Pick Up Sticks</t>
+  </si>
+  <si>
+    <t>Audrey</t>
+  </si>
+  <si>
+    <t>WaxTime In Color – 950624, Europe, 2018 (Limited Edition, Reissue, Stereo, Orange 180 Gram DMM pressing)</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** European 180g orange vinyl limited reissue. DMM (Direct Metal Mastering) using the original George Neumann Cutting System. Pressed by GZ Media (85196E). Includes bonus track B5 (Audrey, recorded October 12, 1954). Runouts are stamped.</t>
+  </si>
+  <si>
+    <t>5.0</t>
+  </si>
+  <si>
+    <t>4.7</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>4.4</t>
+  </si>
+  <si>
+    <t>4.6</t>
+  </si>
+  <si>
+    <t>Το εναρκτήριο κομμάτι παρουσιάζει αμέσως την ιδέα του album. Το βασικό σχήμα 9/89/89/8 χωρίζεται σε 2+2+2+32+2+2+32+2+2+3, δημιουργώντας χαρακτηριστική, κοφτή ώθηση, πριν η μπάντα μεταβεί σε περισσότερο bluesy 4/4 swing. Η εναλλαγή ανάμεσα στην ασύμμετρη ρυθμική φιγούρα και στο πιο οικείο swing είναι η ουσία της σύνθεσης, γεφυρώνει έναν ρυθμό που ο Brubeck συνέδεσε με τουρκική μουσική με την αμερικανική jazz γλώσσα.</t>
+  </si>
+  <si>
+    <t>Μετά την ένταση του πρώτου κομματιού, το quartet κατεβάζει τους τόνους. Η σύνθεση είναι λυρική και ανοιχτή, με πιάνο και alto sax να επικοινωνούν μέσα από αργές μελωδικές γραμμές. Ο τίτλος φέρνει εικόνα φυσικού τοπίου και η μουσική λειτουργεί αντίστοιχα: δεν βιάζεται, αφήνει αρμονικό χώρο και δείχνει τη λεπτότερη, ballad πλευρά του Brubeck.</t>
+  </si>
+  <si>
+    <t>Το πιο αναγνωρίσιμο 5/45/45/4 κομμάτι στην ιστορία της jazz. Ο Desmond έγραψε τη βασική μελωδία και το alto sax του είναι το κέντρο της σύνθεσης, ενώ ο Morello δίνει στο 5/45/45/4 μια αίσθηση φυσικής κυκλοφορίας αντί για μαθηματικό περιορισμό. Το piano vamp, το drum solo και η τελική επιστροφή της μελωδίας σχηματίζουν σχεδόν τέλεια compact δομή. Η εμπορική επιτυχία του αποδεικνύει πως ένα odd-meter jazz track μπορεί να έχει και άμεση pop μνήμη.</t>
+  </si>
+  <si>
+    <t>Το πιο κομψό ρυθμικό πείραμα του album. Η σύνθεση εναλλάσσει δύο μέτρα σε 3/43/43/4 με δύο σε 2/42/42/4, άρα η αίσθηση αλλάζει διαρκώς ανάμεσα σε jazz waltz και πιο συνηθισμένο pulse. Η μπάντα το κάνει να ακούγεται ανεπιτήδευτο, δεν “τονίζει” το τέχνασμα, αλλά το χρησιμοποιεί για να κρατά τον αυτοσχεδιασμό ζωντανό.</t>
+  </si>
+  <si>
+    <t>Πιο ανάλαφρο και γλυκό, αλλά όχι ασήμαντο. Η φόρμα του waltz δίνει στον Brubeck χώρο να αναπτύξει πιο παιγνιώδεις πιανιστικές κινήσεις, ενώ ο Desmond φέρνει τη χαρακτηριστική αβίαστη μελωδικότητα. Λειτουργεί ως ανθρώπινη, ζεστή ανάσα ανάμεσα στα πιο απαιτητικά rhythm experiments.</t>
+  </si>
+  <si>
+    <t>Up-tempo ensemble κομμάτι που τονίζει το swing της μπάντας. Δεν στηρίζεται τόσο σε ένα διάσημο odd-meter concept όσο άλλα tracks, αλλά δείχνει γιατί η τετράδα μπορεί να κρατήσει την πειραματική της λογική χωρίς να χάνει την αίσθηση χαράς ή αυθορμητισμού. Το μπάσο του Wright και τα drums του Morello είναι ιδιαίτερα σημαντικά στην προώθηση του κομματιού.</t>
+  </si>
+  <si>
+    <t>Το κλείσιμο της original έκδοσης. Η σύνθεση βασίζεται σε 6/46/46/4 και δίνει μεγαλύτερη έμφαση στον ρυθμικό διάλογο Wright–Morello. Η κινούμενη bass figure, οι πιανιστικές συγχορδίες και το σαξόφωνο του Desmond χτίζουν ένα κομμάτι που είναι ταυτόχρονα ελεγχόμενο και παιχνιδιάρικο. Αφήνει τον δίσκο να κλείσει με κίνηση και όχι με ballad τελεία.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve">Δεν ανήκει στο αρχικό </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Time Out</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> του 1959. Στη δική σου WaxTime edition εμφανίζεται ως bonus track στη B5. Είναι χρήσιμο ως επιπλέον Brubeck material, αλλά δεν πρέπει να αξιολογείται ως μέρος της αρχικής επτά-track δραματουργίας του album. Η παρουσία του μετατρέπει τη δεύτερη πλευρά από το καθαρό closing arc του “Pick Up Sticks” σε expanded/reissue programme.</t>
+    </r>
+  </si>
+  <si>
+    <t>Cool Jazz, Post-Bop [Odd-Meter Jazz, Turkish-Influenced Rhythm, Modern Jazz Quartet]</t>
+  </si>
+  <si>
+    <t>Cool Jazz, Jazz Ballad [Lyrical Jazz, Piano Ballad, Chamber Jazz]</t>
+  </si>
+  <si>
+    <t>Cool Jazz, Jazz [5/4 Jazz, Alto Sax Feature, Jazz Standard]</t>
+  </si>
+  <si>
+    <t>Cool Jazz, Post-Bop [Alternating 3/4–2/4 Jazz, Piano Quartet, Odd-Meter Swing]</t>
+  </si>
+  <si>
+    <t>Cool Jazz, Jazz Waltz [Lyrical Jazz Waltz, Modern Jazz, Piano-Sax Dialogue]</t>
+  </si>
+  <si>
+    <t>Cool Jazz, Swing [Up-tempo Modern Jazz, Swinging Quartet, Sax-Piano Feature]</t>
+  </si>
+  <si>
+    <t>Cool Jazz, Post-Bop [6/4 Jazz, Bass-Drum Groove, Modern Jazz]</t>
+  </si>
+  <si>
+    <t>Cool Jazz, Jazz Ballad [Lyrical Jazz, Film-Theme Ballad, Alto Sax Feature]</t>
+  </si>
+  <si>
+    <t>Cool Jazz, West Coast Jazz [Odd-Meter Jazz, Post-Bop, Chamber Jazz]</t>
   </si>
 </sst>
 </file>
@@ -8384,7 +8522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -10700,6 +10838,38 @@
       </c>
       <c r="J72" s="11" t="s">
         <v>2361</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+      <c r="A73" s="6">
+        <v>11898961</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>2408</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>2409</v>
+      </c>
+      <c r="D73" s="6">
+        <v>1959</v>
+      </c>
+      <c r="E73" s="10">
+        <v>3.94</v>
+      </c>
+      <c r="F73" s="9" t="s">
+        <v>2443</v>
+      </c>
+      <c r="G73" s="7" t="s">
+        <v>2421</v>
+      </c>
+      <c r="H73" s="6" t="s">
+        <v>2420</v>
+      </c>
+      <c r="I73" s="11" t="s">
+        <v>2410</v>
+      </c>
+      <c r="J73" s="11" t="s">
+        <v>2411</v>
       </c>
     </row>
   </sheetData>
@@ -10844,6 +11014,8 @@
     <hyperlink ref="J71" r:id="rId138" xr:uid="{2B75F78E-758A-4053-AE75-07DCB5BE6D3E}"/>
     <hyperlink ref="I72" r:id="rId139" xr:uid="{BD740605-5FB0-4AEE-B015-353A212878C4}"/>
     <hyperlink ref="J72" r:id="rId140" xr:uid="{C15841C1-57C4-460F-B85E-70AD289D0DB2}"/>
+    <hyperlink ref="I73" r:id="rId141" xr:uid="{00289898-76D1-487C-BD85-6F5E4366363B}"/>
+    <hyperlink ref="J73" r:id="rId142" xr:uid="{15FF9A37-B212-4ED6-A513-C5B683682229}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10851,7 +11023,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I671"/>
+  <dimension ref="A1:I679"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -29105,6 +29277,224 @@
       </c>
       <c r="I671" s="6"/>
     </row>
+    <row r="672" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A672" s="6">
+        <v>11898961</v>
+      </c>
+      <c r="B672" s="6">
+        <v>1</v>
+      </c>
+      <c r="C672" s="22" t="s">
+        <v>2412</v>
+      </c>
+      <c r="D672" s="7" t="s">
+        <v>2435</v>
+      </c>
+      <c r="E672" s="20">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="F672" s="12" t="s">
+        <v>2422</v>
+      </c>
+      <c r="G672" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H672" s="7" t="s">
+        <v>2427</v>
+      </c>
+      <c r="I672" s="6"/>
+    </row>
+    <row r="673" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A673" s="6">
+        <v>11898961</v>
+      </c>
+      <c r="B673" s="6">
+        <v>2</v>
+      </c>
+      <c r="C673" s="22" t="s">
+        <v>2413</v>
+      </c>
+      <c r="D673" s="7" t="s">
+        <v>2436</v>
+      </c>
+      <c r="E673" s="20">
+        <v>4.01</v>
+      </c>
+      <c r="F673" s="12" t="s">
+        <v>2423</v>
+      </c>
+      <c r="G673" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H673" s="7" t="s">
+        <v>2428</v>
+      </c>
+      <c r="I673" s="6"/>
+    </row>
+    <row r="674" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A674" s="6">
+        <v>11898961</v>
+      </c>
+      <c r="B674" s="6">
+        <v>3</v>
+      </c>
+      <c r="C674" s="22" t="s">
+        <v>2414</v>
+      </c>
+      <c r="D674" s="7" t="s">
+        <v>2437</v>
+      </c>
+      <c r="E674" s="20">
+        <v>4.59</v>
+      </c>
+      <c r="F674" s="12" t="s">
+        <v>2422</v>
+      </c>
+      <c r="G674" s="12">
+        <v>5</v>
+      </c>
+      <c r="H674" s="7" t="s">
+        <v>2429</v>
+      </c>
+      <c r="I674" s="6" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="675" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A675" s="6">
+        <v>11898961</v>
+      </c>
+      <c r="B675" s="6">
+        <v>4</v>
+      </c>
+      <c r="C675" s="22" t="s">
+        <v>2415</v>
+      </c>
+      <c r="D675" s="7" t="s">
+        <v>2438</v>
+      </c>
+      <c r="E675" s="20">
+        <v>3.89</v>
+      </c>
+      <c r="F675" s="12" t="s">
+        <v>2423</v>
+      </c>
+      <c r="G675" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H675" s="7" t="s">
+        <v>2430</v>
+      </c>
+      <c r="I675" s="6"/>
+    </row>
+    <row r="676" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A676" s="6">
+        <v>11898961</v>
+      </c>
+      <c r="B676" s="6">
+        <v>5</v>
+      </c>
+      <c r="C676" s="22" t="s">
+        <v>2416</v>
+      </c>
+      <c r="D676" s="7" t="s">
+        <v>2439</v>
+      </c>
+      <c r="E676" s="20">
+        <v>3.84</v>
+      </c>
+      <c r="F676" s="12" t="s">
+        <v>2424</v>
+      </c>
+      <c r="G676" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H676" s="7" t="s">
+        <v>2431</v>
+      </c>
+      <c r="I676" s="6"/>
+    </row>
+    <row r="677" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A677" s="6">
+        <v>11898961</v>
+      </c>
+      <c r="B677" s="6">
+        <v>6</v>
+      </c>
+      <c r="C677" s="22" t="s">
+        <v>2417</v>
+      </c>
+      <c r="D677" s="7" t="s">
+        <v>2440</v>
+      </c>
+      <c r="E677" s="20">
+        <v>3.79</v>
+      </c>
+      <c r="F677" s="12" t="s">
+        <v>2425</v>
+      </c>
+      <c r="G677" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H677" s="7" t="s">
+        <v>2432</v>
+      </c>
+      <c r="I677" s="6"/>
+    </row>
+    <row r="678" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A678" s="6">
+        <v>11898961</v>
+      </c>
+      <c r="B678" s="6">
+        <v>7</v>
+      </c>
+      <c r="C678" s="22" t="s">
+        <v>2418</v>
+      </c>
+      <c r="D678" s="7" t="s">
+        <v>2441</v>
+      </c>
+      <c r="E678" s="20">
+        <v>3.72</v>
+      </c>
+      <c r="F678" s="12" t="s">
+        <v>2426</v>
+      </c>
+      <c r="G678" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H678" s="7" t="s">
+        <v>2433</v>
+      </c>
+      <c r="I678" s="6"/>
+    </row>
+    <row r="679" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A679" s="6">
+        <v>11898961</v>
+      </c>
+      <c r="B679" s="6">
+        <v>8</v>
+      </c>
+      <c r="C679" s="22" t="s">
+        <v>2419</v>
+      </c>
+      <c r="D679" s="7" t="s">
+        <v>2442</v>
+      </c>
+      <c r="E679" s="20">
+        <v>3.75</v>
+      </c>
+      <c r="F679" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G679" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H679" s="7" t="s">
+        <v>2434</v>
+      </c>
+      <c r="I679" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5D52D19-F2CC-4384-9298-0A7497F711DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9C48E6C-60C2-4123-B649-8A304492DBB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2667" uniqueCount="2452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2704" uniqueCount="2489">
   <si>
     <t>No</t>
   </si>
@@ -8020,6 +8020,147 @@
   </si>
   <si>
     <t>Heavy Metal, Doom Metal [Proto-Stoner, Doom Metal, Heavy Riff Rock]</t>
+  </si>
+  <si>
+    <t>Dissonance Theory</t>
+  </si>
+  <si>
+    <t>Coroner</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/35389759-Coroner-Dissonance-Theory</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/TUaHqbj3ngG4sQa6xU7Vzwc-UI-wZSYXVr2_Wqlk-mI/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTM1Mzg5/NzU5LTE3NjA2Mjg1/MDctMzQyMy5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Oxymoron</t>
+  </si>
+  <si>
+    <t>Consequence</t>
+  </si>
+  <si>
+    <t>Sacrificial Lamb</t>
+  </si>
+  <si>
+    <t>Crisium Bound</t>
+  </si>
+  <si>
+    <t>Symmetry</t>
+  </si>
+  <si>
+    <t>The Law</t>
+  </si>
+  <si>
+    <t>Transparent Eye</t>
+  </si>
+  <si>
+    <t>Trinity</t>
+  </si>
+  <si>
+    <t>Renewal</t>
+  </si>
+  <si>
+    <t>Prolonging</t>
+  </si>
+  <si>
+    <t>Σύντομο instrumental εισαγωγικό κομμάτι, σχεδόν ενός λεπτού. Δεν λειτουργεί ως κανονικό τραγούδι, αλλά ως sound-design πύλη, δημιουργεί ένταση και προσδοκία πριν μπει η πλήρης μπάντα. Η 3.5/5 βαθμολογία αφορά τη λειτουργικότητά του ως intro, όχι σύγκριση με ολοκληρωμένες συνθέσεις.</t>
+  </si>
+  <si>
+    <t>Πιο επιθετικό και riff-centered, αλλά όχι απλοϊκό. Ο τίτλος δημιουργεί εικόνα θυσίας ή χειραγώγησης, και η μουσική χτίζει αίσθηση πίεσης μέσα από τεμαχισμένα rhythms και ψυχρή, πειθαρχημένη κιθάρα. Η σύνθεση πατά σε κλασική Coroner ακρίβεια, αλλά η παραγωγή της δίνει σύγχρονο low-end βάρος.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve">Το “Crisium” είναι σκόπιμα παράξενος τίτλος και ταιριάζει στη dissonant λογική του κομματιού. Η σύνθεση χτίζεται με μετατοπιζόμενα riffs και groove που ποτέ δεν σταθεροποιείται για πολύ. Είναι από τα tracks όπου φαίνεται καθαρότερα η σύνδεση με το μεταγενέστερο, πιο πειραματικό </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Grin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> ύφος, περισσότερο ψυχολογική αστάθεια και λιγότερο καθαρό thrash momentum.</t>
+    </r>
+  </si>
+  <si>
+    <t>Από τα πιο γρήγορα και άμεσα σημεία του δίσκου, με speed-driven riffing και αποφασιστική δομή. Η “συμμετρία” του τίτλου ακούγεται ειρωνική, αφού οι Coroner ενσωματώνουν μικρές ρυθμικές μετατοπίσεις και ασύμμετρα accents. Είναι track που ικανοποιεί τους ακροατές του παλαιότερου technical thrash χωρίς να απλουστεύει τη νέα κατεύθυνση.</t>
+  </si>
+  <si>
+    <t>Από τις πιο φιλόδοξες και δομικά μεταβαλλόμενες συνθέσεις. Οι κριτικές το ξεχωρίζουν ως ένα από τα πιο σύνθετα και “structurally wavering” κομμάτια, δηλαδή δεν κρατά απλώς ένα riff αλλά αλλάζει συνεχώς ισορροπία, ρυθμικό κέντρο και ατμόσφαιρα. Η 4.2/5 βαθμολογία αποδίδει την τεχνική του δύναμη, με μικρή επιφύλαξη για την απαιτητική, λιγότερο άμεση μορφή του.</t>
+  </si>
+  <si>
+    <t>Mid-tempo, ψυχρό και υποβλητικό. Αντί να βασιστεί στην ταχύτητα, το track δημιουργεί βάρος με dissonant intervals και controlled groove. Η “διαφάνεια” του τίτλου λειτουργεί αντιστικτικά, η μουσική δεν δίνει άμεση καθαρότητα, αλλά αφήνει τον ακροατή να ψάχνει μέσα σε στρώσεις κιθάρας, μπάσου και drums.</t>
+  </si>
+  <si>
+    <t>Ένα από τα πιο ατμοσφαιρικά tracks, με διάθεση που ενώνει heavy riffing και πιο ανοιχτές, προοδευτικές μεταβάσεις. Ο τίτλος επιτρέπει πολλές αναγνώσεις —τριμερής δομή, τρεις δυνάμεις, ή τριάδα μελών, αλλά δεν υπάρχει τεκμηριωμένη lyric-by-lyric εξήγηση. Καλύτερα να το ακούμε ως μουσική κλιμάκωση, όχι να του αποδίδουμε βέβαιο στιχουργικό νόημα.</t>
+  </si>
+  <si>
+    <t>Η δεύτερη καθαρή speed-thrash κορυφή μαζί με το “Symmetry”. Παίζει με ανανεωμένη ενέργεια, διατηρώντας την ακρίβεια των παλιών Coroner χωρίς να ακούγεται σαν αναπαράσταση της δεκαετίας του ’80. Οι κριτικές του OndaRock αναφέρουν ρητά τα “Symmetry” και “Renewal” ως τα πιο speed-driven σημεία του δίσκου.</t>
+  </si>
+  <si>
+    <t>Τρίλεπτο instrumental outro που κλείνει χωρίς θριαμβευτικό “τελικό riff”. Η επιλογή του ονόματος ταιριάζει, αντί να ολοκληρώνει καθαρά την ένταση, την παρατείνει. Οι ενορχηστρωτικές/sound-effect πινελιές της Skal δίνουν κινηματογραφική, σχεδόν ανήσυχη αίσθηση, αφήνοντας το album να εξατμιστεί μέσα σε ατμόσφαιρα.</t>
+  </si>
+  <si>
+    <t>Η πρώτη ολοκληρωμένη δήλωση του δίσκου. Οι κιθάρες του Vetterli κινούνται με κοφτές, γωνιώδεις φράσεις, ενώ το rhythm section αποφεύγει το ευθύ thrash sprint. Η δύναμή του είναι ότι συνδυάζει technical detail με πραγματικό βάρος, δεν ακούγεται σαν επίδειξη, αλλά σαν διαρκής κίνηση προς αναπόφευκτη συνέπεια.</t>
+  </si>
+  <si>
+    <t>Century Media – 19802944511, Europe, 2025 (LP, Album, 180g Black Vinyl)</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** LP on 180g black vinyl, made in the EU. Pressed by Optimal Media GmbH (BP43030). Runouts are etched. Issued with a double-sided printed insert with lyrics, band image, and thanks list. Some early copies came with 3 stickers and a postcard.</t>
+  </si>
+  <si>
+    <t>Technical Thrash Metal, Progressive Metal [Progressive Thrash, Dissonant Thrash, Avant-Garde Metal]</t>
+  </si>
+  <si>
+    <t>Progressive Metal, Ambient Metal [Instrumental Intro, Dissonant Sound Design, Suspense]</t>
+  </si>
+  <si>
+    <t>Technical Thrash Metal, Progressive Metal [Dissonant Thrash, Technical Groove, Dark Progressive Metal]</t>
+  </si>
+  <si>
+    <t>Technical Thrash Metal, Thrash Metal [Precision Thrash, Progressive Riff Metal, Dark Metal]</t>
+  </si>
+  <si>
+    <t>Progressive Metal, Technical Thrash Metal [Dissonant Progressive Metal, Angular Riffs, Heavy Groove]</t>
+  </si>
+  <si>
+    <t>Thrash Metal, Technical Thrash Metal [Speed Thrash, Precision Riffing, Classic Coroner Drive]</t>
+  </si>
+  <si>
+    <t>Progressive Metal, Technical Thrash Metal [Progressive Thrash, Structural Metal, Dissonant Heavy Metal]</t>
+  </si>
+  <si>
+    <t>Technical Thrash Metal, Progressive Metal [Mid-Tempo Dissonant Metal, Technical Groove, Dark Thrash]</t>
+  </si>
+  <si>
+    <t>Progressive Metal, Technical Thrash Metal [Atmospheric Thrash, Progressive Heavy Metal, Dynamic Metal]</t>
+  </si>
+  <si>
+    <t>Thrash Metal, Technical Thrash Metal [Speed-Driven Thrash, Progressive Riff Metal, Aggressive Metal]</t>
+  </si>
+  <si>
+    <t>Progressive Metal, Ambient Metal [Instrumental Outro, Atmospheric Dissonance, Cinematic Metal]</t>
   </si>
 </sst>
 </file>
@@ -8546,7 +8687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:M74"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -10608,7 +10749,7 @@
         <v>2055</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" ht="42" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
         <v>32916789</v>
       </c>
@@ -10640,7 +10781,7 @@
         <v>2089</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
         <v>15960193</v>
       </c>
@@ -10672,7 +10813,7 @@
         <v>2111</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>28423156</v>
       </c>
@@ -10704,7 +10845,7 @@
         <v>2157</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" ht="42" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
         <v>25766467</v>
       </c>
@@ -10736,7 +10877,7 @@
         <v>2202</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" ht="42" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
         <v>18001219</v>
       </c>
@@ -10768,7 +10909,7 @@
         <v>2226</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
         <v>15223559</v>
       </c>
@@ -10800,7 +10941,7 @@
         <v>2254</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" ht="42" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
         <v>21826186</v>
       </c>
@@ -10832,7 +10973,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" ht="42" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
         <v>28699510</v>
       </c>
@@ -10864,7 +11005,7 @@
         <v>2330</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" ht="42" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
         <v>11898961</v>
       </c>
@@ -10895,6 +11036,41 @@
       <c r="J73" s="11" t="s">
         <v>2380</v>
       </c>
+    </row>
+    <row r="74" spans="1:13" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A74" s="6">
+        <v>35389759</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>2453</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>2452</v>
+      </c>
+      <c r="D74" s="6">
+        <v>2025</v>
+      </c>
+      <c r="E74" s="10">
+        <v>3.74</v>
+      </c>
+      <c r="F74" s="9" t="s">
+        <v>2478</v>
+      </c>
+      <c r="G74" s="7" t="s">
+        <v>2477</v>
+      </c>
+      <c r="H74" s="6" t="s">
+        <v>2476</v>
+      </c>
+      <c r="I74" s="11" t="s">
+        <v>2454</v>
+      </c>
+      <c r="J74" s="11" t="s">
+        <v>2455</v>
+      </c>
+      <c r="K74" s="6"/>
+      <c r="L74" s="11"/>
+      <c r="M74" s="11"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -11040,6 +11216,8 @@
     <hyperlink ref="J72" r:id="rId140" xr:uid="{C15841C1-57C4-460F-B85E-70AD289D0DB2}"/>
     <hyperlink ref="I73" r:id="rId141" xr:uid="{00289898-76D1-487C-BD85-6F5E4366363B}"/>
     <hyperlink ref="J73" r:id="rId142" xr:uid="{15FF9A37-B212-4ED6-A513-C5B683682229}"/>
+    <hyperlink ref="I74" r:id="rId143" xr:uid="{26A09476-022E-49A1-8D96-8F51CBE08EDA}"/>
+    <hyperlink ref="J74" r:id="rId144" xr:uid="{89FDA199-13C2-4B65-9BBF-977C7BB3C8EA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11047,7 +11225,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I679"/>
+  <dimension ref="A1:I689"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -29519,6 +29697,276 @@
       </c>
       <c r="I679" s="6"/>
     </row>
+    <row r="680" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A680" s="6">
+        <v>35389759</v>
+      </c>
+      <c r="B680" s="6">
+        <v>1</v>
+      </c>
+      <c r="C680" s="22" t="s">
+        <v>2456</v>
+      </c>
+      <c r="D680" s="7" t="s">
+        <v>2479</v>
+      </c>
+      <c r="E680" s="20">
+        <v>3.06</v>
+      </c>
+      <c r="F680" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="G680" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H680" s="7" t="s">
+        <v>2466</v>
+      </c>
+      <c r="I680" s="6"/>
+    </row>
+    <row r="681" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A681" s="6">
+        <v>35389759</v>
+      </c>
+      <c r="B681" s="6">
+        <v>2</v>
+      </c>
+      <c r="C681" s="22" t="s">
+        <v>2457</v>
+      </c>
+      <c r="D681" s="7" t="s">
+        <v>2480</v>
+      </c>
+      <c r="E681" s="20">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="F681" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G681" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H681" s="7" t="s">
+        <v>2475</v>
+      </c>
+      <c r="I681" s="6"/>
+    </row>
+    <row r="682" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A682" s="6">
+        <v>35389759</v>
+      </c>
+      <c r="B682" s="6">
+        <v>3</v>
+      </c>
+      <c r="C682" s="22" t="s">
+        <v>2458</v>
+      </c>
+      <c r="D682" s="7" t="s">
+        <v>2481</v>
+      </c>
+      <c r="E682" s="20">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="F682" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G682" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H682" s="7" t="s">
+        <v>2467</v>
+      </c>
+      <c r="I682" s="6"/>
+    </row>
+    <row r="683" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A683" s="6">
+        <v>35389759</v>
+      </c>
+      <c r="B683" s="6">
+        <v>4</v>
+      </c>
+      <c r="C683" s="22" t="s">
+        <v>2459</v>
+      </c>
+      <c r="D683" s="7" t="s">
+        <v>2482</v>
+      </c>
+      <c r="E683" s="20">
+        <v>3.94</v>
+      </c>
+      <c r="F683" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G683" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H683" s="7" t="s">
+        <v>2468</v>
+      </c>
+      <c r="I683" s="6"/>
+    </row>
+    <row r="684" spans="1:9" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A684" s="6">
+        <v>35389759</v>
+      </c>
+      <c r="B684" s="6">
+        <v>5</v>
+      </c>
+      <c r="C684" s="22" t="s">
+        <v>2460</v>
+      </c>
+      <c r="D684" s="7" t="s">
+        <v>2483</v>
+      </c>
+      <c r="E684" s="20">
+        <v>4.09</v>
+      </c>
+      <c r="F684" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G684" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="H684" s="7" t="s">
+        <v>2469</v>
+      </c>
+      <c r="I684" s="6"/>
+    </row>
+    <row r="685" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A685" s="6">
+        <v>35389759</v>
+      </c>
+      <c r="B685" s="6">
+        <v>6</v>
+      </c>
+      <c r="C685" s="22" t="s">
+        <v>2461</v>
+      </c>
+      <c r="D685" s="7" t="s">
+        <v>2484</v>
+      </c>
+      <c r="E685" s="20">
+        <v>4.04</v>
+      </c>
+      <c r="F685" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G685" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H685" s="7" t="s">
+        <v>2470</v>
+      </c>
+      <c r="I685" s="6"/>
+    </row>
+    <row r="686" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A686" s="6">
+        <v>35389759</v>
+      </c>
+      <c r="B686" s="6">
+        <v>7</v>
+      </c>
+      <c r="C686" s="22" t="s">
+        <v>2462</v>
+      </c>
+      <c r="D686" s="7" t="s">
+        <v>2485</v>
+      </c>
+      <c r="E686" s="20">
+        <v>3.98</v>
+      </c>
+      <c r="F686" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G686" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H686" s="7" t="s">
+        <v>2471</v>
+      </c>
+      <c r="I686" s="6"/>
+    </row>
+    <row r="687" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A687" s="6">
+        <v>35389759</v>
+      </c>
+      <c r="B687" s="6">
+        <v>8</v>
+      </c>
+      <c r="C687" s="22" t="s">
+        <v>2463</v>
+      </c>
+      <c r="D687" s="7" t="s">
+        <v>2486</v>
+      </c>
+      <c r="E687" s="20">
+        <v>3.94</v>
+      </c>
+      <c r="F687" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G687" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H687" s="7" t="s">
+        <v>2472</v>
+      </c>
+      <c r="I687" s="6"/>
+    </row>
+    <row r="688" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A688" s="6">
+        <v>35389759</v>
+      </c>
+      <c r="B688" s="6">
+        <v>9</v>
+      </c>
+      <c r="C688" s="22" t="s">
+        <v>2464</v>
+      </c>
+      <c r="D688" s="7" t="s">
+        <v>2487</v>
+      </c>
+      <c r="E688" s="20">
+        <v>4.12</v>
+      </c>
+      <c r="F688" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G688" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H688" s="7" t="s">
+        <v>2473</v>
+      </c>
+      <c r="I688" s="6"/>
+    </row>
+    <row r="689" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A689" s="6">
+        <v>35389759</v>
+      </c>
+      <c r="B689" s="6">
+        <v>10</v>
+      </c>
+      <c r="C689" s="22" t="s">
+        <v>2465</v>
+      </c>
+      <c r="D689" s="7" t="s">
+        <v>2488</v>
+      </c>
+      <c r="E689" s="20">
+        <v>3.72</v>
+      </c>
+      <c r="F689" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G689" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H689" s="7" t="s">
+        <v>2474</v>
+      </c>
+      <c r="I689" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
